--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AC$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AM$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC191"/>
+  <dimension ref="A1:AM191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -469,12 +469,22 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
+    <col width="26" customWidth="1" min="35" max="35"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="38" max="38"/>
+    <col width="26" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,32 +605,82 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>T-level (computed floor)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>T-level target (suggested)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Class (attested-static / unauthored / authored-ok)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Historical actions summary (owner/consult)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Historical casualties (killed/wounded/missing, source)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Proposed changes (keyframes/events to author)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Priority (1-3)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>EC1 identity/command</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>EC2 engaged strength</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>EC3 position anchors</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>EC4 movement legs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>EC5 activity record</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>EC6 casualty apportionment</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Target T-level</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Achieved T-level (audited)</t>
         </is>
       </c>
     </row>
@@ -713,12 +773,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
+      <c r="AD2" s="4" t="n"/>
+      <c r="AE2" s="4" t="n"/>
+      <c r="AF2" s="4" t="n"/>
+      <c r="AG2" s="4" t="n"/>
+      <c r="AH2" s="4" t="n"/>
+      <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="4" t="n"/>
+      <c r="AL2" s="4" t="n"/>
+      <c r="AM2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -809,12 +887,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
+      <c r="AD3" s="4" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+      <c r="AF3" s="4" t="n"/>
+      <c r="AG3" s="4" t="n"/>
+      <c r="AH3" s="4" t="n"/>
+      <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -905,12 +1001,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z4" s="4" t="n"/>
       <c r="AA4" s="4" t="n"/>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
+      <c r="AD4" s="4" t="n"/>
+      <c r="AE4" s="4" t="n"/>
+      <c r="AF4" s="4" t="n"/>
+      <c r="AG4" s="4" t="n"/>
+      <c r="AH4" s="4" t="n"/>
+      <c r="AI4" s="4" t="n"/>
+      <c r="AJ4" s="4" t="n"/>
+      <c r="AK4" s="4" t="n"/>
+      <c r="AL4" s="4" t="n"/>
+      <c r="AM4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1001,12 +1115,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+      <c r="AF5" s="4" t="n"/>
+      <c r="AG5" s="4" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n"/>
+      <c r="AL5" s="4" t="n"/>
+      <c r="AM5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1097,12 +1229,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
+      <c r="AD6" s="4" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+      <c r="AF6" s="4" t="n"/>
+      <c r="AG6" s="4" t="n"/>
+      <c r="AH6" s="4" t="n"/>
+      <c r="AI6" s="4" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4" t="n"/>
+      <c r="AL6" s="4" t="n"/>
+      <c r="AM6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1193,12 +1343,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="n"/>
+      <c r="AF7" s="4" t="n"/>
+      <c r="AG7" s="4" t="n"/>
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4" t="n"/>
+      <c r="AL7" s="4" t="n"/>
+      <c r="AM7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1289,12 +1457,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
       <c r="AC8" s="4" t="n"/>
+      <c r="AD8" s="4" t="n"/>
+      <c r="AE8" s="4" t="n"/>
+      <c r="AF8" s="4" t="n"/>
+      <c r="AG8" s="4" t="n"/>
+      <c r="AH8" s="4" t="n"/>
+      <c r="AI8" s="4" t="n"/>
+      <c r="AJ8" s="4" t="n"/>
+      <c r="AK8" s="4" t="n"/>
+      <c r="AL8" s="4" t="n"/>
+      <c r="AM8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1385,12 +1571,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
+      <c r="AD9" s="4" t="n"/>
+      <c r="AE9" s="4" t="n"/>
+      <c r="AF9" s="4" t="n"/>
+      <c r="AG9" s="4" t="n"/>
+      <c r="AH9" s="4" t="n"/>
+      <c r="AI9" s="4" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4" t="n"/>
+      <c r="AL9" s="4" t="n"/>
+      <c r="AM9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1481,12 +1685,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z10" s="4" t="n"/>
       <c r="AA10" s="4" t="n"/>
       <c r="AB10" s="4" t="n"/>
       <c r="AC10" s="4" t="n"/>
+      <c r="AD10" s="4" t="n"/>
+      <c r="AE10" s="4" t="n"/>
+      <c r="AF10" s="4" t="n"/>
+      <c r="AG10" s="4" t="n"/>
+      <c r="AH10" s="4" t="n"/>
+      <c r="AI10" s="4" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4" t="n"/>
+      <c r="AL10" s="4" t="n"/>
+      <c r="AM10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1577,12 +1799,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n"/>
+      <c r="AE11" s="4" t="n"/>
+      <c r="AF11" s="4" t="n"/>
+      <c r="AG11" s="4" t="n"/>
+      <c r="AH11" s="4" t="n"/>
+      <c r="AI11" s="4" t="n"/>
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="4" t="n"/>
+      <c r="AL11" s="4" t="n"/>
+      <c r="AM11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1673,12 +1913,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
+      <c r="AD12" s="4" t="n"/>
+      <c r="AE12" s="4" t="n"/>
+      <c r="AF12" s="4" t="n"/>
+      <c r="AG12" s="4" t="n"/>
+      <c r="AH12" s="4" t="n"/>
+      <c r="AI12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="4" t="n"/>
+      <c r="AM12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1769,12 +2027,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="4" t="n"/>
+      <c r="AD13" s="4" t="n"/>
+      <c r="AE13" s="4" t="n"/>
+      <c r="AF13" s="4" t="n"/>
+      <c r="AG13" s="4" t="n"/>
+      <c r="AH13" s="4" t="n"/>
+      <c r="AI13" s="4" t="n"/>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4" t="n"/>
+      <c r="AL13" s="4" t="n"/>
+      <c r="AM13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1865,12 +2141,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z14" s="4" t="n"/>
       <c r="AA14" s="4" t="n"/>
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
+      <c r="AD14" s="4" t="n"/>
+      <c r="AE14" s="4" t="n"/>
+      <c r="AF14" s="4" t="n"/>
+      <c r="AG14" s="4" t="n"/>
+      <c r="AH14" s="4" t="n"/>
+      <c r="AI14" s="4" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4" t="n"/>
+      <c r="AL14" s="4" t="n"/>
+      <c r="AM14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1961,12 +2255,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
+      <c r="AD15" s="4" t="n"/>
+      <c r="AE15" s="4" t="n"/>
+      <c r="AF15" s="4" t="n"/>
+      <c r="AG15" s="4" t="n"/>
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="n"/>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4" t="n"/>
+      <c r="AL15" s="4" t="n"/>
+      <c r="AM15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2057,12 +2369,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
+      <c r="AD16" s="4" t="n"/>
+      <c r="AE16" s="4" t="n"/>
+      <c r="AF16" s="4" t="n"/>
+      <c r="AG16" s="4" t="n"/>
+      <c r="AH16" s="4" t="n"/>
+      <c r="AI16" s="4" t="n"/>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="4" t="n"/>
+      <c r="AL16" s="4" t="n"/>
+      <c r="AM16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2153,12 +2483,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
+      <c r="AD17" s="4" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+      <c r="AF17" s="4" t="n"/>
+      <c r="AG17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n"/>
+      <c r="AI17" s="4" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="n"/>
+      <c r="AL17" s="4" t="n"/>
+      <c r="AM17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2249,12 +2597,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
+      <c r="AD18" s="4" t="n"/>
+      <c r="AE18" s="4" t="n"/>
+      <c r="AF18" s="4" t="n"/>
+      <c r="AG18" s="4" t="n"/>
+      <c r="AH18" s="4" t="n"/>
+      <c r="AI18" s="4" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="4" t="n"/>
+      <c r="AL18" s="4" t="n"/>
+      <c r="AM18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2345,12 +2711,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z19" s="4" t="n"/>
       <c r="AA19" s="4" t="n"/>
       <c r="AB19" s="4" t="n"/>
       <c r="AC19" s="4" t="n"/>
+      <c r="AD19" s="4" t="n"/>
+      <c r="AE19" s="4" t="n"/>
+      <c r="AF19" s="4" t="n"/>
+      <c r="AG19" s="4" t="n"/>
+      <c r="AH19" s="4" t="n"/>
+      <c r="AI19" s="4" t="n"/>
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4" t="n"/>
+      <c r="AL19" s="4" t="n"/>
+      <c r="AM19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2441,12 +2825,30 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
+      <c r="AD20" s="4" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+      <c r="AF20" s="4" t="n"/>
+      <c r="AG20" s="4" t="n"/>
+      <c r="AH20" s="4" t="n"/>
+      <c r="AI20" s="4" t="n"/>
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="4" t="n"/>
+      <c r="AL20" s="4" t="n"/>
+      <c r="AM20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2537,12 +2939,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
+      <c r="AD21" s="4" t="n"/>
+      <c r="AE21" s="4" t="n"/>
+      <c r="AF21" s="4" t="n"/>
+      <c r="AG21" s="4" t="n"/>
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="n"/>
+      <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="4" t="n"/>
+      <c r="AL21" s="4" t="n"/>
+      <c r="AM21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2633,12 +3053,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X22" s="4" t="n"/>
-      <c r="Y22" s="4" t="n"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="4" t="n"/>
+      <c r="AD22" s="4" t="n"/>
+      <c r="AE22" s="4" t="n"/>
+      <c r="AF22" s="4" t="n"/>
+      <c r="AG22" s="4" t="n"/>
+      <c r="AH22" s="4" t="n"/>
+      <c r="AI22" s="4" t="n"/>
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="4" t="n"/>
+      <c r="AL22" s="4" t="n"/>
+      <c r="AM22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2729,12 +3167,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X23" s="4" t="n"/>
-      <c r="Y23" s="4" t="n"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
+      <c r="AD23" s="4" t="n"/>
+      <c r="AE23" s="4" t="n"/>
+      <c r="AF23" s="4" t="n"/>
+      <c r="AG23" s="4" t="n"/>
+      <c r="AH23" s="4" t="n"/>
+      <c r="AI23" s="4" t="n"/>
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="4" t="n"/>
+      <c r="AL23" s="4" t="n"/>
+      <c r="AM23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2825,12 +3281,30 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="4" t="n"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
       <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="4" t="n"/>
+      <c r="AD24" s="4" t="n"/>
+      <c r="AE24" s="4" t="n"/>
+      <c r="AF24" s="4" t="n"/>
+      <c r="AG24" s="4" t="n"/>
+      <c r="AH24" s="4" t="n"/>
+      <c r="AI24" s="4" t="n"/>
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="4" t="n"/>
+      <c r="AL24" s="4" t="n"/>
+      <c r="AM24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2921,12 +3395,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X25" s="4" t="n"/>
-      <c r="Y25" s="4" t="n"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="4" t="n"/>
       <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="4" t="n"/>
+      <c r="AD25" s="4" t="n"/>
+      <c r="AE25" s="4" t="n"/>
+      <c r="AF25" s="4" t="n"/>
+      <c r="AG25" s="4" t="n"/>
+      <c r="AH25" s="4" t="n"/>
+      <c r="AI25" s="4" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4" t="n"/>
+      <c r="AL25" s="4" t="n"/>
+      <c r="AM25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3017,12 +3509,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="4" t="n"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="4" t="n"/>
+      <c r="AD26" s="4" t="n"/>
+      <c r="AE26" s="4" t="n"/>
+      <c r="AF26" s="4" t="n"/>
+      <c r="AG26" s="4" t="n"/>
+      <c r="AH26" s="4" t="n"/>
+      <c r="AI26" s="4" t="n"/>
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="4" t="n"/>
+      <c r="AL26" s="4" t="n"/>
+      <c r="AM26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3113,12 +3623,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="4" t="n"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="4" t="n"/>
+      <c r="AD27" s="4" t="n"/>
+      <c r="AE27" s="4" t="n"/>
+      <c r="AF27" s="4" t="n"/>
+      <c r="AG27" s="4" t="n"/>
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="n"/>
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="4" t="n"/>
+      <c r="AL27" s="4" t="n"/>
+      <c r="AM27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3209,12 +3737,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="4" t="n"/>
+      <c r="AD28" s="4" t="n"/>
+      <c r="AE28" s="4" t="n"/>
+      <c r="AF28" s="4" t="n"/>
+      <c r="AG28" s="4" t="n"/>
+      <c r="AH28" s="4" t="n"/>
+      <c r="AI28" s="4" t="n"/>
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="4" t="n"/>
+      <c r="AL28" s="4" t="n"/>
+      <c r="AM28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3305,12 +3851,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="4" t="n"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
+      <c r="AD29" s="4" t="n"/>
+      <c r="AE29" s="4" t="n"/>
+      <c r="AF29" s="4" t="n"/>
+      <c r="AG29" s="4" t="n"/>
+      <c r="AH29" s="4" t="n"/>
+      <c r="AI29" s="4" t="n"/>
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="4" t="n"/>
+      <c r="AL29" s="4" t="n"/>
+      <c r="AM29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3401,12 +3965,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X30" s="4" t="n"/>
-      <c r="Y30" s="4" t="n"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
+      <c r="AD30" s="4" t="n"/>
+      <c r="AE30" s="4" t="n"/>
+      <c r="AF30" s="4" t="n"/>
+      <c r="AG30" s="4" t="n"/>
+      <c r="AH30" s="4" t="n"/>
+      <c r="AI30" s="4" t="n"/>
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="4" t="n"/>
+      <c r="AL30" s="4" t="n"/>
+      <c r="AM30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3497,12 +4079,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
+      <c r="AD31" s="4" t="n"/>
+      <c r="AE31" s="4" t="n"/>
+      <c r="AF31" s="4" t="n"/>
+      <c r="AG31" s="4" t="n"/>
+      <c r="AH31" s="4" t="n"/>
+      <c r="AI31" s="4" t="n"/>
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4" t="n"/>
+      <c r="AL31" s="4" t="n"/>
+      <c r="AM31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3593,12 +4193,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="4" t="n"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
+      <c r="AD32" s="4" t="n"/>
+      <c r="AE32" s="4" t="n"/>
+      <c r="AF32" s="4" t="n"/>
+      <c r="AG32" s="4" t="n"/>
+      <c r="AH32" s="4" t="n"/>
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="4" t="n"/>
+      <c r="AL32" s="4" t="n"/>
+      <c r="AM32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3689,12 +4307,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X33" s="4" t="n"/>
-      <c r="Y33" s="4" t="n"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
+      <c r="AD33" s="4" t="n"/>
+      <c r="AE33" s="4" t="n"/>
+      <c r="AF33" s="4" t="n"/>
+      <c r="AG33" s="4" t="n"/>
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="n"/>
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="4" t="n"/>
+      <c r="AL33" s="4" t="n"/>
+      <c r="AM33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3785,12 +4421,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
+      <c r="AD34" s="4" t="n"/>
+      <c r="AE34" s="4" t="n"/>
+      <c r="AF34" s="4" t="n"/>
+      <c r="AG34" s="4" t="n"/>
+      <c r="AH34" s="4" t="n"/>
+      <c r="AI34" s="4" t="n"/>
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="4" t="n"/>
+      <c r="AL34" s="4" t="n"/>
+      <c r="AM34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3881,12 +4535,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X35" s="4" t="n"/>
-      <c r="Y35" s="4" t="n"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
+      <c r="AD35" s="4" t="n"/>
+      <c r="AE35" s="4" t="n"/>
+      <c r="AF35" s="4" t="n"/>
+      <c r="AG35" s="4" t="n"/>
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="n"/>
+      <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="4" t="n"/>
+      <c r="AL35" s="4" t="n"/>
+      <c r="AM35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3977,12 +4649,30 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="X36" s="4" t="n"/>
-      <c r="Y36" s="4" t="n"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z36" s="4" t="n"/>
       <c r="AA36" s="4" t="n"/>
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="4" t="n"/>
+      <c r="AD36" s="4" t="n"/>
+      <c r="AE36" s="4" t="n"/>
+      <c r="AF36" s="4" t="n"/>
+      <c r="AG36" s="4" t="n"/>
+      <c r="AH36" s="4" t="n"/>
+      <c r="AI36" s="4" t="n"/>
+      <c r="AJ36" s="4" t="n"/>
+      <c r="AK36" s="4" t="n"/>
+      <c r="AL36" s="4" t="n"/>
+      <c r="AM36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4073,12 +4763,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X37" s="4" t="n"/>
-      <c r="Y37" s="4" t="n"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z37" s="4" t="n"/>
       <c r="AA37" s="4" t="n"/>
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
+      <c r="AD37" s="4" t="n"/>
+      <c r="AE37" s="4" t="n"/>
+      <c r="AF37" s="4" t="n"/>
+      <c r="AG37" s="4" t="n"/>
+      <c r="AH37" s="4" t="n"/>
+      <c r="AI37" s="4" t="n"/>
+      <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="4" t="n"/>
+      <c r="AL37" s="4" t="n"/>
+      <c r="AM37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4169,12 +4877,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X38" s="4" t="n"/>
-      <c r="Y38" s="4" t="n"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
+      <c r="AD38" s="4" t="n"/>
+      <c r="AE38" s="4" t="n"/>
+      <c r="AF38" s="4" t="n"/>
+      <c r="AG38" s="4" t="n"/>
+      <c r="AH38" s="4" t="n"/>
+      <c r="AI38" s="4" t="n"/>
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="4" t="n"/>
+      <c r="AL38" s="4" t="n"/>
+      <c r="AM38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4265,12 +4991,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X39" s="4" t="n"/>
-      <c r="Y39" s="4" t="n"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z39" s="4" t="n"/>
       <c r="AA39" s="4" t="n"/>
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
+      <c r="AD39" s="4" t="n"/>
+      <c r="AE39" s="4" t="n"/>
+      <c r="AF39" s="4" t="n"/>
+      <c r="AG39" s="4" t="n"/>
+      <c r="AH39" s="4" t="n"/>
+      <c r="AI39" s="4" t="n"/>
+      <c r="AJ39" s="4" t="n"/>
+      <c r="AK39" s="4" t="n"/>
+      <c r="AL39" s="4" t="n"/>
+      <c r="AM39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4361,12 +5105,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X40" s="4" t="n"/>
-      <c r="Y40" s="4" t="n"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
+      <c r="AD40" s="4" t="n"/>
+      <c r="AE40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="n"/>
+      <c r="AH40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n"/>
+      <c r="AJ40" s="4" t="n"/>
+      <c r="AK40" s="4" t="n"/>
+      <c r="AL40" s="4" t="n"/>
+      <c r="AM40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4457,12 +5219,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X41" s="4" t="n"/>
-      <c r="Y41" s="4" t="n"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z41" s="4" t="n"/>
       <c r="AA41" s="4" t="n"/>
       <c r="AB41" s="4" t="n"/>
       <c r="AC41" s="4" t="n"/>
+      <c r="AD41" s="4" t="n"/>
+      <c r="AE41" s="4" t="n"/>
+      <c r="AF41" s="4" t="n"/>
+      <c r="AG41" s="4" t="n"/>
+      <c r="AH41" s="4" t="n"/>
+      <c r="AI41" s="4" t="n"/>
+      <c r="AJ41" s="4" t="n"/>
+      <c r="AK41" s="4" t="n"/>
+      <c r="AL41" s="4" t="n"/>
+      <c r="AM41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4553,12 +5333,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="4" t="n"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z42" s="4" t="n"/>
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="n"/>
+      <c r="AD42" s="4" t="n"/>
+      <c r="AE42" s="4" t="n"/>
+      <c r="AF42" s="4" t="n"/>
+      <c r="AG42" s="4" t="n"/>
+      <c r="AH42" s="4" t="n"/>
+      <c r="AI42" s="4" t="n"/>
+      <c r="AJ42" s="4" t="n"/>
+      <c r="AK42" s="4" t="n"/>
+      <c r="AL42" s="4" t="n"/>
+      <c r="AM42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4649,12 +5447,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X43" s="4" t="n"/>
-      <c r="Y43" s="4" t="n"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="4" t="n"/>
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="4" t="n"/>
+      <c r="AD43" s="4" t="n"/>
+      <c r="AE43" s="4" t="n"/>
+      <c r="AF43" s="4" t="n"/>
+      <c r="AG43" s="4" t="n"/>
+      <c r="AH43" s="4" t="n"/>
+      <c r="AI43" s="4" t="n"/>
+      <c r="AJ43" s="4" t="n"/>
+      <c r="AK43" s="4" t="n"/>
+      <c r="AL43" s="4" t="n"/>
+      <c r="AM43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4745,12 +5561,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="4" t="n"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
+      <c r="AD44" s="4" t="n"/>
+      <c r="AE44" s="4" t="n"/>
+      <c r="AF44" s="4" t="n"/>
+      <c r="AG44" s="4" t="n"/>
+      <c r="AH44" s="4" t="n"/>
+      <c r="AI44" s="4" t="n"/>
+      <c r="AJ44" s="4" t="n"/>
+      <c r="AK44" s="4" t="n"/>
+      <c r="AL44" s="4" t="n"/>
+      <c r="AM44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4841,12 +5675,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X45" s="4" t="n"/>
-      <c r="Y45" s="4" t="n"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z45" s="4" t="n"/>
       <c r="AA45" s="4" t="n"/>
       <c r="AB45" s="4" t="n"/>
       <c r="AC45" s="4" t="n"/>
+      <c r="AD45" s="4" t="n"/>
+      <c r="AE45" s="4" t="n"/>
+      <c r="AF45" s="4" t="n"/>
+      <c r="AG45" s="4" t="n"/>
+      <c r="AH45" s="4" t="n"/>
+      <c r="AI45" s="4" t="n"/>
+      <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="4" t="n"/>
+      <c r="AL45" s="4" t="n"/>
+      <c r="AM45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4937,12 +5789,30 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="X46" s="4" t="n"/>
-      <c r="Y46" s="4" t="n"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z46" s="4" t="n"/>
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="4" t="n"/>
+      <c r="AD46" s="4" t="n"/>
+      <c r="AE46" s="4" t="n"/>
+      <c r="AF46" s="4" t="n"/>
+      <c r="AG46" s="4" t="n"/>
+      <c r="AH46" s="4" t="n"/>
+      <c r="AI46" s="4" t="n"/>
+      <c r="AJ46" s="4" t="n"/>
+      <c r="AK46" s="4" t="n"/>
+      <c r="AL46" s="4" t="n"/>
+      <c r="AM46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5033,12 +5903,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X47" s="4" t="n"/>
-      <c r="Y47" s="4" t="n"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z47" s="4" t="n"/>
       <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="4" t="n"/>
+      <c r="AD47" s="4" t="n"/>
+      <c r="AE47" s="4" t="n"/>
+      <c r="AF47" s="4" t="n"/>
+      <c r="AG47" s="4" t="n"/>
+      <c r="AH47" s="4" t="n"/>
+      <c r="AI47" s="4" t="n"/>
+      <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="4" t="n"/>
+      <c r="AL47" s="4" t="n"/>
+      <c r="AM47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5129,12 +6017,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X48" s="4" t="n"/>
-      <c r="Y48" s="4" t="n"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
       <c r="AC48" s="4" t="n"/>
+      <c r="AD48" s="4" t="n"/>
+      <c r="AE48" s="4" t="n"/>
+      <c r="AF48" s="4" t="n"/>
+      <c r="AG48" s="4" t="n"/>
+      <c r="AH48" s="4" t="n"/>
+      <c r="AI48" s="4" t="n"/>
+      <c r="AJ48" s="4" t="n"/>
+      <c r="AK48" s="4" t="n"/>
+      <c r="AL48" s="4" t="n"/>
+      <c r="AM48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5225,12 +6131,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="4" t="n"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="4" t="n"/>
+      <c r="AD49" s="4" t="n"/>
+      <c r="AE49" s="4" t="n"/>
+      <c r="AF49" s="4" t="n"/>
+      <c r="AG49" s="4" t="n"/>
+      <c r="AH49" s="4" t="n"/>
+      <c r="AI49" s="4" t="n"/>
+      <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="4" t="n"/>
+      <c r="AL49" s="4" t="n"/>
+      <c r="AM49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5321,12 +6245,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
+      <c r="AD50" s="4" t="n"/>
+      <c r="AE50" s="4" t="n"/>
+      <c r="AF50" s="4" t="n"/>
+      <c r="AG50" s="4" t="n"/>
+      <c r="AH50" s="4" t="n"/>
+      <c r="AI50" s="4" t="n"/>
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="4" t="n"/>
+      <c r="AL50" s="4" t="n"/>
+      <c r="AM50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5417,12 +6359,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X51" s="4" t="n"/>
-      <c r="Y51" s="4" t="n"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z51" s="4" t="n"/>
       <c r="AA51" s="4" t="n"/>
       <c r="AB51" s="4" t="n"/>
       <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="n"/>
+      <c r="AE51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5513,12 +6473,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X52" s="4" t="n"/>
-      <c r="Y52" s="4" t="n"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z52" s="4" t="n"/>
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
       <c r="AC52" s="4" t="n"/>
+      <c r="AD52" s="4" t="n"/>
+      <c r="AE52" s="4" t="n"/>
+      <c r="AF52" s="4" t="n"/>
+      <c r="AG52" s="4" t="n"/>
+      <c r="AH52" s="4" t="n"/>
+      <c r="AI52" s="4" t="n"/>
+      <c r="AJ52" s="4" t="n"/>
+      <c r="AK52" s="4" t="n"/>
+      <c r="AL52" s="4" t="n"/>
+      <c r="AM52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5609,36 +6587,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X53" s="4" t="inlineStr">
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="Z53" s="4" t="inlineStr">
         <is>
           <t>authored-ok</t>
         </is>
       </c>
-      <c r="Y53" s="4" t="inlineStr">
+      <c r="AA53" s="4" t="inlineStr">
         <is>
           <t>Advanced in Pickett's front line from Spangler's Woods; halted under fire at the Emmitsburg Road fences (~15:16-15:18, ED-12/claim-fences-high-climb); crossed under canister; reached the wall; repulsed ~15:25+ (V2 corpus: 7 segments, ED-2 timing frame).</t>
         </is>
       </c>
-      <c r="Z53" s="4" t="inlineStr">
+      <c r="AB53" s="4" t="inlineStr">
         <is>
           <t>In-build decay 1480-&gt;539 over the slice; V2 casualty profiles reconcile exactly (e.g. cas-garnett-angle-approach: 510, rising, musketry/canister). Battle-total K/W/M per OOB research doc - layer in.</t>
         </is>
       </c>
-      <c r="AA53" s="4" t="inlineStr">
+      <c r="AC53" s="4" t="inlineStr">
         <is>
           <t>None needed for the slice window (Angle cast).</t>
         </is>
       </c>
-      <c r="AB53" s="4" t="inlineStr">
+      <c r="AD53" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC53" s="4" t="inlineStr">
+      <c r="AE53" s="4" t="inlineStr">
         <is>
           <t>Format example row - overwrite freely.</t>
         </is>
       </c>
+      <c r="AF53" s="4" t="n"/>
+      <c r="AG53" s="4" t="n"/>
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="n"/>
+      <c r="AJ53" s="4" t="n"/>
+      <c r="AK53" s="4" t="n"/>
+      <c r="AL53" s="4" t="n"/>
+      <c r="AM53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5729,12 +6725,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X54" s="4" t="n"/>
-      <c r="Y54" s="4" t="n"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
       <c r="AC54" s="4" t="n"/>
+      <c r="AD54" s="4" t="n"/>
+      <c r="AE54" s="4" t="n"/>
+      <c r="AF54" s="4" t="n"/>
+      <c r="AG54" s="4" t="n"/>
+      <c r="AH54" s="4" t="n"/>
+      <c r="AI54" s="4" t="n"/>
+      <c r="AJ54" s="4" t="n"/>
+      <c r="AK54" s="4" t="n"/>
+      <c r="AL54" s="4" t="n"/>
+      <c r="AM54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5825,12 +6839,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X55" s="4" t="n"/>
-      <c r="Y55" s="4" t="n"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="n"/>
+      <c r="AD55" s="4" t="n"/>
+      <c r="AE55" s="4" t="n"/>
+      <c r="AF55" s="4" t="n"/>
+      <c r="AG55" s="4" t="n"/>
+      <c r="AH55" s="4" t="n"/>
+      <c r="AI55" s="4" t="n"/>
+      <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="4" t="n"/>
+      <c r="AL55" s="4" t="n"/>
+      <c r="AM55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5921,12 +6953,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X56" s="4" t="n"/>
-      <c r="Y56" s="4" t="n"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z56" s="4" t="n"/>
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="4" t="n"/>
+      <c r="AD56" s="4" t="n"/>
+      <c r="AE56" s="4" t="n"/>
+      <c r="AF56" s="4" t="n"/>
+      <c r="AG56" s="4" t="n"/>
+      <c r="AH56" s="4" t="n"/>
+      <c r="AI56" s="4" t="n"/>
+      <c r="AJ56" s="4" t="n"/>
+      <c r="AK56" s="4" t="n"/>
+      <c r="AL56" s="4" t="n"/>
+      <c r="AM56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -6017,12 +7067,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X57" s="4" t="n"/>
-      <c r="Y57" s="4" t="n"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
+      <c r="AD57" s="4" t="n"/>
+      <c r="AE57" s="4" t="n"/>
+      <c r="AF57" s="4" t="n"/>
+      <c r="AG57" s="4" t="n"/>
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="n"/>
+      <c r="AJ57" s="4" t="n"/>
+      <c r="AK57" s="4" t="n"/>
+      <c r="AL57" s="4" t="n"/>
+      <c r="AM57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -6113,12 +7181,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="4" t="n"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="4" t="n"/>
+      <c r="AD58" s="4" t="n"/>
+      <c r="AE58" s="4" t="n"/>
+      <c r="AF58" s="4" t="n"/>
+      <c r="AG58" s="4" t="n"/>
+      <c r="AH58" s="4" t="n"/>
+      <c r="AI58" s="4" t="n"/>
+      <c r="AJ58" s="4" t="n"/>
+      <c r="AK58" s="4" t="n"/>
+      <c r="AL58" s="4" t="n"/>
+      <c r="AM58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -6209,12 +7295,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X59" s="4" t="n"/>
-      <c r="Y59" s="4" t="n"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z59" s="4" t="n"/>
       <c r="AA59" s="4" t="n"/>
       <c r="AB59" s="4" t="n"/>
       <c r="AC59" s="4" t="n"/>
+      <c r="AD59" s="4" t="n"/>
+      <c r="AE59" s="4" t="n"/>
+      <c r="AF59" s="4" t="n"/>
+      <c r="AG59" s="4" t="n"/>
+      <c r="AH59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n"/>
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="4" t="n"/>
+      <c r="AL59" s="4" t="n"/>
+      <c r="AM59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -6305,12 +7409,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X60" s="4" t="n"/>
-      <c r="Y60" s="4" t="n"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
+      <c r="AD60" s="4" t="n"/>
+      <c r="AE60" s="4" t="n"/>
+      <c r="AF60" s="4" t="n"/>
+      <c r="AG60" s="4" t="n"/>
+      <c r="AH60" s="4" t="n"/>
+      <c r="AI60" s="4" t="n"/>
+      <c r="AJ60" s="4" t="n"/>
+      <c r="AK60" s="4" t="n"/>
+      <c r="AL60" s="4" t="n"/>
+      <c r="AM60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -6401,12 +7523,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="4" t="n"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n"/>
+      <c r="AD61" s="4" t="n"/>
+      <c r="AE61" s="4" t="n"/>
+      <c r="AF61" s="4" t="n"/>
+      <c r="AG61" s="4" t="n"/>
+      <c r="AH61" s="4" t="n"/>
+      <c r="AI61" s="4" t="n"/>
+      <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="4" t="n"/>
+      <c r="AL61" s="4" t="n"/>
+      <c r="AM61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6497,12 +7637,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X62" s="4" t="n"/>
-      <c r="Y62" s="4" t="n"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z62" s="4" t="n"/>
       <c r="AA62" s="4" t="n"/>
       <c r="AB62" s="4" t="n"/>
       <c r="AC62" s="4" t="n"/>
+      <c r="AD62" s="4" t="n"/>
+      <c r="AE62" s="4" t="n"/>
+      <c r="AF62" s="4" t="n"/>
+      <c r="AG62" s="4" t="n"/>
+      <c r="AH62" s="4" t="n"/>
+      <c r="AI62" s="4" t="n"/>
+      <c r="AJ62" s="4" t="n"/>
+      <c r="AK62" s="4" t="n"/>
+      <c r="AL62" s="4" t="n"/>
+      <c r="AM62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6593,12 +7751,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X63" s="4" t="n"/>
-      <c r="Y63" s="4" t="n"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n"/>
+      <c r="AD63" s="4" t="n"/>
+      <c r="AE63" s="4" t="n"/>
+      <c r="AF63" s="4" t="n"/>
+      <c r="AG63" s="4" t="n"/>
+      <c r="AH63" s="4" t="n"/>
+      <c r="AI63" s="4" t="n"/>
+      <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="4" t="n"/>
+      <c r="AL63" s="4" t="n"/>
+      <c r="AM63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6689,12 +7865,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X64" s="4" t="n"/>
-      <c r="Y64" s="4" t="n"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z64" s="4" t="n"/>
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="4" t="n"/>
+      <c r="AD64" s="4" t="n"/>
+      <c r="AE64" s="4" t="n"/>
+      <c r="AF64" s="4" t="n"/>
+      <c r="AG64" s="4" t="n"/>
+      <c r="AH64" s="4" t="n"/>
+      <c r="AI64" s="4" t="n"/>
+      <c r="AJ64" s="4" t="n"/>
+      <c r="AK64" s="4" t="n"/>
+      <c r="AL64" s="4" t="n"/>
+      <c r="AM64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6785,12 +7979,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X65" s="4" t="n"/>
-      <c r="Y65" s="4" t="n"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
+      <c r="AD65" s="4" t="n"/>
+      <c r="AE65" s="4" t="n"/>
+      <c r="AF65" s="4" t="n"/>
+      <c r="AG65" s="4" t="n"/>
+      <c r="AH65" s="4" t="n"/>
+      <c r="AI65" s="4" t="n"/>
+      <c r="AJ65" s="4" t="n"/>
+      <c r="AK65" s="4" t="n"/>
+      <c r="AL65" s="4" t="n"/>
+      <c r="AM65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6881,12 +8093,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X66" s="4" t="n"/>
-      <c r="Y66" s="4" t="n"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z66" s="4" t="n"/>
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="n"/>
+      <c r="AD66" s="4" t="n"/>
+      <c r="AE66" s="4" t="n"/>
+      <c r="AF66" s="4" t="n"/>
+      <c r="AG66" s="4" t="n"/>
+      <c r="AH66" s="4" t="n"/>
+      <c r="AI66" s="4" t="n"/>
+      <c r="AJ66" s="4" t="n"/>
+      <c r="AK66" s="4" t="n"/>
+      <c r="AL66" s="4" t="n"/>
+      <c r="AM66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6977,12 +8207,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="4" t="n"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
+      <c r="AD67" s="4" t="n"/>
+      <c r="AE67" s="4" t="n"/>
+      <c r="AF67" s="4" t="n"/>
+      <c r="AG67" s="4" t="n"/>
+      <c r="AH67" s="4" t="n"/>
+      <c r="AI67" s="4" t="n"/>
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="4" t="n"/>
+      <c r="AL67" s="4" t="n"/>
+      <c r="AM67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7073,12 +8321,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="4" t="n"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z68" s="4" t="n"/>
       <c r="AA68" s="4" t="n"/>
       <c r="AB68" s="4" t="n"/>
       <c r="AC68" s="4" t="n"/>
+      <c r="AD68" s="4" t="n"/>
+      <c r="AE68" s="4" t="n"/>
+      <c r="AF68" s="4" t="n"/>
+      <c r="AG68" s="4" t="n"/>
+      <c r="AH68" s="4" t="n"/>
+      <c r="AI68" s="4" t="n"/>
+      <c r="AJ68" s="4" t="n"/>
+      <c r="AK68" s="4" t="n"/>
+      <c r="AL68" s="4" t="n"/>
+      <c r="AM68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -7169,12 +8435,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="4" t="n"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
+      <c r="AD69" s="4" t="n"/>
+      <c r="AE69" s="4" t="n"/>
+      <c r="AF69" s="4" t="n"/>
+      <c r="AG69" s="4" t="n"/>
+      <c r="AH69" s="4" t="n"/>
+      <c r="AI69" s="4" t="n"/>
+      <c r="AJ69" s="4" t="n"/>
+      <c r="AK69" s="4" t="n"/>
+      <c r="AL69" s="4" t="n"/>
+      <c r="AM69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7265,12 +8549,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X70" s="4" t="n"/>
-      <c r="Y70" s="4" t="n"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z70" s="4" t="n"/>
       <c r="AA70" s="4" t="n"/>
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
+      <c r="AD70" s="4" t="n"/>
+      <c r="AE70" s="4" t="n"/>
+      <c r="AF70" s="4" t="n"/>
+      <c r="AG70" s="4" t="n"/>
+      <c r="AH70" s="4" t="n"/>
+      <c r="AI70" s="4" t="n"/>
+      <c r="AJ70" s="4" t="n"/>
+      <c r="AK70" s="4" t="n"/>
+      <c r="AL70" s="4" t="n"/>
+      <c r="AM70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7361,12 +8663,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X71" s="4" t="n"/>
-      <c r="Y71" s="4" t="n"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
+      <c r="AD71" s="4" t="n"/>
+      <c r="AE71" s="4" t="n"/>
+      <c r="AF71" s="4" t="n"/>
+      <c r="AG71" s="4" t="n"/>
+      <c r="AH71" s="4" t="n"/>
+      <c r="AI71" s="4" t="n"/>
+      <c r="AJ71" s="4" t="n"/>
+      <c r="AK71" s="4" t="n"/>
+      <c r="AL71" s="4" t="n"/>
+      <c r="AM71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7457,12 +8777,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X72" s="4" t="n"/>
-      <c r="Y72" s="4" t="n"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
+      <c r="AD72" s="4" t="n"/>
+      <c r="AE72" s="4" t="n"/>
+      <c r="AF72" s="4" t="n"/>
+      <c r="AG72" s="4" t="n"/>
+      <c r="AH72" s="4" t="n"/>
+      <c r="AI72" s="4" t="n"/>
+      <c r="AJ72" s="4" t="n"/>
+      <c r="AK72" s="4" t="n"/>
+      <c r="AL72" s="4" t="n"/>
+      <c r="AM72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -7553,12 +8891,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X73" s="4" t="n"/>
-      <c r="Y73" s="4" t="n"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z73" s="4" t="n"/>
       <c r="AA73" s="4" t="n"/>
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
+      <c r="AD73" s="4" t="n"/>
+      <c r="AE73" s="4" t="n"/>
+      <c r="AF73" s="4" t="n"/>
+      <c r="AG73" s="4" t="n"/>
+      <c r="AH73" s="4" t="n"/>
+      <c r="AI73" s="4" t="n"/>
+      <c r="AJ73" s="4" t="n"/>
+      <c r="AK73" s="4" t="n"/>
+      <c r="AL73" s="4" t="n"/>
+      <c r="AM73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7649,12 +9005,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
+      <c r="AD74" s="4" t="n"/>
+      <c r="AE74" s="4" t="n"/>
+      <c r="AF74" s="4" t="n"/>
+      <c r="AG74" s="4" t="n"/>
+      <c r="AH74" s="4" t="n"/>
+      <c r="AI74" s="4" t="n"/>
+      <c r="AJ74" s="4" t="n"/>
+      <c r="AK74" s="4" t="n"/>
+      <c r="AL74" s="4" t="n"/>
+      <c r="AM74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7745,12 +9119,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="n"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z75" s="4" t="n"/>
       <c r="AA75" s="4" t="n"/>
       <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
+      <c r="AD75" s="4" t="n"/>
+      <c r="AE75" s="4" t="n"/>
+      <c r="AF75" s="4" t="n"/>
+      <c r="AG75" s="4" t="n"/>
+      <c r="AH75" s="4" t="n"/>
+      <c r="AI75" s="4" t="n"/>
+      <c r="AJ75" s="4" t="n"/>
+      <c r="AK75" s="4" t="n"/>
+      <c r="AL75" s="4" t="n"/>
+      <c r="AM75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7841,12 +9233,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="4" t="n"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="4" t="n"/>
+      <c r="AD76" s="4" t="n"/>
+      <c r="AE76" s="4" t="n"/>
+      <c r="AF76" s="4" t="n"/>
+      <c r="AG76" s="4" t="n"/>
+      <c r="AH76" s="4" t="n"/>
+      <c r="AI76" s="4" t="n"/>
+      <c r="AJ76" s="4" t="n"/>
+      <c r="AK76" s="4" t="n"/>
+      <c r="AL76" s="4" t="n"/>
+      <c r="AM76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7937,12 +9347,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="4" t="n"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z77" s="4" t="n"/>
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
       <c r="AC77" s="4" t="n"/>
+      <c r="AD77" s="4" t="n"/>
+      <c r="AE77" s="4" t="n"/>
+      <c r="AF77" s="4" t="n"/>
+      <c r="AG77" s="4" t="n"/>
+      <c r="AH77" s="4" t="n"/>
+      <c r="AI77" s="4" t="n"/>
+      <c r="AJ77" s="4" t="n"/>
+      <c r="AK77" s="4" t="n"/>
+      <c r="AL77" s="4" t="n"/>
+      <c r="AM77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -8033,12 +9461,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X78" s="4" t="n"/>
-      <c r="Y78" s="4" t="n"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z78" s="4" t="n"/>
       <c r="AA78" s="4" t="n"/>
       <c r="AB78" s="4" t="n"/>
       <c r="AC78" s="4" t="n"/>
+      <c r="AD78" s="4" t="n"/>
+      <c r="AE78" s="4" t="n"/>
+      <c r="AF78" s="4" t="n"/>
+      <c r="AG78" s="4" t="n"/>
+      <c r="AH78" s="4" t="n"/>
+      <c r="AI78" s="4" t="n"/>
+      <c r="AJ78" s="4" t="n"/>
+      <c r="AK78" s="4" t="n"/>
+      <c r="AL78" s="4" t="n"/>
+      <c r="AM78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8129,12 +9575,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X79" s="4" t="n"/>
-      <c r="Y79" s="4" t="n"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z79" s="4" t="n"/>
       <c r="AA79" s="4" t="n"/>
       <c r="AB79" s="4" t="n"/>
       <c r="AC79" s="4" t="n"/>
+      <c r="AD79" s="4" t="n"/>
+      <c r="AE79" s="4" t="n"/>
+      <c r="AF79" s="4" t="n"/>
+      <c r="AG79" s="4" t="n"/>
+      <c r="AH79" s="4" t="n"/>
+      <c r="AI79" s="4" t="n"/>
+      <c r="AJ79" s="4" t="n"/>
+      <c r="AK79" s="4" t="n"/>
+      <c r="AL79" s="4" t="n"/>
+      <c r="AM79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8225,12 +9689,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X80" s="4" t="n"/>
-      <c r="Y80" s="4" t="n"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z80" s="4" t="n"/>
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
       <c r="AC80" s="4" t="n"/>
+      <c r="AD80" s="4" t="n"/>
+      <c r="AE80" s="4" t="n"/>
+      <c r="AF80" s="4" t="n"/>
+      <c r="AG80" s="4" t="n"/>
+      <c r="AH80" s="4" t="n"/>
+      <c r="AI80" s="4" t="n"/>
+      <c r="AJ80" s="4" t="n"/>
+      <c r="AK80" s="4" t="n"/>
+      <c r="AL80" s="4" t="n"/>
+      <c r="AM80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8321,12 +9803,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X81" s="4" t="n"/>
-      <c r="Y81" s="4" t="n"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z81" s="4" t="n"/>
       <c r="AA81" s="4" t="n"/>
       <c r="AB81" s="4" t="n"/>
       <c r="AC81" s="4" t="n"/>
+      <c r="AD81" s="4" t="n"/>
+      <c r="AE81" s="4" t="n"/>
+      <c r="AF81" s="4" t="n"/>
+      <c r="AG81" s="4" t="n"/>
+      <c r="AH81" s="4" t="n"/>
+      <c r="AI81" s="4" t="n"/>
+      <c r="AJ81" s="4" t="n"/>
+      <c r="AK81" s="4" t="n"/>
+      <c r="AL81" s="4" t="n"/>
+      <c r="AM81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8417,12 +9917,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X82" s="4" t="n"/>
-      <c r="Y82" s="4" t="n"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z82" s="4" t="n"/>
       <c r="AA82" s="4" t="n"/>
       <c r="AB82" s="4" t="n"/>
       <c r="AC82" s="4" t="n"/>
+      <c r="AD82" s="4" t="n"/>
+      <c r="AE82" s="4" t="n"/>
+      <c r="AF82" s="4" t="n"/>
+      <c r="AG82" s="4" t="n"/>
+      <c r="AH82" s="4" t="n"/>
+      <c r="AI82" s="4" t="n"/>
+      <c r="AJ82" s="4" t="n"/>
+      <c r="AK82" s="4" t="n"/>
+      <c r="AL82" s="4" t="n"/>
+      <c r="AM82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8513,12 +10031,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X83" s="4" t="n"/>
-      <c r="Y83" s="4" t="n"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z83" s="4" t="n"/>
       <c r="AA83" s="4" t="n"/>
       <c r="AB83" s="4" t="n"/>
       <c r="AC83" s="4" t="n"/>
+      <c r="AD83" s="4" t="n"/>
+      <c r="AE83" s="4" t="n"/>
+      <c r="AF83" s="4" t="n"/>
+      <c r="AG83" s="4" t="n"/>
+      <c r="AH83" s="4" t="n"/>
+      <c r="AI83" s="4" t="n"/>
+      <c r="AJ83" s="4" t="n"/>
+      <c r="AK83" s="4" t="n"/>
+      <c r="AL83" s="4" t="n"/>
+      <c r="AM83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -8609,12 +10145,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="n"/>
+      <c r="AF84" s="4" t="n"/>
+      <c r="AG84" s="4" t="n"/>
+      <c r="AH84" s="4" t="n"/>
+      <c r="AI84" s="4" t="n"/>
+      <c r="AJ84" s="4" t="n"/>
+      <c r="AK84" s="4" t="n"/>
+      <c r="AL84" s="4" t="n"/>
+      <c r="AM84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8705,12 +10259,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X85" s="4" t="n"/>
-      <c r="Y85" s="4" t="n"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z85" s="4" t="n"/>
       <c r="AA85" s="4" t="n"/>
       <c r="AB85" s="4" t="n"/>
       <c r="AC85" s="4" t="n"/>
+      <c r="AD85" s="4" t="n"/>
+      <c r="AE85" s="4" t="n"/>
+      <c r="AF85" s="4" t="n"/>
+      <c r="AG85" s="4" t="n"/>
+      <c r="AH85" s="4" t="n"/>
+      <c r="AI85" s="4" t="n"/>
+      <c r="AJ85" s="4" t="n"/>
+      <c r="AK85" s="4" t="n"/>
+      <c r="AL85" s="4" t="n"/>
+      <c r="AM85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -8801,12 +10373,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X86" s="4" t="n"/>
-      <c r="Y86" s="4" t="n"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z86" s="4" t="n"/>
       <c r="AA86" s="4" t="n"/>
       <c r="AB86" s="4" t="n"/>
       <c r="AC86" s="4" t="n"/>
+      <c r="AD86" s="4" t="n"/>
+      <c r="AE86" s="4" t="n"/>
+      <c r="AF86" s="4" t="n"/>
+      <c r="AG86" s="4" t="n"/>
+      <c r="AH86" s="4" t="n"/>
+      <c r="AI86" s="4" t="n"/>
+      <c r="AJ86" s="4" t="n"/>
+      <c r="AK86" s="4" t="n"/>
+      <c r="AL86" s="4" t="n"/>
+      <c r="AM86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8897,12 +10487,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X87" s="4" t="n"/>
-      <c r="Y87" s="4" t="n"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z87" s="4" t="n"/>
       <c r="AA87" s="4" t="n"/>
       <c r="AB87" s="4" t="n"/>
       <c r="AC87" s="4" t="n"/>
+      <c r="AD87" s="4" t="n"/>
+      <c r="AE87" s="4" t="n"/>
+      <c r="AF87" s="4" t="n"/>
+      <c r="AG87" s="4" t="n"/>
+      <c r="AH87" s="4" t="n"/>
+      <c r="AI87" s="4" t="n"/>
+      <c r="AJ87" s="4" t="n"/>
+      <c r="AK87" s="4" t="n"/>
+      <c r="AL87" s="4" t="n"/>
+      <c r="AM87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -8993,12 +10601,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X88" s="4" t="n"/>
-      <c r="Y88" s="4" t="n"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z88" s="4" t="n"/>
       <c r="AA88" s="4" t="n"/>
       <c r="AB88" s="4" t="n"/>
       <c r="AC88" s="4" t="n"/>
+      <c r="AD88" s="4" t="n"/>
+      <c r="AE88" s="4" t="n"/>
+      <c r="AF88" s="4" t="n"/>
+      <c r="AG88" s="4" t="n"/>
+      <c r="AH88" s="4" t="n"/>
+      <c r="AI88" s="4" t="n"/>
+      <c r="AJ88" s="4" t="n"/>
+      <c r="AK88" s="4" t="n"/>
+      <c r="AL88" s="4" t="n"/>
+      <c r="AM88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -9089,12 +10715,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X89" s="4" t="n"/>
-      <c r="Y89" s="4" t="n"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z89" s="4" t="n"/>
       <c r="AA89" s="4" t="n"/>
       <c r="AB89" s="4" t="n"/>
       <c r="AC89" s="4" t="n"/>
+      <c r="AD89" s="4" t="n"/>
+      <c r="AE89" s="4" t="n"/>
+      <c r="AF89" s="4" t="n"/>
+      <c r="AG89" s="4" t="n"/>
+      <c r="AH89" s="4" t="n"/>
+      <c r="AI89" s="4" t="n"/>
+      <c r="AJ89" s="4" t="n"/>
+      <c r="AK89" s="4" t="n"/>
+      <c r="AL89" s="4" t="n"/>
+      <c r="AM89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9185,12 +10829,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X90" s="4" t="n"/>
-      <c r="Y90" s="4" t="n"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z90" s="4" t="n"/>
       <c r="AA90" s="4" t="n"/>
       <c r="AB90" s="4" t="n"/>
       <c r="AC90" s="4" t="n"/>
+      <c r="AD90" s="4" t="n"/>
+      <c r="AE90" s="4" t="n"/>
+      <c r="AF90" s="4" t="n"/>
+      <c r="AG90" s="4" t="n"/>
+      <c r="AH90" s="4" t="n"/>
+      <c r="AI90" s="4" t="n"/>
+      <c r="AJ90" s="4" t="n"/>
+      <c r="AK90" s="4" t="n"/>
+      <c r="AL90" s="4" t="n"/>
+      <c r="AM90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9281,12 +10943,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X91" s="4" t="n"/>
-      <c r="Y91" s="4" t="n"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z91" s="4" t="n"/>
       <c r="AA91" s="4" t="n"/>
       <c r="AB91" s="4" t="n"/>
       <c r="AC91" s="4" t="n"/>
+      <c r="AD91" s="4" t="n"/>
+      <c r="AE91" s="4" t="n"/>
+      <c r="AF91" s="4" t="n"/>
+      <c r="AG91" s="4" t="n"/>
+      <c r="AH91" s="4" t="n"/>
+      <c r="AI91" s="4" t="n"/>
+      <c r="AJ91" s="4" t="n"/>
+      <c r="AK91" s="4" t="n"/>
+      <c r="AL91" s="4" t="n"/>
+      <c r="AM91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9377,12 +11057,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X92" s="4" t="n"/>
-      <c r="Y92" s="4" t="n"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z92" s="4" t="n"/>
       <c r="AA92" s="4" t="n"/>
       <c r="AB92" s="4" t="n"/>
       <c r="AC92" s="4" t="n"/>
+      <c r="AD92" s="4" t="n"/>
+      <c r="AE92" s="4" t="n"/>
+      <c r="AF92" s="4" t="n"/>
+      <c r="AG92" s="4" t="n"/>
+      <c r="AH92" s="4" t="n"/>
+      <c r="AI92" s="4" t="n"/>
+      <c r="AJ92" s="4" t="n"/>
+      <c r="AK92" s="4" t="n"/>
+      <c r="AL92" s="4" t="n"/>
+      <c r="AM92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9473,12 +11171,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X93" s="4" t="n"/>
-      <c r="Y93" s="4" t="n"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z93" s="4" t="n"/>
       <c r="AA93" s="4" t="n"/>
       <c r="AB93" s="4" t="n"/>
       <c r="AC93" s="4" t="n"/>
+      <c r="AD93" s="4" t="n"/>
+      <c r="AE93" s="4" t="n"/>
+      <c r="AF93" s="4" t="n"/>
+      <c r="AG93" s="4" t="n"/>
+      <c r="AH93" s="4" t="n"/>
+      <c r="AI93" s="4" t="n"/>
+      <c r="AJ93" s="4" t="n"/>
+      <c r="AK93" s="4" t="n"/>
+      <c r="AL93" s="4" t="n"/>
+      <c r="AM93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9569,12 +11285,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X94" s="4" t="n"/>
-      <c r="Y94" s="4" t="n"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z94" s="4" t="n"/>
       <c r="AA94" s="4" t="n"/>
       <c r="AB94" s="4" t="n"/>
       <c r="AC94" s="4" t="n"/>
+      <c r="AD94" s="4" t="n"/>
+      <c r="AE94" s="4" t="n"/>
+      <c r="AF94" s="4" t="n"/>
+      <c r="AG94" s="4" t="n"/>
+      <c r="AH94" s="4" t="n"/>
+      <c r="AI94" s="4" t="n"/>
+      <c r="AJ94" s="4" t="n"/>
+      <c r="AK94" s="4" t="n"/>
+      <c r="AL94" s="4" t="n"/>
+      <c r="AM94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9665,12 +11399,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X95" s="4" t="n"/>
-      <c r="Y95" s="4" t="n"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z95" s="4" t="n"/>
       <c r="AA95" s="4" t="n"/>
       <c r="AB95" s="4" t="n"/>
       <c r="AC95" s="4" t="n"/>
+      <c r="AD95" s="4" t="n"/>
+      <c r="AE95" s="4" t="n"/>
+      <c r="AF95" s="4" t="n"/>
+      <c r="AG95" s="4" t="n"/>
+      <c r="AH95" s="4" t="n"/>
+      <c r="AI95" s="4" t="n"/>
+      <c r="AJ95" s="4" t="n"/>
+      <c r="AK95" s="4" t="n"/>
+      <c r="AL95" s="4" t="n"/>
+      <c r="AM95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9761,12 +11513,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X96" s="4" t="n"/>
-      <c r="Y96" s="4" t="n"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z96" s="4" t="n"/>
       <c r="AA96" s="4" t="n"/>
       <c r="AB96" s="4" t="n"/>
       <c r="AC96" s="4" t="n"/>
+      <c r="AD96" s="4" t="n"/>
+      <c r="AE96" s="4" t="n"/>
+      <c r="AF96" s="4" t="n"/>
+      <c r="AG96" s="4" t="n"/>
+      <c r="AH96" s="4" t="n"/>
+      <c r="AI96" s="4" t="n"/>
+      <c r="AJ96" s="4" t="n"/>
+      <c r="AK96" s="4" t="n"/>
+      <c r="AL96" s="4" t="n"/>
+      <c r="AM96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9857,12 +11627,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X97" s="4" t="n"/>
-      <c r="Y97" s="4" t="n"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z97" s="4" t="n"/>
       <c r="AA97" s="4" t="n"/>
       <c r="AB97" s="4" t="n"/>
       <c r="AC97" s="4" t="n"/>
+      <c r="AD97" s="4" t="n"/>
+      <c r="AE97" s="4" t="n"/>
+      <c r="AF97" s="4" t="n"/>
+      <c r="AG97" s="4" t="n"/>
+      <c r="AH97" s="4" t="n"/>
+      <c r="AI97" s="4" t="n"/>
+      <c r="AJ97" s="4" t="n"/>
+      <c r="AK97" s="4" t="n"/>
+      <c r="AL97" s="4" t="n"/>
+      <c r="AM97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9953,12 +11741,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X98" s="4" t="n"/>
-      <c r="Y98" s="4" t="n"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z98" s="4" t="n"/>
       <c r="AA98" s="4" t="n"/>
       <c r="AB98" s="4" t="n"/>
       <c r="AC98" s="4" t="n"/>
+      <c r="AD98" s="4" t="n"/>
+      <c r="AE98" s="4" t="n"/>
+      <c r="AF98" s="4" t="n"/>
+      <c r="AG98" s="4" t="n"/>
+      <c r="AH98" s="4" t="n"/>
+      <c r="AI98" s="4" t="n"/>
+      <c r="AJ98" s="4" t="n"/>
+      <c r="AK98" s="4" t="n"/>
+      <c r="AL98" s="4" t="n"/>
+      <c r="AM98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -10049,12 +11855,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X99" s="4" t="n"/>
-      <c r="Y99" s="4" t="n"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z99" s="4" t="n"/>
       <c r="AA99" s="4" t="n"/>
       <c r="AB99" s="4" t="n"/>
       <c r="AC99" s="4" t="n"/>
+      <c r="AD99" s="4" t="n"/>
+      <c r="AE99" s="4" t="n"/>
+      <c r="AF99" s="4" t="n"/>
+      <c r="AG99" s="4" t="n"/>
+      <c r="AH99" s="4" t="n"/>
+      <c r="AI99" s="4" t="n"/>
+      <c r="AJ99" s="4" t="n"/>
+      <c r="AK99" s="4" t="n"/>
+      <c r="AL99" s="4" t="n"/>
+      <c r="AM99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -10145,12 +11969,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X100" s="4" t="n"/>
-      <c r="Y100" s="4" t="n"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z100" s="4" t="n"/>
       <c r="AA100" s="4" t="n"/>
       <c r="AB100" s="4" t="n"/>
       <c r="AC100" s="4" t="n"/>
+      <c r="AD100" s="4" t="n"/>
+      <c r="AE100" s="4" t="n"/>
+      <c r="AF100" s="4" t="n"/>
+      <c r="AG100" s="4" t="n"/>
+      <c r="AH100" s="4" t="n"/>
+      <c r="AI100" s="4" t="n"/>
+      <c r="AJ100" s="4" t="n"/>
+      <c r="AK100" s="4" t="n"/>
+      <c r="AL100" s="4" t="n"/>
+      <c r="AM100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -10241,12 +12083,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X101" s="4" t="n"/>
-      <c r="Y101" s="4" t="n"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z101" s="4" t="n"/>
       <c r="AA101" s="4" t="n"/>
       <c r="AB101" s="4" t="n"/>
       <c r="AC101" s="4" t="n"/>
+      <c r="AD101" s="4" t="n"/>
+      <c r="AE101" s="4" t="n"/>
+      <c r="AF101" s="4" t="n"/>
+      <c r="AG101" s="4" t="n"/>
+      <c r="AH101" s="4" t="n"/>
+      <c r="AI101" s="4" t="n"/>
+      <c r="AJ101" s="4" t="n"/>
+      <c r="AK101" s="4" t="n"/>
+      <c r="AL101" s="4" t="n"/>
+      <c r="AM101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -10337,12 +12197,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X102" s="4" t="n"/>
-      <c r="Y102" s="4" t="n"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z102" s="4" t="n"/>
       <c r="AA102" s="4" t="n"/>
       <c r="AB102" s="4" t="n"/>
       <c r="AC102" s="4" t="n"/>
+      <c r="AD102" s="4" t="n"/>
+      <c r="AE102" s="4" t="n"/>
+      <c r="AF102" s="4" t="n"/>
+      <c r="AG102" s="4" t="n"/>
+      <c r="AH102" s="4" t="n"/>
+      <c r="AI102" s="4" t="n"/>
+      <c r="AJ102" s="4" t="n"/>
+      <c r="AK102" s="4" t="n"/>
+      <c r="AL102" s="4" t="n"/>
+      <c r="AM102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -10433,12 +12311,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X103" s="4" t="n"/>
-      <c r="Y103" s="4" t="n"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z103" s="4" t="n"/>
       <c r="AA103" s="4" t="n"/>
       <c r="AB103" s="4" t="n"/>
       <c r="AC103" s="4" t="n"/>
+      <c r="AD103" s="4" t="n"/>
+      <c r="AE103" s="4" t="n"/>
+      <c r="AF103" s="4" t="n"/>
+      <c r="AG103" s="4" t="n"/>
+      <c r="AH103" s="4" t="n"/>
+      <c r="AI103" s="4" t="n"/>
+      <c r="AJ103" s="4" t="n"/>
+      <c r="AK103" s="4" t="n"/>
+      <c r="AL103" s="4" t="n"/>
+      <c r="AM103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -10529,12 +12425,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X104" s="4" t="n"/>
-      <c r="Y104" s="4" t="n"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z104" s="4" t="n"/>
       <c r="AA104" s="4" t="n"/>
       <c r="AB104" s="4" t="n"/>
       <c r="AC104" s="4" t="n"/>
+      <c r="AD104" s="4" t="n"/>
+      <c r="AE104" s="4" t="n"/>
+      <c r="AF104" s="4" t="n"/>
+      <c r="AG104" s="4" t="n"/>
+      <c r="AH104" s="4" t="n"/>
+      <c r="AI104" s="4" t="n"/>
+      <c r="AJ104" s="4" t="n"/>
+      <c r="AK104" s="4" t="n"/>
+      <c r="AL104" s="4" t="n"/>
+      <c r="AM104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -10625,12 +12539,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X105" s="4" t="n"/>
-      <c r="Y105" s="4" t="n"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z105" s="4" t="n"/>
       <c r="AA105" s="4" t="n"/>
       <c r="AB105" s="4" t="n"/>
       <c r="AC105" s="4" t="n"/>
+      <c r="AD105" s="4" t="n"/>
+      <c r="AE105" s="4" t="n"/>
+      <c r="AF105" s="4" t="n"/>
+      <c r="AG105" s="4" t="n"/>
+      <c r="AH105" s="4" t="n"/>
+      <c r="AI105" s="4" t="n"/>
+      <c r="AJ105" s="4" t="n"/>
+      <c r="AK105" s="4" t="n"/>
+      <c r="AL105" s="4" t="n"/>
+      <c r="AM105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -10721,12 +12653,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X106" s="4" t="n"/>
-      <c r="Y106" s="4" t="n"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z106" s="4" t="n"/>
       <c r="AA106" s="4" t="n"/>
       <c r="AB106" s="4" t="n"/>
       <c r="AC106" s="4" t="n"/>
+      <c r="AD106" s="4" t="n"/>
+      <c r="AE106" s="4" t="n"/>
+      <c r="AF106" s="4" t="n"/>
+      <c r="AG106" s="4" t="n"/>
+      <c r="AH106" s="4" t="n"/>
+      <c r="AI106" s="4" t="n"/>
+      <c r="AJ106" s="4" t="n"/>
+      <c r="AK106" s="4" t="n"/>
+      <c r="AL106" s="4" t="n"/>
+      <c r="AM106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -10817,12 +12767,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X107" s="4" t="n"/>
-      <c r="Y107" s="4" t="n"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z107" s="4" t="n"/>
       <c r="AA107" s="4" t="n"/>
       <c r="AB107" s="4" t="n"/>
       <c r="AC107" s="4" t="n"/>
+      <c r="AD107" s="4" t="n"/>
+      <c r="AE107" s="4" t="n"/>
+      <c r="AF107" s="4" t="n"/>
+      <c r="AG107" s="4" t="n"/>
+      <c r="AH107" s="4" t="n"/>
+      <c r="AI107" s="4" t="n"/>
+      <c r="AJ107" s="4" t="n"/>
+      <c r="AK107" s="4" t="n"/>
+      <c r="AL107" s="4" t="n"/>
+      <c r="AM107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -10913,12 +12881,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X108" s="4" t="n"/>
-      <c r="Y108" s="4" t="n"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z108" s="4" t="n"/>
       <c r="AA108" s="4" t="n"/>
       <c r="AB108" s="4" t="n"/>
       <c r="AC108" s="4" t="n"/>
+      <c r="AD108" s="4" t="n"/>
+      <c r="AE108" s="4" t="n"/>
+      <c r="AF108" s="4" t="n"/>
+      <c r="AG108" s="4" t="n"/>
+      <c r="AH108" s="4" t="n"/>
+      <c r="AI108" s="4" t="n"/>
+      <c r="AJ108" s="4" t="n"/>
+      <c r="AK108" s="4" t="n"/>
+      <c r="AL108" s="4" t="n"/>
+      <c r="AM108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -11009,12 +12995,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X109" s="4" t="n"/>
-      <c r="Y109" s="4" t="n"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z109" s="4" t="n"/>
       <c r="AA109" s="4" t="n"/>
       <c r="AB109" s="4" t="n"/>
       <c r="AC109" s="4" t="n"/>
+      <c r="AD109" s="4" t="n"/>
+      <c r="AE109" s="4" t="n"/>
+      <c r="AF109" s="4" t="n"/>
+      <c r="AG109" s="4" t="n"/>
+      <c r="AH109" s="4" t="n"/>
+      <c r="AI109" s="4" t="n"/>
+      <c r="AJ109" s="4" t="n"/>
+      <c r="AK109" s="4" t="n"/>
+      <c r="AL109" s="4" t="n"/>
+      <c r="AM109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -11105,12 +13109,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X110" s="4" t="n"/>
-      <c r="Y110" s="4" t="n"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z110" s="4" t="n"/>
       <c r="AA110" s="4" t="n"/>
       <c r="AB110" s="4" t="n"/>
       <c r="AC110" s="4" t="n"/>
+      <c r="AD110" s="4" t="n"/>
+      <c r="AE110" s="4" t="n"/>
+      <c r="AF110" s="4" t="n"/>
+      <c r="AG110" s="4" t="n"/>
+      <c r="AH110" s="4" t="n"/>
+      <c r="AI110" s="4" t="n"/>
+      <c r="AJ110" s="4" t="n"/>
+      <c r="AK110" s="4" t="n"/>
+      <c r="AL110" s="4" t="n"/>
+      <c r="AM110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -11201,12 +13223,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X111" s="4" t="n"/>
-      <c r="Y111" s="4" t="n"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z111" s="4" t="n"/>
       <c r="AA111" s="4" t="n"/>
       <c r="AB111" s="4" t="n"/>
       <c r="AC111" s="4" t="n"/>
+      <c r="AD111" s="4" t="n"/>
+      <c r="AE111" s="4" t="n"/>
+      <c r="AF111" s="4" t="n"/>
+      <c r="AG111" s="4" t="n"/>
+      <c r="AH111" s="4" t="n"/>
+      <c r="AI111" s="4" t="n"/>
+      <c r="AJ111" s="4" t="n"/>
+      <c r="AK111" s="4" t="n"/>
+      <c r="AL111" s="4" t="n"/>
+      <c r="AM111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -11297,12 +13337,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X112" s="4" t="n"/>
-      <c r="Y112" s="4" t="n"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z112" s="4" t="n"/>
       <c r="AA112" s="4" t="n"/>
       <c r="AB112" s="4" t="n"/>
       <c r="AC112" s="4" t="n"/>
+      <c r="AD112" s="4" t="n"/>
+      <c r="AE112" s="4" t="n"/>
+      <c r="AF112" s="4" t="n"/>
+      <c r="AG112" s="4" t="n"/>
+      <c r="AH112" s="4" t="n"/>
+      <c r="AI112" s="4" t="n"/>
+      <c r="AJ112" s="4" t="n"/>
+      <c r="AK112" s="4" t="n"/>
+      <c r="AL112" s="4" t="n"/>
+      <c r="AM112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -11393,12 +13451,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X113" s="4" t="n"/>
-      <c r="Y113" s="4" t="n"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z113" s="4" t="n"/>
       <c r="AA113" s="4" t="n"/>
       <c r="AB113" s="4" t="n"/>
       <c r="AC113" s="4" t="n"/>
+      <c r="AD113" s="4" t="n"/>
+      <c r="AE113" s="4" t="n"/>
+      <c r="AF113" s="4" t="n"/>
+      <c r="AG113" s="4" t="n"/>
+      <c r="AH113" s="4" t="n"/>
+      <c r="AI113" s="4" t="n"/>
+      <c r="AJ113" s="4" t="n"/>
+      <c r="AK113" s="4" t="n"/>
+      <c r="AL113" s="4" t="n"/>
+      <c r="AM113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -11489,12 +13565,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X114" s="4" t="n"/>
-      <c r="Y114" s="4" t="n"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z114" s="4" t="n"/>
       <c r="AA114" s="4" t="n"/>
       <c r="AB114" s="4" t="n"/>
       <c r="AC114" s="4" t="n"/>
+      <c r="AD114" s="4" t="n"/>
+      <c r="AE114" s="4" t="n"/>
+      <c r="AF114" s="4" t="n"/>
+      <c r="AG114" s="4" t="n"/>
+      <c r="AH114" s="4" t="n"/>
+      <c r="AI114" s="4" t="n"/>
+      <c r="AJ114" s="4" t="n"/>
+      <c r="AK114" s="4" t="n"/>
+      <c r="AL114" s="4" t="n"/>
+      <c r="AM114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -11585,12 +13679,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X115" s="4" t="n"/>
-      <c r="Y115" s="4" t="n"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z115" s="4" t="n"/>
       <c r="AA115" s="4" t="n"/>
       <c r="AB115" s="4" t="n"/>
       <c r="AC115" s="4" t="n"/>
+      <c r="AD115" s="4" t="n"/>
+      <c r="AE115" s="4" t="n"/>
+      <c r="AF115" s="4" t="n"/>
+      <c r="AG115" s="4" t="n"/>
+      <c r="AH115" s="4" t="n"/>
+      <c r="AI115" s="4" t="n"/>
+      <c r="AJ115" s="4" t="n"/>
+      <c r="AK115" s="4" t="n"/>
+      <c r="AL115" s="4" t="n"/>
+      <c r="AM115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -11681,12 +13793,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X116" s="4" t="n"/>
-      <c r="Y116" s="4" t="n"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z116" s="4" t="n"/>
       <c r="AA116" s="4" t="n"/>
       <c r="AB116" s="4" t="n"/>
       <c r="AC116" s="4" t="n"/>
+      <c r="AD116" s="4" t="n"/>
+      <c r="AE116" s="4" t="n"/>
+      <c r="AF116" s="4" t="n"/>
+      <c r="AG116" s="4" t="n"/>
+      <c r="AH116" s="4" t="n"/>
+      <c r="AI116" s="4" t="n"/>
+      <c r="AJ116" s="4" t="n"/>
+      <c r="AK116" s="4" t="n"/>
+      <c r="AL116" s="4" t="n"/>
+      <c r="AM116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -11777,12 +13907,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X117" s="4" t="n"/>
-      <c r="Y117" s="4" t="n"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z117" s="4" t="n"/>
       <c r="AA117" s="4" t="n"/>
       <c r="AB117" s="4" t="n"/>
       <c r="AC117" s="4" t="n"/>
+      <c r="AD117" s="4" t="n"/>
+      <c r="AE117" s="4" t="n"/>
+      <c r="AF117" s="4" t="n"/>
+      <c r="AG117" s="4" t="n"/>
+      <c r="AH117" s="4" t="n"/>
+      <c r="AI117" s="4" t="n"/>
+      <c r="AJ117" s="4" t="n"/>
+      <c r="AK117" s="4" t="n"/>
+      <c r="AL117" s="4" t="n"/>
+      <c r="AM117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -11873,12 +14021,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X118" s="4" t="n"/>
-      <c r="Y118" s="4" t="n"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z118" s="4" t="n"/>
       <c r="AA118" s="4" t="n"/>
       <c r="AB118" s="4" t="n"/>
       <c r="AC118" s="4" t="n"/>
+      <c r="AD118" s="4" t="n"/>
+      <c r="AE118" s="4" t="n"/>
+      <c r="AF118" s="4" t="n"/>
+      <c r="AG118" s="4" t="n"/>
+      <c r="AH118" s="4" t="n"/>
+      <c r="AI118" s="4" t="n"/>
+      <c r="AJ118" s="4" t="n"/>
+      <c r="AK118" s="4" t="n"/>
+      <c r="AL118" s="4" t="n"/>
+      <c r="AM118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -11969,12 +14135,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X119" s="4" t="n"/>
-      <c r="Y119" s="4" t="n"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z119" s="4" t="n"/>
       <c r="AA119" s="4" t="n"/>
       <c r="AB119" s="4" t="n"/>
       <c r="AC119" s="4" t="n"/>
+      <c r="AD119" s="4" t="n"/>
+      <c r="AE119" s="4" t="n"/>
+      <c r="AF119" s="4" t="n"/>
+      <c r="AG119" s="4" t="n"/>
+      <c r="AH119" s="4" t="n"/>
+      <c r="AI119" s="4" t="n"/>
+      <c r="AJ119" s="4" t="n"/>
+      <c r="AK119" s="4" t="n"/>
+      <c r="AL119" s="4" t="n"/>
+      <c r="AM119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -12065,12 +14249,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X120" s="4" t="n"/>
-      <c r="Y120" s="4" t="n"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z120" s="4" t="n"/>
       <c r="AA120" s="4" t="n"/>
       <c r="AB120" s="4" t="n"/>
       <c r="AC120" s="4" t="n"/>
+      <c r="AD120" s="4" t="n"/>
+      <c r="AE120" s="4" t="n"/>
+      <c r="AF120" s="4" t="n"/>
+      <c r="AG120" s="4" t="n"/>
+      <c r="AH120" s="4" t="n"/>
+      <c r="AI120" s="4" t="n"/>
+      <c r="AJ120" s="4" t="n"/>
+      <c r="AK120" s="4" t="n"/>
+      <c r="AL120" s="4" t="n"/>
+      <c r="AM120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -12161,12 +14363,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X121" s="4" t="n"/>
-      <c r="Y121" s="4" t="n"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z121" s="4" t="n"/>
       <c r="AA121" s="4" t="n"/>
       <c r="AB121" s="4" t="n"/>
       <c r="AC121" s="4" t="n"/>
+      <c r="AD121" s="4" t="n"/>
+      <c r="AE121" s="4" t="n"/>
+      <c r="AF121" s="4" t="n"/>
+      <c r="AG121" s="4" t="n"/>
+      <c r="AH121" s="4" t="n"/>
+      <c r="AI121" s="4" t="n"/>
+      <c r="AJ121" s="4" t="n"/>
+      <c r="AK121" s="4" t="n"/>
+      <c r="AL121" s="4" t="n"/>
+      <c r="AM121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -12257,12 +14477,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X122" s="4" t="n"/>
-      <c r="Y122" s="4" t="n"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z122" s="4" t="n"/>
       <c r="AA122" s="4" t="n"/>
       <c r="AB122" s="4" t="n"/>
       <c r="AC122" s="4" t="n"/>
+      <c r="AD122" s="4" t="n"/>
+      <c r="AE122" s="4" t="n"/>
+      <c r="AF122" s="4" t="n"/>
+      <c r="AG122" s="4" t="n"/>
+      <c r="AH122" s="4" t="n"/>
+      <c r="AI122" s="4" t="n"/>
+      <c r="AJ122" s="4" t="n"/>
+      <c r="AK122" s="4" t="n"/>
+      <c r="AL122" s="4" t="n"/>
+      <c r="AM122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -12353,12 +14591,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X123" s="4" t="n"/>
-      <c r="Y123" s="4" t="n"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z123" s="4" t="n"/>
       <c r="AA123" s="4" t="n"/>
       <c r="AB123" s="4" t="n"/>
       <c r="AC123" s="4" t="n"/>
+      <c r="AD123" s="4" t="n"/>
+      <c r="AE123" s="4" t="n"/>
+      <c r="AF123" s="4" t="n"/>
+      <c r="AG123" s="4" t="n"/>
+      <c r="AH123" s="4" t="n"/>
+      <c r="AI123" s="4" t="n"/>
+      <c r="AJ123" s="4" t="n"/>
+      <c r="AK123" s="4" t="n"/>
+      <c r="AL123" s="4" t="n"/>
+      <c r="AM123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -12449,12 +14705,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X124" s="4" t="n"/>
-      <c r="Y124" s="4" t="n"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z124" s="4" t="n"/>
       <c r="AA124" s="4" t="n"/>
       <c r="AB124" s="4" t="n"/>
       <c r="AC124" s="4" t="n"/>
+      <c r="AD124" s="4" t="n"/>
+      <c r="AE124" s="4" t="n"/>
+      <c r="AF124" s="4" t="n"/>
+      <c r="AG124" s="4" t="n"/>
+      <c r="AH124" s="4" t="n"/>
+      <c r="AI124" s="4" t="n"/>
+      <c r="AJ124" s="4" t="n"/>
+      <c r="AK124" s="4" t="n"/>
+      <c r="AL124" s="4" t="n"/>
+      <c r="AM124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -12545,12 +14819,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X125" s="4" t="n"/>
-      <c r="Y125" s="4" t="n"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z125" s="4" t="n"/>
       <c r="AA125" s="4" t="n"/>
       <c r="AB125" s="4" t="n"/>
       <c r="AC125" s="4" t="n"/>
+      <c r="AD125" s="4" t="n"/>
+      <c r="AE125" s="4" t="n"/>
+      <c r="AF125" s="4" t="n"/>
+      <c r="AG125" s="4" t="n"/>
+      <c r="AH125" s="4" t="n"/>
+      <c r="AI125" s="4" t="n"/>
+      <c r="AJ125" s="4" t="n"/>
+      <c r="AK125" s="4" t="n"/>
+      <c r="AL125" s="4" t="n"/>
+      <c r="AM125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -12641,12 +14933,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X126" s="4" t="n"/>
-      <c r="Y126" s="4" t="n"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z126" s="4" t="n"/>
       <c r="AA126" s="4" t="n"/>
       <c r="AB126" s="4" t="n"/>
       <c r="AC126" s="4" t="n"/>
+      <c r="AD126" s="4" t="n"/>
+      <c r="AE126" s="4" t="n"/>
+      <c r="AF126" s="4" t="n"/>
+      <c r="AG126" s="4" t="n"/>
+      <c r="AH126" s="4" t="n"/>
+      <c r="AI126" s="4" t="n"/>
+      <c r="AJ126" s="4" t="n"/>
+      <c r="AK126" s="4" t="n"/>
+      <c r="AL126" s="4" t="n"/>
+      <c r="AM126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -12737,12 +15047,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X127" s="4" t="n"/>
-      <c r="Y127" s="4" t="n"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z127" s="4" t="n"/>
       <c r="AA127" s="4" t="n"/>
       <c r="AB127" s="4" t="n"/>
       <c r="AC127" s="4" t="n"/>
+      <c r="AD127" s="4" t="n"/>
+      <c r="AE127" s="4" t="n"/>
+      <c r="AF127" s="4" t="n"/>
+      <c r="AG127" s="4" t="n"/>
+      <c r="AH127" s="4" t="n"/>
+      <c r="AI127" s="4" t="n"/>
+      <c r="AJ127" s="4" t="n"/>
+      <c r="AK127" s="4" t="n"/>
+      <c r="AL127" s="4" t="n"/>
+      <c r="AM127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -12833,12 +15161,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X128" s="4" t="n"/>
-      <c r="Y128" s="4" t="n"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z128" s="4" t="n"/>
       <c r="AA128" s="4" t="n"/>
       <c r="AB128" s="4" t="n"/>
       <c r="AC128" s="4" t="n"/>
+      <c r="AD128" s="4" t="n"/>
+      <c r="AE128" s="4" t="n"/>
+      <c r="AF128" s="4" t="n"/>
+      <c r="AG128" s="4" t="n"/>
+      <c r="AH128" s="4" t="n"/>
+      <c r="AI128" s="4" t="n"/>
+      <c r="AJ128" s="4" t="n"/>
+      <c r="AK128" s="4" t="n"/>
+      <c r="AL128" s="4" t="n"/>
+      <c r="AM128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -12929,12 +15275,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X129" s="4" t="n"/>
-      <c r="Y129" s="4" t="n"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z129" s="4" t="n"/>
       <c r="AA129" s="4" t="n"/>
       <c r="AB129" s="4" t="n"/>
       <c r="AC129" s="4" t="n"/>
+      <c r="AD129" s="4" t="n"/>
+      <c r="AE129" s="4" t="n"/>
+      <c r="AF129" s="4" t="n"/>
+      <c r="AG129" s="4" t="n"/>
+      <c r="AH129" s="4" t="n"/>
+      <c r="AI129" s="4" t="n"/>
+      <c r="AJ129" s="4" t="n"/>
+      <c r="AK129" s="4" t="n"/>
+      <c r="AL129" s="4" t="n"/>
+      <c r="AM129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -13025,12 +15389,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X130" s="4" t="n"/>
-      <c r="Y130" s="4" t="n"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z130" s="4" t="n"/>
       <c r="AA130" s="4" t="n"/>
       <c r="AB130" s="4" t="n"/>
       <c r="AC130" s="4" t="n"/>
+      <c r="AD130" s="4" t="n"/>
+      <c r="AE130" s="4" t="n"/>
+      <c r="AF130" s="4" t="n"/>
+      <c r="AG130" s="4" t="n"/>
+      <c r="AH130" s="4" t="n"/>
+      <c r="AI130" s="4" t="n"/>
+      <c r="AJ130" s="4" t="n"/>
+      <c r="AK130" s="4" t="n"/>
+      <c r="AL130" s="4" t="n"/>
+      <c r="AM130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -13121,12 +15503,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X131" s="4" t="n"/>
-      <c r="Y131" s="4" t="n"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z131" s="4" t="n"/>
       <c r="AA131" s="4" t="n"/>
       <c r="AB131" s="4" t="n"/>
       <c r="AC131" s="4" t="n"/>
+      <c r="AD131" s="4" t="n"/>
+      <c r="AE131" s="4" t="n"/>
+      <c r="AF131" s="4" t="n"/>
+      <c r="AG131" s="4" t="n"/>
+      <c r="AH131" s="4" t="n"/>
+      <c r="AI131" s="4" t="n"/>
+      <c r="AJ131" s="4" t="n"/>
+      <c r="AK131" s="4" t="n"/>
+      <c r="AL131" s="4" t="n"/>
+      <c r="AM131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -13217,12 +15617,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X132" s="4" t="n"/>
-      <c r="Y132" s="4" t="n"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z132" s="4" t="n"/>
       <c r="AA132" s="4" t="n"/>
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="4" t="n"/>
+      <c r="AD132" s="4" t="n"/>
+      <c r="AE132" s="4" t="n"/>
+      <c r="AF132" s="4" t="n"/>
+      <c r="AG132" s="4" t="n"/>
+      <c r="AH132" s="4" t="n"/>
+      <c r="AI132" s="4" t="n"/>
+      <c r="AJ132" s="4" t="n"/>
+      <c r="AK132" s="4" t="n"/>
+      <c r="AL132" s="4" t="n"/>
+      <c r="AM132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -13313,12 +15731,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X133" s="4" t="n"/>
-      <c r="Y133" s="4" t="n"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z133" s="4" t="n"/>
       <c r="AA133" s="4" t="n"/>
       <c r="AB133" s="4" t="n"/>
       <c r="AC133" s="4" t="n"/>
+      <c r="AD133" s="4" t="n"/>
+      <c r="AE133" s="4" t="n"/>
+      <c r="AF133" s="4" t="n"/>
+      <c r="AG133" s="4" t="n"/>
+      <c r="AH133" s="4" t="n"/>
+      <c r="AI133" s="4" t="n"/>
+      <c r="AJ133" s="4" t="n"/>
+      <c r="AK133" s="4" t="n"/>
+      <c r="AL133" s="4" t="n"/>
+      <c r="AM133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -13409,12 +15845,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X134" s="4" t="n"/>
-      <c r="Y134" s="4" t="n"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z134" s="4" t="n"/>
       <c r="AA134" s="4" t="n"/>
       <c r="AB134" s="4" t="n"/>
       <c r="AC134" s="4" t="n"/>
+      <c r="AD134" s="4" t="n"/>
+      <c r="AE134" s="4" t="n"/>
+      <c r="AF134" s="4" t="n"/>
+      <c r="AG134" s="4" t="n"/>
+      <c r="AH134" s="4" t="n"/>
+      <c r="AI134" s="4" t="n"/>
+      <c r="AJ134" s="4" t="n"/>
+      <c r="AK134" s="4" t="n"/>
+      <c r="AL134" s="4" t="n"/>
+      <c r="AM134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -13505,12 +15959,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X135" s="4" t="n"/>
-      <c r="Y135" s="4" t="n"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z135" s="4" t="n"/>
       <c r="AA135" s="4" t="n"/>
       <c r="AB135" s="4" t="n"/>
       <c r="AC135" s="4" t="n"/>
+      <c r="AD135" s="4" t="n"/>
+      <c r="AE135" s="4" t="n"/>
+      <c r="AF135" s="4" t="n"/>
+      <c r="AG135" s="4" t="n"/>
+      <c r="AH135" s="4" t="n"/>
+      <c r="AI135" s="4" t="n"/>
+      <c r="AJ135" s="4" t="n"/>
+      <c r="AK135" s="4" t="n"/>
+      <c r="AL135" s="4" t="n"/>
+      <c r="AM135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -13601,12 +16073,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X136" s="4" t="n"/>
-      <c r="Y136" s="4" t="n"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z136" s="4" t="n"/>
       <c r="AA136" s="4" t="n"/>
       <c r="AB136" s="4" t="n"/>
       <c r="AC136" s="4" t="n"/>
+      <c r="AD136" s="4" t="n"/>
+      <c r="AE136" s="4" t="n"/>
+      <c r="AF136" s="4" t="n"/>
+      <c r="AG136" s="4" t="n"/>
+      <c r="AH136" s="4" t="n"/>
+      <c r="AI136" s="4" t="n"/>
+      <c r="AJ136" s="4" t="n"/>
+      <c r="AK136" s="4" t="n"/>
+      <c r="AL136" s="4" t="n"/>
+      <c r="AM136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -13697,12 +16187,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X137" s="4" t="n"/>
-      <c r="Y137" s="4" t="n"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z137" s="4" t="n"/>
       <c r="AA137" s="4" t="n"/>
       <c r="AB137" s="4" t="n"/>
       <c r="AC137" s="4" t="n"/>
+      <c r="AD137" s="4" t="n"/>
+      <c r="AE137" s="4" t="n"/>
+      <c r="AF137" s="4" t="n"/>
+      <c r="AG137" s="4" t="n"/>
+      <c r="AH137" s="4" t="n"/>
+      <c r="AI137" s="4" t="n"/>
+      <c r="AJ137" s="4" t="n"/>
+      <c r="AK137" s="4" t="n"/>
+      <c r="AL137" s="4" t="n"/>
+      <c r="AM137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -13793,12 +16301,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X138" s="4" t="n"/>
-      <c r="Y138" s="4" t="n"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z138" s="4" t="n"/>
       <c r="AA138" s="4" t="n"/>
       <c r="AB138" s="4" t="n"/>
       <c r="AC138" s="4" t="n"/>
+      <c r="AD138" s="4" t="n"/>
+      <c r="AE138" s="4" t="n"/>
+      <c r="AF138" s="4" t="n"/>
+      <c r="AG138" s="4" t="n"/>
+      <c r="AH138" s="4" t="n"/>
+      <c r="AI138" s="4" t="n"/>
+      <c r="AJ138" s="4" t="n"/>
+      <c r="AK138" s="4" t="n"/>
+      <c r="AL138" s="4" t="n"/>
+      <c r="AM138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -13889,12 +16415,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X139" s="4" t="n"/>
-      <c r="Y139" s="4" t="n"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z139" s="4" t="n"/>
       <c r="AA139" s="4" t="n"/>
       <c r="AB139" s="4" t="n"/>
       <c r="AC139" s="4" t="n"/>
+      <c r="AD139" s="4" t="n"/>
+      <c r="AE139" s="4" t="n"/>
+      <c r="AF139" s="4" t="n"/>
+      <c r="AG139" s="4" t="n"/>
+      <c r="AH139" s="4" t="n"/>
+      <c r="AI139" s="4" t="n"/>
+      <c r="AJ139" s="4" t="n"/>
+      <c r="AK139" s="4" t="n"/>
+      <c r="AL139" s="4" t="n"/>
+      <c r="AM139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -13985,12 +16529,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X140" s="4" t="n"/>
-      <c r="Y140" s="4" t="n"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z140" s="4" t="n"/>
       <c r="AA140" s="4" t="n"/>
       <c r="AB140" s="4" t="n"/>
       <c r="AC140" s="4" t="n"/>
+      <c r="AD140" s="4" t="n"/>
+      <c r="AE140" s="4" t="n"/>
+      <c r="AF140" s="4" t="n"/>
+      <c r="AG140" s="4" t="n"/>
+      <c r="AH140" s="4" t="n"/>
+      <c r="AI140" s="4" t="n"/>
+      <c r="AJ140" s="4" t="n"/>
+      <c r="AK140" s="4" t="n"/>
+      <c r="AL140" s="4" t="n"/>
+      <c r="AM140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -14081,12 +16643,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X141" s="4" t="n"/>
-      <c r="Y141" s="4" t="n"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z141" s="4" t="n"/>
       <c r="AA141" s="4" t="n"/>
       <c r="AB141" s="4" t="n"/>
       <c r="AC141" s="4" t="n"/>
+      <c r="AD141" s="4" t="n"/>
+      <c r="AE141" s="4" t="n"/>
+      <c r="AF141" s="4" t="n"/>
+      <c r="AG141" s="4" t="n"/>
+      <c r="AH141" s="4" t="n"/>
+      <c r="AI141" s="4" t="n"/>
+      <c r="AJ141" s="4" t="n"/>
+      <c r="AK141" s="4" t="n"/>
+      <c r="AL141" s="4" t="n"/>
+      <c r="AM141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -14177,12 +16757,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X142" s="4" t="n"/>
-      <c r="Y142" s="4" t="n"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z142" s="4" t="n"/>
       <c r="AA142" s="4" t="n"/>
       <c r="AB142" s="4" t="n"/>
       <c r="AC142" s="4" t="n"/>
+      <c r="AD142" s="4" t="n"/>
+      <c r="AE142" s="4" t="n"/>
+      <c r="AF142" s="4" t="n"/>
+      <c r="AG142" s="4" t="n"/>
+      <c r="AH142" s="4" t="n"/>
+      <c r="AI142" s="4" t="n"/>
+      <c r="AJ142" s="4" t="n"/>
+      <c r="AK142" s="4" t="n"/>
+      <c r="AL142" s="4" t="n"/>
+      <c r="AM142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -14273,12 +16871,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X143" s="4" t="n"/>
-      <c r="Y143" s="4" t="n"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z143" s="4" t="n"/>
       <c r="AA143" s="4" t="n"/>
       <c r="AB143" s="4" t="n"/>
       <c r="AC143" s="4" t="n"/>
+      <c r="AD143" s="4" t="n"/>
+      <c r="AE143" s="4" t="n"/>
+      <c r="AF143" s="4" t="n"/>
+      <c r="AG143" s="4" t="n"/>
+      <c r="AH143" s="4" t="n"/>
+      <c r="AI143" s="4" t="n"/>
+      <c r="AJ143" s="4" t="n"/>
+      <c r="AK143" s="4" t="n"/>
+      <c r="AL143" s="4" t="n"/>
+      <c r="AM143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -14369,12 +16985,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X144" s="4" t="n"/>
-      <c r="Y144" s="4" t="n"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z144" s="4" t="n"/>
       <c r="AA144" s="4" t="n"/>
       <c r="AB144" s="4" t="n"/>
       <c r="AC144" s="4" t="n"/>
+      <c r="AD144" s="4" t="n"/>
+      <c r="AE144" s="4" t="n"/>
+      <c r="AF144" s="4" t="n"/>
+      <c r="AG144" s="4" t="n"/>
+      <c r="AH144" s="4" t="n"/>
+      <c r="AI144" s="4" t="n"/>
+      <c r="AJ144" s="4" t="n"/>
+      <c r="AK144" s="4" t="n"/>
+      <c r="AL144" s="4" t="n"/>
+      <c r="AM144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -14465,12 +17099,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X145" s="4" t="n"/>
-      <c r="Y145" s="4" t="n"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z145" s="4" t="n"/>
       <c r="AA145" s="4" t="n"/>
       <c r="AB145" s="4" t="n"/>
       <c r="AC145" s="4" t="n"/>
+      <c r="AD145" s="4" t="n"/>
+      <c r="AE145" s="4" t="n"/>
+      <c r="AF145" s="4" t="n"/>
+      <c r="AG145" s="4" t="n"/>
+      <c r="AH145" s="4" t="n"/>
+      <c r="AI145" s="4" t="n"/>
+      <c r="AJ145" s="4" t="n"/>
+      <c r="AK145" s="4" t="n"/>
+      <c r="AL145" s="4" t="n"/>
+      <c r="AM145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -14561,12 +17213,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X146" s="4" t="n"/>
-      <c r="Y146" s="4" t="n"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z146" s="4" t="n"/>
       <c r="AA146" s="4" t="n"/>
       <c r="AB146" s="4" t="n"/>
       <c r="AC146" s="4" t="n"/>
+      <c r="AD146" s="4" t="n"/>
+      <c r="AE146" s="4" t="n"/>
+      <c r="AF146" s="4" t="n"/>
+      <c r="AG146" s="4" t="n"/>
+      <c r="AH146" s="4" t="n"/>
+      <c r="AI146" s="4" t="n"/>
+      <c r="AJ146" s="4" t="n"/>
+      <c r="AK146" s="4" t="n"/>
+      <c r="AL146" s="4" t="n"/>
+      <c r="AM146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -14657,12 +17327,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X147" s="4" t="n"/>
-      <c r="Y147" s="4" t="n"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z147" s="4" t="n"/>
       <c r="AA147" s="4" t="n"/>
       <c r="AB147" s="4" t="n"/>
       <c r="AC147" s="4" t="n"/>
+      <c r="AD147" s="4" t="n"/>
+      <c r="AE147" s="4" t="n"/>
+      <c r="AF147" s="4" t="n"/>
+      <c r="AG147" s="4" t="n"/>
+      <c r="AH147" s="4" t="n"/>
+      <c r="AI147" s="4" t="n"/>
+      <c r="AJ147" s="4" t="n"/>
+      <c r="AK147" s="4" t="n"/>
+      <c r="AL147" s="4" t="n"/>
+      <c r="AM147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -14753,12 +17441,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X148" s="4" t="n"/>
-      <c r="Y148" s="4" t="n"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z148" s="4" t="n"/>
       <c r="AA148" s="4" t="n"/>
       <c r="AB148" s="4" t="n"/>
       <c r="AC148" s="4" t="n"/>
+      <c r="AD148" s="4" t="n"/>
+      <c r="AE148" s="4" t="n"/>
+      <c r="AF148" s="4" t="n"/>
+      <c r="AG148" s="4" t="n"/>
+      <c r="AH148" s="4" t="n"/>
+      <c r="AI148" s="4" t="n"/>
+      <c r="AJ148" s="4" t="n"/>
+      <c r="AK148" s="4" t="n"/>
+      <c r="AL148" s="4" t="n"/>
+      <c r="AM148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -14849,12 +17555,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X149" s="4" t="n"/>
-      <c r="Y149" s="4" t="n"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z149" s="4" t="n"/>
       <c r="AA149" s="4" t="n"/>
       <c r="AB149" s="4" t="n"/>
       <c r="AC149" s="4" t="n"/>
+      <c r="AD149" s="4" t="n"/>
+      <c r="AE149" s="4" t="n"/>
+      <c r="AF149" s="4" t="n"/>
+      <c r="AG149" s="4" t="n"/>
+      <c r="AH149" s="4" t="n"/>
+      <c r="AI149" s="4" t="n"/>
+      <c r="AJ149" s="4" t="n"/>
+      <c r="AK149" s="4" t="n"/>
+      <c r="AL149" s="4" t="n"/>
+      <c r="AM149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -14945,12 +17669,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X150" s="4" t="n"/>
-      <c r="Y150" s="4" t="n"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z150" s="4" t="n"/>
       <c r="AA150" s="4" t="n"/>
       <c r="AB150" s="4" t="n"/>
       <c r="AC150" s="4" t="n"/>
+      <c r="AD150" s="4" t="n"/>
+      <c r="AE150" s="4" t="n"/>
+      <c r="AF150" s="4" t="n"/>
+      <c r="AG150" s="4" t="n"/>
+      <c r="AH150" s="4" t="n"/>
+      <c r="AI150" s="4" t="n"/>
+      <c r="AJ150" s="4" t="n"/>
+      <c r="AK150" s="4" t="n"/>
+      <c r="AL150" s="4" t="n"/>
+      <c r="AM150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -15041,12 +17783,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X151" s="4" t="n"/>
-      <c r="Y151" s="4" t="n"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z151" s="4" t="n"/>
       <c r="AA151" s="4" t="n"/>
       <c r="AB151" s="4" t="n"/>
       <c r="AC151" s="4" t="n"/>
+      <c r="AD151" s="4" t="n"/>
+      <c r="AE151" s="4" t="n"/>
+      <c r="AF151" s="4" t="n"/>
+      <c r="AG151" s="4" t="n"/>
+      <c r="AH151" s="4" t="n"/>
+      <c r="AI151" s="4" t="n"/>
+      <c r="AJ151" s="4" t="n"/>
+      <c r="AK151" s="4" t="n"/>
+      <c r="AL151" s="4" t="n"/>
+      <c r="AM151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -15137,12 +17897,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X152" s="4" t="n"/>
-      <c r="Y152" s="4" t="n"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z152" s="4" t="n"/>
       <c r="AA152" s="4" t="n"/>
       <c r="AB152" s="4" t="n"/>
       <c r="AC152" s="4" t="n"/>
+      <c r="AD152" s="4" t="n"/>
+      <c r="AE152" s="4" t="n"/>
+      <c r="AF152" s="4" t="n"/>
+      <c r="AG152" s="4" t="n"/>
+      <c r="AH152" s="4" t="n"/>
+      <c r="AI152" s="4" t="n"/>
+      <c r="AJ152" s="4" t="n"/>
+      <c r="AK152" s="4" t="n"/>
+      <c r="AL152" s="4" t="n"/>
+      <c r="AM152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -15233,12 +18011,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X153" s="4" t="n"/>
-      <c r="Y153" s="4" t="n"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z153" s="4" t="n"/>
       <c r="AA153" s="4" t="n"/>
       <c r="AB153" s="4" t="n"/>
       <c r="AC153" s="4" t="n"/>
+      <c r="AD153" s="4" t="n"/>
+      <c r="AE153" s="4" t="n"/>
+      <c r="AF153" s="4" t="n"/>
+      <c r="AG153" s="4" t="n"/>
+      <c r="AH153" s="4" t="n"/>
+      <c r="AI153" s="4" t="n"/>
+      <c r="AJ153" s="4" t="n"/>
+      <c r="AK153" s="4" t="n"/>
+      <c r="AL153" s="4" t="n"/>
+      <c r="AM153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -15329,12 +18125,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X154" s="4" t="n"/>
-      <c r="Y154" s="4" t="n"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z154" s="4" t="n"/>
       <c r="AA154" s="4" t="n"/>
       <c r="AB154" s="4" t="n"/>
       <c r="AC154" s="4" t="n"/>
+      <c r="AD154" s="4" t="n"/>
+      <c r="AE154" s="4" t="n"/>
+      <c r="AF154" s="4" t="n"/>
+      <c r="AG154" s="4" t="n"/>
+      <c r="AH154" s="4" t="n"/>
+      <c r="AI154" s="4" t="n"/>
+      <c r="AJ154" s="4" t="n"/>
+      <c r="AK154" s="4" t="n"/>
+      <c r="AL154" s="4" t="n"/>
+      <c r="AM154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -15425,12 +18239,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X155" s="4" t="n"/>
-      <c r="Y155" s="4" t="n"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z155" s="4" t="n"/>
       <c r="AA155" s="4" t="n"/>
       <c r="AB155" s="4" t="n"/>
       <c r="AC155" s="4" t="n"/>
+      <c r="AD155" s="4" t="n"/>
+      <c r="AE155" s="4" t="n"/>
+      <c r="AF155" s="4" t="n"/>
+      <c r="AG155" s="4" t="n"/>
+      <c r="AH155" s="4" t="n"/>
+      <c r="AI155" s="4" t="n"/>
+      <c r="AJ155" s="4" t="n"/>
+      <c r="AK155" s="4" t="n"/>
+      <c r="AL155" s="4" t="n"/>
+      <c r="AM155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -15521,12 +18353,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X156" s="4" t="n"/>
-      <c r="Y156" s="4" t="n"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z156" s="4" t="n"/>
       <c r="AA156" s="4" t="n"/>
       <c r="AB156" s="4" t="n"/>
       <c r="AC156" s="4" t="n"/>
+      <c r="AD156" s="4" t="n"/>
+      <c r="AE156" s="4" t="n"/>
+      <c r="AF156" s="4" t="n"/>
+      <c r="AG156" s="4" t="n"/>
+      <c r="AH156" s="4" t="n"/>
+      <c r="AI156" s="4" t="n"/>
+      <c r="AJ156" s="4" t="n"/>
+      <c r="AK156" s="4" t="n"/>
+      <c r="AL156" s="4" t="n"/>
+      <c r="AM156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -15617,12 +18467,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X157" s="4" t="n"/>
-      <c r="Y157" s="4" t="n"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z157" s="4" t="n"/>
       <c r="AA157" s="4" t="n"/>
       <c r="AB157" s="4" t="n"/>
       <c r="AC157" s="4" t="n"/>
+      <c r="AD157" s="4" t="n"/>
+      <c r="AE157" s="4" t="n"/>
+      <c r="AF157" s="4" t="n"/>
+      <c r="AG157" s="4" t="n"/>
+      <c r="AH157" s="4" t="n"/>
+      <c r="AI157" s="4" t="n"/>
+      <c r="AJ157" s="4" t="n"/>
+      <c r="AK157" s="4" t="n"/>
+      <c r="AL157" s="4" t="n"/>
+      <c r="AM157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -15713,12 +18581,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X158" s="4" t="n"/>
-      <c r="Y158" s="4" t="n"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z158" s="4" t="n"/>
       <c r="AA158" s="4" t="n"/>
       <c r="AB158" s="4" t="n"/>
       <c r="AC158" s="4" t="n"/>
+      <c r="AD158" s="4" t="n"/>
+      <c r="AE158" s="4" t="n"/>
+      <c r="AF158" s="4" t="n"/>
+      <c r="AG158" s="4" t="n"/>
+      <c r="AH158" s="4" t="n"/>
+      <c r="AI158" s="4" t="n"/>
+      <c r="AJ158" s="4" t="n"/>
+      <c r="AK158" s="4" t="n"/>
+      <c r="AL158" s="4" t="n"/>
+      <c r="AM158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -15809,12 +18695,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X159" s="4" t="n"/>
-      <c r="Y159" s="4" t="n"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z159" s="4" t="n"/>
       <c r="AA159" s="4" t="n"/>
       <c r="AB159" s="4" t="n"/>
       <c r="AC159" s="4" t="n"/>
+      <c r="AD159" s="4" t="n"/>
+      <c r="AE159" s="4" t="n"/>
+      <c r="AF159" s="4" t="n"/>
+      <c r="AG159" s="4" t="n"/>
+      <c r="AH159" s="4" t="n"/>
+      <c r="AI159" s="4" t="n"/>
+      <c r="AJ159" s="4" t="n"/>
+      <c r="AK159" s="4" t="n"/>
+      <c r="AL159" s="4" t="n"/>
+      <c r="AM159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -15905,12 +18809,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X160" s="4" t="n"/>
-      <c r="Y160" s="4" t="n"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z160" s="4" t="n"/>
       <c r="AA160" s="4" t="n"/>
       <c r="AB160" s="4" t="n"/>
       <c r="AC160" s="4" t="n"/>
+      <c r="AD160" s="4" t="n"/>
+      <c r="AE160" s="4" t="n"/>
+      <c r="AF160" s="4" t="n"/>
+      <c r="AG160" s="4" t="n"/>
+      <c r="AH160" s="4" t="n"/>
+      <c r="AI160" s="4" t="n"/>
+      <c r="AJ160" s="4" t="n"/>
+      <c r="AK160" s="4" t="n"/>
+      <c r="AL160" s="4" t="n"/>
+      <c r="AM160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -16001,12 +18923,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X161" s="4" t="n"/>
-      <c r="Y161" s="4" t="n"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z161" s="4" t="n"/>
       <c r="AA161" s="4" t="n"/>
       <c r="AB161" s="4" t="n"/>
       <c r="AC161" s="4" t="n"/>
+      <c r="AD161" s="4" t="n"/>
+      <c r="AE161" s="4" t="n"/>
+      <c r="AF161" s="4" t="n"/>
+      <c r="AG161" s="4" t="n"/>
+      <c r="AH161" s="4" t="n"/>
+      <c r="AI161" s="4" t="n"/>
+      <c r="AJ161" s="4" t="n"/>
+      <c r="AK161" s="4" t="n"/>
+      <c r="AL161" s="4" t="n"/>
+      <c r="AM161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -16097,12 +19037,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X162" s="4" t="n"/>
-      <c r="Y162" s="4" t="n"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z162" s="4" t="n"/>
       <c r="AA162" s="4" t="n"/>
       <c r="AB162" s="4" t="n"/>
       <c r="AC162" s="4" t="n"/>
+      <c r="AD162" s="4" t="n"/>
+      <c r="AE162" s="4" t="n"/>
+      <c r="AF162" s="4" t="n"/>
+      <c r="AG162" s="4" t="n"/>
+      <c r="AH162" s="4" t="n"/>
+      <c r="AI162" s="4" t="n"/>
+      <c r="AJ162" s="4" t="n"/>
+      <c r="AK162" s="4" t="n"/>
+      <c r="AL162" s="4" t="n"/>
+      <c r="AM162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -16193,12 +19151,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X163" s="4" t="n"/>
-      <c r="Y163" s="4" t="n"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z163" s="4" t="n"/>
       <c r="AA163" s="4" t="n"/>
       <c r="AB163" s="4" t="n"/>
       <c r="AC163" s="4" t="n"/>
+      <c r="AD163" s="4" t="n"/>
+      <c r="AE163" s="4" t="n"/>
+      <c r="AF163" s="4" t="n"/>
+      <c r="AG163" s="4" t="n"/>
+      <c r="AH163" s="4" t="n"/>
+      <c r="AI163" s="4" t="n"/>
+      <c r="AJ163" s="4" t="n"/>
+      <c r="AK163" s="4" t="n"/>
+      <c r="AL163" s="4" t="n"/>
+      <c r="AM163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -16289,12 +19265,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X164" s="4" t="n"/>
-      <c r="Y164" s="4" t="n"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z164" s="4" t="n"/>
       <c r="AA164" s="4" t="n"/>
       <c r="AB164" s="4" t="n"/>
       <c r="AC164" s="4" t="n"/>
+      <c r="AD164" s="4" t="n"/>
+      <c r="AE164" s="4" t="n"/>
+      <c r="AF164" s="4" t="n"/>
+      <c r="AG164" s="4" t="n"/>
+      <c r="AH164" s="4" t="n"/>
+      <c r="AI164" s="4" t="n"/>
+      <c r="AJ164" s="4" t="n"/>
+      <c r="AK164" s="4" t="n"/>
+      <c r="AL164" s="4" t="n"/>
+      <c r="AM164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -16385,12 +19379,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X165" s="4" t="n"/>
-      <c r="Y165" s="4" t="n"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z165" s="4" t="n"/>
       <c r="AA165" s="4" t="n"/>
       <c r="AB165" s="4" t="n"/>
       <c r="AC165" s="4" t="n"/>
+      <c r="AD165" s="4" t="n"/>
+      <c r="AE165" s="4" t="n"/>
+      <c r="AF165" s="4" t="n"/>
+      <c r="AG165" s="4" t="n"/>
+      <c r="AH165" s="4" t="n"/>
+      <c r="AI165" s="4" t="n"/>
+      <c r="AJ165" s="4" t="n"/>
+      <c r="AK165" s="4" t="n"/>
+      <c r="AL165" s="4" t="n"/>
+      <c r="AM165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -16481,12 +19493,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X166" s="4" t="n"/>
-      <c r="Y166" s="4" t="n"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z166" s="4" t="n"/>
       <c r="AA166" s="4" t="n"/>
       <c r="AB166" s="4" t="n"/>
       <c r="AC166" s="4" t="n"/>
+      <c r="AD166" s="4" t="n"/>
+      <c r="AE166" s="4" t="n"/>
+      <c r="AF166" s="4" t="n"/>
+      <c r="AG166" s="4" t="n"/>
+      <c r="AH166" s="4" t="n"/>
+      <c r="AI166" s="4" t="n"/>
+      <c r="AJ166" s="4" t="n"/>
+      <c r="AK166" s="4" t="n"/>
+      <c r="AL166" s="4" t="n"/>
+      <c r="AM166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -16577,12 +19607,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X167" s="4" t="n"/>
-      <c r="Y167" s="4" t="n"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z167" s="4" t="n"/>
       <c r="AA167" s="4" t="n"/>
       <c r="AB167" s="4" t="n"/>
       <c r="AC167" s="4" t="n"/>
+      <c r="AD167" s="4" t="n"/>
+      <c r="AE167" s="4" t="n"/>
+      <c r="AF167" s="4" t="n"/>
+      <c r="AG167" s="4" t="n"/>
+      <c r="AH167" s="4" t="n"/>
+      <c r="AI167" s="4" t="n"/>
+      <c r="AJ167" s="4" t="n"/>
+      <c r="AK167" s="4" t="n"/>
+      <c r="AL167" s="4" t="n"/>
+      <c r="AM167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -16673,12 +19721,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X168" s="4" t="n"/>
-      <c r="Y168" s="4" t="n"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z168" s="4" t="n"/>
       <c r="AA168" s="4" t="n"/>
       <c r="AB168" s="4" t="n"/>
       <c r="AC168" s="4" t="n"/>
+      <c r="AD168" s="4" t="n"/>
+      <c r="AE168" s="4" t="n"/>
+      <c r="AF168" s="4" t="n"/>
+      <c r="AG168" s="4" t="n"/>
+      <c r="AH168" s="4" t="n"/>
+      <c r="AI168" s="4" t="n"/>
+      <c r="AJ168" s="4" t="n"/>
+      <c r="AK168" s="4" t="n"/>
+      <c r="AL168" s="4" t="n"/>
+      <c r="AM168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -16769,12 +19835,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X169" s="4" t="n"/>
-      <c r="Y169" s="4" t="n"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z169" s="4" t="n"/>
       <c r="AA169" s="4" t="n"/>
       <c r="AB169" s="4" t="n"/>
       <c r="AC169" s="4" t="n"/>
+      <c r="AD169" s="4" t="n"/>
+      <c r="AE169" s="4" t="n"/>
+      <c r="AF169" s="4" t="n"/>
+      <c r="AG169" s="4" t="n"/>
+      <c r="AH169" s="4" t="n"/>
+      <c r="AI169" s="4" t="n"/>
+      <c r="AJ169" s="4" t="n"/>
+      <c r="AK169" s="4" t="n"/>
+      <c r="AL169" s="4" t="n"/>
+      <c r="AM169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -16865,12 +19949,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X170" s="4" t="n"/>
-      <c r="Y170" s="4" t="n"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z170" s="4" t="n"/>
       <c r="AA170" s="4" t="n"/>
       <c r="AB170" s="4" t="n"/>
       <c r="AC170" s="4" t="n"/>
+      <c r="AD170" s="4" t="n"/>
+      <c r="AE170" s="4" t="n"/>
+      <c r="AF170" s="4" t="n"/>
+      <c r="AG170" s="4" t="n"/>
+      <c r="AH170" s="4" t="n"/>
+      <c r="AI170" s="4" t="n"/>
+      <c r="AJ170" s="4" t="n"/>
+      <c r="AK170" s="4" t="n"/>
+      <c r="AL170" s="4" t="n"/>
+      <c r="AM170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -16961,12 +20063,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X171" s="4" t="n"/>
-      <c r="Y171" s="4" t="n"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z171" s="4" t="n"/>
       <c r="AA171" s="4" t="n"/>
       <c r="AB171" s="4" t="n"/>
       <c r="AC171" s="4" t="n"/>
+      <c r="AD171" s="4" t="n"/>
+      <c r="AE171" s="4" t="n"/>
+      <c r="AF171" s="4" t="n"/>
+      <c r="AG171" s="4" t="n"/>
+      <c r="AH171" s="4" t="n"/>
+      <c r="AI171" s="4" t="n"/>
+      <c r="AJ171" s="4" t="n"/>
+      <c r="AK171" s="4" t="n"/>
+      <c r="AL171" s="4" t="n"/>
+      <c r="AM171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -17057,12 +20177,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X172" s="4" t="n"/>
-      <c r="Y172" s="4" t="n"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z172" s="4" t="n"/>
       <c r="AA172" s="4" t="n"/>
       <c r="AB172" s="4" t="n"/>
       <c r="AC172" s="4" t="n"/>
+      <c r="AD172" s="4" t="n"/>
+      <c r="AE172" s="4" t="n"/>
+      <c r="AF172" s="4" t="n"/>
+      <c r="AG172" s="4" t="n"/>
+      <c r="AH172" s="4" t="n"/>
+      <c r="AI172" s="4" t="n"/>
+      <c r="AJ172" s="4" t="n"/>
+      <c r="AK172" s="4" t="n"/>
+      <c r="AL172" s="4" t="n"/>
+      <c r="AM172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -17153,12 +20291,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X173" s="4" t="n"/>
-      <c r="Y173" s="4" t="n"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z173" s="4" t="n"/>
       <c r="AA173" s="4" t="n"/>
       <c r="AB173" s="4" t="n"/>
       <c r="AC173" s="4" t="n"/>
+      <c r="AD173" s="4" t="n"/>
+      <c r="AE173" s="4" t="n"/>
+      <c r="AF173" s="4" t="n"/>
+      <c r="AG173" s="4" t="n"/>
+      <c r="AH173" s="4" t="n"/>
+      <c r="AI173" s="4" t="n"/>
+      <c r="AJ173" s="4" t="n"/>
+      <c r="AK173" s="4" t="n"/>
+      <c r="AL173" s="4" t="n"/>
+      <c r="AM173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -17249,12 +20405,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X174" s="4" t="n"/>
-      <c r="Y174" s="4" t="n"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z174" s="4" t="n"/>
       <c r="AA174" s="4" t="n"/>
       <c r="AB174" s="4" t="n"/>
       <c r="AC174" s="4" t="n"/>
+      <c r="AD174" s="4" t="n"/>
+      <c r="AE174" s="4" t="n"/>
+      <c r="AF174" s="4" t="n"/>
+      <c r="AG174" s="4" t="n"/>
+      <c r="AH174" s="4" t="n"/>
+      <c r="AI174" s="4" t="n"/>
+      <c r="AJ174" s="4" t="n"/>
+      <c r="AK174" s="4" t="n"/>
+      <c r="AL174" s="4" t="n"/>
+      <c r="AM174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -17345,12 +20519,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X175" s="4" t="n"/>
-      <c r="Y175" s="4" t="n"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z175" s="4" t="n"/>
       <c r="AA175" s="4" t="n"/>
       <c r="AB175" s="4" t="n"/>
       <c r="AC175" s="4" t="n"/>
+      <c r="AD175" s="4" t="n"/>
+      <c r="AE175" s="4" t="n"/>
+      <c r="AF175" s="4" t="n"/>
+      <c r="AG175" s="4" t="n"/>
+      <c r="AH175" s="4" t="n"/>
+      <c r="AI175" s="4" t="n"/>
+      <c r="AJ175" s="4" t="n"/>
+      <c r="AK175" s="4" t="n"/>
+      <c r="AL175" s="4" t="n"/>
+      <c r="AM175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -17441,12 +20633,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X176" s="4" t="n"/>
-      <c r="Y176" s="4" t="n"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z176" s="4" t="n"/>
       <c r="AA176" s="4" t="n"/>
       <c r="AB176" s="4" t="n"/>
       <c r="AC176" s="4" t="n"/>
+      <c r="AD176" s="4" t="n"/>
+      <c r="AE176" s="4" t="n"/>
+      <c r="AF176" s="4" t="n"/>
+      <c r="AG176" s="4" t="n"/>
+      <c r="AH176" s="4" t="n"/>
+      <c r="AI176" s="4" t="n"/>
+      <c r="AJ176" s="4" t="n"/>
+      <c r="AK176" s="4" t="n"/>
+      <c r="AL176" s="4" t="n"/>
+      <c r="AM176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -17537,12 +20747,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X177" s="4" t="n"/>
-      <c r="Y177" s="4" t="n"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z177" s="4" t="n"/>
       <c r="AA177" s="4" t="n"/>
       <c r="AB177" s="4" t="n"/>
       <c r="AC177" s="4" t="n"/>
+      <c r="AD177" s="4" t="n"/>
+      <c r="AE177" s="4" t="n"/>
+      <c r="AF177" s="4" t="n"/>
+      <c r="AG177" s="4" t="n"/>
+      <c r="AH177" s="4" t="n"/>
+      <c r="AI177" s="4" t="n"/>
+      <c r="AJ177" s="4" t="n"/>
+      <c r="AK177" s="4" t="n"/>
+      <c r="AL177" s="4" t="n"/>
+      <c r="AM177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -17633,12 +20861,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X178" s="4" t="n"/>
-      <c r="Y178" s="4" t="n"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z178" s="4" t="n"/>
       <c r="AA178" s="4" t="n"/>
       <c r="AB178" s="4" t="n"/>
       <c r="AC178" s="4" t="n"/>
+      <c r="AD178" s="4" t="n"/>
+      <c r="AE178" s="4" t="n"/>
+      <c r="AF178" s="4" t="n"/>
+      <c r="AG178" s="4" t="n"/>
+      <c r="AH178" s="4" t="n"/>
+      <c r="AI178" s="4" t="n"/>
+      <c r="AJ178" s="4" t="n"/>
+      <c r="AK178" s="4" t="n"/>
+      <c r="AL178" s="4" t="n"/>
+      <c r="AM178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -17729,12 +20975,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X179" s="4" t="n"/>
-      <c r="Y179" s="4" t="n"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z179" s="4" t="n"/>
       <c r="AA179" s="4" t="n"/>
       <c r="AB179" s="4" t="n"/>
       <c r="AC179" s="4" t="n"/>
+      <c r="AD179" s="4" t="n"/>
+      <c r="AE179" s="4" t="n"/>
+      <c r="AF179" s="4" t="n"/>
+      <c r="AG179" s="4" t="n"/>
+      <c r="AH179" s="4" t="n"/>
+      <c r="AI179" s="4" t="n"/>
+      <c r="AJ179" s="4" t="n"/>
+      <c r="AK179" s="4" t="n"/>
+      <c r="AL179" s="4" t="n"/>
+      <c r="AM179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -17825,12 +21089,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X180" s="4" t="n"/>
-      <c r="Y180" s="4" t="n"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z180" s="4" t="n"/>
       <c r="AA180" s="4" t="n"/>
       <c r="AB180" s="4" t="n"/>
       <c r="AC180" s="4" t="n"/>
+      <c r="AD180" s="4" t="n"/>
+      <c r="AE180" s="4" t="n"/>
+      <c r="AF180" s="4" t="n"/>
+      <c r="AG180" s="4" t="n"/>
+      <c r="AH180" s="4" t="n"/>
+      <c r="AI180" s="4" t="n"/>
+      <c r="AJ180" s="4" t="n"/>
+      <c r="AK180" s="4" t="n"/>
+      <c r="AL180" s="4" t="n"/>
+      <c r="AM180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -17921,12 +21203,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X181" s="4" t="n"/>
-      <c r="Y181" s="4" t="n"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z181" s="4" t="n"/>
       <c r="AA181" s="4" t="n"/>
       <c r="AB181" s="4" t="n"/>
       <c r="AC181" s="4" t="n"/>
+      <c r="AD181" s="4" t="n"/>
+      <c r="AE181" s="4" t="n"/>
+      <c r="AF181" s="4" t="n"/>
+      <c r="AG181" s="4" t="n"/>
+      <c r="AH181" s="4" t="n"/>
+      <c r="AI181" s="4" t="n"/>
+      <c r="AJ181" s="4" t="n"/>
+      <c r="AK181" s="4" t="n"/>
+      <c r="AL181" s="4" t="n"/>
+      <c r="AM181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -18017,12 +21317,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X182" s="4" t="n"/>
-      <c r="Y182" s="4" t="n"/>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
       <c r="Z182" s="4" t="n"/>
       <c r="AA182" s="4" t="n"/>
       <c r="AB182" s="4" t="n"/>
       <c r="AC182" s="4" t="n"/>
+      <c r="AD182" s="4" t="n"/>
+      <c r="AE182" s="4" t="n"/>
+      <c r="AF182" s="4" t="n"/>
+      <c r="AG182" s="4" t="n"/>
+      <c r="AH182" s="4" t="n"/>
+      <c r="AI182" s="4" t="n"/>
+      <c r="AJ182" s="4" t="n"/>
+      <c r="AK182" s="4" t="n"/>
+      <c r="AL182" s="4" t="n"/>
+      <c r="AM182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -18113,12 +21431,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X183" s="4" t="n"/>
-      <c r="Y183" s="4" t="n"/>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z183" s="4" t="n"/>
       <c r="AA183" s="4" t="n"/>
       <c r="AB183" s="4" t="n"/>
       <c r="AC183" s="4" t="n"/>
+      <c r="AD183" s="4" t="n"/>
+      <c r="AE183" s="4" t="n"/>
+      <c r="AF183" s="4" t="n"/>
+      <c r="AG183" s="4" t="n"/>
+      <c r="AH183" s="4" t="n"/>
+      <c r="AI183" s="4" t="n"/>
+      <c r="AJ183" s="4" t="n"/>
+      <c r="AK183" s="4" t="n"/>
+      <c r="AL183" s="4" t="n"/>
+      <c r="AM183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -18209,12 +21545,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X184" s="4" t="n"/>
-      <c r="Y184" s="4" t="n"/>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z184" s="4" t="n"/>
       <c r="AA184" s="4" t="n"/>
       <c r="AB184" s="4" t="n"/>
       <c r="AC184" s="4" t="n"/>
+      <c r="AD184" s="4" t="n"/>
+      <c r="AE184" s="4" t="n"/>
+      <c r="AF184" s="4" t="n"/>
+      <c r="AG184" s="4" t="n"/>
+      <c r="AH184" s="4" t="n"/>
+      <c r="AI184" s="4" t="n"/>
+      <c r="AJ184" s="4" t="n"/>
+      <c r="AK184" s="4" t="n"/>
+      <c r="AL184" s="4" t="n"/>
+      <c r="AM184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -18305,12 +21659,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X185" s="4" t="n"/>
-      <c r="Y185" s="4" t="n"/>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
       <c r="Z185" s="4" t="n"/>
       <c r="AA185" s="4" t="n"/>
       <c r="AB185" s="4" t="n"/>
       <c r="AC185" s="4" t="n"/>
+      <c r="AD185" s="4" t="n"/>
+      <c r="AE185" s="4" t="n"/>
+      <c r="AF185" s="4" t="n"/>
+      <c r="AG185" s="4" t="n"/>
+      <c r="AH185" s="4" t="n"/>
+      <c r="AI185" s="4" t="n"/>
+      <c r="AJ185" s="4" t="n"/>
+      <c r="AK185" s="4" t="n"/>
+      <c r="AL185" s="4" t="n"/>
+      <c r="AM185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -18401,12 +21773,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X186" s="4" t="n"/>
-      <c r="Y186" s="4" t="n"/>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z186" s="4" t="n"/>
       <c r="AA186" s="4" t="n"/>
       <c r="AB186" s="4" t="n"/>
       <c r="AC186" s="4" t="n"/>
+      <c r="AD186" s="4" t="n"/>
+      <c r="AE186" s="4" t="n"/>
+      <c r="AF186" s="4" t="n"/>
+      <c r="AG186" s="4" t="n"/>
+      <c r="AH186" s="4" t="n"/>
+      <c r="AI186" s="4" t="n"/>
+      <c r="AJ186" s="4" t="n"/>
+      <c r="AK186" s="4" t="n"/>
+      <c r="AL186" s="4" t="n"/>
+      <c r="AM186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -18497,12 +21887,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X187" s="4" t="n"/>
-      <c r="Y187" s="4" t="n"/>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z187" s="4" t="n"/>
       <c r="AA187" s="4" t="n"/>
       <c r="AB187" s="4" t="n"/>
       <c r="AC187" s="4" t="n"/>
+      <c r="AD187" s="4" t="n"/>
+      <c r="AE187" s="4" t="n"/>
+      <c r="AF187" s="4" t="n"/>
+      <c r="AG187" s="4" t="n"/>
+      <c r="AH187" s="4" t="n"/>
+      <c r="AI187" s="4" t="n"/>
+      <c r="AJ187" s="4" t="n"/>
+      <c r="AK187" s="4" t="n"/>
+      <c r="AL187" s="4" t="n"/>
+      <c r="AM187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -18593,12 +22001,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X188" s="4" t="n"/>
-      <c r="Y188" s="4" t="n"/>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z188" s="4" t="n"/>
       <c r="AA188" s="4" t="n"/>
       <c r="AB188" s="4" t="n"/>
       <c r="AC188" s="4" t="n"/>
+      <c r="AD188" s="4" t="n"/>
+      <c r="AE188" s="4" t="n"/>
+      <c r="AF188" s="4" t="n"/>
+      <c r="AG188" s="4" t="n"/>
+      <c r="AH188" s="4" t="n"/>
+      <c r="AI188" s="4" t="n"/>
+      <c r="AJ188" s="4" t="n"/>
+      <c r="AK188" s="4" t="n"/>
+      <c r="AL188" s="4" t="n"/>
+      <c r="AM188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -18689,12 +22115,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X189" s="4" t="n"/>
-      <c r="Y189" s="4" t="n"/>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z189" s="4" t="n"/>
       <c r="AA189" s="4" t="n"/>
       <c r="AB189" s="4" t="n"/>
       <c r="AC189" s="4" t="n"/>
+      <c r="AD189" s="4" t="n"/>
+      <c r="AE189" s="4" t="n"/>
+      <c r="AF189" s="4" t="n"/>
+      <c r="AG189" s="4" t="n"/>
+      <c r="AH189" s="4" t="n"/>
+      <c r="AI189" s="4" t="n"/>
+      <c r="AJ189" s="4" t="n"/>
+      <c r="AK189" s="4" t="n"/>
+      <c r="AL189" s="4" t="n"/>
+      <c r="AM189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -18785,12 +22229,30 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X190" s="4" t="n"/>
-      <c r="Y190" s="4" t="n"/>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z190" s="4" t="n"/>
       <c r="AA190" s="4" t="n"/>
       <c r="AB190" s="4" t="n"/>
       <c r="AC190" s="4" t="n"/>
+      <c r="AD190" s="4" t="n"/>
+      <c r="AE190" s="4" t="n"/>
+      <c r="AF190" s="4" t="n"/>
+      <c r="AG190" s="4" t="n"/>
+      <c r="AH190" s="4" t="n"/>
+      <c r="AI190" s="4" t="n"/>
+      <c r="AJ190" s="4" t="n"/>
+      <c r="AK190" s="4" t="n"/>
+      <c r="AL190" s="4" t="n"/>
+      <c r="AM190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -18881,15 +22343,33 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="X191" s="4" t="n"/>
-      <c r="Y191" s="4" t="n"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="Z191" s="4" t="n"/>
       <c r="AA191" s="4" t="n"/>
       <c r="AB191" s="4" t="n"/>
       <c r="AC191" s="4" t="n"/>
+      <c r="AD191" s="4" t="n"/>
+      <c r="AE191" s="4" t="n"/>
+      <c r="AF191" s="4" t="n"/>
+      <c r="AG191" s="4" t="n"/>
+      <c r="AH191" s="4" t="n"/>
+      <c r="AI191" s="4" t="n"/>
+      <c r="AJ191" s="4" t="n"/>
+      <c r="AK191" s="4" t="n"/>
+      <c r="AL191" s="4" t="n"/>
+      <c r="AM191" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC191"/>
+  <autoFilter ref="A1:AM191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -1385,20 +1385,56 @@
           <t>reg-csa-1c-wsh-3</t>
         </is>
       </c>
-      <c r="AB9" s="5" t="n"/>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (battalion in-build only)</t>
+        </is>
+      </c>
       <c r="AC9" s="5" t="n"/>
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
-      <c r="AG9" s="5" t="n"/>
-      <c r="AH9" s="5" t="n"/>
-      <c r="AI9" s="5" t="n"/>
-      <c r="AJ9" s="5" t="n"/>
-      <c r="AK9" s="5" t="n"/>
-      <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="5" t="n"/>
+      <c r="AG9" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-wsh-3-miller.md</t>
+        </is>
+      </c>
+      <c r="AH9" s="5" t="inlineStr">
+        <is>
+          <t>Capt. M.B. Miller, 3rd Co. Washington Arty; order chain Longstreet -&gt; Walton -&gt; Miller (or-27-2-longstreet verified)</t>
+        </is>
+      </c>
+      <c r="AI9" s="5" t="inlineStr">
+        <is>
+          <t>no company figure located (gap); battalion 240 at build grain</t>
+        </is>
+      </c>
+      <c r="AJ9" s="5" t="inlineStr">
+        <is>
+          <t>[E] inside battalion Peach Orchard frontage, parent centroid (3220,3550) f55; company coord inference +-150m marked</t>
+        </is>
+      </c>
+      <c r="AK9" s="5" t="inlineStr">
+        <is>
+          <t>[D pre-daylight] night arrival with battalion; none in-window</t>
+        </is>
+      </c>
+      <c r="AL9" s="5" t="inlineStr">
+        <is>
+          <t>[A = CA-J3A-1] FIRES THE SIGNAL GUNS 13:07 (jacobs-1864 reading; martin-smith participant grade); then general bombardment fire</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr">
+        <is>
+          <t>no company K/W/M located (gap); no officer pin (negative at corpus grain)</t>
+        </is>
+      </c>
       <c r="AN9" s="5" t="n"/>
-      <c r="AO9" s="5" t="n"/>
+      <c r="AO9" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7249,20 +7285,56 @@
           <t>reg-csa-1c-bn-alexander</t>
         </is>
       </c>
-      <c r="AB74" s="5" t="n"/>
+      <c r="AB74" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (static line)</t>
+        </is>
+      </c>
       <c r="AC74" s="5" t="n"/>
       <c r="AD74" s="5" t="n"/>
       <c r="AE74" s="5" t="n"/>
       <c r="AF74" s="5" t="n"/>
-      <c r="AG74" s="5" t="n"/>
-      <c r="AH74" s="5" t="n"/>
-      <c r="AI74" s="5" t="n"/>
-      <c r="AJ74" s="5" t="n"/>
-      <c r="AK74" s="5" t="n"/>
-      <c r="AL74" s="5" t="n"/>
-      <c r="AM74" s="5" t="n"/>
+      <c r="AG74" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-bn-alexander.md; the Alexander-notes-vs-long-cannonade crux recorded not resolved (ED-24 tension 2)</t>
+        </is>
+      </c>
+      <c r="AH74" s="5" t="inlineStr">
+        <is>
+          <t>Col. E.P. Alexander (directing corps arty Jul 3, Longstreet's order) / Maj. Huger at the battalion; 6 batteries; Woolfolk w Jul 2</t>
+        </is>
+      </c>
+      <c r="AI74" s="5" t="inlineStr">
+        <is>
+          <t>576 build adoption; ~24-26 guns (tablet-grade); per-battery figures open</t>
+        </is>
+      </c>
+      <c r="AJ74" s="5" t="inlineStr">
+        <is>
+          <t>[E] ridge line from Peach Orchard NE (tablet verbatim), centroid (3170,4150) f78, frontage ~400-500m; Jul 2 Peach Orchard fight line deferred</t>
+        </is>
+      </c>
+      <c r="AK74" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 night redeploy into bombardment line; none in-window (fwd displacement NOT attested - negative + conflict slot)</t>
+        </is>
+      </c>
+      <c r="AL74" s="5" t="inlineStr">
+        <is>
+          <t>[A window] core of the cannonade; [C 13:32/13:47 corrected] the two notes to Pickett = CA-J3A-2/3 written from this line; ammunition famine defines the record</t>
+        </is>
+      </c>
+      <c r="AM74" s="5" t="inlineStr">
+        <is>
+          <t>battalion K/W/M open (gap); Jul 2 the bloody day; pin: Woolfolk w Jul 2</t>
+        </is>
+      </c>
       <c r="AN74" s="5" t="n"/>
-      <c r="AO74" s="5" t="n"/>
+      <c r="AO74" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7993,20 +8065,56 @@
           <t>reg-csa-1c-bn-wash</t>
         </is>
       </c>
-      <c r="AB80" s="5" t="n"/>
+      <c r="AB80" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (static line)</t>
+        </is>
+      </c>
       <c r="AC80" s="5" t="n"/>
       <c r="AD80" s="5" t="n"/>
       <c r="AE80" s="5" t="n"/>
       <c r="AF80" s="5" t="n"/>
-      <c r="AG80" s="5" t="n"/>
-      <c r="AH80" s="5" t="n"/>
-      <c r="AI80" s="5" t="n"/>
-      <c r="AJ80" s="5" t="n"/>
-      <c r="AK80" s="5" t="n"/>
-      <c r="AL80" s="5" t="n"/>
-      <c r="AM80" s="5" t="n"/>
+      <c r="AG80" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-bn-wash-eshleman.md</t>
+        </is>
+      </c>
+      <c r="AH80" s="5" t="inlineStr">
+        <is>
+          <t>Maj. B.F. Eshleman; 4 cos (Squires/Richardson/Miller/Norcom-w-Jul3); Walton nominal chief with the battalion (divided command vs Alexander recorded)</t>
+        </is>
+      </c>
+      <c r="AI80" s="5" t="inlineStr">
+        <is>
+          <t>240 build adoption (tablet-cited); per-company figures open</t>
+        </is>
+      </c>
+      <c r="AJ80" s="5" t="inlineStr">
+        <is>
+          <t>[D/E] 'Arrived on the field before daylight' Jul 3 (tablet verbatim); [E] Peach Orchard line (3220,3550) f55, frontage ~300m</t>
+        </is>
+      </c>
+      <c r="AK80" s="5" t="inlineStr">
+        <is>
+          <t>[D before ~04:30 daylight] night march onto field; attested-static in window</t>
+        </is>
+      </c>
+      <c r="AL80" s="5" t="inlineStr">
+        <is>
+          <t>[A] CA-J3A-1 signal guns via 3rd Co.; [A window] 10 guns in the general bombardment ('YES + the 13:07 signal guns', tablet-grade)</t>
+        </is>
+      </c>
+      <c r="AM80" s="5" t="inlineStr">
+        <is>
+          <t>battalion K/W/M open (gap); pin: Capt. Norcom w Jul 3; clean single-episode shape (arrived Jul 3)</t>
+        </is>
+      </c>
       <c r="AN80" s="5" t="n"/>
-      <c r="AO80" s="5" t="n"/>
+      <c r="AO80" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -17953,20 +18061,56 @@
           <t>reg-us-ar-1v</t>
         </is>
       </c>
-      <c r="AB164" s="5" t="n"/>
+      <c r="AB164" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (only Phillips in build)</t>
+        </is>
+      </c>
       <c r="AC164" s="5" t="n"/>
       <c r="AD164" s="5" t="n"/>
       <c r="AE164" s="5" t="n"/>
       <c r="AF164" s="5" t="n"/>
-      <c r="AG164" s="5" t="n"/>
-      <c r="AH164" s="5" t="n"/>
-      <c r="AI164" s="5" t="n"/>
-      <c r="AJ164" s="5" t="n"/>
-      <c r="AK164" s="5" t="n"/>
-      <c r="AL164" s="5" t="n"/>
-      <c r="AM164" s="5" t="n"/>
+      <c r="AG164" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-1v-mcgilvery.md; his July 3 opening clock (OR pp.882-883) still unverified; ED-35 candidate: cast the line as a command unit</t>
+        </is>
+      </c>
+      <c r="AH164" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. McGilvery; July 3 line = composite command of 3 Reserve brigades + III Corps battery under Hunt's direct control; Bigelow w July 2 -&gt; Milton</t>
+        </is>
+      </c>
+      <c r="AI164" s="5" t="inlineStr">
+        <is>
+          <t>no engaged-men figure located (gap); '39 guns' secondary-grade; tablet-verified 9-battery roster is the stronger form</t>
+        </is>
+      </c>
+      <c r="AJ164" s="5" t="inlineStr">
+        <is>
+          <t>[C p.881] July 2 Wheatfield Rd line from ~15:30; [D] Trostle stand + Plum Run line; [E] July 3 massed lower-Cemetery-Ridge line, ref point Phillips (4212,4080) f265; sheet-8 Daniels/Rank labels CONFLICT with OOB (ECF)</t>
+        </is>
+      </c>
+      <c r="AK164" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:30 Jul 2] march to Sickles; [D] fighting retreat by prolonge; [C tablet ~15:00 Jul 3] Cooper's B/1st PA joins line from E Cemetery Hill [B: ~15-20 min leg]</t>
+        </is>
+      </c>
+      <c r="AL164" s="5" t="inlineStr">
+        <is>
+          <t>[A window] ORDERED SILENCE under Hunt's policy (CA-J3A-4's largest component); 'fired about one hour and a half... 10,000 rounds' (or-27-1-mcgilvery p.884); [C ~15:00] first line 'completely broken up and scattered by our fire'; oblique raking fire through all three lines; then Wilcox/Lang smashed with 16th VT</t>
+        </is>
+      </c>
+      <c r="AM164" s="5" t="inlineStr">
+        <is>
+          <t>brigade K/W/M not located (gap; July 2 dominates via Bigelow's stand); pin: Bigelow w July 2</t>
+        </is>
+      </c>
       <c r="AN164" s="5" t="n"/>
-      <c r="AO164" s="5" t="n"/>
+      <c r="AO164" s="5" t="inlineStr">
+        <is>
+          <t>T4 (brigade grain)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -18481,20 +18625,56 @@
           <t>reg-us-ii-arty</t>
         </is>
       </c>
-      <c r="AB170" s="5" t="n"/>
+      <c r="AB170" s="5" t="inlineStr">
+        <is>
+          <t>command record (batteries in-build individually)</t>
+        </is>
+      </c>
       <c r="AC170" s="5" t="n"/>
       <c r="AD170" s="5" t="n"/>
       <c r="AE170" s="5" t="n"/>
       <c r="AF170" s="5" t="n"/>
-      <c r="AG170" s="5" t="n"/>
-      <c r="AH170" s="5" t="n"/>
-      <c r="AI170" s="5" t="n"/>
-      <c r="AJ170" s="5" t="n"/>
-      <c r="AK170" s="5" t="n"/>
-      <c r="AL170" s="5" t="n"/>
-      <c r="AM170" s="5" t="n"/>
+      <c r="AG170" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-arty-hazard.md; ED-34 candidate (activity classes)</t>
+        </is>
+      </c>
+      <c r="AH170" s="5" t="inlineStr">
+        <is>
+          <t>Capt. J.G. Hazard; worst commander attrition of any Union arty bde: Rorty k, Cushing k, Woodruff mw, Sheldon w, Milne mw (or-27-1-hazard)</t>
+        </is>
+      </c>
+      <c r="AI170" s="5" t="inlineStr">
+        <is>
+          <t>600 aggregate (stone-sentinels) vs battery-page sum 602 - consistent, both carried; 26 guns</t>
+        </is>
+      </c>
+      <c r="AJ170" s="5" t="inlineStr">
+        <is>
+          <t>[E] 5-battery line Ziegler's Grove -&gt; Rorty's left, ~530m frontage = the convergence target square (battery coords in their rows)</t>
+        </is>
+      </c>
+      <c r="AK170" s="5" t="inlineStr">
+        <is>
+          <t>static except Brown's ordered withdrawal + post-repulse replacements</t>
+        </is>
+      </c>
+      <c r="AL170" s="5" t="inlineStr">
+        <is>
+          <t>[A window] FOUGHT THE CANNONADE THROUGHOUT under Hancock's counter-order; long-range ammo exhausted (or-27-1-hazard) -&gt; canister-only repulse fight</t>
+        </is>
+      </c>
+      <c r="AM170" s="5" t="inlineStr">
+        <is>
+          <t>150 (25k/120w/5m), 35% - highest-pct Union arty bde loss; flat-then-spike shape vs the silent-then-fire lines; 5 officer pins at battery grain</t>
+        </is>
+      </c>
       <c r="AN170" s="5" t="n"/>
-      <c r="AO170" s="5" t="n"/>
+      <c r="AO170" s="5" t="inlineStr">
+        <is>
+          <t>T4 (brigade grain)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -18833,20 +19013,56 @@
           <t>reg-us-xi-arty</t>
         </is>
       </c>
-      <c r="AB174" s="5" t="n"/>
+      <c r="AB174" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC174" s="5" t="n"/>
       <c r="AD174" s="5" t="n"/>
       <c r="AE174" s="5" t="n"/>
       <c r="AF174" s="5" t="n"/>
-      <c r="AG174" s="5" t="n"/>
-      <c r="AH174" s="5" t="n"/>
-      <c r="AI174" s="5" t="n"/>
-      <c r="AJ174" s="5" t="n"/>
-      <c r="AK174" s="5" t="n"/>
-      <c r="AL174" s="5" t="n"/>
-      <c r="AM174" s="5" t="n"/>
+      <c r="AG174" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-arty-osborn.md</t>
+        </is>
+      </c>
+      <c r="AH174" s="5" t="inlineStr">
+        <is>
+          <t>Maj. T.W. Osborn; Jul 3 group exceeds organic brigade (Reserve + I Corps attachments under his direction)</t>
+        </is>
+      </c>
+      <c r="AI174" s="5" t="inlineStr">
+        <is>
+          <t>no men figure located (gap); ~39 guns secondary-grade; tablet-verified 9-battery roster is the stronger form</t>
+        </is>
+      </c>
+      <c r="AJ174" s="5" t="inlineStr">
+        <is>
+          <t>[E multi-day] Cemetery Hill plateau Jul 1 retreat -&gt; Jul 4; coords deferred (square's N margin)</t>
+        </is>
+      </c>
+      <c r="AK174" s="5" t="inlineStr">
+        <is>
+          <t>group attested-static Jul 3</t>
+        </is>
+      </c>
+      <c r="AL174" s="5" t="inlineStr">
+        <is>
+          <t>[A window] counter-battery under the crossfire; [C ~14:30] THE CEASE-FIRE RUSE (proposed Osborn, adopted Hunt/Howard) = CA-J3A-4/5's sharpest component; [D] ~1,600 rounds into Pettigrew's left (secondary-grade)</t>
+        </is>
+      </c>
+      <c r="AM174" s="5" t="inlineStr">
+        <is>
+          <t>brigade K/W/M open (gap); Jul 1-2 dominate the shape; no Jul 3 officer pin located (negative)</t>
+        </is>
+      </c>
       <c r="AN174" s="5" t="n"/>
-      <c r="AO174" s="5" t="n"/>
+      <c r="AO174" s="5" t="inlineStr">
+        <is>
+          <t>T4 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -21385,20 +21601,56 @@
           <t>reg-us-arty-hq</t>
         </is>
       </c>
-      <c r="AB203" s="5" t="n"/>
+      <c r="AB203" s="5" t="inlineStr">
+        <is>
+          <t>command record</t>
+        </is>
+      </c>
       <c r="AC203" s="5" t="n"/>
       <c r="AD203" s="5" t="n"/>
       <c r="AE203" s="5" t="n"/>
       <c r="AF203" s="5" t="n"/>
-      <c r="AG203" s="5" t="n"/>
-      <c r="AH203" s="5" t="n"/>
-      <c r="AI203" s="5" t="n"/>
-      <c r="AJ203" s="5" t="n"/>
-      <c r="AK203" s="5" t="n"/>
-      <c r="AL203" s="5" t="n"/>
-      <c r="AM203" s="5" t="n"/>
+      <c r="AG203" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-arty-hq-hunt.md; NEW register row this pass</t>
+        </is>
+      </c>
+      <c r="AH203" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. H.J. Hunt, Chief of Artillery AoP; authority contested by Hancock on the II Corps front - the dispute IS CA-J3A-4's sectoral shape</t>
+        </is>
+      </c>
+      <c r="AI203" s="5" t="inlineStr">
+        <is>
+          <t>n/a (command entry); Reserve 2,375 men / 114 guns nominal under command</t>
+        </is>
+      </c>
+      <c r="AJ203" s="5" t="inlineStr">
+        <is>
+          <t>[C] ~11-13:00 line inspection ride; [A vs CA-J3A-1] on Little Round Top at the opening; [A window] at Cowan's guns at the climax (horse shot, brown-1985-filson)</t>
+        </is>
+      </c>
+      <c r="AK203" s="5" t="inlineStr">
+        <is>
+          <t>command-grain ride sequence (times the order delivery)</t>
+        </is>
+      </c>
+      <c r="AL203" s="5" t="inlineStr">
+        <is>
+          <t>[C ~11:00] withhold-fire instruction; [C ~14:30] the slacken/cease order (CA-J3A-4); [D] Hancock counter-order conflict; [D] repulse-window battery reinforcements</t>
+        </is>
+      </c>
+      <c r="AM203" s="5" t="inlineStr">
+        <is>
+          <t>n/a; horse killed at Cowan's guns</t>
+        </is>
+      </c>
       <c r="AN203" s="5" t="n"/>
-      <c r="AO203" s="5" t="n"/>
+      <c r="AO203" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command record)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -21633,20 +21885,56 @@
           <t>reg-us-ii-b2</t>
         </is>
       </c>
-      <c r="AB205" s="5" t="n"/>
+      <c r="AB205" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (ED-7 stands)</t>
+        </is>
+      </c>
       <c r="AC205" s="5" t="n"/>
       <c r="AD205" s="5" t="n"/>
       <c r="AE205" s="5" t="n"/>
       <c r="AF205" s="5" t="n"/>
-      <c r="AG205" s="5" t="n"/>
-      <c r="AH205" s="5" t="n"/>
-      <c r="AI205" s="5" t="n"/>
-      <c r="AJ205" s="5" t="n"/>
-      <c r="AK205" s="5" t="n"/>
-      <c r="AL205" s="5" t="n"/>
-      <c r="AM205" s="5" t="n"/>
+      <c r="AG205" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-arnold.md</t>
+        </is>
+      </c>
+      <c r="AH205" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Arnold survived unwounded ('gallantly fighting his own battery and saving it', or-27-1-hazard); 6x 3-in Ordnance rifles</t>
+        </is>
+      </c>
+      <c r="AI205" s="5" t="inlineStr">
+        <is>
+          <t>139 men (stone-sentinels; civilwarintheeast derivative corroboration only)</t>
+        </is>
+      </c>
+      <c r="AJ205" s="5" t="inlineStr">
+        <is>
+          <t>[E] wall N of inner angle (4425,4955) f260 +-30m, ~80m N of Angle corner (Bachelder); attested-static with ED-7 withdrawal dispute riding the claim</t>
+        </is>
+      </c>
+      <c r="AK205" s="5" t="inlineStr">
+        <is>
+          <t>none authored (ED-7: neither withdrawal-timing reading strong enough to move traced geometry)</t>
+        </is>
+      </c>
+      <c r="AL205" s="5" t="inlineStr">
+        <is>
+          <t>[A window] served through the cannonade; [D] canister into Fry/Marshall closing on the wall; left-section gun's last double-shotted round into 26th NC (claim-arnold-canister)</t>
+        </is>
+      </c>
+      <c r="AM205" s="5" t="inlineStr">
+        <is>
+          <t>4k/24w of 139 (stone-sentinels); July 3 cannonade-window dominated; pin (negative): Arnold unwounded per Hazard's report</t>
+        </is>
+      </c>
       <c r="AN205" s="5" t="n"/>
-      <c r="AO205" s="5" t="n"/>
+      <c r="AO205" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -22253,20 +22541,56 @@
           <t>reg-us-ii-b3</t>
         </is>
       </c>
-      <c r="AB210" s="5" t="n"/>
+      <c r="AB210" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC210" s="5" t="n"/>
       <c r="AD210" s="5" t="n"/>
       <c r="AE210" s="5" t="n"/>
       <c r="AF210" s="5" t="n"/>
-      <c r="AG210" s="5" t="n"/>
-      <c r="AH210" s="5" t="n"/>
-      <c r="AI210" s="5" t="n"/>
-      <c r="AJ210" s="5" t="n"/>
-      <c r="AK210" s="5" t="n"/>
-      <c r="AL210" s="5" t="n"/>
-      <c r="AM210" s="5" t="n"/>
+      <c r="AG210" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-brown.md; ED-33 candidate on what 'the 18 guns have gone' observed</t>
+        </is>
+      </c>
+      <c r="AH210" s="5" t="inlineStr">
+        <is>
+          <t>Lt. T.F. Brown w July 2 -&gt; Lt. Perrin July 3; Lt. Milne detached to Cushing (mw); 6 Napoleons, 4 serviceable July 3 (brown-1985-filson)</t>
+        </is>
+      </c>
+      <c r="AI210" s="5" t="inlineStr">
+        <is>
+          <t>103 men (stone-sentinels, single-source, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ210" s="5" t="inlineStr">
+        <is>
+          <t>[E] 4-gun line S of Copse (4445,4785) f262 +-30m (Bachelder); [C/D ~14:40] withdrawn over crest to park (4610,4800)</t>
+        </is>
+      </c>
+      <c r="AK210" s="5" t="inlineStr">
+        <is>
+          <t>[D mid-cannonade] ordered withdrawal ~165m by piece [B: &lt;=10 min leg]; no other July 3 movement</t>
+        </is>
+      </c>
+      <c r="AL210" s="5" t="inlineStr">
+        <is>
+          <t>[A window] counter-battery 13:07-~14:40 until long-range ammo out; then SILENT (withdrawn) - one of two real events behind Alexander's 'guns have gone' reading (CA-J3A-4)</t>
+        </is>
+      </c>
+      <c r="AM210" s="5" t="inlineStr">
+        <is>
+          <t>28 whole-battle (stone-sentinels), K/W split not carried - thin; mostly July 2; pins: Brown w Jul 2, Milne mw Jul 3 (on Cushing's rolls)</t>
+        </is>
+      </c>
       <c r="AN210" s="5" t="n"/>
-      <c r="AO210" s="5" t="n"/>
+      <c r="AO210" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -24981,20 +25305,56 @@
           <t>reg-us-ii-b1</t>
         </is>
       </c>
-      <c r="AB232" s="5" t="n"/>
+      <c r="AB232" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC232" s="5" t="n"/>
       <c r="AD232" s="5" t="n"/>
       <c r="AE232" s="5" t="n"/>
       <c r="AF232" s="5" t="n"/>
-      <c r="AG232" s="5" t="n"/>
-      <c r="AH232" s="5" t="n"/>
-      <c r="AI232" s="5" t="n"/>
-      <c r="AJ232" s="5" t="n"/>
-      <c r="AK232" s="5" t="n"/>
-      <c r="AL232" s="5" t="n"/>
-      <c r="AM232" s="5" t="n"/>
+      <c r="AG232" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-rorty.md; no rounds-expended record (negative)</t>
+        </is>
+      </c>
+      <c r="AH232" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Rorty k July 3 (overrun, hand-to-hand) -&gt; Lt. Sheldon w same action -&gt; Lt. Rogers; 4x 10-pdr Parrotts (stone-sentinels)</t>
+        </is>
+      </c>
+      <c r="AI232" s="5" t="inlineStr">
+        <is>
+          <t>114 men (stone-sentinels, single-source)</t>
+        </is>
+      </c>
+      <c r="AJ232" s="5" t="inlineStr">
+        <is>
+          <t>[E] (4435,4570) f262 ~250m S of Copse, fronting prone 19th MA (Bachelder; waitt-1906 pp.234-237); attested-static</t>
+        </is>
+      </c>
+      <c r="AK232" s="5" t="inlineStr">
+        <is>
+          <t>none July 3 (died in place)</t>
+        </is>
+      </c>
+      <c r="AL232" s="5" t="inlineStr">
+        <is>
+          <t>[A window vs CA-J3A-1/5] fought the cannonade to wreckage: 4-&gt;3-&gt;2-&gt;1 gun sequence + caisson burst (waitt-1906 verbatim) - the line's most granular gun-attrition record; [D] canister into Kemper, position briefly overrun</t>
+        </is>
+      </c>
+      <c r="AM232" s="5" t="inlineStr">
+        <is>
+          <t>10k/16w of 114 (stone-sentinels); inverse of the usual shape: steady loss under cannonade + spike at the melee; pins: Rorty k, Sheldon w [D ~15:20-30]</t>
+        </is>
+      </c>
       <c r="AN232" s="5" t="n"/>
-      <c r="AO232" s="5" t="n"/>
+      <c r="AO232" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -26469,20 +26829,56 @@
           <t>reg-us-ii-b4</t>
         </is>
       </c>
-      <c r="AB244" s="5" t="n"/>
+      <c r="AB244" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC244" s="5" t="n"/>
       <c r="AD244" s="5" t="n"/>
       <c r="AE244" s="5" t="n"/>
       <c r="AF244" s="5" t="n"/>
-      <c r="AG244" s="5" t="n"/>
-      <c r="AH244" s="5" t="n"/>
-      <c r="AI244" s="5" t="n"/>
-      <c r="AJ244" s="5" t="n"/>
-      <c r="AK244" s="5" t="n"/>
-      <c r="AL244" s="5" t="n"/>
-      <c r="AM244" s="5" t="n"/>
+      <c r="AG244" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-woodruff.md</t>
+        </is>
+      </c>
+      <c r="AH244" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Woodruff mw July 3 (d. July 4) -&gt; Lt. McCrea (or-27-1-hazard); 6 Napoleons</t>
+        </is>
+      </c>
+      <c r="AI244" s="5" t="inlineStr">
+        <is>
+          <t>120 men (stone-sentinels, single-source)</t>
+        </is>
+      </c>
+      <c r="AJ244" s="5" t="inlineStr">
+        <is>
+          <t>[E] Ziegler's Grove (4570,5095) f252 +-40m - NOT the Angle proper (library note; OSM grove centroid (4584,5101)); attested-static</t>
+        </is>
+      </c>
+      <c r="AK244" s="5" t="inlineStr">
+        <is>
+          <t>none July 3</t>
+        </is>
+      </c>
+      <c r="AL244" s="5" t="inlineStr">
+        <is>
+          <t>[A window] under the cannonade, Napoleons outranged; [D 15:16-30] canister into Pettigrew's left with Osborn's converging fire - half of why ED-5 authors no northern breach</t>
+        </is>
+      </c>
+      <c r="AM244" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT carried: 1k+29w (30) vs 1k+24w (25), same nominal source two extractions (oob-strengths); repulse-window dominated; pin: Woodruff mw [D in repulse fight]</t>
+        </is>
+      </c>
       <c r="AN244" s="5" t="n"/>
-      <c r="AO244" s="5" t="n"/>
+      <c r="AO244" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -28901,20 +29297,56 @@
           <t>reg-us-i-3-3</t>
         </is>
       </c>
-      <c r="AB266" s="5" t="n"/>
+      <c r="AB266" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC266" s="5" t="n"/>
       <c r="AD266" s="5" t="n"/>
       <c r="AE266" s="5" t="n"/>
       <c r="AF266" s="5" t="n"/>
-      <c r="AG266" s="5" t="n"/>
-      <c r="AH266" s="5" t="n"/>
-      <c r="AI266" s="5" t="n"/>
-      <c r="AJ266" s="5" t="n"/>
-      <c r="AK266" s="5" t="n"/>
-      <c r="AL266" s="5" t="n"/>
-      <c r="AM266" s="5" t="n"/>
+      <c r="AG266" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; wheel clock verified-negative (no witness clock exists)</t>
+        </is>
+      </c>
+      <c r="AH266" s="5" t="inlineStr">
+        <is>
+          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
+        </is>
+      </c>
+      <c r="AI266" s="5" t="inlineStr">
+        <is>
+          <t>1,950 brigade (stone-sentinels) vs 1,788 sum of engaged rgts (480+647+661) - ~160-man gap, both carried (oob-strengths #3)</t>
+        </is>
+      </c>
+      <c r="AJ266" s="5" t="inlineStr">
+        <is>
+          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
+        </is>
+      </c>
+      <c r="AK266" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
+        </is>
+      </c>
+      <c r="AL266" s="5" t="inlineStr">
+        <is>
+          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
+        </is>
+      </c>
+      <c r="AM266" s="5" t="inlineStr">
+        <is>
+          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
+        </is>
+      </c>
       <c r="AN266" s="5" t="n"/>
-      <c r="AO266" s="5" t="n"/>
+      <c r="AO266" s="5" t="inlineStr">
+        <is>
+          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB9" s="5" t="inlineStr">
         <is>
-          <t>unauthored (battalion in-build only)</t>
+          <t>unauthored (documented in-window mover - battalion in-build only)</t>
         </is>
       </c>
       <c r="AC9" s="5" t="n"/>
@@ -1396,37 +1396,37 @@
       <c r="AF9" s="5" t="n"/>
       <c r="AG9" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-1c-wsh-3-miller.md</t>
+          <t>Dossier: reconstruction/dossiers/csa-1c-wsh-3-miller.md; second-gun/Owen detail OPEN (owen-1885 access failed)</t>
         </is>
       </c>
       <c r="AH9" s="5" t="inlineStr">
         <is>
-          <t>Capt. M.B. Miller, 3rd Co. Washington Arty; order chain Longstreet -&gt; Walton -&gt; Miller (or-27-2-longstreet verified)</t>
+          <t>Capt. M.B. Miller; 3 Napoleons (Lts Hero, McElroy) + Squires's 1st Co. Napoleon attached 'all under command of Captain Miller' (or-27-2-eshleman); order chain Longstreet -&gt; Walton -&gt; Eshleman/Miller closed verbatim at every link</t>
         </is>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
-          <t>no company figure located (gap); battalion 240 at build grain</t>
+          <t>92 men / 3 Napoleons (addressing-gettysburg-oob, B&amp;M-type, hop flagged) + 1st Co. gun (77-man company)</t>
         </is>
       </c>
       <c r="AJ9" s="5" t="inlineStr">
         <is>
-          <t>[E] inside battalion Peach Orchard frontage, parent centroid (3220,3550) f55; company coord inference +-150m marked</t>
+          <t>[D pre-daylight] 'about 100 yards to the left of the peach orchard, and on the immediate left of Captain Taylor's battery' (or-27-2-eshleman) - company-grain, +-80m; [D post-cannonade] advanced position 400-500 yd to the front</t>
         </is>
       </c>
       <c r="AK9" s="5" t="inlineStr">
         <is>
-          <t>[D pre-daylight] night arrival with battalion; none in-window</t>
+          <t>[D] night arrival; [D after CA-J3A-5/6] ADVANCED 400-500 yd supporting the charge, 'opened with deadly effect' [B: ~410m ~6-8 min] - retires the attested-static reading; horse losses left 'but one gun' usable (marker)</t>
         </is>
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>[A = CA-J3A-1] FIRES THE SIGNAL GUNS 13:07 (jacobs-1864 reading; martin-smith participant grade); then general bombardment fire</t>
+          <t>[A = CA-J3A-1] 'Two guns in quick succession were fired from Captain Miller's battery' (or-27-2-eshleman); 13:07 = Jacobs's reading; then bombardment + advanced-position canister work; rounds expended: attested-absent</t>
         </is>
       </c>
       <c r="AM9" s="5" t="inlineStr">
         <is>
-          <t>no company K/W/M located (gap); no officer pin (negative at corpus grain)</t>
+          <t>'Losses heavy but not reported in detail' (marker) - attested-unreported; battalion aggregate 3 off w + 3k/23w/16m is the ceiling</t>
         </is>
       </c>
       <c r="AN9" s="5" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="AI74" s="5" t="inlineStr">
         <is>
-          <t>576 build adoption; ~24-26 guns (tablet-grade); per-battery figures open</t>
+          <t>576 men / 24 guns (B&amp;M-type, hop flagged; matches build); tablet armament verbatim; Ashland Parrott conflict (20-pdr tablet vs 10-pdr reproduction) carried</t>
         </is>
       </c>
       <c r="AJ74" s="5" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="AK74" s="5" t="inlineStr">
         <is>
-          <t>[D] Jul 2 night redeploy into bombardment line; none in-window (fwd displacement NOT attested - negative + conflict slot)</t>
+          <t>[D] Jul 2 night redeploy to dawn line (Taylor tablet 03:00); IN-WINDOW CONFLICT: SHSP 'ordering those that had over 20 rounds left to limber up and follow Pickett' vs OR 'batteries all maintained their respective positions' - carried; build follows the OR</t>
         </is>
       </c>
       <c r="AL74" s="5" t="inlineStr">
         <is>
-          <t>[A window] core of the cannonade; [C 13:32/13:47 corrected] the two notes to Pickett = CA-J3A-2/3 written from this line; ammunition famine defines the record</t>
+          <t>[A window] core of cannonade, '75 guns' in his wing (SHSP); [C 13:32/13:47 corr.] the two notes = CA-J3A-2/3 (SHSP wording verified; 13:30-vs-13:25 internal variant); ammunition famine verbatim ('not over 20 rounds to the gun were left'); rounds expended attested-absent in OR</t>
         </is>
       </c>
       <c r="AM74" s="5" t="inlineStr">
         <is>
-          <t>battalion K/W/M open (gap); Jul 2 the bloody day; pin: Woolfolk w Jul 2</t>
+          <t>OR return verbatim: 19k/114w/6m = 139 + 116 horses, 1 howitzer destroyed (Jul 2-3 joint - no primary day split); Taylor's marker 2k/10w only per-battery figure; pins: Woolfolk w Jul 2, Gilbert w (SNIPPET)</t>
         </is>
       </c>
       <c r="AN74" s="5" t="n"/>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="AI80" s="5" t="inlineStr">
         <is>
-          <t>240 build adoption (tablet-cited); per-company figures open</t>
+          <t>CONFLICT: build 240 vs 338 (B&amp;M-type, hop flagged; '340' SNIPPET variant); 8 Napoleons + 2 12-pdr howitzers (tablet + OR concur) -&gt; ED-38 candidate</t>
         </is>
       </c>
       <c r="AJ80" s="5" t="inlineStr">
         <is>
-          <t>[D/E] 'Arrived on the field before daylight' Jul 3 (tablet verbatim); [E] Peach Orchard line (3220,3550) f55, frontage ~300m</t>
+          <t>[D before daylight] per-company layout verbatim (or-27-2-eshleman): 3rd Co ~100yd left of Peach Orchard on Taylor's left, 4th on Miller's left, 2nd on Norcom's left, 2 howitzers reserve; Pendleton: 'nearly sixty guns for that wing'; centroid (3220,3550) f55; [E] park near old school-house at dark; [C 09:00 Jul 4] Cashtown (tablet-only)</t>
         </is>
       </c>
       <c r="AK80" s="5" t="inlineStr">
         <is>
-          <t>[D before ~04:30 daylight] night march onto field; attested-static in window</t>
+          <t>[D] night march (Sorrel's July 1 5:30 PM order verbatim, walton-shsp5-1877; Owen-as-quoted: started ~10:30-11 PM, wagon-train delay); in-window: Miller+Battles advance 400-500yd; Norcom's Napoleons moved several hundred yd left then disabled; howitzers brought forward</t>
         </is>
       </c>
       <c r="AL80" s="5" t="inlineStr">
         <is>
-          <t>[A] CA-J3A-1 signal guns via 3rd Co.; [A window] 10 guns in the general bombardment ('YES + the 13:07 signal guns', tablet-grade)</t>
+          <t>[A = CA-J3A-1] the signal guns verbatim; bombardment; captured Union 3-in rifle served by Richardson's co. until axle-struck (marker + OR); 'About thirty minutes after the signal guns... our infantry moved forward' AMBIGUOUS - conflict-flagged, rule 4; rounds: attested-absent</t>
         </is>
       </c>
       <c r="AM80" s="5" t="inlineStr">
         <is>
-          <t>battalion K/W/M open (gap); pin: Capt. Norcom w Jul 3; clean single-episode shape (arrived Jul 3)</t>
+          <t>OR return verbatim: 3 officers w; 3k/23w/16m men + 37 horses, 3 guns disabled, 1 limber blown up (tablet folds to 3/26/16=45); all July 3 (clean single-day); pin: Norcom w 'early in the day'</t>
         </is>
       </c>
       <c r="AN80" s="5" t="n"/>
@@ -18082,12 +18082,12 @@
       </c>
       <c r="AI164" s="5" t="inlineStr">
         <is>
-          <t>no engaged-men figure located (gap); '39 guns' secondary-grade; tablet-verified 9-battery roster is the stronger form</t>
+          <t>PRIMARY now: 15 officers + 368 men taken into action (organic 4 batteries, OR p. 884 footnote); line gun count 'total, thirty-nine guns' (his OR) vs Hunt B&amp;L 41 - carried</t>
         </is>
       </c>
       <c r="AJ164" s="5" t="inlineStr">
         <is>
-          <t>[C p.881] July 2 Wheatfield Rd line from ~15:30; [D] Trostle stand + Plum Run line; [E] July 3 massed lower-Cemetery-Ridge line, ref point Phillips (4212,4080) f265; sheet-8 Daniels/Rank labels CONFLICT with OOB (ECF)</t>
+          <t>[C ~15:30 Jul 2] Wheatfield Rd line; [C 17:45] retire 250 yd by stages; Trostle stand; 400-yd-rear line; [E Jul 3] low-ground line w/ earthwork, roster VERBATIM left-&gt;right incl. 'a New Jersey battery' + Rank's section (OR-vs-OOB conflict -&gt; ED-37); ref point Phillips (4212,4080)</t>
         </is>
       </c>
       <c r="AK164" s="5" t="inlineStr">
@@ -18097,18 +18097,18 @@
       </c>
       <c r="AL164" s="5" t="inlineStr">
         <is>
-          <t>[A window] ORDERED SILENCE under Hunt's policy (CA-J3A-4's largest component); 'fired about one hour and a half... 10,000 rounds' (or-27-1-mcgilvery p.884); [C ~15:00] first line 'completely broken up and scattered by our fire'; oblique raking fire through all three lines; then Wilcox/Lang smashed with 16th VT</t>
+          <t>[C 12:30 stated] opening '140 guns', overshoots 20-100 ft; [A window] pre-arranged hold-fire verbatim; the 'some general' breach put down; [C] 1.5h then deliberate battery-by-battery reply; [C ~15:00] first line 'completely broken up and scattered'; oblique raking fire through all three lines; Wilcox/Lang smashed</t>
         </is>
       </c>
       <c r="AM164" s="5" t="inlineStr">
         <is>
-          <t>brigade K/W/M not located (gap; July 2 dominates via Bigelow's stand); pin: Bigelow w July 2</t>
+          <t>tablet verbatim: 1 off + 16 men k, 10 off + 61 w, 5 m = 93 (~24% of 383); July 2 dominates (Bigelow w at the Trostle stand; horse pins); July 3 light per his own overshoot statement</t>
         </is>
       </c>
       <c r="AN164" s="5" t="n"/>
       <c r="AO164" s="5" t="inlineStr">
         <is>
-          <t>T4 (brigade grain)</t>
+          <t>T4 (brigade/line grain)</t>
         </is>
       </c>
     </row>
@@ -18661,12 +18661,12 @@
       </c>
       <c r="AL170" s="5" t="inlineStr">
         <is>
-          <t>[A window] FOUGHT THE CANNONADE THROUGHOUT under Hancock's counter-order; long-range ammo exhausted (or-27-1-hazard) -&gt; canister-only repulse fight</t>
+          <t>[C ~08:00] morning exchanges (3 of Cushing's limbers exploded; Woodruff 8 forenoon engagements); [A window] 'did not at first reply, till the fire of the enemy becoming too terrible' then fired ALL long-range ammo in 'an hour and a quarter'; [D] 'half the valley had been passed over... before the guns dared expend a round'; canister 'with terrible effect'; consolidation 5-&gt;3 batteries after (all or-27-1-hazard, read live pp. 477-481)</t>
         </is>
       </c>
       <c r="AM170" s="5" t="inlineStr">
         <is>
-          <t>150 (25k/120w/5m), 35% - highest-pct Union arty bde loss; flat-then-spike shape vs the silent-then-fire lines; 5 officer pins at battery grain</t>
+          <t>'one-third' of the brigade; 28k/119w/3m (report note) vs tablet 3+24k/5+114w/3m = 149; July 2 splits primary for Brown's (1k/7w/2m+24 horses) and Rorty's (1k/8w); 5 officer pins verbatim</t>
         </is>
       </c>
       <c r="AN170" s="5" t="n"/>
@@ -19024,7 +19024,7 @@
       <c r="AF174" s="5" t="n"/>
       <c r="AG174" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-arty-osborn.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-arty-osborn.md; HEADLINE: contemporary motive ('no satisfactory results') vs postwar ruse - ED-33's sharpest evidence; ruse verbatim unreachable (verified absence)</t>
         </is>
       </c>
       <c r="AH174" s="5" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="AI174" s="5" t="inlineStr">
         <is>
-          <t>no men figure located (gap); ~39 guns secondary-grade; tablet-verified 9-battery roster is the stronger form</t>
+          <t>his OR: 26 guns organic Jul 1 -&gt; 52 on the hill Jul 2 morning (roster verbatim); ~36 his command Jul 3 (seminar); men figure still open; '~1,600 rounds' DOWNGRADED - his report: 'I am unable to give any definite estimate'</t>
         </is>
       </c>
       <c r="AJ174" s="5" t="inlineStr">
@@ -19049,12 +19049,12 @@
       </c>
       <c r="AL174" s="5" t="inlineStr">
         <is>
-          <t>[A window] counter-battery under the crossfire; [C ~14:30] THE CEASE-FIRE RUSE (proposed Osborn, adopted Hunt/Howard) = CA-J3A-4/5's sharpest component; [D] ~1,600 rounds into Pettigrew's left (secondary-grade)</t>
+          <t>[A window] deliberate counter-battery under the crossfire; [D] HIS OWN cease verbatim: 'as no satisfactory results were obtained, I ordered all our guns to cease firing... a few moments later the infantry of the enemy broke over the crest' - tightest Union cease-to-step-off coupling; [D] repulse fire 'havoc... truly surprising', artillery ignored by his order</t>
         </is>
       </c>
       <c r="AM174" s="5" t="inlineStr">
         <is>
-          <t>brigade K/W/M open (gap); Jul 1-2 dominate the shape; no Jul 3 officer pin located (negative)</t>
+          <t>tablet verbatim: 1 off + 6 men k, 3 off + 50 w, 9 m = 69; 98 horses (OR materiel table concurs); 1 gun captured/1 disabled/2 dismounted; pin: Wilkeson mw Jul 1 at the first fire -&gt; Bancroft</t>
         </is>
       </c>
       <c r="AN174" s="5" t="n"/>
@@ -21637,18 +21637,18 @@
       </c>
       <c r="AL203" s="5" t="inlineStr">
         <is>
-          <t>[C ~11:00] withhold-fire instruction; [C ~14:30] the slacken/cease order (CA-J3A-4); [D] Hancock counter-order conflict; [D] repulse-window battery reinforcements</t>
+          <t>[C 10:00] husband-ammunition instruction verbatim; [C 14:30] 'About 2.30 p.m. ... I directed that the fire should be gradually stopped... and the enemy soon slackened his fire also' (or-27-1-hunt) = CA-J3A-4 clock-fixed by its author; [C ~15:00] 'About 3 p.m., and soon after the enemy's fire had ceased, he formed a column of attack'; [B] 32,781 rounds of 270/gun carried - the economy arithmetic primary</t>
         </is>
       </c>
       <c r="AM203" s="5" t="inlineStr">
         <is>
-          <t>n/a; horse killed at Cowan's guns</t>
+          <t>army artillery return: 7 off + 98 men k, 33 off + 532 w, 67 m, 881 horses (or-27-1-hunt); July 3 officer list confirms Rorty/Cushing k, Woodruff/Milne mw</t>
         </is>
       </c>
       <c r="AN203" s="5" t="n"/>
       <c r="AO203" s="5" t="inlineStr">
         <is>
-          <t>T2 (command record)</t>
+          <t>T2 (command record; order events clock-fixed)</t>
         </is>
       </c>
     </row>
@@ -21921,7 +21921,7 @@
       </c>
       <c r="AL205" s="5" t="inlineStr">
         <is>
-          <t>[A window] served through the cannonade; [D] canister into Fry/Marshall closing on the wall; left-section gun's last double-shotted round into 26th NC (claim-arnold-canister)</t>
+          <t>[A window] served through the cannonade; 'expended every round, and the lines of the enemy still advanced' (or-27-1-hazard); [D] 'final shots were double-shotted canister' into Fry/Marshall; then withdrew his own AND Cushing's battery (Hazard); Hunt: withdrawn 'toward the close'</t>
         </is>
       </c>
       <c r="AM205" s="5" t="inlineStr">
@@ -22582,7 +22582,7 @@
       </c>
       <c r="AM210" s="5" t="inlineStr">
         <is>
-          <t>28 whole-battle (stone-sentinels), K/W split not carried - thin; mostly July 2; pins: Brown w Jul 2, Milne mw Jul 3 (on Cushing's rolls)</t>
+          <t>7k/19w/2m = 28 whole battle (tablet split closes the flag); July 2 PRIMARY: 1k/7w/2m + 24 horses killed 6 disabled, 2 guns to rear (or-27-1-hazard); Brown w neck by musket-shot; Milne mw on Cushing's rolls</t>
         </is>
       </c>
       <c r="AN210" s="5" t="n"/>
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AM232" s="5" t="inlineStr">
         <is>
-          <t>10k/16w of 114 (stone-sentinels); inverse of the usual shape: steady loss under cannonade + spike at the melee; pins: Rorty k, Sheldon w [D ~15:20-30]</t>
+          <t>10k/16w of 114 (monument); July 2 PRIMARY: 1k/8w + 13 horses (or-27-1-hazard); 'entirely exhausted; its ammunition expended; its horses and men killed and disabled'; pins Rorty k (1 day in command), Sheldon w - confirmed in Hunt's officer list</t>
         </is>
       </c>
       <c r="AN232" s="5" t="n"/>
@@ -26865,12 +26865,12 @@
       </c>
       <c r="AL244" s="5" t="inlineStr">
         <is>
-          <t>[A window] under the cannonade, Napoleons outranged; [D 15:16-30] canister into Pettigrew's left with Osborn's converging fire - half of why ED-5 authors no northern breach</t>
+          <t>[C ~08:00-noon] EIGHT separate forenoon engagements (only II Corps battery active); [A window] under the cannonade; [D] canister into Pettigrew's left; last battery in action - 'Woodruff still remained in the grove, and poured death and destruction' (or-27-1-hazard)</t>
         </is>
       </c>
       <c r="AM244" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT carried: 1k+29w (30) vs 1k+24w (25), same nominal source two extractions (oob-strengths); repulse-window dominated; pin: Woodruff mw [D in repulse fight]</t>
+          <t>RESOLVED toward 30: tablet 'killed 1 man, wounded 1 officer and 28 men' (re-verified); pin: Woodruff mw 'at the very moment of victory', d. Jul 4, buried on the field at his own request (or-27-1-hazard)</t>
         </is>
       </c>
       <c r="AN244" s="5" t="n"/>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -7445,20 +7445,56 @@
           <t>reg-csa-2c-bn-latimer</t>
         </is>
       </c>
-      <c r="AB75" s="5" t="n"/>
+      <c r="AB75" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC75" s="5" t="n"/>
       <c r="AD75" s="5" t="n"/>
       <c r="AE75" s="5" t="n"/>
       <c r="AF75" s="5" t="n"/>
-      <c r="AG75" s="5" t="n"/>
-      <c r="AH75" s="5" t="n"/>
-      <c r="AI75" s="5" t="n"/>
-      <c r="AJ75" s="5" t="n"/>
-      <c r="AK75" s="5" t="n"/>
-      <c r="AL75" s="5" t="n"/>
-      <c r="AM75" s="5" t="n"/>
+      <c r="AG75" s="5" t="inlineStr">
+        <is>
+          <t>Group dossier: reconstruction/dossiers/csa-2c-arty-ewell-wing.md - Brown's corps report corrects 'near-silence' to structured partial participation (ED-45 candidate)</t>
+        </is>
+      </c>
+      <c r="AH75" s="5" t="inlineStr">
+        <is>
+          <t>Latimer mw Jul 2 (Benner's Hill) -&gt; Capt. Raine</t>
+        </is>
+      </c>
+      <c r="AI75" s="5" t="inlineStr">
+        <is>
+          <t>356 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ75" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 Benner's Hill (the Wainwright-group duel's other side); Jul 3 position unstated (open)</t>
+        </is>
+      </c>
+      <c r="AK75" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 withdrawal of three batteries under fire</t>
+        </is>
+      </c>
+      <c r="AL75" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 duel; Jul 3 ABSENT-FROM-RECORD in Brown's report (probably-limited, NOT attested-silent)</t>
+        </is>
+      </c>
+      <c r="AM75" s="5" t="inlineStr">
+        <is>
+          <t>Latimer mw = the pin; figures unfetched</t>
+        </is>
+      </c>
       <c r="AN75" s="5" t="n"/>
-      <c r="AO75" s="5" t="n"/>
+      <c r="AO75" s="5" t="inlineStr">
+        <is>
+          <t>T2 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7569,20 +7605,56 @@
           <t>reg-csa-1c-bn-cabell</t>
         </is>
       </c>
-      <c r="AB76" s="5" t="n"/>
+      <c r="AB76" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (consolidated line + post-assault forward move)</t>
+        </is>
+      </c>
       <c r="AC76" s="5" t="n"/>
       <c r="AD76" s="5" t="n"/>
       <c r="AE76" s="5" t="n"/>
       <c r="AF76" s="5" t="n"/>
-      <c r="AG76" s="5" t="n"/>
-      <c r="AH76" s="5" t="n"/>
-      <c r="AI76" s="5" t="n"/>
-      <c r="AJ76" s="5" t="n"/>
-      <c r="AK76" s="5" t="n"/>
-      <c r="AL76" s="5" t="n"/>
-      <c r="AM76" s="5" t="n"/>
+      <c r="AG76" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-bn-cabell.md</t>
+        </is>
+      </c>
+      <c r="AH76" s="5" t="inlineStr">
+        <is>
+          <t>Col. Cabell; Manly/Fraser/McCarthy/Carlton; 16 guns (tablet); Fraser w Jul 2 (dangerous), Carlton w Jul 3, Couper/Jennings w</t>
+        </is>
+      </c>
+      <c r="AI76" s="5" t="inlineStr">
+        <is>
+          <t>384 (build) vs 380 (SS compilation) - both hops carried (ED-38)</t>
+        </is>
+      </c>
+      <c r="AJ76" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 wood-edge line, right near the Emmitsburg road, 600-700 yd from the Peach Orchard guns; [C/D] Jul 3 six guns near a brick house on the road + Carlton/McCarthy en echelon BEFORE Pickett; [C ~16:00] post-assault line on the road ~700 yd from Cemetery Hill, held till night; j3-03 McCARTY label ~(3500,4670)</t>
+        </is>
+      </c>
+      <c r="AK76" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 3 pre-dawn consolidation move north; [C ~16:00] forward onto the road; [D] withdrawal after dark</t>
+        </is>
+      </c>
+      <c r="AL76" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 duel; [C +7] 'about 1 p.m....over two hours' cannonade (chain-agreeing CSA clock); McCarthy morning probe fired 20 rounds; ROUNDS: ~3,300 Jul 2-3 (tablet) [B: ~206/gun]</t>
+        </is>
+      </c>
+      <c r="AM76" s="5" t="inlineStr">
+        <is>
+          <t>tablet 12k/30w/4m + 80 horses vs SS 15k/57w - carried (report table unfetched); Jul 2 pins Fraser; Jul 3 pins Carlton/Jennings</t>
+        </is>
+      </c>
       <c r="AN76" s="5" t="n"/>
-      <c r="AO76" s="5" t="n"/>
+      <c r="AO76" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7693,20 +7765,56 @@
           <t>reg-csa-2c-bn-carter</t>
         </is>
       </c>
-      <c r="AB77" s="5" t="n"/>
+      <c r="AB77" s="5" t="inlineStr">
+        <is>
+          <t>attested-static</t>
+        </is>
+      </c>
       <c r="AC77" s="5" t="n"/>
       <c r="AD77" s="5" t="n"/>
       <c r="AE77" s="5" t="n"/>
       <c r="AF77" s="5" t="n"/>
-      <c r="AG77" s="5" t="n"/>
-      <c r="AH77" s="5" t="n"/>
-      <c r="AI77" s="5" t="n"/>
-      <c r="AJ77" s="5" t="n"/>
-      <c r="AK77" s="5" t="n"/>
-      <c r="AL77" s="5" t="n"/>
-      <c r="AM77" s="5" t="n"/>
+      <c r="AG77" s="5" t="inlineStr">
+        <is>
+          <t>Group dossier: reconstruction/dossiers/csa-2c-arty-ewell-wing.md - Brown's corps report corrects 'near-silence' to structured partial participation (ED-45 candidate)</t>
+        </is>
+      </c>
+      <c r="AH77" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Carter (Rodes); Reese/W.Carter/Page/Fry</t>
+        </is>
+      </c>
+      <c r="AI77" s="5" t="inlineStr">
+        <is>
+          <t>384 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ77" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 foot of the high ridge (Page vs O'Neal front); [C] Jul 3 ten rifled guns 'on the high ridge on the right and left of the railroad cut'</t>
+        </is>
+      </c>
+      <c r="AK77" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 legs; [C] Jul 2 ATTESTED IDLE ('held in readiness...not engaged')</t>
+        </is>
+      </c>
+      <c r="AL77" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 fights; [C] Jul 3 diversion fire on Cemetery Hill covering Dance; observation 'Their fire slackened, and finally ceased' = CSA-side CA-J3A-4-&gt;5 sequence witness [D]</t>
+        </is>
+      </c>
+      <c r="AM77" s="5" t="inlineStr">
+        <is>
+          <t>Jul 1 PRIMARY per-battery: Page 2k/2mw/26w + 17 horses; rest unfetched</t>
+        </is>
+      </c>
       <c r="AN77" s="5" t="n"/>
-      <c r="AO77" s="5" t="n"/>
+      <c r="AO77" s="5" t="inlineStr">
+        <is>
+          <t>T2 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7817,20 +7925,56 @@
           <t>reg-csa-2c-bn-dance</t>
         </is>
       </c>
-      <c r="AB78" s="5" t="n"/>
+      <c r="AB78" s="5" t="inlineStr">
+        <is>
+          <t>attested-static</t>
+        </is>
+      </c>
       <c r="AC78" s="5" t="n"/>
       <c r="AD78" s="5" t="n"/>
       <c r="AE78" s="5" t="n"/>
       <c r="AF78" s="5" t="n"/>
-      <c r="AG78" s="5" t="n"/>
-      <c r="AH78" s="5" t="n"/>
-      <c r="AI78" s="5" t="n"/>
-      <c r="AJ78" s="5" t="n"/>
-      <c r="AK78" s="5" t="n"/>
-      <c r="AL78" s="5" t="n"/>
-      <c r="AM78" s="5" t="n"/>
+      <c r="AG78" s="5" t="inlineStr">
+        <is>
+          <t>Group dossier: reconstruction/dossiers/csa-2c-arty-ewell-wing.md - Brown's corps report corrects 'near-silence' to structured partial participation (ED-45 candidate)</t>
+        </is>
+      </c>
+      <c r="AH78" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Dance; 2nd Corps reserve (Brown)</t>
+        </is>
+      </c>
+      <c r="AI78" s="5" t="inlineStr">
+        <is>
+          <t>480 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ78" s="5" t="inlineStr">
+        <is>
+          <t>[C] Seminary/Oak ridge north sector, covered by Carter's ten rifles at the railroad cut</t>
+        </is>
+      </c>
+      <c r="AK78" s="5" t="inlineStr">
+        <is>
+          <t>none Jul 3 (static)</t>
+        </is>
+      </c>
+      <c r="AL78" s="5" t="inlineStr">
+        <is>
+          <t>[C] JUL 3 ENGAGED: 'The First Virginia Artillery...engaged the enemy's batteries, in order to divert their fire' (or-27-2-jtbrown) - the wing's firing battalion; Jul 2 Watson's/Smith's batteries aided Latimer's duel</t>
+        </is>
+      </c>
+      <c r="AM78" s="5" t="inlineStr">
+        <is>
+          <t>unfetched (open)</t>
+        </is>
+      </c>
       <c r="AN78" s="5" t="n"/>
-      <c r="AO78" s="5" t="n"/>
+      <c r="AO78" s="5" t="inlineStr">
+        <is>
+          <t>T2 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7941,20 +8085,56 @@
           <t>reg-csa-1c-bn-dearing</t>
         </is>
       </c>
-      <c r="AB79" s="5" t="n"/>
+      <c r="AB79" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (static line; daybreak advance attested)</t>
+        </is>
+      </c>
       <c r="AC79" s="5" t="n"/>
       <c r="AD79" s="5" t="n"/>
       <c r="AE79" s="5" t="n"/>
       <c r="AF79" s="5" t="n"/>
-      <c r="AG79" s="5" t="n"/>
-      <c r="AH79" s="5" t="n"/>
-      <c r="AI79" s="5" t="n"/>
-      <c r="AJ79" s="5" t="n"/>
-      <c r="AK79" s="5" t="n"/>
-      <c r="AL79" s="5" t="n"/>
-      <c r="AM79" s="5" t="n"/>
+      <c r="AG79" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-bn-dearing.md</t>
+        </is>
+      </c>
+      <c r="AH79" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Dearing; Stribling/Caskie/Macon/Blount; 18 guns (tablet verbatim); Maj. Read w Jul 3 morning; HIS OWN OR REPORT FOUND (pass 1 assumed none)</t>
+        </is>
+      </c>
+      <c r="AI79" s="5" t="inlineStr">
+        <is>
+          <t>432 (B&amp;M-type hop per ED-38)</t>
+        </is>
+      </c>
+      <c r="AJ79" s="5" t="inlineStr">
+        <is>
+          <t>[C] arrived dusk Jul 2 (Pendleton chain); [C/D] daybreak Jul 3 to 'the crest of the hill immediately in front of the enemy's position'; RELATIONS PRIMARY: Cabell left+rear, Washington Arty right+rear; j3-03 labels CASKIE(3610,4480) BLOUNT(3670,4550) MACON(3620,4310) on the road-crest line</t>
+        </is>
+      </c>
+      <c r="AK79" s="5" t="inlineStr">
+        <is>
+          <t>[D] night march chain; [C/D] daybreak advance; withdrawal CONFLICT: tablet 'about 4 P.M.' vs his own 18:00 repulse fire - carried</t>
+        </is>
+      </c>
+      <c r="AL79" s="5" t="inlineStr">
+        <is>
+          <t>[D] daybreak skirmish (Stribling ~12 rounds); [A vs CA-J3A-1] deliberate by-battery fire at the signal; ammunition 'completely exhausted, excepting a few round in my rifled guns'; silent-under-fire 'upward of an hour'; rounds total attested-absent</t>
+        </is>
+      </c>
+      <c r="AM79" s="5" t="inlineStr">
+        <is>
+          <t>per-battery PRIMARY (3 of 4): Stribling 3w+10h, Macon 3k/3w+8h, Blount 5kw+12h; Caskie = extraction gap (flagged); all Jul 3</t>
+        </is>
+      </c>
       <c r="AN79" s="5" t="n"/>
-      <c r="AO79" s="5" t="n"/>
+      <c r="AO79" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8086,7 +8266,7 @@
       </c>
       <c r="AI80" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT: build 240 vs 338 (B&amp;M-type, hop flagged; '340' SNIPPET variant); 8 Napoleons + 2 12-pdr howitzers (tablet + OR concur) -&gt; ED-38 candidate</t>
+          <t>ADOPTED ED-38: 338 (B&amp;M-type, hop cited; build's 240 retired; '340' SNIPPET variant recorded); 8 Napoleons + 2 12-pdr howitzers (tablet + OR concur)</t>
         </is>
       </c>
       <c r="AJ80" s="5" t="inlineStr">
@@ -8225,20 +8405,56 @@
           <t>reg-csa-3c-bn-garnett</t>
         </is>
       </c>
-      <c r="AB81" s="5" t="n"/>
+      <c r="AB81" s="5" t="inlineStr">
+        <is>
+          <t>attested-static + ATTESTED SILENT Jul 3</t>
+        </is>
+      </c>
       <c r="AC81" s="5" t="n"/>
       <c r="AD81" s="5" t="n"/>
       <c r="AE81" s="5" t="n"/>
       <c r="AF81" s="5" t="n"/>
-      <c r="AG81" s="5" t="n"/>
-      <c r="AH81" s="5" t="n"/>
-      <c r="AI81" s="5" t="n"/>
-      <c r="AJ81" s="5" t="n"/>
-      <c r="AK81" s="5" t="n"/>
-      <c r="AL81" s="5" t="n"/>
-      <c r="AM81" s="5" t="n"/>
+      <c r="AG81" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-bn-garnett.md; ED-44 candidate (attested-silence rendering rule); subtracts 15 tubes from every cannonade gun-count claim</t>
+        </is>
+      </c>
+      <c r="AH81" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. J.J. Garnett / Maj. Richardson (rifle group); Maurin/Moore/Lewis/Grandy; 9 rifles + 6 smoothbores</t>
+        </is>
+      </c>
+      <c r="AI81" s="5" t="inlineStr">
+        <is>
+          <t>360 (hop, ED-38)</t>
+        </is>
+      </c>
+      <c r="AJ81" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 pike support; [C] Jul 2 rifles opposite Cemetery Hill; [C/D] Jul 3 rifles right of Pegram on Anderson's front; smoothbores in reserve (park class, 200m)</t>
+        </is>
+      </c>
+      <c r="AK81" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1/2/3 postings; [C] Jul 4 reoccupation; Richardson + 5 rifles to Imboden's train</t>
+        </is>
+      </c>
+      <c r="AL81" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 fire 15:00 -&gt; ~30 min before sunset (the one fire episode); JUL 3 NEGATIVE VERBATIM: 'did not fire a single shot, having received orders to that effect'; smoothbores 'bore no part in these actions'; tablet concurs</t>
+        </is>
+      </c>
+      <c r="AM81" s="5" t="inlineStr">
+        <is>
+          <t>UNFETCHED (p. 654 gap - open slot, not attested-absent)</t>
+        </is>
+      </c>
       <c r="AN81" s="5" t="n"/>
-      <c r="AO81" s="5" t="n"/>
+      <c r="AO81" s="5" t="inlineStr">
+        <is>
+          <t>T2 (negative-evidence)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8349,20 +8565,56 @@
           <t>reg-csa-2c-bn-jones</t>
         </is>
       </c>
-      <c r="AB82" s="5" t="n"/>
+      <c r="AB82" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC82" s="5" t="n"/>
       <c r="AD82" s="5" t="n"/>
       <c r="AE82" s="5" t="n"/>
       <c r="AF82" s="5" t="n"/>
-      <c r="AG82" s="5" t="n"/>
-      <c r="AH82" s="5" t="n"/>
-      <c r="AI82" s="5" t="n"/>
-      <c r="AJ82" s="5" t="n"/>
-      <c r="AK82" s="5" t="n"/>
-      <c r="AL82" s="5" t="n"/>
-      <c r="AM82" s="5" t="n"/>
+      <c r="AG82" s="5" t="inlineStr">
+        <is>
+          <t>Group dossier: reconstruction/dossiers/csa-2c-arty-ewell-wing.md - Brown's corps report corrects 'near-silence' to structured partial participation (ED-45 candidate)</t>
+        </is>
+      </c>
+      <c r="AH82" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. H.P. Jones (Early)</t>
+        </is>
+      </c>
+      <c r="AI82" s="5" t="inlineStr">
+        <is>
+          <t>290 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ82" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 3 ATTESTED-ELSEWHERE: 'operated with the cavalry'; Tanner's battery with the wagon train (Williamsport)</t>
+        </is>
+      </c>
+      <c r="AK82" s="5" t="inlineStr">
+        <is>
+          <t>off-field legs (not researched this pass)</t>
+        </is>
+      </c>
+      <c r="AL82" s="5" t="inlineStr">
+        <is>
+          <t>[C] off the main field Jul 3 - subtracts ~16 tubes from cannonade census</t>
+        </is>
+      </c>
+      <c r="AM82" s="5" t="inlineStr">
+        <is>
+          <t>unfetched (open)</t>
+        </is>
+      </c>
       <c r="AN82" s="5" t="n"/>
-      <c r="AO82" s="5" t="n"/>
+      <c r="AO82" s="5" t="inlineStr">
+        <is>
+          <t>T2 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8597,20 +8849,56 @@
           <t>reg-csa-3c-bn-mcintosh</t>
         </is>
       </c>
-      <c r="AB84" s="5" t="n"/>
+      <c r="AB84" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (Jul 2-3 line)</t>
+        </is>
+      </c>
       <c r="AC84" s="5" t="n"/>
       <c r="AD84" s="5" t="n"/>
       <c r="AE84" s="5" t="n"/>
       <c r="AF84" s="5" t="n"/>
-      <c r="AG84" s="5" t="n"/>
-      <c r="AH84" s="5" t="n"/>
-      <c r="AI84" s="5" t="n"/>
-      <c r="AJ84" s="5" t="n"/>
-      <c r="AK84" s="5" t="n"/>
-      <c r="AL84" s="5" t="n"/>
-      <c r="AM84" s="5" t="n"/>
+      <c r="AG84" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-bn-mcintosh.md</t>
+        </is>
+      </c>
+      <c r="AH84" s="5" t="inlineStr">
+        <is>
+          <t>Maj. McIntosh; Rice/Hurt/Wallace/Johnson; 16 guns incl. 2 Whitworths (tablet)</t>
+        </is>
+      </c>
+      <c r="AI84" s="5" t="inlineStr">
+        <is>
+          <t>384 (hop, ED-38)</t>
+        </is>
+      </c>
+      <c r="AJ84" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 Cashtown pike flank (railroad-cut enfilade); [C] Jul 2-3 'behind a stone wall, on the range of hills to the left of the town' (wall segment unresolved - radius 150m band; pass-3 crop item)</t>
+        </is>
+      </c>
+      <c r="AK84" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 in with Pender; [D] one-mile advance Jul 1-&gt;2; [C] Jul 4 afternoon withdrawal to Marsh Creek</t>
+        </is>
+      </c>
+      <c r="AL84" s="5" t="inlineStr">
+        <is>
+          <t>[C] railroad-cut enfilade Jul 1; [A window] Jul 3 sustained fire; ROUNDS ITEMIZED: 213 Napoleon + 1,049 rifle + 133 Whitworth = 1,395 (verbatim) [B: Napoleon 36/gun = range-limited signature]</t>
+        </is>
+      </c>
+      <c r="AM84" s="5" t="inlineStr">
+        <is>
+          <t>24 k&amp;w + 16 captured + 38 horses (report) vs tablet 7k/25w(16 captured) - k+w totals disagree, carried; no per-day split</t>
+        </is>
+      </c>
       <c r="AN84" s="5" t="n"/>
-      <c r="AO84" s="5" t="n"/>
+      <c r="AO84" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8721,20 +9009,56 @@
           <t>reg-csa-2c-bn-nelson</t>
         </is>
       </c>
-      <c r="AB85" s="5" t="n"/>
+      <c r="AB85" s="5" t="inlineStr">
+        <is>
+          <t>attested-static</t>
+        </is>
+      </c>
       <c r="AC85" s="5" t="n"/>
       <c r="AD85" s="5" t="n"/>
       <c r="AE85" s="5" t="n"/>
       <c r="AF85" s="5" t="n"/>
-      <c r="AG85" s="5" t="n"/>
-      <c r="AH85" s="5" t="n"/>
-      <c r="AI85" s="5" t="n"/>
-      <c r="AJ85" s="5" t="n"/>
-      <c r="AK85" s="5" t="n"/>
-      <c r="AL85" s="5" t="n"/>
-      <c r="AM85" s="5" t="n"/>
+      <c r="AG85" s="5" t="inlineStr">
+        <is>
+          <t>Group dossier: reconstruction/dossiers/csa-2c-arty-ewell-wing.md - Brown's corps report corrects 'near-silence' to structured partial participation (ED-45 candidate)</t>
+        </is>
+      </c>
+      <c r="AH85" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Nelson</t>
+        </is>
+      </c>
+      <c r="AI85" s="5" t="inlineStr">
+        <is>
+          <t>264 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ85" s="5" t="inlineStr">
+        <is>
+          <t>[D] Oak Hill sector, position unstated in fetched pages (radius 300m, flagged)</t>
+        </is>
+      </c>
+      <c r="AK85" s="5" t="inlineStr">
+        <is>
+          <t>none stated</t>
+        </is>
+      </c>
+      <c r="AL85" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 3 'a portion' engaged (diversion mission, or-27-2-jtbrown); remainder = absence-of-record, NOT attested-silent</t>
+        </is>
+      </c>
+      <c r="AM85" s="5" t="inlineStr">
+        <is>
+          <t>unfetched (open)</t>
+        </is>
+      </c>
       <c r="AN85" s="5" t="n"/>
-      <c r="AO85" s="5" t="n"/>
+      <c r="AO85" s="5" t="inlineStr">
+        <is>
+          <t>T2 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -8845,20 +9169,56 @@
           <t>reg-csa-3c-bn-pegram</t>
         </is>
       </c>
-      <c r="AB86" s="5" t="n"/>
+      <c r="AB86" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (Jul 2-3 line)</t>
+        </is>
+      </c>
       <c r="AC86" s="5" t="n"/>
       <c r="AD86" s="5" t="n"/>
       <c r="AE86" s="5" t="n"/>
       <c r="AF86" s="5" t="n"/>
-      <c r="AG86" s="5" t="n"/>
-      <c r="AH86" s="5" t="n"/>
-      <c r="AI86" s="5" t="n"/>
-      <c r="AJ86" s="5" t="n"/>
-      <c r="AK86" s="5" t="n"/>
-      <c r="AL86" s="5" t="n"/>
-      <c r="AM86" s="5" t="n"/>
+      <c r="AG86" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-bn-pegram.md; ED-43 candidate (tablet casualty scope rule)</t>
+        </is>
+      </c>
+      <c r="AH86" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Pegram / report by Capt. Brunson; Crenshaw/Marye/Brander/Zimmerman/McGraw; 20 guns (tablet); ordnance officer mw Jul 1</t>
+        </is>
+      </c>
+      <c r="AI86" s="5" t="inlineStr">
+        <is>
+          <t>480 (hop, ED-38)</t>
+        </is>
+      </c>
+      <c r="AJ86" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 eminence ~1 mi west (Marye's section fired the arc's opening 8-10 rounds); [C] Jul 2-3 right of Fairfield pike, ~1,400 yd from the Union guns; j3-03 labels BRANDER(3900,5900) ZIMMERMAN(3820,5720) MARYE(3720,5620)</t>
+        </is>
+      </c>
+      <c r="AK86" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 approach; [D] one-mile-forward repost Jul 1-&gt;2; static after; retreat losses recorded</t>
+        </is>
+      </c>
+      <c r="AL86" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 line forced Union guns back 'three distinct times'; [C] Jul 2 opportunistic enfilade; [A window] Jul 3 cannonade; ROUNDS: 3,800 three days (report verbatim; tablet concurs)</t>
+        </is>
+      </c>
+      <c r="AM86" s="5" t="inlineStr">
+        <is>
+          <t>PER-DAY PRIMARY (only one in set): Jul 1 2k/8w/6h; Jul 2 2k/7w/25h; Jul 3 10k/37w/38h; tablet's 47 = Jul 3 row misread as total (conflict carried)</t>
+        </is>
+      </c>
       <c r="AN86" s="5" t="n"/>
-      <c r="AO86" s="5" t="n"/>
+      <c r="AO86" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -18072,7 +18432,7 @@
       <c r="AF164" s="5" t="n"/>
       <c r="AG164" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ar-1v-mcgilvery.md; his July 3 opening clock (OR pp.882-883) still unverified; ED-35 candidate: cast the line as a command unit</t>
+          <t>Dossier: reconstruction/dossiers/us-ar-1v-mcgilvery.md; ED-35 ADOPTED (cast the line as a command unit); ED-37 ADOPTED as recorded conflict (resolution open)</t>
         </is>
       </c>
       <c r="AH164" s="5" t="inlineStr">
@@ -18087,7 +18447,7 @@
       </c>
       <c r="AJ164" s="5" t="inlineStr">
         <is>
-          <t>[C ~15:30 Jul 2] Wheatfield Rd line; [C 17:45] retire 250 yd by stages; Trostle stand; 400-yd-rear line; [E Jul 3] low-ground line w/ earthwork, roster VERBATIM left-&gt;right incl. 'a New Jersey battery' + Rank's section (OR-vs-OOB conflict -&gt; ED-37); ref point Phillips (4212,4080)</t>
+          <t>[C ~15:30 Jul 2] Wheatfield Rd line; [C 17:45] retire 250 yd by stages; Trostle stand; 400-yd-rear line; [E Jul 3] low-ground line w/ earthwork, roster VERBATIM left-&gt;right incl. 'a New Jersey battery' + Rank's section (OR-vs-OOB conflict, ED-37 adopted-as-recorded); ref point Phillips (4212,4080)</t>
         </is>
       </c>
       <c r="AK164" s="5" t="inlineStr">
@@ -18537,20 +18897,56 @@
           <t>reg-us-i-arty</t>
         </is>
       </c>
-      <c r="AB169" s="5" t="n"/>
+      <c r="AB169" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (components partially in-build)</t>
+        </is>
+      </c>
       <c r="AC169" s="5" t="n"/>
       <c r="AD169" s="5" t="n"/>
       <c r="AE169" s="5" t="n"/>
       <c r="AF169" s="5" t="n"/>
-      <c r="AG169" s="5" t="n"/>
-      <c r="AH169" s="5" t="n"/>
-      <c r="AI169" s="5" t="n"/>
-      <c r="AJ169" s="5" t="n"/>
-      <c r="AK169" s="5" t="n"/>
-      <c r="AL169" s="5" t="n"/>
-      <c r="AM169" s="5" t="n"/>
+      <c r="AG169" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-arty-wainwright.md; p. 356 fetch gap recorded</t>
+        </is>
+      </c>
+      <c r="AH169" s="5" t="inlineStr">
+        <is>
+          <t>Col. Wainwright; Hall/Stevens/Reynolds-Wilber/Cooper/Stewart batteries; Davison w Jul 1 -&gt; Sgt. Mitchell commended</t>
+        </is>
+      </c>
+      <c r="AI169" s="5" t="inlineStr">
+        <is>
+          <t>no brigade figure (negative); component strengths on battery rows</t>
+        </is>
+      </c>
+      <c r="AJ169" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 Seminary Ridge; [C] E Cemetery Hill layout VERBATIM (B/4US across the road, I/1NY, Cooper, Reynolds = 13 three-inch guns; 5th ME 50 yd forward on the knoll) - the East-Hill left-to-right frame</t>
+        </is>
+      </c>
+      <c r="AK169" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 fighting withdrawal (peremptory order); [C] Jul 2 Cooper-out/Ricketts-in rotation; [A 15:00] Cooper detached to left centre Jul 3</t>
+        </is>
+      </c>
+      <c r="AL169" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 fight (83 men + 80 horses day-1 loss); [C] Jul 2 wheat-field battery silenced in ~90 min (28 dead horses = Latimer's ground); dusk assault 'almost entirely repelled by the artillery'; Jul 3 occasional + general; rounds via components (Cooper 1,050; Breck 1,290 itemized; Ricketts 1,200; Hill WV 1,120)</t>
+        </is>
+      </c>
+      <c r="AM169" s="5" t="inlineStr">
+        <is>
+          <t>Jul 1 primary 83+80 horses; Jul 2-3 on component returns (no roll-up fetched)</t>
+        </is>
+      </c>
       <c r="AN169" s="5" t="n"/>
-      <c r="AO169" s="5" t="n"/>
+      <c r="AO169" s="5" t="inlineStr">
+        <is>
+          <t>T4 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -18636,7 +19032,7 @@
       <c r="AF170" s="5" t="n"/>
       <c r="AG170" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-arty-hazard.md; ED-34 candidate (activity classes)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-arty-hazard.md; ED-34 ADOPTED (fought-to-exhaustion class exemplar)</t>
         </is>
       </c>
       <c r="AH170" s="5" t="inlineStr">
@@ -19024,7 +19420,7 @@
       <c r="AF174" s="5" t="n"/>
       <c r="AG174" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-arty-osborn.md; HEADLINE: contemporary motive ('no satisfactory results') vs postwar ruse - ED-33's sharpest evidence; ruse verbatim unreachable (verified absence)</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-arty-osborn.md; HEADLINE: contemporary motive ('no satisfactory results') vs postwar ruse - ED-33 adopted on this evidence; ruse verbatim unreachable (verified absence)</t>
         </is>
       </c>
       <c r="AH174" s="5" t="inlineStr">
@@ -22045,20 +22441,56 @@
           <t>reg-us-ar-hq</t>
         </is>
       </c>
-      <c r="AB206" s="5" t="n"/>
+      <c r="AB206" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (park track)</t>
+        </is>
+      </c>
       <c r="AC206" s="5" t="n"/>
       <c r="AD206" s="5" t="n"/>
       <c r="AE206" s="5" t="n"/>
       <c r="AF206" s="5" t="n"/>
-      <c r="AG206" s="5" t="n"/>
-      <c r="AH206" s="5" t="n"/>
-      <c r="AI206" s="5" t="n"/>
-      <c r="AJ206" s="5" t="n"/>
-      <c r="AK206" s="5" t="n"/>
-      <c r="AL206" s="5" t="n"/>
-      <c r="AM206" s="5" t="n"/>
+      <c r="AG206" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-hq-tyler-park.md; ED-42 candidate (issues-vs-expenditures two-ledger rule)</t>
+        </is>
+      </c>
+      <c r="AH206" s="5" t="inlineStr">
+        <is>
+          <t>Tyler -&gt; Robertson after Jul 3 incapacitation (register; report silent - carried); 5 brigades + ammunition train; Gillett ordnance officer</t>
+        </is>
+      </c>
+      <c r="AI206" s="5" t="inlineStr">
+        <is>
+          <t>2,375 / 114 guns nominal (hop) minus B+M 1st CT Heavy (to Westminster, verbatim)</t>
+        </is>
+      </c>
+      <c r="AJ206" s="5" t="inlineStr">
+        <is>
+          <t>[C] June 29-Jul 1 march (Frederick-&gt;Taneytown; 22:30 Jul 1 report to Gibbon); [C] park ~1.5 mi from town; [C] 70 wagons sent rear morning Jul 3</t>
+        </is>
+      </c>
+      <c r="AK206" s="5" t="inlineStr">
+        <is>
+          <t>[C] march legs; [C] Jul 2 six batteries/34 guns to Sickles (moves by detachment); [A window] crisis battery legs originate here</t>
+        </is>
+      </c>
+      <c r="AL206" s="5" t="inlineStr">
+        <is>
+          <t>AMMUNITION LEDGER PRIMARY: 19,189 rounds ISSUED + 4,694 left (Gillett annex) - the supply-side physics of Hunt's economy order; wagon-doctrine caution verbatim</t>
+        </is>
+      </c>
+      <c r="AM206" s="5" t="inlineStr">
+        <is>
+          <t>distributed to component returns (Turnbull's 1+8k/14w/45 horses worst); consolidated tables pp. 874-877 unfetched (open)</t>
+        </is>
+      </c>
       <c r="AN206" s="5" t="n"/>
-      <c r="AO206" s="5" t="n"/>
+      <c r="AO206" s="5" t="inlineStr">
+        <is>
+          <t>T3 (park/command grain)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -22552,7 +22984,7 @@
       <c r="AF210" s="5" t="n"/>
       <c r="AG210" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-brown.md; ED-33 candidate on what 'the 18 guns have gone' observed</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-brown.md; ED-33 ADOPTED: his ~14:40 withdrawal = the contributing event behind Alexander's '18 guns' reading (Osborn's cease primary)</t>
         </is>
       </c>
       <c r="AH210" s="5" t="inlineStr">
@@ -22701,20 +23133,56 @@
           <t>reg-us-i-b4</t>
         </is>
       </c>
-      <c r="AB211" s="5" t="n"/>
+      <c r="AB211" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC211" s="5" t="n"/>
       <c r="AD211" s="5" t="n"/>
       <c r="AE211" s="5" t="n"/>
       <c r="AF211" s="5" t="n"/>
-      <c r="AG211" s="5" t="n"/>
-      <c r="AH211" s="5" t="n"/>
-      <c r="AI211" s="5" t="n"/>
-      <c r="AJ211" s="5" t="n"/>
-      <c r="AK211" s="5" t="n"/>
-      <c r="AL211" s="5" t="n"/>
-      <c r="AM211" s="5" t="n"/>
+      <c r="AG211" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-cooper.md; best tier-B rounds basis in the set</t>
+        </is>
+      </c>
+      <c r="AH211" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Cooper; B/1st PA; I Corps bde (Wainwright); 4x 3-in rifles</t>
+        </is>
+      </c>
+      <c r="AI211" s="5" t="inlineStr">
+        <is>
+          <t>114 (monument verbatim; build concurs)</t>
+        </is>
+      </c>
+      <c r="AJ211" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 noon left of 3rd Div then Seminary (Reynolds Ave mon (3172,7044)); [C] E Cemetery Hill Jul 1 dusk - Jul 3 (Wainwright layout verbatim; main mon (5050,5776)); [A tablet 15:00] Hancock Ave tablet (4473,4096) = ridge crest at I/II Corps boundary - RESOLVES pass-1 'joins McGilvery' slot (sheet-vs-tablet conflict carried)</t>
+        </is>
+      </c>
+      <c r="AK211" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 legs; [C ~19:00 Jul 2] out to refit (Ricketts in); [A vs CA-J3A-5; B: 8-12 min] the 15:00 during-cannonade transfer</t>
+        </is>
+      </c>
+      <c r="AL211" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 25-shot opening + Seminary fight; [C] Jul 2 2.5-h silencing duel; [C] Jul 3 case-&gt;canister rout; ROUNDS PER DAY: ~400/500/150 = 1,050 (report + monument concur) [B: Jul 3 ~20-25 min fire]</t>
+        </is>
+      </c>
+      <c r="AM211" s="5" t="inlineStr">
+        <is>
+          <t>12 total (3k/9w); PER-DAY PINS: Jul 2 2k/6w, Jul 3 1w (report) - monument's July-3 heading wrong by the battery's own report</t>
+        </is>
+      </c>
       <c r="AN211" s="5" t="n"/>
-      <c r="AO211" s="5" t="n"/>
+      <c r="AO211" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -22825,20 +23293,56 @@
           <t>reg-us-vi-b2</t>
         </is>
       </c>
-      <c r="AB212" s="5" t="n"/>
+      <c r="AB212" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (T5 window in Angle cast)</t>
+        </is>
+      </c>
       <c r="AC212" s="5" t="n"/>
       <c r="AD212" s="5" t="n"/>
       <c r="AE212" s="5" t="n"/>
       <c r="AF212" s="5" t="n"/>
-      <c r="AG212" s="5" t="n"/>
-      <c r="AH212" s="5" t="n"/>
-      <c r="AI212" s="5" t="n"/>
-      <c r="AJ212" s="5" t="n"/>
-      <c r="AK212" s="5" t="n"/>
-      <c r="AL212" s="5" t="n"/>
-      <c r="AM212" s="5" t="n"/>
+      <c r="AG212" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-cowan.md; ED-40 candidate (crisis slot naming)</t>
+        </is>
+      </c>
+      <c r="AH212" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Cowan unwounded; 6x 3-in rifles; VI Corps battery detached to II Corps front; Hunt at the guns at climax</t>
+        </is>
+      </c>
+      <c r="AI212" s="5" t="inlineStr">
+        <is>
+          <t>113 (stone-sentinels, single-source; build concurs)</t>
+        </is>
+      </c>
+      <c r="AJ212" s="5" t="inlineStr">
+        <is>
+          <t>[C] VI Corps march arrival 22:00 Jul 2; [C ~10:00] to Newton, park &lt;100 yd rear; [A vs CA-J3A-7..9] the Brown slot: mon-cowan (4428,4788), 17m from build hold; j3-03 'COWAN' between CUSHING and BROWN</t>
+        </is>
+      </c>
+      <c r="AK212" s="5" t="inlineStr">
+        <is>
+          <t>[C] march legs; [A] slot-fill move at a gallop ~150m [B: ~1 min]</t>
+        </is>
+      </c>
+      <c r="AL212" s="5" t="inlineStr">
+        <is>
+          <t>[C +67] opening 'about noon' (early pole, rule 4); [A] canister 200 yd -&gt; &lt;20 yd ('DOUBLE CANISTER AT TEN YARDS' monument); [D] exploded 4 limbers of one CSA battery; rounds attested-absent</t>
+        </is>
+      </c>
+      <c r="AM212" s="5" t="inlineStr">
+        <is>
+          <t>5k/6w + 14 horses (report; monument + SS page variants carried); single-episode Jul 3 profile</t>
+        </is>
+      </c>
       <c r="AN212" s="5" t="n"/>
-      <c r="AO212" s="5" t="n"/>
+      <c r="AO212" s="5" t="inlineStr">
+        <is>
+          <t>T4 (full arc; T5 window in-build)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -23569,20 +24073,56 @@
           <t>reg-us-ar-4v-5</t>
         </is>
       </c>
-      <c r="AB218" s="5" t="n"/>
+      <c r="AB218" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC218" s="5" t="n"/>
       <c r="AD218" s="5" t="n"/>
       <c r="AE218" s="5" t="n"/>
       <c r="AF218" s="5" t="n"/>
-      <c r="AG218" s="5" t="n"/>
-      <c r="AH218" s="5" t="n"/>
-      <c r="AI218" s="5" t="n"/>
-      <c r="AJ218" s="5" t="n"/>
-      <c r="AK218" s="5" t="n"/>
-      <c r="AL218" s="5" t="n"/>
-      <c r="AM218" s="5" t="n"/>
+      <c r="AG218" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-fitzhugh.md; ED-41 candidate (crisis-reinforcement class)</t>
+        </is>
+      </c>
+      <c r="AH218" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Fitzhugh (also cmdg 4th Vol Bde); K/1st NY + 11th NY attached; 6x 3-in rifles</t>
+        </is>
+      </c>
+      <c r="AI218" s="5" t="inlineStr">
+        <is>
+          <t>149 (stone-sentinels; build concurs)</t>
+        </is>
+      </c>
+      <c r="AJ218" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2-3 Baltimore pike near Slocum; [crisis] 'near the stone fence in front of General Webb's division', enemy at 75 yd; monument on Cemetery Hill = pre-crisis semantics</t>
+        </is>
+      </c>
+      <c r="AK218" s="5" t="inlineStr">
+        <is>
+          <t>13:00-vs-15:00 move-clock CONFLICT (his 1 p.m. vs Parsons's 3 p.m. + SS at-the-gallop); 89-round expenditure is the physical tiebreaker toward 15:00</t>
+        </is>
+      </c>
+      <c r="AL218" s="5" t="inlineStr">
+        <is>
+          <t>[A window] first attack collapsed in 30-45 min of his fire; second (Wilcox/Lang) broken by enfilade; ROUNDS ITEMIZED: 57 percussion + 15 shrapnel + 17 time = 89 [B: ~8-10 min full-battery fire]</t>
+        </is>
+      </c>
+      <c r="AM218" s="5" t="inlineStr">
+        <is>
+          <t>K+11NY: 7w + 5 horses; brigade 36 (2k/34w tablet); single-episode</t>
+        </is>
+      </c>
       <c r="AN218" s="5" t="n"/>
-      <c r="AO218" s="5" t="n"/>
+      <c r="AO218" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -24685,20 +25225,56 @@
           <t>reg-us-ar-4v-3</t>
         </is>
       </c>
-      <c r="AB227" s="5" t="n"/>
+      <c r="AB227" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC227" s="5" t="n"/>
       <c r="AD227" s="5" t="n"/>
       <c r="AE227" s="5" t="n"/>
       <c r="AF227" s="5" t="n"/>
-      <c r="AG227" s="5" t="n"/>
-      <c r="AH227" s="5" t="n"/>
-      <c r="AI227" s="5" t="n"/>
-      <c r="AJ227" s="5" t="n"/>
-      <c r="AK227" s="5" t="n"/>
-      <c r="AL227" s="5" t="n"/>
-      <c r="AM227" s="5" t="n"/>
+      <c r="AG227" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-parsons.md; ED-37 file: Parsons ELIMINATED as McGilvery's 'New Jersey battery' (was at the pike all morning); Clark's B/1st NJ the surviving candidate</t>
+        </is>
+      </c>
+      <c r="AH227" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Parsons; A/1st NJ; 4th Vol Bde; 6 guns (armament single-source, flagged)</t>
+        </is>
+      </c>
+      <c r="AI227" s="5" t="inlineStr">
+        <is>
+          <t>116 (build compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ227" s="5" t="inlineStr">
+        <is>
+          <t>[C] Baltimore pike Jul 2-3; [C +10] 'about one-fourth of a mile south of Gettysburg Cemetery and near the Second Division' - vs Fitzhugh's in-front-of-Webb (tension carried); pair order: Parsons left, Fitzhugh right</t>
+        </is>
+      </c>
+      <c r="AK227" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:00] Hunt's order, pike-&gt;ridge at speed [B: 5-8 min]</t>
+        </is>
+      </c>
+      <c r="AL227" s="5" t="inlineStr">
+        <is>
+          <t>[A] case into the advancing infantry (~40 rds per Fitzhugh); [D] then ~120 shot + ~80 shell counter-battery until Hunt's cease = ~240 rounds total [B: 20-30 min]</t>
+        </is>
+      </c>
+      <c r="AM227" s="5" t="inlineStr">
+        <is>
+          <t>2k/7w + 5 horses; single-episode</t>
+        </is>
+      </c>
       <c r="AN227" s="5" t="n"/>
-      <c r="AO227" s="5" t="n"/>
+      <c r="AO227" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -25181,20 +25757,56 @@
           <t>reg-us-v-b4</t>
         </is>
       </c>
-      <c r="AB231" s="5" t="n"/>
+      <c r="AB231" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (Jul 3)</t>
+        </is>
+      </c>
       <c r="AC231" s="5" t="n"/>
       <c r="AD231" s="5" t="n"/>
       <c r="AE231" s="5" t="n"/>
       <c r="AF231" s="5" t="n"/>
-      <c r="AG231" s="5" t="n"/>
-      <c r="AH231" s="5" t="n"/>
-      <c r="AI231" s="5" t="n"/>
-      <c r="AJ231" s="5" t="n"/>
-      <c r="AK231" s="5" t="n"/>
-      <c r="AL231" s="5" t="n"/>
-      <c r="AM231" s="5" t="n"/>
+      <c r="AG231" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-rittenhouse.md; rittenhouse-mollus-1887 = the T-ceiling item</t>
+        </is>
+      </c>
+      <c r="AH231" s="5" t="inlineStr">
+        <is>
+          <t>Hazlett k Jul 2 on the summit -&gt; Rittenhouse; D/5th US; 6x 10-pdr Parrotts; V Corps bde (Martin)</t>
+        </is>
+      </c>
+      <c r="AI231" s="5" t="inlineStr">
+        <is>
+          <t>73 = 2 off + 71 men (tablet)</t>
+        </is>
+      </c>
+      <c r="AJ231" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet 17:45 Jul 2] LRT summit, hand-hauled; ~(4430,2600) +-50m (j3-03 HAZLETT'S bar; NO register marker - gap flagged); attested-static Jul 3</t>
+        </is>
+      </c>
+      <c r="AK231" s="5" t="inlineStr">
+        <is>
+          <t>[C 16:30-17:45 Jul 2] march + summit haul [B: haul is the constraint]; none after</t>
+        </is>
+      </c>
+      <c r="AL231" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 evening fire into the Devil's Den flank; [E + cross-cited] Jul 3 enfilade on the assault (Hunt's 'McGilvery and Rittenhouse...drift' statement); OWN ACCOUNT ACCESS-FAILED (gdg.org TLS) - EC5 deliberately thin; rounds unfetched</t>
+        </is>
+      </c>
+      <c r="AM231" s="5" t="inlineStr">
+        <is>
+          <t>14 (1 off + 8 men k, 5 w, tablet; ~19% of 73); Jul 2 dominates [D]; brigade frame 44 total (Martin)</t>
+        </is>
+      </c>
       <c r="AN231" s="5" t="n"/>
-      <c r="AO231" s="5" t="n"/>
+      <c r="AO231" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -26333,20 +26945,56 @@
           <t>reg-us-ar-1r-4</t>
         </is>
       </c>
-      <c r="AB240" s="5" t="n"/>
+      <c r="AB240" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC240" s="5" t="n"/>
       <c r="AD240" s="5" t="n"/>
       <c r="AE240" s="5" t="n"/>
       <c r="AF240" s="5" t="n"/>
-      <c r="AG240" s="5" t="n"/>
-      <c r="AH240" s="5" t="n"/>
-      <c r="AI240" s="5" t="n"/>
-      <c r="AJ240" s="5" t="n"/>
-      <c r="AK240" s="5" t="n"/>
-      <c r="AL240" s="5" t="n"/>
-      <c r="AM240" s="5" t="n"/>
+      <c r="AG240" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-weir.md; Tyler's 'no report received' vs the printed report - OR artifact recorded</t>
+        </is>
+      </c>
+      <c r="AH240" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Weir (w Jul 3 per register; report silent - carried); 6 Napoleons; 1st Regular Bde (Ransom w), Artillery Reserve</t>
+        </is>
+      </c>
+      <c r="AI240" s="5" t="inlineStr">
+        <is>
+          <t>123 = 2 off + 121 men (tablet verbatim)</t>
+        </is>
+      </c>
+      <c r="AJ240" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 park then 16:00 forward position ~500 yd (Hancock order); 3 guns lost/recaptured by 13th VT (tablet verbatim); [D] Jul 3 fell back, then 'conducted to General Webb's position...under a heavy musketry fire' (crisis window)</t>
+        </is>
+      </c>
+      <c r="AK240" s="5" t="inlineStr">
+        <is>
+          <t>[C 16:00 Jul 2] park-&gt;front [B: 15-20 min]; [D] Jul 2 overrun scramble; [D] Jul 3 crisis move to Webb</t>
+        </is>
+      </c>
+      <c r="AL240" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 shot/case, canister out; [D] Jul 3 canister at short range; ROUNDS PRIMARY: 50 shot + 160 case + 70 canister = 280 (or-27-1-weir) [B: ~23-31 min cumulative battery fire]</t>
+        </is>
+      </c>
+      <c r="AM240" s="5" t="inlineStr">
+        <is>
+          <t>16 = 2k + 2 off/12 men w (tablet); Jul 2 dominates [D]; Baldwin w pin</t>
+        </is>
+      </c>
       <c r="AN240" s="5" t="n"/>
-      <c r="AO240" s="5" t="n"/>
+      <c r="AO240" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -26457,20 +27105,56 @@
           <t>reg-us-xi-b2</t>
         </is>
       </c>
-      <c r="AB241" s="5" t="n"/>
+      <c r="AB241" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC241" s="5" t="n"/>
       <c r="AD241" s="5" t="n"/>
       <c r="AE241" s="5" t="n"/>
       <c r="AF241" s="5" t="n"/>
-      <c r="AG241" s="5" t="n"/>
-      <c r="AH241" s="5" t="n"/>
-      <c r="AI241" s="5" t="n"/>
-      <c r="AJ241" s="5" t="n"/>
-      <c r="AK241" s="5" t="n"/>
-      <c r="AL241" s="5" t="n"/>
-      <c r="AM241" s="5" t="n"/>
+      <c r="AG241" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-wheeler.md; three-halt rhythm = pass-3 approach-leg pacing input</t>
+        </is>
+      </c>
+      <c r="AH241" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Wheeler; 13th NY Indep; XI Corps bde (Osborn); 4x 3-in rifles</t>
+        </is>
+      </c>
+      <c r="AI241" s="5" t="inlineStr">
+        <is>
+          <t>118 (stone-sentinels; build concurs)</t>
+        </is>
+      </c>
+      <c r="AJ241" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 Dilger's right then wheat field; [E] Jul 2-3 Cemetery Hill (Osborn group); [C stated 16:00, profile -35] crisis position by Hancock, enemy column 400 yd off</t>
+        </is>
+      </c>
+      <c r="AK241" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 double-quick legs + retreat; [C] crisis move hill-&gt;II Corps front [B: 3-5 min; build path 668m matches]</t>
+        </is>
+      </c>
+      <c r="AL241" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 counter-battery; [E] hill group fire; [A] crisis canister enfilade - column 'brought to a halt three times'; ROUNDS: 850 whole battle [B: ~212/gun, needs per-day split - none stated]</t>
+        </is>
+      </c>
+      <c r="AM241" s="5" t="inlineStr">
+        <is>
+          <t>10w/3m + 12 horses (report; monument 8w variant); Jul 1 vs Jul 3 split bracketed only</t>
+        </is>
+      </c>
       <c r="AN241" s="5" t="n"/>
-      <c r="AO241" s="5" t="n"/>
+      <c r="AO241" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -29173,20 +29857,56 @@
           <t>reg-us-ii-2-3</t>
         </is>
       </c>
-      <c r="AB265" s="5" t="n"/>
+      <c r="AB265" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (crisis rush authored in Angle cast)</t>
+        </is>
+      </c>
       <c r="AC265" s="5" t="n"/>
       <c r="AD265" s="5" t="n"/>
       <c r="AE265" s="5" t="n"/>
       <c r="AF265" s="5" t="n"/>
-      <c r="AG265" s="5" t="n"/>
-      <c r="AH265" s="5" t="n"/>
-      <c r="AI265" s="5" t="n"/>
-      <c r="AJ265" s="5" t="n"/>
-      <c r="AK265" s="5" t="n"/>
-      <c r="AL265" s="5" t="n"/>
-      <c r="AM265" s="5" t="n"/>
+      <c r="AG265" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate</t>
+        </is>
+      </c>
+      <c r="AH265" s="5" t="inlineStr">
+        <is>
+          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
+        </is>
+      </c>
+      <c r="AI265" s="5" t="inlineStr">
+        <is>
+          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
+        </is>
+      </c>
+      <c r="AJ265" s="5" t="inlineStr">
+        <is>
+          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
+        </is>
+      </c>
+      <c r="AK265" s="5" t="inlineStr">
+        <is>
+          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
+        </is>
+      </c>
+      <c r="AL265" s="5" t="inlineStr">
+        <is>
+          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
+        </is>
+      </c>
+      <c r="AM265" s="5" t="inlineStr">
+        <is>
+          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
+        </is>
+      </c>
       <c r="AN265" s="5" t="n"/>
-      <c r="AO265" s="5" t="n"/>
+      <c r="AO265" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -29308,7 +30028,7 @@
       <c r="AF266" s="5" t="n"/>
       <c r="AG266" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; wheel clock verified-negative (no witness clock exists)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
         </is>
       </c>
       <c r="AH266" s="5" t="inlineStr">
@@ -29318,7 +30038,7 @@
       </c>
       <c r="AI266" s="5" t="inlineStr">
         <is>
-          <t>1,950 brigade (stone-sentinels) vs 1,788 sum of engaged rgts (480+647+661) - ~160-man gap, both carried (oob-strengths #3)</t>
+          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
         </is>
       </c>
       <c r="AJ266" s="5" t="inlineStr">
@@ -32677,20 +33397,56 @@
           <t>reg-us-ii-2-1</t>
         </is>
       </c>
-      <c r="AB293" s="5" t="n"/>
+      <c r="AB293" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (crisis incline-right)</t>
+        </is>
+      </c>
       <c r="AC293" s="5" t="n"/>
       <c r="AD293" s="5" t="n"/>
       <c r="AE293" s="5" t="n"/>
       <c r="AF293" s="5" t="n"/>
-      <c r="AG293" s="5" t="n"/>
-      <c r="AH293" s="5" t="n"/>
-      <c r="AI293" s="5" t="n"/>
-      <c r="AJ293" s="5" t="n"/>
-      <c r="AK293" s="5" t="n"/>
-      <c r="AL293" s="5" t="n"/>
-      <c r="AM293" s="5" t="n"/>
+      <c r="AG293" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded</t>
+        </is>
+      </c>
+      <c r="AH293" s="5" t="inlineStr">
+        <is>
+          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
+        </is>
+      </c>
+      <c r="AI293" s="5" t="inlineStr">
+        <is>
+          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
+        </is>
+      </c>
+      <c r="AJ293" s="5" t="inlineStr">
+        <is>
+          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
+        </is>
+      </c>
+      <c r="AK293" s="5" t="inlineStr">
+        <is>
+          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]</t>
+        </is>
+      </c>
+      <c r="AL293" s="5" t="inlineStr">
+        <is>
+          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
+        </is>
+      </c>
+      <c r="AM293" s="5" t="inlineStr">
+        <is>
+          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
+        </is>
+      </c>
       <c r="AN293" s="5" t="n"/>
-      <c r="AO293" s="5" t="n"/>
+      <c r="AO293" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -34537,20 +35293,56 @@
           <t>reg-us-ii-3-3</t>
         </is>
       </c>
-      <c r="AB308" s="5" t="n"/>
+      <c r="AB308" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (one in-window leg)</t>
+        </is>
+      </c>
       <c r="AC308" s="5" t="n"/>
       <c r="AD308" s="5" t="n"/>
       <c r="AE308" s="5" t="n"/>
       <c r="AF308" s="5" t="n"/>
-      <c r="AG308" s="5" t="n"/>
-      <c r="AH308" s="5" t="n"/>
-      <c r="AI308" s="5" t="n"/>
-      <c r="AJ308" s="5" t="n"/>
-      <c r="AK308" s="5" t="n"/>
-      <c r="AL308" s="5" t="n"/>
-      <c r="AM308" s="5" t="n"/>
+      <c r="AG308" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
+        </is>
+      </c>
+      <c r="AH308" s="5" t="inlineStr">
+        <is>
+          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
+        </is>
+      </c>
+      <c r="AI308" s="5" t="inlineStr">
+        <is>
+          <t>1,510 (build compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ308" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
+        </is>
+      </c>
+      <c r="AK308" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
+        </is>
+      </c>
+      <c r="AL308" s="5" t="inlineStr">
+        <is>
+          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
+        </is>
+      </c>
+      <c r="AM308" s="5" t="inlineStr">
+        <is>
+          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
+        </is>
+      </c>
       <c r="AN308" s="5" t="n"/>
-      <c r="AO308" s="5" t="n"/>
+      <c r="AO308" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -34785,20 +35577,56 @@
           <t>reg-us-ii-3-2</t>
         </is>
       </c>
-      <c r="AB310" s="5" t="n"/>
+      <c r="AB310" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (July 2-4 wall line)</t>
+        </is>
+      </c>
       <c r="AC310" s="5" t="n"/>
       <c r="AD310" s="5" t="n"/>
       <c r="AE310" s="5" t="n"/>
       <c r="AF310" s="5" t="n"/>
-      <c r="AG310" s="5" t="n"/>
-      <c r="AH310" s="5" t="n"/>
-      <c r="AI310" s="5" t="n"/>
-      <c r="AJ310" s="5" t="n"/>
-      <c r="AK310" s="5" t="n"/>
-      <c r="AL310" s="5" t="n"/>
-      <c r="AM310" s="5" t="n"/>
+      <c r="AG310" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
+        </is>
+      </c>
+      <c r="AH310" s="5" t="inlineStr">
+        <is>
+          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
+        </is>
+      </c>
+      <c r="AI310" s="5" t="inlineStr">
+        <is>
+          <t>1,190 (build compilation, hop flagged; no primary)</t>
+        </is>
+      </c>
+      <c r="AJ310" s="5" t="inlineStr">
+        <is>
+          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
+        </is>
+      </c>
+      <c r="AK310" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
+        </is>
+      </c>
+      <c r="AL310" s="5" t="inlineStr">
+        <is>
+          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
+        </is>
+      </c>
+      <c r="AM310" s="5" t="inlineStr">
+        <is>
+          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
+        </is>
+      </c>
       <c r="AN310" s="5" t="n"/>
-      <c r="AO310" s="5" t="n"/>
+      <c r="AO310" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -13669,20 +13669,56 @@
           <t>reg-csa-1c-pic-3</t>
         </is>
       </c>
-      <c r="AB125" s="5" t="n"/>
+      <c r="AB125" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (T5 window)</t>
+        </is>
+      </c>
       <c r="AC125" s="5" t="n"/>
       <c r="AD125" s="5" t="n"/>
       <c r="AE125" s="5" t="n"/>
       <c r="AF125" s="5" t="n"/>
-      <c r="AG125" s="5" t="n"/>
-      <c r="AH125" s="5" t="n"/>
-      <c r="AI125" s="5" t="n"/>
-      <c r="AJ125" s="5" t="n"/>
-      <c r="AK125" s="5" t="n"/>
-      <c r="AL125" s="5" t="n"/>
-      <c r="AM125" s="5" t="n"/>
+      <c r="AG125" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-pic-3-armistead.md; NO brigade OR report (verified negative)</t>
+        </is>
+      </c>
+      <c r="AH125" s="5" t="inlineStr">
+        <is>
+          <t>Armistead mw&amp;c under captured guns (T5 t~8720; mon-armistead 16m agreement) -&gt; Col. Aylett (w); Hodges k, Edmonds k at wall</t>
+        </is>
+      </c>
+      <c r="AI125" s="5" t="inlineStr">
+        <is>
+          <t>1,650 (ED-9, no primary); crossing party ~150 (T5)</t>
+        </is>
+      </c>
+      <c r="AJ125" s="5" t="inlineStr">
+        <is>
+          <t>[E +-120m] j3-02 morning label ~(3150,4780) behind Spangler's Woods (2nd line west of crest); fall point (4412,4865)+-25 (T5)</t>
+        </is>
+      </c>
+      <c r="AK125" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-6] second-line step-off; closed onto first line BEFORE wall (peyton 75-paces relation); ED-8 recross 8700-9000</t>
+        </is>
+      </c>
+      <c r="AL125" s="5" t="inlineStr">
+        <is>
+          <t>[A window] bombardment share UNQUANTIFIED (open); activity concentrates at wall - crossing, Cushing's guns, ~10-min penetration (T5)</t>
+        </is>
+      </c>
+      <c r="AM125" s="5" t="inlineStr">
+        <is>
+          <t>1,191 = 88/460/643 (anv-return = aylett-1863 EXACT match; regt k+w 71/108/170/104/121); 643 missing at/east of wall; headnote missing-scope at full force</t>
+        </is>
+      </c>
       <c r="AN125" s="5" t="n"/>
-      <c r="AO125" s="5" t="n"/>
+      <c r="AO125" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (T5 in Angle window)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -13793,20 +13829,56 @@
           <t>reg-csa-3c-het-2</t>
         </is>
       </c>
-      <c r="AB126" s="5" t="n"/>
+      <c r="AB126" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (wings flagged reconstruction)</t>
+        </is>
+      </c>
       <c r="AC126" s="5" t="n"/>
       <c r="AD126" s="5" t="n"/>
       <c r="AE126" s="5" t="n"/>
       <c r="AF126" s="5" t="n"/>
-      <c r="AG126" s="5" t="n"/>
-      <c r="AH126" s="5" t="n"/>
-      <c r="AI126" s="5" t="n"/>
-      <c r="AJ126" s="5" t="n"/>
-      <c r="AK126" s="5" t="n"/>
-      <c r="AL126" s="5" t="n"/>
-      <c r="AM126" s="5" t="n"/>
+      <c r="AG126" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-2-brockenbrough.md; NO OR report (verified negative)</t>
+        </is>
+      </c>
+      <c r="AH126" s="5" t="inlineStr">
+        <is>
+          <t>Col. Brockenbrough (unwounded; replaced after battle); NO officer pins located (open); two-wing split (Mayo) has NO primary in corpus - build-inherited, flagged</t>
+        </is>
+      </c>
+      <c r="AI126" s="5" t="inlineStr">
+        <is>
+          <t>CORRUPTED record bounded: stone-sentinels page = Davis duplicate (DO-NOT-USE stands); range 800-1,100, Mayo-hop ~880 = build basis (ED-48 candidate)</t>
+        </is>
+      </c>
+      <c r="AJ126" s="5" t="inlineStr">
+        <is>
+          <t>[D] division LEFT (davis-jr order); j3-02 label ~(3320,5980)+-120 (northernmost of column); advance axis toward Bliss/Bryan north front (+-150m)</t>
+        </is>
+      </c>
+      <c r="AK126" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-5/6] step-off w/ division; THE EARLY BREAK - documented from outside (Jones 'whole line on the left had given way'; Engelhard/Lane enfilade column)</t>
+        </is>
+      </c>
+      <c r="AL126" s="5" t="inlineStr">
+        <is>
+          <t>[A window] bombardment w/ division (no figure, open); received 8th Ohio flank + Osborn arc; no brigade-authored fire statement (negative)</t>
+        </is>
+      </c>
+      <c r="AM126" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY FLOOR (new): 148 = 25/123/no-missing (anv-return regt-grain 42/48/34/24); build's 100 decay is BELOW the documented k+w floor (ED-48 consequence); no episode split exists (open)</t>
+        </is>
+      </c>
       <c r="AN126" s="5" t="n"/>
-      <c r="AO126" s="5" t="n"/>
+      <c r="AO126" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -13917,20 +13989,56 @@
           <t>reg-csa-3c-het-4</t>
         </is>
       </c>
-      <c r="AB127" s="5" t="n"/>
+      <c r="AB127" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC127" s="5" t="n"/>
       <c r="AD127" s="5" t="n"/>
       <c r="AE127" s="5" t="n"/>
       <c r="AF127" s="5" t="n"/>
-      <c r="AG127" s="5" t="n"/>
-      <c r="AH127" s="5" t="n"/>
-      <c r="AI127" s="5" t="n"/>
-      <c r="AJ127" s="5" t="n"/>
-      <c r="AK127" s="5" t="n"/>
-      <c r="AL127" s="5" t="n"/>
-      <c r="AM127" s="5" t="n"/>
+      <c r="AG127" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-4-davis.md; division report clock +5 (CSA twin of Hall)</t>
+        </is>
+      </c>
+      <c r="AH127" s="5" t="inlineStr">
+        <is>
+          <t>Davis (unwounded, wrote brigade + division reports); Jul 1: 7 of 9 field officers hit; Jul 3: ALL field officers k/w</t>
+        </is>
+      </c>
+      <c r="AI127" s="5" t="inlineStr">
+        <is>
+          <t>2,000 'present first day' (stone-sentinels, scope caveat); 11th Miss DETACHED Jul 1 (division train guard, primary) - fresh regiment atop Jul 1 survivors on Jul 3</t>
+        </is>
+      </c>
+      <c r="AJ127" s="5" t="inlineStr">
+        <is>
+          <t>[C +5] 9am shift behind Pegram's bn; j3-02 label ~(3330,5760)+-100; mon-11ms start (3471,5621) corroborates (modern-era caution); farthest advance mon-11ms-1 Bryan barn (4448,5115)</t>
+        </is>
+      </c>
+      <c r="AK127" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-5/6] cease-fire trigger, dressed right, oblique left; fences deranging/rectified; fall-back to morning line ~16:00 [C +5]</t>
+        </is>
+      </c>
+      <c r="AL127" s="5" t="inlineStr">
+        <is>
+          <t>[A window] 2-hr bombardment 'no time to prepare means for protection'; no fire until 3/4-mi fence then grape/canister/shell; musket-range 'suffered severely'</t>
+        </is>
+      </c>
+      <c r="AM127" s="5" t="inlineStr">
+        <is>
+          <t>897 = 180/717/NO-missing (anv-return: 232/202/265/198); BOMBARDMENT PRIMARY 2k/21w (best in batch, pairs w/ Garnett's ~20); 11th Miss 202 k+w = Jul 3 only (day-split anchor)</t>
+        </is>
+      </c>
       <c r="AN127" s="5" t="n"/>
-      <c r="AO127" s="5" t="n"/>
+      <c r="AO127" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -14041,20 +14149,56 @@
           <t>reg-csa-3c-het-3</t>
         </is>
       </c>
-      <c r="AB128" s="5" t="n"/>
+      <c r="AB128" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC128" s="5" t="n"/>
       <c r="AD128" s="5" t="n"/>
       <c r="AE128" s="5" t="n"/>
       <c r="AF128" s="5" t="n"/>
-      <c r="AG128" s="5" t="n"/>
-      <c r="AH128" s="5" t="n"/>
-      <c r="AI128" s="5" t="n"/>
-      <c r="AJ128" s="5" t="n"/>
-      <c r="AK128" s="5" t="n"/>
-      <c r="AL128" s="5" t="n"/>
-      <c r="AM128" s="5" t="n"/>
+      <c r="AG128" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-3-fry.md; claim-fry-guide now executor-documented</t>
+        </is>
+      </c>
+      <c r="AH128" s="5" t="inlineStr">
+        <is>
+          <t>Archer c Jul 1 -&gt; Fry (w&amp;c Jul 3 at works) -&gt; Shepard; 7 field officers in, 2 out; order 1TN-13AL-14TN-7TN-5ALbn</t>
+        </is>
+      </c>
+      <c r="AI128" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 1,048 (shepard, =build); Jul 3 basis = 1,048 - Jul 1 losses (open); NOT engaged Jul 2 (attested negative)</t>
+        </is>
+      </c>
+      <c r="AJ128" s="5" t="inlineStr">
+        <is>
+          <t>[D] division right in front of works from night Jul 2; j3-02 label ~(3400,5100)+-100; lane w/ two stout fences at 180-200 yd from works</t>
+        </is>
+      </c>
+      <c r="AK128" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-5/6] step-off at cease-fire trigger; the CONVERGENCE executed ('Guide right', touched Pickett's left at half-way); lane crossing; fell back to start</t>
+        </is>
+      </c>
+      <c r="AL128" s="5" t="inlineStr">
+        <is>
+          <t>[D] enemy held fire until 'fine range'; at works 'as long as any other troops'; color record: 4 of 5 flags captured AT/WITHIN works (13 color-bearers down) - ED-5 substance</t>
+        </is>
+      </c>
+      <c r="AM128" s="5" t="inlineStr">
+        <is>
+          <t>677 = 16/144/517 (anv-return; =shepard's own 677 of 1,048 EXACT); 76% capture share (Jul 1 creek pocket ~75 + Jul 3 works); ED-49 exemplar</t>
+        </is>
+      </c>
       <c r="AN128" s="5" t="n"/>
-      <c r="AO128" s="5" t="n"/>
+      <c r="AO128" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -14167,7 +14311,7 @@
       </c>
       <c r="AB129" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (T5 window)</t>
         </is>
       </c>
       <c r="AC129" s="5" t="inlineStr">
@@ -14192,17 +14336,45 @@
       </c>
       <c r="AG129" s="5" t="inlineStr">
         <is>
-          <t>Format example row - overwrite freely.</t>
-        </is>
-      </c>
-      <c r="AH129" s="5" t="n"/>
-      <c r="AI129" s="5" t="n"/>
-      <c r="AJ129" s="5" t="n"/>
-      <c r="AK129" s="5" t="n"/>
-      <c r="AL129" s="5" t="n"/>
-      <c r="AM129" s="5" t="n"/>
+          <t>Dossier: reconstruction/dossiers/csa-1c-pic-1-garnett.md; Peyton page-verified this pass</t>
+        </is>
+      </c>
+      <c r="AH129" s="5" t="inlineStr">
+        <is>
+          <t>Garnett k ~25 paces from wall (peyton) -&gt; Maj. Peyton; pins: Ellis (19VA) k in bombardment, every rgt cdr k/w</t>
+        </is>
+      </c>
+      <c r="AI129" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 1,287 men + ~140 officers (peyton, previous-evening report; ED-46 candidate) vs 1,480 ED-9 build basis - conflict carried</t>
+        </is>
+      </c>
+      <c r="AJ129" s="5" t="inlineStr">
+        <is>
+          <t>[C ~09:00] reached field; [C/E ~12:00] behind Alexander's gun crest; build start (3200,4930)+-60 (j3-03 bars); 800-1,000 yd to the line (peyton)</t>
+        </is>
+      </c>
+      <c r="AK129" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-6] Pickett-in-person order, quick time; three-fence climb w/ skirmishers at last fence; recoil at 20 paces then three-line rush; dissolution-class retreat (~300 came off)</t>
+        </is>
+      </c>
+      <c r="AL129" s="5" t="inlineStr">
+        <is>
+          <t>[A window] under cannonade overs 'one hour' (duration conflict carried); LRT enfilade received (10 men/shell, peyton); loading-and-firing advance; hand-to-hand at works</t>
+        </is>
+      </c>
+      <c r="AM129" s="5" t="inlineStr">
+        <is>
+          <t>941 = 78/324/539 (anv-return regt-grain: 54/87/44/77/62 + staff; ED-49 scope); bombardment ~20 k&amp;w PRIMARY; &gt;half fallen by wall fight; missing mostly k/w (report+headnote)</t>
+        </is>
+      </c>
       <c r="AN129" s="5" t="n"/>
-      <c r="AO129" s="5" t="n"/>
+      <c r="AO129" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (T5 in Angle window)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -14313,20 +14485,56 @@
           <t>reg-csa-1c-pic-2</t>
         </is>
       </c>
-      <c r="AB130" s="5" t="n"/>
+      <c r="AB130" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (T5 window)</t>
+        </is>
+      </c>
       <c r="AC130" s="5" t="n"/>
       <c r="AD130" s="5" t="n"/>
       <c r="AE130" s="5" t="n"/>
       <c r="AF130" s="5" t="n"/>
-      <c r="AG130" s="5" t="n"/>
-      <c r="AH130" s="5" t="n"/>
-      <c r="AI130" s="5" t="n"/>
-      <c r="AJ130" s="5" t="n"/>
-      <c r="AK130" s="5" t="n"/>
-      <c r="AL130" s="5" t="n"/>
-      <c r="AM130" s="5" t="n"/>
+      <c r="AG130" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-pic-2-kemper.md; NO brigade OR report (verified negative)</t>
+        </is>
+      </c>
+      <c r="AH130" s="5" t="inlineStr">
+        <is>
+          <t>Kemper w&amp;c (rescued; T5 t~8640, Peyton brackets earlier) -&gt; Col. Mayo; Williams/Patton mw, Otey w; staff 1k/3w (return)</t>
+        </is>
+      </c>
+      <c r="AI130" s="5" t="inlineStr">
+        <is>
+          <t>1,575 (ED-9/stone-sentinels, no primary; negative - no morning report survives)</t>
+        </is>
+      </c>
+      <c r="AJ130" s="5" t="inlineStr">
+        <is>
+          <t>[E] right of Garnett behind gun line; oblique/lapping convergence (peyton); wounding point (4370,4790)+-50 (T5)</t>
+        </is>
+      </c>
+      <c r="AK130" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-6] step-off w/ division; convergence leg 50-60 yd behind-right of Garnett; flank crisis vs Stannard wheel (CA-J3A-8)</t>
+        </is>
+      </c>
+      <c r="AL130" s="5" t="inlineStr">
+        <is>
+          <t>[A window] bombardment: 'suffered severely' (Wilcox cross-brigade comparison - worse than Garnett's ~20); LRT enfilade on right; Rorty canister + Stannard front/flank fire received</t>
+        </is>
+      </c>
+      <c r="AM130" s="5" t="inlineStr">
+        <is>
+          <t>731 = 58/356/317 (anv-return regt-grain: 64/67/94/109/128; 58k vs stone-sentinels 56k conflict carried); 317 missing concentrate at flank collapse (Stannard's 243 prisoners = Union pin)</t>
+        </is>
+      </c>
       <c r="AN130" s="5" t="n"/>
-      <c r="AO130" s="5" t="n"/>
+      <c r="AO130" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (T5 in Angle window)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -14437,20 +14645,56 @@
           <t>reg-csa-3c-het-1</t>
         </is>
       </c>
-      <c r="AB131" s="5" t="n"/>
+      <c r="AB131" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC131" s="5" t="n"/>
       <c r="AD131" s="5" t="n"/>
       <c r="AE131" s="5" t="n"/>
       <c r="AF131" s="5" t="n"/>
-      <c r="AG131" s="5" t="n"/>
-      <c r="AH131" s="5" t="n"/>
-      <c r="AI131" s="5" t="n"/>
-      <c r="AJ131" s="5" t="n"/>
-      <c r="AK131" s="5" t="n"/>
-      <c r="AL131" s="5" t="n"/>
-      <c r="AM131" s="5" t="n"/>
+      <c r="AG131" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-1-marshall.md</t>
+        </is>
+      </c>
+      <c r="AH131" s="5" t="inlineStr">
+        <is>
+          <t>Pettigrew (to division) -&gt; Marshall k Jul 3 (CONFLICT: Davis rpt 'w&amp;c' vs Young 'supposed killed' vs register k - k adopted) -&gt; Maj. Jones; Jul 1: Burgwyn k, Lane w; 1 field officer left after Jul 3</t>
+        </is>
+      </c>
+      <c r="AI131" s="5" t="inlineStr">
+        <is>
+          <t>2,000 'present on the first day' (stone-sentinels, Jul-1 scope caveat); 26NC regt primary: 800+ -&gt; 216 unhurt (Jul 1) -&gt; ~80 (Jul 4) (young-26nc); Jul 3 basis ~900 [B subtraction, open for primary]</t>
+        </is>
+      </c>
+      <c r="AJ131" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 eve: 1 mi right, rear of batteries; [C +5] 9am quarter-mile shift behind Pegram; j3-02 label ~(3550,5360)+-100; farthest advance mon-26nc-1 (4431.7,4923.9) at the wall</t>
+        </is>
+      </c>
+      <c r="AK131" s="5" t="inlineStr">
+        <is>
+          <t>[C +65 via jones] 'About 2 o'clock' step-off w/ launch confusion (close-right vs give-way-left, corrected); ~3/4 mi advance; deadly volley from left at wall; retreat to morning line by ~16:00</t>
+        </is>
+      </c>
+      <c r="AL131" s="5" t="inlineStr">
+        <is>
+          <t>[A window] two-hour bombardment (division); canister from half-way, musketry hail at 250-300 yd (range ladder cross vs Woodruff/Arnold/Smyth)</t>
+        </is>
+      </c>
+      <c r="AM131" s="5" t="inlineStr">
+        <is>
+          <t>1,105 = 190/915/NO-missing-column (anv-return; 26NC 588 = 86k/502w); ED-49 cleanest exemplar (Jul 3 capture mass absent); 26NC day split ~584 Jul 1 / ~136 Jul 3 [B]; 11 color-bearers down Jul 1, colors lost Jul 3</t>
+        </is>
+      </c>
       <c r="AN131" s="5" t="n"/>
-      <c r="AO131" s="5" t="n"/>
+      <c r="AO131" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -15925,20 +16169,56 @@
           <t>reg-csa-3c-pen-2</t>
         </is>
       </c>
-      <c r="AB143" s="5" t="n"/>
+      <c r="AB143" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC143" s="5" t="n"/>
       <c r="AD143" s="5" t="n"/>
       <c r="AE143" s="5" t="n"/>
       <c r="AF143" s="5" t="n"/>
-      <c r="AG143" s="5" t="n"/>
-      <c r="AH143" s="5" t="n"/>
-      <c r="AI143" s="5" t="n"/>
-      <c r="AJ143" s="5" t="n"/>
-      <c r="AK143" s="5" t="n"/>
-      <c r="AL143" s="5" t="n"/>
-      <c r="AM143" s="5" t="n"/>
+      <c r="AG143" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-pen-2-lane.md</t>
+        </is>
+      </c>
+      <c r="AH143" s="5" t="inlineStr">
+        <is>
+          <t>Lane (cdr; division command Jul 2 eve + after Trimble fell) -&gt; Col. Avery in intervals; Avery/Barry brought left rgts out under orders</t>
+        </is>
+      </c>
+      <c r="AI143" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 1,355 effective incl. ambulance/rear guard (lane-jh, =build); Jul 1-2 loss 'but slight' - serviceable Jul 3 basis</t>
+        </is>
+      </c>
+      <c r="AJ143" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 by Garnett's bn (frame); Jul 3 rear of Heth's right, Lowrance on right, behind Poague/Pegram line; j3-02 pre-move label ~(3050,5750)+-120; 'no second line in rear of [Heth's] left' (structural primary)</t>
+        </is>
+      </c>
+      <c r="AK143" s="5" t="inlineStr">
+        <is>
+          <t>[D] morning lateral ~1.2km [B 15-20 min]; advance ~1 mi, left checked by Trimble; passed through collapsing front WITHOUT halting; withdrew when enfiladed from left; reformed in rear of artillery</t>
+        </is>
+      </c>
+      <c r="AL143" s="5" t="inlineStr">
+        <is>
+          <t>[A window] two-hour bombardment exposure (no figure); fire reserved to 'good range' then silenced guns on front (reads vs Woodruff/Arnold wreckage - corroborated); raking artillery from right</t>
+        </is>
+      </c>
+      <c r="AM143" s="5" t="inlineStr">
+        <is>
+          <t>ED-47 candidate: Lane's 660 of 1,355 (total) vs return 389 (k+w only; return's own footnote carries the 660); regt k+w 89/45/104/63/88; mass falls Jul 3 (crest fire window + flank collapse)</t>
+        </is>
+      </c>
       <c r="AN143" s="5" t="n"/>
-      <c r="AO143" s="5" t="n"/>
+      <c r="AO143" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -16049,20 +16329,56 @@
           <t>reg-csa-3c-and-4</t>
         </is>
       </c>
-      <c r="AB144" s="5" t="n"/>
+      <c r="AB144" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC144" s="5" t="n"/>
       <c r="AD144" s="5" t="n"/>
       <c r="AE144" s="5" t="n"/>
       <c r="AF144" s="5" t="n"/>
-      <c r="AG144" s="5" t="n"/>
-      <c r="AH144" s="5" t="n"/>
-      <c r="AI144" s="5" t="n"/>
-      <c r="AJ144" s="5" t="n"/>
-      <c r="AK144" s="5" t="n"/>
-      <c r="AL144" s="5" t="n"/>
-      <c r="AM144" s="5" t="n"/>
+      <c r="AG144" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-4-lang.md</t>
+        </is>
+      </c>
+      <c r="AH144" s="5" t="inlineStr">
+        <is>
+          <t>Col. Lang (Perry absent typhoid); pins: McCaslan (AAAG) k in Jul 3 retreat; Moore (2FL) w&amp;c, Gardner (5FL) w; 8FL colors lost Jul 2</t>
+        </is>
+      </c>
+      <c r="AI144" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 'near 700 strong' (lang, =build) - smallest brigade in the assault's orbit</t>
+        </is>
+      </c>
+      <c r="AJ144" s="5" t="inlineStr">
+        <is>
+          <t>[C/D ~07:00] up with Wilcox's left to foot of gun hill, skirmishers one crest fwd; j3-01 label ~(3230,4820)+-120; reform on old line, night withdrawal to woods</t>
+        </is>
+      </c>
+      <c r="AK144" s="5" t="inlineStr">
+        <is>
+          <t>[D] standing conform-to-Wilcox order ('I would receive no further orders'); advanced after Pickett's troops retired; left flanked in the woods, retreat order inaudible in the din; 2FL colors + pocket captured (16th VT object, veazey cross)</t>
+        </is>
+      </c>
+      <c r="AL144" s="5" t="inlineStr">
+        <is>
+          <t>[C -53] bombardment 'nearly 2 p.m. ... till nearly 4 p.m.' (late-stated pole, joins Longstreet/Smyth cluster); no formed fire window Jul 3 (movement and reception only)</t>
+        </is>
+      </c>
+      <c r="AM144" s="5" t="inlineStr">
+        <is>
+          <t>455 = 33/217/205 (return = lang's own 455 of ~700 EXACT; regt k+w 81/75/94) - 65% loss rate, highest documented in batch; day split [B]: Jul 2 ~300 (his figure) -&gt; Jul 3 ~155 concentrated in the capture pocket + retreat</t>
+        </is>
+      </c>
       <c r="AN144" s="5" t="n"/>
-      <c r="AO144" s="5" t="n"/>
+      <c r="AO144" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -16297,20 +16613,56 @@
           <t>reg-csa-3c-pen-4</t>
         </is>
       </c>
-      <c r="AB146" s="5" t="n"/>
+      <c r="AB146" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC146" s="5" t="n"/>
       <c r="AD146" s="5" t="n"/>
       <c r="AE146" s="5" t="n"/>
       <c r="AF146" s="5" t="n"/>
-      <c r="AG146" s="5" t="n"/>
-      <c r="AH146" s="5" t="n"/>
-      <c r="AI146" s="5" t="n"/>
-      <c r="AJ146" s="5" t="n"/>
-      <c r="AK146" s="5" t="n"/>
-      <c r="AL146" s="5" t="n"/>
-      <c r="AM146" s="5" t="n"/>
+      <c r="AG146" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-pen-4-lowrance.md</t>
+        </is>
+      </c>
+      <c r="AH146" s="5" t="inlineStr">
+        <is>
+          <t>Scales w Jul 1 -&gt; Lowrance (w Jul 1, again Jul 3 per register - report silent, flag); Jul 1: every field officer save one disabled</t>
+        </is>
+      </c>
+      <c r="AI146" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY ~500 from Jul 1 evening ('depressed, dilapidated, almost unorganized') = Jul 3 basis; build 1,250 = pre-Jul-1 (decay must cross the 500 waypoint)</t>
+        </is>
+      </c>
+      <c r="AJ146" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2: extreme right on line w/ artillery (its only guard); Jul 3: second line in rear of POAGUE's bn (primary frame anchor); right of Lane; works touched on right at climax</t>
+        </is>
+      </c>
+      <c r="AK146" s="5" t="inlineStr">
+        <is>
+          <t>[D] morning lateral right; advance 1 mi over 'wide, hot, already crimson plain'; at 2/3 way front-line troops 'came tearing through our ranks'; retreat without orders, rallied on start line</t>
+        </is>
+      </c>
+      <c r="AL146" s="5" t="inlineStr">
+        <is>
+          <t>[A window + B] '&gt;= one hour under a most galling fire' (his duration) / 'two hours' (Engelhard) - both carried; climax: '800 guns' combined two-brigade strength pin at the works</t>
+        </is>
+      </c>
+      <c r="AM146" s="5" t="inlineStr">
+        <is>
+          <t>535 = 102/323/110 (anv-return regt k+w 126/66/89/64/79) vs SCALES'S OWN Jul-1 table 545 (48/381/116) - July-1-scoped table LARGER than 3-day return (ED-49 starkest exemplar); build decay 599 flagged for reconciliation</t>
+        </is>
+      </c>
       <c r="AN146" s="5" t="n"/>
-      <c r="AO146" s="5" t="n"/>
+      <c r="AO146" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -17909,20 +18261,56 @@
           <t>reg-csa-3c-and-1</t>
         </is>
       </c>
-      <c r="AB159" s="5" t="n"/>
+      <c r="AB159" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC159" s="5" t="n"/>
       <c r="AD159" s="5" t="n"/>
       <c r="AE159" s="5" t="n"/>
       <c r="AF159" s="5" t="n"/>
-      <c r="AG159" s="5" t="n"/>
-      <c r="AH159" s="5" t="n"/>
-      <c r="AI159" s="5" t="n"/>
-      <c r="AJ159" s="5" t="n"/>
-      <c r="AK159" s="5" t="n"/>
-      <c r="AL159" s="5" t="n"/>
-      <c r="AM159" s="5" t="n"/>
+      <c r="AG159" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-1-wilcox.md; CA-J3A-10 executor</t>
+        </is>
+      </c>
+      <c r="AH159" s="5" t="inlineStr">
+        <is>
+          <t>Wilcox (unwounded); 4 of 5 rgt cdrs w JUL 2 (Forney, Pinckard, Sanders, Fletcher); no rgt-cdr losses Jul 3</t>
+        </is>
+      </c>
+      <c r="AI159" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY Jul 3: 'about 1,200' (wilcox) - closes exactly vs build 1,777 start - 577 Jul 2 loss; order R-L 9-10-11-8-14 Ala</t>
+        </is>
+      </c>
+      <c r="AJ159" s="5" t="inlineStr">
+        <is>
+          <t>[D] before sunrise: line parallel to Emmitsburg pike ~200 yd W, Alexander's guns in front; j3-01 label ~(3100,4400)+-120 (04:00-08:00 window = exact bracket); farthest advance = ravine below McGilvery crest (build displacement understates - flag)</t>
+        </is>
+      </c>
+      <c r="AK159" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-6 +20-30 min] the DELAYED LAUNCH (three staff officers in succession; Alexander concurs; Lang sequences after repulse - one envelope); halt at ravine awaiting artillery that had no ammunition; withdrew on own judgment</t>
+        </is>
+      </c>
+      <c r="AL159" s="5" t="inlineStr">
+        <is>
+          <t>[A window] bombardment: '&lt;a dozen k&amp;w' + Kemper-severity contrast + Anderson's 'suffered most seriously' of his division (compatible); advance under three-sided artillery, no musketry phase; 'Not a man of the division ... could I see'</t>
+        </is>
+      </c>
+      <c r="AM159" s="5" t="inlineStr">
+        <is>
+          <t>PER-DAY PRIMARY: Jul 2 577 / Jul 3 204 / total 777 = return 51/469/257 EXACT; 257 missing 'nearly all killed or wounded, few unwounded prisoners'; Jul 3 cause mix artillery-dominated (distinct from every front-line brigade)</t>
+        </is>
+      </c>
       <c r="AN159" s="5" t="n"/>
-      <c r="AO159" s="5" t="n"/>
+      <c r="AO159" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -9329,20 +9329,56 @@
           <t>reg-csa-3c-bn-poague</t>
         </is>
       </c>
-      <c r="AB87" s="5" t="n"/>
+      <c r="AB87" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC87" s="5" t="n"/>
       <c r="AD87" s="5" t="n"/>
       <c r="AE87" s="5" t="n"/>
       <c r="AF87" s="5" t="n"/>
-      <c r="AG87" s="5" t="n"/>
-      <c r="AH87" s="5" t="n"/>
-      <c r="AI87" s="5" t="n"/>
-      <c r="AJ87" s="5" t="n"/>
-      <c r="AK87" s="5" t="n"/>
-      <c r="AL87" s="5" t="n"/>
-      <c r="AM87" s="5" t="n"/>
+      <c r="AG87" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-bn-poague.md; ED-36 Third Corps frame COMPLETE (Lowrance's anchor closed); memoir (Gunner with Stonewall) print-only acquisition item</t>
+        </is>
+      </c>
+      <c r="AH87" s="5" t="inlineStr">
+        <is>
+          <t>Maj. W.T. Poague; Wyatt (Albemarle Va), Graham (Charlotte NC), Ward (Madison Miss), Brooke (Va); 16 guns: 7 Nap + 6 how + 1 Parrott + 2 3-in (tablet); Jul 3 split command Wyatt/Ward; Ward-mw tradition NOT in corpus (open pin)</t>
+        </is>
+      </c>
+      <c r="AI87" s="5" t="inlineStr">
+        <is>
+          <t>build 384 (B&amp;M-type hop, ED-38 class); no personnel primary</t>
+        </is>
+      </c>
+      <c r="AJ87" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 1-2 OFF THE LINE (Cashtown detach, attested non-participation); [C] Jul 2 late evening two-position line: 5 guns left of Anderson's division near Pegram + 5 Napoleons 400 yd right, ~1,400 yd from the Union batteries; j3-03 WYATT (3427,5220), GRAHAM (3489,5325), POAGUE'S BATT. bar (3467,4894) +-120m</t>
+        </is>
+      </c>
+      <c r="AK87" s="5" t="inlineStr">
+        <is>
+          <t>[C/D] Jul 2 night effortful emplacement ('at last succeeded'); [D] post-repulse howitzers ordered up (no fire); [C] Jul 4 dusk withdrawal to Hagerstown</t>
+        </is>
+      </c>
+      <c r="AL87" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 3 ~07:00 unordered affair (Hill's order; Poague ceased it; 8 Wyatt horses; enemy caisson exploded) - do NOT smooth into the cannonade; [A window] participated in the 13:07 general engagement; HOWITZER NEGATIVE: 6 tubes present-never-firing all battle (ED-44); tablet expenditure 657 rounds / 17 horses (ED-42 battery-side) [B: ~60-90 min deliberate fire for 10 guns]</t>
+        </is>
+      </c>
+      <c r="AM87" s="5" t="inlineStr">
+        <is>
+          <t>return 2/24/6 = 32, batteries '*Not reported in detail' (ED-49 gap); tablet prints the same 32 - ED-43 corroboration SATISFIED; episode split: morning affair + cannonade window, Jul 1-2 zero</t>
+        </is>
+      </c>
       <c r="AN87" s="5" t="n"/>
-      <c r="AO87" s="5" t="n"/>
+      <c r="AO87" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -30565,20 +30601,56 @@
           <t>reg-us-ii-2-2</t>
         </is>
       </c>
-      <c r="AB267" s="5" t="n"/>
+      <c r="AB267" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC267" s="5" t="n"/>
       <c r="AD267" s="5" t="n"/>
       <c r="AE267" s="5" t="n"/>
       <c r="AF267" s="5" t="n"/>
-      <c r="AG267" s="5" t="n"/>
-      <c r="AH267" s="5" t="n"/>
-      <c r="AI267" s="5" t="n"/>
-      <c r="AJ267" s="5" t="n"/>
-      <c r="AK267" s="5" t="n"/>
-      <c r="AL267" s="5" t="n"/>
-      <c r="AM267" s="5" t="n"/>
+      <c r="AG267" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
+        </is>
+      </c>
+      <c r="AH267" s="5" t="inlineStr">
+        <is>
+          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
+        </is>
+      </c>
+      <c r="AI267" s="5" t="inlineStr">
+        <is>
+          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
+        </is>
+      </c>
+      <c r="AJ267" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
+        </is>
+      </c>
+      <c r="AK267" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
+        </is>
+      </c>
+      <c r="AL267" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
+        </is>
+      </c>
+      <c r="AM267" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
+        </is>
+      </c>
       <c r="AN267" s="5" t="n"/>
-      <c r="AO267" s="5" t="n"/>
+      <c r="AO267" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (T5 window held)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -30685,20 +30757,56 @@
         </is>
       </c>
       <c r="AA268" s="2" t="inlineStr"/>
-      <c r="AB268" s="5" t="n"/>
+      <c r="AB268" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC268" s="5" t="n"/>
       <c r="AD268" s="5" t="n"/>
       <c r="AE268" s="5" t="n"/>
       <c r="AF268" s="5" t="n"/>
-      <c r="AG268" s="5" t="n"/>
-      <c r="AH268" s="5" t="n"/>
-      <c r="AI268" s="5" t="n"/>
-      <c r="AJ268" s="5" t="n"/>
-      <c r="AK268" s="5" t="n"/>
-      <c r="AL268" s="5" t="n"/>
-      <c r="AM268" s="5" t="n"/>
+      <c r="AG268" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+        </is>
+      </c>
+      <c r="AH268" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+        </is>
+      </c>
+      <c r="AI268" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 209 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ268" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+        </is>
+      </c>
+      <c r="AK268" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+        </is>
+      </c>
+      <c r="AL268" s="5" t="inlineStr">
+        <is>
+          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+        </is>
+      </c>
+      <c r="AM268" s="5" t="inlineStr">
+        <is>
+          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+        </is>
+      </c>
       <c r="AN268" s="5" t="n"/>
-      <c r="AO268" s="5" t="n"/>
+      <c r="AO268" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -31181,20 +31289,56 @@
           <t>reg-us-i-3-1</t>
         </is>
       </c>
-      <c r="AB272" s="5" t="n"/>
+      <c r="AB272" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC272" s="5" t="n"/>
       <c r="AD272" s="5" t="n"/>
       <c r="AE272" s="5" t="n"/>
       <c r="AF272" s="5" t="n"/>
-      <c r="AG272" s="5" t="n"/>
-      <c r="AH272" s="5" t="n"/>
-      <c r="AI272" s="5" t="n"/>
-      <c r="AJ272" s="5" t="n"/>
-      <c r="AK272" s="5" t="n"/>
-      <c r="AL272" s="5" t="n"/>
-      <c r="AM272" s="5" t="n"/>
+      <c r="AG272" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
+        </is>
+      </c>
+      <c r="AH272" s="5" t="inlineStr">
+        <is>
+          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
+        </is>
+      </c>
+      <c r="AI272" s="5" t="inlineStr">
+        <is>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
+        </is>
+      </c>
+      <c r="AJ272" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
+        </is>
+      </c>
+      <c r="AK272" s="5" t="inlineStr">
+        <is>
+          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
+        </is>
+      </c>
+      <c r="AL272" s="5" t="inlineStr">
+        <is>
+          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
+        </is>
+      </c>
+      <c r="AM272" s="5" t="inlineStr">
+        <is>
+          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
+        </is>
+      </c>
       <c r="AN272" s="5" t="n"/>
-      <c r="AO272" s="5" t="n"/>
+      <c r="AO272" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -32049,20 +32193,56 @@
           <t>reg-us-ii-3-1</t>
         </is>
       </c>
-      <c r="AB279" s="5" t="n"/>
+      <c r="AB279" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+        </is>
+      </c>
       <c r="AC279" s="5" t="n"/>
       <c r="AD279" s="5" t="n"/>
       <c r="AE279" s="5" t="n"/>
       <c r="AF279" s="5" t="n"/>
-      <c r="AG279" s="5" t="n"/>
-      <c r="AH279" s="5" t="n"/>
-      <c r="AI279" s="5" t="n"/>
-      <c r="AJ279" s="5" t="n"/>
-      <c r="AK279" s="5" t="n"/>
-      <c r="AL279" s="5" t="n"/>
-      <c r="AM279" s="5" t="n"/>
+      <c r="AG279" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+        </is>
+      </c>
+      <c r="AH279" s="5" t="inlineStr">
+        <is>
+          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+        </is>
+      </c>
+      <c r="AI279" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 640 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ279" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265))</t>
+        </is>
+      </c>
+      <c r="AK279" s="5" t="inlineStr">
+        <is>
+          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+        </is>
+      </c>
+      <c r="AL279" s="5" t="inlineStr">
+        <is>
+          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+        </is>
+      </c>
+      <c r="AM279" s="5" t="inlineStr">
+        <is>
+          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+        </is>
+      </c>
       <c r="AN279" s="5" t="n"/>
-      <c r="AO279" s="5" t="n"/>
+      <c r="AO279" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -32669,20 +32849,56 @@
           <t>reg-us-i-3-2</t>
         </is>
       </c>
-      <c r="AB284" s="5" t="n"/>
+      <c r="AB284" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (sheet grain)</t>
+        </is>
+      </c>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="n"/>
-      <c r="AH284" s="5" t="n"/>
-      <c r="AI284" s="5" t="n"/>
-      <c r="AJ284" s="5" t="n"/>
-      <c r="AK284" s="5" t="n"/>
-      <c r="AL284" s="5" t="n"/>
-      <c r="AM284" s="5" t="n"/>
+      <c r="AG284" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list)</t>
+        </is>
+      </c>
+      <c r="AH284" s="5" t="inlineStr">
+        <is>
+          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
+        </is>
+      </c>
+      <c r="AI284" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 465 remnant (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ284" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
+        </is>
+      </c>
+      <c r="AK284" s="5" t="inlineStr">
+        <is>
+          <t>none attested Jul 2-3 (sheet states agree; no report-level stillness statement - negative at sheet grain only)</t>
+        </is>
+      </c>
+      <c r="AL284" s="5" t="inlineStr">
+        <is>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
+        </is>
+      </c>
+      <c r="AM284" s="5" t="inlineStr">
+        <is>
+          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
+        </is>
+      </c>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="n"/>
+      <c r="AO284" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -15461,20 +15461,56 @@
           <t>reg-csa-1c-mcl-3</t>
         </is>
       </c>
-      <c r="AB137" s="5" t="n"/>
+      <c r="AB137" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC137" s="5" t="n"/>
       <c r="AD137" s="5" t="n"/>
       <c r="AE137" s="5" t="n"/>
       <c r="AF137" s="5" t="n"/>
-      <c r="AG137" s="5" t="n"/>
-      <c r="AH137" s="5" t="n"/>
-      <c r="AI137" s="5" t="n"/>
-      <c r="AJ137" s="5" t="n"/>
-      <c r="AK137" s="5" t="n"/>
-      <c r="AL137" s="5" t="n"/>
-      <c r="AM137" s="5" t="n"/>
+      <c r="AG137" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-mcl-3-barksdale.md</t>
+        </is>
+      </c>
+      <c r="AH137" s="5" t="inlineStr">
+        <is>
+          <t>Barksdale's bde (13/17/18/21 MS); Barksdale mw at Plum Run ~19:00 (tablet + Hall's 20-yards receiving-side pin, compatible ~100 m grain), d. July 3 Hummelbaugh farm -&gt; Humphreys. NO OR REPORT at any echelon (verified-negative class)</t>
+        </is>
+      </c>
+      <c r="AI137" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present 1,598' (compilation, hop flagged); no primary</t>
+        </is>
+      </c>
+      <c r="AJ137" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Warfield line from ~15:00; [E drawn j2-03 17:00] rgt numbers with advance arrows POISED not advanced (2923,3865) - drawn state contradicts the tablet's 'Advanced at 5 P.M.'; [E drawn j2-04 19:00] TWO ELEMENTS: main body vs Willard at Plum Run (4053,4080), 21st MS at Trostle/Bigelow (3617,3643) with WATSON (4093,3607)</t>
+        </is>
+      </c>
+      <c r="AK137" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-9 ~18:15] step-off via Lamar order + drums pin + Alexander's 20-min ladder interval; the battery-extraction delay (McLaws); [B] ~600 m to the orchard then divergent axes; Plum Run collapse 19:00-19:15</t>
+        </is>
+      </c>
+      <c r="AL137" s="5" t="inlineStr">
+        <is>
+          <t>[D] the salient breach with Kershaw's 8th SC flank fire; 21st MS took Bigelow's 9th MA + Watson's I/5th US 'unable to bring off'; July 3 artillery support at the orchard (ED-44 adjacent)</t>
+        </is>
+      </c>
+      <c r="AM137" s="5" t="inlineStr">
+        <is>
+          <t>tablet ITEMIZES the return's pooled missing: 105/550/92 = 747 EXACT match (first tablet-closes-ED-49-gap case); ~804 B&amp;M variant carried; split concentrated 18:15-19:15</t>
+        </is>
+      </c>
       <c r="AN137" s="5" t="n"/>
-      <c r="AO137" s="5" t="n"/>
+      <c r="AO137" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -16577,20 +16613,56 @@
           <t>reg-csa-1c-mcl-1</t>
         </is>
       </c>
-      <c r="AB146" s="5" t="n"/>
+      <c r="AB146" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC146" s="5" t="n"/>
       <c r="AD146" s="5" t="n"/>
       <c r="AE146" s="5" t="n"/>
       <c r="AF146" s="5" t="n"/>
-      <c r="AG146" s="5" t="n"/>
-      <c r="AH146" s="5" t="n"/>
-      <c r="AI146" s="5" t="n"/>
-      <c r="AJ146" s="5" t="n"/>
-      <c r="AK146" s="5" t="n"/>
-      <c r="AL146" s="5" t="n"/>
-      <c r="AM146" s="5" t="n"/>
+      <c r="AG146" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-mcl-1-kershaw.md; ED-55 candidate exemplar (wing report-clock skew +90)</t>
+        </is>
+      </c>
+      <c r="AH146" s="5" t="inlineStr">
+        <is>
+          <t>Kershaw's bde (2/3/7/8/15 SC + 3d SC Bn); Kershaw unwounded; De Saussure k, McLeod mw, Kennedy/Bland/Miller w (all July 2)</t>
+        </is>
+      </c>
+      <c r="AI146" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present about 1800' (compilation); no report statement</t>
+        </is>
+      </c>
+      <c r="AJ146" s="5" t="inlineStr">
+        <is>
+          <t>[C report +90] the stone wall 'about 3 p.m.' stated; [E drawn] KERSHAW advance line (3941,3263) at 17:00 j2-03; stony-hill W edge (3308,3336) at 19:00 j2-04; July 2 dark Peach Orchard -&gt; July 3 13:00 original wall (tablet+report)</t>
+        </is>
+      </c>
+      <c r="AK146" s="5" t="inlineStr">
+        <is>
+          <t>[trigger first-class] CABELL'S THREE-GUN SIGNAL step-off; Longstreet on foot to the road; [D] Barksdale's drums heard at the road (the ladder interval, Alexander: 20+ min); Wheatfield oscillation; nightfall withdrawal</t>
+        </is>
+      </c>
+      <c r="AL146" s="5" t="inlineStr">
+        <is>
+          <t>[D] stony hill fight at 30 paces; Caldwell's two-line counterattack; the Wofford resweep to the mountain's foot; July 3 Peach Orchard skirmish only</t>
+        </is>
+      </c>
+      <c r="AM146" s="5" t="inlineStr">
+        <is>
+          <t>THE CLEAN CASE: report = return = tablet 115/483/32 = 630 (2nd SC row blank - itemization gap flagged)</t>
+        </is>
+      </c>
       <c r="AN146" s="5" t="n"/>
-      <c r="AO146" s="5" t="n"/>
+      <c r="AO146" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -17021,20 +17093,56 @@
           <t>reg-csa-1c-hood-1</t>
         </is>
       </c>
-      <c r="AB149" s="5" t="n"/>
+      <c r="AB149" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC149" s="5" t="n"/>
       <c r="AD149" s="5" t="n"/>
       <c r="AE149" s="5" t="n"/>
       <c r="AF149" s="5" t="n"/>
-      <c r="AG149" s="5" t="n"/>
-      <c r="AH149" s="5" t="n"/>
-      <c r="AI149" s="5" t="n"/>
-      <c r="AJ149" s="5" t="n"/>
-      <c r="AK149" s="5" t="n"/>
-      <c r="AL149" s="5" t="n"/>
-      <c r="AM149" s="5" t="n"/>
+      <c r="AG149" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-hood-1-law.md; contributes CSA side of ED-53 candidate (step-off ~16:30 +-15)</t>
+        </is>
+      </c>
+      <c r="AH149" s="5" t="inlineStr">
+        <is>
+          <t>Law's bde (4/15/44/47/48 AL); Law to DIVISION at the step-off (Hood w) -&gt; Sheffield; Feagin w; no brigade report by Law (verified negative - five regimental reports are the OR base)</t>
+        </is>
+      </c>
+      <c r="AI149" s="5" t="inlineStr">
+        <is>
+          <t>tablet ~1,500 (compilation); 15th AL 'about five hundred' primary (oates-1905); the 22-man water detail captured entire pre-fight</t>
+        </is>
+      </c>
+      <c r="AJ149" s="5" t="inlineStr">
+        <is>
+          <t>[C] step-off line 50 yd W of tablet; [E drawn j2-03] 15 Ala bar (4345,2343) vs VINCENT'S SPUR, 44 Ala (3795,2538) at Plum Run; night line Round Top west foot (j2-05 drawn)</t>
+        </is>
+      </c>
+      <c r="AK149" s="5" t="inlineStr">
+        <is>
+          <t>[B] New Guilford 25 mi 03:30-04:00 -&gt; 12:00-14:00 (three-way arrival spread carried); [A vs CA-J2A-3 ~16:30] assault leg; Oates's Round Top excursion [D]; dusk withdrawal</t>
+        </is>
+      </c>
+      <c r="AL149" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-6] the five-charges fight (attacker's own count = Chamberlain's); Devil's Den taken 'in less than an hour' (Law, tier-B input); July 3 skirmish + Farnsworth repulse 17:00 [C tablet]</t>
+        </is>
+      </c>
+      <c r="AM149" s="5" t="inlineStr">
+        <is>
+          <t>return 74/276/146-pooled=496 (ED-49); 15th AL report 161 vs row 83 and 4th AL 87 vs 66 (rule-4 exemplars); ~400 prisoners receiving-side cross-check</t>
+        </is>
+      </c>
       <c r="AN149" s="5" t="n"/>
-      <c r="AO149" s="5" t="n"/>
+      <c r="AO149" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -18049,20 +18157,56 @@
           <t>reg-csa-1c-hood-2</t>
         </is>
       </c>
-      <c r="AB157" s="5" t="n"/>
+      <c r="AB157" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC157" s="5" t="n"/>
       <c r="AD157" s="5" t="n"/>
       <c r="AE157" s="5" t="n"/>
       <c r="AF157" s="5" t="n"/>
-      <c r="AG157" s="5" t="n"/>
-      <c r="AH157" s="5" t="n"/>
-      <c r="AI157" s="5" t="n"/>
-      <c r="AJ157" s="5" t="n"/>
-      <c r="AK157" s="5" t="n"/>
-      <c r="AL157" s="5" t="n"/>
-      <c r="AM157" s="5" t="n"/>
+      <c r="AG157" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-hood-2-robertson.md</t>
+        </is>
+      </c>
+      <c r="AH157" s="5" t="inlineStr">
+        <is>
+          <t>Texas bde (1/4/5 TX + 3 AR); Robertson w late evening July 2 -&gt; Work; six field-officer w pins July 2; Price AAG lost July 3 morning</t>
+        </is>
+      </c>
+      <c r="AI157" s="5" t="inlineStr">
+        <is>
+          <t>tablet ~1,100 (compilation); no primary statement</t>
+        </is>
+      </c>
+      <c r="AJ157" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] arrived ~16:00, left ordered on the pike - ABANDONED by his decision to close on Law (primary); [E drawn j2-03] TX bars in Plum Run valley; July 3 Big Round Top NW spur (tablet)</t>
+        </is>
+      </c>
+      <c r="AK157" s="5" t="inlineStr">
+        <is>
+          <t>[B] half-mile open-ground assault leg under Smith's canister; the 4th/5th TX right-drift to Law; 1st TX battery-hill sequence</t>
+        </is>
+      </c>
+      <c r="AL157" s="5" t="inlineStr">
+        <is>
+          <t>[B] over-an-hour Devil's Den contest; 3 of 6 Smith's guns (CROSS-CREDIT conflict with Law's 44th/48th - carried); July 3 continuous skirmishing (primary)</t>
+        </is>
+      </c>
+      <c r="AM157" s="5" t="inlineStr">
+        <is>
+          <t>return 84/393/120-pooled=597 (ED-49; 1st TX row transcription inconsistency flagged); tablet ~540 variant</t>
+        </is>
+      </c>
       <c r="AN157" s="5" t="n"/>
-      <c r="AO157" s="5" t="n"/>
+      <c r="AO157" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -26688,7 +26832,7 @@
       <c r="AF235" s="5" t="n"/>
       <c r="AG235" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-rittenhouse.md; rittenhouse-mollus-1887 = the T-ceiling item</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-rittenhouse.md; rittenhouse-mollus-1887 = the T-ceiling item; pass-5: MOLLUS round 4 TERMINAL (library/CDL); summit anchor refined to (4200,2600) +-80</t>
         </is>
       </c>
       <c r="AH235" s="5" t="inlineStr">
@@ -26718,13 +26862,13 @@
       </c>
       <c r="AM235" s="5" t="inlineStr">
         <is>
-          <t>14 (1 off + 8 men k, 5 w, tablet; ~19% of 73); Jul 2 dominates [D]; brigade frame 44 total (Martin)</t>
+          <t>return row 7/6/0=13 (p. 180, landed pass 5) vs tablet 14 - ED-52 adopts the return; episode split July 2 dominant (Hazlett mw)</t>
         </is>
       </c>
       <c r="AN235" s="5" t="n"/>
       <c r="AO235" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
@@ -31284,7 +31428,7 @@
       <c r="AF273" s="5" t="n"/>
       <c r="AG273" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
         </is>
       </c>
       <c r="AH273" s="5" t="inlineStr">
@@ -31320,7 +31464,7 @@
       <c r="AN273" s="5" t="n"/>
       <c r="AO273" s="5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4 full-arc (T5-grade window via V2 claims)</t>
         </is>
       </c>
     </row>
@@ -33852,7 +33996,7 @@
       <c r="AF292" s="5" t="n"/>
       <c r="AG292" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
         </is>
       </c>
       <c r="AH292" s="5" t="inlineStr">
@@ -33862,7 +34006,7 @@
       </c>
       <c r="AI292" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 465 remnant (compilation, flagged)</t>
+          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
         </is>
       </c>
       <c r="AJ292" s="5" t="inlineStr">
@@ -33872,7 +34016,7 @@
       </c>
       <c r="AK292" s="5" t="inlineStr">
         <is>
-          <t>none attested Jul 2-3 (sheet states agree; no report-level stillness statement - negative at sheet grain only)</t>
+          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
         </is>
       </c>
       <c r="AL292" s="5" t="inlineStr">
@@ -33888,7 +34032,7 @@
       <c r="AN292" s="5" t="n"/>
       <c r="AO292" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
@@ -34497,20 +34641,56 @@
           <t>reg-us-v-2-3</t>
         </is>
       </c>
-      <c r="AB297" s="5" t="n"/>
+      <c r="AB297" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC297" s="5" t="n"/>
       <c r="AD297" s="5" t="n"/>
       <c r="AE297" s="5" t="n"/>
       <c r="AF297" s="5" t="n"/>
-      <c r="AG297" s="5" t="n"/>
-      <c r="AH297" s="5" t="n"/>
-      <c r="AI297" s="5" t="n"/>
-      <c r="AJ297" s="5" t="n"/>
-      <c r="AK297" s="5" t="n"/>
-      <c r="AL297" s="5" t="n"/>
-      <c r="AM297" s="5" t="n"/>
+      <c r="AG297" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+        </is>
+      </c>
+      <c r="AH297" s="5" t="inlineStr">
+        <is>
+          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+        </is>
+      </c>
+      <c r="AI297" s="5" t="inlineStr">
+        <is>
+          <t>no brigade primary (open; compilation tier)</t>
+        </is>
+      </c>
+      <c r="AJ297" s="5" t="inlineStr">
+        <is>
+          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+        </is>
+      </c>
+      <c r="AK297" s="5" t="inlineStr">
+        <is>
+          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+        </is>
+      </c>
+      <c r="AL297" s="5" t="inlineStr">
+        <is>
+          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+        </is>
+      </c>
+      <c r="AM297" s="5" t="inlineStr">
+        <is>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
+        </is>
+      </c>
       <c r="AN297" s="5" t="n"/>
-      <c r="AO297" s="5" t="n"/>
+      <c r="AO297" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -35004,7 +35184,7 @@
       <c r="AF301" s="5" t="n"/>
       <c r="AG301" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31)</t>
         </is>
       </c>
       <c r="AH301" s="5" t="inlineStr">
@@ -35040,7 +35220,7 @@
       <c r="AN301" s="5" t="n"/>
       <c r="AO301" s="5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
@@ -36517,20 +36697,56 @@
           <t>reg-us-v-1-3</t>
         </is>
       </c>
-      <c r="AB313" s="5" t="n"/>
+      <c r="AB313" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+        </is>
+      </c>
       <c r="AC313" s="5" t="n"/>
       <c r="AD313" s="5" t="n"/>
       <c r="AE313" s="5" t="n"/>
       <c r="AF313" s="5" t="n"/>
-      <c r="AG313" s="5" t="n"/>
-      <c r="AH313" s="5" t="n"/>
-      <c r="AI313" s="5" t="n"/>
-      <c r="AJ313" s="5" t="n"/>
-      <c r="AK313" s="5" t="n"/>
-      <c r="AL313" s="5" t="n"/>
-      <c r="AM313" s="5" t="n"/>
+      <c r="AG313" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+        </is>
+      </c>
+      <c r="AH313" s="5" t="inlineStr">
+        <is>
+          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+        </is>
+      </c>
+      <c r="AI313" s="5" t="inlineStr">
+        <is>
+          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+        </is>
+      </c>
+      <c r="AJ313" s="5" t="inlineStr">
+        <is>
+          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+        </is>
+      </c>
+      <c r="AK313" s="5" t="inlineStr">
+        <is>
+          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+        </is>
+      </c>
+      <c r="AL313" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+        </is>
+      </c>
+      <c r="AM313" s="5" t="inlineStr">
+        <is>
+          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+        </is>
+      </c>
       <c r="AN313" s="5" t="n"/>
-      <c r="AO313" s="5" t="n"/>
+      <c r="AO313" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -15337,20 +15337,56 @@
           <t>reg-csa-1c-hood-3</t>
         </is>
       </c>
-      <c r="AB136" s="5" t="n"/>
+      <c r="AB136" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC136" s="5" t="n"/>
       <c r="AD136" s="5" t="n"/>
       <c r="AE136" s="5" t="n"/>
       <c r="AF136" s="5" t="n"/>
-      <c r="AG136" s="5" t="n"/>
-      <c r="AH136" s="5" t="n"/>
-      <c r="AI136" s="5" t="n"/>
-      <c r="AJ136" s="5" t="n"/>
-      <c r="AK136" s="5" t="n"/>
-      <c r="AL136" s="5" t="n"/>
-      <c r="AM136" s="5" t="n"/>
+      <c r="AG136" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-hood-3-anderson.md; White's report is a consolidation (one hop above regimental layer, carried)</t>
+        </is>
+      </c>
+      <c r="AH136" s="5" t="inlineStr">
+        <is>
+          <t>G.T. Anderson's bde (7/8/9/11/59 GA); ANDERSON W in the second advance (marker (3529,2729) = check point) -&gt; Luffman register succession; report filed by Col. W. W. White (7th GA) - the report chain attests the churn</t>
+        </is>
+      </c>
+      <c r="AI136" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present about 1800'; 7th GA detached to the cavalry flank pre-fight (named EC2 subtraction, ~4/5 engaged)</t>
+        </is>
+      </c>
+      <c r="AJ136" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] formed ~16:00 division left; [E drawn j2-03] 'ANDERSON'S GA' advancing (3269,2902) + Rose Woods red line (3549,2849); third-advance end = woodland to Plum Run border; July 3 = the Emmitsburg Rd cavalry flank (NOT a Wheatfield hold)</t>
+        </is>
+      </c>
+      <c r="AK136" s="5" t="inlineStr">
+        <is>
+          <t>[D structure] THREE ADVANCES stated (stone fence taken / outflanked-retired / Anderson w / third 'half an hour in the ravine' - wave-4 duration input)</t>
+        </is>
+      </c>
+      <c r="AL136" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-1 stone-fence fight vs de Trobriand (both-sided); wave-3 receiving (Kelly tablet NAMES this brigade); July 3 Farnsworth-front actions</t>
+        </is>
+      </c>
+      <c r="AM136" s="5" t="inlineStr">
+        <is>
+          <t>tablet total = return total EXACT 671 (105/512/[54 pooled]); White's composition agrees at class; July2/3 split unstated (flagged)</t>
+        </is>
+      </c>
       <c r="AN136" s="5" t="n"/>
-      <c r="AO136" s="5" t="n"/>
+      <c r="AO136" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -15621,20 +15657,56 @@
           <t>reg-csa-1c-hood-4</t>
         </is>
       </c>
-      <c r="AB138" s="5" t="n"/>
+      <c r="AB138" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; July 2-3 holder)</t>
+        </is>
+      </c>
       <c r="AC138" s="5" t="n"/>
       <c r="AD138" s="5" t="n"/>
       <c r="AE138" s="5" t="n"/>
       <c r="AF138" s="5" t="n"/>
-      <c r="AG138" s="5" t="n"/>
-      <c r="AH138" s="5" t="n"/>
-      <c r="AI138" s="5" t="n"/>
-      <c r="AJ138" s="5" t="n"/>
-      <c r="AK138" s="5" t="n"/>
-      <c r="AL138" s="5" t="n"/>
-      <c r="AM138" s="5" t="n"/>
+      <c r="AG138" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-hood-4-benning.md; third claimant in the guns cross-credit - ED-56 convergent-capture candidate; count/type agreement with Smith across the lines</t>
+        </is>
+      </c>
+      <c r="AH138" s="5" t="inlineStr">
+        <is>
+          <t>Benning's bde (2/15/17/20 GA); Benning unwounded; Cols. Jones (20GA) k + Harris (2GA) k in the Den fight</t>
+        </is>
+      </c>
+      <c r="AI138" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present about 1500' (compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ138" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] formed ~400yd behind the first line (2785,2269); [A vs CA-J2A-5] Devil's Den taken ~17:30 AND HELD to July 3 late day (advance marker (3697,2461)); [E drawn j2-04+j2-05] red line holding the Den across two sheets - drawn-state continuity</t>
+        </is>
+      </c>
+      <c r="AK138" s="5" t="inlineStr">
+        <is>
+          <t>[D first-person] THE WRONG-BRIGADE FOLLOW ('In truth, it was Robertson's') - the ladder's best-documented formation error; [B] 600-800yd ascent under fire 15-25 min; [D] the 15th GA mistaken-orders withdrawal disaster July 3</t>
+        </is>
+      </c>
+      <c r="AL138" s="5" t="inlineStr">
+        <is>
+          <t>[D] Den fight intermixed with 1st TX; gun-shelf enumeration matches Union battery dossiers gun-for-gun; overnight+July 3 hold under fire; McLaws-withdrawn-from-my-left exposure note</t>
+        </is>
+      </c>
+      <c r="AM138" s="5" t="inlineStr">
+        <is>
+          <t>three readings carried: report floor 'not less than 400', return 76/299/[122 pooled]=497 (adopted basis), tablet 509; loss SPREAD over the 2-day hold (not a single spike); 15th GA July 3 component unquantified (flagged)</t>
+        </is>
+      </c>
       <c r="AN138" s="5" t="n"/>
-      <c r="AO138" s="5" t="n"/>
+      <c r="AO138" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -18317,20 +18389,56 @@
           <t>reg-csa-1c-mcl-2</t>
         </is>
       </c>
-      <c r="AB158" s="5" t="n"/>
+      <c r="AB158" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC158" s="5" t="n"/>
       <c r="AD158" s="5" t="n"/>
       <c r="AE158" s="5" t="n"/>
       <c r="AF158" s="5" t="n"/>
-      <c r="AG158" s="5" t="n"/>
-      <c r="AH158" s="5" t="n"/>
-      <c r="AI158" s="5" t="n"/>
-      <c r="AJ158" s="5" t="n"/>
-      <c r="AK158" s="5" t="n"/>
-      <c r="AL158" s="5" t="n"/>
-      <c r="AM158" s="5" t="n"/>
+      <c r="AG158" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-mcl-2-semmes.md</t>
+        </is>
+      </c>
+      <c r="AH158" s="5" t="inlineStr">
+        <is>
+          <t>Semmes's bde (10/50/51/53 GA); SEMMES MW 'in the ravine near the Loop' (tablet verbatim; advance marker (3357,2864) = check point), d. July 10 -&gt; Bryan. NO OR REPORT at any echelon (verified-negative - the Barksdale class)</t>
+        </is>
+      </c>
+      <c r="AI158" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present about 1200' (compilation, hop flagged); no primary</t>
+        </is>
+      </c>
+      <c r="AJ158" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-7] Kershaw's support slot (Alexander ladder attack 3); [C tablet] Rose Hill/ravine/Loop fight; wave-4 sweep to Plum Run; July 3 the woodland S of Wheatfield to 13:00 (Benning's exposed-left note cross-bears the extraction)</t>
+        </is>
+      </c>
+      <c r="AK158" s="5" t="inlineStr">
+        <is>
+          <t>[D trigger] committal = Kershaw's 'Semmes brought up' (supported unit's primary); [B] 400m ravine advance</t>
+        </is>
+      </c>
+      <c r="AL158" s="5" t="inlineStr">
+        <is>
+          <t>[D] ravine fight vs Kelly/Zook/Brooke prongs (both-sided); July 3 woodland occupancy (ED-44 adjacent)</t>
+        </is>
+      </c>
+      <c r="AM158" s="5" t="inlineStr">
+        <is>
+          <t>tablet total = return total EXACT 430 (55/284/[91 pooled]); the SECOND tablet-corroborates-pooled-scope case after Barksdale; split: waves 2-4 ~all</t>
+        </is>
+      </c>
       <c r="AN158" s="5" t="n"/>
-      <c r="AO158" s="5" t="n"/>
+      <c r="AO158" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (thin - no-report class)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -18948,7 +19056,7 @@
       <c r="AF163" s="5" t="n"/>
       <c r="AG163" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-and-1-wilcox.md; CA-J3A-10 executor</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-1-wilcox.md; CA-J3A-10 executor; July 2 arc extended backward pass 6 (CA-J2A-10 executor leg)</t>
         </is>
       </c>
       <c r="AH163" s="5" t="inlineStr">
@@ -18963,12 +19071,12 @@
       </c>
       <c r="AJ163" s="5" t="inlineStr">
         <is>
-          <t>[D] before sunrise: line parallel to Emmitsburg pike ~200 yd W, Alexander's guns in front; j3-01 label ~(3100,4400)+-120 (04:00-08:00 window = exact bracket); farthest advance = ravine below McGilvery crest (build displacement understates - flag)</t>
+          <t>[D] before sunrise: line parallel to Emmitsburg pike ~200 yd W, Alexander's guns in front; j3-01 label ~(3100,4400)+-120 (04:00-08:00 window = exact bracket); farthest advance = ravine below McGilvery crest (build displacement understates - flag); PASS-6 BACKWARD-EXTENSION: [A vs CA-J2A-10] July 2 evening advance (pike crossing, two lines broken, 2+6 guns claimed, the ravine climb); [E drawn j2-04] WILCOX ALA (4112,4368) opposite '1 Minn' (4230,4282) - the sheet draws BOTH sides of the charge moment</t>
         </is>
       </c>
       <c r="AK163" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-6 +20-30 min] the DELAYED LAUNCH (three staff officers in succession; Alexander concurs; Lang sequences after repulse - one envelope); halt at ravine awaiting artillery that had no ammunition; withdrew on own judgment</t>
+          <t>[A vs CA-J3A-6 +20-30 min] the DELAYED LAUNCH (three staff officers in succession; Alexander concurs; Lang sequences after repulse - one envelope); halt at ravine awaiting artillery that had no ammunition; withdrew on own judgment; PASS-6: [D duration] the thirty-minute unsupported stand + withdrawal; the third-line-at-the-double-quick = the 1st MN charge from the receiving side (both-sided with or-27-1-coates-1mn)</t>
         </is>
       </c>
       <c r="AL163" s="5" t="inlineStr">
@@ -19097,20 +19205,56 @@
           <t>reg-csa-1c-mcl-4</t>
         </is>
       </c>
-      <c r="AB164" s="5" t="n"/>
+      <c r="AB164" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC164" s="5" t="n"/>
       <c r="AD164" s="5" t="n"/>
       <c r="AE164" s="5" t="n"/>
       <c r="AF164" s="5" t="n"/>
-      <c r="AG164" s="5" t="n"/>
-      <c r="AH164" s="5" t="n"/>
-      <c r="AI164" s="5" t="n"/>
-      <c r="AJ164" s="5" t="n"/>
-      <c r="AK164" s="5" t="n"/>
-      <c r="AL164" s="5" t="n"/>
-      <c r="AM164" s="5" t="n"/>
+      <c r="AG164" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-mcl-4-wofford.md; tablet clock 'about 6 P.M.' is a NEAR-ZERO skew exemplar - the wing's tablet skew is heterogeneous (ED-58 discussion)</t>
+        </is>
+      </c>
+      <c r="AH164" s="5" t="inlineStr">
+        <is>
+          <t>Wofford's bde (16/18/24 GA, Cobb's + Phillips Legions); Wofford unwounded; NO OR REPORT (verified-negative)</t>
+        </is>
+      </c>
+      <c r="AI164" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present about 1350' (compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ164" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] formed 100yd W of tablet (2652,3802); the Wheatfield-Rd sweep axis; farthest = LRT foot; [A vs CA-J2A-11] FELL BACK AT SUNSET (19:29 astronomical pin - the ladder's only document-grade end clock); [E drawn j2-05] red bars w/ withdrawal arrows on the Wheatfield's W ravine slope, '...FORD GA' label class (legibility partial, flagged) opposite McCandless (4011,3016)/Nevin (4290,3119)</t>
+        </is>
+      </c>
+      <c r="AK164" s="5" t="inlineStr">
+        <is>
+          <t>[B] ~1200m road-axis sweep 15-20 min; trigger both-sided (Kershaw's 'Wofford coming in in splendid style' + Fraser's flanked-right + Alexander's attack-4 ladder)</t>
+        </is>
+      </c>
+      <c r="AL164" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-4 flank sweep to the mountain's foot; the Crawford/McCandless collision; July 3 orchard-ridge artillery support</t>
+        </is>
+      </c>
+      <c r="AM164" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: tablet itemizes 36/207/112=355 vs return 30/192/[112 pooled]=334 - missing agrees EXACTLY, k/w disagree; no own report to resolve; EC6 carries '334-355, missing 112 firm', NO promotion</t>
+        </is>
+      </c>
       <c r="AN164" s="5" t="n"/>
-      <c r="AO164" s="5" t="n"/>
+      <c r="AO164" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc (EC6 conflicted)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -20949,20 +21093,56 @@
           <t>reg-us-iii-b3</t>
         </is>
       </c>
-      <c r="AB183" s="5" t="n"/>
+      <c r="AB183" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (not-yet-cast)</t>
+        </is>
+      </c>
       <c r="AC183" s="5" t="n"/>
       <c r="AD183" s="5" t="n"/>
       <c r="AE183" s="5" t="n"/>
       <c r="AF183" s="5" t="n"/>
-      <c r="AG183" s="5" t="n"/>
-      <c r="AH183" s="5" t="n"/>
-      <c r="AI183" s="5" t="n"/>
-      <c r="AJ183" s="5" t="n"/>
-      <c r="AK183" s="5" t="n"/>
-      <c r="AL183" s="5" t="n"/>
-      <c r="AM183" s="5" t="n"/>
+      <c r="AG183" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-smith.md; THE GUNS CROSS-CREDIT closed both-sided - exactly 3 Parrotts lost, CSA count/type agrees; ED-56 convergent-capture candidate</t>
+        </is>
+      </c>
+      <c r="AH183" s="5" t="inlineStr">
+        <is>
+          <t>Smith's 4th NY Independent (6x 10-pdr Parrott); Smith unwounded; 2 k named</t>
+        </is>
+      </c>
+      <c r="AI183" s="5" t="inlineStr">
+        <is>
+          <t>six guns, two elements (4 forward + 2 rear); personnel compilation-tier</t>
+        </is>
+      </c>
+      <c r="AJ183" s="5" t="inlineStr">
+        <is>
+          <t>[C report] forward guns on the Devil's Den hill (mon (3787,2551)); rear section 150yd back in Plum Run valley (mon (4016,2802)); [E drawn j2-03] 'Smith' drawn as a SEPARATE rear element (4016,2946) - two-element drawn state</t>
+        </is>
+      </c>
+      <c r="AK183" s="5" t="inlineStr">
+        <is>
+          <t>[D] forward guns attested-static to loss (kept firing rather than signal retreat); captain's shift to the rear section at the fall</t>
+        </is>
+      </c>
+      <c r="AL183" s="5" t="inlineStr">
+        <is>
+          <t>[C +90] duel from stated 14:30; munition ladder case-&gt;shell-&gt;canister (range-attesting); 140 ROUNDS EXPENDED (expenditure ledger, ED-42); oblique gully fire</t>
+        </is>
+      </c>
+      <c r="AM183" s="5" t="inlineStr">
+        <is>
+          <t>return 13 adopted (2/10/1) vs report 12 named (ED-52); concentrated in the forward fight</t>
+        </is>
+      </c>
       <c r="AN183" s="5" t="n"/>
-      <c r="AO183" s="5" t="n"/>
+      <c r="AO183" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -32301,20 +32481,56 @@
           <t>reg-us-iii-1-2</t>
         </is>
       </c>
-      <c r="AB279" s="5" t="n"/>
+      <c r="AB279" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 defender)</t>
+        </is>
+      </c>
       <c r="AC279" s="5" t="n"/>
       <c r="AD279" s="5" t="n"/>
       <c r="AE279" s="5" t="n"/>
       <c r="AF279" s="5" t="n"/>
-      <c r="AG279" s="5" t="n"/>
-      <c r="AH279" s="5" t="n"/>
-      <c r="AI279" s="5" t="n"/>
-      <c r="AJ279" s="5" t="n"/>
-      <c r="AK279" s="5" t="n"/>
-      <c r="AL279" s="5" t="n"/>
-      <c r="AM279" s="5" t="n"/>
+      <c r="AG279" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
+        </is>
+      </c>
+      <c r="AH279" s="5" t="inlineStr">
+        <is>
+          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
+        </is>
+      </c>
+      <c r="AI279" s="5" t="inlineStr">
+        <is>
+          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
+        </is>
+      </c>
+      <c r="AJ279" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
+        </is>
+      </c>
+      <c r="AK279" s="5" t="inlineStr">
+        <is>
+          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
+        </is>
+      </c>
+      <c r="AL279" s="5" t="inlineStr">
+        <is>
+          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
+        </is>
+      </c>
+      <c r="AM279" s="5" t="inlineStr">
+        <is>
+          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row column-noise flagged (144-class); ~all July 2</t>
+        </is>
+      </c>
       <c r="AN279" s="5" t="n"/>
-      <c r="AO279" s="5" t="n"/>
+      <c r="AO279" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -32709,20 +32925,56 @@
           <t>reg-us-ii-1-4</t>
         </is>
       </c>
-      <c r="AB282" s="5" t="n"/>
+      <c r="AB282" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC282" s="5" t="n"/>
       <c r="AD282" s="5" t="n"/>
       <c r="AE282" s="5" t="n"/>
       <c r="AF282" s="5" t="n"/>
-      <c r="AG282" s="5" t="n"/>
-      <c r="AH282" s="5" t="n"/>
-      <c r="AI282" s="5" t="n"/>
-      <c r="AJ282" s="5" t="n"/>
-      <c r="AK282" s="5" t="n"/>
-      <c r="AL282" s="5" t="n"/>
-      <c r="AM282" s="5" t="n"/>
+      <c r="AG282" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+        </is>
+      </c>
+      <c r="AH282" s="5" t="inlineStr">
+        <is>
+          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+        </is>
+      </c>
+      <c r="AI282" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+        </is>
+      </c>
+      <c r="AJ282" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+        </is>
+      </c>
+      <c r="AK282" s="5" t="inlineStr">
+        <is>
+          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+        </is>
+      </c>
+      <c r="AL282" s="5" t="inlineStr">
+        <is>
+          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+        </is>
+      </c>
+      <c r="AM282" s="5" t="inlineStr">
+        <is>
+          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+        </is>
+      </c>
       <c r="AN282" s="5" t="n"/>
-      <c r="AO282" s="5" t="n"/>
+      <c r="AO282" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -34517,20 +34769,56 @@
           <t>reg-us-ii-1-3</t>
         </is>
       </c>
-      <c r="AB296" s="5" t="n"/>
+      <c r="AB296" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC296" s="5" t="n"/>
       <c r="AD296" s="5" t="n"/>
       <c r="AE296" s="5" t="n"/>
       <c r="AF296" s="5" t="n"/>
-      <c r="AG296" s="5" t="n"/>
-      <c r="AH296" s="5" t="n"/>
-      <c r="AI296" s="5" t="n"/>
-      <c r="AJ296" s="5" t="n"/>
-      <c r="AK296" s="5" t="n"/>
-      <c r="AL296" s="5" t="n"/>
-      <c r="AM296" s="5" t="n"/>
+      <c r="AG296" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
+        </is>
+      </c>
+      <c r="AH296" s="5" t="inlineStr">
+        <is>
+          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
+        </is>
+      </c>
+      <c r="AI296" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~975 compilation hop-flagged</t>
+        </is>
+      </c>
+      <c r="AJ296" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
+        </is>
+      </c>
+      <c r="AK296" s="5" t="inlineStr">
+        <is>
+          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
+        </is>
+      </c>
+      <c r="AL296" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-3 crest fight 18:15-18:45</t>
+        </is>
+      </c>
+      <c r="AM296" s="5" t="inlineStr">
+        <is>
+          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
+        </is>
+      </c>
       <c r="AN296" s="5" t="n"/>
-      <c r="AO296" s="5" t="n"/>
+      <c r="AO296" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -35184,7 +35472,7 @@
       <c r="AF301" s="5" t="n"/>
       <c r="AG301" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
         </is>
       </c>
       <c r="AH301" s="5" t="inlineStr">
@@ -35204,7 +35492,7 @@
       </c>
       <c r="AK301" s="5" t="inlineStr">
         <is>
-          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]</t>
+          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
         </is>
       </c>
       <c r="AL301" s="5" t="inlineStr">
@@ -35457,20 +35745,56 @@
           <t>reg-us-ii-1-2</t>
         </is>
       </c>
-      <c r="AB303" s="5" t="n"/>
+      <c r="AB303" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC303" s="5" t="n"/>
       <c r="AD303" s="5" t="n"/>
       <c r="AE303" s="5" t="n"/>
       <c r="AF303" s="5" t="n"/>
-      <c r="AG303" s="5" t="n"/>
-      <c r="AH303" s="5" t="n"/>
-      <c r="AI303" s="5" t="n"/>
-      <c r="AJ303" s="5" t="n"/>
-      <c r="AK303" s="5" t="n"/>
-      <c r="AL303" s="5" t="n"/>
-      <c r="AM303" s="5" t="n"/>
+      <c r="AG303" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
+        </is>
+      </c>
+      <c r="AH303" s="5" t="inlineStr">
+        <is>
+          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
+        </is>
+      </c>
+      <c r="AI303" s="5" t="inlineStr">
+        <is>
+          <t>530 into action PRIMARY (Kelly)</t>
+        </is>
+      </c>
+      <c r="AJ303" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
+        </is>
+      </c>
+      <c r="AK303" s="5" t="inlineStr">
+        <is>
+          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
+        </is>
+      </c>
+      <c r="AL303" s="5" t="inlineStr">
+        <is>
+          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
+        </is>
+      </c>
+      <c r="AM303" s="5" t="inlineStr">
+        <is>
+          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
+        </is>
+      </c>
       <c r="AN303" s="5" t="n"/>
-      <c r="AO303" s="5" t="n"/>
+      <c r="AO303" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -36201,20 +36525,56 @@
           <t>reg-us-ii-1-1</t>
         </is>
       </c>
-      <c r="AB309" s="5" t="n"/>
+      <c r="AB309" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC309" s="5" t="n"/>
       <c r="AD309" s="5" t="n"/>
       <c r="AE309" s="5" t="n"/>
       <c r="AF309" s="5" t="n"/>
-      <c r="AG309" s="5" t="n"/>
-      <c r="AH309" s="5" t="n"/>
-      <c r="AI309" s="5" t="n"/>
-      <c r="AJ309" s="5" t="n"/>
-      <c r="AK309" s="5" t="n"/>
-      <c r="AL309" s="5" t="n"/>
-      <c r="AM309" s="5" t="n"/>
+      <c r="AG309" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+        </is>
+      </c>
+      <c r="AH309" s="5" t="inlineStr">
+        <is>
+          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+        </is>
+      </c>
+      <c r="AI309" s="5" t="inlineStr">
+        <is>
+          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+        </is>
+      </c>
+      <c r="AJ309" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+        </is>
+      </c>
+      <c r="AK309" s="5" t="inlineStr">
+        <is>
+          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+        </is>
+      </c>
+      <c r="AL309" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+        </is>
+      </c>
+      <c r="AM309" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+        </is>
+      </c>
       <c r="AN309" s="5" t="n"/>
-      <c r="AO309" s="5" t="n"/>
+      <c r="AO309" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -37549,20 +37909,56 @@
           <t>reg-us-v-1-2</t>
         </is>
       </c>
-      <c r="AB319" s="5" t="n"/>
+      <c r="AB319" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 twice-committed)</t>
+        </is>
+      </c>
       <c r="AC319" s="5" t="n"/>
       <c r="AD319" s="5" t="n"/>
       <c r="AE319" s="5" t="n"/>
       <c r="AF319" s="5" t="n"/>
-      <c r="AG319" s="5" t="n"/>
-      <c r="AH319" s="5" t="n"/>
-      <c r="AI319" s="5" t="n"/>
-      <c r="AJ319" s="5" t="n"/>
-      <c r="AK319" s="5" t="n"/>
-      <c r="AL319" s="5" t="n"/>
-      <c r="AM319" s="5" t="n"/>
+      <c r="AG319" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
+        </is>
+      </c>
+      <c r="AH319" s="5" t="inlineStr">
+        <is>
+          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
+        </is>
+      </c>
+      <c r="AI319" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
+        </is>
+      </c>
+      <c r="AJ319" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
+        </is>
+      </c>
+      <c r="AK319" s="5" t="inlineStr">
+        <is>
+          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
+        </is>
+      </c>
+      <c r="AL319" s="5" t="inlineStr">
+        <is>
+          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
+        </is>
+      </c>
+      <c r="AM319" s="5" t="inlineStr">
+        <is>
+          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
+        </is>
+      </c>
       <c r="AN319" s="5" t="n"/>
-      <c r="AO319" s="5" t="n"/>
+      <c r="AO319" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -37673,20 +38069,56 @@
           <t>reg-us-v-1-1</t>
         </is>
       </c>
-      <c r="AB320" s="5" t="n"/>
+      <c r="AB320" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC320" s="5" t="n"/>
       <c r="AD320" s="5" t="n"/>
       <c r="AE320" s="5" t="n"/>
       <c r="AF320" s="5" t="n"/>
-      <c r="AG320" s="5" t="n"/>
-      <c r="AH320" s="5" t="n"/>
-      <c r="AI320" s="5" t="n"/>
-      <c r="AJ320" s="5" t="n"/>
-      <c r="AK320" s="5" t="n"/>
-      <c r="AL320" s="5" t="n"/>
-      <c r="AM320" s="5" t="n"/>
+      <c r="AG320" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+        </is>
+      </c>
+      <c r="AH320" s="5" t="inlineStr">
+        <is>
+          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+        </is>
+      </c>
+      <c r="AI320" s="5" t="inlineStr">
+        <is>
+          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+        </is>
+      </c>
+      <c r="AJ320" s="5" t="inlineStr">
+        <is>
+          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+        </is>
+      </c>
+      <c r="AK320" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+        </is>
+      </c>
+      <c r="AL320" s="5" t="inlineStr">
+        <is>
+          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+        </is>
+      </c>
+      <c r="AM320" s="5" t="inlineStr">
+        <is>
+          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+        </is>
+      </c>
       <c r="AN320" s="5" t="n"/>
-      <c r="AO320" s="5" t="n"/>
+      <c r="AO320" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -37921,20 +38353,56 @@
           <t>reg-us-iii-1-3</t>
         </is>
       </c>
-      <c r="AB322" s="5" t="n"/>
+      <c r="AB322" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC322" s="5" t="n"/>
       <c r="AD322" s="5" t="n"/>
       <c r="AE322" s="5" t="n"/>
       <c r="AF322" s="5" t="n"/>
-      <c r="AG322" s="5" t="n"/>
-      <c r="AH322" s="5" t="n"/>
-      <c r="AI322" s="5" t="n"/>
-      <c r="AJ322" s="5" t="n"/>
-      <c r="AK322" s="5" t="n"/>
-      <c r="AL322" s="5" t="n"/>
-      <c r="AM322" s="5" t="n"/>
+      <c r="AG322" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
+        </is>
+      </c>
+      <c r="AH322" s="5" t="inlineStr">
+        <is>
+          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
+        </is>
+      </c>
+      <c r="AI322" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
+        </is>
+      </c>
+      <c r="AJ322" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
+        </is>
+      </c>
+      <c r="AK322" s="5" t="inlineStr">
+        <is>
+          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
+        </is>
+      </c>
+      <c r="AL322" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
+        </is>
+      </c>
+      <c r="AM322" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
+        </is>
+      </c>
       <c r="AN322" s="5" t="n"/>
-      <c r="AO322" s="5" t="n"/>
+      <c r="AO322" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$325</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO324"/>
+  <dimension ref="A1:AO325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17016,7 +17016,7 @@
       <c r="AF148" s="5" t="n"/>
       <c r="AG148" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-and-4-lang.md</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-4-lang.md (July 2 arc extended backward, pass 7)</t>
         </is>
       </c>
       <c r="AH148" s="5" t="inlineStr">
@@ -17031,17 +17031,17 @@
       </c>
       <c r="AJ148" s="5" t="inlineStr">
         <is>
-          <t>[C/D ~07:00] up with Wilcox's left to foot of gun hill, skirmishers one crest fwd; j3-01 label ~(3230,4820)+-120; reform on old line, night withdrawal to woods</t>
+          <t>[Pass 7 backward-extension] July 2: WCA tablet (2917.2,4693.8) + the ADVANCED Emmitsburg-Rd tablet (3740.5,4421.3) (1,100-ft Codori distance check EXACT); j2-04 'PERRY FLA.' (4160,4502) vs 19th-Maine-class blue (4215,4475). [C/D ~07:00] up with Wilcox's left to foot of gun hill, skirmishers one crest fwd; j3-01 label ~(3230,4820)+-120; reform on old line, night withdrawal to woods</t>
         </is>
       </c>
       <c r="AK148" s="5" t="inlineStr">
         <is>
-          <t>[D] standing conform-to-Wilcox order ('I would receive no further orders'); advanced after Pickett's troops retired; left flanked in the woods, retreat order inaudible in the din; 2FL colors + pocket captured (16th VT object, veazey cross)</t>
+          <t>[Pass 7] July 2 advance 'at 6 p.m.' stated (+45..+60 ED-58 class - OPPOSITE-direction skew from its July 3 -53 clocks, the audit's sharpest single-source heterogeneity); double-quick past the guns ('four or five pieces' - the modest counterpart of Wright's twenty); withdrawal on the Wilcox-forced-back report (trigger). [D] standing conform-to-Wilcox order ('I would receive no further orders'); advanced after Pickett's troops retired; left flanked in the woods, retreat order inaudible in the din; 2FL colors + pocket captured (16th VT object, veazey cross)</t>
         </is>
       </c>
       <c r="AL148" s="5" t="inlineStr">
         <is>
-          <t>[C -53] bombardment 'nearly 2 p.m. ... till nearly 4 p.m.' (late-stated pole, joins Longstreet/Smyth cluster); no formed fire window Jul 3 (movement and reception only)</t>
+          <t>[C -53] bombardment 'nearly 2 p.m. ... till nearly 4 p.m.' (late-stated pole, joins Longstreet/Smyth cluster); no formed fire window Jul 3 (movement and reception only); [Pass 7] the 8th FLORIDA COLORS BOTH-SIDED (advanced tablet = Brewster/Hogan captor record) - colors lost BOTH days, each with a Union captor record</t>
         </is>
       </c>
       <c r="AM148" s="5" t="inlineStr">
@@ -19365,20 +19365,56 @@
           <t>reg-csa-3c-and-3</t>
         </is>
       </c>
-      <c r="AB165" s="5" t="n"/>
+      <c r="AB165" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; THE conflict-record unit)</t>
+        </is>
+      </c>
       <c r="AC165" s="5" t="n"/>
       <c r="AD165" s="5" t="n"/>
       <c r="AE165" s="5" t="n"/>
       <c r="AF165" s="5" t="n"/>
-      <c r="AG165" s="5" t="n"/>
-      <c r="AH165" s="5" t="n"/>
-      <c r="AI165" s="5" t="n"/>
-      <c r="AJ165" s="5" t="n"/>
-      <c r="AK165" s="5" t="n"/>
-      <c r="AL165" s="5" t="n"/>
-      <c r="AM165" s="5" t="n"/>
+      <c r="AG165" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-3-wright.md; proposes ED-60 (the high-water ruling); CA-J2A-10's 'notoriously self-serving' flag executor-substantiated</t>
+        </is>
+      </c>
+      <c r="AH165" s="5" t="inlineStr">
+        <is>
+          <t>Wright's bde (3/22/48 GA, 2 GA Bn); Wright resumed command 7 a.m. July 2; pins: Col. Wasden (22 GA) k near the turnpike, Col. Gibson (48 GA) w; 48th GA colors lost (shot down seven times)</t>
+        </is>
+      </c>
+      <c r="AI165" s="5" t="inlineStr">
+        <is>
+          <t>tablet 'Present 1,450' vs B&amp;M 1,413 (both hops, carried un-averaged); no primary</t>
+        </is>
+      </c>
+      <c r="AJ165" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] WCA formation line (3119.9,5004.0); [E drawn j2-04] the attack IN PROGRESS - regt numbers strung ridge-to-road, advanced label (4289,4852), red bars ON the 15th MA/82nd NY road position and ON Brown's battery ground (4314,4724), Union ridge hatching UNBROKEN east; ADOPTED farthest advance = the Cemetery Ridge marker (4330.6,4746.9) - 28 m agreement with the drawn state (the crest claims are carried as claims, not geometry)</t>
+        </is>
+      </c>
+      <c r="AK165" s="5" t="inlineStr">
+        <is>
+          <t>[D] the echelon trigger verbatim ('as soon as the brigade on its immediate right commenced'); [A vs CA-J2A-10; stated 'about 5 p.m.' profiled +100] the mile advance -&gt; road gun line -&gt; west slope [B 22-30 min]; [D] THE CUT-OUT (both supports failed; abandoned the captured guns, faced about) [B 15-20 min]; July 3: the 500-600 yd Pickett-retreat cover move + Lee's personal order rightward</t>
+        </is>
+      </c>
+      <c r="AL165" s="5" t="inlineStr">
+        <is>
+          <t>[D both-sided] the Codori-front overrun (15th MA/82nd NY; Ward-KIA marker 47 m from the drawn bar); THE GUN-COUNT CONFLICT 'over twenty pieces' carried vs receiving-side temporary losses (Brown, Weir); the 48th GA enfilade; July 3 present-but-covering (ED-44 adjacent)</t>
+        </is>
+      </c>
+      <c r="AM165" s="5" t="inlineStr">
+        <is>
+          <t>THREE READINGS CARRIED: report 688 / return 668 (40/295/333, full columns) / tablet 873 (146/394/333) - missing 333 AGREES return=tablet, k/w composition conflicts; return adopted (ED-49/52 posture), no averaging; episode: the evening hour dominant, cut-out the peak (333 missing its trace)</t>
+        </is>
+      </c>
       <c r="AN165" s="5" t="n"/>
-      <c r="AO165" s="5" t="n"/>
+      <c r="AO165" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -31031,12 +31067,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-hq</t>
+          <t>reg-us-iii-2-hq</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>3rd Division, I Corps headquarters (division command)</t>
+          <t>2nd Division, III Corps headquarters (division command)</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -31077,7 +31113,7 @@
       </c>
       <c r="V269" s="2" t="inlineStr">
         <is>
-          <t>3rd Division</t>
+          <t>2nd Division</t>
         </is>
       </c>
       <c r="W269" s="2" t="inlineStr">
@@ -31098,12 +31134,12 @@
       </c>
       <c r="AA269" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-hq</t>
+          <t>reg-us-iii-2-hq</t>
         </is>
       </c>
       <c r="AB269" s="5" t="inlineStr">
         <is>
-          <t>unauthored (command record)</t>
+          <t>command record (not-yet-cast; register row added pass 7)</t>
         </is>
       </c>
       <c r="AC269" s="5" t="n"/>
@@ -31112,55 +31148,55 @@
       <c r="AF269" s="5" t="n"/>
       <c r="AG269" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-hq-doubleday.md; register row added pass 5</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-hq-humphreys.md; division-grain clocks are the ED-58 COUNTER-class (Humphreys ~0, Carr 0 medium, Birney +30 mild)</t>
         </is>
       </c>
       <c r="AH269" s="5" t="inlineStr">
         <is>
-          <t>Maj. Gen. Abner Doubleday (I Corps command July 1 after Reynolds; superseded by Newton July 2; division command July 2-3)</t>
+          <t>Humphreys 2nd Div III Corps; the command seam: Sickles mw 'At 6 o'clock' (Birney) -&gt; Birney corps -&gt; Hancock ~19:30; Sickles marker (3789.9,3715.2) OSM/SS 2.1 m</t>
         </is>
       </c>
       <c r="AI269" s="5" t="inlineStr">
         <is>
-          <t>not stated for July 3 (open); division regiment grain in or-27-1-union-return (2,103 battle aggregate)</t>
+          <t>PRIMARY ~5,000 into action (his own report p. 534)</t>
         </is>
       </c>
       <c r="AJ269" s="5" t="inlineStr">
         <is>
-          <t>[E] second line behind the left-center; his own July 3 station OPEN (no primary pin)</t>
+          <t>[D] midday line; [C ~0] the Emmitsburg-road line ~16:00; tablet (3657.7,4241.9) (793 m duplicate node FLAGGED); [E drawn j2-03/j2-04] division label at the road then REDRAWN with NE withdrawal arrows + rallied on the ridge (4488,4469) - both ends in one window</t>
         </is>
       </c>
       <c r="AK269" s="5" t="inlineStr">
         <is>
-          <t>n/a (command entry)</t>
+          <t>[C ~0] 'about 4 p.m.' advance (= Carr's 4.08); [D] the Birney oblique order under fire; [B 12-20 min] THE FIGHTING WITHDRAWAL 'slowly, continuing the contest' ~550 m road-&gt;crest; the dusk counterattack</t>
         </is>
       </c>
       <c r="AL269" s="5" t="inlineStr">
         <is>
-          <t>[C report -53] late litigious report (the Meade feud shapes it); late-stated clock cluster member</t>
+          <t>[D] reinforcement dispatching under pressure (Burns's 4th Excelsior to Graham - both order ends primary; Christiancy to Hancock); battery direction (Seeley/Turnbull, losses itemized at division grain)</t>
         </is>
       </c>
       <c r="AM269" s="5" t="inlineStr">
         <is>
-          <t>division 2,103 (return, p. 174); apportionment at brigade rows</t>
+          <t>division roll-up: return 2,092 vs stated 2,088 (ED-52 cleanest exercise); his own missing-scope caveat first-class; Burling detachment 430 k+w stated</t>
         </is>
       </c>
       <c r="AN269" s="5" t="n"/>
       <c r="AO269" s="5" t="inlineStr">
         <is>
-          <t>T2 (command record)</t>
+          <t>T3 (command record)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-hq</t>
+          <t>reg-us-i-3-hq</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>3rd Division, II Corps headquarters (division command)</t>
+          <t>3rd Division, I Corps headquarters (division command)</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -31222,7 +31258,7 @@
       </c>
       <c r="AA270" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-hq</t>
+          <t>reg-us-i-3-hq</t>
         </is>
       </c>
       <c r="AB270" s="5" t="inlineStr">
@@ -31236,22 +31272,22 @@
       <c r="AF270" s="5" t="n"/>
       <c r="AG270" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-hq-hays.md; register row added pass 5</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-hq-doubleday.md; register row added pass 5</t>
         </is>
       </c>
       <c r="AH270" s="5" t="inlineStr">
         <is>
-          <t>Brig. Gen. Alexander Hays; division command over the Pettigrew-front wall</t>
+          <t>Maj. Gen. Abner Doubleday (I Corps command July 1 after Reynolds; superseded by Newton July 2; division command July 2-3)</t>
         </is>
       </c>
       <c r="AI270" s="5" t="inlineStr">
         <is>
-          <t>division strength unstated in the report (open at primary grade)</t>
+          <t>not stated for July 3 (open); division regiment grain in or-27-1-union-return (2,103 battle aggregate)</t>
         </is>
       </c>
       <c r="AJ270" s="5" t="inlineStr">
         <is>
-          <t>[E] the Ziegler's Grove-Bryan barn front; [D] his mounted presence along the wall through the repulse</t>
+          <t>[E] second line behind the left-center; his own July 3 station OPEN (no primary pin)</t>
         </is>
       </c>
       <c r="AK270" s="5" t="inlineStr">
@@ -31261,30 +31297,30 @@
       </c>
       <c r="AL270" s="5" t="inlineStr">
         <is>
-          <t>[C report -55] the four-lines repulse record ('Four lines rose from behind our stone wall'); Bliss barn burning order ~10:00-10:30; late-stated clock cluster member; the flag-drag ride NOT in his report (not asserted)</t>
+          <t>[C report -53] late litigious report (the Meade feud shapes it); late-stated clock cluster member</t>
         </is>
       </c>
       <c r="AM270" s="5" t="inlineStr">
         <is>
-          <t>division two-day 1,285 k+w+m (report) vs return grain per ED-52</t>
+          <t>division 2,103 (return, p. 174); apportionment at brigade rows</t>
         </is>
       </c>
       <c r="AN270" s="5" t="n"/>
       <c r="AO270" s="5" t="inlineStr">
         <is>
-          <t>T3 (command record)</t>
+          <t>T2 (command record)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-hq</t>
+          <t>reg-us-ii-3-hq</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>II Corps headquarters (corps command)</t>
+          <t>3rd Division, II Corps headquarters (division command)</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -31321,16 +31357,16 @@
       <c r="S271" s="2" t="inlineStr"/>
       <c r="T271" s="2" t="inlineStr"/>
       <c r="U271" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V271" s="2" t="inlineStr">
         <is>
-          <t>II Corps headquarters</t>
-        </is>
-      </c>
-      <c r="W271" s="4" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>3rd Division</t>
+        </is>
+      </c>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="X271" s="2" t="inlineStr"/>
@@ -31346,7 +31382,7 @@
       </c>
       <c r="AA271" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-hq</t>
+          <t>reg-us-ii-3-hq</t>
         </is>
       </c>
       <c r="AB271" s="5" t="inlineStr">
@@ -31360,22 +31396,22 @@
       <c r="AF271" s="5" t="n"/>
       <c r="AG271" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-hq-hancock.md; register row added pass 5</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-hq-hays.md; register row added pass 5</t>
         </is>
       </c>
       <c r="AH271" s="5" t="inlineStr">
         <is>
-          <t>Maj. Gen. W. S. Hancock (w July 3, 'toward the close'); corps + left-center wing command; July 1 arrival is ruled CA-J1P-7 (~16:15, partisan-dispute note)</t>
+          <t>Brig. Gen. Alexander Hays; division command over the Pettigrew-front wall</t>
         </is>
       </c>
       <c r="AI271" s="5" t="inlineStr">
         <is>
-          <t>n/a (command entry); corps regiment grain in or-27-1-union-return</t>
+          <t>division strength unstated in the report (open at primary grade)</t>
         </is>
       </c>
       <c r="AJ271" s="5" t="inlineStr">
         <is>
-          <t>[D] the mounted ride along the line under the cannonade; wounding position near Stannard's front (Vermont accounts)</t>
+          <t>[E] the Ziegler's Grove-Bryan barn front; [D] his mounted presence along the wall through the repulse</t>
         </is>
       </c>
       <c r="AK271" s="5" t="inlineStr">
@@ -31385,12 +31421,12 @@
       </c>
       <c r="AL271" s="5" t="inlineStr">
         <is>
-          <t>[C report ~+7] his OR cannonade ladder ('About 1 o'clock ... After an hour and forty-five minutes') corroborates CA-J3A-1/4; the wounding TIME is a CONFLICT RECORD by design (no clock invented)</t>
+          <t>[C report -55] the four-lines repulse record ('Four lines rose from behind our stone wall'); Bliss barn burning order ~10:00-10:30; late-stated clock cluster member; the flag-drag ride NOT in his report (not asserted)</t>
         </is>
       </c>
       <c r="AM271" s="5" t="inlineStr">
         <is>
-          <t>wounding pin sequenced after Gibbon's ('A short time afterward I was myself wounded'); corps losses at regiment grain per ED-52</t>
+          <t>division two-day 1,285 k+w+m (report) vs return grain per ED-52</t>
         </is>
       </c>
       <c r="AN271" s="5" t="n"/>
@@ -31403,12 +31439,12 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>reg-us-hq-provost</t>
+          <t>reg-us-ii-hq</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Provost Guard and army headquarters detachments (Brig. Gen. Marsena R. Patrick)</t>
+          <t>II Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -31449,7 +31485,7 @@
       </c>
       <c r="V272" s="2" t="inlineStr">
         <is>
-          <t>Provost Guard and army headquarters detachments</t>
+          <t>II Corps headquarters</t>
         </is>
       </c>
       <c r="W272" s="4" t="inlineStr">
@@ -31470,33 +31506,69 @@
       </c>
       <c r="AA272" s="2" t="inlineStr">
         <is>
-          <t>reg-us-hq-provost</t>
-        </is>
-      </c>
-      <c r="AB272" s="5" t="n"/>
+          <t>reg-us-ii-hq</t>
+        </is>
+      </c>
+      <c r="AB272" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (command record)</t>
+        </is>
+      </c>
       <c r="AC272" s="5" t="n"/>
       <c r="AD272" s="5" t="n"/>
       <c r="AE272" s="5" t="n"/>
       <c r="AF272" s="5" t="n"/>
-      <c r="AG272" s="5" t="n"/>
-      <c r="AH272" s="5" t="n"/>
-      <c r="AI272" s="5" t="n"/>
-      <c r="AJ272" s="5" t="n"/>
-      <c r="AK272" s="5" t="n"/>
-      <c r="AL272" s="5" t="n"/>
-      <c r="AM272" s="5" t="n"/>
+      <c r="AG272" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-hq-hancock.md; register row added pass 5</t>
+        </is>
+      </c>
+      <c r="AH272" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Gen. W. S. Hancock (w July 3, 'toward the close'); corps + left-center wing command; July 1 arrival is ruled CA-J1P-7 (~16:15, partisan-dispute note)</t>
+        </is>
+      </c>
+      <c r="AI272" s="5" t="inlineStr">
+        <is>
+          <t>n/a (command entry); corps regiment grain in or-27-1-union-return</t>
+        </is>
+      </c>
+      <c r="AJ272" s="5" t="inlineStr">
+        <is>
+          <t>[D] the mounted ride along the line under the cannonade; wounding position near Stannard's front (Vermont accounts)</t>
+        </is>
+      </c>
+      <c r="AK272" s="5" t="inlineStr">
+        <is>
+          <t>n/a (command entry)</t>
+        </is>
+      </c>
+      <c r="AL272" s="5" t="inlineStr">
+        <is>
+          <t>[C report ~+7] his OR cannonade ladder ('About 1 o'clock ... After an hour and forty-five minutes') corroborates CA-J3A-1/4; the wounding TIME is a CONFLICT RECORD by design (no clock invented)</t>
+        </is>
+      </c>
+      <c r="AM272" s="5" t="inlineStr">
+        <is>
+          <t>wounding pin sequenced after Gibbon's ('A short time afterward I was myself wounded'); corps losses at regiment grain per ED-52</t>
+        </is>
+      </c>
       <c r="AN272" s="5" t="n"/>
-      <c r="AO272" s="5" t="n"/>
+      <c r="AO272" s="5" t="inlineStr">
+        <is>
+          <t>T3 (command record)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>us-hall</t>
+          <t>reg-us-hq-provost</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Hall's Brigade</t>
+          <t>Provost Guard and army headquarters detachments (Brig. Gen. Marsena R. Patrick)</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -31506,7 +31578,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>parent-brigade</t>
+          <t>command</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -31514,149 +31586,77 @@
           <t>infantry</t>
         </is>
       </c>
-      <c r="F273" s="2" t="n">
-        <v>920</v>
-      </c>
-      <c r="G273" s="2" t="n">
-        <v>555</v>
-      </c>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr"/>
       <c r="H273" s="3">
         <f>IF(F273=0,0,1-G273/F273)</f>
         <v/>
       </c>
-      <c r="I273" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="J273" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K273" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L273" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M273" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O273" s="2" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="P273" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q273" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R273" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S273" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T273" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr"/>
+      <c r="O273" s="2" t="inlineStr"/>
+      <c r="P273" s="2" t="inlineStr"/>
+      <c r="Q273" s="2" t="inlineStr"/>
+      <c r="R273" s="2" t="inlineStr"/>
+      <c r="S273" s="2" t="inlineStr"/>
+      <c r="T273" s="2" t="inlineStr"/>
       <c r="U273" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V273" s="2" t="inlineStr">
         <is>
-          <t>Hall</t>
-        </is>
-      </c>
-      <c r="W273" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X273" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
+          <t>Provost Guard and army headquarters detachments</t>
+        </is>
+      </c>
+      <c r="W273" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="inlineStr"/>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr">
         <is>
-          <t>in-build</t>
+          <t>not-yet-cast</t>
         </is>
       </c>
       <c r="AA273" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-3</t>
-        </is>
-      </c>
-      <c r="AB273" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (crisis rush authored in Angle cast)</t>
-        </is>
-      </c>
+          <t>reg-us-hq-provost</t>
+        </is>
+      </c>
+      <c r="AB273" s="5" t="n"/>
       <c r="AC273" s="5" t="n"/>
       <c r="AD273" s="5" t="n"/>
       <c r="AE273" s="5" t="n"/>
       <c r="AF273" s="5" t="n"/>
-      <c r="AG273" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
-        </is>
-      </c>
-      <c r="AH273" s="5" t="inlineStr">
-        <is>
-          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
-        </is>
-      </c>
-      <c r="AI273" s="5" t="inlineStr">
-        <is>
-          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
-        </is>
-      </c>
-      <c r="AJ273" s="5" t="inlineStr">
-        <is>
-          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
-        </is>
-      </c>
-      <c r="AK273" s="5" t="inlineStr">
-        <is>
-          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
-        </is>
-      </c>
-      <c r="AL273" s="5" t="inlineStr">
-        <is>
-          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
-        </is>
-      </c>
-      <c r="AM273" s="5" t="inlineStr">
-        <is>
-          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
-        </is>
-      </c>
+      <c r="AG273" s="5" t="n"/>
+      <c r="AH273" s="5" t="n"/>
+      <c r="AI273" s="5" t="n"/>
+      <c r="AJ273" s="5" t="n"/>
+      <c r="AK273" s="5" t="n"/>
+      <c r="AL273" s="5" t="n"/>
+      <c r="AM273" s="5" t="n"/>
       <c r="AN273" s="5" t="n"/>
-      <c r="AO273" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc (T5-grade window via V2 claims)</t>
-        </is>
-      </c>
+      <c r="AO273" s="5" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>us-stannard</t>
+          <t>us-hall</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Stannard's Vermont Brigade</t>
+          <t>Hall's Brigade</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -31675,68 +31675,68 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>1950</v>
+        <v>920</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1600</v>
+        <v>555</v>
       </c>
       <c r="H274" s="3">
         <f>IF(F274=0,0,1-G274/F274)</f>
         <v/>
       </c>
       <c r="I274" s="2" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K274" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L274" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M274" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N274" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>297.9</v>
+        <v>60.9</v>
       </c>
       <c r="P274" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q274" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V274" s="2" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R274" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S274" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T274" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U274" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V274" s="2" t="inlineStr">
-        <is>
-          <t>Stannard</t>
-        </is>
-      </c>
-      <c r="W274" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
           <t>T5</t>
@@ -31754,12 +31754,12 @@
       </c>
       <c r="AA274" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-3</t>
+          <t>reg-us-ii-2-3</t>
         </is>
       </c>
       <c r="AB274" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (crisis rush authored in Angle cast)</t>
         </is>
       </c>
       <c r="AC274" s="5" t="n"/>
@@ -31768,55 +31768,55 @@
       <c r="AF274" s="5" t="n"/>
       <c r="AG274" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
         </is>
       </c>
       <c r="AH274" s="5" t="inlineStr">
         <is>
-          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
+          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
         </is>
       </c>
       <c r="AI274" s="5" t="inlineStr">
         <is>
-          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
+          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
         </is>
       </c>
       <c r="AJ274" s="5" t="inlineStr">
         <is>
-          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
+          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
         </is>
       </c>
       <c r="AK274" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
+          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
         </is>
       </c>
       <c r="AL274" s="5" t="inlineStr">
         <is>
-          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
+          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
         </is>
       </c>
       <c r="AM274" s="5" t="inlineStr">
         <is>
-          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
+          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
         </is>
       </c>
       <c r="AN274" s="5" t="n"/>
       <c r="AO274" s="5" t="inlineStr">
         <is>
-          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
+          <t>T4 full-arc (T5-grade window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>us-webb</t>
+          <t>us-stannard</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Webb's Brigade (Philadelphia Brigade)</t>
+          <t>Stannard's Vermont Brigade</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -31835,61 +31835,61 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>1250</v>
+        <v>1950</v>
       </c>
       <c r="G275" s="2" t="n">
-        <v>760</v>
+        <v>1600</v>
       </c>
       <c r="H275" s="3">
         <f>IF(F275=0,0,1-G275/F275)</f>
         <v/>
       </c>
       <c r="I275" s="2" t="n">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="J275" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K275" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L275" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="M275" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N275" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O275" s="2" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="P275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T275" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U275" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O275" s="2" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P275" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q275" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R275" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S275" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T275" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U275" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V275" s="2" t="inlineStr">
         <is>
-          <t>Webb</t>
+          <t>Stannard</t>
         </is>
       </c>
       <c r="W275" s="2" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="AA275" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-2</t>
+          <t>reg-us-i-3-3</t>
         </is>
       </c>
       <c r="AB275" s="5" t="inlineStr">
@@ -31928,55 +31928,55 @@
       <c r="AF275" s="5" t="n"/>
       <c r="AG275" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
         </is>
       </c>
       <c r="AH275" s="5" t="inlineStr">
         <is>
-          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
+          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
         </is>
       </c>
       <c r="AI275" s="5" t="inlineStr">
         <is>
-          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
+          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
         </is>
       </c>
       <c r="AJ275" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
+          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
         </is>
       </c>
       <c r="AK275" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
+          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
         </is>
       </c>
       <c r="AL275" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
+          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
         </is>
       </c>
       <c r="AM275" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
+          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
         </is>
       </c>
       <c r="AN275" s="5" t="n"/>
       <c r="AO275" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (T5 window held)</t>
+          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>us-8oh</t>
+          <t>us-webb</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>8th Ohio Infantry</t>
+          <t>Webb's Brigade (Philadelphia Brigade)</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -31986,7 +31986,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>parent-brigade</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -31995,71 +31995,71 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>209</v>
+        <v>1250</v>
       </c>
       <c r="G276" s="2" t="n">
-        <v>170</v>
+        <v>760</v>
       </c>
       <c r="H276" s="3">
         <f>IF(F276=0,0,1-G276/F276)</f>
         <v/>
       </c>
       <c r="I276" s="2" t="n">
-        <v>39</v>
+        <v>490</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L276" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M276" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N276" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>219.5</v>
+        <v>23.3</v>
       </c>
       <c r="P276" s="2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Q276" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U276" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V276" s="2" t="inlineStr">
+        <is>
+          <t>Webb</t>
+        </is>
+      </c>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R276" s="2" t="inlineStr">
-        <is>
-          <t>line/skirmish</t>
-        </is>
-      </c>
-      <c r="S276" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T276" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U276" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V276" s="2" t="inlineStr">
-        <is>
-          <t>8th Ohio</t>
-        </is>
-      </c>
-      <c r="W276" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X276" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="Y276" s="2" t="inlineStr">
@@ -32072,7 +32072,11 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-ii-2-2</t>
+        </is>
+      </c>
       <c r="AB276" s="5" t="inlineStr">
         <is>
           <t>authored-ok</t>
@@ -32084,55 +32088,55 @@
       <c r="AF276" s="5" t="n"/>
       <c r="AG276" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
         </is>
       </c>
       <c r="AH276" s="5" t="inlineStr">
         <is>
-          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
         </is>
       </c>
       <c r="AI276" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 209 (compilation, flagged)</t>
+          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
         </is>
       </c>
       <c r="AJ276" s="5" t="inlineStr">
         <is>
-          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
         </is>
       </c>
       <c r="AK276" s="5" t="inlineStr">
         <is>
-          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
         </is>
       </c>
       <c r="AL276" s="5" t="inlineStr">
         <is>
-          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
         </is>
       </c>
       <c r="AM276" s="5" t="inlineStr">
         <is>
-          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
         </is>
       </c>
       <c r="AN276" s="5" t="n"/>
       <c r="AO276" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 full-arc (T5 window held)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>us-bartlett</t>
+          <t>us-8oh</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
+          <t>8th Ohio Infantry</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -32151,23 +32155,23 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>1325</v>
+        <v>209</v>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1325</v>
+        <v>170</v>
       </c>
       <c r="H277" s="3">
         <f>IF(F277=0,0,1-G277/F277)</f>
         <v/>
       </c>
       <c r="I277" s="2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L277" s="2" t="n">
         <v>0</v>
@@ -32176,36 +32180,36 @@
         <v>0</v>
       </c>
       <c r="N277" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>0</v>
+        <v>219.5</v>
       </c>
       <c r="P277" s="2" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q277" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R277" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>line/skirmish</t>
         </is>
       </c>
       <c r="S277" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T277" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U277" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V277" s="2" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>8th Ohio</t>
         </is>
       </c>
       <c r="W277" s="2" t="inlineStr">
@@ -32220,7 +32224,7 @@
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
@@ -32228,35 +32232,67 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA277" s="2" t="inlineStr">
-        <is>
-          <t>reg-us-vi-1-2</t>
-        </is>
-      </c>
-      <c r="AB277" s="5" t="n"/>
+      <c r="AA277" s="2" t="inlineStr"/>
+      <c r="AB277" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC277" s="5" t="n"/>
       <c r="AD277" s="5" t="n"/>
       <c r="AE277" s="5" t="n"/>
       <c r="AF277" s="5" t="n"/>
-      <c r="AG277" s="5" t="n"/>
-      <c r="AH277" s="5" t="n"/>
-      <c r="AI277" s="5" t="n"/>
-      <c r="AJ277" s="5" t="n"/>
-      <c r="AK277" s="5" t="n"/>
-      <c r="AL277" s="5" t="n"/>
-      <c r="AM277" s="5" t="n"/>
+      <c r="AG277" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+        </is>
+      </c>
+      <c r="AH277" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+        </is>
+      </c>
+      <c r="AI277" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 209 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ277" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+        </is>
+      </c>
+      <c r="AK277" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+        </is>
+      </c>
+      <c r="AL277" s="5" t="inlineStr">
+        <is>
+          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+        </is>
+      </c>
+      <c r="AM277" s="5" t="inlineStr">
+        <is>
+          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+        </is>
+      </c>
       <c r="AN277" s="5" t="n"/>
-      <c r="AO277" s="5" t="n"/>
+      <c r="AO277" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>us-baxter</t>
+          <t>us-bartlett</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
+          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -32275,10 +32311,10 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>800</v>
+        <v>1325</v>
       </c>
       <c r="G278" s="2" t="n">
-        <v>800</v>
+        <v>1325</v>
       </c>
       <c r="H278" s="3">
         <f>IF(F278=0,0,1-G278/F278)</f>
@@ -32288,34 +32324,34 @@
         <v>0</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L278" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N278" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>1021.5</v>
+        <v>0</v>
       </c>
       <c r="P278" s="2" t="n">
-        <v>1021.5</v>
+        <v>0</v>
       </c>
       <c r="Q278" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R278" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S278" s="2" t="n">
@@ -32329,7 +32365,7 @@
       </c>
       <c r="V278" s="2" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="W278" s="2" t="inlineStr">
@@ -32344,7 +32380,7 @@
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
@@ -32354,7 +32390,7 @@
       </c>
       <c r="AA278" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-2</t>
+          <t>reg-us-vi-1-2</t>
         </is>
       </c>
       <c r="AB278" s="5" t="n"/>
@@ -32375,12 +32411,12 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>us-berdan</t>
+          <t>us-baxter</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
+          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -32399,10 +32435,10 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>1405</v>
+        <v>800</v>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1405</v>
+        <v>800</v>
       </c>
       <c r="H279" s="3">
         <f>IF(F279=0,0,1-G279/F279)</f>
@@ -32412,34 +32448,34 @@
         <v>0</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L279" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M279" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N279" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O279" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="P279" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="Q279" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R279" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S279" s="2" t="n">
@@ -32453,7 +32489,7 @@
       </c>
       <c r="V279" s="2" t="inlineStr">
         <is>
-          <t>Berdan</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="W279" s="2" t="inlineStr">
@@ -32468,7 +32504,7 @@
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
@@ -32478,69 +32514,33 @@
       </c>
       <c r="AA279" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-2</t>
-        </is>
-      </c>
-      <c r="AB279" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 defender)</t>
-        </is>
-      </c>
+          <t>reg-us-i-2-2</t>
+        </is>
+      </c>
+      <c r="AB279" s="5" t="n"/>
       <c r="AC279" s="5" t="n"/>
       <c r="AD279" s="5" t="n"/>
       <c r="AE279" s="5" t="n"/>
       <c r="AF279" s="5" t="n"/>
-      <c r="AG279" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
-        </is>
-      </c>
-      <c r="AH279" s="5" t="inlineStr">
-        <is>
-          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
-        </is>
-      </c>
-      <c r="AI279" s="5" t="inlineStr">
-        <is>
-          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
-        </is>
-      </c>
-      <c r="AJ279" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
-        </is>
-      </c>
-      <c r="AK279" s="5" t="inlineStr">
-        <is>
-          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
-        </is>
-      </c>
-      <c r="AL279" s="5" t="inlineStr">
-        <is>
-          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
-        </is>
-      </c>
-      <c r="AM279" s="5" t="inlineStr">
-        <is>
-          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row column-noise flagged (144-class); ~all July 2</t>
-        </is>
-      </c>
+      <c r="AG279" s="5" t="n"/>
+      <c r="AH279" s="5" t="n"/>
+      <c r="AI279" s="5" t="n"/>
+      <c r="AJ279" s="5" t="n"/>
+      <c r="AK279" s="5" t="n"/>
+      <c r="AL279" s="5" t="n"/>
+      <c r="AM279" s="5" t="n"/>
       <c r="AN279" s="5" t="n"/>
-      <c r="AO279" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO279" s="5" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>us-biddle</t>
+          <t>us-berdan</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
+          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -32559,10 +32559,10 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>460</v>
+        <v>1405</v>
       </c>
       <c r="G280" s="2" t="n">
-        <v>460</v>
+        <v>1405</v>
       </c>
       <c r="H280" s="3">
         <f>IF(F280=0,0,1-G280/F280)</f>
@@ -32599,11 +32599,11 @@
       </c>
       <c r="R280" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S280" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T280" s="2" t="n">
         <v>0</v>
@@ -32613,7 +32613,7 @@
       </c>
       <c r="V280" s="2" t="inlineStr">
         <is>
-          <t>Biddle</t>
+          <t>Berdan</t>
         </is>
       </c>
       <c r="W280" s="2" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr">
@@ -32638,12 +32638,12 @@
       </c>
       <c r="AA280" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-1</t>
+          <t>reg-us-iii-1-2</t>
         </is>
       </c>
       <c r="AB280" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 defender)</t>
         </is>
       </c>
       <c r="AC280" s="5" t="n"/>
@@ -32652,55 +32652,55 @@
       <c r="AF280" s="5" t="n"/>
       <c r="AG280" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
         </is>
       </c>
       <c r="AH280" s="5" t="inlineStr">
         <is>
-          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
+          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
         </is>
       </c>
       <c r="AI280" s="5" t="inlineStr">
         <is>
-          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
+          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
         </is>
       </c>
       <c r="AJ280" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
+          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
         </is>
       </c>
       <c r="AK280" s="5" t="inlineStr">
         <is>
-          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
+          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
         </is>
       </c>
       <c r="AL280" s="5" t="inlineStr">
         <is>
-          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
+          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
         </is>
       </c>
       <c r="AM280" s="5" t="inlineStr">
         <is>
-          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
+          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row column-noise flagged (144-class); ~all July 2</t>
         </is>
       </c>
       <c r="AN280" s="5" t="n"/>
       <c r="AO280" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>us-brewster</t>
+          <t>us-biddle</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
+          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -32719,10 +32719,10 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>1060</v>
+        <v>460</v>
       </c>
       <c r="G281" s="2" t="n">
-        <v>1060</v>
+        <v>460</v>
       </c>
       <c r="H281" s="3">
         <f>IF(F281=0,0,1-G281/F281)</f>
@@ -32759,11 +32759,11 @@
       </c>
       <c r="R281" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S281" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T281" s="2" t="n">
         <v>0</v>
@@ -32773,7 +32773,7 @@
       </c>
       <c r="V281" s="2" t="inlineStr">
         <is>
-          <t>Brewster</t>
+          <t>Biddle</t>
         </is>
       </c>
       <c r="W281" s="2" t="inlineStr">
@@ -32788,7 +32788,7 @@
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
@@ -32798,33 +32798,69 @@
       </c>
       <c r="AA281" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-2</t>
-        </is>
-      </c>
-      <c r="AB281" s="5" t="n"/>
+          <t>reg-us-i-3-1</t>
+        </is>
+      </c>
+      <c r="AB281" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC281" s="5" t="n"/>
       <c r="AD281" s="5" t="n"/>
       <c r="AE281" s="5" t="n"/>
       <c r="AF281" s="5" t="n"/>
-      <c r="AG281" s="5" t="n"/>
-      <c r="AH281" s="5" t="n"/>
-      <c r="AI281" s="5" t="n"/>
-      <c r="AJ281" s="5" t="n"/>
-      <c r="AK281" s="5" t="n"/>
-      <c r="AL281" s="5" t="n"/>
-      <c r="AM281" s="5" t="n"/>
+      <c r="AG281" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
+        </is>
+      </c>
+      <c r="AH281" s="5" t="inlineStr">
+        <is>
+          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
+        </is>
+      </c>
+      <c r="AI281" s="5" t="inlineStr">
+        <is>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
+        </is>
+      </c>
+      <c r="AJ281" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
+        </is>
+      </c>
+      <c r="AK281" s="5" t="inlineStr">
+        <is>
+          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
+        </is>
+      </c>
+      <c r="AL281" s="5" t="inlineStr">
+        <is>
+          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
+        </is>
+      </c>
+      <c r="AM281" s="5" t="inlineStr">
+        <is>
+          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
+        </is>
+      </c>
       <c r="AN281" s="5" t="n"/>
-      <c r="AO281" s="5" t="n"/>
+      <c r="AO281" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>us-brooke</t>
+          <t>us-brewster</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
+          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -32843,10 +32879,10 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>460</v>
+        <v>1060</v>
       </c>
       <c r="G282" s="2" t="n">
-        <v>460</v>
+        <v>1060</v>
       </c>
       <c r="H282" s="3">
         <f>IF(F282=0,0,1-G282/F282)</f>
@@ -32883,7 +32919,7 @@
       </c>
       <c r="R282" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S282" s="2" t="n">
@@ -32897,7 +32933,7 @@
       </c>
       <c r="V282" s="2" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Brewster</t>
         </is>
       </c>
       <c r="W282" s="2" t="inlineStr">
@@ -32922,7 +32958,7 @@
       </c>
       <c r="AA282" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-4</t>
+          <t>reg-us-iii-2-2</t>
         </is>
       </c>
       <c r="AB282" s="5" t="inlineStr">
@@ -32936,37 +32972,37 @@
       <c r="AF282" s="5" t="n"/>
       <c r="AG282" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
         </is>
       </c>
       <c r="AH282" s="5" t="inlineStr">
         <is>
-          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
         </is>
       </c>
       <c r="AI282" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
         </is>
       </c>
       <c r="AJ282" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
         </is>
       </c>
       <c r="AK282" s="5" t="inlineStr">
         <is>
-          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
         </is>
       </c>
       <c r="AL282" s="5" t="inlineStr">
         <is>
-          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
         </is>
       </c>
       <c r="AM282" s="5" t="inlineStr">
         <is>
-          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
         </is>
       </c>
       <c r="AN282" s="5" t="n"/>
@@ -32979,12 +33015,12 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>us-burbank</t>
+          <t>us-brooke</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
+          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -33003,10 +33039,10 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="G283" s="2" t="n">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="H283" s="3">
         <f>IF(F283=0,0,1-G283/F283)</f>
@@ -33057,7 +33093,7 @@
       </c>
       <c r="V283" s="2" t="inlineStr">
         <is>
-          <t>Burbank</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="W283" s="2" t="inlineStr">
@@ -33082,33 +33118,69 @@
       </c>
       <c r="AA283" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-2</t>
-        </is>
-      </c>
-      <c r="AB283" s="5" t="n"/>
+          <t>reg-us-ii-1-4</t>
+        </is>
+      </c>
+      <c r="AB283" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC283" s="5" t="n"/>
       <c r="AD283" s="5" t="n"/>
       <c r="AE283" s="5" t="n"/>
       <c r="AF283" s="5" t="n"/>
-      <c r="AG283" s="5" t="n"/>
-      <c r="AH283" s="5" t="n"/>
-      <c r="AI283" s="5" t="n"/>
-      <c r="AJ283" s="5" t="n"/>
-      <c r="AK283" s="5" t="n"/>
-      <c r="AL283" s="5" t="n"/>
-      <c r="AM283" s="5" t="n"/>
+      <c r="AG283" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+        </is>
+      </c>
+      <c r="AH283" s="5" t="inlineStr">
+        <is>
+          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+        </is>
+      </c>
+      <c r="AI283" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+        </is>
+      </c>
+      <c r="AJ283" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+        </is>
+      </c>
+      <c r="AK283" s="5" t="inlineStr">
+        <is>
+          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+        </is>
+      </c>
+      <c r="AL283" s="5" t="inlineStr">
+        <is>
+          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+        </is>
+      </c>
+      <c r="AM283" s="5" t="inlineStr">
+        <is>
+          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+        </is>
+      </c>
       <c r="AN283" s="5" t="n"/>
-      <c r="AO283" s="5" t="n"/>
+      <c r="AO283" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>us-burling</t>
+          <t>us-burbank</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
+          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -33127,10 +33199,10 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>850</v>
+        <v>505</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>850</v>
+        <v>505</v>
       </c>
       <c r="H284" s="3">
         <f>IF(F284=0,0,1-G284/F284)</f>
@@ -33167,7 +33239,7 @@
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S284" s="2" t="n">
@@ -33181,7 +33253,7 @@
       </c>
       <c r="V284" s="2" t="inlineStr">
         <is>
-          <t>Burling</t>
+          <t>Burbank</t>
         </is>
       </c>
       <c r="W284" s="2" t="inlineStr">
@@ -33206,33 +33278,69 @@
       </c>
       <c r="AA284" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-3</t>
-        </is>
-      </c>
-      <c r="AB284" s="5" t="n"/>
+          <t>reg-us-v-2-2</t>
+        </is>
+      </c>
+      <c r="AB284" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 single-window mover)</t>
+        </is>
+      </c>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="n"/>
-      <c r="AH284" s="5" t="n"/>
-      <c r="AI284" s="5" t="n"/>
-      <c r="AJ284" s="5" t="n"/>
-      <c r="AK284" s="5" t="n"/>
-      <c r="AL284" s="5" t="n"/>
-      <c r="AM284" s="5" t="n"/>
+      <c r="AG284" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
+        </is>
+      </c>
+      <c r="AH284" s="5" t="inlineStr">
+        <is>
+          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
+        </is>
+      </c>
+      <c r="AI284" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
+        </is>
+      </c>
+      <c r="AJ284" s="5" t="inlineStr">
+        <is>
+          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
+        </is>
+      </c>
+      <c r="AK284" s="5" t="inlineStr">
+        <is>
+          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
+        </is>
+      </c>
+      <c r="AL284" s="5" t="inlineStr">
+        <is>
+          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
+        </is>
+      </c>
+      <c r="AM284" s="5" t="inlineStr">
+        <is>
+          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
+        </is>
+      </c>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="n"/>
+      <c r="AO284" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>us-candy</t>
+          <t>us-burling</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
+          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -33251,10 +33359,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="G285" s="2" t="n">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="H285" s="3">
         <f>IF(F285=0,0,1-G285/F285)</f>
@@ -33291,7 +33399,7 @@
       </c>
       <c r="R285" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S285" s="2" t="n">
@@ -33305,7 +33413,7 @@
       </c>
       <c r="V285" s="2" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Burling</t>
         </is>
       </c>
       <c r="W285" s="2" t="inlineStr">
@@ -33330,33 +33438,69 @@
       </c>
       <c r="AA285" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-1</t>
-        </is>
-      </c>
-      <c r="AB285" s="5" t="n"/>
+          <t>reg-us-iii-2-3</t>
+        </is>
+      </c>
+      <c r="AB285" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 DISPERSED class)</t>
+        </is>
+      </c>
       <c r="AC285" s="5" t="n"/>
       <c r="AD285" s="5" t="n"/>
       <c r="AE285" s="5" t="n"/>
       <c r="AF285" s="5" t="n"/>
-      <c r="AG285" s="5" t="n"/>
-      <c r="AH285" s="5" t="n"/>
-      <c r="AI285" s="5" t="n"/>
-      <c r="AJ285" s="5" t="n"/>
-      <c r="AK285" s="5" t="n"/>
-      <c r="AL285" s="5" t="n"/>
-      <c r="AM285" s="5" t="n"/>
+      <c r="AG285" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
+        </is>
+      </c>
+      <c r="AH285" s="5" t="inlineStr">
+        <is>
+          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
+        </is>
+      </c>
+      <c r="AI285" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
+        </is>
+      </c>
+      <c r="AJ285" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
+        </is>
+      </c>
+      <c r="AK285" s="5" t="inlineStr">
+        <is>
+          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
+        </is>
+      </c>
+      <c r="AL285" s="5" t="inlineStr">
+        <is>
+          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
+        </is>
+      </c>
+      <c r="AM285" s="5" t="inlineStr">
+        <is>
+          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
+        </is>
+      </c>
       <c r="AN285" s="5" t="n"/>
-      <c r="AO285" s="5" t="n"/>
+      <c r="AO285" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (dispersed class)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>us-carr</t>
+          <t>us-candy</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
+          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -33375,10 +33519,10 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="G286" s="2" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="H286" s="3">
         <f>IF(F286=0,0,1-G286/F286)</f>
@@ -33415,7 +33559,7 @@
       </c>
       <c r="R286" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S286" s="2" t="n">
@@ -33425,11 +33569,11 @@
         <v>0</v>
       </c>
       <c r="U286" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V286" s="2" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="W286" s="2" t="inlineStr">
@@ -33454,7 +33598,7 @@
       </c>
       <c r="AA286" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-1</t>
+          <t>reg-us-xii-2-1</t>
         </is>
       </c>
       <c r="AB286" s="5" t="n"/>
@@ -33475,12 +33619,12 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>us-carroll</t>
+          <t>us-carr</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
+          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -33499,10 +33643,10 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>640</v>
+        <v>925</v>
       </c>
       <c r="G287" s="2" t="n">
-        <v>640</v>
+        <v>925</v>
       </c>
       <c r="H287" s="3">
         <f>IF(F287=0,0,1-G287/F287)</f>
@@ -33539,7 +33683,7 @@
       </c>
       <c r="R287" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S287" s="2" t="n">
@@ -33553,7 +33697,7 @@
       </c>
       <c r="V287" s="2" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="W287" s="2" t="inlineStr">
@@ -33578,12 +33722,12 @@
       </c>
       <c r="AA287" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-1</t>
+          <t>reg-us-iii-2-1</t>
         </is>
       </c>
       <c r="AB287" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC287" s="5" t="n"/>
@@ -33592,37 +33736,37 @@
       <c r="AF287" s="5" t="n"/>
       <c r="AG287" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
         </is>
       </c>
       <c r="AH287" s="5" t="inlineStr">
         <is>
-          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
         </is>
       </c>
       <c r="AI287" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 640 (compilation, flagged)</t>
+          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AJ287" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265))</t>
+          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
         </is>
       </c>
       <c r="AK287" s="5" t="inlineStr">
         <is>
-          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
         </is>
       </c>
       <c r="AL287" s="5" t="inlineStr">
         <is>
-          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
         </is>
       </c>
       <c r="AM287" s="5" t="inlineStr">
         <is>
-          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
         </is>
       </c>
       <c r="AN287" s="5" t="n"/>
@@ -33635,12 +33779,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>us-colgrove</t>
+          <t>us-carroll</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
+          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -33659,10 +33803,10 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>1170</v>
+        <v>640</v>
       </c>
       <c r="G288" s="2" t="n">
-        <v>1170</v>
+        <v>640</v>
       </c>
       <c r="H288" s="3">
         <f>IF(F288=0,0,1-G288/F288)</f>
@@ -33709,11 +33853,11 @@
         <v>0</v>
       </c>
       <c r="U288" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V288" s="2" t="inlineStr">
         <is>
-          <t>Colgrove</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="W288" s="2" t="inlineStr">
@@ -33738,33 +33882,69 @@
       </c>
       <c r="AA288" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-3</t>
-        </is>
-      </c>
-      <c r="AB288" s="5" t="n"/>
+          <t>reg-us-ii-3-1</t>
+        </is>
+      </c>
+      <c r="AB288" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+        </is>
+      </c>
       <c r="AC288" s="5" t="n"/>
       <c r="AD288" s="5" t="n"/>
       <c r="AE288" s="5" t="n"/>
       <c r="AF288" s="5" t="n"/>
-      <c r="AG288" s="5" t="n"/>
-      <c r="AH288" s="5" t="n"/>
-      <c r="AI288" s="5" t="n"/>
-      <c r="AJ288" s="5" t="n"/>
-      <c r="AK288" s="5" t="n"/>
-      <c r="AL288" s="5" t="n"/>
-      <c r="AM288" s="5" t="n"/>
+      <c r="AG288" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+        </is>
+      </c>
+      <c r="AH288" s="5" t="inlineStr">
+        <is>
+          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+        </is>
+      </c>
+      <c r="AI288" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 640 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ288" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265))</t>
+        </is>
+      </c>
+      <c r="AK288" s="5" t="inlineStr">
+        <is>
+          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+        </is>
+      </c>
+      <c r="AL288" s="5" t="inlineStr">
+        <is>
+          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+        </is>
+      </c>
+      <c r="AM288" s="5" t="inlineStr">
+        <is>
+          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+        </is>
+      </c>
       <c r="AN288" s="5" t="n"/>
-      <c r="AO288" s="5" t="n"/>
+      <c r="AO288" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>us-coster</t>
+          <t>us-colgrove</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
+          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -33783,10 +33963,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>655</v>
+        <v>1170</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>655</v>
+        <v>1170</v>
       </c>
       <c r="H289" s="3">
         <f>IF(F289=0,0,1-G289/F289)</f>
@@ -33837,7 +34017,7 @@
       </c>
       <c r="V289" s="2" t="inlineStr">
         <is>
-          <t>Coster</t>
+          <t>Colgrove</t>
         </is>
       </c>
       <c r="W289" s="2" t="inlineStr">
@@ -33862,7 +34042,7 @@
       </c>
       <c r="AA289" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-1</t>
+          <t>reg-us-xii-1-3</t>
         </is>
       </c>
       <c r="AB289" s="5" t="n"/>
@@ -33883,12 +34063,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>us-coulter</t>
+          <t>us-coster</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
+          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -33907,10 +34087,10 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>510</v>
+        <v>655</v>
       </c>
       <c r="G290" s="2" t="n">
-        <v>510</v>
+        <v>655</v>
       </c>
       <c r="H290" s="3">
         <f>IF(F290=0,0,1-G290/F290)</f>
@@ -33920,34 +34100,34 @@
         <v>0</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L290" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M290" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N290" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="P290" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="Q290" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R290" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S290" s="2" t="n">
@@ -33961,7 +34141,7 @@
       </c>
       <c r="V290" s="2" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Coster</t>
         </is>
       </c>
       <c r="W290" s="2" t="inlineStr">
@@ -33976,7 +34156,7 @@
       </c>
       <c r="Y290" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z290" s="2" t="inlineStr">
@@ -33986,7 +34166,7 @@
       </c>
       <c r="AA290" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-1</t>
+          <t>reg-us-xi-2-1</t>
         </is>
       </c>
       <c r="AB290" s="5" t="n"/>
@@ -34007,12 +34187,12 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>us-cutler</t>
+          <t>us-coulter</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
+          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -34031,10 +34211,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>1015</v>
+        <v>510</v>
       </c>
       <c r="G291" s="2" t="n">
-        <v>1015</v>
+        <v>510</v>
       </c>
       <c r="H291" s="3">
         <f>IF(F291=0,0,1-G291/F291)</f>
@@ -34044,34 +34224,34 @@
         <v>0</v>
       </c>
       <c r="J291" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L291" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N291" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="P291" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S291" s="2" t="n">
@@ -34085,7 +34265,7 @@
       </c>
       <c r="V291" s="2" t="inlineStr">
         <is>
-          <t>Cutler</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="W291" s="2" t="inlineStr">
@@ -34100,7 +34280,7 @@
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr">
@@ -34110,7 +34290,7 @@
       </c>
       <c r="AA291" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-2</t>
+          <t>reg-us-i-2-1</t>
         </is>
       </c>
       <c r="AB291" s="5" t="n"/>
@@ -34131,12 +34311,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>us-dana</t>
+          <t>us-cutler</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
+          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -34155,10 +34335,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="G292" s="2" t="n">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="H292" s="3">
         <f>IF(F292=0,0,1-G292/F292)</f>
@@ -34199,7 +34379,7 @@
         </is>
       </c>
       <c r="S292" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T292" s="2" t="n">
         <v>0</v>
@@ -34209,7 +34389,7 @@
       </c>
       <c r="V292" s="2" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Cutler</t>
         </is>
       </c>
       <c r="W292" s="2" t="inlineStr">
@@ -34224,7 +34404,7 @@
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr">
@@ -34234,69 +34414,33 @@
       </c>
       <c r="AA292" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-2</t>
-        </is>
-      </c>
-      <c r="AB292" s="5" t="inlineStr">
-        <is>
-          <t>attested-static (sheet grain)</t>
-        </is>
-      </c>
+          <t>reg-us-i-1-2</t>
+        </is>
+      </c>
+      <c r="AB292" s="5" t="n"/>
       <c r="AC292" s="5" t="n"/>
       <c r="AD292" s="5" t="n"/>
       <c r="AE292" s="5" t="n"/>
       <c r="AF292" s="5" t="n"/>
-      <c r="AG292" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
-        </is>
-      </c>
-      <c r="AH292" s="5" t="inlineStr">
-        <is>
-          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
-        </is>
-      </c>
-      <c r="AI292" s="5" t="inlineStr">
-        <is>
-          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
-        </is>
-      </c>
-      <c r="AJ292" s="5" t="inlineStr">
-        <is>
-          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
-        </is>
-      </c>
-      <c r="AK292" s="5" t="inlineStr">
-        <is>
-          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
-        </is>
-      </c>
-      <c r="AL292" s="5" t="inlineStr">
-        <is>
-          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
-        </is>
-      </c>
-      <c r="AM292" s="5" t="inlineStr">
-        <is>
-          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
-        </is>
-      </c>
+      <c r="AG292" s="5" t="n"/>
+      <c r="AH292" s="5" t="n"/>
+      <c r="AI292" s="5" t="n"/>
+      <c r="AJ292" s="5" t="n"/>
+      <c r="AK292" s="5" t="n"/>
+      <c r="AL292" s="5" t="n"/>
+      <c r="AM292" s="5" t="n"/>
       <c r="AN292" s="5" t="n"/>
-      <c r="AO292" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO292" s="5" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>us-day</t>
+          <t>us-dana</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
+          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -34315,10 +34459,10 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>1170</v>
+        <v>465</v>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1170</v>
+        <v>465</v>
       </c>
       <c r="H293" s="3">
         <f>IF(F293=0,0,1-G293/F293)</f>
@@ -34359,17 +34503,17 @@
         </is>
       </c>
       <c r="S293" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T293" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U293" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V293" s="2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="W293" s="2" t="inlineStr">
@@ -34384,7 +34528,7 @@
       </c>
       <c r="Y293" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z293" s="2" t="inlineStr">
@@ -34394,33 +34538,69 @@
       </c>
       <c r="AA293" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-1</t>
-        </is>
-      </c>
-      <c r="AB293" s="5" t="n"/>
+          <t>reg-us-i-3-2</t>
+        </is>
+      </c>
+      <c r="AB293" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (sheet grain)</t>
+        </is>
+      </c>
       <c r="AC293" s="5" t="n"/>
       <c r="AD293" s="5" t="n"/>
       <c r="AE293" s="5" t="n"/>
       <c r="AF293" s="5" t="n"/>
-      <c r="AG293" s="5" t="n"/>
-      <c r="AH293" s="5" t="n"/>
-      <c r="AI293" s="5" t="n"/>
-      <c r="AJ293" s="5" t="n"/>
-      <c r="AK293" s="5" t="n"/>
-      <c r="AL293" s="5" t="n"/>
-      <c r="AM293" s="5" t="n"/>
+      <c r="AG293" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
+        </is>
+      </c>
+      <c r="AH293" s="5" t="inlineStr">
+        <is>
+          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
+        </is>
+      </c>
+      <c r="AI293" s="5" t="inlineStr">
+        <is>
+          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
+        </is>
+      </c>
+      <c r="AJ293" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
+        </is>
+      </c>
+      <c r="AK293" s="5" t="inlineStr">
+        <is>
+          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
+        </is>
+      </c>
+      <c r="AL293" s="5" t="inlineStr">
+        <is>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
+        </is>
+      </c>
+      <c r="AM293" s="5" t="inlineStr">
+        <is>
+          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
+        </is>
+      </c>
       <c r="AN293" s="5" t="n"/>
-      <c r="AO293" s="5" t="n"/>
+      <c r="AO293" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>us-eustis</t>
+          <t>us-day</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
+          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -34439,10 +34619,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>1595</v>
+        <v>1170</v>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1595</v>
+        <v>1170</v>
       </c>
       <c r="H294" s="3">
         <f>IF(F294=0,0,1-G294/F294)</f>
@@ -34479,7 +34659,7 @@
       </c>
       <c r="R294" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S294" s="2" t="n">
@@ -34489,11 +34669,11 @@
         <v>0</v>
       </c>
       <c r="U294" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V294" s="2" t="inlineStr">
         <is>
-          <t>Eustis</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="W294" s="2" t="inlineStr">
@@ -34518,33 +34698,69 @@
       </c>
       <c r="AA294" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-2</t>
-        </is>
-      </c>
-      <c r="AB294" s="5" t="n"/>
+          <t>reg-us-v-2-1</t>
+        </is>
+      </c>
+      <c r="AB294" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 single-window mover)</t>
+        </is>
+      </c>
       <c r="AC294" s="5" t="n"/>
       <c r="AD294" s="5" t="n"/>
       <c r="AE294" s="5" t="n"/>
       <c r="AF294" s="5" t="n"/>
-      <c r="AG294" s="5" t="n"/>
-      <c r="AH294" s="5" t="n"/>
-      <c r="AI294" s="5" t="n"/>
-      <c r="AJ294" s="5" t="n"/>
-      <c r="AK294" s="5" t="n"/>
-      <c r="AL294" s="5" t="n"/>
-      <c r="AM294" s="5" t="n"/>
+      <c r="AG294" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+        </is>
+      </c>
+      <c r="AH294" s="5" t="inlineStr">
+        <is>
+          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+        </is>
+      </c>
+      <c r="AI294" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+        </is>
+      </c>
+      <c r="AJ294" s="5" t="inlineStr">
+        <is>
+          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+        </is>
+      </c>
+      <c r="AK294" s="5" t="inlineStr">
+        <is>
+          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+        </is>
+      </c>
+      <c r="AL294" s="5" t="inlineStr">
+        <is>
+          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+        </is>
+      </c>
+      <c r="AM294" s="5" t="inlineStr">
+        <is>
+          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+        </is>
+      </c>
       <c r="AN294" s="5" t="n"/>
-      <c r="AO294" s="5" t="n"/>
+      <c r="AO294" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (thin - division-report class)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>us-fisher</t>
+          <t>us-eustis</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
+          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -34563,10 +34779,10 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="H295" s="3">
         <f>IF(F295=0,0,1-G295/F295)</f>
@@ -34603,7 +34819,7 @@
       </c>
       <c r="R295" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S295" s="2" t="n">
@@ -34617,7 +34833,7 @@
       </c>
       <c r="V295" s="2" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Eustis</t>
         </is>
       </c>
       <c r="W295" s="2" t="inlineStr">
@@ -34642,7 +34858,7 @@
       </c>
       <c r="AA295" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-2</t>
+          <t>reg-us-vi-3-2</t>
         </is>
       </c>
       <c r="AB295" s="5" t="n"/>
@@ -34663,12 +34879,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>us-fraser</t>
+          <t>us-fisher</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
+          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -34687,10 +34903,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>615</v>
+        <v>1555</v>
       </c>
       <c r="G296" s="2" t="n">
-        <v>615</v>
+        <v>1555</v>
       </c>
       <c r="H296" s="3">
         <f>IF(F296=0,0,1-G296/F296)</f>
@@ -34741,7 +34957,7 @@
       </c>
       <c r="V296" s="2" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="W296" s="2" t="inlineStr">
@@ -34766,69 +34982,33 @@
       </c>
       <c r="AA296" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-3</t>
-        </is>
-      </c>
-      <c r="AB296" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-v-3-2</t>
+        </is>
+      </c>
+      <c r="AB296" s="5" t="n"/>
       <c r="AC296" s="5" t="n"/>
       <c r="AD296" s="5" t="n"/>
       <c r="AE296" s="5" t="n"/>
       <c r="AF296" s="5" t="n"/>
-      <c r="AG296" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
-        </is>
-      </c>
-      <c r="AH296" s="5" t="inlineStr">
-        <is>
-          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
-        </is>
-      </c>
-      <c r="AI296" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~975 compilation hop-flagged</t>
-        </is>
-      </c>
-      <c r="AJ296" s="5" t="inlineStr">
-        <is>
-          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
-        </is>
-      </c>
-      <c r="AK296" s="5" t="inlineStr">
-        <is>
-          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
-        </is>
-      </c>
-      <c r="AL296" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-3 crest fight 18:15-18:45</t>
-        </is>
-      </c>
-      <c r="AM296" s="5" t="inlineStr">
-        <is>
-          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
-        </is>
-      </c>
+      <c r="AG296" s="5" t="n"/>
+      <c r="AH296" s="5" t="n"/>
+      <c r="AI296" s="5" t="n"/>
+      <c r="AJ296" s="5" t="n"/>
+      <c r="AK296" s="5" t="n"/>
+      <c r="AL296" s="5" t="n"/>
+      <c r="AM296" s="5" t="n"/>
       <c r="AN296" s="5" t="n"/>
-      <c r="AO296" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO296" s="5" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>us-garrard</t>
+          <t>us-fraser</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
+          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -34847,10 +35027,10 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>1290</v>
+        <v>615</v>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1290</v>
+        <v>615</v>
       </c>
       <c r="H297" s="3">
         <f>IF(F297=0,0,1-G297/F297)</f>
@@ -34901,7 +35081,7 @@
       </c>
       <c r="V297" s="2" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="W297" s="2" t="inlineStr">
@@ -34926,7 +35106,7 @@
       </c>
       <c r="AA297" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-3</t>
+          <t>reg-us-ii-1-3</t>
         </is>
       </c>
       <c r="AB297" s="5" t="inlineStr">
@@ -34940,37 +35120,37 @@
       <c r="AF297" s="5" t="n"/>
       <c r="AG297" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
         </is>
       </c>
       <c r="AH297" s="5" t="inlineStr">
         <is>
-          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
         </is>
       </c>
       <c r="AI297" s="5" t="inlineStr">
         <is>
-          <t>no brigade primary (open; compilation tier)</t>
+          <t>no primary (negative); ~975 compilation hop-flagged</t>
         </is>
       </c>
       <c r="AJ297" s="5" t="inlineStr">
         <is>
-          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
         </is>
       </c>
       <c r="AK297" s="5" t="inlineStr">
         <is>
-          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
         </is>
       </c>
       <c r="AL297" s="5" t="inlineStr">
         <is>
-          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+          <t>[D] wave-3 crest fight 18:15-18:45</t>
         </is>
       </c>
       <c r="AM297" s="5" t="inlineStr">
         <is>
-          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
+          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AN297" s="5" t="n"/>
@@ -34983,12 +35163,12 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>us-grant</t>
+          <t>us-garrard</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
+          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -35007,10 +35187,10 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>1830</v>
+        <v>1290</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>1830</v>
+        <v>1290</v>
       </c>
       <c r="H298" s="3">
         <f>IF(F298=0,0,1-G298/F298)</f>
@@ -35061,7 +35241,7 @@
       </c>
       <c r="V298" s="2" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="W298" s="2" t="inlineStr">
@@ -35086,33 +35266,69 @@
       </c>
       <c r="AA298" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-1</t>
-        </is>
-      </c>
-      <c r="AB298" s="5" t="n"/>
+          <t>reg-us-v-2-3</t>
+        </is>
+      </c>
+      <c r="AB298" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC298" s="5" t="n"/>
       <c r="AD298" s="5" t="n"/>
       <c r="AE298" s="5" t="n"/>
       <c r="AF298" s="5" t="n"/>
-      <c r="AG298" s="5" t="n"/>
-      <c r="AH298" s="5" t="n"/>
-      <c r="AI298" s="5" t="n"/>
-      <c r="AJ298" s="5" t="n"/>
-      <c r="AK298" s="5" t="n"/>
-      <c r="AL298" s="5" t="n"/>
-      <c r="AM298" s="5" t="n"/>
+      <c r="AG298" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+        </is>
+      </c>
+      <c r="AH298" s="5" t="inlineStr">
+        <is>
+          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+        </is>
+      </c>
+      <c r="AI298" s="5" t="inlineStr">
+        <is>
+          <t>no brigade primary (open; compilation tier)</t>
+        </is>
+      </c>
+      <c r="AJ298" s="5" t="inlineStr">
+        <is>
+          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+        </is>
+      </c>
+      <c r="AK298" s="5" t="inlineStr">
+        <is>
+          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+        </is>
+      </c>
+      <c r="AL298" s="5" t="inlineStr">
+        <is>
+          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+        </is>
+      </c>
+      <c r="AM298" s="5" t="inlineStr">
+        <is>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
+        </is>
+      </c>
       <c r="AN298" s="5" t="n"/>
-      <c r="AO298" s="5" t="n"/>
+      <c r="AO298" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>us-greene</t>
+          <t>us-grant</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
+          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -35131,10 +35347,10 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>1125</v>
+        <v>1830</v>
       </c>
       <c r="G299" s="2" t="n">
-        <v>1125</v>
+        <v>1830</v>
       </c>
       <c r="H299" s="3">
         <f>IF(F299=0,0,1-G299/F299)</f>
@@ -35185,7 +35401,7 @@
       </c>
       <c r="V299" s="2" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="W299" s="2" t="inlineStr">
@@ -35210,7 +35426,7 @@
       </c>
       <c r="AA299" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-3</t>
+          <t>reg-us-vi-2-1</t>
         </is>
       </c>
       <c r="AB299" s="5" t="n"/>
@@ -35231,12 +35447,12 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>us-harris</t>
+          <t>us-greene</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
+          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -35255,10 +35471,10 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>565</v>
+        <v>1125</v>
       </c>
       <c r="G300" s="2" t="n">
-        <v>565</v>
+        <v>1125</v>
       </c>
       <c r="H300" s="3">
         <f>IF(F300=0,0,1-G300/F300)</f>
@@ -35305,11 +35521,11 @@
         <v>0</v>
       </c>
       <c r="U300" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V300" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Greene</t>
         </is>
       </c>
       <c r="W300" s="2" t="inlineStr">
@@ -35334,7 +35550,7 @@
       </c>
       <c r="AA300" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-2</t>
+          <t>reg-us-xii-2-3</t>
         </is>
       </c>
       <c r="AB300" s="5" t="n"/>
@@ -35355,12 +35571,12 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>us-harrow</t>
+          <t>us-harris</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Harrow's Brigade</t>
+          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -35379,76 +35595,76 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>1410</v>
+        <v>565</v>
       </c>
       <c r="G301" s="2" t="n">
-        <v>630</v>
+        <v>565</v>
       </c>
       <c r="H301" s="3">
         <f>IF(F301=0,0,1-G301/F301)</f>
         <v/>
       </c>
       <c r="I301" s="2" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L301" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M301" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N301" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>121.7</v>
+        <v>0</v>
       </c>
       <c r="P301" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V301" s="2" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="W301" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R301" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S301" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T301" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U301" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V301" s="2" t="inlineStr">
-        <is>
-          <t>Harrow</t>
-        </is>
-      </c>
-      <c r="W301" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
@@ -35458,69 +35674,33 @@
       </c>
       <c r="AA301" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-1</t>
-        </is>
-      </c>
-      <c r="AB301" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (crisis incline-right)</t>
-        </is>
-      </c>
+          <t>reg-us-xi-1-2</t>
+        </is>
+      </c>
+      <c r="AB301" s="5" t="n"/>
       <c r="AC301" s="5" t="n"/>
       <c r="AD301" s="5" t="n"/>
       <c r="AE301" s="5" t="n"/>
       <c r="AF301" s="5" t="n"/>
-      <c r="AG301" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
-        </is>
-      </c>
-      <c r="AH301" s="5" t="inlineStr">
-        <is>
-          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
-        </is>
-      </c>
-      <c r="AI301" s="5" t="inlineStr">
-        <is>
-          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
-        </is>
-      </c>
-      <c r="AJ301" s="5" t="inlineStr">
-        <is>
-          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
-        </is>
-      </c>
-      <c r="AK301" s="5" t="inlineStr">
-        <is>
-          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
-        </is>
-      </c>
-      <c r="AL301" s="5" t="inlineStr">
-        <is>
-          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
-        </is>
-      </c>
-      <c r="AM301" s="5" t="inlineStr">
-        <is>
-          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
-        </is>
-      </c>
+      <c r="AG301" s="5" t="n"/>
+      <c r="AH301" s="5" t="n"/>
+      <c r="AI301" s="5" t="n"/>
+      <c r="AJ301" s="5" t="n"/>
+      <c r="AK301" s="5" t="n"/>
+      <c r="AL301" s="5" t="n"/>
+      <c r="AM301" s="5" t="n"/>
       <c r="AN301" s="5" t="n"/>
-      <c r="AO301" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>us-kane</t>
+          <t>us-harrow</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
+          <t>Harrow's Brigade</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -35539,42 +35719,42 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>600</v>
+        <v>1410</v>
       </c>
       <c r="G302" s="2" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="H302" s="3">
         <f>IF(F302=0,0,1-G302/F302)</f>
         <v/>
       </c>
       <c r="I302" s="2" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L302" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M302" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N302" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>0</v>
+        <v>121.7</v>
       </c>
       <c r="P302" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R302" s="2" t="inlineStr">
@@ -35583,17 +35763,17 @@
         </is>
       </c>
       <c r="S302" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T302" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U302" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V302" s="2" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="W302" s="2" t="inlineStr">
@@ -35603,12 +35783,12 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
@@ -35618,33 +35798,69 @@
       </c>
       <c r="AA302" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-2</t>
-        </is>
-      </c>
-      <c r="AB302" s="5" t="n"/>
+          <t>reg-us-ii-2-1</t>
+        </is>
+      </c>
+      <c r="AB302" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (crisis incline-right)</t>
+        </is>
+      </c>
       <c r="AC302" s="5" t="n"/>
       <c r="AD302" s="5" t="n"/>
       <c r="AE302" s="5" t="n"/>
       <c r="AF302" s="5" t="n"/>
-      <c r="AG302" s="5" t="n"/>
-      <c r="AH302" s="5" t="n"/>
-      <c r="AI302" s="5" t="n"/>
-      <c r="AJ302" s="5" t="n"/>
-      <c r="AK302" s="5" t="n"/>
-      <c r="AL302" s="5" t="n"/>
-      <c r="AM302" s="5" t="n"/>
+      <c r="AG302" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
+        </is>
+      </c>
+      <c r="AH302" s="5" t="inlineStr">
+        <is>
+          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
+        </is>
+      </c>
+      <c r="AI302" s="5" t="inlineStr">
+        <is>
+          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
+        </is>
+      </c>
+      <c r="AJ302" s="5" t="inlineStr">
+        <is>
+          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
+        </is>
+      </c>
+      <c r="AK302" s="5" t="inlineStr">
+        <is>
+          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
+        </is>
+      </c>
+      <c r="AL302" s="5" t="inlineStr">
+        <is>
+          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
+        </is>
+      </c>
+      <c r="AM302" s="5" t="inlineStr">
+        <is>
+          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
+        </is>
+      </c>
       <c r="AN302" s="5" t="n"/>
-      <c r="AO302" s="5" t="n"/>
+      <c r="AO302" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>us-kelly</t>
+          <t>us-kane</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
+          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -35663,10 +35879,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="H303" s="3">
         <f>IF(F303=0,0,1-G303/F303)</f>
@@ -35717,7 +35933,7 @@
       </c>
       <c r="V303" s="2" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="W303" s="2" t="inlineStr">
@@ -35742,69 +35958,33 @@
       </c>
       <c r="AA303" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-2</t>
-        </is>
-      </c>
-      <c r="AB303" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-xii-2-2</t>
+        </is>
+      </c>
+      <c r="AB303" s="5" t="n"/>
       <c r="AC303" s="5" t="n"/>
       <c r="AD303" s="5" t="n"/>
       <c r="AE303" s="5" t="n"/>
       <c r="AF303" s="5" t="n"/>
-      <c r="AG303" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
-        </is>
-      </c>
-      <c r="AH303" s="5" t="inlineStr">
-        <is>
-          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
-        </is>
-      </c>
-      <c r="AI303" s="5" t="inlineStr">
-        <is>
-          <t>530 into action PRIMARY (Kelly)</t>
-        </is>
-      </c>
-      <c r="AJ303" s="5" t="inlineStr">
-        <is>
-          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
-        </is>
-      </c>
-      <c r="AK303" s="5" t="inlineStr">
-        <is>
-          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
-        </is>
-      </c>
-      <c r="AL303" s="5" t="inlineStr">
-        <is>
-          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
-        </is>
-      </c>
-      <c r="AM303" s="5" t="inlineStr">
-        <is>
-          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
-        </is>
-      </c>
+      <c r="AG303" s="5" t="n"/>
+      <c r="AH303" s="5" t="n"/>
+      <c r="AI303" s="5" t="n"/>
+      <c r="AJ303" s="5" t="n"/>
+      <c r="AK303" s="5" t="n"/>
+      <c r="AL303" s="5" t="n"/>
+      <c r="AM303" s="5" t="n"/>
       <c r="AN303" s="5" t="n"/>
-      <c r="AO303" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO303" s="5" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>us-krzyzanowski</t>
+          <t>us-kelly</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
+          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -35823,10 +36003,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>750</v>
+        <v>330</v>
       </c>
       <c r="G304" s="2" t="n">
-        <v>750</v>
+        <v>330</v>
       </c>
       <c r="H304" s="3">
         <f>IF(F304=0,0,1-G304/F304)</f>
@@ -35877,7 +36057,7 @@
       </c>
       <c r="V304" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="W304" s="2" t="inlineStr">
@@ -35902,33 +36082,69 @@
       </c>
       <c r="AA304" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-2</t>
-        </is>
-      </c>
-      <c r="AB304" s="5" t="n"/>
+          <t>reg-us-ii-1-2</t>
+        </is>
+      </c>
+      <c r="AB304" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC304" s="5" t="n"/>
       <c r="AD304" s="5" t="n"/>
       <c r="AE304" s="5" t="n"/>
       <c r="AF304" s="5" t="n"/>
-      <c r="AG304" s="5" t="n"/>
-      <c r="AH304" s="5" t="n"/>
-      <c r="AI304" s="5" t="n"/>
-      <c r="AJ304" s="5" t="n"/>
-      <c r="AK304" s="5" t="n"/>
-      <c r="AL304" s="5" t="n"/>
-      <c r="AM304" s="5" t="n"/>
+      <c r="AG304" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
+        </is>
+      </c>
+      <c r="AH304" s="5" t="inlineStr">
+        <is>
+          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
+        </is>
+      </c>
+      <c r="AI304" s="5" t="inlineStr">
+        <is>
+          <t>530 into action PRIMARY (Kelly)</t>
+        </is>
+      </c>
+      <c r="AJ304" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
+        </is>
+      </c>
+      <c r="AK304" s="5" t="inlineStr">
+        <is>
+          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
+        </is>
+      </c>
+      <c r="AL304" s="5" t="inlineStr">
+        <is>
+          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
+        </is>
+      </c>
+      <c r="AM304" s="5" t="inlineStr">
+        <is>
+          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
+        </is>
+      </c>
       <c r="AN304" s="5" t="n"/>
-      <c r="AO304" s="5" t="n"/>
+      <c r="AO304" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>us-lockwood</t>
+          <t>us-krzyzanowski</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
+          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -35947,10 +36163,10 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>1650</v>
+        <v>750</v>
       </c>
       <c r="G305" s="2" t="n">
-        <v>1650</v>
+        <v>750</v>
       </c>
       <c r="H305" s="3">
         <f>IF(F305=0,0,1-G305/F305)</f>
@@ -36001,7 +36217,7 @@
       </c>
       <c r="V305" s="2" t="inlineStr">
         <is>
-          <t>Lockwood</t>
+          <t>Krzyżanowski</t>
         </is>
       </c>
       <c r="W305" s="2" t="inlineStr">
@@ -36026,7 +36242,7 @@
       </c>
       <c r="AA305" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-2</t>
+          <t>reg-us-xi-3-2</t>
         </is>
       </c>
       <c r="AB305" s="5" t="n"/>
@@ -36047,12 +36263,12 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>us-madill</t>
+          <t>us-lockwood</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
+          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -36071,10 +36287,10 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>775</v>
+        <v>1650</v>
       </c>
       <c r="G306" s="2" t="n">
-        <v>775</v>
+        <v>1650</v>
       </c>
       <c r="H306" s="3">
         <f>IF(F306=0,0,1-G306/F306)</f>
@@ -36111,7 +36327,7 @@
       </c>
       <c r="R306" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S306" s="2" t="n">
@@ -36125,7 +36341,7 @@
       </c>
       <c r="V306" s="2" t="inlineStr">
         <is>
-          <t>Madill</t>
+          <t>Lockwood</t>
         </is>
       </c>
       <c r="W306" s="2" t="inlineStr">
@@ -36150,7 +36366,7 @@
       </c>
       <c r="AA306" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-1</t>
+          <t>reg-us-xii-1-2</t>
         </is>
       </c>
       <c r="AB306" s="5" t="n"/>
@@ -36171,12 +36387,12 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>us-mccandless</t>
+          <t>us-madill</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
+          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -36195,10 +36411,10 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>1095</v>
+        <v>775</v>
       </c>
       <c r="G307" s="2" t="n">
-        <v>1095</v>
+        <v>775</v>
       </c>
       <c r="H307" s="3">
         <f>IF(F307=0,0,1-G307/F307)</f>
@@ -36235,7 +36451,7 @@
       </c>
       <c r="R307" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S307" s="2" t="n">
@@ -36249,7 +36465,7 @@
       </c>
       <c r="V307" s="2" t="inlineStr">
         <is>
-          <t>McCandless</t>
+          <t>Madill</t>
         </is>
       </c>
       <c r="W307" s="2" t="inlineStr">
@@ -36274,33 +36490,69 @@
       </c>
       <c r="AA307" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-1</t>
-        </is>
-      </c>
-      <c r="AB307" s="5" t="n"/>
+          <t>reg-us-iii-1-1</t>
+        </is>
+      </c>
+      <c r="AB307" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 static-then-forced-back)</t>
+        </is>
+      </c>
       <c r="AC307" s="5" t="n"/>
       <c r="AD307" s="5" t="n"/>
       <c r="AE307" s="5" t="n"/>
       <c r="AF307" s="5" t="n"/>
-      <c r="AG307" s="5" t="n"/>
-      <c r="AH307" s="5" t="n"/>
-      <c r="AI307" s="5" t="n"/>
-      <c r="AJ307" s="5" t="n"/>
-      <c r="AK307" s="5" t="n"/>
-      <c r="AL307" s="5" t="n"/>
-      <c r="AM307" s="5" t="n"/>
+      <c r="AG307" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
+        </is>
+      </c>
+      <c r="AH307" s="5" t="inlineStr">
+        <is>
+          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
+        </is>
+      </c>
+      <c r="AI307" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
+        </is>
+      </c>
+      <c r="AJ307" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
+        </is>
+      </c>
+      <c r="AK307" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
+        </is>
+      </c>
+      <c r="AL307" s="5" t="inlineStr">
+        <is>
+          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
+        </is>
+      </c>
+      <c r="AM307" s="5" t="inlineStr">
+        <is>
+          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
+        </is>
+      </c>
       <c r="AN307" s="5" t="n"/>
-      <c r="AO307" s="5" t="n"/>
+      <c r="AO307" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>us-mcdougall</t>
+          <t>us-mccandless</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
+          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -36319,10 +36571,10 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>1755</v>
+        <v>1095</v>
       </c>
       <c r="G308" s="2" t="n">
-        <v>1755</v>
+        <v>1095</v>
       </c>
       <c r="H308" s="3">
         <f>IF(F308=0,0,1-G308/F308)</f>
@@ -36373,7 +36625,7 @@
       </c>
       <c r="V308" s="2" t="inlineStr">
         <is>
-          <t>McDougall</t>
+          <t>McCandless</t>
         </is>
       </c>
       <c r="W308" s="2" t="inlineStr">
@@ -36398,33 +36650,69 @@
       </c>
       <c r="AA308" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-1</t>
-        </is>
-      </c>
-      <c r="AB308" s="5" t="n"/>
+          <t>reg-us-v-3-1</t>
+        </is>
+      </c>
+      <c r="AB308" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
+        </is>
+      </c>
       <c r="AC308" s="5" t="n"/>
       <c r="AD308" s="5" t="n"/>
       <c r="AE308" s="5" t="n"/>
       <c r="AF308" s="5" t="n"/>
-      <c r="AG308" s="5" t="n"/>
-      <c r="AH308" s="5" t="n"/>
-      <c r="AI308" s="5" t="n"/>
-      <c r="AJ308" s="5" t="n"/>
-      <c r="AK308" s="5" t="n"/>
-      <c r="AL308" s="5" t="n"/>
-      <c r="AM308" s="5" t="n"/>
+      <c r="AG308" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
+        </is>
+      </c>
+      <c r="AH308" s="5" t="inlineStr">
+        <is>
+          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
+        </is>
+      </c>
+      <c r="AI308" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
+        </is>
+      </c>
+      <c r="AJ308" s="5" t="inlineStr">
+        <is>
+          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
+        </is>
+      </c>
+      <c r="AK308" s="5" t="inlineStr">
+        <is>
+          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
+        </is>
+      </c>
+      <c r="AL308" s="5" t="inlineStr">
+        <is>
+          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
+        </is>
+      </c>
+      <c r="AM308" s="5" t="inlineStr">
+        <is>
+          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
+        </is>
+      </c>
       <c r="AN308" s="5" t="n"/>
-      <c r="AO308" s="5" t="n"/>
+      <c r="AO308" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>us-mckeen</t>
+          <t>us-mcdougall</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
+          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -36443,10 +36731,10 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>520</v>
+        <v>1755</v>
       </c>
       <c r="G309" s="2" t="n">
-        <v>520</v>
+        <v>1755</v>
       </c>
       <c r="H309" s="3">
         <f>IF(F309=0,0,1-G309/F309)</f>
@@ -36497,7 +36785,7 @@
       </c>
       <c r="V309" s="2" t="inlineStr">
         <is>
-          <t>McKeen</t>
+          <t>McDougall</t>
         </is>
       </c>
       <c r="W309" s="2" t="inlineStr">
@@ -36522,69 +36810,33 @@
       </c>
       <c r="AA309" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-1</t>
-        </is>
-      </c>
-      <c r="AB309" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-xii-1-1</t>
+        </is>
+      </c>
+      <c r="AB309" s="5" t="n"/>
       <c r="AC309" s="5" t="n"/>
       <c r="AD309" s="5" t="n"/>
       <c r="AE309" s="5" t="n"/>
       <c r="AF309" s="5" t="n"/>
-      <c r="AG309" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
-        </is>
-      </c>
-      <c r="AH309" s="5" t="inlineStr">
-        <is>
-          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
-        </is>
-      </c>
-      <c r="AI309" s="5" t="inlineStr">
-        <is>
-          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
-        </is>
-      </c>
-      <c r="AJ309" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
-        </is>
-      </c>
-      <c r="AK309" s="5" t="inlineStr">
-        <is>
-          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
-        </is>
-      </c>
-      <c r="AL309" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
-        </is>
-      </c>
-      <c r="AM309" s="5" t="inlineStr">
-        <is>
-          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
-        </is>
-      </c>
+      <c r="AG309" s="5" t="n"/>
+      <c r="AH309" s="5" t="n"/>
+      <c r="AI309" s="5" t="n"/>
+      <c r="AJ309" s="5" t="n"/>
+      <c r="AK309" s="5" t="n"/>
+      <c r="AL309" s="5" t="n"/>
+      <c r="AM309" s="5" t="n"/>
       <c r="AN309" s="5" t="n"/>
-      <c r="AO309" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO309" s="5" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>us-meredith</t>
+          <t>us-mckeen</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
+          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -36603,10 +36855,10 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="G310" s="2" t="n">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="H310" s="3">
         <f>IF(F310=0,0,1-G310/F310)</f>
@@ -36657,7 +36909,7 @@
       </c>
       <c r="V310" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>McKeen</t>
         </is>
       </c>
       <c r="W310" s="2" t="inlineStr">
@@ -36682,33 +36934,69 @@
       </c>
       <c r="AA310" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-1</t>
-        </is>
-      </c>
-      <c r="AB310" s="5" t="n"/>
+          <t>reg-us-ii-1-1</t>
+        </is>
+      </c>
+      <c r="AB310" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC310" s="5" t="n"/>
       <c r="AD310" s="5" t="n"/>
       <c r="AE310" s="5" t="n"/>
       <c r="AF310" s="5" t="n"/>
-      <c r="AG310" s="5" t="n"/>
-      <c r="AH310" s="5" t="n"/>
-      <c r="AI310" s="5" t="n"/>
-      <c r="AJ310" s="5" t="n"/>
-      <c r="AK310" s="5" t="n"/>
-      <c r="AL310" s="5" t="n"/>
-      <c r="AM310" s="5" t="n"/>
+      <c r="AG310" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+        </is>
+      </c>
+      <c r="AH310" s="5" t="inlineStr">
+        <is>
+          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+        </is>
+      </c>
+      <c r="AI310" s="5" t="inlineStr">
+        <is>
+          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+        </is>
+      </c>
+      <c r="AJ310" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+        </is>
+      </c>
+      <c r="AK310" s="5" t="inlineStr">
+        <is>
+          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+        </is>
+      </c>
+      <c r="AL310" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+        </is>
+      </c>
+      <c r="AM310" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+        </is>
+      </c>
       <c r="AN310" s="5" t="n"/>
-      <c r="AO310" s="5" t="n"/>
+      <c r="AO310" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>us-neill</t>
+          <t>us-meredith</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
+          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -36727,10 +37015,10 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>1775</v>
+        <v>730</v>
       </c>
       <c r="G311" s="2" t="n">
-        <v>1775</v>
+        <v>730</v>
       </c>
       <c r="H311" s="3">
         <f>IF(F311=0,0,1-G311/F311)</f>
@@ -36771,7 +37059,7 @@
         </is>
       </c>
       <c r="S311" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T311" s="2" t="n">
         <v>0</v>
@@ -36781,7 +37069,7 @@
       </c>
       <c r="V311" s="2" t="inlineStr">
         <is>
-          <t>Neill</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="W311" s="2" t="inlineStr">
@@ -36796,7 +37084,7 @@
       </c>
       <c r="Y311" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z311" s="2" t="inlineStr">
@@ -36806,7 +37094,7 @@
       </c>
       <c r="AA311" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-2</t>
+          <t>reg-us-i-1-1</t>
         </is>
       </c>
       <c r="AB311" s="5" t="n"/>
@@ -36827,12 +37115,12 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>us-nevin</t>
+          <t>us-neill</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
+          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -36851,10 +37139,10 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>1370</v>
+        <v>1775</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>1370</v>
+        <v>1775</v>
       </c>
       <c r="H312" s="3">
         <f>IF(F312=0,0,1-G312/F312)</f>
@@ -36895,7 +37183,7 @@
         </is>
       </c>
       <c r="S312" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T312" s="2" t="n">
         <v>0</v>
@@ -36905,7 +37193,7 @@
       </c>
       <c r="V312" s="2" t="inlineStr">
         <is>
-          <t>Nevin</t>
+          <t>Neill</t>
         </is>
       </c>
       <c r="W312" s="2" t="inlineStr">
@@ -36920,7 +37208,7 @@
       </c>
       <c r="Y312" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z312" s="2" t="inlineStr">
@@ -36930,7 +37218,7 @@
       </c>
       <c r="AA312" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-3</t>
+          <t>reg-us-vi-2-2</t>
         </is>
       </c>
       <c r="AB312" s="5" t="n"/>
@@ -36951,12 +37239,12 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>us-rice</t>
+          <t>us-nevin</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
+          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -36975,10 +37263,10 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>985</v>
+        <v>1370</v>
       </c>
       <c r="G313" s="2" t="n">
-        <v>985</v>
+        <v>1370</v>
       </c>
       <c r="H313" s="3">
         <f>IF(F313=0,0,1-G313/F313)</f>
@@ -37029,7 +37317,7 @@
       </c>
       <c r="V313" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Nevin</t>
         </is>
       </c>
       <c r="W313" s="2" t="inlineStr">
@@ -37054,12 +37342,12 @@
       </c>
       <c r="AA313" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-3</t>
+          <t>reg-us-vi-3-3</t>
         </is>
       </c>
       <c r="AB313" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+          <t>authored-ok (July 2 W5 executor)</t>
         </is>
       </c>
       <c r="AC313" s="5" t="n"/>
@@ -37068,37 +37356,37 @@
       <c r="AF313" s="5" t="n"/>
       <c r="AG313" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposes ED-61 (Plum Run gun-recovery cross-credit; precondition Bigelow/Watson fetches)</t>
         </is>
       </c>
       <c r="AH313" s="5" t="inlineStr">
         <is>
-          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
         </is>
       </c>
       <c r="AI313" s="5" t="inlineStr">
         <is>
-          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
         </is>
       </c>
       <c r="AJ313" s="5" t="inlineStr">
         <is>
-          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
         </is>
       </c>
       <c r="AK313" s="5" t="inlineStr">
         <is>
-          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
         </is>
       </c>
       <c r="AL313" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
         </is>
       </c>
       <c r="AM313" s="5" t="inlineStr">
         <is>
-          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+          <t>tablet 53 (2k/7+44w, no missing); Union-return row UNFETCHED (p. 181 region, flagged) - tablet is the working reading; two-episode light shape</t>
         </is>
       </c>
       <c r="AN313" s="5" t="n"/>
@@ -37111,12 +37399,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>us-russell</t>
+          <t>us-rice</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
+          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -37135,10 +37423,10 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>1480</v>
+        <v>985</v>
       </c>
       <c r="G314" s="2" t="n">
-        <v>1480</v>
+        <v>985</v>
       </c>
       <c r="H314" s="3">
         <f>IF(F314=0,0,1-G314/F314)</f>
@@ -37189,7 +37477,7 @@
       </c>
       <c r="V314" s="2" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="W314" s="2" t="inlineStr">
@@ -37214,33 +37502,69 @@
       </c>
       <c r="AA314" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-3</t>
-        </is>
-      </c>
-      <c r="AB314" s="5" t="n"/>
+          <t>reg-us-v-1-3</t>
+        </is>
+      </c>
+      <c r="AB314" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+        </is>
+      </c>
       <c r="AC314" s="5" t="n"/>
       <c r="AD314" s="5" t="n"/>
       <c r="AE314" s="5" t="n"/>
       <c r="AF314" s="5" t="n"/>
-      <c r="AG314" s="5" t="n"/>
-      <c r="AH314" s="5" t="n"/>
-      <c r="AI314" s="5" t="n"/>
-      <c r="AJ314" s="5" t="n"/>
-      <c r="AK314" s="5" t="n"/>
-      <c r="AL314" s="5" t="n"/>
-      <c r="AM314" s="5" t="n"/>
+      <c r="AG314" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+        </is>
+      </c>
+      <c r="AH314" s="5" t="inlineStr">
+        <is>
+          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+        </is>
+      </c>
+      <c r="AI314" s="5" t="inlineStr">
+        <is>
+          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+        </is>
+      </c>
+      <c r="AJ314" s="5" t="inlineStr">
+        <is>
+          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+        </is>
+      </c>
+      <c r="AK314" s="5" t="inlineStr">
+        <is>
+          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+        </is>
+      </c>
+      <c r="AL314" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+        </is>
+      </c>
+      <c r="AM314" s="5" t="inlineStr">
+        <is>
+          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+        </is>
+      </c>
       <c r="AN314" s="5" t="n"/>
-      <c r="AO314" s="5" t="n"/>
+      <c r="AO314" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>us-shaler</t>
+          <t>us-russell</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
+          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -37259,10 +37583,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>1770</v>
+        <v>1480</v>
       </c>
       <c r="G315" s="2" t="n">
-        <v>1770</v>
+        <v>1480</v>
       </c>
       <c r="H315" s="3">
         <f>IF(F315=0,0,1-G315/F315)</f>
@@ -37272,34 +37596,34 @@
         <v>0</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K315" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L315" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M315" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N315" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="P315" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="Q315" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R315" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S315" s="2" t="n">
@@ -37313,7 +37637,7 @@
       </c>
       <c r="V315" s="2" t="inlineStr">
         <is>
-          <t>Shaler</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="W315" s="2" t="inlineStr">
@@ -37323,12 +37647,12 @@
       </c>
       <c r="X315" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y315" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z315" s="2" t="inlineStr">
@@ -37338,7 +37662,7 @@
       </c>
       <c r="AA315" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-1</t>
+          <t>reg-us-vi-1-3</t>
         </is>
       </c>
       <c r="AB315" s="5" t="n"/>
@@ -37359,12 +37683,12 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>us-sherrill</t>
+          <t>us-shaler</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Sherrill's Brigade (Willard's)</t>
+          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -37383,61 +37707,61 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1510</v>
+        <v>1770</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>800</v>
+        <v>1770</v>
       </c>
       <c r="H316" s="3">
         <f>IF(F316=0,0,1-G316/F316)</f>
         <v/>
       </c>
       <c r="I316" s="2" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K316" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L316" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M316" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N316" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>0</v>
+        <v>1210.8</v>
       </c>
       <c r="P316" s="2" t="n">
-        <v>0</v>
+        <v>1210.8</v>
       </c>
       <c r="Q316" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R316" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S316" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T316" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U316" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T316" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U316" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="V316" s="2" t="inlineStr">
         <is>
-          <t>Sherrill</t>
+          <t>Shaler</t>
         </is>
       </c>
       <c r="W316" s="2" t="inlineStr">
@@ -37452,7 +37776,7 @@
       </c>
       <c r="Y316" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z316" s="2" t="inlineStr">
@@ -37462,69 +37786,33 @@
       </c>
       <c r="AA316" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-3</t>
-        </is>
-      </c>
-      <c r="AB316" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (one in-window leg)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-3-1</t>
+        </is>
+      </c>
+      <c r="AB316" s="5" t="n"/>
       <c r="AC316" s="5" t="n"/>
       <c r="AD316" s="5" t="n"/>
       <c r="AE316" s="5" t="n"/>
       <c r="AF316" s="5" t="n"/>
-      <c r="AG316" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
-        </is>
-      </c>
-      <c r="AH316" s="5" t="inlineStr">
-        <is>
-          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
-        </is>
-      </c>
-      <c r="AI316" s="5" t="inlineStr">
-        <is>
-          <t>1,510 (build compilation, hop flagged)</t>
-        </is>
-      </c>
-      <c r="AJ316" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
-        </is>
-      </c>
-      <c r="AK316" s="5" t="inlineStr">
-        <is>
-          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
-        </is>
-      </c>
-      <c r="AL316" s="5" t="inlineStr">
-        <is>
-          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
-        </is>
-      </c>
-      <c r="AM316" s="5" t="inlineStr">
-        <is>
-          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
-        </is>
-      </c>
+      <c r="AG316" s="5" t="n"/>
+      <c r="AH316" s="5" t="n"/>
+      <c r="AI316" s="5" t="n"/>
+      <c r="AJ316" s="5" t="n"/>
+      <c r="AK316" s="5" t="n"/>
+      <c r="AL316" s="5" t="n"/>
+      <c r="AM316" s="5" t="n"/>
       <c r="AN316" s="5" t="n"/>
-      <c r="AO316" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AO316" s="5" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>us-smith</t>
+          <t>us-sherrill</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
+          <t>Sherrill's Brigade (Willard's)</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -37543,32 +37831,32 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>1290</v>
+        <v>1510</v>
       </c>
       <c r="G317" s="2" t="n">
-        <v>1290</v>
+        <v>800</v>
       </c>
       <c r="H317" s="3">
         <f>IF(F317=0,0,1-G317/F317)</f>
         <v/>
       </c>
       <c r="I317" s="2" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="J317" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L317" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M317" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N317" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>0</v>
@@ -37587,17 +37875,17 @@
         </is>
       </c>
       <c r="S317" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T317" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U317" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V317" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Sherrill</t>
         </is>
       </c>
       <c r="W317" s="2" t="inlineStr">
@@ -37607,12 +37895,12 @@
       </c>
       <c r="X317" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z317" s="2" t="inlineStr">
@@ -37622,33 +37910,69 @@
       </c>
       <c r="AA317" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-2</t>
-        </is>
-      </c>
-      <c r="AB317" s="5" t="n"/>
+          <t>reg-us-ii-3-3</t>
+        </is>
+      </c>
+      <c r="AB317" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (one in-window leg)</t>
+        </is>
+      </c>
       <c r="AC317" s="5" t="n"/>
       <c r="AD317" s="5" t="n"/>
       <c r="AE317" s="5" t="n"/>
       <c r="AF317" s="5" t="n"/>
-      <c r="AG317" s="5" t="n"/>
-      <c r="AH317" s="5" t="n"/>
-      <c r="AI317" s="5" t="n"/>
-      <c r="AJ317" s="5" t="n"/>
-      <c r="AK317" s="5" t="n"/>
-      <c r="AL317" s="5" t="n"/>
-      <c r="AM317" s="5" t="n"/>
+      <c r="AG317" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
+        </is>
+      </c>
+      <c r="AH317" s="5" t="inlineStr">
+        <is>
+          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
+        </is>
+      </c>
+      <c r="AI317" s="5" t="inlineStr">
+        <is>
+          <t>1,510 (build compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ317" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
+        </is>
+      </c>
+      <c r="AK317" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
+        </is>
+      </c>
+      <c r="AL317" s="5" t="inlineStr">
+        <is>
+          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
+        </is>
+      </c>
+      <c r="AM317" s="5" t="inlineStr">
+        <is>
+          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
+        </is>
+      </c>
       <c r="AN317" s="5" t="n"/>
-      <c r="AO317" s="5" t="n"/>
+      <c r="AO317" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>us-smyth</t>
+          <t>us-smith</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Smyth's Brigade</t>
+          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -37667,32 +37991,32 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>825</v>
+        <v>1290</v>
       </c>
       <c r="H318" s="3">
         <f>IF(F318=0,0,1-G318/F318)</f>
         <v/>
       </c>
       <c r="I318" s="2" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K318" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L318" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M318" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N318" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O318" s="2" t="n">
         <v>0</v>
@@ -37711,17 +38035,17 @@
         </is>
       </c>
       <c r="S318" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T318" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U318" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V318" s="2" t="inlineStr">
         <is>
-          <t>Smyth</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="W318" s="2" t="inlineStr">
@@ -37731,12 +38055,12 @@
       </c>
       <c r="X318" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y318" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z318" s="2" t="inlineStr">
@@ -37746,69 +38070,33 @@
       </c>
       <c r="AA318" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-2</t>
-        </is>
-      </c>
-      <c r="AB318" s="5" t="inlineStr">
-        <is>
-          <t>attested-static (July 2-4 wall line)</t>
-        </is>
-      </c>
+          <t>reg-us-xi-2-2</t>
+        </is>
+      </c>
+      <c r="AB318" s="5" t="n"/>
       <c r="AC318" s="5" t="n"/>
       <c r="AD318" s="5" t="n"/>
       <c r="AE318" s="5" t="n"/>
       <c r="AF318" s="5" t="n"/>
-      <c r="AG318" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
-        </is>
-      </c>
-      <c r="AH318" s="5" t="inlineStr">
-        <is>
-          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
-        </is>
-      </c>
-      <c r="AI318" s="5" t="inlineStr">
-        <is>
-          <t>1,190 (build compilation, hop flagged; no primary)</t>
-        </is>
-      </c>
-      <c r="AJ318" s="5" t="inlineStr">
-        <is>
-          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
-        </is>
-      </c>
-      <c r="AK318" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
-        </is>
-      </c>
-      <c r="AL318" s="5" t="inlineStr">
-        <is>
-          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
-        </is>
-      </c>
-      <c r="AM318" s="5" t="inlineStr">
-        <is>
-          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
-        </is>
-      </c>
+      <c r="AG318" s="5" t="n"/>
+      <c r="AH318" s="5" t="n"/>
+      <c r="AI318" s="5" t="n"/>
+      <c r="AJ318" s="5" t="n"/>
+      <c r="AK318" s="5" t="n"/>
+      <c r="AL318" s="5" t="n"/>
+      <c r="AM318" s="5" t="n"/>
       <c r="AN318" s="5" t="n"/>
-      <c r="AO318" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AO318" s="5" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>us-sweitzer</t>
+          <t>us-smyth</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
+          <t>Smyth's Brigade</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -37827,32 +38115,32 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>995</v>
+        <v>1190</v>
       </c>
       <c r="G319" s="2" t="n">
-        <v>995</v>
+        <v>825</v>
       </c>
       <c r="H319" s="3">
         <f>IF(F319=0,0,1-G319/F319)</f>
         <v/>
       </c>
       <c r="I319" s="2" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L319" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M319" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N319" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O319" s="2" t="n">
         <v>0</v>
@@ -37871,17 +38159,17 @@
         </is>
       </c>
       <c r="S319" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T319" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U319" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V319" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer</t>
+          <t>Smyth</t>
         </is>
       </c>
       <c r="W319" s="2" t="inlineStr">
@@ -37891,12 +38179,12 @@
       </c>
       <c r="X319" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y319" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z319" s="2" t="inlineStr">
@@ -37906,12 +38194,12 @@
       </c>
       <c r="AA319" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-2</t>
+          <t>reg-us-ii-3-2</t>
         </is>
       </c>
       <c r="AB319" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 twice-committed)</t>
+          <t>attested-static (July 2-4 wall line)</t>
         </is>
       </c>
       <c r="AC319" s="5" t="n"/>
@@ -37920,55 +38208,55 @@
       <c r="AF319" s="5" t="n"/>
       <c r="AG319" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
         </is>
       </c>
       <c r="AH319" s="5" t="inlineStr">
         <is>
-          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
+          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
         </is>
       </c>
       <c r="AI319" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
+          <t>1,190 (build compilation, hop flagged; no primary)</t>
         </is>
       </c>
       <c r="AJ319" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
+          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
         </is>
       </c>
       <c r="AK319" s="5" t="inlineStr">
         <is>
-          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
+          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
         </is>
       </c>
       <c r="AL319" s="5" t="inlineStr">
         <is>
-          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
+          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
         </is>
       </c>
       <c r="AM319" s="5" t="inlineStr">
         <is>
-          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
+          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
         </is>
       </c>
       <c r="AN319" s="5" t="n"/>
       <c r="AO319" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>us-tilton</t>
+          <t>us-sweitzer</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
+          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -37987,10 +38275,10 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>530</v>
+        <v>995</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>530</v>
+        <v>995</v>
       </c>
       <c r="H320" s="3">
         <f>IF(F320=0,0,1-G320/F320)</f>
@@ -38041,7 +38329,7 @@
       </c>
       <c r="V320" s="2" t="inlineStr">
         <is>
-          <t>Tilton</t>
+          <t>Sweitzer</t>
         </is>
       </c>
       <c r="W320" s="2" t="inlineStr">
@@ -38066,12 +38354,12 @@
       </c>
       <c r="AA320" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-1</t>
+          <t>reg-us-v-1-2</t>
         </is>
       </c>
       <c r="AB320" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 twice-committed)</t>
         </is>
       </c>
       <c r="AC320" s="5" t="n"/>
@@ -38080,37 +38368,37 @@
       <c r="AF320" s="5" t="n"/>
       <c r="AG320" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
         </is>
       </c>
       <c r="AH320" s="5" t="inlineStr">
         <is>
-          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
         </is>
       </c>
       <c r="AI320" s="5" t="inlineStr">
         <is>
-          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
         </is>
       </c>
       <c r="AJ320" s="5" t="inlineStr">
         <is>
-          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
         </is>
       </c>
       <c r="AK320" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
         </is>
       </c>
       <c r="AL320" s="5" t="inlineStr">
         <is>
-          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
         </is>
       </c>
       <c r="AM320" s="5" t="inlineStr">
         <is>
-          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AN320" s="5" t="n"/>
@@ -38123,12 +38411,12 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>us-torbert</t>
+          <t>us-tilton</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
+          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -38147,10 +38435,10 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>1320</v>
+        <v>530</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>1320</v>
+        <v>530</v>
       </c>
       <c r="H321" s="3">
         <f>IF(F321=0,0,1-G321/F321)</f>
@@ -38201,7 +38489,7 @@
       </c>
       <c r="V321" s="2" t="inlineStr">
         <is>
-          <t>Torbert</t>
+          <t>Tilton</t>
         </is>
       </c>
       <c r="W321" s="2" t="inlineStr">
@@ -38226,33 +38514,69 @@
       </c>
       <c r="AA321" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-1</t>
-        </is>
-      </c>
-      <c r="AB321" s="5" t="n"/>
+          <t>reg-us-v-1-1</t>
+        </is>
+      </c>
+      <c r="AB321" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC321" s="5" t="n"/>
       <c r="AD321" s="5" t="n"/>
       <c r="AE321" s="5" t="n"/>
       <c r="AF321" s="5" t="n"/>
-      <c r="AG321" s="5" t="n"/>
-      <c r="AH321" s="5" t="n"/>
-      <c r="AI321" s="5" t="n"/>
-      <c r="AJ321" s="5" t="n"/>
-      <c r="AK321" s="5" t="n"/>
-      <c r="AL321" s="5" t="n"/>
-      <c r="AM321" s="5" t="n"/>
+      <c r="AG321" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+        </is>
+      </c>
+      <c r="AH321" s="5" t="inlineStr">
+        <is>
+          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+        </is>
+      </c>
+      <c r="AI321" s="5" t="inlineStr">
+        <is>
+          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+        </is>
+      </c>
+      <c r="AJ321" s="5" t="inlineStr">
+        <is>
+          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+        </is>
+      </c>
+      <c r="AK321" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+        </is>
+      </c>
+      <c r="AL321" s="5" t="inlineStr">
+        <is>
+          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+        </is>
+      </c>
+      <c r="AM321" s="5" t="inlineStr">
+        <is>
+          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+        </is>
+      </c>
       <c r="AN321" s="5" t="n"/>
-      <c r="AO321" s="5" t="n"/>
+      <c r="AO321" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>us-detrobriand</t>
+          <t>us-torbert</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
+          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -38271,10 +38595,10 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>895</v>
+        <v>1320</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>895</v>
+        <v>1320</v>
       </c>
       <c r="H322" s="3">
         <f>IF(F322=0,0,1-G322/F322)</f>
@@ -38311,7 +38635,7 @@
       </c>
       <c r="R322" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S322" s="2" t="n">
@@ -38325,7 +38649,7 @@
       </c>
       <c r="V322" s="2" t="inlineStr">
         <is>
-          <t>Trobriand</t>
+          <t>Torbert</t>
         </is>
       </c>
       <c r="W322" s="2" t="inlineStr">
@@ -38350,69 +38674,33 @@
       </c>
       <c r="AA322" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-3</t>
-        </is>
-      </c>
-      <c r="AB322" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-1-1</t>
+        </is>
+      </c>
+      <c r="AB322" s="5" t="n"/>
       <c r="AC322" s="5" t="n"/>
       <c r="AD322" s="5" t="n"/>
       <c r="AE322" s="5" t="n"/>
       <c r="AF322" s="5" t="n"/>
-      <c r="AG322" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
-        </is>
-      </c>
-      <c r="AH322" s="5" t="inlineStr">
-        <is>
-          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
-        </is>
-      </c>
-      <c r="AI322" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
-        </is>
-      </c>
-      <c r="AJ322" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
-        </is>
-      </c>
-      <c r="AK322" s="5" t="inlineStr">
-        <is>
-          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
-        </is>
-      </c>
-      <c r="AL322" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
-        </is>
-      </c>
-      <c r="AM322" s="5" t="inlineStr">
-        <is>
-          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
-        </is>
-      </c>
+      <c r="AG322" s="5" t="n"/>
+      <c r="AH322" s="5" t="n"/>
+      <c r="AI322" s="5" t="n"/>
+      <c r="AJ322" s="5" t="n"/>
+      <c r="AK322" s="5" t="n"/>
+      <c r="AL322" s="5" t="n"/>
+      <c r="AM322" s="5" t="n"/>
       <c r="AN322" s="5" t="n"/>
-      <c r="AO322" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO322" s="5" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>us-vonamsberg</t>
+          <t>us-detrobriand</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -38431,10 +38719,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="H323" s="3">
         <f>IF(F323=0,0,1-G323/F323)</f>
@@ -38471,7 +38759,7 @@
       </c>
       <c r="R323" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S323" s="2" t="n">
@@ -38485,7 +38773,7 @@
       </c>
       <c r="V323" s="2" t="inlineStr">
         <is>
-          <t>Amsberg</t>
+          <t>Trobriand</t>
         </is>
       </c>
       <c r="W323" s="2" t="inlineStr">
@@ -38510,33 +38798,69 @@
       </c>
       <c r="AA323" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-1</t>
-        </is>
-      </c>
-      <c r="AB323" s="5" t="n"/>
+          <t>reg-us-iii-1-3</t>
+        </is>
+      </c>
+      <c r="AB323" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC323" s="5" t="n"/>
       <c r="AD323" s="5" t="n"/>
       <c r="AE323" s="5" t="n"/>
       <c r="AF323" s="5" t="n"/>
-      <c r="AG323" s="5" t="n"/>
-      <c r="AH323" s="5" t="n"/>
-      <c r="AI323" s="5" t="n"/>
-      <c r="AJ323" s="5" t="n"/>
-      <c r="AK323" s="5" t="n"/>
-      <c r="AL323" s="5" t="n"/>
-      <c r="AM323" s="5" t="n"/>
+      <c r="AG323" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
+        </is>
+      </c>
+      <c r="AH323" s="5" t="inlineStr">
+        <is>
+          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
+        </is>
+      </c>
+      <c r="AI323" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
+        </is>
+      </c>
+      <c r="AJ323" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
+        </is>
+      </c>
+      <c r="AK323" s="5" t="inlineStr">
+        <is>
+          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
+        </is>
+      </c>
+      <c r="AL323" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
+        </is>
+      </c>
+      <c r="AM323" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
+        </is>
+      </c>
       <c r="AN323" s="5" t="n"/>
-      <c r="AO323" s="5" t="n"/>
+      <c r="AO323" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>us-vongilsa</t>
+          <t>us-vonamsberg</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -38555,10 +38879,10 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>605</v>
+        <v>875</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>605</v>
+        <v>875</v>
       </c>
       <c r="H324" s="3">
         <f>IF(F324=0,0,1-G324/F324)</f>
@@ -38609,7 +38933,7 @@
       </c>
       <c r="V324" s="2" t="inlineStr">
         <is>
-          <t>Gilsa</t>
+          <t>Amsberg</t>
         </is>
       </c>
       <c r="W324" s="2" t="inlineStr">
@@ -38634,7 +38958,7 @@
       </c>
       <c r="AA324" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-1</t>
+          <t>reg-us-xi-3-1</t>
         </is>
       </c>
       <c r="AB324" s="5" t="n"/>
@@ -38652,8 +38976,132 @@
       <c r="AN324" s="5" t="n"/>
       <c r="AO324" s="5" t="n"/>
     </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>us-vongilsa</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="H325" s="3">
+        <f>IF(F325=0,0,1-G325/F325)</f>
+        <v/>
+      </c>
+      <c r="I325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K325" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U325" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V325" s="2" t="inlineStr">
+        <is>
+          <t>Gilsa</t>
+        </is>
+      </c>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="Z325" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AA325" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-1-1</t>
+        </is>
+      </c>
+      <c r="AB325" s="5" t="n"/>
+      <c r="AC325" s="5" t="n"/>
+      <c r="AD325" s="5" t="n"/>
+      <c r="AE325" s="5" t="n"/>
+      <c r="AF325" s="5" t="n"/>
+      <c r="AG325" s="5" t="n"/>
+      <c r="AH325" s="5" t="n"/>
+      <c r="AI325" s="5" t="n"/>
+      <c r="AJ325" s="5" t="n"/>
+      <c r="AK325" s="5" t="n"/>
+      <c r="AL325" s="5" t="n"/>
+      <c r="AM325" s="5" t="n"/>
+      <c r="AN325" s="5" t="n"/>
+      <c r="AO325" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO324"/>
+  <autoFilter ref="A1:AO325"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -15905,20 +15905,56 @@
           <t>reg-csa-2c-rod-1</t>
         </is>
       </c>
-      <c r="AB140" s="5" t="n"/>
+      <c r="AB140" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC140" s="5" t="n"/>
       <c r="AD140" s="5" t="n"/>
       <c r="AE140" s="5" t="n"/>
       <c r="AF140" s="5" t="n"/>
-      <c r="AG140" s="5" t="n"/>
-      <c r="AH140" s="5" t="n"/>
-      <c r="AI140" s="5" t="n"/>
-      <c r="AJ140" s="5" t="n"/>
-      <c r="AK140" s="5" t="n"/>
-      <c r="AL140" s="5" t="n"/>
-      <c r="AM140" s="5" t="n"/>
+      <c r="AG140" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-rod-1-daniel.md; 4 a.m. vs recap 5 a.m. intra-report pair carried</t>
+        </is>
+      </c>
+      <c r="AH140" s="5" t="inlineStr">
+        <is>
+          <t>Daniel's Bde, Rodes's Div (32/43/45/53 NC + 2nd NC Bn); Daniel throughout; Bond/Green w July 1 pins</t>
+        </is>
+      </c>
+      <c r="AI140" s="5" t="inlineStr">
+        <is>
+          <t>OPEN; July 1 cost 'nearly one-third' = July 3 at two-thirds-strength CLASS (his fraction, not a number)</t>
+        </is>
+      </c>
+      <c r="AJ140" s="5" t="inlineStr">
+        <is>
+          <t>[C] 1.30 a.m. off / 4 a.m. reported to Johnson; [D+drawn] j3-01 DANIEL (5754,5842) behind JONES (5721,5780); j3-02 (6035,5465) the left-flank move drawn; E Conf Ave tablet (formation-line semantics)</t>
+        </is>
+      </c>
+      <c r="AK140" s="5" t="inlineStr">
+        <is>
+          <t>[B] the 4-mile night march at ~0.7 m/s (physics-consistent); [D] into Jones's support; the costly staff-guided lateral leg; the Steuart co-charge</t>
+        </is>
+      </c>
+      <c r="AL140" s="5" t="inlineStr">
+        <is>
+          <t>THE ASSESSMENT PRIMARY ('could not have been carried by any force'); the co-charge both-sided (Daniel/Steuart/Kane); the holding phase to 15:00-16:00 + midnight skirmishers</t>
+        </is>
+      </c>
+      <c r="AM140" s="5" t="inlineStr">
+        <is>
+          <t>ANV return 916 (165/635/116) w/ regiment rows — the Second Corps' largest; July-1-dominant by his own fraction; no per-day numbers</t>
+        </is>
+      </c>
       <c r="AN140" s="5" t="n"/>
-      <c r="AO140" s="5" t="n"/>
+      <c r="AO140" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -16732,7 +16768,7 @@
       <c r="AF146" s="5" t="n"/>
       <c r="AG146" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-joh-4-jones.md; register commander note corrected (w July 2, not July 3)</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-joh-4-jones.md; register commander note corrected (w July 2, not July 3) | PASS 9: Daniel-supports-Dungan weld (the succession named by the supporting brigade); j3-01 drawn arrival pair.</t>
         </is>
       </c>
       <c r="AH146" s="5" t="inlineStr">
@@ -17816,7 +17852,7 @@
       <c r="AF153" s="5" t="n"/>
       <c r="AG153" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-joh-3-nicholls.md; the evening chain's first agreeing CSA clock (ED-62 core)</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-joh-3-nicholls.md; the evening chain's first agreeing CSA clock (ED-62 core) | PASS 9: morning-fire arc framed (program + seven hours + the Rodes wave on its left).</t>
         </is>
       </c>
       <c r="AH153" s="5" t="inlineStr">
@@ -17965,20 +18001,56 @@
           <t>reg-csa-2c-rod-5</t>
         </is>
       </c>
-      <c r="AB154" s="5" t="n"/>
+      <c r="AB154" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC154" s="5" t="n"/>
       <c r="AD154" s="5" t="n"/>
       <c r="AE154" s="5" t="n"/>
       <c r="AF154" s="5" t="n"/>
-      <c r="AG154" s="5" t="n"/>
-      <c r="AH154" s="5" t="n"/>
-      <c r="AI154" s="5" t="n"/>
-      <c r="AJ154" s="5" t="n"/>
-      <c r="AK154" s="5" t="n"/>
-      <c r="AL154" s="5" t="n"/>
-      <c r="AM154" s="5" t="n"/>
+      <c r="AG154" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-rod-5-oneal.md; the skeleton's softest clock (wave 2) answered at executor grain</t>
+        </is>
+      </c>
+      <c r="AH154" s="5" t="inlineStr">
+        <is>
+          <t>O'Neal's (Rodes's old) Bde (3/5/6/12/26 AL); O'Neal (senior colonel, commission withheld); July 3 orders direct from Johnson</t>
+        </is>
+      </c>
+      <c r="AI154" s="5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AJ154" s="5" t="inlineStr">
+        <is>
+          <t>[C] 2 a.m. off / arrived at daylight; [D+drawn] j3-01 (6223,5804) NE arrival vs j3-02 (5721,5694) north-slope attack — the ~510 m drawn advance IS the 8 a.m. attack; E Conf Ave tablet</t>
+        </is>
+      </c>
+      <c r="AK154" s="5" t="inlineStr">
+        <is>
+          <t>[B] the same-route night march; [C 8 a.m.] the wave-2 attack (four named regiments); [D] fall back with the entire line -&gt; behind-the-hill hold till midnight</t>
+        </is>
+      </c>
+      <c r="AL154" s="5" t="inlineStr">
+        <is>
+          <t>THE CA-J3M-2 WAVE-2 EXECUTOR CLOCK ('did not actively engage the foe until 8 a.m.'); grape-range attestation; the three-hour murderous-fire hold</t>
+        </is>
+      </c>
+      <c r="AM154" s="5" t="inlineStr">
+        <is>
+          <t>ANV return 696 (73/430/193) w/ asterisked regimental counter-readings carried; July-1-heavy, July 3 in the 8-11 hold</t>
+        </is>
+      </c>
       <c r="AN154" s="5" t="n"/>
-      <c r="AO154" s="5" t="n"/>
+      <c r="AO154" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -18781,20 +18853,56 @@
           <t>reg-csa-2c-ear-2</t>
         </is>
       </c>
-      <c r="AB160" s="5" t="n"/>
+      <c r="AB160" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command-note grain)</t>
+        </is>
+      </c>
       <c r="AC160" s="5" t="n"/>
       <c r="AD160" s="5" t="n"/>
       <c r="AE160" s="5" t="n"/>
       <c r="AF160" s="5" t="n"/>
-      <c r="AG160" s="5" t="n"/>
-      <c r="AH160" s="5" t="n"/>
-      <c r="AI160" s="5" t="n"/>
-      <c r="AJ160" s="5" t="n"/>
-      <c r="AK160" s="5" t="n"/>
-      <c r="AL160" s="5" t="n"/>
-      <c r="AM160" s="5" t="n"/>
+      <c r="AG160" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-ear-2-smith.md; T2 ceiling accepted, not padded</t>
+        </is>
+      </c>
+      <c r="AH160" s="5" t="inlineStr">
+        <is>
+          <t>Smith's Bde, Early's Div (31/49/52 VA — three regiments); 'Extra Billy' Smith; Hoffman the later commander</t>
+        </is>
+      </c>
+      <c r="AI160" s="5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AJ160" s="5" t="inlineStr">
+        <is>
+          <t>[E] July 1-2 York-road flank guard (Early); [D+drawn] Johnson's extreme left near the creek (j3-01 SMITH VA (6324,5152); j3-02 (6107,5116)); E Conf Ave tablet</t>
+        </is>
+      </c>
+      <c r="AK160" s="5" t="inlineStr">
+        <is>
+          <t>[D] the by-daylight night detachment march (Early's order primary; no own clock)</t>
+        </is>
+      </c>
+      <c r="AL160" s="5" t="inlineStr">
+        <is>
+          <t>'his three regiments were engaged on the 3rd on the extreme left, under General Johnson's directions' (Early) — vs JOHNSON'S SILENCE (his July 3 paragraph names only Daniel/O'Neal): the echelon-asymmetry record; Hoffman report referral UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="AM160" s="5" t="inlineStr">
+        <is>
+          <t>not consulted this pass (Early-division return block holds the row; open at this grain)</t>
+        </is>
+      </c>
       <c r="AN160" s="5" t="n"/>
-      <c r="AO160" s="5" t="n"/>
+      <c r="AO160" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command-note grain)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -18916,7 +19024,7 @@
       <c r="AF161" s="5" t="n"/>
       <c r="AG161" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-joh-1-steuart.md; action clocks +75 profiled vs his own 11 p.m. ~0 - in-division heterogeneity documented</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-joh-1-steuart.md; action clocks +75 profiled vs his own 11 p.m. ~0 - in-division heterogeneity documented | PASS 9: the 10 a.m. charge BOTH-SIDED at three grains (Daniel co-charge / Kane 10.30 receiving / Colgrove prisoner ID).</t>
         </is>
       </c>
       <c r="AH161" s="5" t="inlineStr">
@@ -19076,7 +19184,7 @@
       <c r="AF162" s="5" t="n"/>
       <c r="AG162" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-joh-2-walker.md; Gregg cavalry companion flagged for the cavalry batch</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-joh-2-walker.md; Gregg cavalry companion flagged for the cavalry batch | PASS 9: wave-1 composition pin (Johnson's Stonewall-up verbatim); drawn-static WALKER labels across j3-01/j3-02.</t>
         </is>
       </c>
       <c r="AH162" s="5" t="inlineStr">
@@ -21081,20 +21189,56 @@
           <t>reg-us-xii-arty</t>
         </is>
       </c>
-      <c r="AB180" s="5" t="n"/>
+      <c r="AB180" s="5" t="inlineStr">
+        <is>
+          <t>not-yet-cast (group grain)</t>
+        </is>
+      </c>
       <c r="AC180" s="5" t="n"/>
       <c r="AD180" s="5" t="n"/>
       <c r="AE180" s="5" t="n"/>
       <c r="AF180" s="5" t="n"/>
-      <c r="AG180" s="5" t="n"/>
-      <c r="AH180" s="5" t="n"/>
-      <c r="AI180" s="5" t="n"/>
-      <c r="AJ180" s="5" t="n"/>
-      <c r="AK180" s="5" t="n"/>
-      <c r="AL180" s="5" t="n"/>
-      <c r="AM180" s="5" t="n"/>
+      <c r="AG180" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-arty-muhlenberg.md; report-vs-tablet conflicts (20-vs-26 guns; 10:00-vs-10:30 end) carried on CA-J3M-1/4</t>
+        </is>
+      </c>
+      <c r="AH180" s="5" t="inlineStr">
+        <is>
+          <t>Muhlenberg (1st Lt, 4th US) commanding; F 4th US (Rugg), K 5th US (Kinzie), Knap's E PA (Atwell), M 1st NY (Winegar)</t>
+        </is>
+      </c>
+      <c r="AI180" s="5" t="inlineStr">
+        <is>
+          <t>20 guns in the July 3 program BY THE AUTHOR (10 rifles + 10 Napoleons) vs tablet 26 — Rigby A 1st MD reconciliation flagged, not adopted; personnel OPEN</t>
+        </is>
+      </c>
+      <c r="AJ180" s="5" t="inlineStr">
+        <is>
+          <t>[E] the pike/Powers/McAllister's program arc 600-800 yards out (four program-ground markers registered incl. Rigby); July 2 park negative (F + K 'remained in park')</t>
+        </is>
+      </c>
+      <c r="AK180" s="5" t="inlineStr">
+        <is>
+          <t>[C ~17:00 July 2] the Geary/Van Reed forward sections; otherwise attested-static</t>
+        </is>
+      </c>
+      <c r="AL180" s="5" t="inlineStr">
+        <is>
+          <t>THE CA-J3M-1 AUTHOR PRIMARY: 4.30 open / 15 min without intermission / 5.30 resume / 'until 10 a.m.'; Williams verbatim-class corroboration; the July 2 eight-gun thirty-minute Latimer duel received; NO rounds figures (verified negative)</t>
+        </is>
+      </c>
+      <c r="AM180" s="5" t="inlineStr">
+        <is>
+          <t>9 w aggregate (return p. 185) + the July 2 section losses itemized; July-2-weighted</t>
+        </is>
+      </c>
       <c r="AN180" s="5" t="n"/>
-      <c r="AO180" s="5" t="n"/>
+      <c r="AO180" s="5" t="inlineStr">
+        <is>
+          <t>T3 (group grain)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -34333,20 +34477,56 @@
           <t>reg-us-xii-2-1</t>
         </is>
       </c>
-      <c r="AB289" s="5" t="n"/>
+      <c r="AB289" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC289" s="5" t="n"/>
       <c r="AD289" s="5" t="n"/>
       <c r="AE289" s="5" t="n"/>
       <c r="AF289" s="5" t="n"/>
-      <c r="AG289" s="5" t="n"/>
-      <c r="AH289" s="5" t="n"/>
-      <c r="AI289" s="5" t="n"/>
-      <c r="AJ289" s="5" t="n"/>
-      <c r="AK289" s="5" t="n"/>
-      <c r="AL289" s="5" t="n"/>
-      <c r="AM289" s="5" t="n"/>
+      <c r="AG289" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md</t>
+        </is>
+      </c>
+      <c r="AH289" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
+        </is>
+      </c>
+      <c r="AI289" s="5" t="inlineStr">
+        <is>
+          <t>OPEN (no primary; no hop)</t>
+        </is>
+      </c>
+      <c r="AJ289" s="5" t="inlineStr">
+        <is>
+          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
+        </is>
+      </c>
+      <c r="AK289" s="5" t="inlineStr">
+        <is>
+          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
+        </is>
+      </c>
+      <c r="AL289" s="5" t="inlineStr">
+        <is>
+          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
+        </is>
+      </c>
+      <c r="AM289" s="5" t="inlineStr">
+        <is>
+          <t>return brigade total 139 (division arithmetic closes 540=303+139+98); regiment rows the cheap residual</t>
+        </is>
+      </c>
       <c r="AN289" s="5" t="n"/>
-      <c r="AO289" s="5" t="n"/>
+      <c r="AO289" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -34777,20 +34957,56 @@
           <t>reg-us-xii-1-3</t>
         </is>
       </c>
-      <c r="AB292" s="5" t="n"/>
+      <c r="AB292" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (the CA-J3M-3 executor)</t>
+        </is>
+      </c>
       <c r="AC292" s="5" t="n"/>
       <c r="AD292" s="5" t="n"/>
       <c r="AE292" s="5" t="n"/>
       <c r="AF292" s="5" t="n"/>
-      <c r="AG292" s="5" t="n"/>
-      <c r="AH292" s="5" t="n"/>
-      <c r="AI292" s="5" t="n"/>
-      <c r="AJ292" s="5" t="n"/>
-      <c r="AK292" s="5" t="n"/>
-      <c r="AL292" s="5" t="n"/>
-      <c r="AM292" s="5" t="n"/>
+      <c r="AG292" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
+        </is>
+      </c>
+      <c r="AH292" s="5" t="inlineStr">
+        <is>
+          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
+        </is>
+      </c>
+      <c r="AI292" s="5" t="inlineStr">
+        <is>
+          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
+        </is>
+      </c>
+      <c r="AJ292" s="5" t="inlineStr">
+        <is>
+          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
+        </is>
+      </c>
+      <c r="AK292" s="5" t="inlineStr">
+        <is>
+          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
+        </is>
+      </c>
+      <c r="AL292" s="5" t="inlineStr">
+        <is>
+          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
+        </is>
+      </c>
+      <c r="AM292" s="5" t="inlineStr">
+        <is>
+          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
+        </is>
+      </c>
       <c r="AN292" s="5" t="n"/>
-      <c r="AO292" s="5" t="n"/>
+      <c r="AO292" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -36296,7 +36512,7 @@
       <c r="AF303" s="5" t="n"/>
       <c r="AG303" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
         </is>
       </c>
       <c r="AH303" s="5" t="inlineStr">
@@ -36765,20 +36981,56 @@
           <t>reg-us-xii-2-2</t>
         </is>
       </c>
-      <c r="AB306" s="5" t="n"/>
+      <c r="AB306" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC306" s="5" t="n"/>
       <c r="AD306" s="5" t="n"/>
       <c r="AE306" s="5" t="n"/>
       <c r="AF306" s="5" t="n"/>
-      <c r="AG306" s="5" t="n"/>
-      <c r="AH306" s="5" t="n"/>
-      <c r="AI306" s="5" t="n"/>
-      <c r="AJ306" s="5" t="n"/>
-      <c r="AK306" s="5" t="n"/>
-      <c r="AL306" s="5" t="n"/>
-      <c r="AM306" s="5" t="n"/>
+      <c r="AG306" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder</t>
+        </is>
+      </c>
+      <c r="AH306" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
+        </is>
+      </c>
+      <c r="AI306" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY: 652 in action (Kane p. 848)</t>
+        </is>
+      </c>
+      <c r="AJ306" s="5" t="inlineStr">
+        <is>
+          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
+        </is>
+      </c>
+      <c r="AK306" s="5" t="inlineStr">
+        <is>
+          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
+        </is>
+      </c>
+      <c r="AL306" s="5" t="inlineStr">
+        <is>
+          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
+        </is>
+      </c>
+      <c r="AM306" s="5" t="inlineStr">
+        <is>
+          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening)</t>
+        </is>
+      </c>
       <c r="AN306" s="5" t="n"/>
-      <c r="AO306" s="5" t="n"/>
+      <c r="AO306" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -37173,20 +37425,56 @@
           <t>reg-us-xii-1-2</t>
         </is>
       </c>
-      <c r="AB309" s="5" t="n"/>
+      <c r="AB309" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC309" s="5" t="n"/>
       <c r="AD309" s="5" t="n"/>
       <c r="AE309" s="5" t="n"/>
       <c r="AF309" s="5" t="n"/>
-      <c r="AG309" s="5" t="n"/>
-      <c r="AH309" s="5" t="n"/>
-      <c r="AI309" s="5" t="n"/>
-      <c r="AJ309" s="5" t="n"/>
-      <c r="AK309" s="5" t="n"/>
-      <c r="AL309" s="5" t="n"/>
-      <c r="AM309" s="5" t="n"/>
+      <c r="AG309" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md</t>
+        </is>
+      </c>
+      <c r="AH309" s="5" t="inlineStr">
+        <is>
+          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
+        </is>
+      </c>
+      <c r="AI309" s="5" t="inlineStr">
+        <is>
+          <t>OPEN; two-regiment July 2 vs three-regiment July 3 composition fact</t>
+        </is>
+      </c>
+      <c r="AJ309" s="5" t="inlineStr">
+        <is>
+          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
+        </is>
+      </c>
+      <c r="AK309" s="5" t="inlineStr">
+        <is>
+          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
+        </is>
+      </c>
+      <c r="AL309" s="5" t="inlineStr">
+        <is>
+          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
+        </is>
+      </c>
+      <c r="AM309" s="5" t="inlineStr">
+        <is>
+          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
+        </is>
+      </c>
       <c r="AN309" s="5" t="n"/>
-      <c r="AO309" s="5" t="n"/>
+      <c r="AO309" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -37617,20 +37905,56 @@
           <t>reg-us-xii-1-1</t>
         </is>
       </c>
-      <c r="AB312" s="5" t="n"/>
+      <c r="AB312" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC312" s="5" t="n"/>
       <c r="AD312" s="5" t="n"/>
       <c r="AE312" s="5" t="n"/>
       <c r="AF312" s="5" t="n"/>
-      <c r="AG312" s="5" t="n"/>
-      <c r="AH312" s="5" t="n"/>
-      <c r="AI312" s="5" t="n"/>
-      <c r="AJ312" s="5" t="n"/>
-      <c r="AK312" s="5" t="n"/>
-      <c r="AL312" s="5" t="n"/>
-      <c r="AM312" s="5" t="n"/>
+      <c r="AG312" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
+        </is>
+      </c>
+      <c r="AH312" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
+        </is>
+      </c>
+      <c r="AI312" s="5" t="inlineStr">
+        <is>
+          <t>OPEN (no primary; no hop)</t>
+        </is>
+      </c>
+      <c r="AJ312" s="5" t="inlineStr">
+        <is>
+          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
+        </is>
+      </c>
+      <c r="AK312" s="5" t="inlineStr">
+        <is>
+          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
+        </is>
+      </c>
+      <c r="AL312" s="5" t="inlineStr">
+        <is>
+          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
+        </is>
+      </c>
+      <c r="AM312" s="5" t="inlineStr">
+        <is>
+          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
+        </is>
+      </c>
       <c r="AN312" s="5" t="n"/>
-      <c r="AO312" s="5" t="n"/>
+      <c r="AO312" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$330</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO328"/>
+  <dimension ref="A1:AO330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14460,7 +14460,7 @@
       <c r="AF131" s="5" t="n"/>
       <c r="AG131" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-het-2-brockenbrough.md; NO OR report (verified negative)</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-2-brockenbrough.md; NO OR report (verified negative); July 1 extended pass 10 (thin; no-report negative governs)</t>
         </is>
       </c>
       <c r="AH131" s="5" t="inlineStr">
@@ -14620,7 +14620,7 @@
       <c r="AF132" s="5" t="n"/>
       <c r="AG132" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-het-4-davis.md; division report clock +5 (CSA twin of Hall)</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-4-davis.md; division report clock +5 (CSA twin of Hall); July 1 extended pass 10 (THE 10.30 ATTACK-POLE CLOCK - ED-66 keystone)</t>
         </is>
       </c>
       <c r="AH132" s="5" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AJ132" s="5" t="inlineStr">
         <is>
-          <t>[C +5] 9am shift behind Pegram's bn; j3-02 label ~(3330,5760)+-100; mon-11ms start (3471,5621) corroborates (modern-era caution); farthest advance mon-11ms-1 Bryan barn (4448,5115)</t>
+          <t>[C +5] 9am shift behind Pegram's bn; j3-02 label ~(3330,5760)+-100; mon-11ms start (3471,5621) corroborates (modern-era caution); farthest advance mon-11ms-1 Bryan barn (4448,5115); [C] July 1: 10.30 line-formed-and-attacked / ~1 p.m. retirement / ~3 p.m. re-advance (pass 10)</t>
         </is>
       </c>
       <c r="AK132" s="5" t="inlineStr">
@@ -14780,7 +14780,7 @@
       <c r="AF133" s="5" t="n"/>
       <c r="AG133" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-het-3-fry.md; claim-fry-guide now executor-documented</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-3-fry.md; claim-fry-guide now executor-documented; July 1 extended pass 10 (the creek pocket both-sided; Archer-captured marker registered)</t>
         </is>
       </c>
       <c r="AH133" s="5" t="inlineStr">
@@ -15276,7 +15276,7 @@
       <c r="AF136" s="5" t="n"/>
       <c r="AG136" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-3c-het-1-marshall.md</t>
+          <t>Dossier: reconstruction/dossiers/csa-3c-het-1-marshall.md; July 1 extended pass 10 (the 26th NC vs 24th Mich facing color ledgers)</t>
         </is>
       </c>
       <c r="AH136" s="5" t="inlineStr">
@@ -16189,20 +16189,56 @@
           <t>reg-csa-2c-ear-4</t>
         </is>
       </c>
-      <c r="AB142" s="5" t="n"/>
+      <c r="AB142" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC142" s="5" t="n"/>
       <c r="AD142" s="5" t="n"/>
       <c r="AE142" s="5" t="n"/>
       <c r="AF142" s="5" t="n"/>
-      <c r="AG142" s="5" t="n"/>
-      <c r="AH142" s="5" t="n"/>
-      <c r="AI142" s="5" t="n"/>
-      <c r="AJ142" s="5" t="n"/>
-      <c r="AK142" s="5" t="n"/>
-      <c r="AL142" s="5" t="n"/>
-      <c r="AM142" s="5" t="n"/>
+      <c r="AG142" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-ear-4-gordon.md; THE 3 P.M. CROSS-LINE PAIR with Schurz (CA-J1P-3 upgraded, ED-67 rider)</t>
+        </is>
+      </c>
+      <c r="AH142" s="5" t="inlineStr">
+        <is>
+          <t>Gordon; 26th Ga detached to Jones's artillery (EC2 primary)</t>
+        </is>
+      </c>
+      <c r="AI142" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 'about 1,200 men' (one regiment detached); tablet class pending</t>
+        </is>
+      </c>
+      <c r="AJ142" s="5" t="inlineStr">
+        <is>
+          <t>[D+drawn+tablet] Blocher's formation (GORDON GA label 5254,8676); the contact bar 82 m from the Barlow statue; mon-gordon-tablet ON the knoll; the halt line; July 2-3 the dismissal-sentence negative</t>
+        </is>
+      </c>
+      <c r="AK142" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:00] the 3 p.m. commitment (deliberate slow approach); THE FENCE-AND-CREEK OBSTACLE LEG (abrupt banks, certain points only); the two-line break to the halt order</t>
+        </is>
+      </c>
+      <c r="AL142" s="5" t="inlineStr">
+        <is>
+          <t>the knoll fight (50-paces colors range); the Barlow w&amp;c pin; July 5 Fairfield rear guard</t>
+        </is>
+      </c>
+      <c r="AM142" s="5" t="inlineStr">
+        <is>
+          <t>his 350 k&amp;w (40 k) vs return 380 (71 k) - the k conflict carried; 'nearly 300 buried'; the 1,800-prisoner inspector credit (not adopted); 26th Ga 11 = the structural control row</t>
+        </is>
+      </c>
       <c r="AN142" s="5" t="n"/>
-      <c r="AO142" s="5" t="n"/>
+      <c r="AO142" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -16324,7 +16360,7 @@
       <c r="AF143" s="5" t="n"/>
       <c r="AG143" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-ear-1-hays.md; 'a little before 8' + Wiedrich + Ricketts = the three-source cross-armies agreement (ED-62); ED-63 core</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-ear-1-hays.md; 'a little before 8' + Wiedrich + Ricketts = the three-source cross-armies agreement (ED-62); ED-63 core; July 1 extended + EC2 tablet hop (~1,200) pass 10; Gordon-non-advance conflict CLOSED</t>
         </is>
       </c>
       <c r="AH143" s="5" t="inlineStr">
@@ -16334,7 +16370,7 @@
       </c>
       <c r="AI143" s="5" t="inlineStr">
         <is>
-          <t>OPEN (hop flagged); July 1 loss pre-shrinks the line (his own figures)</t>
+          <t>OPEN (hop flagged); July 1 loss pre-shrinks the line (his own figures); tablet 'Present about 1200' (pass-10 hop; k/w cells = return exact)</t>
         </is>
       </c>
       <c r="AJ143" s="5" t="inlineStr">
@@ -16484,7 +16520,7 @@
       <c r="AF144" s="5" t="n"/>
       <c r="AG144" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-ear-3-avery.md; no brigade report verified negative (Avery dead, Godwin silent)</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-ear-3-avery.md; no brigade report verified negative (Avery dead, Godwin silent); July 1 extended + EC2 tablet hop (~900) pass 10</t>
         </is>
       </c>
       <c r="AH144" s="5" t="inlineStr">
@@ -16494,7 +16530,7 @@
       </c>
       <c r="AI144" s="5" t="inlineStr">
         <is>
-          <t>OPEN; three-regiment structure the operative fact</t>
+          <t>tablet 'Present about 900' (pass-10 hop); no report primary</t>
         </is>
       </c>
       <c r="AJ144" s="5" t="inlineStr">
@@ -16633,20 +16669,56 @@
           <t>reg-csa-2c-rod-2</t>
         </is>
       </c>
-      <c r="AB145" s="5" t="n"/>
+      <c r="AB145" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC145" s="5" t="n"/>
       <c r="AD145" s="5" t="n"/>
       <c r="AE145" s="5" t="n"/>
       <c r="AF145" s="5" t="n"/>
-      <c r="AG145" s="5" t="n"/>
-      <c r="AH145" s="5" t="n"/>
-      <c r="AI145" s="5" t="n"/>
-      <c r="AJ145" s="5" t="n"/>
-      <c r="AK145" s="5" t="n"/>
-      <c r="AL145" s="5" t="n"/>
-      <c r="AM145" s="5" t="n"/>
+      <c r="AG145" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-rod-2-iverson.md; CA-J1P-2 upgraded to bracketed+geometric (ED-67 rider)</t>
+        </is>
+      </c>
+      <c r="AH145" s="5" t="inlineStr">
+        <is>
+          <t>Iverson; Halsey's remnant rally; Davis's intact 12th NC; the quiet post-battle relief ('my connection with the brigade ceased')</t>
+        </is>
+      </c>
+      <c r="AI145" s="5" t="inlineStr">
+        <is>
+          <t>tablet '820 of 1,470' (adjudicated class); no report primary</t>
+        </is>
+      </c>
+      <c r="AJ145" s="5" t="inlineStr">
+        <is>
+          <t>[E+tablet] Oak Hill launch (mon-iverson-hq + mon-rodes-div); [D+drawn] j1-09 mid-advance bar 408 m SE along the axis; THE DEATH LINE ('a line as straight as a dress parade' = Rodes 'distinctly marked line of battle'); evening street line w/ Ramseur</t>
+        </is>
+      </c>
+      <c r="AK145" s="5" t="inlineStr">
+        <is>
+          <t>[D 14:00-15:00 bracket] the advance to 100 yards; the surrender of three regiments' survivors; the remnant charge + railroad pursuit; July 4 train escort</t>
+        </is>
+      </c>
+      <c r="AL145" s="5" t="inlineStr">
+        <is>
+          <t>the destruction fight + THE SURRENDER-AND-EXONERATION RECORD (verbatim two-stage); the support-miscarriage ledger; July 2 night 'advancing to certain destruction'</t>
+        </is>
+      </c>
+      <c r="AM145" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 342) 820 = 130/382/308 (m POOLED - the capture mass; single-cell OCR flag on w); THE SINGLE-SPIKE EXEMPLAR - one line, one field, minutes-scale; 12th NC 56 bounds the residue</t>
+        </is>
+      </c>
       <c r="AN145" s="5" t="n"/>
-      <c r="AO145" s="5" t="n"/>
+      <c r="AO145" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -16778,7 +16850,7 @@
       </c>
       <c r="AI146" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present 1600' (pass-10 hop)</t>
         </is>
       </c>
       <c r="AJ146" s="5" t="inlineStr">
@@ -17862,7 +17934,7 @@
       </c>
       <c r="AI153" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1100' (pass-10 hop)</t>
         </is>
       </c>
       <c r="AJ153" s="5" t="inlineStr">
@@ -18409,20 +18481,56 @@
           <t>reg-csa-2c-rod-4</t>
         </is>
       </c>
-      <c r="AB157" s="5" t="n"/>
+      <c r="AB157" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC157" s="5" t="n"/>
       <c r="AD157" s="5" t="n"/>
       <c r="AE157" s="5" t="n"/>
       <c r="AF157" s="5" t="n"/>
-      <c r="AG157" s="5" t="n"/>
-      <c r="AH157" s="5" t="n"/>
-      <c r="AI157" s="5" t="n"/>
-      <c r="AJ157" s="5" t="n"/>
-      <c r="AK157" s="5" t="n"/>
-      <c r="AL157" s="5" t="n"/>
-      <c r="AM157" s="5" t="n"/>
+      <c r="AG157" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-rod-4-ramseur.md; kind-none</t>
+        </is>
+      </c>
+      <c r="AH157" s="5" t="inlineStr">
+        <is>
+          <t>Ramseur; Parker/Bennett/Grimes/Hurtt credited; Harney (14th NC) mw taking the 150th Pa colors - the pass-4 Stone record closed both-sided at man grain</t>
+        </is>
+      </c>
+      <c r="AI157" s="5" t="inlineStr">
+        <is>
+          <t>OPEN (no primary)</t>
+        </is>
+      </c>
+      <c r="AJ157" s="5" t="inlineStr">
+        <is>
+          <t>[D+tablet] Oak Hill reserve ground; the wall-and-woods counter-stroke ground; the east-west street line; July 2 night THE 200-YARD POINT (the reconnaissance that stopped the division); the deep-road withdrawal</t>
+        </is>
+      </c>
+      <c r="AK157" s="5" t="inlineStr">
+        <is>
+          <t>[D] the fifteen-minute commitment; the 2+4/14+30 split order; the en-masse flank attack w/ Battle's self-attached 3rd Ala; the through-town pursuit to the halt</t>
+        </is>
+      </c>
+      <c r="AL157" s="5" t="inlineStr">
+        <is>
+          <t>the counter-stroke ('800 and 900 prisoners'); the street fighting + colors; July 3 friendly-fire row (7 k+w by 'our own short-range guns')</t>
+        </is>
+      </c>
+      <c r="AM157" s="5" t="inlineStr">
+        <is>
+          <t>REPORT=RETURN EXACT x4 (32/56/44/45 = 177) - the audit's fourth full-grain exact agreement</t>
+        </is>
+      </c>
       <c r="AN157" s="5" t="n"/>
-      <c r="AO157" s="5" t="n"/>
+      <c r="AO157" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -18864,7 +18972,7 @@
       <c r="AF160" s="5" t="n"/>
       <c r="AG160" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/csa-2c-ear-2-smith.md; T2 ceiling accepted, not padded</t>
+          <t>Dossier: reconstruction/dossiers/csa-2c-ear-2-smith.md; T2 ceiling accepted, not padded; THE HOFFMAN HUNT LANDED pass 10 (No. 476; T2-&gt;T3)</t>
         </is>
       </c>
       <c r="AH160" s="5" t="inlineStr">
@@ -18874,7 +18982,7 @@
       </c>
       <c r="AI160" s="5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>three-regiment structure primary (13th/58th VA detached, Hoffman); tablet 'Present about 800' (pass-10 hop)</t>
         </is>
       </c>
       <c r="AJ160" s="5" t="inlineStr">
@@ -18894,13 +19002,13 @@
       </c>
       <c r="AM160" s="5" t="inlineStr">
         <is>
-          <t>not consulted this pass (Early-division return block holds the row; open at this grain)</t>
+          <t>Hoffman 15 k / 110 w / 17 m = 142 = TABLET TOTAL EXACT (cell variance recorded); the 49th VA 'more than two-fifths' July 3</t>
         </is>
       </c>
       <c r="AN160" s="5" t="n"/>
       <c r="AO160" s="5" t="inlineStr">
         <is>
-          <t>T2 (command-note grain)</t>
+          <t>T3 (report-grain arc)</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19142,7 @@
       </c>
       <c r="AI161" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1700' (pass-10 hop)</t>
         </is>
       </c>
       <c r="AJ161" s="5" t="inlineStr">
@@ -19194,7 +19302,7 @@
       </c>
       <c r="AI162" s="5" t="inlineStr">
         <is>
-          <t>OPEN; Terry's 4th VA 'three-fourths' fraction primary carried w/ scope flag (vs return 86)</t>
+          <t>OPEN; Terry's 4th VA 'three-fourths' fraction primary carried w/ scope flag (vs return 86); tablet 'Present about 1450' (pass-10 hop)</t>
         </is>
       </c>
       <c r="AJ162" s="5" t="inlineStr">
@@ -29545,20 +29653,56 @@
           <t>reg-us-cav-1-1</t>
         </is>
       </c>
-      <c r="AB250" s="5" t="n"/>
+      <c r="AB250" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC250" s="5" t="n"/>
       <c r="AD250" s="5" t="n"/>
       <c r="AE250" s="5" t="n"/>
       <c r="AF250" s="5" t="n"/>
-      <c r="AG250" s="5" t="n"/>
-      <c r="AH250" s="5" t="n"/>
-      <c r="AI250" s="5" t="n"/>
-      <c r="AJ250" s="5" t="n"/>
-      <c r="AK250" s="5" t="n"/>
-      <c r="AL250" s="5" t="n"/>
-      <c r="AM250" s="5" t="n"/>
+      <c r="AG250" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-1-1-gamble.md; CA-J1M-2 executor</t>
+        </is>
+      </c>
+      <c r="AH250" s="5" t="inlineStr">
+        <is>
+          <t>Gamble (8th Ill); Buford present in person; Calef's A/2nd US (six 3-inch rifles) attached; Lemon mw + 5 officer pins</t>
+        </is>
+      </c>
+      <c r="AI250" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 'about 1,600 strong' + the battery</t>
+        </is>
+      </c>
+      <c r="AJ250" s="5" t="inlineStr">
+        <is>
+          <t>[C ~8:00 + drawn] the delay line geometry primary (1 mi W of seminary, RR to Fairfield rd); j1-03 drawn bar vs OSM Gamble-HQ marker 115 m (HQ-on-the-line); [D+drawn] the j1-13 afternoon stand, seminary on the right as reported</t>
+        </is>
+      </c>
+      <c r="AK250" s="5" t="inlineStr">
+        <is>
+          <t>[D] camp-&gt;line on the 8:00 warning; the 200-yd fall-back; the relief hand-off; the afternoon trot + dismount + mounted withdrawal</t>
+        </is>
+      </c>
+      <c r="AL250" s="5" t="inlineStr">
+        <is>
+          <t>THE CA-J1M-2 EXECUTOR ('checking and retarding... several hours'; Buford: 'held its own for more than two hours'); the afternoon carbine stand ('saved a division of our infantry'); 'commenced the fight in the morning and close it in the evening'</t>
+        </is>
+      </c>
+      <c r="AM250" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 185) 99 campaign aggregate; July 1 dominant; no per-day split (flagged)</t>
+        </is>
+      </c>
       <c r="AN250" s="5" t="n"/>
-      <c r="AO250" s="5" t="n"/>
+      <c r="AO250" s="5" t="inlineStr">
+        <is>
+          <t>T4 (July 1 grain)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -29721,20 +29865,56 @@
           <t>reg-us-cav-1-2</t>
         </is>
       </c>
-      <c r="AB252" s="5" t="n"/>
+      <c r="AB252" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC252" s="5" t="n"/>
       <c r="AD252" s="5" t="n"/>
       <c r="AE252" s="5" t="n"/>
       <c r="AF252" s="5" t="n"/>
-      <c r="AG252" s="5" t="n"/>
-      <c r="AH252" s="5" t="n"/>
-      <c r="AI252" s="5" t="n"/>
-      <c r="AJ252" s="5" t="n"/>
-      <c r="AK252" s="5" t="n"/>
-      <c r="AL252" s="5" t="n"/>
-      <c r="AM252" s="5" t="n"/>
+      <c r="AG252" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-1-2-devin.md; kind-none (no clock in the whole narrative)</t>
+        </is>
+      </c>
+      <c r="AH252" s="5" t="inlineStr">
+        <is>
+          <t>Devin (6th NY); 9th NY named twice (Heidlersburg support; the town counter-charge)</t>
+        </is>
+      </c>
+      <c r="AI252" s="5" t="inlineStr">
+        <is>
+          <t>OPEN (no primary; B&amp;M-class reading not located)</t>
+        </is>
+      </c>
+      <c r="AJ252" s="5" t="inlineStr">
+        <is>
+          <t>[D] the four-road screen geometry primary (York-&gt;Cashtown continuous line); OSM Devin-HQ marker; the York-road post; night extreme left</t>
+        </is>
+      </c>
+      <c r="AK252" s="5" t="inlineStr">
+        <is>
+          <t>[D] the successive-formations-by-regiment withdrawal drill; the through-town displacement under friendly shells</t>
+        </is>
+      </c>
+      <c r="AL252" s="5" t="inlineStr">
+        <is>
+          <t>the two-hour Heidlersburg hold until XI Corps relief; THE FRIENDLY-FIRE RECORD (own Cemetery Hill battery); the 9th NY town counter-charge; July 2 Berdan support (Pitzer Woods both-sided)</t>
+        </is>
+      </c>
+      <c r="AM252" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 185) 28 campaign aggregate (the screen's low-contact profile)</t>
+        </is>
+      </c>
       <c r="AN252" s="5" t="n"/>
-      <c r="AO252" s="5" t="n"/>
+      <c r="AO252" s="5" t="inlineStr">
+        <is>
+          <t>T3 (July 1 grain)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -31900,7 +32080,7 @@
       <c r="AF271" s="5" t="n"/>
       <c r="AG271" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-hq-geary.md; Geary's own wrong-road narrative (pp. 828+) flagged unfetched</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-hq-geary.md; Geary's own wrong-road narrative (pp. 828+) flagged unfetched; pp. 826-830 read pass 10 (own wrong-road version; THE 3.30-vs-4.30 CA-J3M-1 conflict pair; the 8 a.m. wave-2 receiving clock pairing O'Neal)</t>
         </is>
       </c>
       <c r="AH271" s="5" t="inlineStr">
@@ -32191,12 +32371,12 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-hq</t>
+          <t>reg-us-i-hq</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>II Corps headquarters (corps command)</t>
+          <t>I Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -32237,7 +32417,7 @@
       </c>
       <c r="V274" s="2" t="inlineStr">
         <is>
-          <t>II Corps headquarters</t>
+          <t>I Corps headquarters</t>
         </is>
       </c>
       <c r="W274" s="4" t="inlineStr">
@@ -32258,12 +32438,12 @@
       </c>
       <c r="AA274" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-hq</t>
+          <t>reg-us-i-hq</t>
         </is>
       </c>
       <c r="AB274" s="5" t="inlineStr">
         <is>
-          <t>unauthored (command record)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC274" s="5" t="n"/>
@@ -32272,37 +32452,37 @@
       <c r="AF274" s="5" t="n"/>
       <c r="AG274" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-hq-hancock.md; register row added pass 5</t>
+          <t>Dossier: reconstruction/dossiers/us-i-hq-reynolds.md; register row added pass 10; Howard-11:30 conflict COLLAPSED (death vs word-reaching)</t>
         </is>
       </c>
       <c r="AH274" s="5" t="inlineStr">
         <is>
-          <t>Maj. Gen. W. S. Hancock (w July 3, 'toward the close'); corps + left-center wing command; July 1 arrival is ruled CA-J1P-7 (~16:15, partisan-dispute note)</t>
+          <t>Reynolds (corps + left wing; k ~10:15) -&gt; Doubleday (corps) / Howard (field); Newton July 2</t>
         </is>
       </c>
       <c r="AI274" s="5" t="inlineStr">
         <is>
-          <t>n/a (command entry); corps regiment grain in or-27-1-union-return</t>
+          <t>Doubleday's 8,200 -&gt; ~2,450 frame (litigious caveat)</t>
         </is>
       </c>
       <c r="AJ274" s="5" t="inlineStr">
         <is>
-          <t>[D] the mounted ride along the line under the cannonade; wounding position near Stannard's front (Vermont accounts)</t>
+          <t>the death site (mon-reynolds-kia); the seminary command node; the cemetery rally</t>
         </is>
       </c>
       <c r="AK274" s="5" t="inlineStr">
         <is>
-          <t>n/a (command entry)</t>
+          <t>command displacements; the corps' 1.5-2 h stagger primary</t>
         </is>
       </c>
       <c r="AL274" s="5" t="inlineStr">
         <is>
-          <t>[C report ~+7] his OR cannonade ladder ('About 1 o'clock ... After an hour and forty-five minutes') corroborates CA-J3A-1/4; the wounding TIME is a CONFLICT RECORD by design (no clock invented)</t>
+          <t>Reynolds's four last acts (the 10:10-dispatch promise; Wadsworth deployment; the Hall-support detachment; the Iron Bde launch); THE 10:15 PIN THREE-PRIMARY (tablet=Wadsworth=Doubleday); the 4 p.m. collapse; the Hancock/Howard dual-command scene</t>
         </is>
       </c>
       <c r="AM274" s="5" t="inlineStr">
         <is>
-          <t>wounding pin sequenced after Gibbon's ('A short time afterward I was myself wounded'); corps losses at regiment grain per ED-52</t>
+          <t>command grain (Reynolds k; the corps frame)</t>
         </is>
       </c>
       <c r="AN274" s="5" t="n"/>
@@ -32315,12 +32495,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>reg-us-hq-provost</t>
+          <t>reg-us-ii-hq</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Provost Guard and army headquarters detachments (Brig. Gen. Marsena R. Patrick)</t>
+          <t>II Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -32361,7 +32541,7 @@
       </c>
       <c r="V275" s="2" t="inlineStr">
         <is>
-          <t>Provost Guard and army headquarters detachments</t>
+          <t>II Corps headquarters</t>
         </is>
       </c>
       <c r="W275" s="4" t="inlineStr">
@@ -32382,33 +32562,69 @@
       </c>
       <c r="AA275" s="2" t="inlineStr">
         <is>
-          <t>reg-us-hq-provost</t>
-        </is>
-      </c>
-      <c r="AB275" s="5" t="n"/>
+          <t>reg-us-ii-hq</t>
+        </is>
+      </c>
+      <c r="AB275" s="5" t="inlineStr">
+        <is>
+          <t>unauthored (command record)</t>
+        </is>
+      </c>
       <c r="AC275" s="5" t="n"/>
       <c r="AD275" s="5" t="n"/>
       <c r="AE275" s="5" t="n"/>
       <c r="AF275" s="5" t="n"/>
-      <c r="AG275" s="5" t="n"/>
-      <c r="AH275" s="5" t="n"/>
-      <c r="AI275" s="5" t="n"/>
-      <c r="AJ275" s="5" t="n"/>
-      <c r="AK275" s="5" t="n"/>
-      <c r="AL275" s="5" t="n"/>
-      <c r="AM275" s="5" t="n"/>
+      <c r="AG275" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-hq-hancock.md; register row added pass 5; CA-J1P-7 conflict record FORMALIZED pass 10 (document pin + Doubleday scene + Schurz bound; ED-68 component)</t>
+        </is>
+      </c>
+      <c r="AH275" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Gen. W. S. Hancock (w July 3, 'toward the close'); corps + left-center wing command; July 1 arrival is ruled CA-J1P-7 (~16:15, partisan-dispute note)</t>
+        </is>
+      </c>
+      <c r="AI275" s="5" t="inlineStr">
+        <is>
+          <t>n/a (command entry); corps regiment grain in or-27-1-union-return</t>
+        </is>
+      </c>
+      <c r="AJ275" s="5" t="inlineStr">
+        <is>
+          <t>[D] the mounted ride along the line under the cannonade; wounding position near Stannard's front (Vermont accounts)</t>
+        </is>
+      </c>
+      <c r="AK275" s="5" t="inlineStr">
+        <is>
+          <t>n/a (command entry)</t>
+        </is>
+      </c>
+      <c r="AL275" s="5" t="inlineStr">
+        <is>
+          <t>[C report ~+7] his OR cannonade ladder ('About 1 o'clock ... After an hour and forty-five minutes') corroborates CA-J3A-1/4; the wounding TIME is a CONFLICT RECORD by design (no clock invented)</t>
+        </is>
+      </c>
+      <c r="AM275" s="5" t="inlineStr">
+        <is>
+          <t>wounding pin sequenced after Gibbon's ('A short time afterward I was myself wounded'); corps losses at regiment grain per ED-52</t>
+        </is>
+      </c>
       <c r="AN275" s="5" t="n"/>
-      <c r="AO275" s="5" t="n"/>
+      <c r="AO275" s="5" t="inlineStr">
+        <is>
+          <t>T3 (command record)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-hq</t>
+          <t>reg-us-hq-provost</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>XII Corps headquarters (corps command)</t>
+          <t>Provost Guard and army headquarters detachments (Brig. Gen. Marsena R. Patrick)</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -32449,7 +32665,7 @@
       </c>
       <c r="V276" s="2" t="inlineStr">
         <is>
-          <t>XII Corps headquarters</t>
+          <t>Provost Guard and army headquarters detachments</t>
         </is>
       </c>
       <c r="W276" s="4" t="inlineStr">
@@ -32470,69 +32686,33 @@
       </c>
       <c r="AA276" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-hq</t>
-        </is>
-      </c>
-      <c r="AB276" s="5" t="inlineStr">
-        <is>
-          <t>command record (the absent-then-returning frame)</t>
-        </is>
-      </c>
+          <t>reg-us-hq-provost</t>
+        </is>
+      </c>
+      <c r="AB276" s="5" t="n"/>
       <c r="AC276" s="5" t="n"/>
       <c r="AD276" s="5" t="n"/>
       <c r="AE276" s="5" t="n"/>
       <c r="AF276" s="5" t="n"/>
-      <c r="AG276" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-hq-slocum-williams.md; added pass 8 w/ register row</t>
-        </is>
-      </c>
-      <c r="AH276" s="5" t="inlineStr">
-        <is>
-          <t>Slocum right wing / WILLIAMS commanding the corps July 1-3 / Ruger 1st Div (cascade verbatim; return still heads the corps Slocum - metadata hazard)</t>
-        </is>
-      </c>
-      <c r="AI276" s="5" t="inlineStr">
-        <is>
-          <t>corps aggregate OPEN by design (unit EC2s carry it)</t>
-        </is>
-      </c>
-      <c r="AJ276" s="5" t="inlineStr">
-        <is>
-          <t>[E] the works line to McAllister's mill-pond (drawn+computed 140 m); [D] THE ABSENCE drawn on j2-04 (departing labels) + j2-05 '9. P.M.' return annotation (5931,4723) - a sheet-internal clock; HQ pin tab-us-xii-1-hq-williams</t>
-        </is>
-      </c>
-      <c r="AK276" s="5" t="inlineStr">
-        <is>
-          <t>[D] the detachment (Ruger+Lockwood to the left; Geary to cover); the left-wing round trip ending 'quite dark' (ED-31 physics); the return + the near-midnight wrong-road discovery</t>
-        </is>
-      </c>
-      <c r="AL276" s="5" t="inlineStr">
-        <is>
-          <t>the breastworks decision (Slocum, credited verbatim); THE McGILVERY MEETING + Lockwood's three-pieces recapture (ED-61 ledger, command grain); July 3 daylight plan (15-min artillery prep)</t>
-        </is>
-      </c>
-      <c r="AM276" s="5" t="inlineStr">
-        <is>
-          <t>corps total 1,082 (return p. 185); brigade rows recorded for the absent frame's future dossiers</t>
-        </is>
-      </c>
+      <c r="AG276" s="5" t="n"/>
+      <c r="AH276" s="5" t="n"/>
+      <c r="AI276" s="5" t="n"/>
+      <c r="AJ276" s="5" t="n"/>
+      <c r="AK276" s="5" t="n"/>
+      <c r="AL276" s="5" t="n"/>
+      <c r="AM276" s="5" t="n"/>
       <c r="AN276" s="5" t="n"/>
-      <c r="AO276" s="5" t="inlineStr">
-        <is>
-          <t>T3 (command record)</t>
-        </is>
-      </c>
+      <c r="AO276" s="5" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>us-hall</t>
+          <t>reg-us-xi-hq</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Hall's Brigade</t>
+          <t>XI Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -32542,7 +32722,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>parent-brigade</t>
+          <t>command</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -32550,92 +32730,56 @@
           <t>infantry</t>
         </is>
       </c>
-      <c r="F277" s="2" t="n">
-        <v>920</v>
-      </c>
-      <c r="G277" s="2" t="n">
-        <v>555</v>
-      </c>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="3">
         <f>IF(F277=0,0,1-G277/F277)</f>
         <v/>
       </c>
-      <c r="I277" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="J277" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K277" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L277" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M277" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O277" s="2" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="P277" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R277" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S277" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="I277" s="2" t="inlineStr"/>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr"/>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr"/>
+      <c r="O277" s="2" t="inlineStr"/>
+      <c r="P277" s="2" t="inlineStr"/>
+      <c r="Q277" s="2" t="inlineStr"/>
+      <c r="R277" s="2" t="inlineStr"/>
+      <c r="S277" s="2" t="inlineStr"/>
+      <c r="T277" s="2" t="inlineStr"/>
       <c r="U277" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V277" s="2" t="inlineStr">
         <is>
-          <t>Hall</t>
-        </is>
-      </c>
-      <c r="W277" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X277" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
+          <t>XI Corps headquarters</t>
+        </is>
+      </c>
+      <c r="W277" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="inlineStr"/>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
         <is>
-          <t>in-build</t>
+          <t>not-yet-cast</t>
         </is>
       </c>
       <c r="AA277" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-3</t>
+          <t>reg-us-xi-hq</t>
         </is>
       </c>
       <c r="AB277" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (crisis rush authored in Angle cast)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC277" s="5" t="n"/>
@@ -32644,55 +32788,55 @@
       <c r="AF277" s="5" t="n"/>
       <c r="AG277" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-hq-howard.md; register row added pass 10; ED-68 candidate (sub-anchor ~11:30)</t>
         </is>
       </c>
       <c r="AH277" s="5" t="inlineStr">
         <is>
-          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
+          <t>Howard (field command ~11:30-evening; corps to Schurz); Barlow w -&gt; Ames; Schimmelfennig cut off</t>
         </is>
       </c>
       <c r="AI277" s="5" t="inlineStr">
         <is>
-          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
+          <t>Schurz's 'hardly over 6,000' two-division frame</t>
         </is>
       </c>
       <c r="AJ277" s="5" t="inlineStr">
         <is>
-          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
+          <t>the cemetery eminence (the rally position chosen ~11:30); command nodes registered (town + hill pair)</t>
         </is>
       </c>
       <c r="AK277" s="5" t="inlineStr">
         <is>
-          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
+          <t>the corps approach ladder (3:30 orders / 8:00 march / 10:30 hurry / ~14:00 deployed)</t>
         </is>
       </c>
       <c r="AL277" s="5" t="inlineStr">
         <is>
-          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
+          <t>THE ASSUMPTION TWO-PRIMARY (Howard 11.30 = Schurz 11.30; tablet 10.30 collapsed onto the hurry-forward order); the 16:00/16:10/16:30 fall-back ladder; the CA-J1P-7 Howard pole</t>
         </is>
       </c>
       <c r="AM277" s="5" t="inlineStr">
         <is>
-          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
+          <t>corps 3,801 (1,448 c/m - the through-town capture mass)</t>
         </is>
       </c>
       <c r="AN277" s="5" t="n"/>
       <c r="AO277" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (T5-grade window via V2 claims)</t>
+          <t>T3 (command record)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>us-stannard</t>
+          <t>reg-us-xii-hq</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Stannard's Vermont Brigade</t>
+          <t>XII Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -32702,7 +32846,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>parent-brigade</t>
+          <t>command</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -32710,92 +32854,56 @@
           <t>infantry</t>
         </is>
       </c>
-      <c r="F278" s="2" t="n">
-        <v>1950</v>
-      </c>
-      <c r="G278" s="2" t="n">
-        <v>1600</v>
-      </c>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="3">
         <f>IF(F278=0,0,1-G278/F278)</f>
         <v/>
       </c>
-      <c r="I278" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="J278" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K278" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L278" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M278" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O278" s="2" t="n">
-        <v>297.9</v>
-      </c>
-      <c r="P278" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="R278" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S278" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr"/>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="2" t="inlineStr"/>
+      <c r="P278" s="2" t="inlineStr"/>
+      <c r="Q278" s="2" t="inlineStr"/>
+      <c r="R278" s="2" t="inlineStr"/>
+      <c r="S278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr"/>
       <c r="U278" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V278" s="2" t="inlineStr">
         <is>
-          <t>Stannard</t>
-        </is>
-      </c>
-      <c r="W278" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X278" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
+          <t>XII Corps headquarters</t>
+        </is>
+      </c>
+      <c r="W278" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="inlineStr"/>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>in-build</t>
+          <t>not-yet-cast</t>
         </is>
       </c>
       <c r="AA278" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-3</t>
+          <t>reg-us-xii-hq</t>
         </is>
       </c>
       <c r="AB278" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>command record (the absent-then-returning frame)</t>
         </is>
       </c>
       <c r="AC278" s="5" t="n"/>
@@ -32804,55 +32912,55 @@
       <c r="AF278" s="5" t="n"/>
       <c r="AG278" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-hq-slocum-williams.md; added pass 8 w/ register row</t>
         </is>
       </c>
       <c r="AH278" s="5" t="inlineStr">
         <is>
-          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
+          <t>Slocum right wing / WILLIAMS commanding the corps July 1-3 / Ruger 1st Div (cascade verbatim; return still heads the corps Slocum - metadata hazard)</t>
         </is>
       </c>
       <c r="AI278" s="5" t="inlineStr">
         <is>
-          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
+          <t>corps aggregate OPEN by design (unit EC2s carry it)</t>
         </is>
       </c>
       <c r="AJ278" s="5" t="inlineStr">
         <is>
-          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
+          <t>[E] the works line to McAllister's mill-pond (drawn+computed 140 m); [D] THE ABSENCE drawn on j2-04 (departing labels) + j2-05 '9. P.M.' return annotation (5931,4723) - a sheet-internal clock; HQ pin tab-us-xii-1-hq-williams</t>
         </is>
       </c>
       <c r="AK278" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
+          <t>[D] the detachment (Ruger+Lockwood to the left; Geary to cover); the left-wing round trip ending 'quite dark' (ED-31 physics); the return + the near-midnight wrong-road discovery</t>
         </is>
       </c>
       <c r="AL278" s="5" t="inlineStr">
         <is>
-          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
+          <t>the breastworks decision (Slocum, credited verbatim); THE McGILVERY MEETING + Lockwood's three-pieces recapture (ED-61 ledger, command grain); July 3 daylight plan (15-min artillery prep)</t>
         </is>
       </c>
       <c r="AM278" s="5" t="inlineStr">
         <is>
-          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
+          <t>corps total 1,082 (return p. 185); brigade rows recorded for the absent frame's future dossiers</t>
         </is>
       </c>
       <c r="AN278" s="5" t="n"/>
       <c r="AO278" s="5" t="inlineStr">
         <is>
-          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
+          <t>T3 (command record)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>us-webb</t>
+          <t>us-hall</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Webb's Brigade (Philadelphia Brigade)</t>
+          <t>Hall's Brigade</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -32871,23 +32979,23 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>1250</v>
+        <v>920</v>
       </c>
       <c r="G279" s="2" t="n">
-        <v>760</v>
+        <v>555</v>
       </c>
       <c r="H279" s="3">
         <f>IF(F279=0,0,1-G279/F279)</f>
         <v/>
       </c>
       <c r="I279" s="2" t="n">
-        <v>490</v>
+        <v>365</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L279" s="2" t="n">
         <v>4</v>
@@ -32896,10 +33004,10 @@
         <v>0</v>
       </c>
       <c r="N279" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O279" s="2" t="n">
-        <v>23.3</v>
+        <v>60.9</v>
       </c>
       <c r="P279" s="2" t="n">
         <v>0</v>
@@ -32918,14 +33026,14 @@
         <v>0</v>
       </c>
       <c r="T279" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U279" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V279" s="2" t="inlineStr">
         <is>
-          <t>Webb</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="W279" s="2" t="inlineStr">
@@ -32950,12 +33058,12 @@
       </c>
       <c r="AA279" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-2</t>
+          <t>reg-us-ii-2-3</t>
         </is>
       </c>
       <c r="AB279" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (crisis rush authored in Angle cast)</t>
         </is>
       </c>
       <c r="AC279" s="5" t="n"/>
@@ -32964,55 +33072,55 @@
       <c r="AF279" s="5" t="n"/>
       <c r="AG279" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
         </is>
       </c>
       <c r="AH279" s="5" t="inlineStr">
         <is>
-          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
+          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
         </is>
       </c>
       <c r="AI279" s="5" t="inlineStr">
         <is>
-          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
+          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
         </is>
       </c>
       <c r="AJ279" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
+          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
         </is>
       </c>
       <c r="AK279" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
+          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
         </is>
       </c>
       <c r="AL279" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
+          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
         </is>
       </c>
       <c r="AM279" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
+          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
         </is>
       </c>
       <c r="AN279" s="5" t="n"/>
       <c r="AO279" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (T5 window held)</t>
+          <t>T4 full-arc (T5-grade window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>us-8oh</t>
+          <t>us-stannard</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>8th Ohio Infantry</t>
+          <t>Stannard's Vermont Brigade</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -33022,7 +33130,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>parent-brigade</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -33031,71 +33139,71 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>209</v>
+        <v>1950</v>
       </c>
       <c r="G280" s="2" t="n">
-        <v>170</v>
+        <v>1600</v>
       </c>
       <c r="H280" s="3">
         <f>IF(F280=0,0,1-G280/F280)</f>
         <v/>
       </c>
       <c r="I280" s="2" t="n">
-        <v>39</v>
+        <v>350</v>
       </c>
       <c r="J280" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O280" s="2" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K280" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L280" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M280" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O280" s="2" t="n">
-        <v>219.5</v>
-      </c>
-      <c r="P280" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q280" s="2" t="inlineStr">
+      <c r="U280" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V280" s="2" t="inlineStr">
+        <is>
+          <t>Stannard</t>
+        </is>
+      </c>
+      <c r="W280" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R280" s="2" t="inlineStr">
-        <is>
-          <t>line/skirmish</t>
-        </is>
-      </c>
-      <c r="S280" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T280" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U280" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V280" s="2" t="inlineStr">
-        <is>
-          <t>8th Ohio</t>
-        </is>
-      </c>
-      <c r="W280" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="Y280" s="2" t="inlineStr">
@@ -33108,7 +33216,11 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-i-3-3</t>
+        </is>
+      </c>
       <c r="AB280" s="5" t="inlineStr">
         <is>
           <t>authored-ok</t>
@@ -33120,55 +33232,55 @@
       <c r="AF280" s="5" t="n"/>
       <c r="AG280" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
         </is>
       </c>
       <c r="AH280" s="5" t="inlineStr">
         <is>
-          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
         </is>
       </c>
       <c r="AI280" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 209 (compilation, flagged)</t>
+          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
         </is>
       </c>
       <c r="AJ280" s="5" t="inlineStr">
         <is>
-          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
         </is>
       </c>
       <c r="AK280" s="5" t="inlineStr">
         <is>
-          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
         </is>
       </c>
       <c r="AL280" s="5" t="inlineStr">
         <is>
-          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
         </is>
       </c>
       <c r="AM280" s="5" t="inlineStr">
         <is>
-          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
         </is>
       </c>
       <c r="AN280" s="5" t="n"/>
       <c r="AO280" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>us-bartlett</t>
+          <t>us-webb</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
+          <t>Webb's Brigade (Philadelphia Brigade)</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -33178,7 +33290,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>parent-brigade</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -33187,35 +33299,35 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>1325</v>
+        <v>1250</v>
       </c>
       <c r="G281" s="2" t="n">
-        <v>1325</v>
+        <v>760</v>
       </c>
       <c r="H281" s="3">
         <f>IF(F281=0,0,1-G281/F281)</f>
         <v/>
       </c>
       <c r="I281" s="2" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="J281" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K281" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L281" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M281" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N281" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O281" s="2" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="P281" s="2" t="n">
         <v>0</v>
@@ -33234,14 +33346,14 @@
         <v>0</v>
       </c>
       <c r="T281" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U281" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V281" s="2" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>Webb</t>
         </is>
       </c>
       <c r="W281" s="2" t="inlineStr">
@@ -33251,12 +33363,12 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
@@ -33266,33 +33378,69 @@
       </c>
       <c r="AA281" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-2</t>
-        </is>
-      </c>
-      <c r="AB281" s="5" t="n"/>
+          <t>reg-us-ii-2-2</t>
+        </is>
+      </c>
+      <c r="AB281" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC281" s="5" t="n"/>
       <c r="AD281" s="5" t="n"/>
       <c r="AE281" s="5" t="n"/>
       <c r="AF281" s="5" t="n"/>
-      <c r="AG281" s="5" t="n"/>
-      <c r="AH281" s="5" t="n"/>
-      <c r="AI281" s="5" t="n"/>
-      <c r="AJ281" s="5" t="n"/>
-      <c r="AK281" s="5" t="n"/>
-      <c r="AL281" s="5" t="n"/>
-      <c r="AM281" s="5" t="n"/>
+      <c r="AG281" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
+        </is>
+      </c>
+      <c r="AH281" s="5" t="inlineStr">
+        <is>
+          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
+        </is>
+      </c>
+      <c r="AI281" s="5" t="inlineStr">
+        <is>
+          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
+        </is>
+      </c>
+      <c r="AJ281" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
+        </is>
+      </c>
+      <c r="AK281" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
+        </is>
+      </c>
+      <c r="AL281" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
+        </is>
+      </c>
+      <c r="AM281" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
+        </is>
+      </c>
       <c r="AN281" s="5" t="n"/>
-      <c r="AO281" s="5" t="n"/>
+      <c r="AO281" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (T5 window held)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>us-baxter</t>
+          <t>us-8oh</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
+          <t>8th Ohio Infantry</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -33311,68 +33459,68 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>800</v>
+        <v>209</v>
       </c>
       <c r="G282" s="2" t="n">
-        <v>800</v>
+        <v>170</v>
       </c>
       <c r="H282" s="3">
         <f>IF(F282=0,0,1-G282/F282)</f>
         <v/>
       </c>
       <c r="I282" s="2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J282" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K282" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O282" s="2" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="P282" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>line/skirmish</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M282" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N282" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="O282" s="2" t="n">
-        <v>1021.5</v>
-      </c>
-      <c r="P282" s="2" t="n">
-        <v>1021.5</v>
-      </c>
-      <c r="Q282" s="2" t="inlineStr">
+      <c r="T282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V282" s="2" t="inlineStr">
+        <is>
+          <t>8th Ohio</t>
+        </is>
+      </c>
+      <c r="W282" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R282" s="2" t="inlineStr">
-        <is>
-          <t>column/line</t>
-        </is>
-      </c>
-      <c r="S282" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T282" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U282" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V282" s="2" t="inlineStr">
-        <is>
-          <t>Baxter</t>
-        </is>
-      </c>
-      <c r="W282" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
           <t>T1</t>
@@ -33380,7 +33528,7 @@
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
@@ -33388,35 +33536,67 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA282" s="2" t="inlineStr">
-        <is>
-          <t>reg-us-i-2-2</t>
-        </is>
-      </c>
-      <c r="AB282" s="5" t="n"/>
+      <c r="AA282" s="2" t="inlineStr"/>
+      <c r="AB282" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC282" s="5" t="n"/>
       <c r="AD282" s="5" t="n"/>
       <c r="AE282" s="5" t="n"/>
       <c r="AF282" s="5" t="n"/>
-      <c r="AG282" s="5" t="n"/>
-      <c r="AH282" s="5" t="n"/>
-      <c r="AI282" s="5" t="n"/>
-      <c r="AJ282" s="5" t="n"/>
-      <c r="AK282" s="5" t="n"/>
-      <c r="AL282" s="5" t="n"/>
-      <c r="AM282" s="5" t="n"/>
+      <c r="AG282" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+        </is>
+      </c>
+      <c r="AH282" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+        </is>
+      </c>
+      <c r="AI282" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 209 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ282" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+        </is>
+      </c>
+      <c r="AK282" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+        </is>
+      </c>
+      <c r="AL282" s="5" t="inlineStr">
+        <is>
+          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+        </is>
+      </c>
+      <c r="AM282" s="5" t="inlineStr">
+        <is>
+          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+        </is>
+      </c>
       <c r="AN282" s="5" t="n"/>
-      <c r="AO282" s="5" t="n"/>
+      <c r="AO282" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>us-berdan</t>
+          <t>us-bartlett</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
+          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -33435,10 +33615,10 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>1405</v>
+        <v>1325</v>
       </c>
       <c r="G283" s="2" t="n">
-        <v>1405</v>
+        <v>1325</v>
       </c>
       <c r="H283" s="3">
         <f>IF(F283=0,0,1-G283/F283)</f>
@@ -33475,7 +33655,7 @@
       </c>
       <c r="R283" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S283" s="2" t="n">
@@ -33489,7 +33669,7 @@
       </c>
       <c r="V283" s="2" t="inlineStr">
         <is>
-          <t>Berdan</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="W283" s="2" t="inlineStr">
@@ -33514,69 +33694,33 @@
       </c>
       <c r="AA283" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-2</t>
-        </is>
-      </c>
-      <c r="AB283" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 defender)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-1-2</t>
+        </is>
+      </c>
+      <c r="AB283" s="5" t="n"/>
       <c r="AC283" s="5" t="n"/>
       <c r="AD283" s="5" t="n"/>
       <c r="AE283" s="5" t="n"/>
       <c r="AF283" s="5" t="n"/>
-      <c r="AG283" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
-        </is>
-      </c>
-      <c r="AH283" s="5" t="inlineStr">
-        <is>
-          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
-        </is>
-      </c>
-      <c r="AI283" s="5" t="inlineStr">
-        <is>
-          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
-        </is>
-      </c>
-      <c r="AJ283" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
-        </is>
-      </c>
-      <c r="AK283" s="5" t="inlineStr">
-        <is>
-          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
-        </is>
-      </c>
-      <c r="AL283" s="5" t="inlineStr">
-        <is>
-          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
-        </is>
-      </c>
-      <c r="AM283" s="5" t="inlineStr">
-        <is>
-          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
-        </is>
-      </c>
+      <c r="AG283" s="5" t="n"/>
+      <c r="AH283" s="5" t="n"/>
+      <c r="AI283" s="5" t="n"/>
+      <c r="AJ283" s="5" t="n"/>
+      <c r="AK283" s="5" t="n"/>
+      <c r="AL283" s="5" t="n"/>
+      <c r="AM283" s="5" t="n"/>
       <c r="AN283" s="5" t="n"/>
-      <c r="AO283" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO283" s="5" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>us-biddle</t>
+          <t>us-baxter</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
+          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -33595,10 +33739,10 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>460</v>
+        <v>800</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>460</v>
+        <v>800</v>
       </c>
       <c r="H284" s="3">
         <f>IF(F284=0,0,1-G284/F284)</f>
@@ -33608,38 +33752,38 @@
         <v>0</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M284" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N284" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O284" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="P284" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T284" s="2" t="n">
         <v>0</v>
@@ -33649,7 +33793,7 @@
       </c>
       <c r="V284" s="2" t="inlineStr">
         <is>
-          <t>Biddle</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="W284" s="2" t="inlineStr">
@@ -33664,7 +33808,7 @@
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
@@ -33674,69 +33818,33 @@
       </c>
       <c r="AA284" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-1</t>
-        </is>
-      </c>
-      <c r="AB284" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok</t>
-        </is>
-      </c>
+          <t>reg-us-i-2-2</t>
+        </is>
+      </c>
+      <c r="AB284" s="5" t="n"/>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
-        </is>
-      </c>
-      <c r="AH284" s="5" t="inlineStr">
-        <is>
-          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
-        </is>
-      </c>
-      <c r="AI284" s="5" t="inlineStr">
-        <is>
-          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
-        </is>
-      </c>
-      <c r="AJ284" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
-        </is>
-      </c>
-      <c r="AK284" s="5" t="inlineStr">
-        <is>
-          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
-        </is>
-      </c>
-      <c r="AL284" s="5" t="inlineStr">
-        <is>
-          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
-        </is>
-      </c>
-      <c r="AM284" s="5" t="inlineStr">
-        <is>
-          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
-        </is>
-      </c>
+      <c r="AG284" s="5" t="n"/>
+      <c r="AH284" s="5" t="n"/>
+      <c r="AI284" s="5" t="n"/>
+      <c r="AJ284" s="5" t="n"/>
+      <c r="AK284" s="5" t="n"/>
+      <c r="AL284" s="5" t="n"/>
+      <c r="AM284" s="5" t="n"/>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="inlineStr">
-        <is>
-          <t>T3 full-arc</t>
-        </is>
-      </c>
+      <c r="AO284" s="5" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>us-brewster</t>
+          <t>us-berdan</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
+          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -33755,10 +33863,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>1060</v>
+        <v>1405</v>
       </c>
       <c r="G285" s="2" t="n">
-        <v>1060</v>
+        <v>1405</v>
       </c>
       <c r="H285" s="3">
         <f>IF(F285=0,0,1-G285/F285)</f>
@@ -33809,7 +33917,7 @@
       </c>
       <c r="V285" s="2" t="inlineStr">
         <is>
-          <t>Brewster</t>
+          <t>Berdan</t>
         </is>
       </c>
       <c r="W285" s="2" t="inlineStr">
@@ -33834,12 +33942,12 @@
       </c>
       <c r="AA285" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-2</t>
+          <t>reg-us-iii-1-2</t>
         </is>
       </c>
       <c r="AB285" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 defender)</t>
         </is>
       </c>
       <c r="AC285" s="5" t="n"/>
@@ -33848,37 +33956,37 @@
       <c r="AF285" s="5" t="n"/>
       <c r="AG285" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
         </is>
       </c>
       <c r="AH285" s="5" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
+          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
         </is>
       </c>
       <c r="AI285" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
+          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
         </is>
       </c>
       <c r="AJ285" s="5" t="inlineStr">
         <is>
-          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
+          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
         </is>
       </c>
       <c r="AK285" s="5" t="inlineStr">
         <is>
-          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
+          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
         </is>
       </c>
       <c r="AL285" s="5" t="inlineStr">
         <is>
-          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
+          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
         </is>
       </c>
       <c r="AM285" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
+          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
         </is>
       </c>
       <c r="AN285" s="5" t="n"/>
@@ -33891,12 +33999,12 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>us-brooke</t>
+          <t>us-biddle</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
+          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -33959,7 +34067,7 @@
         </is>
       </c>
       <c r="S286" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T286" s="2" t="n">
         <v>0</v>
@@ -33969,7 +34077,7 @@
       </c>
       <c r="V286" s="2" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Biddle</t>
         </is>
       </c>
       <c r="W286" s="2" t="inlineStr">
@@ -33984,7 +34092,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
@@ -33994,12 +34102,12 @@
       </c>
       <c r="AA286" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-4</t>
+          <t>reg-us-i-3-1</t>
         </is>
       </c>
       <c r="AB286" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC286" s="5" t="n"/>
@@ -34008,55 +34116,55 @@
       <c r="AF286" s="5" t="n"/>
       <c r="AG286" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
         </is>
       </c>
       <c r="AH286" s="5" t="inlineStr">
         <is>
-          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AI286" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
         </is>
       </c>
       <c r="AJ286" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
         </is>
       </c>
       <c r="AK286" s="5" t="inlineStr">
         <is>
-          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
         </is>
       </c>
       <c r="AL286" s="5" t="inlineStr">
         <is>
-          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AM286" s="5" t="inlineStr">
         <is>
-          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
         </is>
       </c>
       <c r="AN286" s="5" t="n"/>
       <c r="AO286" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>us-burbank</t>
+          <t>us-brewster</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
+          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -34075,10 +34183,10 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>505</v>
+        <v>1060</v>
       </c>
       <c r="G287" s="2" t="n">
-        <v>505</v>
+        <v>1060</v>
       </c>
       <c r="H287" s="3">
         <f>IF(F287=0,0,1-G287/F287)</f>
@@ -34115,7 +34223,7 @@
       </c>
       <c r="R287" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S287" s="2" t="n">
@@ -34129,7 +34237,7 @@
       </c>
       <c r="V287" s="2" t="inlineStr">
         <is>
-          <t>Burbank</t>
+          <t>Brewster</t>
         </is>
       </c>
       <c r="W287" s="2" t="inlineStr">
@@ -34154,12 +34262,12 @@
       </c>
       <c r="AA287" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-2</t>
+          <t>reg-us-iii-2-2</t>
         </is>
       </c>
       <c r="AB287" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC287" s="5" t="n"/>
@@ -34168,37 +34276,37 @@
       <c r="AF287" s="5" t="n"/>
       <c r="AG287" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
         </is>
       </c>
       <c r="AH287" s="5" t="inlineStr">
         <is>
-          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
+          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
         </is>
       </c>
       <c r="AI287" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
+          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
         </is>
       </c>
       <c r="AJ287" s="5" t="inlineStr">
         <is>
-          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
+          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
         </is>
       </c>
       <c r="AK287" s="5" t="inlineStr">
         <is>
-          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
+          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
         </is>
       </c>
       <c r="AL287" s="5" t="inlineStr">
         <is>
-          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
+          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
         </is>
       </c>
       <c r="AM287" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
+          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
         </is>
       </c>
       <c r="AN287" s="5" t="n"/>
@@ -34211,12 +34319,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>us-burling</t>
+          <t>us-brooke</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
+          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -34235,10 +34343,10 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>850</v>
+        <v>460</v>
       </c>
       <c r="G288" s="2" t="n">
-        <v>850</v>
+        <v>460</v>
       </c>
       <c r="H288" s="3">
         <f>IF(F288=0,0,1-G288/F288)</f>
@@ -34275,7 +34383,7 @@
       </c>
       <c r="R288" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S288" s="2" t="n">
@@ -34289,7 +34397,7 @@
       </c>
       <c r="V288" s="2" t="inlineStr">
         <is>
-          <t>Burling</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="W288" s="2" t="inlineStr">
@@ -34314,12 +34422,12 @@
       </c>
       <c r="AA288" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-3</t>
+          <t>reg-us-ii-1-4</t>
         </is>
       </c>
       <c r="AB288" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 DISPERSED class)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC288" s="5" t="n"/>
@@ -34328,55 +34436,55 @@
       <c r="AF288" s="5" t="n"/>
       <c r="AG288" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
         </is>
       </c>
       <c r="AH288" s="5" t="inlineStr">
         <is>
-          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
+          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
         </is>
       </c>
       <c r="AI288" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
+          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
         </is>
       </c>
       <c r="AJ288" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
+          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
         </is>
       </c>
       <c r="AK288" s="5" t="inlineStr">
         <is>
-          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
+          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
         </is>
       </c>
       <c r="AL288" s="5" t="inlineStr">
         <is>
-          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
+          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
         </is>
       </c>
       <c r="AM288" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
+          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
         </is>
       </c>
       <c r="AN288" s="5" t="n"/>
       <c r="AO288" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (dispersed class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>us-candy</t>
+          <t>us-burbank</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
+          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -34395,10 +34503,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>1400</v>
+        <v>505</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1400</v>
+        <v>505</v>
       </c>
       <c r="H289" s="3">
         <f>IF(F289=0,0,1-G289/F289)</f>
@@ -34449,7 +34557,7 @@
       </c>
       <c r="V289" s="2" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Burbank</t>
         </is>
       </c>
       <c r="W289" s="2" t="inlineStr">
@@ -34474,12 +34582,12 @@
       </c>
       <c r="AA289" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-1</t>
+          <t>reg-us-v-2-2</t>
         </is>
       </c>
       <c r="AB289" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 single-window mover)</t>
         </is>
       </c>
       <c r="AC289" s="5" t="n"/>
@@ -34488,55 +34596,55 @@
       <c r="AF289" s="5" t="n"/>
       <c r="AG289" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
         </is>
       </c>
       <c r="AH289" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
+          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
         </is>
       </c>
       <c r="AI289" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
         </is>
       </c>
       <c r="AJ289" s="5" t="inlineStr">
         <is>
-          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
+          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
         </is>
       </c>
       <c r="AK289" s="5" t="inlineStr">
         <is>
-          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
+          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
         </is>
       </c>
       <c r="AL289" s="5" t="inlineStr">
         <is>
-          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
+          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
         </is>
       </c>
       <c r="AM289" s="5" t="inlineStr">
         <is>
-          <t>return brigade total 139 (division arithmetic closes 540=303+139+98); regiment rows the cheap residual</t>
+          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
         </is>
       </c>
       <c r="AN289" s="5" t="n"/>
       <c r="AO289" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>us-carr</t>
+          <t>us-burling</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
+          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -34555,10 +34663,10 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>925</v>
+        <v>850</v>
       </c>
       <c r="G290" s="2" t="n">
-        <v>925</v>
+        <v>850</v>
       </c>
       <c r="H290" s="3">
         <f>IF(F290=0,0,1-G290/F290)</f>
@@ -34605,11 +34713,11 @@
         <v>0</v>
       </c>
       <c r="U290" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V290" s="2" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Burling</t>
         </is>
       </c>
       <c r="W290" s="2" t="inlineStr">
@@ -34634,12 +34742,12 @@
       </c>
       <c r="AA290" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-1</t>
+          <t>reg-us-iii-2-3</t>
         </is>
       </c>
       <c r="AB290" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 DISPERSED class)</t>
         </is>
       </c>
       <c r="AC290" s="5" t="n"/>
@@ -34648,55 +34756,55 @@
       <c r="AF290" s="5" t="n"/>
       <c r="AG290" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
         </is>
       </c>
       <c r="AH290" s="5" t="inlineStr">
         <is>
-          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
+          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
         </is>
       </c>
       <c r="AI290" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
+          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
         </is>
       </c>
       <c r="AJ290" s="5" t="inlineStr">
         <is>
-          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
+          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
         </is>
       </c>
       <c r="AK290" s="5" t="inlineStr">
         <is>
-          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
+          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
         </is>
       </c>
       <c r="AL290" s="5" t="inlineStr">
         <is>
-          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
+          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
         </is>
       </c>
       <c r="AM290" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
+          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
         </is>
       </c>
       <c r="AN290" s="5" t="n"/>
       <c r="AO290" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 full-arc (dispersed class)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>us-carroll</t>
+          <t>us-candy</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
+          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -34715,10 +34823,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>640</v>
+        <v>1400</v>
       </c>
       <c r="G291" s="2" t="n">
-        <v>640</v>
+        <v>1400</v>
       </c>
       <c r="H291" s="3">
         <f>IF(F291=0,0,1-G291/F291)</f>
@@ -34765,11 +34873,11 @@
         <v>0</v>
       </c>
       <c r="U291" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V291" s="2" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="W291" s="2" t="inlineStr">
@@ -34794,12 +34902,12 @@
       </c>
       <c r="AA291" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-1</t>
+          <t>reg-us-xii-2-1</t>
         </is>
       </c>
       <c r="AB291" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC291" s="5" t="n"/>
@@ -34808,55 +34916,55 @@
       <c r="AF291" s="5" t="n"/>
       <c r="AG291" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md; the Geary 5/5.45/6 a.m. ladder + rows landed pass 10</t>
         </is>
       </c>
       <c r="AH291" s="5" t="inlineStr">
         <is>
-          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
         </is>
       </c>
       <c r="AI291" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 640 (compilation, flagged)</t>
+          <t>OPEN (no primary; no hop)</t>
         </is>
       </c>
       <c r="AJ291" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
+          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
         </is>
       </c>
       <c r="AK291" s="5" t="inlineStr">
         <is>
-          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
         </is>
       </c>
       <c r="AL291" s="5" t="inlineStr">
         <is>
-          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
         </is>
       </c>
       <c r="AM291" s="5" t="inlineStr">
         <is>
-          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+          <t>p. 184 rows (pass 10): 139 = 5 OH 18, 7 OH 18, 29 OH 38, 66 OH 17, 28 Pa 28, 147 Pa 20 (sum exact)</t>
         </is>
       </c>
       <c r="AN291" s="5" t="n"/>
       <c r="AO291" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>us-colgrove</t>
+          <t>us-carr</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
+          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -34875,10 +34983,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>1170</v>
+        <v>925</v>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1170</v>
+        <v>925</v>
       </c>
       <c r="H292" s="3">
         <f>IF(F292=0,0,1-G292/F292)</f>
@@ -34915,7 +35023,7 @@
       </c>
       <c r="R292" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S292" s="2" t="n">
@@ -34925,11 +35033,11 @@
         <v>0</v>
       </c>
       <c r="U292" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V292" s="2" t="inlineStr">
         <is>
-          <t>Colgrove</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="W292" s="2" t="inlineStr">
@@ -34954,12 +35062,12 @@
       </c>
       <c r="AA292" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-3</t>
+          <t>reg-us-iii-2-1</t>
         </is>
       </c>
       <c r="AB292" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (the CA-J3M-3 executor)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC292" s="5" t="n"/>
@@ -34968,37 +35076,37 @@
       <c r="AF292" s="5" t="n"/>
       <c r="AG292" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
         </is>
       </c>
       <c r="AH292" s="5" t="inlineStr">
         <is>
-          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
+          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
         </is>
       </c>
       <c r="AI292" s="5" t="inlineStr">
         <is>
-          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
+          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AJ292" s="5" t="inlineStr">
         <is>
-          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
+          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
         </is>
       </c>
       <c r="AK292" s="5" t="inlineStr">
         <is>
-          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
+          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
         </is>
       </c>
       <c r="AL292" s="5" t="inlineStr">
         <is>
-          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
+          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
         </is>
       </c>
       <c r="AM292" s="5" t="inlineStr">
         <is>
-          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
+          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
         </is>
       </c>
       <c r="AN292" s="5" t="n"/>
@@ -35011,12 +35119,12 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>us-coster</t>
+          <t>us-carroll</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
+          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -35035,10 +35143,10 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="G293" s="2" t="n">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="H293" s="3">
         <f>IF(F293=0,0,1-G293/F293)</f>
@@ -35085,11 +35193,11 @@
         <v>0</v>
       </c>
       <c r="U293" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V293" s="2" t="inlineStr">
         <is>
-          <t>Coster</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="W293" s="2" t="inlineStr">
@@ -35114,33 +35222,69 @@
       </c>
       <c r="AA293" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-1</t>
-        </is>
-      </c>
-      <c r="AB293" s="5" t="n"/>
+          <t>reg-us-ii-3-1</t>
+        </is>
+      </c>
+      <c r="AB293" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+        </is>
+      </c>
       <c r="AC293" s="5" t="n"/>
       <c r="AD293" s="5" t="n"/>
       <c r="AE293" s="5" t="n"/>
       <c r="AF293" s="5" t="n"/>
-      <c r="AG293" s="5" t="n"/>
-      <c r="AH293" s="5" t="n"/>
-      <c r="AI293" s="5" t="n"/>
-      <c r="AJ293" s="5" t="n"/>
-      <c r="AK293" s="5" t="n"/>
-      <c r="AL293" s="5" t="n"/>
-      <c r="AM293" s="5" t="n"/>
+      <c r="AG293" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+        </is>
+      </c>
+      <c r="AH293" s="5" t="inlineStr">
+        <is>
+          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+        </is>
+      </c>
+      <c r="AI293" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 640 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ293" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
+        </is>
+      </c>
+      <c r="AK293" s="5" t="inlineStr">
+        <is>
+          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+        </is>
+      </c>
+      <c r="AL293" s="5" t="inlineStr">
+        <is>
+          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+        </is>
+      </c>
+      <c r="AM293" s="5" t="inlineStr">
+        <is>
+          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+        </is>
+      </c>
       <c r="AN293" s="5" t="n"/>
-      <c r="AO293" s="5" t="n"/>
+      <c r="AO293" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>us-coulter</t>
+          <t>us-colgrove</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
+          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -35159,10 +35303,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="G294" s="2" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="H294" s="3">
         <f>IF(F294=0,0,1-G294/F294)</f>
@@ -35172,34 +35316,34 @@
         <v>0</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L294" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N294" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="P294" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R294" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S294" s="2" t="n">
@@ -35213,7 +35357,7 @@
       </c>
       <c r="V294" s="2" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Colgrove</t>
         </is>
       </c>
       <c r="W294" s="2" t="inlineStr">
@@ -35228,7 +35372,7 @@
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr">
@@ -35238,33 +35382,69 @@
       </c>
       <c r="AA294" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-1</t>
-        </is>
-      </c>
-      <c r="AB294" s="5" t="n"/>
+          <t>reg-us-xii-1-3</t>
+        </is>
+      </c>
+      <c r="AB294" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (the CA-J3M-3 executor)</t>
+        </is>
+      </c>
       <c r="AC294" s="5" t="n"/>
       <c r="AD294" s="5" t="n"/>
       <c r="AE294" s="5" t="n"/>
       <c r="AF294" s="5" t="n"/>
-      <c r="AG294" s="5" t="n"/>
-      <c r="AH294" s="5" t="n"/>
-      <c r="AI294" s="5" t="n"/>
-      <c r="AJ294" s="5" t="n"/>
-      <c r="AK294" s="5" t="n"/>
-      <c r="AL294" s="5" t="n"/>
-      <c r="AM294" s="5" t="n"/>
+      <c r="AG294" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
+        </is>
+      </c>
+      <c r="AH294" s="5" t="inlineStr">
+        <is>
+          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
+        </is>
+      </c>
+      <c r="AI294" s="5" t="inlineStr">
+        <is>
+          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
+        </is>
+      </c>
+      <c r="AJ294" s="5" t="inlineStr">
+        <is>
+          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
+        </is>
+      </c>
+      <c r="AK294" s="5" t="inlineStr">
+        <is>
+          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
+        </is>
+      </c>
+      <c r="AL294" s="5" t="inlineStr">
+        <is>
+          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
+        </is>
+      </c>
+      <c r="AM294" s="5" t="inlineStr">
+        <is>
+          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
+        </is>
+      </c>
       <c r="AN294" s="5" t="n"/>
-      <c r="AO294" s="5" t="n"/>
+      <c r="AO294" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>us-cutler</t>
+          <t>us-coster</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
+          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -35283,10 +35463,10 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>1015</v>
+        <v>655</v>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1015</v>
+        <v>655</v>
       </c>
       <c r="H295" s="3">
         <f>IF(F295=0,0,1-G295/F295)</f>
@@ -35337,7 +35517,7 @@
       </c>
       <c r="V295" s="2" t="inlineStr">
         <is>
-          <t>Cutler</t>
+          <t>Coster</t>
         </is>
       </c>
       <c r="W295" s="2" t="inlineStr">
@@ -35362,7 +35542,7 @@
       </c>
       <c r="AA295" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-2</t>
+          <t>reg-us-xi-2-1</t>
         </is>
       </c>
       <c r="AB295" s="5" t="n"/>
@@ -35383,12 +35563,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>us-dana</t>
+          <t>us-coulter</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
+          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -35407,10 +35587,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="G296" s="2" t="n">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="H296" s="3">
         <f>IF(F296=0,0,1-G296/F296)</f>
@@ -35420,38 +35600,38 @@
         <v>0</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L296" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N296" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="P296" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R296" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S296" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T296" s="2" t="n">
         <v>0</v>
@@ -35461,7 +35641,7 @@
       </c>
       <c r="V296" s="2" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="W296" s="2" t="inlineStr">
@@ -35476,7 +35656,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
@@ -35486,69 +35666,33 @@
       </c>
       <c r="AA296" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-2</t>
-        </is>
-      </c>
-      <c r="AB296" s="5" t="inlineStr">
-        <is>
-          <t>attested-static (sheet grain)</t>
-        </is>
-      </c>
+          <t>reg-us-i-2-1</t>
+        </is>
+      </c>
+      <c r="AB296" s="5" t="n"/>
       <c r="AC296" s="5" t="n"/>
       <c r="AD296" s="5" t="n"/>
       <c r="AE296" s="5" t="n"/>
       <c r="AF296" s="5" t="n"/>
-      <c r="AG296" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
-        </is>
-      </c>
-      <c r="AH296" s="5" t="inlineStr">
-        <is>
-          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
-        </is>
-      </c>
-      <c r="AI296" s="5" t="inlineStr">
-        <is>
-          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
-        </is>
-      </c>
-      <c r="AJ296" s="5" t="inlineStr">
-        <is>
-          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
-        </is>
-      </c>
-      <c r="AK296" s="5" t="inlineStr">
-        <is>
-          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
-        </is>
-      </c>
-      <c r="AL296" s="5" t="inlineStr">
-        <is>
-          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
-        </is>
-      </c>
-      <c r="AM296" s="5" t="inlineStr">
-        <is>
-          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
-        </is>
-      </c>
+      <c r="AG296" s="5" t="n"/>
+      <c r="AH296" s="5" t="n"/>
+      <c r="AI296" s="5" t="n"/>
+      <c r="AJ296" s="5" t="n"/>
+      <c r="AK296" s="5" t="n"/>
+      <c r="AL296" s="5" t="n"/>
+      <c r="AM296" s="5" t="n"/>
       <c r="AN296" s="5" t="n"/>
-      <c r="AO296" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO296" s="5" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>us-day</t>
+          <t>us-cutler</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
+          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -35567,10 +35711,10 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>1170</v>
+        <v>1015</v>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1170</v>
+        <v>1015</v>
       </c>
       <c r="H297" s="3">
         <f>IF(F297=0,0,1-G297/F297)</f>
@@ -35617,11 +35761,11 @@
         <v>0</v>
       </c>
       <c r="U297" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V297" s="2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Cutler</t>
         </is>
       </c>
       <c r="W297" s="2" t="inlineStr">
@@ -35646,12 +35790,12 @@
       </c>
       <c r="AA297" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-1</t>
+          <t>reg-us-i-1-2</t>
         </is>
       </c>
       <c r="AB297" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC297" s="5" t="n"/>
@@ -35660,55 +35804,55 @@
       <c r="AF297" s="5" t="n"/>
       <c r="AG297" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+          <t>Dossier: reconstruction/dossiers/us-i-1-2-cutler.md; three agreeing clocks (10/2/4)</t>
         </is>
       </c>
       <c r="AH297" s="5" t="inlineStr">
         <is>
-          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+          <t>Cutler; Grover k, Miller w (the order-undelivered cause), Biddle (95 NY) w; 7th Ind detached in rear July 1</t>
         </is>
       </c>
       <c r="AI297" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+          <t>regiment primaries: 147 NY 380, 76 NY 375, 56 Pa 252</t>
         </is>
       </c>
       <c r="AJ297" s="5" t="inlineStr">
         <is>
-          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+          <t>[B+drawn] the opening line across the RR (j1-03 CUTLER label + 147 NY bar + HALL 2'ME); the 2 o'clock changed front; the embankment retreat line; the 7th Ind Culp's Hill first-occupation pin; July 2-3 next to Greene</t>
         </is>
       </c>
       <c r="AK297" s="5" t="inlineStr">
         <is>
-          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+          <t>[D] leading-brigade march; the Wadsworth fall-back; the changed front; the perfect-steadiness embankment retreat</t>
         </is>
       </c>
       <c r="AL297" s="5" t="inlineStr">
         <is>
-          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+          <t>first infantry engaged ('in action from 10 a.m. until 4 p.m.'); the 147th's stranded half-hour; the afternoon flank volley (a CSA regiment surrendered - Iverson-front both-sided); Hubbard's 18-man provost guard in the line</t>
         </is>
       </c>
       <c r="AM297" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+          <t>return (p. 173) 1,002; RATE-CLASS primaries: 147 NY 207/380 in half an hour, 76 NY 169 in thirty minutes</t>
         </is>
       </c>
       <c r="AN297" s="5" t="n"/>
       <c r="AO297" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (thin - division-report class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>us-eustis</t>
+          <t>us-dana</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
+          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -35727,10 +35871,10 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>1595</v>
+        <v>465</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>1595</v>
+        <v>465</v>
       </c>
       <c r="H298" s="3">
         <f>IF(F298=0,0,1-G298/F298)</f>
@@ -35767,11 +35911,11 @@
       </c>
       <c r="R298" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S298" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T298" s="2" t="n">
         <v>0</v>
@@ -35781,7 +35925,7 @@
       </c>
       <c r="V298" s="2" t="inlineStr">
         <is>
-          <t>Eustis</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="W298" s="2" t="inlineStr">
@@ -35796,7 +35940,7 @@
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
@@ -35806,33 +35950,69 @@
       </c>
       <c r="AA298" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-2</t>
-        </is>
-      </c>
-      <c r="AB298" s="5" t="n"/>
+          <t>reg-us-i-3-2</t>
+        </is>
+      </c>
+      <c r="AB298" s="5" t="inlineStr">
+        <is>
+          <t>attested-static (sheet grain)</t>
+        </is>
+      </c>
       <c r="AC298" s="5" t="n"/>
       <c r="AD298" s="5" t="n"/>
       <c r="AE298" s="5" t="n"/>
       <c r="AF298" s="5" t="n"/>
-      <c r="AG298" s="5" t="n"/>
-      <c r="AH298" s="5" t="n"/>
-      <c r="AI298" s="5" t="n"/>
-      <c r="AJ298" s="5" t="n"/>
-      <c r="AK298" s="5" t="n"/>
-      <c r="AL298" s="5" t="n"/>
-      <c r="AM298" s="5" t="n"/>
+      <c r="AG298" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
+        </is>
+      </c>
+      <c r="AH298" s="5" t="inlineStr">
+        <is>
+          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
+        </is>
+      </c>
+      <c r="AI298" s="5" t="inlineStr">
+        <is>
+          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
+        </is>
+      </c>
+      <c r="AJ298" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
+        </is>
+      </c>
+      <c r="AK298" s="5" t="inlineStr">
+        <is>
+          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
+        </is>
+      </c>
+      <c r="AL298" s="5" t="inlineStr">
+        <is>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
+        </is>
+      </c>
+      <c r="AM298" s="5" t="inlineStr">
+        <is>
+          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
+        </is>
+      </c>
       <c r="AN298" s="5" t="n"/>
-      <c r="AO298" s="5" t="n"/>
+      <c r="AO298" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>us-fisher</t>
+          <t>us-day</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
+          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -35851,10 +36031,10 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>1555</v>
+        <v>1170</v>
       </c>
       <c r="G299" s="2" t="n">
-        <v>1555</v>
+        <v>1170</v>
       </c>
       <c r="H299" s="3">
         <f>IF(F299=0,0,1-G299/F299)</f>
@@ -35901,11 +36081,11 @@
         <v>0</v>
       </c>
       <c r="U299" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V299" s="2" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="W299" s="2" t="inlineStr">
@@ -35930,33 +36110,69 @@
       </c>
       <c r="AA299" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-2</t>
-        </is>
-      </c>
-      <c r="AB299" s="5" t="n"/>
+          <t>reg-us-v-2-1</t>
+        </is>
+      </c>
+      <c r="AB299" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 single-window mover)</t>
+        </is>
+      </c>
       <c r="AC299" s="5" t="n"/>
       <c r="AD299" s="5" t="n"/>
       <c r="AE299" s="5" t="n"/>
       <c r="AF299" s="5" t="n"/>
-      <c r="AG299" s="5" t="n"/>
-      <c r="AH299" s="5" t="n"/>
-      <c r="AI299" s="5" t="n"/>
-      <c r="AJ299" s="5" t="n"/>
-      <c r="AK299" s="5" t="n"/>
-      <c r="AL299" s="5" t="n"/>
-      <c r="AM299" s="5" t="n"/>
+      <c r="AG299" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+        </is>
+      </c>
+      <c r="AH299" s="5" t="inlineStr">
+        <is>
+          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+        </is>
+      </c>
+      <c r="AI299" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+        </is>
+      </c>
+      <c r="AJ299" s="5" t="inlineStr">
+        <is>
+          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+        </is>
+      </c>
+      <c r="AK299" s="5" t="inlineStr">
+        <is>
+          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+        </is>
+      </c>
+      <c r="AL299" s="5" t="inlineStr">
+        <is>
+          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+        </is>
+      </c>
+      <c r="AM299" s="5" t="inlineStr">
+        <is>
+          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+        </is>
+      </c>
       <c r="AN299" s="5" t="n"/>
-      <c r="AO299" s="5" t="n"/>
+      <c r="AO299" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (thin - division-report class)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>us-fraser</t>
+          <t>us-eustis</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
+          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -35975,10 +36191,10 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>615</v>
+        <v>1595</v>
       </c>
       <c r="G300" s="2" t="n">
-        <v>615</v>
+        <v>1595</v>
       </c>
       <c r="H300" s="3">
         <f>IF(F300=0,0,1-G300/F300)</f>
@@ -36015,7 +36231,7 @@
       </c>
       <c r="R300" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S300" s="2" t="n">
@@ -36029,7 +36245,7 @@
       </c>
       <c r="V300" s="2" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Eustis</t>
         </is>
       </c>
       <c r="W300" s="2" t="inlineStr">
@@ -36054,69 +36270,33 @@
       </c>
       <c r="AA300" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-3</t>
-        </is>
-      </c>
-      <c r="AB300" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-3-2</t>
+        </is>
+      </c>
+      <c r="AB300" s="5" t="n"/>
       <c r="AC300" s="5" t="n"/>
       <c r="AD300" s="5" t="n"/>
       <c r="AE300" s="5" t="n"/>
       <c r="AF300" s="5" t="n"/>
-      <c r="AG300" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
-        </is>
-      </c>
-      <c r="AH300" s="5" t="inlineStr">
-        <is>
-          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
-        </is>
-      </c>
-      <c r="AI300" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~975 compilation hop-flagged</t>
-        </is>
-      </c>
-      <c r="AJ300" s="5" t="inlineStr">
-        <is>
-          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
-        </is>
-      </c>
-      <c r="AK300" s="5" t="inlineStr">
-        <is>
-          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
-        </is>
-      </c>
-      <c r="AL300" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-3 crest fight 18:15-18:45</t>
-        </is>
-      </c>
-      <c r="AM300" s="5" t="inlineStr">
-        <is>
-          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
-        </is>
-      </c>
+      <c r="AG300" s="5" t="n"/>
+      <c r="AH300" s="5" t="n"/>
+      <c r="AI300" s="5" t="n"/>
+      <c r="AJ300" s="5" t="n"/>
+      <c r="AK300" s="5" t="n"/>
+      <c r="AL300" s="5" t="n"/>
+      <c r="AM300" s="5" t="n"/>
       <c r="AN300" s="5" t="n"/>
-      <c r="AO300" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO300" s="5" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>us-garrard</t>
+          <t>us-fisher</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
+          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -36135,10 +36315,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>1290</v>
+        <v>1555</v>
       </c>
       <c r="G301" s="2" t="n">
-        <v>1290</v>
+        <v>1555</v>
       </c>
       <c r="H301" s="3">
         <f>IF(F301=0,0,1-G301/F301)</f>
@@ -36189,7 +36369,7 @@
       </c>
       <c r="V301" s="2" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="W301" s="2" t="inlineStr">
@@ -36214,69 +36394,33 @@
       </c>
       <c r="AA301" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-3</t>
-        </is>
-      </c>
-      <c r="AB301" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-v-3-2</t>
+        </is>
+      </c>
+      <c r="AB301" s="5" t="n"/>
       <c r="AC301" s="5" t="n"/>
       <c r="AD301" s="5" t="n"/>
       <c r="AE301" s="5" t="n"/>
       <c r="AF301" s="5" t="n"/>
-      <c r="AG301" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
-        </is>
-      </c>
-      <c r="AH301" s="5" t="inlineStr">
-        <is>
-          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
-        </is>
-      </c>
-      <c r="AI301" s="5" t="inlineStr">
-        <is>
-          <t>no brigade primary (open; compilation tier)</t>
-        </is>
-      </c>
-      <c r="AJ301" s="5" t="inlineStr">
-        <is>
-          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
-        </is>
-      </c>
-      <c r="AK301" s="5" t="inlineStr">
-        <is>
-          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
-        </is>
-      </c>
-      <c r="AL301" s="5" t="inlineStr">
-        <is>
-          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
-        </is>
-      </c>
-      <c r="AM301" s="5" t="inlineStr">
-        <is>
-          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
-        </is>
-      </c>
+      <c r="AG301" s="5" t="n"/>
+      <c r="AH301" s="5" t="n"/>
+      <c r="AI301" s="5" t="n"/>
+      <c r="AJ301" s="5" t="n"/>
+      <c r="AK301" s="5" t="n"/>
+      <c r="AL301" s="5" t="n"/>
+      <c r="AM301" s="5" t="n"/>
       <c r="AN301" s="5" t="n"/>
-      <c r="AO301" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>us-grant</t>
+          <t>us-fraser</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
+          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -36295,10 +36439,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>1830</v>
+        <v>615</v>
       </c>
       <c r="G302" s="2" t="n">
-        <v>1830</v>
+        <v>615</v>
       </c>
       <c r="H302" s="3">
         <f>IF(F302=0,0,1-G302/F302)</f>
@@ -36349,7 +36493,7 @@
       </c>
       <c r="V302" s="2" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="W302" s="2" t="inlineStr">
@@ -36374,33 +36518,69 @@
       </c>
       <c r="AA302" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-1</t>
-        </is>
-      </c>
-      <c r="AB302" s="5" t="n"/>
+          <t>reg-us-ii-1-3</t>
+        </is>
+      </c>
+      <c r="AB302" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC302" s="5" t="n"/>
       <c r="AD302" s="5" t="n"/>
       <c r="AE302" s="5" t="n"/>
       <c r="AF302" s="5" t="n"/>
-      <c r="AG302" s="5" t="n"/>
-      <c r="AH302" s="5" t="n"/>
-      <c r="AI302" s="5" t="n"/>
-      <c r="AJ302" s="5" t="n"/>
-      <c r="AK302" s="5" t="n"/>
-      <c r="AL302" s="5" t="n"/>
-      <c r="AM302" s="5" t="n"/>
+      <c r="AG302" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
+        </is>
+      </c>
+      <c r="AH302" s="5" t="inlineStr">
+        <is>
+          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
+        </is>
+      </c>
+      <c r="AI302" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~975 compilation hop-flagged</t>
+        </is>
+      </c>
+      <c r="AJ302" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
+        </is>
+      </c>
+      <c r="AK302" s="5" t="inlineStr">
+        <is>
+          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
+        </is>
+      </c>
+      <c r="AL302" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-3 crest fight 18:15-18:45</t>
+        </is>
+      </c>
+      <c r="AM302" s="5" t="inlineStr">
+        <is>
+          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
+        </is>
+      </c>
       <c r="AN302" s="5" t="n"/>
-      <c r="AO302" s="5" t="n"/>
+      <c r="AO302" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>us-greene</t>
+          <t>us-garrard</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
+          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -36419,10 +36599,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>1125</v>
+        <v>1290</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>1125</v>
+        <v>1290</v>
       </c>
       <c r="H303" s="3">
         <f>IF(F303=0,0,1-G303/F303)</f>
@@ -36473,7 +36653,7 @@
       </c>
       <c r="V303" s="2" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="W303" s="2" t="inlineStr">
@@ -36498,12 +36678,12 @@
       </c>
       <c r="AA303" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-3</t>
+          <t>reg-us-v-2-3</t>
         </is>
       </c>
       <c r="AB303" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC303" s="5" t="n"/>
@@ -36512,37 +36692,37 @@
       <c r="AF303" s="5" t="n"/>
       <c r="AG303" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
         </is>
       </c>
       <c r="AH303" s="5" t="inlineStr">
         <is>
-          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
+          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
         </is>
       </c>
       <c r="AI303" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
+          <t>no brigade primary (open; compilation tier)</t>
         </is>
       </c>
       <c r="AJ303" s="5" t="inlineStr">
         <is>
-          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
+          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
         </is>
       </c>
       <c r="AK303" s="5" t="inlineStr">
         <is>
-          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
+          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
         </is>
       </c>
       <c r="AL303" s="5" t="inlineStr">
         <is>
-          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
+          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
         </is>
       </c>
       <c r="AM303" s="5" t="inlineStr">
         <is>
-          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
         </is>
       </c>
       <c r="AN303" s="5" t="n"/>
@@ -36555,12 +36735,12 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>us-harris</t>
+          <t>us-grant</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
+          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -36579,10 +36759,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>565</v>
+        <v>1830</v>
       </c>
       <c r="G304" s="2" t="n">
-        <v>565</v>
+        <v>1830</v>
       </c>
       <c r="H304" s="3">
         <f>IF(F304=0,0,1-G304/F304)</f>
@@ -36629,11 +36809,11 @@
         <v>0</v>
       </c>
       <c r="U304" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V304" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="W304" s="2" t="inlineStr">
@@ -36658,69 +36838,33 @@
       </c>
       <c r="AA304" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-2</t>
-        </is>
-      </c>
-      <c r="AB304" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (the breached base wall)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-2-1</t>
+        </is>
+      </c>
+      <c r="AB304" s="5" t="n"/>
       <c r="AC304" s="5" t="n"/>
       <c r="AD304" s="5" t="n"/>
       <c r="AE304" s="5" t="n"/>
       <c r="AF304" s="5" t="n"/>
-      <c r="AG304" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged</t>
-        </is>
-      </c>
-      <c r="AH304" s="5" t="inlineStr">
-        <is>
-          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4</t>
-        </is>
-      </c>
-      <c r="AI304" s="5" t="inlineStr">
-        <is>
-          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
-        </is>
-      </c>
-      <c r="AJ304" s="5" t="inlineStr">
-        <is>
-          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
-        </is>
-      </c>
-      <c r="AK304" s="5" t="inlineStr">
-        <is>
-          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
-        </is>
-      </c>
-      <c r="AL304" s="5" t="inlineStr">
-        <is>
-          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
-        </is>
-      </c>
-      <c r="AM304" s="5" t="inlineStr">
-        <is>
-          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
-        </is>
-      </c>
+      <c r="AG304" s="5" t="n"/>
+      <c r="AH304" s="5" t="n"/>
+      <c r="AI304" s="5" t="n"/>
+      <c r="AJ304" s="5" t="n"/>
+      <c r="AK304" s="5" t="n"/>
+      <c r="AL304" s="5" t="n"/>
+      <c r="AM304" s="5" t="n"/>
       <c r="AN304" s="5" t="n"/>
-      <c r="AO304" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO304" s="5" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>us-harrow</t>
+          <t>us-greene</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Harrow's Brigade</t>
+          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -36739,76 +36883,76 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>1410</v>
+        <v>1125</v>
       </c>
       <c r="G305" s="2" t="n">
-        <v>630</v>
+        <v>1125</v>
       </c>
       <c r="H305" s="3">
         <f>IF(F305=0,0,1-G305/F305)</f>
         <v/>
       </c>
       <c r="I305" s="2" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K305" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L305" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M305" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N305" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O305" s="2" t="n">
-        <v>121.7</v>
-      </c>
-      <c r="P305" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q305" s="2" t="inlineStr">
+      <c r="V305" s="2" t="inlineStr">
+        <is>
+          <t>Greene</t>
+        </is>
+      </c>
+      <c r="W305" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R305" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S305" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T305" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U305" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V305" s="2" t="inlineStr">
-        <is>
-          <t>Harrow</t>
-        </is>
-      </c>
-      <c r="W305" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
@@ -36818,12 +36962,12 @@
       </c>
       <c r="AA305" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-1</t>
+          <t>reg-us-xii-2-3</t>
         </is>
       </c>
       <c r="AB305" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (crisis incline-right)</t>
+          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
         </is>
       </c>
       <c r="AC305" s="5" t="n"/>
@@ -36832,37 +36976,37 @@
       <c r="AF305" s="5" t="n"/>
       <c r="AG305" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
         </is>
       </c>
       <c r="AH305" s="5" t="inlineStr">
         <is>
-          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
+          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
         </is>
       </c>
       <c r="AI305" s="5" t="inlineStr">
         <is>
-          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
+          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
         </is>
       </c>
       <c r="AJ305" s="5" t="inlineStr">
         <is>
-          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
+          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
         </is>
       </c>
       <c r="AK305" s="5" t="inlineStr">
         <is>
-          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
+          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
         </is>
       </c>
       <c r="AL305" s="5" t="inlineStr">
         <is>
-          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
+          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
         </is>
       </c>
       <c r="AM305" s="5" t="inlineStr">
         <is>
-          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
+          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
         </is>
       </c>
       <c r="AN305" s="5" t="n"/>
@@ -36875,12 +37019,12 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>us-kane</t>
+          <t>us-harris</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
+          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -36899,10 +37043,10 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>600</v>
+        <v>565</v>
       </c>
       <c r="G306" s="2" t="n">
-        <v>600</v>
+        <v>565</v>
       </c>
       <c r="H306" s="3">
         <f>IF(F306=0,0,1-G306/F306)</f>
@@ -36949,11 +37093,11 @@
         <v>0</v>
       </c>
       <c r="U306" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V306" s="2" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="W306" s="2" t="inlineStr">
@@ -36978,12 +37122,12 @@
       </c>
       <c r="AA306" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-2</t>
+          <t>reg-us-xi-1-2</t>
         </is>
       </c>
       <c r="AB306" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (the breached base wall)</t>
         </is>
       </c>
       <c r="AC306" s="5" t="n"/>
@@ -36992,37 +37136,37 @@
       <c r="AF306" s="5" t="n"/>
       <c r="AG306" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged; July 1 knoll extension pass 10 (drawn crest bar 57 m from the Barlow statue; the Barlow-wounding pin in Ames's echelon record)</t>
         </is>
       </c>
       <c r="AH306" s="5" t="inlineStr">
         <is>
-          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
+          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4</t>
         </is>
       </c>
       <c r="AI306" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY: 652 in action (Kane p. 848)</t>
+          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
         </is>
       </c>
       <c r="AJ306" s="5" t="inlineStr">
         <is>
-          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
+          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
         </is>
       </c>
       <c r="AK306" s="5" t="inlineStr">
         <is>
-          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
+          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
         </is>
       </c>
       <c r="AL306" s="5" t="inlineStr">
         <is>
-          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
+          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
         </is>
       </c>
       <c r="AM306" s="5" t="inlineStr">
         <is>
-          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening)</t>
+          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
         </is>
       </c>
       <c r="AN306" s="5" t="n"/>
@@ -37035,12 +37179,12 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>us-kelly</t>
+          <t>us-harrow</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
+          <t>Harrow's Brigade</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -37059,42 +37203,42 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>330</v>
+        <v>1410</v>
       </c>
       <c r="G307" s="2" t="n">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="H307" s="3">
         <f>IF(F307=0,0,1-G307/F307)</f>
         <v/>
       </c>
       <c r="I307" s="2" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L307" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N307" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O307" s="2" t="n">
-        <v>0</v>
+        <v>121.7</v>
       </c>
       <c r="P307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q307" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R307" s="2" t="inlineStr">
@@ -37103,17 +37247,17 @@
         </is>
       </c>
       <c r="S307" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U307" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V307" s="2" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="W307" s="2" t="inlineStr">
@@ -37123,12 +37267,12 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
@@ -37138,12 +37282,12 @@
       </c>
       <c r="AA307" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-2</t>
+          <t>reg-us-ii-2-1</t>
         </is>
       </c>
       <c r="AB307" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (crisis incline-right)</t>
         </is>
       </c>
       <c r="AC307" s="5" t="n"/>
@@ -37152,37 +37296,37 @@
       <c r="AF307" s="5" t="n"/>
       <c r="AG307" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
         </is>
       </c>
       <c r="AH307" s="5" t="inlineStr">
         <is>
-          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
+          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
         </is>
       </c>
       <c r="AI307" s="5" t="inlineStr">
         <is>
-          <t>530 into action PRIMARY (Kelly)</t>
+          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
         </is>
       </c>
       <c r="AJ307" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
+          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
         </is>
       </c>
       <c r="AK307" s="5" t="inlineStr">
         <is>
-          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
+          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
         </is>
       </c>
       <c r="AL307" s="5" t="inlineStr">
         <is>
-          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
+          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
         </is>
       </c>
       <c r="AM307" s="5" t="inlineStr">
         <is>
-          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
+          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
         </is>
       </c>
       <c r="AN307" s="5" t="n"/>
@@ -37195,12 +37339,12 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>us-krzyzanowski</t>
+          <t>us-kane</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
+          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -37219,10 +37363,10 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="G308" s="2" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="H308" s="3">
         <f>IF(F308=0,0,1-G308/F308)</f>
@@ -37273,7 +37417,7 @@
       </c>
       <c r="V308" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="W308" s="2" t="inlineStr">
@@ -37298,33 +37442,69 @@
       </c>
       <c r="AA308" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-2</t>
-        </is>
-      </c>
-      <c r="AB308" s="5" t="n"/>
+          <t>reg-us-xii-2-2</t>
+        </is>
+      </c>
+      <c r="AB308" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC308" s="5" t="n"/>
       <c r="AD308" s="5" t="n"/>
       <c r="AE308" s="5" t="n"/>
       <c r="AF308" s="5" t="n"/>
-      <c r="AG308" s="5" t="n"/>
-      <c r="AH308" s="5" t="n"/>
-      <c r="AI308" s="5" t="n"/>
-      <c r="AJ308" s="5" t="n"/>
-      <c r="AK308" s="5" t="n"/>
-      <c r="AL308" s="5" t="n"/>
-      <c r="AM308" s="5" t="n"/>
+      <c r="AG308" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder; the 9 a.m. relief clock landed pass 10</t>
+        </is>
+      </c>
+      <c r="AH308" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
+        </is>
+      </c>
+      <c r="AI308" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY: 652 in action (Kane p. 848)</t>
+        </is>
+      </c>
+      <c r="AJ308" s="5" t="inlineStr">
+        <is>
+          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
+        </is>
+      </c>
+      <c r="AK308" s="5" t="inlineStr">
+        <is>
+          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
+        </is>
+      </c>
+      <c r="AL308" s="5" t="inlineStr">
+        <is>
+          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
+        </is>
+      </c>
+      <c r="AM308" s="5" t="inlineStr">
+        <is>
+          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening); p. 184 rows (pass 10): 98 = 29 Pa 66, 109 Pa 10, 111 Pa 22 (sum exact)</t>
+        </is>
+      </c>
       <c r="AN308" s="5" t="n"/>
-      <c r="AO308" s="5" t="n"/>
+      <c r="AO308" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>us-lockwood</t>
+          <t>us-kelly</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
+          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -37343,10 +37523,10 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>1650</v>
+        <v>330</v>
       </c>
       <c r="G309" s="2" t="n">
-        <v>1650</v>
+        <v>330</v>
       </c>
       <c r="H309" s="3">
         <f>IF(F309=0,0,1-G309/F309)</f>
@@ -37397,7 +37577,7 @@
       </c>
       <c r="V309" s="2" t="inlineStr">
         <is>
-          <t>Lockwood</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="W309" s="2" t="inlineStr">
@@ -37422,12 +37602,12 @@
       </c>
       <c r="AA309" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-2</t>
+          <t>reg-us-ii-1-2</t>
         </is>
       </c>
       <c r="AB309" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC309" s="5" t="n"/>
@@ -37436,55 +37616,55 @@
       <c r="AF309" s="5" t="n"/>
       <c r="AG309" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
         </is>
       </c>
       <c r="AH309" s="5" t="inlineStr">
         <is>
-          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
+          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
         </is>
       </c>
       <c r="AI309" s="5" t="inlineStr">
         <is>
-          <t>OPEN; two-regiment July 2 vs three-regiment July 3 composition fact</t>
+          <t>530 into action PRIMARY (Kelly)</t>
         </is>
       </c>
       <c r="AJ309" s="5" t="inlineStr">
         <is>
-          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
+          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
         </is>
       </c>
       <c r="AK309" s="5" t="inlineStr">
         <is>
-          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
+          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
         </is>
       </c>
       <c r="AL309" s="5" t="inlineStr">
         <is>
-          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
+          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
         </is>
       </c>
       <c r="AM309" s="5" t="inlineStr">
         <is>
-          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
+          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
         </is>
       </c>
       <c r="AN309" s="5" t="n"/>
       <c r="AO309" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>us-madill</t>
+          <t>us-krzyzanowski</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
+          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -37503,10 +37683,10 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G310" s="2" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="H310" s="3">
         <f>IF(F310=0,0,1-G310/F310)</f>
@@ -37543,7 +37723,7 @@
       </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S310" s="2" t="n">
@@ -37557,7 +37737,7 @@
       </c>
       <c r="V310" s="2" t="inlineStr">
         <is>
-          <t>Madill</t>
+          <t>Krzyżanowski</t>
         </is>
       </c>
       <c r="W310" s="2" t="inlineStr">
@@ -37582,69 +37762,33 @@
       </c>
       <c r="AA310" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-1</t>
-        </is>
-      </c>
-      <c r="AB310" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 static-then-forced-back)</t>
-        </is>
-      </c>
+          <t>reg-us-xi-3-2</t>
+        </is>
+      </c>
+      <c r="AB310" s="5" t="n"/>
       <c r="AC310" s="5" t="n"/>
       <c r="AD310" s="5" t="n"/>
       <c r="AE310" s="5" t="n"/>
       <c r="AF310" s="5" t="n"/>
-      <c r="AG310" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
-        </is>
-      </c>
-      <c r="AH310" s="5" t="inlineStr">
-        <is>
-          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
-        </is>
-      </c>
-      <c r="AI310" s="5" t="inlineStr">
-        <is>
-          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
-        </is>
-      </c>
-      <c r="AJ310" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
-        </is>
-      </c>
-      <c r="AK310" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
-        </is>
-      </c>
-      <c r="AL310" s="5" t="inlineStr">
-        <is>
-          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
-        </is>
-      </c>
-      <c r="AM310" s="5" t="inlineStr">
-        <is>
-          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
-        </is>
-      </c>
+      <c r="AG310" s="5" t="n"/>
+      <c r="AH310" s="5" t="n"/>
+      <c r="AI310" s="5" t="n"/>
+      <c r="AJ310" s="5" t="n"/>
+      <c r="AK310" s="5" t="n"/>
+      <c r="AL310" s="5" t="n"/>
+      <c r="AM310" s="5" t="n"/>
       <c r="AN310" s="5" t="n"/>
-      <c r="AO310" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO310" s="5" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>us-mccandless</t>
+          <t>us-lockwood</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
+          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -37663,10 +37807,10 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>1095</v>
+        <v>1650</v>
       </c>
       <c r="G311" s="2" t="n">
-        <v>1095</v>
+        <v>1650</v>
       </c>
       <c r="H311" s="3">
         <f>IF(F311=0,0,1-G311/F311)</f>
@@ -37717,7 +37861,7 @@
       </c>
       <c r="V311" s="2" t="inlineStr">
         <is>
-          <t>McCandless</t>
+          <t>Lockwood</t>
         </is>
       </c>
       <c r="W311" s="2" t="inlineStr">
@@ -37742,12 +37886,12 @@
       </c>
       <c r="AA311" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-1</t>
+          <t>reg-us-xii-1-2</t>
         </is>
       </c>
       <c r="AB311" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC311" s="5" t="n"/>
@@ -37756,55 +37900,55 @@
       <c r="AF311" s="5" t="n"/>
       <c r="AG311" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md; Maulsby pp. 805-807 in full + p. 184 rows (174) pass 10</t>
         </is>
       </c>
       <c r="AH311" s="5" t="inlineStr">
         <is>
-          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
+          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
         </is>
       </c>
       <c r="AI311" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
+          <t>GEARY PRIMARY (pass 10): '1,700 strong' reported 7.30 a.m. July 3</t>
         </is>
       </c>
       <c r="AJ311" s="5" t="inlineStr">
         <is>
-          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
+          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
         </is>
       </c>
       <c r="AK311" s="5" t="inlineStr">
         <is>
-          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
+          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
         </is>
       </c>
       <c r="AL311" s="5" t="inlineStr">
         <is>
-          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
+          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
         </is>
       </c>
       <c r="AM311" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
+          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
         </is>
       </c>
       <c r="AN311" s="5" t="n"/>
       <c r="AO311" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>us-mcdougall</t>
+          <t>us-madill</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
+          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -37823,10 +37967,10 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>1755</v>
+        <v>775</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>1755</v>
+        <v>775</v>
       </c>
       <c r="H312" s="3">
         <f>IF(F312=0,0,1-G312/F312)</f>
@@ -37863,7 +38007,7 @@
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S312" s="2" t="n">
@@ -37877,7 +38021,7 @@
       </c>
       <c r="V312" s="2" t="inlineStr">
         <is>
-          <t>McDougall</t>
+          <t>Madill</t>
         </is>
       </c>
       <c r="W312" s="2" t="inlineStr">
@@ -37902,12 +38046,12 @@
       </c>
       <c r="AA312" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-1</t>
+          <t>reg-us-iii-1-1</t>
         </is>
       </c>
       <c r="AB312" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 static-then-forced-back)</t>
         </is>
       </c>
       <c r="AC312" s="5" t="n"/>
@@ -37916,55 +38060,55 @@
       <c r="AF312" s="5" t="n"/>
       <c r="AG312" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
         </is>
       </c>
       <c r="AH312" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
+          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
         </is>
       </c>
       <c r="AI312" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
         </is>
       </c>
       <c r="AJ312" s="5" t="inlineStr">
         <is>
-          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
+          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
         </is>
       </c>
       <c r="AK312" s="5" t="inlineStr">
         <is>
-          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
+          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
         </is>
       </c>
       <c r="AL312" s="5" t="inlineStr">
         <is>
-          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
+          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
         </is>
       </c>
       <c r="AM312" s="5" t="inlineStr">
         <is>
-          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
+          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
         </is>
       </c>
       <c r="AN312" s="5" t="n"/>
       <c r="AO312" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>us-mckeen</t>
+          <t>us-mccandless</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
+          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -37983,10 +38127,10 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>520</v>
+        <v>1095</v>
       </c>
       <c r="G313" s="2" t="n">
-        <v>520</v>
+        <v>1095</v>
       </c>
       <c r="H313" s="3">
         <f>IF(F313=0,0,1-G313/F313)</f>
@@ -38037,7 +38181,7 @@
       </c>
       <c r="V313" s="2" t="inlineStr">
         <is>
-          <t>McKeen</t>
+          <t>McCandless</t>
         </is>
       </c>
       <c r="W313" s="2" t="inlineStr">
@@ -38062,12 +38206,12 @@
       </c>
       <c r="AA313" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-1</t>
+          <t>reg-us-v-3-1</t>
         </is>
       </c>
       <c r="AB313" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
         </is>
       </c>
       <c r="AC313" s="5" t="n"/>
@@ -38076,37 +38220,37 @@
       <c r="AF313" s="5" t="n"/>
       <c r="AG313" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
         </is>
       </c>
       <c r="AH313" s="5" t="inlineStr">
         <is>
-          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
         </is>
       </c>
       <c r="AI313" s="5" t="inlineStr">
         <is>
-          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AJ313" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
         </is>
       </c>
       <c r="AK313" s="5" t="inlineStr">
         <is>
-          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
         </is>
       </c>
       <c r="AL313" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
         </is>
       </c>
       <c r="AM313" s="5" t="inlineStr">
         <is>
-          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
         </is>
       </c>
       <c r="AN313" s="5" t="n"/>
@@ -38119,12 +38263,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>us-meredith</t>
+          <t>us-mcdougall</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
+          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -38143,10 +38287,10 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>730</v>
+        <v>1755</v>
       </c>
       <c r="G314" s="2" t="n">
-        <v>730</v>
+        <v>1755</v>
       </c>
       <c r="H314" s="3">
         <f>IF(F314=0,0,1-G314/F314)</f>
@@ -38197,7 +38341,7 @@
       </c>
       <c r="V314" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>McDougall</t>
         </is>
       </c>
       <c r="W314" s="2" t="inlineStr">
@@ -38222,33 +38366,69 @@
       </c>
       <c r="AA314" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-1</t>
-        </is>
-      </c>
-      <c r="AB314" s="5" t="n"/>
+          <t>reg-us-xii-1-1</t>
+        </is>
+      </c>
+      <c r="AB314" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC314" s="5" t="n"/>
       <c r="AD314" s="5" t="n"/>
       <c r="AE314" s="5" t="n"/>
       <c r="AF314" s="5" t="n"/>
-      <c r="AG314" s="5" t="n"/>
-      <c r="AH314" s="5" t="n"/>
-      <c r="AI314" s="5" t="n"/>
-      <c r="AJ314" s="5" t="n"/>
-      <c r="AK314" s="5" t="n"/>
-      <c r="AL314" s="5" t="n"/>
-      <c r="AM314" s="5" t="n"/>
+      <c r="AG314" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
+        </is>
+      </c>
+      <c r="AH314" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
+        </is>
+      </c>
+      <c r="AI314" s="5" t="inlineStr">
+        <is>
+          <t>OPEN (no primary; no hop)</t>
+        </is>
+      </c>
+      <c r="AJ314" s="5" t="inlineStr">
+        <is>
+          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
+        </is>
+      </c>
+      <c r="AK314" s="5" t="inlineStr">
+        <is>
+          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
+        </is>
+      </c>
+      <c r="AL314" s="5" t="inlineStr">
+        <is>
+          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
+        </is>
+      </c>
+      <c r="AM314" s="5" t="inlineStr">
+        <is>
+          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
+        </is>
+      </c>
       <c r="AN314" s="5" t="n"/>
-      <c r="AO314" s="5" t="n"/>
+      <c r="AO314" s="5" t="inlineStr">
+        <is>
+          <t>T3 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>us-neill</t>
+          <t>us-mckeen</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
+          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -38267,10 +38447,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>1775</v>
+        <v>520</v>
       </c>
       <c r="G315" s="2" t="n">
-        <v>1775</v>
+        <v>520</v>
       </c>
       <c r="H315" s="3">
         <f>IF(F315=0,0,1-G315/F315)</f>
@@ -38311,7 +38491,7 @@
         </is>
       </c>
       <c r="S315" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T315" s="2" t="n">
         <v>0</v>
@@ -38321,7 +38501,7 @@
       </c>
       <c r="V315" s="2" t="inlineStr">
         <is>
-          <t>Neill</t>
+          <t>McKeen</t>
         </is>
       </c>
       <c r="W315" s="2" t="inlineStr">
@@ -38336,7 +38516,7 @@
       </c>
       <c r="Y315" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z315" s="2" t="inlineStr">
@@ -38346,33 +38526,69 @@
       </c>
       <c r="AA315" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-2</t>
-        </is>
-      </c>
-      <c r="AB315" s="5" t="n"/>
+          <t>reg-us-ii-1-1</t>
+        </is>
+      </c>
+      <c r="AB315" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC315" s="5" t="n"/>
       <c r="AD315" s="5" t="n"/>
       <c r="AE315" s="5" t="n"/>
       <c r="AF315" s="5" t="n"/>
-      <c r="AG315" s="5" t="n"/>
-      <c r="AH315" s="5" t="n"/>
-      <c r="AI315" s="5" t="n"/>
-      <c r="AJ315" s="5" t="n"/>
-      <c r="AK315" s="5" t="n"/>
-      <c r="AL315" s="5" t="n"/>
-      <c r="AM315" s="5" t="n"/>
+      <c r="AG315" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+        </is>
+      </c>
+      <c r="AH315" s="5" t="inlineStr">
+        <is>
+          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+        </is>
+      </c>
+      <c r="AI315" s="5" t="inlineStr">
+        <is>
+          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+        </is>
+      </c>
+      <c r="AJ315" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+        </is>
+      </c>
+      <c r="AK315" s="5" t="inlineStr">
+        <is>
+          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+        </is>
+      </c>
+      <c r="AL315" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+        </is>
+      </c>
+      <c r="AM315" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+        </is>
+      </c>
       <c r="AN315" s="5" t="n"/>
-      <c r="AO315" s="5" t="n"/>
+      <c r="AO315" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>us-nevin</t>
+          <t>us-meredith</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
+          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -38391,10 +38607,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1370</v>
+        <v>730</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>1370</v>
+        <v>730</v>
       </c>
       <c r="H316" s="3">
         <f>IF(F316=0,0,1-G316/F316)</f>
@@ -38445,7 +38661,7 @@
       </c>
       <c r="V316" s="2" t="inlineStr">
         <is>
-          <t>Nevin</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="W316" s="2" t="inlineStr">
@@ -38470,12 +38686,12 @@
       </c>
       <c r="AA316" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-3</t>
+          <t>reg-us-i-1-1</t>
         </is>
       </c>
       <c r="AB316" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 W5 executor)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC316" s="5" t="n"/>
@@ -38484,37 +38700,37 @@
       <c r="AF316" s="5" t="n"/>
       <c r="AG316" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
+          <t>Dossier: reconstruction/dossiers/us-i-1-1-meredith.md; the 1,000-vs-75 Archer-capture-count conflict carried</t>
         </is>
       </c>
       <c r="AH316" s="5" t="inlineStr">
         <is>
-          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
+          <t>Meredith (w July 1) -&gt; Robinson (7th Wis, pinned in Dawes); 6th Wis + brigade guard detached as corps reserve; Morrow w&amp;c; 24th Mich officer ledger 8k/14w</t>
         </is>
       </c>
       <c r="AI316" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
+          <t>24th Mich PRIMARY 496; brigade aggregate open</t>
         </is>
       </c>
       <c r="AJ316" s="5" t="inlineStr">
         <is>
-          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
+          <t>[B+drawn] the Willoughby Run charge ground (j1-03 bars; Archer-captured marker on the axis); McPherson's woods line (order 19-24-7 curved); j1-13 seminary barricade drawn; Culp's Hill evening</t>
         </is>
       </c>
       <c r="AK316" s="5" t="inlineStr">
         <is>
-          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
+          <t>[D] the unloaded double-quick charge; the east-bank withdrawal; step-by-step to the barricade; through town to Culp's Hill</t>
         </is>
       </c>
       <c r="AL316" s="5" t="inlineStr">
         <is>
-          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
+          <t>the Archer capture (Maloney/2nd Wis, both-sided w/ Shepard's ~75-pocket); the 6th Wis railroad-cut charge (Blair's 2nd Miss surrender, flag, 2nd Me gun recaptured); the woods defense vs the 26th NC (facing color ledgers)</t>
         </is>
       </c>
       <c r="AM316" s="5" t="inlineStr">
         <is>
-          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
+          <t>return (p. 173) 1,153 (the heaviest Union brigade) - 19 Ind 210, 24 Mich 363, 2 Wis 233, 6 Wis 168, 7 Wis 178; single-day concentration, three episodes; 24th Mich nine flag carriers / four bearers k</t>
         </is>
       </c>
       <c r="AN316" s="5" t="n"/>
@@ -38527,12 +38743,12 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>us-rice</t>
+          <t>us-neill</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
+          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -38551,10 +38767,10 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>985</v>
+        <v>1775</v>
       </c>
       <c r="G317" s="2" t="n">
-        <v>985</v>
+        <v>1775</v>
       </c>
       <c r="H317" s="3">
         <f>IF(F317=0,0,1-G317/F317)</f>
@@ -38595,7 +38811,7 @@
         </is>
       </c>
       <c r="S317" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T317" s="2" t="n">
         <v>0</v>
@@ -38605,7 +38821,7 @@
       </c>
       <c r="V317" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Neill</t>
         </is>
       </c>
       <c r="W317" s="2" t="inlineStr">
@@ -38620,7 +38836,7 @@
       </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z317" s="2" t="inlineStr">
@@ -38630,69 +38846,33 @@
       </c>
       <c r="AA317" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-3</t>
-        </is>
-      </c>
-      <c r="AB317" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-2-2</t>
+        </is>
+      </c>
+      <c r="AB317" s="5" t="n"/>
       <c r="AC317" s="5" t="n"/>
       <c r="AD317" s="5" t="n"/>
       <c r="AE317" s="5" t="n"/>
       <c r="AF317" s="5" t="n"/>
-      <c r="AG317" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
-        </is>
-      </c>
-      <c r="AH317" s="5" t="inlineStr">
-        <is>
-          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
-        </is>
-      </c>
-      <c r="AI317" s="5" t="inlineStr">
-        <is>
-          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
-        </is>
-      </c>
-      <c r="AJ317" s="5" t="inlineStr">
-        <is>
-          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
-        </is>
-      </c>
-      <c r="AK317" s="5" t="inlineStr">
-        <is>
-          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
-        </is>
-      </c>
-      <c r="AL317" s="5" t="inlineStr">
-        <is>
-          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
-        </is>
-      </c>
-      <c r="AM317" s="5" t="inlineStr">
-        <is>
-          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
-        </is>
-      </c>
+      <c r="AG317" s="5" t="n"/>
+      <c r="AH317" s="5" t="n"/>
+      <c r="AI317" s="5" t="n"/>
+      <c r="AJ317" s="5" t="n"/>
+      <c r="AK317" s="5" t="n"/>
+      <c r="AL317" s="5" t="n"/>
+      <c r="AM317" s="5" t="n"/>
       <c r="AN317" s="5" t="n"/>
-      <c r="AO317" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO317" s="5" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>us-russell</t>
+          <t>us-nevin</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
+          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -38711,10 +38891,10 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>1480</v>
+        <v>1370</v>
       </c>
       <c r="H318" s="3">
         <f>IF(F318=0,0,1-G318/F318)</f>
@@ -38765,7 +38945,7 @@
       </c>
       <c r="V318" s="2" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Nevin</t>
         </is>
       </c>
       <c r="W318" s="2" t="inlineStr">
@@ -38790,33 +38970,69 @@
       </c>
       <c r="AA318" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-3</t>
-        </is>
-      </c>
-      <c r="AB318" s="5" t="n"/>
+          <t>reg-us-vi-3-3</t>
+        </is>
+      </c>
+      <c r="AB318" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 W5 executor)</t>
+        </is>
+      </c>
       <c r="AC318" s="5" t="n"/>
       <c r="AD318" s="5" t="n"/>
       <c r="AE318" s="5" t="n"/>
       <c r="AF318" s="5" t="n"/>
-      <c r="AG318" s="5" t="n"/>
-      <c r="AH318" s="5" t="n"/>
-      <c r="AI318" s="5" t="n"/>
-      <c r="AJ318" s="5" t="n"/>
-      <c r="AK318" s="5" t="n"/>
-      <c r="AL318" s="5" t="n"/>
-      <c r="AM318" s="5" t="n"/>
+      <c r="AG318" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
+        </is>
+      </c>
+      <c r="AH318" s="5" t="inlineStr">
+        <is>
+          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
+        </is>
+      </c>
+      <c r="AI318" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
+        </is>
+      </c>
+      <c r="AJ318" s="5" t="inlineStr">
+        <is>
+          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
+        </is>
+      </c>
+      <c r="AK318" s="5" t="inlineStr">
+        <is>
+          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
+        </is>
+      </c>
+      <c r="AL318" s="5" t="inlineStr">
+        <is>
+          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
+        </is>
+      </c>
+      <c r="AM318" s="5" t="inlineStr">
+        <is>
+          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
+        </is>
+      </c>
       <c r="AN318" s="5" t="n"/>
-      <c r="AO318" s="5" t="n"/>
+      <c r="AO318" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>us-shaler</t>
+          <t>us-rice</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
+          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -38835,10 +39051,10 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>1770</v>
+        <v>985</v>
       </c>
       <c r="G319" s="2" t="n">
-        <v>1770</v>
+        <v>985</v>
       </c>
       <c r="H319" s="3">
         <f>IF(F319=0,0,1-G319/F319)</f>
@@ -38848,34 +39064,34 @@
         <v>0</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L319" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M319" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N319" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O319" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="P319" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="Q319" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R319" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S319" s="2" t="n">
@@ -38889,7 +39105,7 @@
       </c>
       <c r="V319" s="2" t="inlineStr">
         <is>
-          <t>Shaler</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="W319" s="2" t="inlineStr">
@@ -38899,12 +39115,12 @@
       </c>
       <c r="X319" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y319" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z319" s="2" t="inlineStr">
@@ -38914,33 +39130,69 @@
       </c>
       <c r="AA319" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-1</t>
-        </is>
-      </c>
-      <c r="AB319" s="5" t="n"/>
+          <t>reg-us-v-1-3</t>
+        </is>
+      </c>
+      <c r="AB319" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+        </is>
+      </c>
       <c r="AC319" s="5" t="n"/>
       <c r="AD319" s="5" t="n"/>
       <c r="AE319" s="5" t="n"/>
       <c r="AF319" s="5" t="n"/>
-      <c r="AG319" s="5" t="n"/>
-      <c r="AH319" s="5" t="n"/>
-      <c r="AI319" s="5" t="n"/>
-      <c r="AJ319" s="5" t="n"/>
-      <c r="AK319" s="5" t="n"/>
-      <c r="AL319" s="5" t="n"/>
-      <c r="AM319" s="5" t="n"/>
+      <c r="AG319" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+        </is>
+      </c>
+      <c r="AH319" s="5" t="inlineStr">
+        <is>
+          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+        </is>
+      </c>
+      <c r="AI319" s="5" t="inlineStr">
+        <is>
+          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+        </is>
+      </c>
+      <c r="AJ319" s="5" t="inlineStr">
+        <is>
+          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+        </is>
+      </c>
+      <c r="AK319" s="5" t="inlineStr">
+        <is>
+          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+        </is>
+      </c>
+      <c r="AL319" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+        </is>
+      </c>
+      <c r="AM319" s="5" t="inlineStr">
+        <is>
+          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+        </is>
+      </c>
       <c r="AN319" s="5" t="n"/>
-      <c r="AO319" s="5" t="n"/>
+      <c r="AO319" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>us-sherrill</t>
+          <t>us-russell</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Sherrill's Brigade (Willard's)</t>
+          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -38959,32 +39211,32 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>1510</v>
+        <v>1480</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>800</v>
+        <v>1480</v>
       </c>
       <c r="H320" s="3">
         <f>IF(F320=0,0,1-G320/F320)</f>
         <v/>
       </c>
       <c r="I320" s="2" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K320" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L320" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M320" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N320" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O320" s="2" t="n">
         <v>0</v>
@@ -39003,17 +39255,17 @@
         </is>
       </c>
       <c r="S320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T320" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U320" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="V320" s="2" t="inlineStr">
         <is>
-          <t>Sherrill</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="W320" s="2" t="inlineStr">
@@ -39023,12 +39275,12 @@
       </c>
       <c r="X320" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y320" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z320" s="2" t="inlineStr">
@@ -39038,69 +39290,33 @@
       </c>
       <c r="AA320" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-3</t>
-        </is>
-      </c>
-      <c r="AB320" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (one in-window leg)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-1-3</t>
+        </is>
+      </c>
+      <c r="AB320" s="5" t="n"/>
       <c r="AC320" s="5" t="n"/>
       <c r="AD320" s="5" t="n"/>
       <c r="AE320" s="5" t="n"/>
       <c r="AF320" s="5" t="n"/>
-      <c r="AG320" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
-        </is>
-      </c>
-      <c r="AH320" s="5" t="inlineStr">
-        <is>
-          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
-        </is>
-      </c>
-      <c r="AI320" s="5" t="inlineStr">
-        <is>
-          <t>1,510 (build compilation, hop flagged)</t>
-        </is>
-      </c>
-      <c r="AJ320" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
-        </is>
-      </c>
-      <c r="AK320" s="5" t="inlineStr">
-        <is>
-          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
-        </is>
-      </c>
-      <c r="AL320" s="5" t="inlineStr">
-        <is>
-          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
-        </is>
-      </c>
-      <c r="AM320" s="5" t="inlineStr">
-        <is>
-          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
-        </is>
-      </c>
+      <c r="AG320" s="5" t="n"/>
+      <c r="AH320" s="5" t="n"/>
+      <c r="AI320" s="5" t="n"/>
+      <c r="AJ320" s="5" t="n"/>
+      <c r="AK320" s="5" t="n"/>
+      <c r="AL320" s="5" t="n"/>
+      <c r="AM320" s="5" t="n"/>
       <c r="AN320" s="5" t="n"/>
-      <c r="AO320" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AO320" s="5" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>us-smith</t>
+          <t>us-shaler</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
+          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -39119,10 +39335,10 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>1290</v>
+        <v>1770</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>1290</v>
+        <v>1770</v>
       </c>
       <c r="H321" s="3">
         <f>IF(F321=0,0,1-G321/F321)</f>
@@ -39132,34 +39348,34 @@
         <v>0</v>
       </c>
       <c r="J321" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K321" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L321" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M321" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N321" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>0</v>
+        <v>1210.8</v>
       </c>
       <c r="P321" s="2" t="n">
-        <v>0</v>
+        <v>1210.8</v>
       </c>
       <c r="Q321" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R321" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S321" s="2" t="n">
@@ -39169,11 +39385,11 @@
         <v>0</v>
       </c>
       <c r="U321" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V321" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Shaler</t>
         </is>
       </c>
       <c r="W321" s="2" t="inlineStr">
@@ -39183,12 +39399,12 @@
       </c>
       <c r="X321" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y321" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z321" s="2" t="inlineStr">
@@ -39198,7 +39414,7 @@
       </c>
       <c r="AA321" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-2</t>
+          <t>reg-us-vi-3-1</t>
         </is>
       </c>
       <c r="AB321" s="5" t="n"/>
@@ -39219,12 +39435,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>us-smyth</t>
+          <t>us-sherrill</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Smyth's Brigade</t>
+          <t>Sherrill's Brigade (Willard's)</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -39243,26 +39459,26 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>1190</v>
+        <v>1510</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="H322" s="3">
         <f>IF(F322=0,0,1-G322/F322)</f>
         <v/>
       </c>
       <c r="I322" s="2" t="n">
-        <v>365</v>
+        <v>710</v>
       </c>
       <c r="J322" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L322" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M322" s="2" t="n">
         <v>0</v>
@@ -39293,11 +39509,11 @@
         <v>0</v>
       </c>
       <c r="U322" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V322" s="2" t="inlineStr">
         <is>
-          <t>Smyth</t>
+          <t>Sherrill</t>
         </is>
       </c>
       <c r="W322" s="2" t="inlineStr">
@@ -39322,12 +39538,12 @@
       </c>
       <c r="AA322" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-2</t>
+          <t>reg-us-ii-3-3</t>
         </is>
       </c>
       <c r="AB322" s="5" t="inlineStr">
         <is>
-          <t>attested-static (July 2-4 wall line)</t>
+          <t>authored-ok (one in-window leg)</t>
         </is>
       </c>
       <c r="AC322" s="5" t="n"/>
@@ -39336,37 +39552,37 @@
       <c r="AF322" s="5" t="n"/>
       <c r="AG322" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
         </is>
       </c>
       <c r="AH322" s="5" t="inlineStr">
         <is>
-          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
+          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
         </is>
       </c>
       <c r="AI322" s="5" t="inlineStr">
         <is>
-          <t>1,190 (build compilation, hop flagged; no primary)</t>
+          <t>1,510 (build compilation, hop flagged)</t>
         </is>
       </c>
       <c r="AJ322" s="5" t="inlineStr">
         <is>
-          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
+          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
         </is>
       </c>
       <c r="AK322" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
+          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
         </is>
       </c>
       <c r="AL322" s="5" t="inlineStr">
         <is>
-          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
+          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
         </is>
       </c>
       <c r="AM322" s="5" t="inlineStr">
         <is>
-          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
+          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
         </is>
       </c>
       <c r="AN322" s="5" t="n"/>
@@ -39379,12 +39595,12 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>us-sweitzer</t>
+          <t>us-smith</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
+          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -39403,10 +39619,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>995</v>
+        <v>1290</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>995</v>
+        <v>1290</v>
       </c>
       <c r="H323" s="3">
         <f>IF(F323=0,0,1-G323/F323)</f>
@@ -39453,11 +39669,11 @@
         <v>0</v>
       </c>
       <c r="U323" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V323" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="W323" s="2" t="inlineStr">
@@ -39482,69 +39698,33 @@
       </c>
       <c r="AA323" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-2</t>
-        </is>
-      </c>
-      <c r="AB323" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 twice-committed)</t>
-        </is>
-      </c>
+          <t>reg-us-xi-2-2</t>
+        </is>
+      </c>
+      <c r="AB323" s="5" t="n"/>
       <c r="AC323" s="5" t="n"/>
       <c r="AD323" s="5" t="n"/>
       <c r="AE323" s="5" t="n"/>
       <c r="AF323" s="5" t="n"/>
-      <c r="AG323" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
-        </is>
-      </c>
-      <c r="AH323" s="5" t="inlineStr">
-        <is>
-          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
-        </is>
-      </c>
-      <c r="AI323" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
-        </is>
-      </c>
-      <c r="AJ323" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
-        </is>
-      </c>
-      <c r="AK323" s="5" t="inlineStr">
-        <is>
-          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
-        </is>
-      </c>
-      <c r="AL323" s="5" t="inlineStr">
-        <is>
-          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
-        </is>
-      </c>
-      <c r="AM323" s="5" t="inlineStr">
-        <is>
-          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
-        </is>
-      </c>
+      <c r="AG323" s="5" t="n"/>
+      <c r="AH323" s="5" t="n"/>
+      <c r="AI323" s="5" t="n"/>
+      <c r="AJ323" s="5" t="n"/>
+      <c r="AK323" s="5" t="n"/>
+      <c r="AL323" s="5" t="n"/>
+      <c r="AM323" s="5" t="n"/>
       <c r="AN323" s="5" t="n"/>
-      <c r="AO323" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO323" s="5" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>us-tilton</t>
+          <t>us-smyth</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
+          <t>Smyth's Brigade</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -39563,32 +39743,32 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>530</v>
+        <v>1190</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>530</v>
+        <v>825</v>
       </c>
       <c r="H324" s="3">
         <f>IF(F324=0,0,1-G324/F324)</f>
         <v/>
       </c>
       <c r="I324" s="2" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K324" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L324" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N324" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O324" s="2" t="n">
         <v>0</v>
@@ -39607,17 +39787,17 @@
         </is>
       </c>
       <c r="S324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U324" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V324" s="2" t="inlineStr">
         <is>
-          <t>Tilton</t>
+          <t>Smyth</t>
         </is>
       </c>
       <c r="W324" s="2" t="inlineStr">
@@ -39627,12 +39807,12 @@
       </c>
       <c r="X324" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y324" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z324" s="2" t="inlineStr">
@@ -39642,12 +39822,12 @@
       </c>
       <c r="AA324" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-1</t>
+          <t>reg-us-ii-3-2</t>
         </is>
       </c>
       <c r="AB324" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>attested-static (July 2-4 wall line)</t>
         </is>
       </c>
       <c r="AC324" s="5" t="n"/>
@@ -39656,55 +39836,55 @@
       <c r="AF324" s="5" t="n"/>
       <c r="AG324" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
         </is>
       </c>
       <c r="AH324" s="5" t="inlineStr">
         <is>
-          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
         </is>
       </c>
       <c r="AI324" s="5" t="inlineStr">
         <is>
-          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+          <t>1,190 (build compilation, hop flagged; no primary)</t>
         </is>
       </c>
       <c r="AJ324" s="5" t="inlineStr">
         <is>
-          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
         </is>
       </c>
       <c r="AK324" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
         </is>
       </c>
       <c r="AL324" s="5" t="inlineStr">
         <is>
-          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
         </is>
       </c>
       <c r="AM324" s="5" t="inlineStr">
         <is>
-          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
         </is>
       </c>
       <c r="AN324" s="5" t="n"/>
       <c r="AO324" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>us-torbert</t>
+          <t>us-sweitzer</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
+          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -39723,10 +39903,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>1320</v>
+        <v>995</v>
       </c>
       <c r="G325" s="2" t="n">
-        <v>1320</v>
+        <v>995</v>
       </c>
       <c r="H325" s="3">
         <f>IF(F325=0,0,1-G325/F325)</f>
@@ -39777,7 +39957,7 @@
       </c>
       <c r="V325" s="2" t="inlineStr">
         <is>
-          <t>Torbert</t>
+          <t>Sweitzer</t>
         </is>
       </c>
       <c r="W325" s="2" t="inlineStr">
@@ -39802,33 +39982,69 @@
       </c>
       <c r="AA325" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-1</t>
-        </is>
-      </c>
-      <c r="AB325" s="5" t="n"/>
+          <t>reg-us-v-1-2</t>
+        </is>
+      </c>
+      <c r="AB325" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 twice-committed)</t>
+        </is>
+      </c>
       <c r="AC325" s="5" t="n"/>
       <c r="AD325" s="5" t="n"/>
       <c r="AE325" s="5" t="n"/>
       <c r="AF325" s="5" t="n"/>
-      <c r="AG325" s="5" t="n"/>
-      <c r="AH325" s="5" t="n"/>
-      <c r="AI325" s="5" t="n"/>
-      <c r="AJ325" s="5" t="n"/>
-      <c r="AK325" s="5" t="n"/>
-      <c r="AL325" s="5" t="n"/>
-      <c r="AM325" s="5" t="n"/>
+      <c r="AG325" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
+        </is>
+      </c>
+      <c r="AH325" s="5" t="inlineStr">
+        <is>
+          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
+        </is>
+      </c>
+      <c r="AI325" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
+        </is>
+      </c>
+      <c r="AJ325" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
+        </is>
+      </c>
+      <c r="AK325" s="5" t="inlineStr">
+        <is>
+          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
+        </is>
+      </c>
+      <c r="AL325" s="5" t="inlineStr">
+        <is>
+          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
+        </is>
+      </c>
+      <c r="AM325" s="5" t="inlineStr">
+        <is>
+          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
+        </is>
+      </c>
       <c r="AN325" s="5" t="n"/>
-      <c r="AO325" s="5" t="n"/>
+      <c r="AO325" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>us-detrobriand</t>
+          <t>us-tilton</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
+          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -39847,10 +40063,10 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>895</v>
+        <v>530</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>895</v>
+        <v>530</v>
       </c>
       <c r="H326" s="3">
         <f>IF(F326=0,0,1-G326/F326)</f>
@@ -39887,7 +40103,7 @@
       </c>
       <c r="R326" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S326" s="2" t="n">
@@ -39901,7 +40117,7 @@
       </c>
       <c r="V326" s="2" t="inlineStr">
         <is>
-          <t>Trobriand</t>
+          <t>Tilton</t>
         </is>
       </c>
       <c r="W326" s="2" t="inlineStr">
@@ -39926,7 +40142,7 @@
       </c>
       <c r="AA326" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-3</t>
+          <t>reg-us-v-1-1</t>
         </is>
       </c>
       <c r="AB326" s="5" t="inlineStr">
@@ -39940,37 +40156,37 @@
       <c r="AF326" s="5" t="n"/>
       <c r="AG326" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
         </is>
       </c>
       <c r="AH326" s="5" t="inlineStr">
         <is>
-          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
+          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
         </is>
       </c>
       <c r="AI326" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
+          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
         </is>
       </c>
       <c r="AJ326" s="5" t="inlineStr">
         <is>
-          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
+          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
         </is>
       </c>
       <c r="AK326" s="5" t="inlineStr">
         <is>
-          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
+          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
         </is>
       </c>
       <c r="AL326" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
+          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
         </is>
       </c>
       <c r="AM326" s="5" t="inlineStr">
         <is>
-          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
+          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
         </is>
       </c>
       <c r="AN326" s="5" t="n"/>
@@ -39983,12 +40199,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>us-vonamsberg</t>
+          <t>us-torbert</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -40007,10 +40223,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>875</v>
+        <v>1320</v>
       </c>
       <c r="G327" s="2" t="n">
-        <v>875</v>
+        <v>1320</v>
       </c>
       <c r="H327" s="3">
         <f>IF(F327=0,0,1-G327/F327)</f>
@@ -40061,7 +40277,7 @@
       </c>
       <c r="V327" s="2" t="inlineStr">
         <is>
-          <t>Amsberg</t>
+          <t>Torbert</t>
         </is>
       </c>
       <c r="W327" s="2" t="inlineStr">
@@ -40086,7 +40302,7 @@
       </c>
       <c r="AA327" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-1</t>
+          <t>reg-us-vi-1-1</t>
         </is>
       </c>
       <c r="AB327" s="5" t="n"/>
@@ -40107,12 +40323,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>us-vongilsa</t>
+          <t>us-detrobriand</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -40131,10 +40347,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>605</v>
+        <v>895</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>605</v>
+        <v>895</v>
       </c>
       <c r="H328" s="3">
         <f>IF(F328=0,0,1-G328/F328)</f>
@@ -40171,7 +40387,7 @@
       </c>
       <c r="R328" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S328" s="2" t="n">
@@ -40185,7 +40401,7 @@
       </c>
       <c r="V328" s="2" t="inlineStr">
         <is>
-          <t>Gilsa</t>
+          <t>Trobriand</t>
         </is>
       </c>
       <c r="W328" s="2" t="inlineStr">
@@ -40210,26 +40426,346 @@
       </c>
       <c r="AA328" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-1</t>
-        </is>
-      </c>
-      <c r="AB328" s="5" t="n"/>
+          <t>reg-us-iii-1-3</t>
+        </is>
+      </c>
+      <c r="AB328" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC328" s="5" t="n"/>
       <c r="AD328" s="5" t="n"/>
       <c r="AE328" s="5" t="n"/>
       <c r="AF328" s="5" t="n"/>
-      <c r="AG328" s="5" t="n"/>
-      <c r="AH328" s="5" t="n"/>
-      <c r="AI328" s="5" t="n"/>
-      <c r="AJ328" s="5" t="n"/>
-      <c r="AK328" s="5" t="n"/>
-      <c r="AL328" s="5" t="n"/>
-      <c r="AM328" s="5" t="n"/>
+      <c r="AG328" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
+        </is>
+      </c>
+      <c r="AH328" s="5" t="inlineStr">
+        <is>
+          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
+        </is>
+      </c>
+      <c r="AI328" s="5" t="inlineStr">
+        <is>
+          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
+        </is>
+      </c>
+      <c r="AJ328" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
+        </is>
+      </c>
+      <c r="AK328" s="5" t="inlineStr">
+        <is>
+          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
+        </is>
+      </c>
+      <c r="AL328" s="5" t="inlineStr">
+        <is>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
+        </is>
+      </c>
+      <c r="AM328" s="5" t="inlineStr">
+        <is>
+          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
+        </is>
+      </c>
       <c r="AN328" s="5" t="n"/>
-      <c r="AO328" s="5" t="n"/>
+      <c r="AO328" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>us-vonamsberg</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="H329" s="3">
+        <f>IF(F329=0,0,1-G329/F329)</f>
+        <v/>
+      </c>
+      <c r="I329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V329" s="2" t="inlineStr">
+        <is>
+          <t>Amsberg</t>
+        </is>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AA329" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-3-1</t>
+        </is>
+      </c>
+      <c r="AB329" s="5" t="n"/>
+      <c r="AC329" s="5" t="n"/>
+      <c r="AD329" s="5" t="n"/>
+      <c r="AE329" s="5" t="n"/>
+      <c r="AF329" s="5" t="n"/>
+      <c r="AG329" s="5" t="n"/>
+      <c r="AH329" s="5" t="n"/>
+      <c r="AI329" s="5" t="n"/>
+      <c r="AJ329" s="5" t="n"/>
+      <c r="AK329" s="5" t="n"/>
+      <c r="AL329" s="5" t="n"/>
+      <c r="AM329" s="5" t="n"/>
+      <c r="AN329" s="5" t="n"/>
+      <c r="AO329" s="5" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>us-vongilsa</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="H330" s="3">
+        <f>IF(F330=0,0,1-G330/F330)</f>
+        <v/>
+      </c>
+      <c r="I330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K330" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U330" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V330" s="2" t="inlineStr">
+        <is>
+          <t>Gilsa</t>
+        </is>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="Z330" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AA330" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-1-1</t>
+        </is>
+      </c>
+      <c r="AB330" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
+      <c r="AC330" s="5" t="n"/>
+      <c r="AD330" s="5" t="n"/>
+      <c r="AE330" s="5" t="n"/>
+      <c r="AF330" s="5" t="n"/>
+      <c r="AG330" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-1-vongilsa.md; the which-brigade-broke-first Schurz-vs-Ames conflict carried</t>
+        </is>
+      </c>
+      <c r="AH330" s="5" t="inlineStr">
+        <is>
+          <t>von Gilsa; NO brigade report (verified negative); 41st NY absent July 1 (arrived ~10 p.m.)</t>
+        </is>
+      </c>
+      <c r="AI330" s="5" t="inlineStr">
+        <is>
+          <t>OPEN; three-regiment knoll line (structural)</t>
+        </is>
+      </c>
+      <c r="AJ330" s="5" t="inlineStr">
+        <is>
+          <t>[D+drawn] the knoll north face under the Gordon line; the ECH marker = July 2-3 semantics; no located July 1 brigade marker (negative)</t>
+        </is>
+      </c>
+      <c r="AK330" s="5" t="inlineStr">
+        <is>
+          <t>[D ~15:00-15:30 bracket] Barlow's forward tilt; the break under enfilade + frontal charge; through town</t>
+        </is>
+      </c>
+      <c r="AL330" s="5" t="inlineStr">
+        <is>
+          <t>the receiving side of the 50-paces fight (attested by the attacker); the corps' capture-mass retreat</t>
+        </is>
+      </c>
+      <c r="AM330" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 182) 527 - 41 NY 75 (July 2-3 only - structural day-split anchor), 54 NY 102, 68 NY 138, 153 Pa 211</t>
+        </is>
+      </c>
+      <c r="AN330" s="5" t="n"/>
+      <c r="AO330" s="5" t="inlineStr">
+        <is>
+          <t>T2 (honestly thin)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO328"/>
+  <autoFilter ref="A1:AO330"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -8130,29 +8130,29 @@
         <v>432</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="H80" s="3">
         <f>IF(F80=0,0,1-G80/F80)</f>
         <v/>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>0</v>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -8287,32 +8287,32 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>240</v>
+        <v>338</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="H81" s="3">
         <f>IF(F81=0,0,1-G81/F81)</f>
         <v/>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>0</v>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -9214,29 +9214,29 @@
         <v>480</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="H87" s="3">
         <f>IF(F87=0,0,1-G87/F87)</f>
         <v/>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -17227,17 +17227,17 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="H149" s="3">
         <f>IF(F149=0,0,1-G149/F149)</f>
         <v/>
       </c>
       <c r="I149" s="2" t="n">
-        <v>400</v>
+        <v>155</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>6</v>
@@ -17255,10 +17255,10 @@
         <v>6</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>990.4</v>
+        <v>1448.8</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>170</v>
+        <v>264.8</v>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
@@ -19483,26 +19483,26 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>1777</v>
+        <v>1200</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1577</v>
+        <v>996</v>
       </c>
       <c r="H164" s="3">
         <f>IF(F164=0,0,1-G164/F164)</f>
         <v/>
       </c>
       <c r="I164" s="2" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>6</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M164" s="2" t="n">
         <v>0</v>
@@ -19511,10 +19511,10 @@
         <v>6</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>1011</v>
+        <v>1619</v>
       </c>
       <c r="P164" s="2" t="n">
-        <v>170.1</v>
+        <v>270.7</v>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="S209" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T209" s="2" t="n">
         <v>0</v>
@@ -24998,14 +24998,14 @@
         <v>114</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H216" s="3">
         <f>IF(F216=0,0,1-G216/F216)</f>
         <v/>
       </c>
       <c r="I216" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>4</v>
@@ -25566,29 +25566,29 @@
         <v>103</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H220" s="3">
         <f>IF(F220=0,0,1-G220/F220)</f>
         <v/>
       </c>
       <c r="I220" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O220" s="2" t="n">
         <v>0</v>
@@ -25607,7 +25607,7 @@
         </is>
       </c>
       <c r="S220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T220" s="2" t="n">
         <v>0</v>
@@ -25938,29 +25938,29 @@
         <v>149</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H223" s="3">
         <f>IF(F223=0,0,1-G223/F223)</f>
         <v/>
       </c>
       <c r="I223" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O223" s="2" t="n">
         <v>806.6</v>
@@ -25979,7 +25979,7 @@
         </is>
       </c>
       <c r="S223" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T223" s="2" t="n">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         </is>
       </c>
       <c r="S226" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T226" s="2" t="n">
         <v>0</v>
@@ -27090,29 +27090,29 @@
         <v>116</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H232" s="3">
         <f>IF(F232=0,0,1-G232/F232)</f>
         <v/>
       </c>
       <c r="I232" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K232" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M232" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N232" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>1578.9</v>
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="S233" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T233" s="2" t="n">
         <v>0</v>
@@ -28143,7 +28143,7 @@
         </is>
       </c>
       <c r="S239" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T239" s="2" t="n">
         <v>0</v>
@@ -28763,7 +28763,7 @@
         </is>
       </c>
       <c r="S244" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T244" s="2" t="n">
         <v>0</v>
@@ -33459,17 +33459,17 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="G282" s="2" t="n">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="H282" s="3">
         <f>IF(F282=0,0,1-G282/F282)</f>
         <v/>
       </c>
       <c r="I282" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J282" s="2" t="n">
         <v>3</v>
@@ -39472,10 +39472,10 @@
         <v>710</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L322" s="2" t="n">
         <v>3</v>
@@ -39484,13 +39484,13 @@
         <v>0</v>
       </c>
       <c r="N322" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="P322" s="2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="Q322" s="2" t="inlineStr">
         <is>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -14310,7 +14310,7 @@
       </c>
       <c r="AI130" s="5" t="inlineStr">
         <is>
-          <t>1,650 (ED-9, no primary); crossing party ~150 (T5)</t>
+          <t>1,650 (ED-9, no primary); crossing party ~150 (T5) ; p11 sweep: B&amp;M-repro 2,055 (hop) beside ED-9 1,650 - divergent, both carried, no primary</t>
         </is>
       </c>
       <c r="AJ130" s="5" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="AI135" s="5" t="inlineStr">
         <is>
-          <t>1,575 (ED-9/stone-sentinels, no primary; negative - no morning report survives)</t>
+          <t>1,575 (ED-9/stone-sentinels, no primary; negative - no morning report survives) ; p11 sweep: B&amp;M-repro 1,634 (hop) beside ED-9 1,575</t>
         </is>
       </c>
       <c r="AJ135" s="5" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AI138" s="5" t="inlineStr">
         <is>
-          <t>tablet 'Present 1,598' (compilation, hop flagged); no primary</t>
+          <t>tablet 'Present 1,598' (compilation, hop flagged); no primary ; p11 sweep: B&amp;M-repro 1,620 (Barksdale; hop) beside tablet 1,598</t>
         </is>
       </c>
       <c r="AJ138" s="5" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="AI140" s="5" t="inlineStr">
         <is>
-          <t>OPEN; July 1 cost 'nearly one-third' = July 3 at two-thirds-strength CLASS (his fraction, not a number)</t>
+          <t>OPEN; July 1 cost 'nearly one-third' = July 3 at two-thirds-strength CLASS (his fraction, not a number) ; p11: June-30 return PRIMARY 171+2,123=2,294 (p. 564) beside his 'about 2,200' report figure; B&amp;M-repro 2,162 (hop)</t>
         </is>
       </c>
       <c r="AJ140" s="5" t="inlineStr">
@@ -16065,20 +16065,56 @@
           <t>reg-csa-2c-rod-3</t>
         </is>
       </c>
-      <c r="AB141" s="5" t="n"/>
+      <c r="AB141" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC141" s="5" t="n"/>
       <c r="AD141" s="5" t="n"/>
       <c r="AE141" s="5" t="n"/>
       <c r="AF141" s="5" t="n"/>
-      <c r="AG141" s="5" t="n"/>
-      <c r="AH141" s="5" t="n"/>
-      <c r="AI141" s="5" t="n"/>
-      <c r="AJ141" s="5" t="n"/>
-      <c r="AK141" s="5" t="n"/>
-      <c r="AL141" s="5" t="n"/>
-      <c r="AM141" s="5" t="n"/>
+      <c r="AG141" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-2c-rod-3-doles.md; CA-J1P-1/3 + CA-J2E context</t>
+        </is>
+      </c>
+      <c r="AH141" s="5" t="inlineStr">
+        <is>
+          <t>Doles throughout (the one uninjured Rodes brigade commander); Winn k + Lumpkin severely w (July 1)</t>
+        </is>
+      </c>
+      <c r="AI141" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY 'went into action with 131 officers and 1,238 enlisted men; total, 1,369' + June-30 return 128+1,275=1,403 (p. 564); B&amp;M-repro 1,323 (hop) carried</t>
+        </is>
+      </c>
+      <c r="AJ141" s="5" t="inlineStr">
+        <is>
+          <t>[C ~13:00] the left-of-division formation in the plain; the skirmisher hill (3.30 referent ambiguity recorded); the east-west street line July 1-2; [C ~20:00 Jul 2] within 100 yd of Cemetery Hill -&gt; the dirt road 300 yd back, held to 1 a.m. July 4</t>
+        </is>
+      </c>
+      <c r="AK141" s="5" t="inlineStr">
+        <is>
+          <t>[D] the left-flank moves vs the knoll; the Gordon-conjunction attack; the 157th NY front-change + plain pursuit; the failed college cut-off (pace-class negative); the July 2 evening column with Ramseur/Iverson</t>
+        </is>
+      </c>
+      <c r="AL141" s="5" t="inlineStr">
+        <is>
+          <t>The knoll rock-fence assault; THE 157th NY DESTRUCTION both-sided; THE FRIENDLY-FIRE APPENDIX (the two-gun brass battery at Rodes's HQ hill); July 2-4 heavy skirmishing</t>
+        </is>
+      </c>
+      <c r="AM141" s="5" t="inlineStr">
+        <is>
+          <t>Report=return EXACT 24/124/31 = 179 (regiment rows 45/49/17/68 both ledgers); July-1-dominant shape</t>
+        </is>
+      </c>
       <c r="AN141" s="5" t="n"/>
-      <c r="AO141" s="5" t="n"/>
+      <c r="AO141" s="5" t="inlineStr">
+        <is>
+          <t>T4 (full arc)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -16210,7 +16246,7 @@
       </c>
       <c r="AI142" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY 'about 1,200 men' (one regiment detached); tablet class pending</t>
+          <t>PRIMARY 'about 1,200 men' (one regiment detached); tablet class pending ; p11 sweep: B&amp;M-repro 1,813 (hop) beside the 1,200-engaged primary (one regiment detached)</t>
         </is>
       </c>
       <c r="AJ142" s="5" t="inlineStr">
@@ -16230,7 +16266,7 @@
       </c>
       <c r="AM142" s="5" t="inlineStr">
         <is>
-          <t>his 350 k&amp;w (40 k) vs return 380 (71 k) - the k conflict carried; 'nearly 300 buried'; the 1,800-prisoner inspector credit (not adopted); 26th Ga 11 = the structural control row</t>
+          <t>his 350 k&amp;w (40 k) vs return 380 (71 k) - the k conflict carried; 'nearly 300 buried'; the 1,800-prisoner inspector credit (not adopted); 26th Ga 11 = the structural control row ; p11: 13th Ga row closed at arithmetic grade (103 = 20/83/0); Guild k&amp;w ledger 65/258=323 noted (third count set)</t>
         </is>
       </c>
       <c r="AN142" s="5" t="n"/>
@@ -16370,7 +16406,7 @@
       </c>
       <c r="AI143" s="5" t="inlineStr">
         <is>
-          <t>OPEN (hop flagged); July 1 loss pre-shrinks the line (his own figures); tablet 'Present about 1200' (pass-10 hop; k/w cells = return exact)</t>
+          <t>OPEN (hop flagged); July 1 loss pre-shrinks the line (his own figures); tablet 'Present about 1200' (pass-10 hop; k/w cells = return exact) ; p11 sweep: B&amp;M-repro 1,295 (hop)</t>
         </is>
       </c>
       <c r="AJ143" s="5" t="inlineStr">
@@ -16530,7 +16566,7 @@
       </c>
       <c r="AI144" s="5" t="inlineStr">
         <is>
-          <t>tablet 'Present about 900' (pass-10 hop); no report primary</t>
+          <t>tablet 'Present about 900' (pass-10 hop); no report primary ; p11 sweep: B&amp;M-repro 1,244 (hop) beside the tablet ~900 - both hops, un-averaged</t>
         </is>
       </c>
       <c r="AJ144" s="5" t="inlineStr">
@@ -16550,7 +16586,7 @@
       </c>
       <c r="AM144" s="5" t="inlineStr">
         <is>
-          <t>return 345 (6th NC 172 / 21st 111 / 57th 62 - COLUMN-NOISE '623' cell caught by row arithmetic); no per-day primary - split flagged reconstruction</t>
+          <t>return 345 (6th NC 172 / 21st 111 / 57th 62 - COLUMN-NOISE '623' cell caught by row arithmetic); no per-day primary - split flagged reconstruction ; p11: 57th NC = 62 adopted at quadruple-arithmetic grade (printed '623' both channels; ED-71 candidate)</t>
         </is>
       </c>
       <c r="AN144" s="5" t="n"/>
@@ -16690,7 +16726,7 @@
       </c>
       <c r="AI145" s="5" t="inlineStr">
         <is>
-          <t>tablet '820 of 1,470' (adjudicated class); no report primary</t>
+          <t>tablet '820 of 1,470' (adjudicated class); no report primary ; CLOSED p11: June-30 return PRIMARY 114+1,350=1,464 (p. 564) beside tablet 1,470 + B&amp;M-repro 1,384 (hop) - un-averaged</t>
         </is>
       </c>
       <c r="AJ145" s="5" t="inlineStr">
@@ -16710,7 +16746,7 @@
       </c>
       <c r="AM145" s="5" t="inlineStr">
         <is>
-          <t>return (p. 342) 820 = 130/382/308 (m POOLED - the capture mass; single-cell OCR flag on w); THE SINGLE-SPIKE EXEMPLAR - one line, one field, minutes-scale; 12th NC 56 bounds the residue</t>
+          <t>return (p. 342) 820 = 130/382/308 (m POOLED - the capture mass; single-cell OCR flag on w); THE SINGLE-SPIKE EXEMPLAR - one line, one field, minutes-scale; 12th NC 56 bounds the residue ; p11 re-read: printed total row 130/328/308/820 fails own arithmetic (766 vs 820) both channels; 382 reconciliation-only; regiment rows digit-read (ED-71 candidate)</t>
         </is>
       </c>
       <c r="AN145" s="5" t="n"/>
@@ -16850,7 +16886,7 @@
       </c>
       <c r="AI146" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present 1600' (pass-10 hop)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present 1600' (pass-10 hop) ; p11 sweep: B&amp;M-repro 1,520 (hop) beside tablet ~1,600</t>
         </is>
       </c>
       <c r="AJ146" s="5" t="inlineStr">
@@ -17010,7 +17046,7 @@
       </c>
       <c r="AI147" s="5" t="inlineStr">
         <is>
-          <t>tablet 'Present about 1800' (compilation); no report statement</t>
+          <t>tablet 'Present about 1800' (compilation); no report statement ; p11 sweep: B&amp;M-repro 2,183 (hop) beside tablet ~1,800 - divergent hops, both carried</t>
         </is>
       </c>
       <c r="AJ147" s="5" t="inlineStr">
@@ -17665,7 +17701,7 @@
       </c>
       <c r="AL151" s="5" t="inlineStr">
         <is>
-          <t>[A window + B] '&gt;= one hour under a most galling fire' (his duration) / 'two hours' (Engelhard) - both carried; climax: '800 guns' combined two-brigade strength pin at the works</t>
+          <t>[A window + B] '&gt;= one hour under a most galling fire' (his duration) / 'two hours' (Engelhard) - both carried; climax: '800 guns' combined two-brigade strength pin at the works ; p11 back-extension: Scales's July 1 narrative in full - the Davis rescue, the pass-through of the ammunition-exhausted first line, the 75-yd halt, the ten-minutes-to-breakthrough pin, Perrin both-siding</t>
         </is>
       </c>
       <c r="AM151" s="5" t="inlineStr">
@@ -17934,7 +17970,7 @@
       </c>
       <c r="AI153" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1100' (pass-10 hop)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1100' (pass-10 hop) ; p11 sweep: B&amp;M-repro 1,104 (hop) - agrees with tablet ~1,100</t>
         </is>
       </c>
       <c r="AJ153" s="5" t="inlineStr">
@@ -18094,7 +18130,7 @@
       </c>
       <c r="AI154" s="5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN ; p11: June-30 return PRIMARY 138+1,656=1,794 (p. 564, Rodes' old brigade row); B&amp;M-repro 1,688 (hop)</t>
         </is>
       </c>
       <c r="AJ154" s="5" t="inlineStr">
@@ -18233,20 +18269,56 @@
           <t>reg-csa-3c-pen-1</t>
         </is>
       </c>
-      <c r="AB155" s="5" t="n"/>
+      <c r="AB155" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC155" s="5" t="n"/>
       <c r="AD155" s="5" t="n"/>
       <c r="AE155" s="5" t="n"/>
       <c r="AF155" s="5" t="n"/>
-      <c r="AG155" s="5" t="n"/>
-      <c r="AH155" s="5" t="n"/>
-      <c r="AI155" s="5" t="n"/>
-      <c r="AJ155" s="5" t="n"/>
-      <c r="AK155" s="5" t="n"/>
-      <c r="AL155" s="5" t="n"/>
-      <c r="AM155" s="5" t="n"/>
+      <c r="AG155" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-pen-1-perrin.md; CA-J1P-5 executor; feeds ED-70 candidate</t>
+        </is>
+      </c>
+      <c r="AH155" s="5" t="inlineStr">
+        <is>
+          <t>Perrin (14th SC) commanding McGowan's brigade from June 5; five regimental commanders named; division succession (Pender mw Jul 2 ~sunset -&gt; Lane) recorded</t>
+        </is>
+      </c>
+      <c r="AI155" s="5" t="inlineStr">
+        <is>
+          <t>No report figure (negative); B&amp;M-repro 1,882 (hop); the 1st SC Rifles LEFT AS TRAIN GUARD (named detachment primary) bounds engaged below the hop</t>
+        </is>
+      </c>
+      <c r="AJ155" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00] the march order behind Heth; the deploy 3 mi out; the two bounds ([C ~15:00]; [C after 16:00] the Pender assault order); the fence-&gt;grove-&gt;barricade-&gt;stone-wall-&gt;town axis (both-sided artifacts: Paul's barricade, Gamble's wall, Wainwright's thirty pieces)</t>
+        </is>
+      </c>
+      <c r="AK155" s="5" t="inlineStr">
+        <is>
+          <t>[C after-16:00] THE ASSAULT LEG: pass-through of Pettigrew's exhausted line, the ravine dress, the hold-fire order, the two oblique splits, the town entry</t>
+        </is>
+      </c>
+      <c r="AL155" s="5" t="inlineStr">
+        <is>
+          <t>CA-J1P-5 EXECUTOR: 'the most destructive fire of musketry I have ever been exposed to'; Scales halted / 'Lane did not move upon my right at all' (both both-sided); 'hundreds of prisoners, two field-pieces'; Hill's corps ledger + halt decision</t>
+        </is>
+      </c>
+      <c r="AM155" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 344: 100/477/0 = 577 (division 1,690 printed-exact); the two-left-regiments halving statement; July-1-dominant</t>
+        </is>
+      </c>
       <c r="AN155" s="5" t="n"/>
-      <c r="AO155" s="5" t="n"/>
+      <c r="AO155" s="5" t="inlineStr">
+        <is>
+          <t>T4 (July 1 grain; full arc T3)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -18502,7 +18574,7 @@
       </c>
       <c r="AI157" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary)</t>
+          <t>OPEN (no primary) ; CLOSED p11: June-30 return PRIMARY 119+971=1,090 (p. 564); B&amp;M-repro 1,027 (hop)</t>
         </is>
       </c>
       <c r="AJ157" s="5" t="inlineStr">
@@ -18822,7 +18894,7 @@
       </c>
       <c r="AI159" s="5" t="inlineStr">
         <is>
-          <t>tablet 'Present about 1200' (compilation, hop flagged); no primary</t>
+          <t>tablet 'Present about 1200' (compilation, hop flagged); no primary ; p11 sweep: B&amp;M-repro 1,334 (Semmes; hop) beside tablet ~1,200</t>
         </is>
       </c>
       <c r="AJ159" s="5" t="inlineStr">
@@ -18982,7 +19054,7 @@
       </c>
       <c r="AI160" s="5" t="inlineStr">
         <is>
-          <t>three-regiment structure primary (13th/58th VA detached, Hoffman); tablet 'Present about 800' (pass-10 hop)</t>
+          <t>three-regiment structure primary (13th/58th VA detached, Hoffman); tablet 'Present about 800' (pass-10 hop) ; p11 sweep: B&amp;M-repro 806 (hop) - agrees with the tablet ~800</t>
         </is>
       </c>
       <c r="AJ160" s="5" t="inlineStr">
@@ -19142,7 +19214,7 @@
       </c>
       <c r="AI161" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1700' (pass-10 hop)</t>
+          <t>OPEN (no primary; no hop taken - flagged); tablet 'Present about 1700' (pass-10 hop) ; p11 sweep: B&amp;M-repro 2,121 (hop) beside tablet ~1,700 - divergent hops, both carried</t>
         </is>
       </c>
       <c r="AJ161" s="5" t="inlineStr">
@@ -19302,7 +19374,7 @@
       </c>
       <c r="AI162" s="5" t="inlineStr">
         <is>
-          <t>OPEN; Terry's 4th VA 'three-fourths' fraction primary carried w/ scope flag (vs return 86); tablet 'Present about 1450' (pass-10 hop)</t>
+          <t>OPEN; Terry's 4th VA 'three-fourths' fraction primary carried w/ scope flag (vs return 86); tablet 'Present about 1450' (pass-10 hop) ; p11 sweep: B&amp;M-repro 1,323 (hop)</t>
         </is>
       </c>
       <c r="AJ162" s="5" t="inlineStr">
@@ -19746,7 +19818,7 @@
       </c>
       <c r="AI165" s="5" t="inlineStr">
         <is>
-          <t>tablet 'Present about 1350' (compilation, hop flagged)</t>
+          <t>tablet 'Present about 1350' (compilation, hop flagged) ; p11 sweep: B&amp;M-repro 1,398 (hop) - agrees with tablet ~1,350</t>
         </is>
       </c>
       <c r="AJ165" s="5" t="inlineStr">
@@ -29689,7 +29761,7 @@
       </c>
       <c r="AL250" s="5" t="inlineStr">
         <is>
-          <t>THE CA-J1M-2 EXECUTOR ('checking and retarding... several hours'; Buford: 'held its own for more than two hours'); the afternoon carbine stand ('saved a division of our infantry'); 'commenced the fight in the morning and close it in the evening'</t>
+          <t>THE CA-J1M-2 EXECUTOR ('checking and retarding... several hours'; Buford: 'held its own for more than two hours'); the afternoon carbine stand ('saved a division of our infantry'); 'commenced the fight in the morning and close it in the evening' ; p11: the afternoon stand's CSA half CLOSED (Lane's Hudson-40 detail + Perrin's 'Lane did not move') - the saved-a-division claim now three-report convergent</t>
         </is>
       </c>
       <c r="AM250" s="5" t="inlineStr">
@@ -29886,7 +29958,7 @@
       </c>
       <c r="AI252" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; B&amp;M-class reading not located)</t>
+          <t>OPEN (no primary; B&amp;M-class reading not located) ; CLOSED-at-hop p11: B&amp;M-repro 1,148 (the pass-10 'not located' now located)</t>
         </is>
       </c>
       <c r="AJ252" s="5" t="inlineStr">
@@ -33821,20 +33893,56 @@
           <t>reg-us-i-2-2</t>
         </is>
       </c>
-      <c r="AB284" s="5" t="n"/>
+      <c r="AB284" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="n"/>
-      <c r="AH284" s="5" t="n"/>
-      <c r="AI284" s="5" t="n"/>
-      <c r="AJ284" s="5" t="n"/>
-      <c r="AK284" s="5" t="n"/>
-      <c r="AL284" s="5" t="n"/>
-      <c r="AM284" s="5" t="n"/>
+      <c r="AG284" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-2-2-baxter.md; CA-J1P-2 Union receiving executor</t>
+        </is>
+      </c>
+      <c r="AH284" s="5" t="inlineStr">
+        <is>
+          <t>Baxter uninjured; Bates w x2, Wheelock captured/escaped, Lt. Thomas k in the streets; Coulter+11th Pa transferred out to 1st Bde</t>
+        </is>
+      </c>
+      <c r="AI284" s="5" t="inlineStr">
+        <is>
+          <t>No brigade primary (negative); B&amp;M-repro 1,452 (hop); division frame 'less than 2,500' (Robinson) CONFLICTS with the two-brigade B&amp;M sum 2,989 - both carried</t>
+        </is>
+      </c>
+      <c r="AJ284" s="5" t="inlineStr">
+        <is>
+          <t>[C 11:00] arrival; the two front-changes to the Oak Ridge crest (the pass-10 drawn wall bar = this line); [C ~17:00] the Emmitsburg-road line; [C Jul 2 10:00] relieved by Webb; the July 2-3 support ladder (six clocked moves); [C Jul 3 ~13:00] Cemetery Hill right-front under the cannonade ~2 h, then Hays's right</t>
+        </is>
+      </c>
+      <c r="AK284" s="5" t="inlineStr">
+        <is>
+          <t>[D] the relief hand-off ~15:00+ (Coulter's after-3, ammunition exhausted); the town retreat under fire; the clocked July 2-3 ladder</t>
+        </is>
+      </c>
+      <c r="AL284" s="5" t="inlineStr">
+        <is>
+          <t>THE IVERSON REPULSE RECEIVING RECORD: the deadly fire, the charge (88th Pa two flags + 97th NY one), the 12th Mass flank fire 'great influence upon its surrender'; Coulter 12:30 general-firing pin; division 'three flags and about 1,000 prisoners'; the Northrup conduct record</t>
+        </is>
+      </c>
+      <c r="AM284" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 174 rows (not digit-re-read); division 'lost considerably more than half' of &lt;2,500 (primary); shape: the Oak Ridge window + the town capture spike; July 3 'considerable loss' skirmish clear (unquantified)</t>
+        </is>
+      </c>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="n"/>
+      <c r="AO284" s="5" t="inlineStr">
+        <is>
+          <t>T4 (July 1 grain; full arc T3)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -34126,7 +34234,7 @@
       </c>
       <c r="AI286" s="5" t="inlineStr">
         <is>
-          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale</t>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale ; p11 back-extension: July 1 PRIMARY 1,287 in / 440 k&amp;w + 457 m / 390 left (dated July 2) - the day split lands; B&amp;M-repro 1,361 (hop)</t>
         </is>
       </c>
       <c r="AJ286" s="5" t="inlineStr">
@@ -34152,7 +34260,7 @@
       <c r="AN286" s="5" t="n"/>
       <c r="AO286" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 (July 1 grain; July 3 T3) - p11 upgrade</t>
         </is>
       </c>
     </row>
@@ -35545,20 +35653,56 @@
           <t>reg-us-xi-2-1</t>
         </is>
       </c>
-      <c r="AB295" s="5" t="n"/>
+      <c r="AB295" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC295" s="5" t="n"/>
       <c r="AD295" s="5" t="n"/>
       <c r="AE295" s="5" t="n"/>
       <c r="AF295" s="5" t="n"/>
-      <c r="AG295" s="5" t="n"/>
-      <c r="AH295" s="5" t="n"/>
-      <c r="AI295" s="5" t="n"/>
-      <c r="AJ295" s="5" t="n"/>
-      <c r="AK295" s="5" t="n"/>
-      <c r="AL295" s="5" t="n"/>
-      <c r="AM295" s="5" t="n"/>
+      <c r="AG295" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-2-1-coster.md</t>
+        </is>
+      </c>
+      <c r="AH295" s="5" t="inlineStr">
+        <is>
+          <t>Coster; NO report at any brigade echelon (verified negative - the third XI no-report brigade)</t>
+        </is>
+      </c>
+      <c r="AI295" s="5" t="inlineStr">
+        <is>
+          <t>No primary (negative); B&amp;M-repro 1,156 (hop); the brickyard force = three regiments (73rd Pa stayed on the hill)</t>
+        </is>
+      </c>
+      <c r="AJ295" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00 via von Steinwehr] Cemetery Hill NE supporting Wiedrich (+ the stone-church regiment); [D] the brickyard line NE of town; the fall-back with the brick-house stopper; the hill's NE front July 2-3</t>
+        </is>
+      </c>
+      <c r="AK295" s="5" t="inlineStr">
+        <is>
+          <t>[D] the through-town commitment to the brickyard; the covered fall-back</t>
+        </is>
+      </c>
+      <c r="AL295" s="5" t="inlineStr">
+        <is>
+          <t>The brickyard delaying action (division grain + BOTH-SIDED by Hays/Avery pass 10); the brick-house stopper</t>
+        </is>
+      </c>
+      <c r="AM295" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 183: 252/200/111/34 = 597 aggregate-exact (m column row-forced 313, noisy); the minutes-scale single-spike wreck second only to Iverson's</t>
+        </is>
+      </c>
       <c r="AN295" s="5" t="n"/>
-      <c r="AO295" s="5" t="n"/>
+      <c r="AO295" s="5" t="inlineStr">
+        <is>
+          <t>T2 (honestly thin; the fight T3 via the attackers)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -35669,20 +35813,56 @@
           <t>reg-us-i-2-1</t>
         </is>
       </c>
-      <c r="AB296" s="5" t="n"/>
+      <c r="AB296" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC296" s="5" t="n"/>
       <c r="AD296" s="5" t="n"/>
       <c r="AE296" s="5" t="n"/>
       <c r="AF296" s="5" t="n"/>
-      <c r="AG296" s="5" t="n"/>
-      <c r="AH296" s="5" t="n"/>
-      <c r="AI296" s="5" t="n"/>
-      <c r="AJ296" s="5" t="n"/>
-      <c r="AK296" s="5" t="n"/>
-      <c r="AL296" s="5" t="n"/>
-      <c r="AM296" s="5" t="n"/>
+      <c r="AG296" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-2-1-paul.md; the ED-52 Union day-split exemplar</t>
+        </is>
+      </c>
+      <c r="AH296" s="5" t="inlineStr">
+        <is>
+          <t>THE CASCADE: Paul severely w -&gt; Leonard w -&gt; Root w -&gt; Coulter (assigned on Cemetery Hill, w himself July 3) - five commanders; three Paul staff missing</t>
+        </is>
+      </c>
+      <c r="AI296" s="5" t="inlineStr">
+        <is>
+          <t>No brigade primary (negative); B&amp;M-repro 1,537 (hop); 16th Me ~275 literature-class NOT hopped</t>
+        </is>
+      </c>
+      <c r="AJ296" s="5" t="inlineStr">
+        <is>
+          <t>[D] the seminary rail-barricade (Paul entrenching - the artifact Perrin stormed, both-sided); the Oak Ridge relief slots; the 16th Maine sacrifice hill; Cemetery Hill; the Baxter-parallel July 2-3 ladder</t>
+        </is>
+      </c>
+      <c r="AK296" s="5" t="inlineStr">
+        <is>
+          <t>[D ~15:00] the relief insertion (Coulter-clocked); the 16th Me detachment + three-stage collapse; the town retreat</t>
+        </is>
+      </c>
+      <c r="AL296" s="5" t="inlineStr">
+        <is>
+          <t>The repeated-attacks repulse record (division grain); the 16th Maine hold-as-long-as-there-is-a-man order VERBATIM; July 2 dark gauntlet run; July 3 arrival at the repulse</t>
+        </is>
+      </c>
+      <c r="AM296" s="5" t="inlineStr">
+        <is>
+          <t>THE DAY-SPLIT PRIMARY: 776/28/14/3 = 821 (Coulter's table, excl. 11th Pa Jul 1); 16th Me July 1 223 (162 m = the pocket)</t>
+        </is>
+      </c>
       <c r="AN296" s="5" t="n"/>
-      <c r="AO296" s="5" t="n"/>
+      <c r="AO296" s="5" t="inlineStr">
+        <is>
+          <t>T3 (July 1 grain; full arc T2)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -35989,7 +36169,7 @@
       </c>
       <c r="AL298" s="5" t="inlineStr">
         <is>
-          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative)</t>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative) ; p11 back-extension: Roy Stone's report in full - the 11:00 / 12-1 Oak Hill enfilade / 1.30 grand-advance clock ladder (ED-69 candidate primary); the RR-cut episode; the cascade in action; 'nearly two-thirds... fell'</t>
         </is>
       </c>
       <c r="AM298" s="5" t="inlineStr">
@@ -36722,7 +36902,7 @@
       </c>
       <c r="AM303" s="5" t="inlineStr">
         <is>
-          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed</t>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed ; p11 re-read: 140th NY digit-exact 1+25/5+84/18=133; brigade total row internally perfect 40/142/18=200; small rows off-by-one open (199 vs 200)</t>
         </is>
       </c>
       <c r="AN303" s="5" t="n"/>
@@ -37141,7 +37321,7 @@
       </c>
       <c r="AH306" s="5" t="inlineStr">
         <is>
-          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4</t>
+          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4 ; p11: the structured Barlow-Gordon record added (contemporary layer adopted - the July 7 letter + Gordon's OR pin; the 1903 memoir NO status)</t>
         </is>
       </c>
       <c r="AI306" s="5" t="inlineStr">
@@ -37765,20 +37945,56 @@
           <t>reg-us-xi-3-2</t>
         </is>
       </c>
-      <c r="AB310" s="5" t="n"/>
+      <c r="AB310" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC310" s="5" t="n"/>
       <c r="AD310" s="5" t="n"/>
       <c r="AE310" s="5" t="n"/>
       <c r="AF310" s="5" t="n"/>
-      <c r="AG310" s="5" t="n"/>
-      <c r="AH310" s="5" t="n"/>
-      <c r="AI310" s="5" t="n"/>
-      <c r="AJ310" s="5" t="n"/>
-      <c r="AK310" s="5" t="n"/>
-      <c r="AL310" s="5" t="n"/>
-      <c r="AM310" s="5" t="n"/>
+      <c r="AG310" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-2-krzyzanowski.md; CA-J1P-3 receiving center</t>
+        </is>
+      </c>
+      <c r="AH310" s="5" t="inlineStr">
+        <is>
+          <t>Krzyzanowski (no own report - verified negative); Col. J.S. Robinson (82nd OH) severely w; 26th WI Boebel w -&gt; Fuchs -&gt; Jacobs</t>
+        </is>
+      </c>
+      <c r="AI310" s="5" t="inlineStr">
+        <is>
+          <t>82nd OH PRIMARY 312 PFD (-&gt;220 Jul 11 bracket); no brigade primary; B&amp;M-repro 1,403 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ310" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00 secondhand] arrival + the line north of town (82nd OH left, 26th WI right); [C ~16:00] the Cemetery Hill stone-fence rally; the cemetery-building position Jul 2-5</t>
+        </is>
+      </c>
+      <c r="AK310" s="5" t="inlineStr">
+        <is>
+          <t>[D] the forward commitment; the division-ordered fall-back through town; the ~16:00 rally</t>
+        </is>
+      </c>
+      <c r="AL310" s="5" t="inlineStr">
+        <is>
+          <t>The open-field stand vs Gordon/Doles converging (both-sided); the town gauntlet; July 2-3 attested-quiet (26th WI no-loss negative)</t>
+        </is>
+      </c>
+      <c r="AM310" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 183 digit-exact: 20/140/181/111/217 = 669; 82nd OH report=return EXACT 181; July 1 near-total</t>
+        </is>
+      </c>
       <c r="AN310" s="5" t="n"/>
-      <c r="AO310" s="5" t="n"/>
+      <c r="AO310" s="5" t="inlineStr">
+        <is>
+          <t>T3 (July 1 grain; full arc T2)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -38710,7 +38926,7 @@
       </c>
       <c r="AI316" s="5" t="inlineStr">
         <is>
-          <t>24th Mich PRIMARY 496; brigade aggregate open</t>
+          <t>24th Mich PRIMARY 496; brigade aggregate open ; p11 sweep: B&amp;M-repro 1,829 brigade hop beside the 24th Mich 496 primary</t>
         </is>
       </c>
       <c r="AJ316" s="5" t="inlineStr">
@@ -40450,7 +40666,7 @@
       </c>
       <c r="AI328" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,387 compilation hop-flagged</t>
+          <t>no primary (negative); ~1,387 compilation hop-flagged ; p11: the 1,387 hop CONFIRMED at the sweep source</t>
         </is>
       </c>
       <c r="AJ328" s="5" t="inlineStr">
@@ -40465,7 +40681,7 @@
       </c>
       <c r="AL328" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances)</t>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances) ; p11 clock re-read: 'About 2 p. m.' line-of-battle formation = the tablet's 2-3 P.M. (report=tablet pair; profile upgraded)</t>
         </is>
       </c>
       <c r="AM328" s="5" t="inlineStr">
@@ -40589,20 +40805,56 @@
           <t>reg-us-xi-3-1</t>
         </is>
       </c>
-      <c r="AB329" s="5" t="n"/>
+      <c r="AB329" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC329" s="5" t="n"/>
       <c r="AD329" s="5" t="n"/>
       <c r="AE329" s="5" t="n"/>
       <c r="AF329" s="5" t="n"/>
-      <c r="AG329" s="5" t="n"/>
-      <c r="AH329" s="5" t="n"/>
-      <c r="AI329" s="5" t="n"/>
-      <c r="AJ329" s="5" t="n"/>
-      <c r="AK329" s="5" t="n"/>
-      <c r="AL329" s="5" t="n"/>
-      <c r="AM329" s="5" t="n"/>
+      <c r="AG329" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-1-schimmelfennig.md; Dobke 1:30 feeds ED-69</t>
+        </is>
+      </c>
+      <c r="AH329" s="5" t="inlineStr">
+        <is>
+          <t>THE CASCADE UP: Howard-&gt;field, Schurz-&gt;corps, Schimmelfennig-&gt;division (cut off in town Jul 1-4), von Amsberg-&gt;brigade at commitment</t>
+        </is>
+      </c>
+      <c r="AI329" s="5" t="inlineStr">
+        <is>
+          <t>No brigade primary (negative); B&amp;M-repro 1,670 (hop); 45th NY one-third-assembled fraction; Schurz 'hardly over 6,000' division frame</t>
+        </is>
+      </c>
+      <c r="AJ329" s="5" t="inlineStr">
+        <is>
+          <t>[C 11:00-11:30] the I-Corps-right deploy (45th NY skirmish line, Dilger rear, 61st OH right); the open-field line under Oak Hill fire; [D ~16:00] the seminary cover halt; the town maze; Cemetery Hill stone fence</t>
+        </is>
+      </c>
+      <c r="AK329" s="5" t="inlineStr">
+        <is>
+          <t>[C] double-quick through town to deploy; the 16:00 retreat + THE ALLEY-TRAP town leg (~100 escaped); the July 2 night mile to the Culp's stone wall</t>
+        </is>
+      </c>
+      <c r="AL329" s="5" t="inlineStr">
+        <is>
+          <t>[C 13:30 early-lean] the flank fire + surrender event (the O'Neal/Iverson front from the XI side); the 157th NY vs Doles episode both-sided; the cross-corps retreat-cover order</t>
+        </is>
+      </c>
+      <c r="AM329" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 183 digit-exact: 112/224/307/54/110 = 807 (rows sum); missing 453 = the town pockets</t>
+        </is>
+      </c>
       <c r="AN329" s="5" t="n"/>
-      <c r="AO329" s="5" t="n"/>
+      <c r="AO329" s="5" t="inlineStr">
+        <is>
+          <t>T3 (July 1 grain; full arc T2)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -40734,7 +40986,7 @@
       </c>
       <c r="AI330" s="5" t="inlineStr">
         <is>
-          <t>OPEN; three-regiment knoll line (structural)</t>
+          <t>OPEN; three-regiment knoll line (structural) ; p11 sweep: B&amp;M-repro 1,118 (hop)</t>
         </is>
       </c>
       <c r="AJ330" s="5" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AO$331</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO330"/>
+  <dimension ref="A1:AO331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -769,20 +769,56 @@
           <t>reg-csa-cav-bn-ha</t>
         </is>
       </c>
-      <c r="AB2" s="5" t="n"/>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC2" s="5" t="n"/>
       <c r="AD2" s="5" t="n"/>
       <c r="AE2" s="5" t="n"/>
       <c r="AF2" s="5" t="n"/>
-      <c r="AG2" s="5" t="n"/>
-      <c r="AH2" s="5" t="n"/>
-      <c r="AI2" s="5" t="n"/>
-      <c r="AJ2" s="5" t="n"/>
-      <c r="AK2" s="5" t="n"/>
-      <c r="AL2" s="5" t="n"/>
-      <c r="AM2" s="5" t="n"/>
+      <c r="AG2" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-bn-ha-beckham.md; feeds the battery-triage pass (5 of 6 batteries marked off-ECF-ground); Beckham's own OR report verified thin at the fetched boundary</t>
+        </is>
+      </c>
+      <c r="AH2" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Robert F. Beckham commanding six batteries (Breathed, Chew, Griffin, Hart, McGregor, Moorman)</t>
+        </is>
+      </c>
+      <c r="AI2" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro '15 guns, 406 men' (battalion total)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="5" t="inlineStr">
+        <is>
+          <t>NOT one position — the battalion was DISTRIBUTED, not massed (see EC5 table)</t>
+        </is>
+      </c>
+      <c r="AK2" s="5" t="inlineStr">
+        <is>
+          <t>Not authored this pass (battalion-grain frame dossier)</t>
+        </is>
+      </c>
+      <c r="AL2" s="5" t="inlineStr">
+        <is>
+          <t>THE DISTRIBUTION TABLE (marker verbatim): Breathed w/ W.H.F. Lee's; Chew w/ Jones's (OFF-FIELD); Griffin w/ Second [infantry] Corps; Hart w/ the Army Trains (off-ground); McGregor w/ Hampton's (the one confident ECF placement); Moorman 'no report' — at most TWO of six batteries actually fought at Rummel farm</t>
+        </is>
+      </c>
+      <c r="AM2" s="5" t="inlineStr">
+        <is>
+          <t>'Casualties not reported' (marker, verbatim)</t>
+        </is>
+      </c>
       <c r="AN2" s="5" t="n"/>
-      <c r="AO2" s="5" t="n"/>
+      <c r="AO2" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command/frame grain)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9577,20 +9613,56 @@
           <t>reg-csa-cav-fitz</t>
         </is>
       </c>
-      <c r="AB89" s="5" t="n"/>
+      <c r="AB89" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC89" s="5" t="n"/>
       <c r="AD89" s="5" t="n"/>
       <c r="AE89" s="5" t="n"/>
       <c r="AF89" s="5" t="n"/>
-      <c r="AG89" s="5" t="n"/>
-      <c r="AH89" s="5" t="n"/>
-      <c r="AI89" s="5" t="n"/>
-      <c r="AJ89" s="5" t="n"/>
-      <c r="AK89" s="5" t="n"/>
-      <c r="AL89" s="5" t="n"/>
-      <c r="AM89" s="5" t="n"/>
+      <c r="AG89" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-fitz-lee.md; CA-ECF-1/3 (ED-72 candidate); OR report index attributes pp.737-741 to Munford — an unresolved index mismap, pass-13 item</t>
+        </is>
+      </c>
+      <c r="AH89" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Fitzhugh Lee throughout; NEGATIVE: the 1st Md. Battalion detached with Ewell's corps, NOT present</t>
+        </is>
+      </c>
+      <c r="AI89" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro 1,913 (unclear if this already excludes the detached battalion)</t>
+        </is>
+      </c>
+      <c r="AJ89" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00-13:00, marker] Cress Ridge woods, left of Hampton's brigade — one of four independent noon-arrival agreements</t>
+        </is>
+      </c>
+      <c r="AK89" s="5" t="inlineStr">
+        <is>
+          <t>[C] march and deployment left of Hampton's; the charge leg itself not separately described</t>
+        </is>
+      </c>
+      <c r="AL89" s="5" t="inlineStr">
+        <is>
+          <t>'Participated actively in the conflict which ensued' (marker); co-credited with Hampton on the Union-side (McIntosh) tablet for the ~15:00 charge</t>
+        </is>
+      </c>
+      <c r="AM89" s="5" t="inlineStr">
+        <is>
+          <t>Marker: K5/W16/M29=50 — the lowest of the four engaged CSA brigades</t>
+        </is>
+      </c>
       <c r="AN89" s="5" t="n"/>
-      <c r="AO89" s="5" t="n"/>
+      <c r="AO89" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9665,20 +9737,56 @@
           <t>reg-csa-cav-ham</t>
         </is>
       </c>
-      <c r="AB90" s="5" t="n"/>
+      <c r="AB90" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC90" s="5" t="n"/>
       <c r="AD90" s="5" t="n"/>
       <c r="AE90" s="5" t="n"/>
       <c r="AF90" s="5" t="n"/>
-      <c r="AG90" s="5" t="n"/>
-      <c r="AH90" s="5" t="n"/>
-      <c r="AI90" s="5" t="n"/>
-      <c r="AJ90" s="5" t="n"/>
-      <c r="AK90" s="5" t="n"/>
-      <c r="AL90" s="5" t="n"/>
-      <c r="AM90" s="5" t="n"/>
+      <c r="AG90" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-ham-hampton.md; CA-ECF-1/3 (ED-72 candidate); the marker-provenance caveat (ED-73 candidate) applies</t>
+        </is>
+      </c>
+      <c r="AH90" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Wade Hampton through his wounding; Col. L. S. Baker after — the theater's clearest CSA officer pin, unclocked</t>
+        </is>
+      </c>
+      <c r="AI90" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro 1,751 (brigade total, not itemized)</t>
+        </is>
+      </c>
+      <c r="AJ90" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00, marker] Cress Ridge — one of FOUR independent CSA noon-arrival agreements (CA-ECF-1 candidate); July 2 Hunterstown contact</t>
+        </is>
+      </c>
+      <c r="AK90" s="5" t="inlineStr">
+        <is>
+          <t>[D] the relief-and-melee: the 1st NC + Jeff Davis Legion advance, pinned, Hampton commits the brigade</t>
+        </is>
+      </c>
+      <c r="AL90" s="5" t="inlineStr">
+        <is>
+          <t>The hand-to-hand fight in which Hampton was 'severely wounded' (marker verbatim); wound-mechanism detail (saber cuts + shrapnel) carried at attributed grade only</t>
+        </is>
+      </c>
+      <c r="AM90" s="5" t="inlineStr">
+        <is>
+          <t>Marker: K17/W58/M16=91; no report-side figure (Hampton's own report not located this pass)</t>
+        </is>
+      </c>
       <c r="AN90" s="5" t="n"/>
-      <c r="AO90" s="5" t="n"/>
+      <c r="AO90" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9841,20 +9949,56 @@
           <t>reg-csa-cav-jenkins</t>
         </is>
       </c>
-      <c r="AB92" s="5" t="n"/>
+      <c r="AB92" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC92" s="5" t="n"/>
       <c r="AD92" s="5" t="n"/>
       <c r="AE92" s="5" t="n"/>
       <c r="AF92" s="5" t="n"/>
-      <c r="AG92" s="5" t="n"/>
-      <c r="AH92" s="5" t="n"/>
-      <c r="AI92" s="5" t="n"/>
-      <c r="AJ92" s="5" t="n"/>
-      <c r="AK92" s="5" t="n"/>
-      <c r="AL92" s="5" t="n"/>
-      <c r="AM92" s="5" t="n"/>
+      <c r="AG92" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-jenkins.md; CA-ECF-1 (ED-72 candidate); no OR report exists (verified via the civilwarcycling index)</t>
+        </is>
+      </c>
+      <c r="AH92" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. A. G. Jenkins w July 2 (approach march); Lt. Col. Vincent Witcher commanding at ECF</t>
+        </is>
+      </c>
+      <c r="AI92" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro '2 guns, 1,126 men' (the '2 guns' clause unresolved — brigade ordnance or an attached section)</t>
+        </is>
+      </c>
+      <c r="AJ92" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00, marker] rejoined the division from Ewell's corps assignment — the fourth independent noon-arrival agreement; around/in front of the Rummel barn specifically</t>
+        </is>
+      </c>
+      <c r="AK92" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00] rejoining; [D] dismounting to fight on foot</t>
+        </is>
+      </c>
+      <c r="AL92" s="5" t="inlineStr">
+        <is>
+          <t>THE AMMUNITION NEGATIVE: Enfield rifles, ~10 rounds per man ('an oversight'), engaged dismounted as sharpshooters 'while this lasted' — first-class attested-silence-adjacent record (ED-44 class)</t>
+        </is>
+      </c>
+      <c r="AM92" s="5" t="inlineStr">
+        <is>
+          <t>'Losses not reported' (marker, verbatim) — explicit negative, not a gap</t>
+        </is>
+      </c>
       <c r="AN92" s="5" t="n"/>
-      <c r="AO92" s="5" t="n"/>
+      <c r="AO92" s="5" t="inlineStr">
+        <is>
+          <t>T2 (honestly thin, negative-evidence class)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -10105,20 +10249,56 @@
           <t>reg-csa-cav-chambliss</t>
         </is>
       </c>
-      <c r="AB95" s="5" t="n"/>
+      <c r="AB95" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC95" s="5" t="n"/>
       <c r="AD95" s="5" t="n"/>
       <c r="AE95" s="5" t="n"/>
       <c r="AF95" s="5" t="n"/>
-      <c r="AG95" s="5" t="n"/>
-      <c r="AH95" s="5" t="n"/>
-      <c r="AI95" s="5" t="n"/>
-      <c r="AJ95" s="5" t="n"/>
-      <c r="AK95" s="5" t="n"/>
-      <c r="AL95" s="5" t="n"/>
-      <c r="AM95" s="5" t="n"/>
+      <c r="AG95" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-chambliss.md; the pass's thinnest CSA-side OR-report coverage; CA-ECF-1 (ED-72 candidate)</t>
+        </is>
+      </c>
+      <c r="AH95" s="5" t="inlineStr">
+        <is>
+          <t>Col. John R. Chambliss Jr. (W. H. F. Lee wounded at Brandy Station)</t>
+        </is>
+      </c>
+      <c r="AI95" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro 1,173 (brigade total)</t>
+        </is>
+      </c>
+      <c r="AJ95" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00, marker] arrival — the third of four independent noon-arrival agreements</t>
+        </is>
+      </c>
+      <c r="AK95" s="5" t="inlineStr">
+        <is>
+          <t>[D] the opening advance the theater's own account has Hampton's brigade relieving — attributed grade only, not report-verified</t>
+        </is>
+      </c>
+      <c r="AL95" s="5" t="inlineStr">
+        <is>
+          <t>'Took an active part in the fight until it ended' (marker); own OR report verified THIN for Gettysburg (both fetched pages read as Brandy Station content + a closing casualty transmittal)</t>
+        </is>
+      </c>
+      <c r="AM95" s="5" t="inlineStr">
+        <is>
+          <t>Marker: K8/W41/M25=74; no report-side figure</t>
+        </is>
+      </c>
       <c r="AN95" s="5" t="n"/>
-      <c r="AO95" s="5" t="n"/>
+      <c r="AO95" s="5" t="inlineStr">
+        <is>
+          <t>T2 (honestly thin)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -29849,20 +30029,56 @@
           <t>reg-us-cav-2-1</t>
         </is>
       </c>
-      <c r="AB251" s="5" t="n"/>
+      <c r="AB251" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC251" s="5" t="n"/>
       <c r="AD251" s="5" t="n"/>
       <c r="AE251" s="5" t="n"/>
       <c r="AF251" s="5" t="n"/>
-      <c r="AG251" s="5" t="n"/>
-      <c r="AH251" s="5" t="n"/>
-      <c r="AI251" s="5" t="n"/>
-      <c r="AJ251" s="5" t="n"/>
-      <c r="AK251" s="5" t="n"/>
-      <c r="AL251" s="5" t="n"/>
-      <c r="AM251" s="5" t="n"/>
+      <c r="AG251" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-2-1-mcintosh.md; CA-ECF-2/3 (ED-72 candidate); McIntosh's own OR report verified post-battle-itinerary grade, not a battle narrative</t>
+        </is>
+      </c>
+      <c r="AH251" s="5" t="inlineStr">
+        <is>
+          <t>Col. John B. McIntosh throughout; no officer pin found this pass</t>
+        </is>
+      </c>
+      <c r="AI251" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro sum ~1,206 (a roster ambiguity — a '1st PA Cavalry 355' row — carried unresolved, not summed in); no report primary</t>
+        </is>
+      </c>
+      <c r="AJ251" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Hanover Road right, the ECF ±75 m georef class (ecf-base tie point)</t>
+        </is>
+      </c>
+      <c r="AK251" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00] the Custer-recall trigger (McIntosh tablet = Custer tablet agreement)</t>
+        </is>
+      </c>
+      <c r="AL251" s="5" t="inlineStr">
+        <is>
+          <t>The general engagement ~14:00; the ~15:00 Hampton/Fitz Lee charge repulsed 'with the aid of Artillery' (Stallsmith Farm concealment detail)</t>
+        </is>
+      </c>
+      <c r="AM251" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: W 7 off/19 men, CM 9 men, Total 35 (killed not on the fetched marker text — gap, not zero)</t>
+        </is>
+      </c>
       <c r="AN251" s="5" t="n"/>
-      <c r="AO251" s="5" t="n"/>
+      <c r="AO251" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -30149,20 +30365,56 @@
           <t>reg-us-cav-3-2</t>
         </is>
       </c>
-      <c r="AB254" s="5" t="n"/>
+      <c r="AB254" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC254" s="5" t="n"/>
       <c r="AD254" s="5" t="n"/>
       <c r="AE254" s="5" t="n"/>
       <c r="AF254" s="5" t="n"/>
-      <c r="AG254" s="5" t="n"/>
-      <c r="AH254" s="5" t="n"/>
-      <c r="AI254" s="5" t="n"/>
-      <c r="AJ254" s="5" t="n"/>
-      <c r="AK254" s="5" t="n"/>
-      <c r="AL254" s="5" t="n"/>
-      <c r="AM254" s="5" t="n"/>
+      <c r="AG254" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-3-2-custer.md; CA-ECF-2/3 (ED-72 candidate); own OR report verified diary-form, thin</t>
+        </is>
+      </c>
+      <c r="AH254" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. George A. Custer throughout (first brigade command); Maj. Noah Ferry (5th Mich.) k per the report's own itinerary line</t>
+        </is>
+      </c>
+      <c r="AI254" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro sum 1,933; no report-stated brigade total (report is diary/itinerary form)</t>
+        </is>
+      </c>
+      <c r="AJ254" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00] Two Taverns to the Hanover Road right (own tablet clock); the shared ECF ±75 m frame</t>
+        </is>
+      </c>
+      <c r="AK254" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00] the march; [C ~14:00] the Gregg-retains-Custer command decision overriding Kilpatrick's recall</t>
+        </is>
+      </c>
+      <c r="AL254" s="5" t="inlineStr">
+        <is>
+          <t>7th Michigan's charge checked ('but not successfully', Gregg's report) then the 1st Michigan's advance; Battery M/2nd US 'engaged all day'</t>
+        </is>
+      </c>
+      <c r="AM254" s="5" t="inlineStr">
+        <is>
+          <t>Tablet total 257 (K1/31, W13/134, CM 78) vs the July-3-ONLY return row '1 and 28 killed' — an ED-43-class day-scope conflict, not resolved</t>
+        </is>
+      </c>
       <c r="AN254" s="5" t="n"/>
-      <c r="AO254" s="5" t="n"/>
+      <c r="AO254" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -30237,20 +30489,56 @@
           <t>reg-us-cav-2-3</t>
         </is>
       </c>
-      <c r="AB255" s="5" t="n"/>
+      <c r="AB255" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
       <c r="AC255" s="5" t="n"/>
       <c r="AD255" s="5" t="n"/>
       <c r="AE255" s="5" t="n"/>
       <c r="AF255" s="5" t="n"/>
-      <c r="AG255" s="5" t="n"/>
-      <c r="AH255" s="5" t="n"/>
-      <c r="AI255" s="5" t="n"/>
-      <c r="AJ255" s="5" t="n"/>
-      <c r="AK255" s="5" t="n"/>
-      <c r="AL255" s="5" t="n"/>
-      <c r="AM255" s="5" t="n"/>
+      <c r="AG255" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-2-3-jigregg.md; the pass's weakest-sourced new dossier (tablet page 404'd; own OR report identified, not fetched)</t>
+        </is>
+      </c>
+      <c r="AH255" s="5" t="inlineStr">
+        <is>
+          <t>Col. J. Irvin Gregg throughout (D. McM. Gregg's cousin)</t>
+        </is>
+      </c>
+      <c r="AI255" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro sum 1,255 (agrees with an independently-surveyed 1,265, attributed grade)</t>
+        </is>
+      </c>
+      <c r="AJ255" s="5" t="inlineStr">
+        <is>
+          <t>[D] July 2 Brinkerhoff's Ridge (vs 2nd Va. Infantry); July 3 Baltimore Pike reserve — all attributed grade, not directly fetched this pass</t>
+        </is>
+      </c>
+      <c r="AK255" s="5" t="inlineStr">
+        <is>
+          <t>Not authored this pass</t>
+        </is>
+      </c>
+      <c r="AL255" s="5" t="inlineStr">
+        <is>
+          <t>[D] July 2 skirmish; July 3 reserve with SOME casualties (ED-44 class)</t>
+        </is>
+      </c>
+      <c r="AM255" s="5" t="inlineStr">
+        <is>
+          <t>6 k / 12 w / 3 m = 21 (attributed grade, not independently fetched — pass-13 re-verification flagged)</t>
+        </is>
+      </c>
       <c r="AN255" s="5" t="n"/>
-      <c r="AO255" s="5" t="n"/>
+      <c r="AO255" s="5" t="inlineStr">
+        <is>
+          <t>T2 (honestly thin)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -30361,20 +30649,56 @@
           <t>reg-us-cav-3-1</t>
         </is>
       </c>
-      <c r="AB256" s="5" t="n"/>
+      <c r="AB256" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC256" s="5" t="n"/>
       <c r="AD256" s="5" t="n"/>
       <c r="AE256" s="5" t="n"/>
       <c r="AF256" s="5" t="n"/>
-      <c r="AG256" s="5" t="n"/>
-      <c r="AH256" s="5" t="n"/>
-      <c r="AI256" s="5" t="n"/>
-      <c r="AJ256" s="5" t="n"/>
-      <c r="AK256" s="5" t="n"/>
-      <c r="AL256" s="5" t="n"/>
-      <c r="AM256" s="5" t="n"/>
+      <c r="AG256" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-3-1-farnsworth.md; CA-SCF-1/2 (ED-72 candidate); Kilpatrick's own report identified, not fetched — the ordered-a-futile-charge question left open deliberately</t>
+        </is>
+      </c>
+      <c r="AH256" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Elon J. Farnsworth k in the July 3 charge; Col. N. P. Richmond succeeding</t>
+        </is>
+      </c>
+      <c r="AI256" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro sum 1,924</t>
+        </is>
+      </c>
+      <c r="AJ256" s="5" t="inlineStr">
+        <is>
+          <t>[C ~13:00, marker] arrival on South Cavalry Field ('about 1 P.M.'); the charge ground crosses stone walls held by CSA infantry</t>
+        </is>
+      </c>
+      <c r="AK256" s="5" t="inlineStr">
+        <is>
+          <t>[C ~13:00] arrival; [C ~17:30, TRIPLE tablet agreement] the charge — the theater's strongest single clock</t>
+        </is>
+      </c>
+      <c r="AL256" s="5" t="inlineStr">
+        <is>
+          <t>The charge and repulse 'with heavy loss and Gen. Farnsworth killed'; Parsons's B&amp;L primary (retrospective, attributed grade) — the protest quote, shot five times, refused surrender; the Oates-suicide counter-account carried UNRESOLVED (ED-39 §3 litigated-memory class)</t>
+        </is>
+      </c>
+      <c r="AM256" s="5" t="inlineStr">
+        <is>
+          <t>Brigade tablet: K3/18, W6/28, CM1/42 = 98; the division tablet's 355 total is NOT directly additive with Merritt's total — an open EC6 reconciliation item</t>
+        </is>
+      </c>
       <c r="AN256" s="5" t="n"/>
-      <c r="AO256" s="5" t="n"/>
+      <c r="AO256" s="5" t="inlineStr">
+        <is>
+          <t>T3 (South Cavalry Field grain)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -30485,20 +30809,56 @@
           <t>reg-us-cav-1-3</t>
         </is>
       </c>
-      <c r="AB257" s="5" t="n"/>
+      <c r="AB257" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC257" s="5" t="n"/>
       <c r="AD257" s="5" t="n"/>
       <c r="AE257" s="5" t="n"/>
       <c r="AF257" s="5" t="n"/>
-      <c r="AG257" s="5" t="n"/>
-      <c r="AH257" s="5" t="n"/>
-      <c r="AI257" s="5" t="n"/>
-      <c r="AJ257" s="5" t="n"/>
-      <c r="AK257" s="5" t="n"/>
-      <c r="AL257" s="5" t="n"/>
-      <c r="AM257" s="5" t="n"/>
+      <c r="AG257" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-cav-1-3-merritt.md; CA-SCF-1/2 (ED-72 candidate); the pass's best EC6 finding on the cavalry side</t>
+        </is>
+      </c>
+      <c r="AH257" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Wesley Merritt throughout; Maj. Samuel H. Starr (6th US) w, lost an arm, at Fairfield — PRIMARY pin</t>
+        </is>
+      </c>
+      <c r="AI257" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-repro sum 1,792</t>
+        </is>
+      </c>
+      <c r="AJ257" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00, PRIMARY — Merritt's own report] march start; South Cavalry Field 4 miles out; the 6th US's Fairfield detachment is OFF-MAP (the standing off-square ruling)</t>
+        </is>
+      </c>
+      <c r="AK257" s="5" t="inlineStr">
+        <is>
+          <t>[C ~12:00] the march (report=tablet near-exact agreement); [C ~17:30] 'about four hours... brought to a close by a heavy rain' — independently corroborates the triple tablet agreement</t>
+        </is>
+      </c>
+      <c r="AL257" s="5" t="inlineStr">
+        <is>
+          <t>The stone-fence advance, report=tablet near-exact; the 6th US's separate Fairfield fight ('not without success')</t>
+        </is>
+      </c>
+      <c r="AM257" s="5" t="inlineStr">
+        <is>
+          <t>THE FAIRFIELD-POOLING FINDING: tablet total 418 (K1/27, W12/104, CM6/268) pools TWO fields — the 268 missing is explained by the isolated, overmatched Fairfield action, not South Cavalry Field alone; no per-regiment split authored</t>
+        </is>
+      </c>
       <c r="AN257" s="5" t="n"/>
-      <c r="AO257" s="5" t="n"/>
+      <c r="AO257" s="5" t="inlineStr">
+        <is>
+          <t>T4 (July 3 grain — the EC6 composition finding)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -32779,12 +33139,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-hq</t>
+          <t>reg-us-vi-hq</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>XI Corps headquarters (corps command)</t>
+          <t>VI Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -32825,7 +33185,7 @@
       </c>
       <c r="V277" s="2" t="inlineStr">
         <is>
-          <t>XI Corps headquarters</t>
+          <t>VI Corps headquarters</t>
         </is>
       </c>
       <c r="W277" s="4" t="inlineStr">
@@ -32846,12 +33206,12 @@
       </c>
       <c r="AA277" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-hq</t>
+          <t>reg-us-vi-hq</t>
         </is>
       </c>
       <c r="AB277" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC277" s="5" t="n"/>
@@ -32860,55 +33220,55 @@
       <c r="AF277" s="5" t="n"/>
       <c r="AG277" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-hq-howard.md; register row added pass 10; ED-68 candidate (sub-anchor ~11:30)</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-hq-sedgwick.md; the VI Corps cheap batch; register row reg-us-vi-hq added this pass</t>
         </is>
       </c>
       <c r="AH277" s="5" t="inlineStr">
         <is>
-          <t>Howard (field command ~11:30-evening; corps to Schurz); Barlow w -&gt; Ames; Schimmelfennig cut off</t>
+          <t>Maj. Gen. John Sedgwick; the army's largest corps at Gettysburg (~16,000, attributed)</t>
         </is>
       </c>
       <c r="AI277" s="5" t="inlineStr">
         <is>
-          <t>Schurz's 'hardly over 6,000' two-division frame</t>
+          <t>Not authored at corps grain (would require summing seven brigades + arty brigade, none re-verified this pass)</t>
         </is>
       </c>
       <c r="AJ277" s="5" t="inlineStr">
         <is>
-          <t>the cemetery eminence (the rally position chosen ~11:30); command nodes registered (town + hill pair)</t>
+          <t>[D] the ~30-mile July 2 forced march (Manchester to the field); reserve posture ('operations were mostly by Brigades independent', tablet verbatim)</t>
         </is>
       </c>
       <c r="AK277" s="5" t="inlineStr">
         <is>
-          <t>the corps approach ladder (3:30 orders / 8:00 march / 10:30 hurry / ~14:00 deployed)</t>
+          <t>Not authored at corps grain</t>
         </is>
       </c>
       <c r="AL277" s="5" t="inlineStr">
         <is>
-          <t>THE ASSUMPTION TWO-PRIMARY (Howard 11.30 = Schurz 11.30; tablet 10.30 collapsed onto the hurry-forward order); the 16:00/16:10/16:30 fall-back ladder; the CA-J1P-7 Howard pole</t>
+          <t>Attested-static majority; TWO named exceptions — Nevin's brigade (already T4 full-arc, pass 7) and Shaler's brigade (to Culp's Hill ~08:45 July 3, attributed grade, NOT primary-verified this pass)</t>
         </is>
       </c>
       <c r="AM277" s="5" t="inlineStr">
         <is>
-          <t>corps 3,801 (1,448 c/m - the through-town capture mass)</t>
+          <t>Corps tablet: K2/25, W14/171, CM30 = 242 (not apportioned by brigade here)</t>
         </is>
       </c>
       <c r="AN277" s="5" t="n"/>
       <c r="AO277" s="5" t="inlineStr">
         <is>
-          <t>T3 (command record)</t>
+          <t>T2 (command record, attested-static-with-exceptions)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-hq</t>
+          <t>reg-us-xi-hq</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>XII Corps headquarters (corps command)</t>
+          <t>XI Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -32949,7 +33309,7 @@
       </c>
       <c r="V278" s="2" t="inlineStr">
         <is>
-          <t>XII Corps headquarters</t>
+          <t>XI Corps headquarters</t>
         </is>
       </c>
       <c r="W278" s="4" t="inlineStr">
@@ -32970,12 +33330,12 @@
       </c>
       <c r="AA278" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-hq</t>
+          <t>reg-us-xi-hq</t>
         </is>
       </c>
       <c r="AB278" s="5" t="inlineStr">
         <is>
-          <t>command record (the absent-then-returning frame)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC278" s="5" t="n"/>
@@ -32984,37 +33344,37 @@
       <c r="AF278" s="5" t="n"/>
       <c r="AG278" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-hq-slocum-williams.md; added pass 8 w/ register row</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-hq-howard.md; register row added pass 10; ED-68 candidate (sub-anchor ~11:30)</t>
         </is>
       </c>
       <c r="AH278" s="5" t="inlineStr">
         <is>
-          <t>Slocum right wing / WILLIAMS commanding the corps July 1-3 / Ruger 1st Div (cascade verbatim; return still heads the corps Slocum - metadata hazard)</t>
+          <t>Howard (field command ~11:30-evening; corps to Schurz); Barlow w -&gt; Ames; Schimmelfennig cut off</t>
         </is>
       </c>
       <c r="AI278" s="5" t="inlineStr">
         <is>
-          <t>corps aggregate OPEN by design (unit EC2s carry it)</t>
+          <t>Schurz's 'hardly over 6,000' two-division frame</t>
         </is>
       </c>
       <c r="AJ278" s="5" t="inlineStr">
         <is>
-          <t>[E] the works line to McAllister's mill-pond (drawn+computed 140 m); [D] THE ABSENCE drawn on j2-04 (departing labels) + j2-05 '9. P.M.' return annotation (5931,4723) - a sheet-internal clock; HQ pin tab-us-xii-1-hq-williams</t>
+          <t>the cemetery eminence (the rally position chosen ~11:30); command nodes registered (town + hill pair)</t>
         </is>
       </c>
       <c r="AK278" s="5" t="inlineStr">
         <is>
-          <t>[D] the detachment (Ruger+Lockwood to the left; Geary to cover); the left-wing round trip ending 'quite dark' (ED-31 physics); the return + the near-midnight wrong-road discovery</t>
+          <t>the corps approach ladder (3:30 orders / 8:00 march / 10:30 hurry / ~14:00 deployed)</t>
         </is>
       </c>
       <c r="AL278" s="5" t="inlineStr">
         <is>
-          <t>the breastworks decision (Slocum, credited verbatim); THE McGILVERY MEETING + Lockwood's three-pieces recapture (ED-61 ledger, command grain); July 3 daylight plan (15-min artillery prep)</t>
+          <t>THE ASSUMPTION TWO-PRIMARY (Howard 11.30 = Schurz 11.30; tablet 10.30 collapsed onto the hurry-forward order); the 16:00/16:10/16:30 fall-back ladder; the CA-J1P-7 Howard pole</t>
         </is>
       </c>
       <c r="AM278" s="5" t="inlineStr">
         <is>
-          <t>corps total 1,082 (return p. 185); brigade rows recorded for the absent frame's future dossiers</t>
+          <t>corps 3,801 (1,448 c/m - the through-town capture mass)</t>
         </is>
       </c>
       <c r="AN278" s="5" t="n"/>
@@ -33027,12 +33387,12 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>us-hall</t>
+          <t>reg-us-xii-hq</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Hall's Brigade</t>
+          <t>XII Corps headquarters (corps command)</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -33042,7 +33402,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>parent-brigade</t>
+          <t>command</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -33050,92 +33410,56 @@
           <t>infantry</t>
         </is>
       </c>
-      <c r="F279" s="2" t="n">
-        <v>920</v>
-      </c>
-      <c r="G279" s="2" t="n">
-        <v>555</v>
-      </c>
+      <c r="F279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr"/>
       <c r="H279" s="3">
         <f>IF(F279=0,0,1-G279/F279)</f>
         <v/>
       </c>
-      <c r="I279" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="J279" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K279" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L279" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M279" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O279" s="2" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="P279" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q279" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R279" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S279" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T279" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="I279" s="2" t="inlineStr"/>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr"/>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr"/>
+      <c r="O279" s="2" t="inlineStr"/>
+      <c r="P279" s="2" t="inlineStr"/>
+      <c r="Q279" s="2" t="inlineStr"/>
+      <c r="R279" s="2" t="inlineStr"/>
+      <c r="S279" s="2" t="inlineStr"/>
+      <c r="T279" s="2" t="inlineStr"/>
       <c r="U279" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V279" s="2" t="inlineStr">
         <is>
-          <t>Hall</t>
-        </is>
-      </c>
-      <c r="W279" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X279" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
+          <t>XII Corps headquarters</t>
+        </is>
+      </c>
+      <c r="W279" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="inlineStr"/>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>in-build</t>
+          <t>not-yet-cast</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-3</t>
+          <t>reg-us-xii-hq</t>
         </is>
       </c>
       <c r="AB279" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (crisis rush authored in Angle cast)</t>
+          <t>command record (the absent-then-returning frame)</t>
         </is>
       </c>
       <c r="AC279" s="5" t="n"/>
@@ -33144,55 +33468,55 @@
       <c r="AF279" s="5" t="n"/>
       <c r="AG279" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-hq-slocum-williams.md; added pass 8 w/ register row</t>
         </is>
       </c>
       <c r="AH279" s="5" t="inlineStr">
         <is>
-          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
+          <t>Slocum right wing / WILLIAMS commanding the corps July 1-3 / Ruger 1st Div (cascade verbatim; return still heads the corps Slocum - metadata hazard)</t>
         </is>
       </c>
       <c r="AI279" s="5" t="inlineStr">
         <is>
-          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
+          <t>corps aggregate OPEN by design (unit EC2s carry it)</t>
         </is>
       </c>
       <c r="AJ279" s="5" t="inlineStr">
         <is>
-          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
+          <t>[E] the works line to McAllister's mill-pond (drawn+computed 140 m); [D] THE ABSENCE drawn on j2-04 (departing labels) + j2-05 '9. P.M.' return annotation (5931,4723) - a sheet-internal clock; HQ pin tab-us-xii-1-hq-williams</t>
         </is>
       </c>
       <c r="AK279" s="5" t="inlineStr">
         <is>
-          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
+          <t>[D] the detachment (Ruger+Lockwood to the left; Geary to cover); the left-wing round trip ending 'quite dark' (ED-31 physics); the return + the near-midnight wrong-road discovery</t>
         </is>
       </c>
       <c r="AL279" s="5" t="inlineStr">
         <is>
-          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
+          <t>the breastworks decision (Slocum, credited verbatim); THE McGILVERY MEETING + Lockwood's three-pieces recapture (ED-61 ledger, command grain); July 3 daylight plan (15-min artillery prep)</t>
         </is>
       </c>
       <c r="AM279" s="5" t="inlineStr">
         <is>
-          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
+          <t>corps total 1,082 (return p. 185); brigade rows recorded for the absent frame's future dossiers</t>
         </is>
       </c>
       <c r="AN279" s="5" t="n"/>
       <c r="AO279" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (T5-grade window via V2 claims)</t>
+          <t>T3 (command record)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>us-stannard</t>
+          <t>us-hall</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Stannard's Vermont Brigade</t>
+          <t>Hall's Brigade</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -33211,68 +33535,68 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>1950</v>
+        <v>920</v>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1600</v>
+        <v>555</v>
       </c>
       <c r="H280" s="3">
         <f>IF(F280=0,0,1-G280/F280)</f>
         <v/>
       </c>
       <c r="I280" s="2" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K280" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L280" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M280" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N280" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O280" s="2" t="n">
-        <v>297.9</v>
+        <v>60.9</v>
       </c>
       <c r="P280" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q280" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U280" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V280" s="2" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R280" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S280" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T280" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U280" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V280" s="2" t="inlineStr">
-        <is>
-          <t>Stannard</t>
-        </is>
-      </c>
-      <c r="W280" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
           <t>T5</t>
@@ -33290,12 +33614,12 @@
       </c>
       <c r="AA280" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-3</t>
+          <t>reg-us-ii-2-3</t>
         </is>
       </c>
       <c r="AB280" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (crisis rush authored in Angle cast)</t>
         </is>
       </c>
       <c r="AC280" s="5" t="n"/>
@@ -33304,55 +33628,55 @@
       <c r="AF280" s="5" t="n"/>
       <c r="AG280" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-3-hall.md; p.438 extraction gap + 'Should be Arnold's' footnote -&gt; ED-40 candidate; pass-5: July 2 arc closed both-sided (csa-1c-mcl-3-barksdale.md pairing; Barksdale-pin compatibility note)</t>
         </is>
       </c>
       <c r="AH280" s="5" t="inlineStr">
         <is>
-          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
+          <t>Col. Hall unwounded; Revere (20MA) mw Jul 2, Steele (7MI) k, Thoman (59NY) k Jul 3 (or-27-1-hall pp.435-440, stub UPGRADED)</t>
         </is>
       </c>
       <c r="AI280" s="5" t="inlineStr">
         <is>
-          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
+          <t>920 (build compilation, hop flagged; division 3,773 primary via Harrow)</t>
         </is>
       </c>
       <c r="AJ280" s="5" t="inlineStr">
         <is>
-          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
+          <t>[E] two-line layout: wall row 59NY(4375,4756) 7MI(4379,4728) 20MA(4381,4688) + support row 42NY(4447,4750) 19MA(4445,4692); rails-shelter verbatim; Bachelder j3-03 concurs</t>
         </is>
       </c>
       <c r="AK280" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
+          <t>[D Jul 2] 42NY+19MA to Humphreys; [A vs CA-J3A-9] by-the-flank rush to Webb ~150-250m [B: 3-5 min]; 10-min melee duration stated</t>
         </is>
       </c>
       <c r="AL280" s="5" t="inlineStr">
         <is>
-          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
+          <t>[C +5] 'At 1 o'clock' opening; 'At 3 o'clock exactly the fire slackened, and his first line advanced'; fire ladder 200 yd -&gt; 50 paces; 20 flags in 100 yd square</t>
         </is>
       </c>
       <c r="AM280" s="5" t="inlineStr">
         <is>
-          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
+          <t>tablet 377 (6+75k/29+253w/14m); Jul 2 share attested; pins Revere mw Jul 2, Steele/Thoman k Jul 3 crisis</t>
         </is>
       </c>
       <c r="AN280" s="5" t="n"/>
       <c r="AO280" s="5" t="inlineStr">
         <is>
-          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
+          <t>T4 full-arc (T5-grade window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>us-webb</t>
+          <t>us-stannard</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Webb's Brigade (Philadelphia Brigade)</t>
+          <t>Stannard's Vermont Brigade</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -33371,61 +33695,61 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>1250</v>
+        <v>1950</v>
       </c>
       <c r="G281" s="2" t="n">
-        <v>760</v>
+        <v>1600</v>
       </c>
       <c r="H281" s="3">
         <f>IF(F281=0,0,1-G281/F281)</f>
         <v/>
       </c>
       <c r="I281" s="2" t="n">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="J281" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="K281" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L281" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="M281" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N281" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O281" s="2" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="P281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T281" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U281" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O281" s="2" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="P281" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q281" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="R281" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S281" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T281" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U281" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="V281" s="2" t="inlineStr">
         <is>
-          <t>Webb</t>
+          <t>Stannard</t>
         </is>
       </c>
       <c r="W281" s="2" t="inlineStr">
@@ -33450,7 +33774,7 @@
       </c>
       <c r="AA281" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-2</t>
+          <t>reg-us-i-3-3</t>
         </is>
       </c>
       <c r="AB281" s="5" t="inlineStr">
@@ -33464,55 +33788,55 @@
       <c r="AF281" s="5" t="n"/>
       <c r="AG281" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-3-stannard.md; ED-32 adopted 2026-07-11; wheel clock verified-negative (no witness clock exists)</t>
         </is>
       </c>
       <c r="AH281" s="5" t="inlineStr">
         <is>
-          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
+          <t>Stannard (w July 3 thigh, during 2nd flank move) -&gt; Randall; 13/14/16 VT engaged, 12/15 VT train guard (or-27-oob; stone-sentinels)</t>
         </is>
       </c>
       <c r="AI281" s="5" t="inlineStr">
         <is>
-          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
+          <t>ADOPTED ED-32: 1,788 engaged = sum of engaged rgts (480+647+661); the 1,950 brigade figure failed re-verification and is kept only as a recorded failed reading (oob-strengths #3)</t>
         </is>
       </c>
       <c r="AJ281" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
+          <t>[E] advanced line fwd of main position, ctr (4300,4470) f260 +-50m (Bachelder sheet 3); [A vs CA-J3A-8] 13VT wheeled anchor (4326,4764) f15 (200-yd monument statement, coord inferred +-40m)</t>
         </is>
       </c>
       <c r="AK281" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
+          <t>[A vs CA-J3A-8 ~15:20] change front fwd on 1st co., 13th then 16th, ~180m [B: 3-4 min at 1.4 m/s]; [D after CA-J3A-9] 16th reversal S vs Wilcox/Lang ~300m</t>
         </is>
       </c>
       <c r="AL281" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
+          <t>[D 15:16-20] front fire punishing Kemper's oblique; [A vs CA-J3A-8] flank fire at ~60 yd (Sturtevant pp.304-305), 243 prisoners (13VT monument); [D] 2nd flank fire, 2nd FL colors taken (veazey-or)</t>
         </is>
       </c>
       <c r="AM281" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
+          <t>45/275/30=350 of 1,950, 18% (stone-sentinels); episode split unattested - build decay is reconstruction; pin: Stannard w [D during 2nd flank move]</t>
         </is>
       </c>
       <c r="AN281" s="5" t="n"/>
       <c r="AO281" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (T5 window held)</t>
+          <t>T4 (T5-grade inside Angle window via V2 claims)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>us-8oh</t>
+          <t>us-webb</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>8th Ohio Infantry</t>
+          <t>Webb's Brigade (Philadelphia Brigade)</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -33522,7 +33846,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>parent-brigade</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -33531,71 +33855,71 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>164</v>
+        <v>1250</v>
       </c>
       <c r="G282" s="2" t="n">
-        <v>118</v>
+        <v>760</v>
       </c>
       <c r="H282" s="3">
         <f>IF(F282=0,0,1-G282/F282)</f>
         <v/>
       </c>
       <c r="I282" s="2" t="n">
-        <v>46</v>
+        <v>490</v>
       </c>
       <c r="J282" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L282" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M282" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N282" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O282" s="2" t="n">
-        <v>219.5</v>
+        <v>23.3</v>
       </c>
       <c r="P282" s="2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U282" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V282" s="2" t="inlineStr">
+        <is>
+          <t>Webb</t>
+        </is>
+      </c>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R282" s="2" t="inlineStr">
-        <is>
-          <t>line/skirmish</t>
-        </is>
-      </c>
-      <c r="S282" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T282" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U282" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V282" s="2" t="inlineStr">
-        <is>
-          <t>8th Ohio</t>
-        </is>
-      </c>
-      <c r="W282" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
@@ -33608,7 +33932,11 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-ii-2-2</t>
+        </is>
+      </c>
       <c r="AB282" s="5" t="inlineStr">
         <is>
           <t>authored-ok</t>
@@ -33620,55 +33948,55 @@
       <c r="AF282" s="5" t="n"/>
       <c r="AG282" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-2-webb.md; CA-J3A-9: Armistead 'passed over the fence with probably over 100' - report twin of the ~150 party claim</t>
         </is>
       </c>
       <c r="AH282" s="5" t="inlineStr">
         <is>
-          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+          <t>Webb w Jul 3 (MoH); O'Kane (69th) k Jul 3, Baxter (72nd) w Jul 2; 106th PA detached to Howard Jul 2 'a little before dark' - brigade fights Jul 3 three-regiment (or-27-1-webb)</t>
         </is>
       </c>
       <c r="AI282" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 209 (compilation, flagged)</t>
+          <t>ED-9 1,250 held; NO primary; Jul 3 subtraction of the 106th is primary (or-27-1-webb); division context 3,800 engaged (or-27-1-gibbon)</t>
         </is>
       </c>
       <c r="AJ282" s="5" t="inlineStr">
         <is>
-          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+          <t>[C] Jul 2 06:30 Granite Ridge, 69th at fence in advance; [E/T5] wall/clump geometry held via V2 claims; j3-02 WEBB bar (4391,4827) +-100m</t>
         </is>
       </c>
       <c r="AK282" s="5" t="inlineStr">
         <is>
-          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+          <t>[C] Jul 2 ~18:30 counterattack vs Wright (beyond one Brown gun, ~250 prisoners); [E] Jul 3 morning 71st to the wall, 72nd reserve under crest; [T5] the crisis window held</t>
         </is>
       </c>
       <c r="AL282" s="5" t="inlineStr">
         <is>
-          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+          <t>[A vs CA-J3A-1/4] 'About 1 p.m. more than twenty batteries'; 'By 2.45 silenced the Rhode Island battery' (ED-33 timed by the brigade CO); 3 Cushing guns to the fence (vs V2's 2 - conflict on claim); captures ~1,000 prisoners/6 flags/1,400 arms</t>
         </is>
       </c>
       <c r="AM282" s="5" t="inlineStr">
         <is>
-          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+          <t>CONFLICT: report 525 (43 off + 482 men) vs return 491 (69th 137, 71st 98, 72nd 192, 106th 64); build decay 490 = return; pins Webb w, O'Kane k, Baxter w Jul 2</t>
         </is>
       </c>
       <c r="AN282" s="5" t="n"/>
       <c r="AO282" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 full-arc (T5 window held)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>us-bartlett</t>
+          <t>us-8oh</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
+          <t>8th Ohio Infantry</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -33687,23 +34015,23 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>1325</v>
+        <v>164</v>
       </c>
       <c r="G283" s="2" t="n">
-        <v>1325</v>
+        <v>118</v>
       </c>
       <c r="H283" s="3">
         <f>IF(F283=0,0,1-G283/F283)</f>
         <v/>
       </c>
       <c r="I283" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L283" s="2" t="n">
         <v>0</v>
@@ -33712,36 +34040,36 @@
         <v>0</v>
       </c>
       <c r="N283" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O283" s="2" t="n">
-        <v>0</v>
+        <v>219.5</v>
       </c>
       <c r="P283" s="2" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R283" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>line/skirmish</t>
         </is>
       </c>
       <c r="S283" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T283" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U283" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V283" s="2" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>8th Ohio</t>
         </is>
       </c>
       <c r="W283" s="2" t="inlineStr">
@@ -33756,7 +34084,7 @@
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
@@ -33764,35 +34092,67 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AA283" s="2" t="inlineStr">
-        <is>
-          <t>reg-us-vi-1-2</t>
-        </is>
-      </c>
-      <c r="AB283" s="5" t="n"/>
+      <c r="AA283" s="2" t="inlineStr"/>
+      <c r="AB283" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC283" s="5" t="n"/>
       <c r="AD283" s="5" t="n"/>
       <c r="AE283" s="5" t="n"/>
       <c r="AF283" s="5" t="n"/>
-      <c r="AG283" s="5" t="n"/>
-      <c r="AH283" s="5" t="n"/>
-      <c r="AI283" s="5" t="n"/>
-      <c r="AJ283" s="5" t="n"/>
-      <c r="AK283" s="5" t="n"/>
-      <c r="AL283" s="5" t="n"/>
-      <c r="AM283" s="5" t="n"/>
+      <c r="AG283" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
+        </is>
+      </c>
+      <c r="AH283" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
+        </is>
+      </c>
+      <c r="AI283" s="5" t="inlineStr">
+        <is>
+          <t>no primary; build 209 (compilation, flagged)</t>
+        </is>
+      </c>
+      <c r="AJ283" s="5" t="inlineStr">
+        <is>
+          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
+        </is>
+      </c>
+      <c r="AK283" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
+        </is>
+      </c>
+      <c r="AL283" s="5" t="inlineStr">
+        <is>
+          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
+        </is>
+      </c>
+      <c r="AM283" s="5" t="inlineStr">
+        <is>
+          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
+        </is>
+      </c>
       <c r="AN283" s="5" t="n"/>
-      <c r="AO283" s="5" t="n"/>
+      <c r="AO283" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>us-baxter</t>
+          <t>us-bartlett</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
+          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -33811,10 +34171,10 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>800</v>
+        <v>1325</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>800</v>
+        <v>1325</v>
       </c>
       <c r="H284" s="3">
         <f>IF(F284=0,0,1-G284/F284)</f>
@@ -33824,34 +34184,34 @@
         <v>0</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M284" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N284" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O284" s="2" t="n">
-        <v>1021.5</v>
+        <v>0</v>
       </c>
       <c r="P284" s="2" t="n">
-        <v>1021.5</v>
+        <v>0</v>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S284" s="2" t="n">
@@ -33865,7 +34225,7 @@
       </c>
       <c r="V284" s="2" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="W284" s="2" t="inlineStr">
@@ -33880,7 +34240,7 @@
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
@@ -33890,69 +34250,33 @@
       </c>
       <c r="AA284" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-2</t>
-        </is>
-      </c>
-      <c r="AB284" s="5" t="inlineStr">
-        <is>
-          <t>unauthored</t>
-        </is>
-      </c>
+          <t>reg-us-vi-1-2</t>
+        </is>
+      </c>
+      <c r="AB284" s="5" t="n"/>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-i-2-2-baxter.md; CA-J1P-2 Union receiving executor</t>
-        </is>
-      </c>
-      <c r="AH284" s="5" t="inlineStr">
-        <is>
-          <t>Baxter uninjured; Bates w x2, Wheelock captured/escaped, Lt. Thomas k in the streets; Coulter+11th Pa transferred out to 1st Bde</t>
-        </is>
-      </c>
-      <c r="AI284" s="5" t="inlineStr">
-        <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,452 (hop); division frame 'less than 2,500' (Robinson) CONFLICTS with the two-brigade B&amp;M sum 2,989 - both carried</t>
-        </is>
-      </c>
-      <c r="AJ284" s="5" t="inlineStr">
-        <is>
-          <t>[C 11:00] arrival; the two front-changes to the Oak Ridge crest (the pass-10 drawn wall bar = this line); [C ~17:00] the Emmitsburg-road line; [C Jul 2 10:00] relieved by Webb; the July 2-3 support ladder (six clocked moves); [C Jul 3 ~13:00] Cemetery Hill right-front under the cannonade ~2 h, then Hays's right</t>
-        </is>
-      </c>
-      <c r="AK284" s="5" t="inlineStr">
-        <is>
-          <t>[D] the relief hand-off ~15:00+ (Coulter's after-3, ammunition exhausted); the town retreat under fire; the clocked July 2-3 ladder</t>
-        </is>
-      </c>
-      <c r="AL284" s="5" t="inlineStr">
-        <is>
-          <t>THE IVERSON REPULSE RECEIVING RECORD: the deadly fire, the charge (88th Pa two flags + 97th NY one), the 12th Mass flank fire 'great influence upon its surrender'; Coulter 12:30 general-firing pin; division 'three flags and about 1,000 prisoners'; the Northrup conduct record</t>
-        </is>
-      </c>
-      <c r="AM284" s="5" t="inlineStr">
-        <is>
-          <t>Return p. 174 rows (not digit-re-read); division 'lost considerably more than half' of &lt;2,500 (primary); shape: the Oak Ridge window + the town capture spike; July 3 'considerable loss' skirmish clear (unquantified)</t>
-        </is>
-      </c>
+      <c r="AG284" s="5" t="n"/>
+      <c r="AH284" s="5" t="n"/>
+      <c r="AI284" s="5" t="n"/>
+      <c r="AJ284" s="5" t="n"/>
+      <c r="AK284" s="5" t="n"/>
+      <c r="AL284" s="5" t="n"/>
+      <c r="AM284" s="5" t="n"/>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="inlineStr">
-        <is>
-          <t>T4 (July 1 grain; full arc T3)</t>
-        </is>
-      </c>
+      <c r="AO284" s="5" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>us-berdan</t>
+          <t>us-baxter</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
+          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -33971,10 +34295,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>1405</v>
+        <v>800</v>
       </c>
       <c r="G285" s="2" t="n">
-        <v>1405</v>
+        <v>800</v>
       </c>
       <c r="H285" s="3">
         <f>IF(F285=0,0,1-G285/F285)</f>
@@ -33984,34 +34308,34 @@
         <v>0</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L285" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M285" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N285" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="P285" s="2" t="n">
-        <v>0</v>
+        <v>1021.5</v>
       </c>
       <c r="Q285" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R285" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S285" s="2" t="n">
@@ -34025,7 +34349,7 @@
       </c>
       <c r="V285" s="2" t="inlineStr">
         <is>
-          <t>Berdan</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="W285" s="2" t="inlineStr">
@@ -34040,7 +34364,7 @@
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
@@ -34050,12 +34374,12 @@
       </c>
       <c r="AA285" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-2</t>
+          <t>reg-us-i-2-2</t>
         </is>
       </c>
       <c r="AB285" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 defender)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC285" s="5" t="n"/>
@@ -34064,55 +34388,55 @@
       <c r="AF285" s="5" t="n"/>
       <c r="AG285" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-2-2-baxter.md; CA-J1P-2 Union receiving executor</t>
         </is>
       </c>
       <c r="AH285" s="5" t="inlineStr">
         <is>
-          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
+          <t>Baxter uninjured; Bates w x2, Wheelock captured/escaped, Lt. Thomas k in the streets; Coulter+11th Pa transferred out to 1st Bde</t>
         </is>
       </c>
       <c r="AI285" s="5" t="inlineStr">
         <is>
-          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
+          <t>No brigade primary (negative); B&amp;M-repro 1,452 (hop); division frame 'less than 2,500' (Robinson) CONFLICTS with the two-brigade B&amp;M sum 2,989 - both carried</t>
         </is>
       </c>
       <c r="AJ285" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
+          <t>[C 11:00] arrival; the two front-changes to the Oak Ridge crest (the pass-10 drawn wall bar = this line); [C ~17:00] the Emmitsburg-road line; [C Jul 2 10:00] relieved by Webb; the July 2-3 support ladder (six clocked moves); [C Jul 3 ~13:00] Cemetery Hill right-front under the cannonade ~2 h, then Hays's right</t>
         </is>
       </c>
       <c r="AK285" s="5" t="inlineStr">
         <is>
-          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
+          <t>[D] the relief hand-off ~15:00+ (Coulter's after-3, ammunition exhausted); the town retreat under fire; the clocked July 2-3 ladder</t>
         </is>
       </c>
       <c r="AL285" s="5" t="inlineStr">
         <is>
-          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
+          <t>THE IVERSON REPULSE RECEIVING RECORD: the deadly fire, the charge (88th Pa two flags + 97th NY one), the 12th Mass flank fire 'great influence upon its surrender'; Coulter 12:30 general-firing pin; division 'three flags and about 1,000 prisoners'; the Northrup conduct record</t>
         </is>
       </c>
       <c r="AM285" s="5" t="inlineStr">
         <is>
-          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
+          <t>Return p. 174 rows (not digit-re-read); division 'lost considerably more than half' of &lt;2,500 (primary); shape: the Oak Ridge window + the town capture spike; July 3 'considerable loss' skirmish clear (unquantified)</t>
         </is>
       </c>
       <c r="AN285" s="5" t="n"/>
       <c r="AO285" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 (July 1 grain; full arc T3)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>us-biddle</t>
+          <t>us-berdan</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
+          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -34131,10 +34455,10 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>460</v>
+        <v>1405</v>
       </c>
       <c r="G286" s="2" t="n">
-        <v>460</v>
+        <v>1405</v>
       </c>
       <c r="H286" s="3">
         <f>IF(F286=0,0,1-G286/F286)</f>
@@ -34171,11 +34495,11 @@
       </c>
       <c r="R286" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S286" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T286" s="2" t="n">
         <v>0</v>
@@ -34185,7 +34509,7 @@
       </c>
       <c r="V286" s="2" t="inlineStr">
         <is>
-          <t>Biddle</t>
+          <t>Berdan</t>
         </is>
       </c>
       <c r="W286" s="2" t="inlineStr">
@@ -34200,7 +34524,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
@@ -34210,12 +34534,12 @@
       </c>
       <c r="AA286" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-1</t>
+          <t>reg-us-iii-1-2</t>
         </is>
       </c>
       <c r="AB286" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 defender)</t>
         </is>
       </c>
       <c r="AC286" s="5" t="n"/>
@@ -34224,55 +34548,55 @@
       <c r="AF286" s="5" t="n"/>
       <c r="AG286" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
         </is>
       </c>
       <c r="AH286" s="5" t="inlineStr">
         <is>
-          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
+          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
         </is>
       </c>
       <c r="AI286" s="5" t="inlineStr">
         <is>
-          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale ; p11 back-extension: July 1 PRIMARY 1,287 in / 440 k&amp;w + 457 m / 390 left (dated July 2) - the day split lands; B&amp;M-repro 1,361 (hop)</t>
+          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
         </is>
       </c>
       <c r="AJ286" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
+          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
         </is>
       </c>
       <c r="AK286" s="5" t="inlineStr">
         <is>
-          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
+          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
         </is>
       </c>
       <c r="AL286" s="5" t="inlineStr">
         <is>
-          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
+          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
         </is>
       </c>
       <c r="AM286" s="5" t="inlineStr">
         <is>
-          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
+          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
         </is>
       </c>
       <c r="AN286" s="5" t="n"/>
       <c r="AO286" s="5" t="inlineStr">
         <is>
-          <t>T4 (July 1 grain; July 3 T3) - p11 upgrade</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>us-brewster</t>
+          <t>us-biddle</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
+          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -34291,10 +34615,10 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>1060</v>
+        <v>460</v>
       </c>
       <c r="G287" s="2" t="n">
-        <v>1060</v>
+        <v>460</v>
       </c>
       <c r="H287" s="3">
         <f>IF(F287=0,0,1-G287/F287)</f>
@@ -34331,11 +34655,11 @@
       </c>
       <c r="R287" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S287" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T287" s="2" t="n">
         <v>0</v>
@@ -34345,7 +34669,7 @@
       </c>
       <c r="V287" s="2" t="inlineStr">
         <is>
-          <t>Brewster</t>
+          <t>Biddle</t>
         </is>
       </c>
       <c r="W287" s="2" t="inlineStr">
@@ -34360,7 +34684,7 @@
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
@@ -34370,12 +34694,12 @@
       </c>
       <c r="AA287" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-2</t>
+          <t>reg-us-i-3-1</t>
         </is>
       </c>
       <c r="AB287" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC287" s="5" t="n"/>
@@ -34384,55 +34708,55 @@
       <c r="AF287" s="5" t="n"/>
       <c r="AG287" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
         </is>
       </c>
       <c r="AH287" s="5" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
+          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AI287" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale ; p11 back-extension: July 1 PRIMARY 1,287 in / 440 k&amp;w + 457 m / 390 left (dated July 2) - the day split lands; B&amp;M-repro 1,361 (hop)</t>
         </is>
       </c>
       <c r="AJ287" s="5" t="inlineStr">
         <is>
-          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
+          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
         </is>
       </c>
       <c r="AK287" s="5" t="inlineStr">
         <is>
-          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
+          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
         </is>
       </c>
       <c r="AL287" s="5" t="inlineStr">
         <is>
-          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
+          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AM287" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
+          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
         </is>
       </c>
       <c r="AN287" s="5" t="n"/>
       <c r="AO287" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 (July 1 grain; July 3 T3) - p11 upgrade</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>us-brooke</t>
+          <t>us-brewster</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
+          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -34451,10 +34775,10 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>460</v>
+        <v>1060</v>
       </c>
       <c r="G288" s="2" t="n">
-        <v>460</v>
+        <v>1060</v>
       </c>
       <c r="H288" s="3">
         <f>IF(F288=0,0,1-G288/F288)</f>
@@ -34491,7 +34815,7 @@
       </c>
       <c r="R288" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S288" s="2" t="n">
@@ -34505,7 +34829,7 @@
       </c>
       <c r="V288" s="2" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Brewster</t>
         </is>
       </c>
       <c r="W288" s="2" t="inlineStr">
@@ -34530,7 +34854,7 @@
       </c>
       <c r="AA288" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-4</t>
+          <t>reg-us-iii-2-2</t>
         </is>
       </c>
       <c r="AB288" s="5" t="inlineStr">
@@ -34544,37 +34868,37 @@
       <c r="AF288" s="5" t="n"/>
       <c r="AG288" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
         </is>
       </c>
       <c r="AH288" s="5" t="inlineStr">
         <is>
-          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
         </is>
       </c>
       <c r="AI288" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
         </is>
       </c>
       <c r="AJ288" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
         </is>
       </c>
       <c r="AK288" s="5" t="inlineStr">
         <is>
-          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
         </is>
       </c>
       <c r="AL288" s="5" t="inlineStr">
         <is>
-          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
         </is>
       </c>
       <c r="AM288" s="5" t="inlineStr">
         <is>
-          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
         </is>
       </c>
       <c r="AN288" s="5" t="n"/>
@@ -34587,12 +34911,12 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>us-burbank</t>
+          <t>us-brooke</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
+          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -34611,10 +34935,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="H289" s="3">
         <f>IF(F289=0,0,1-G289/F289)</f>
@@ -34665,7 +34989,7 @@
       </c>
       <c r="V289" s="2" t="inlineStr">
         <is>
-          <t>Burbank</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="W289" s="2" t="inlineStr">
@@ -34690,12 +35014,12 @@
       </c>
       <c r="AA289" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-2</t>
+          <t>reg-us-ii-1-4</t>
         </is>
       </c>
       <c r="AB289" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC289" s="5" t="n"/>
@@ -34704,37 +35028,37 @@
       <c r="AF289" s="5" t="n"/>
       <c r="AG289" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
         </is>
       </c>
       <c r="AH289" s="5" t="inlineStr">
         <is>
-          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
+          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
         </is>
       </c>
       <c r="AI289" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
+          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
         </is>
       </c>
       <c r="AJ289" s="5" t="inlineStr">
         <is>
-          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
+          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
         </is>
       </c>
       <c r="AK289" s="5" t="inlineStr">
         <is>
-          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
+          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
         </is>
       </c>
       <c r="AL289" s="5" t="inlineStr">
         <is>
-          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
+          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
         </is>
       </c>
       <c r="AM289" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
+          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
         </is>
       </c>
       <c r="AN289" s="5" t="n"/>
@@ -34747,12 +35071,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>us-burling</t>
+          <t>us-burbank</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
+          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -34771,10 +35095,10 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>850</v>
+        <v>505</v>
       </c>
       <c r="G290" s="2" t="n">
-        <v>850</v>
+        <v>505</v>
       </c>
       <c r="H290" s="3">
         <f>IF(F290=0,0,1-G290/F290)</f>
@@ -34811,7 +35135,7 @@
       </c>
       <c r="R290" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S290" s="2" t="n">
@@ -34825,7 +35149,7 @@
       </c>
       <c r="V290" s="2" t="inlineStr">
         <is>
-          <t>Burling</t>
+          <t>Burbank</t>
         </is>
       </c>
       <c r="W290" s="2" t="inlineStr">
@@ -34850,12 +35174,12 @@
       </c>
       <c r="AA290" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-3</t>
+          <t>reg-us-v-2-2</t>
         </is>
       </c>
       <c r="AB290" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 DISPERSED class)</t>
+          <t>authored-ok (July 2 single-window mover)</t>
         </is>
       </c>
       <c r="AC290" s="5" t="n"/>
@@ -34864,55 +35188,55 @@
       <c r="AF290" s="5" t="n"/>
       <c r="AG290" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
         </is>
       </c>
       <c r="AH290" s="5" t="inlineStr">
         <is>
-          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
+          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
         </is>
       </c>
       <c r="AI290" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
+          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
         </is>
       </c>
       <c r="AJ290" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
+          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
         </is>
       </c>
       <c r="AK290" s="5" t="inlineStr">
         <is>
-          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
+          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
         </is>
       </c>
       <c r="AL290" s="5" t="inlineStr">
         <is>
-          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
+          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
         </is>
       </c>
       <c r="AM290" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
+          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
         </is>
       </c>
       <c r="AN290" s="5" t="n"/>
       <c r="AO290" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (dispersed class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>us-candy</t>
+          <t>us-burling</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
+          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -34931,10 +35255,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="G291" s="2" t="n">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="H291" s="3">
         <f>IF(F291=0,0,1-G291/F291)</f>
@@ -34971,7 +35295,7 @@
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S291" s="2" t="n">
@@ -34985,7 +35309,7 @@
       </c>
       <c r="V291" s="2" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Burling</t>
         </is>
       </c>
       <c r="W291" s="2" t="inlineStr">
@@ -35010,12 +35334,12 @@
       </c>
       <c r="AA291" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-1</t>
+          <t>reg-us-iii-2-3</t>
         </is>
       </c>
       <c r="AB291" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 DISPERSED class)</t>
         </is>
       </c>
       <c r="AC291" s="5" t="n"/>
@@ -35024,55 +35348,55 @@
       <c r="AF291" s="5" t="n"/>
       <c r="AG291" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md; the Geary 5/5.45/6 a.m. ladder + rows landed pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
         </is>
       </c>
       <c r="AH291" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
+          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
         </is>
       </c>
       <c r="AI291" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
         </is>
       </c>
       <c r="AJ291" s="5" t="inlineStr">
         <is>
-          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
+          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
         </is>
       </c>
       <c r="AK291" s="5" t="inlineStr">
         <is>
-          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
+          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
         </is>
       </c>
       <c r="AL291" s="5" t="inlineStr">
         <is>
-          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
+          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
         </is>
       </c>
       <c r="AM291" s="5" t="inlineStr">
         <is>
-          <t>p. 184 rows (pass 10): 139 = 5 OH 18, 7 OH 18, 29 OH 38, 66 OH 17, 28 Pa 28, 147 Pa 20 (sum exact)</t>
+          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
         </is>
       </c>
       <c r="AN291" s="5" t="n"/>
       <c r="AO291" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc (dispersed class)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>us-carr</t>
+          <t>us-candy</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
+          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -35091,10 +35415,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="G292" s="2" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="H292" s="3">
         <f>IF(F292=0,0,1-G292/F292)</f>
@@ -35131,7 +35455,7 @@
       </c>
       <c r="R292" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S292" s="2" t="n">
@@ -35141,11 +35465,11 @@
         <v>0</v>
       </c>
       <c r="U292" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V292" s="2" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="W292" s="2" t="inlineStr">
@@ -35170,12 +35494,12 @@
       </c>
       <c r="AA292" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-1</t>
+          <t>reg-us-xii-2-1</t>
         </is>
       </c>
       <c r="AB292" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC292" s="5" t="n"/>
@@ -35184,55 +35508,55 @@
       <c r="AF292" s="5" t="n"/>
       <c r="AG292" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md; the Geary 5/5.45/6 a.m. ladder + rows landed pass 10</t>
         </is>
       </c>
       <c r="AH292" s="5" t="inlineStr">
         <is>
-          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
+          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
         </is>
       </c>
       <c r="AI292" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
+          <t>OPEN (no primary; no hop)</t>
         </is>
       </c>
       <c r="AJ292" s="5" t="inlineStr">
         <is>
-          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
+          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
         </is>
       </c>
       <c r="AK292" s="5" t="inlineStr">
         <is>
-          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
+          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
         </is>
       </c>
       <c r="AL292" s="5" t="inlineStr">
         <is>
-          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
+          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
         </is>
       </c>
       <c r="AM292" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
+          <t>p. 184 rows (pass 10): 139 = 5 OH 18, 7 OH 18, 29 OH 38, 66 OH 17, 28 Pa 28, 147 Pa 20 (sum exact)</t>
         </is>
       </c>
       <c r="AN292" s="5" t="n"/>
       <c r="AO292" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>us-carroll</t>
+          <t>us-carr</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
+          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -35251,10 +35575,10 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>640</v>
+        <v>925</v>
       </c>
       <c r="G293" s="2" t="n">
-        <v>640</v>
+        <v>925</v>
       </c>
       <c r="H293" s="3">
         <f>IF(F293=0,0,1-G293/F293)</f>
@@ -35291,7 +35615,7 @@
       </c>
       <c r="R293" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S293" s="2" t="n">
@@ -35305,7 +35629,7 @@
       </c>
       <c r="V293" s="2" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="W293" s="2" t="inlineStr">
@@ -35330,12 +35654,12 @@
       </c>
       <c r="AA293" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-1</t>
+          <t>reg-us-iii-2-1</t>
         </is>
       </c>
       <c r="AB293" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC293" s="5" t="n"/>
@@ -35344,37 +35668,37 @@
       <c r="AF293" s="5" t="n"/>
       <c r="AG293" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
         </is>
       </c>
       <c r="AH293" s="5" t="inlineStr">
         <is>
-          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
         </is>
       </c>
       <c r="AI293" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 640 (compilation, flagged)</t>
+          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AJ293" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
+          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
         </is>
       </c>
       <c r="AK293" s="5" t="inlineStr">
         <is>
-          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
         </is>
       </c>
       <c r="AL293" s="5" t="inlineStr">
         <is>
-          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
         </is>
       </c>
       <c r="AM293" s="5" t="inlineStr">
         <is>
-          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
         </is>
       </c>
       <c r="AN293" s="5" t="n"/>
@@ -35387,12 +35711,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>us-colgrove</t>
+          <t>us-carroll</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
+          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -35411,10 +35735,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>1170</v>
+        <v>640</v>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1170</v>
+        <v>640</v>
       </c>
       <c r="H294" s="3">
         <f>IF(F294=0,0,1-G294/F294)</f>
@@ -35461,11 +35785,11 @@
         <v>0</v>
       </c>
       <c r="U294" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V294" s="2" t="inlineStr">
         <is>
-          <t>Colgrove</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="W294" s="2" t="inlineStr">
@@ -35490,12 +35814,12 @@
       </c>
       <c r="AA294" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-3</t>
+          <t>reg-us-ii-3-1</t>
         </is>
       </c>
       <c r="AB294" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (the CA-J3M-3 executor)</t>
+          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
         </is>
       </c>
       <c r="AC294" s="5" t="n"/>
@@ -35504,37 +35828,37 @@
       <c r="AF294" s="5" t="n"/>
       <c r="AG294" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
         </is>
       </c>
       <c r="AH294" s="5" t="inlineStr">
         <is>
-          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
+          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
         </is>
       </c>
       <c r="AI294" s="5" t="inlineStr">
         <is>
-          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
+          <t>no primary; build 640 (compilation, flagged)</t>
         </is>
       </c>
       <c r="AJ294" s="5" t="inlineStr">
         <is>
-          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
+          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
         </is>
       </c>
       <c r="AK294" s="5" t="inlineStr">
         <is>
-          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
+          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
         </is>
       </c>
       <c r="AL294" s="5" t="inlineStr">
         <is>
-          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
+          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
         </is>
       </c>
       <c r="AM294" s="5" t="inlineStr">
         <is>
-          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
+          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
         </is>
       </c>
       <c r="AN294" s="5" t="n"/>
@@ -35547,12 +35871,12 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>us-coster</t>
+          <t>us-colgrove</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
+          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -35571,10 +35895,10 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>655</v>
+        <v>1170</v>
       </c>
       <c r="G295" s="2" t="n">
-        <v>655</v>
+        <v>1170</v>
       </c>
       <c r="H295" s="3">
         <f>IF(F295=0,0,1-G295/F295)</f>
@@ -35625,7 +35949,7 @@
       </c>
       <c r="V295" s="2" t="inlineStr">
         <is>
-          <t>Coster</t>
+          <t>Colgrove</t>
         </is>
       </c>
       <c r="W295" s="2" t="inlineStr">
@@ -35650,12 +35974,12 @@
       </c>
       <c r="AA295" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-1</t>
+          <t>reg-us-xii-1-3</t>
         </is>
       </c>
       <c r="AB295" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (the CA-J3M-3 executor)</t>
         </is>
       </c>
       <c r="AC295" s="5" t="n"/>
@@ -35664,55 +35988,55 @@
       <c r="AF295" s="5" t="n"/>
       <c r="AG295" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-2-1-coster.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
         </is>
       </c>
       <c r="AH295" s="5" t="inlineStr">
         <is>
-          <t>Coster; NO report at any brigade echelon (verified negative - the third XI no-report brigade)</t>
+          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
         </is>
       </c>
       <c r="AI295" s="5" t="inlineStr">
         <is>
-          <t>No primary (negative); B&amp;M-repro 1,156 (hop); the brickyard force = three regiments (73rd Pa stayed on the hill)</t>
+          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
         </is>
       </c>
       <c r="AJ295" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00 via von Steinwehr] Cemetery Hill NE supporting Wiedrich (+ the stone-church regiment); [D] the brickyard line NE of town; the fall-back with the brick-house stopper; the hill's NE front July 2-3</t>
+          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
         </is>
       </c>
       <c r="AK295" s="5" t="inlineStr">
         <is>
-          <t>[D] the through-town commitment to the brickyard; the covered fall-back</t>
+          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
         </is>
       </c>
       <c r="AL295" s="5" t="inlineStr">
         <is>
-          <t>The brickyard delaying action (division grain + BOTH-SIDED by Hays/Avery pass 10); the brick-house stopper</t>
+          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
         </is>
       </c>
       <c r="AM295" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183: 252/200/111/34 = 597 aggregate-exact (m column row-forced 313, noisy); the minutes-scale single-spike wreck second only to Iverson's</t>
+          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
         </is>
       </c>
       <c r="AN295" s="5" t="n"/>
       <c r="AO295" s="5" t="inlineStr">
         <is>
-          <t>T2 (honestly thin; the fight T3 via the attackers)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>us-coulter</t>
+          <t>us-coster</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
+          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -35731,10 +36055,10 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>510</v>
+        <v>655</v>
       </c>
       <c r="G296" s="2" t="n">
-        <v>510</v>
+        <v>655</v>
       </c>
       <c r="H296" s="3">
         <f>IF(F296=0,0,1-G296/F296)</f>
@@ -35744,34 +36068,34 @@
         <v>0</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L296" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M296" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N296" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="P296" s="2" t="n">
-        <v>1002.4</v>
+        <v>0</v>
       </c>
       <c r="Q296" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R296" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S296" s="2" t="n">
@@ -35785,7 +36109,7 @@
       </c>
       <c r="V296" s="2" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Coster</t>
         </is>
       </c>
       <c r="W296" s="2" t="inlineStr">
@@ -35800,7 +36124,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
@@ -35810,7 +36134,7 @@
       </c>
       <c r="AA296" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-1</t>
+          <t>reg-us-xi-2-1</t>
         </is>
       </c>
       <c r="AB296" s="5" t="inlineStr">
@@ -35824,55 +36148,55 @@
       <c r="AF296" s="5" t="n"/>
       <c r="AG296" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-2-1-paul.md; the ED-52 Union day-split exemplar</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-2-1-coster.md</t>
         </is>
       </c>
       <c r="AH296" s="5" t="inlineStr">
         <is>
-          <t>THE CASCADE: Paul severely w -&gt; Leonard w -&gt; Root w -&gt; Coulter (assigned on Cemetery Hill, w himself July 3) - five commanders; three Paul staff missing</t>
+          <t>Coster; NO report at any brigade echelon (verified negative - the third XI no-report brigade)</t>
         </is>
       </c>
       <c r="AI296" s="5" t="inlineStr">
         <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,537 (hop); 16th Me ~275 literature-class NOT hopped</t>
+          <t>No primary (negative); B&amp;M-repro 1,156 (hop); the brickyard force = three regiments (73rd Pa stayed on the hill)</t>
         </is>
       </c>
       <c r="AJ296" s="5" t="inlineStr">
         <is>
-          <t>[D] the seminary rail-barricade (Paul entrenching - the artifact Perrin stormed, both-sided); the Oak Ridge relief slots; the 16th Maine sacrifice hill; Cemetery Hill; the Baxter-parallel July 2-3 ladder</t>
+          <t>[C ~14:00 via von Steinwehr] Cemetery Hill NE supporting Wiedrich (+ the stone-church regiment); [D] the brickyard line NE of town; the fall-back with the brick-house stopper; the hill's NE front July 2-3</t>
         </is>
       </c>
       <c r="AK296" s="5" t="inlineStr">
         <is>
-          <t>[D ~15:00] the relief insertion (Coulter-clocked); the 16th Me detachment + three-stage collapse; the town retreat</t>
+          <t>[D] the through-town commitment to the brickyard; the covered fall-back</t>
         </is>
       </c>
       <c r="AL296" s="5" t="inlineStr">
         <is>
-          <t>The repeated-attacks repulse record (division grain); the 16th Maine hold-as-long-as-there-is-a-man order VERBATIM; July 2 dark gauntlet run; July 3 arrival at the repulse</t>
+          <t>The brickyard delaying action (division grain + BOTH-SIDED by Hays/Avery pass 10); the brick-house stopper</t>
         </is>
       </c>
       <c r="AM296" s="5" t="inlineStr">
         <is>
-          <t>THE DAY-SPLIT PRIMARY: 776/28/14/3 = 821 (Coulter's table, excl. 11th Pa Jul 1); 16th Me July 1 223 (162 m = the pocket)</t>
+          <t>Return p. 183: 252/200/111/34 = 597 aggregate-exact (m column row-forced 313, noisy); the minutes-scale single-spike wreck second only to Iverson's</t>
         </is>
       </c>
       <c r="AN296" s="5" t="n"/>
       <c r="AO296" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T2 (honestly thin; the fight T3 via the attackers)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>us-cutler</t>
+          <t>us-coulter</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
+          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -35891,10 +36215,10 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>1015</v>
+        <v>510</v>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1015</v>
+        <v>510</v>
       </c>
       <c r="H297" s="3">
         <f>IF(F297=0,0,1-G297/F297)</f>
@@ -35904,34 +36228,34 @@
         <v>0</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L297" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N297" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="P297" s="2" t="n">
-        <v>0</v>
+        <v>1002.4</v>
       </c>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R297" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S297" s="2" t="n">
@@ -35945,7 +36269,7 @@
       </c>
       <c r="V297" s="2" t="inlineStr">
         <is>
-          <t>Cutler</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="W297" s="2" t="inlineStr">
@@ -35960,7 +36284,7 @@
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr">
@@ -35970,12 +36294,12 @@
       </c>
       <c r="AA297" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-2</t>
+          <t>reg-us-i-2-1</t>
         </is>
       </c>
       <c r="AB297" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC297" s="5" t="n"/>
@@ -35984,55 +36308,55 @@
       <c r="AF297" s="5" t="n"/>
       <c r="AG297" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-1-2-cutler.md; three agreeing clocks (10/2/4)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-2-1-paul.md; the ED-52 Union day-split exemplar</t>
         </is>
       </c>
       <c r="AH297" s="5" t="inlineStr">
         <is>
-          <t>Cutler; Grover k, Miller w (the order-undelivered cause), Biddle (95 NY) w; 7th Ind detached in rear July 1</t>
+          <t>THE CASCADE: Paul severely w -&gt; Leonard w -&gt; Root w -&gt; Coulter (assigned on Cemetery Hill, w himself July 3) - five commanders; three Paul staff missing</t>
         </is>
       </c>
       <c r="AI297" s="5" t="inlineStr">
         <is>
-          <t>regiment primaries: 147 NY 380, 76 NY 375, 56 Pa 252</t>
+          <t>No brigade primary (negative); B&amp;M-repro 1,537 (hop); 16th Me ~275 literature-class NOT hopped</t>
         </is>
       </c>
       <c r="AJ297" s="5" t="inlineStr">
         <is>
-          <t>[B+drawn] the opening line across the RR (j1-03 CUTLER label + 147 NY bar + HALL 2'ME); the 2 o'clock changed front; the embankment retreat line; the 7th Ind Culp's Hill first-occupation pin; July 2-3 next to Greene</t>
+          <t>[D] the seminary rail-barricade (Paul entrenching - the artifact Perrin stormed, both-sided); the Oak Ridge relief slots; the 16th Maine sacrifice hill; Cemetery Hill; the Baxter-parallel July 2-3 ladder</t>
         </is>
       </c>
       <c r="AK297" s="5" t="inlineStr">
         <is>
-          <t>[D] leading-brigade march; the Wadsworth fall-back; the changed front; the perfect-steadiness embankment retreat</t>
+          <t>[D ~15:00] the relief insertion (Coulter-clocked); the 16th Me detachment + three-stage collapse; the town retreat</t>
         </is>
       </c>
       <c r="AL297" s="5" t="inlineStr">
         <is>
-          <t>first infantry engaged ('in action from 10 a.m. until 4 p.m.'); the 147th's stranded half-hour; the afternoon flank volley (a CSA regiment surrendered - Iverson-front both-sided); Hubbard's 18-man provost guard in the line</t>
+          <t>The repeated-attacks repulse record (division grain); the 16th Maine hold-as-long-as-there-is-a-man order VERBATIM; July 2 dark gauntlet run; July 3 arrival at the repulse</t>
         </is>
       </c>
       <c r="AM297" s="5" t="inlineStr">
         <is>
-          <t>return (p. 173) 1,002; RATE-CLASS primaries: 147 NY 207/380 in half an hour, 76 NY 169 in thirty minutes</t>
+          <t>THE DAY-SPLIT PRIMARY: 776/28/14/3 = 821 (Coulter's table, excl. 11th Pa Jul 1); 16th Me July 1 223 (162 m = the pocket)</t>
         </is>
       </c>
       <c r="AN297" s="5" t="n"/>
       <c r="AO297" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 (July 1 grain; full arc T2)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>us-dana</t>
+          <t>us-cutler</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
+          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -36051,10 +36375,10 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="H298" s="3">
         <f>IF(F298=0,0,1-G298/F298)</f>
@@ -36095,7 +36419,7 @@
         </is>
       </c>
       <c r="S298" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T298" s="2" t="n">
         <v>0</v>
@@ -36105,7 +36429,7 @@
       </c>
       <c r="V298" s="2" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Cutler</t>
         </is>
       </c>
       <c r="W298" s="2" t="inlineStr">
@@ -36120,7 +36444,7 @@
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
@@ -36130,12 +36454,12 @@
       </c>
       <c r="AA298" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-2</t>
+          <t>reg-us-i-1-2</t>
         </is>
       </c>
       <c r="AB298" s="5" t="inlineStr">
         <is>
-          <t>attested-static (sheet grain)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC298" s="5" t="n"/>
@@ -36144,37 +36468,37 @@
       <c r="AF298" s="5" t="n"/>
       <c r="AG298" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
+          <t>Dossier: reconstruction/dossiers/us-i-1-2-cutler.md; three agreeing clocks (10/2/4)</t>
         </is>
       </c>
       <c r="AH298" s="5" t="inlineStr">
         <is>
-          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
+          <t>Cutler; Grover k, Miller w (the order-undelivered cause), Biddle (95 NY) w; 7th Ind detached in rear July 1</t>
         </is>
       </c>
       <c r="AI298" s="5" t="inlineStr">
         <is>
-          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
+          <t>regiment primaries: 147 NY 380, 76 NY 375, 56 Pa 252</t>
         </is>
       </c>
       <c r="AJ298" s="5" t="inlineStr">
         <is>
-          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
+          <t>[B+drawn] the opening line across the RR (j1-03 CUTLER label + 147 NY bar + HALL 2'ME); the 2 o'clock changed front; the embankment retreat line; the 7th Ind Culp's Hill first-occupation pin; July 2-3 next to Greene</t>
         </is>
       </c>
       <c r="AK298" s="5" t="inlineStr">
         <is>
-          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
+          <t>[D] leading-brigade march; the Wadsworth fall-back; the changed front; the perfect-steadiness embankment retreat</t>
         </is>
       </c>
       <c r="AL298" s="5" t="inlineStr">
         <is>
-          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative) ; p11 back-extension: Roy Stone's report in full - the 11:00 / 12-1 Oak Hill enfilade / 1.30 grand-advance clock ladder (ED-69 candidate primary); the RR-cut episode; the cascade in action; 'nearly two-thirds... fell'</t>
+          <t>first infantry engaged ('in action from 10 a.m. until 4 p.m.'); the 147th's stranded half-hour; the afternoon flank volley (a CSA regiment surrendered - Iverson-front both-sided); Hubbard's 18-man provost guard in the line</t>
         </is>
       </c>
       <c r="AM298" s="5" t="inlineStr">
         <is>
-          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
+          <t>return (p. 173) 1,002; RATE-CLASS primaries: 147 NY 207/380 in half an hour, 76 NY 169 in thirty minutes</t>
         </is>
       </c>
       <c r="AN298" s="5" t="n"/>
@@ -36187,12 +36511,12 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>us-day</t>
+          <t>us-dana</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
+          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -36211,10 +36535,10 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>1170</v>
+        <v>465</v>
       </c>
       <c r="G299" s="2" t="n">
-        <v>1170</v>
+        <v>465</v>
       </c>
       <c r="H299" s="3">
         <f>IF(F299=0,0,1-G299/F299)</f>
@@ -36255,17 +36579,17 @@
         </is>
       </c>
       <c r="S299" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T299" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U299" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V299" s="2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="W299" s="2" t="inlineStr">
@@ -36280,7 +36604,7 @@
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
@@ -36290,12 +36614,12 @@
       </c>
       <c r="AA299" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-1</t>
+          <t>reg-us-i-3-2</t>
         </is>
       </c>
       <c r="AB299" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>attested-static (sheet grain)</t>
         </is>
       </c>
       <c r="AC299" s="5" t="n"/>
@@ -36304,55 +36628,55 @@
       <c r="AF299" s="5" t="n"/>
       <c r="AG299" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
         </is>
       </c>
       <c r="AH299" s="5" t="inlineStr">
         <is>
-          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
         </is>
       </c>
       <c r="AI299" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
         </is>
       </c>
       <c r="AJ299" s="5" t="inlineStr">
         <is>
-          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
         </is>
       </c>
       <c r="AK299" s="5" t="inlineStr">
         <is>
-          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
         </is>
       </c>
       <c r="AL299" s="5" t="inlineStr">
         <is>
-          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative) ; p11 back-extension: Roy Stone's report in full - the 11:00 / 12-1 Oak Hill enfilade / 1.30 grand-advance clock ladder (ED-69 candidate primary); the RR-cut episode; the cascade in action; 'nearly two-thirds... fell'</t>
         </is>
       </c>
       <c r="AM299" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
         </is>
       </c>
       <c r="AN299" s="5" t="n"/>
       <c r="AO299" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (thin - division-report class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>us-eustis</t>
+          <t>us-day</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
+          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -36371,10 +36695,10 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>1595</v>
+        <v>1170</v>
       </c>
       <c r="G300" s="2" t="n">
-        <v>1595</v>
+        <v>1170</v>
       </c>
       <c r="H300" s="3">
         <f>IF(F300=0,0,1-G300/F300)</f>
@@ -36411,7 +36735,7 @@
       </c>
       <c r="R300" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S300" s="2" t="n">
@@ -36421,11 +36745,11 @@
         <v>0</v>
       </c>
       <c r="U300" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V300" s="2" t="inlineStr">
         <is>
-          <t>Eustis</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="W300" s="2" t="inlineStr">
@@ -36450,33 +36774,69 @@
       </c>
       <c r="AA300" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-2</t>
-        </is>
-      </c>
-      <c r="AB300" s="5" t="n"/>
+          <t>reg-us-v-2-1</t>
+        </is>
+      </c>
+      <c r="AB300" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 single-window mover)</t>
+        </is>
+      </c>
       <c r="AC300" s="5" t="n"/>
       <c r="AD300" s="5" t="n"/>
       <c r="AE300" s="5" t="n"/>
       <c r="AF300" s="5" t="n"/>
-      <c r="AG300" s="5" t="n"/>
-      <c r="AH300" s="5" t="n"/>
-      <c r="AI300" s="5" t="n"/>
-      <c r="AJ300" s="5" t="n"/>
-      <c r="AK300" s="5" t="n"/>
-      <c r="AL300" s="5" t="n"/>
-      <c r="AM300" s="5" t="n"/>
+      <c r="AG300" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+        </is>
+      </c>
+      <c r="AH300" s="5" t="inlineStr">
+        <is>
+          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+        </is>
+      </c>
+      <c r="AI300" s="5" t="inlineStr">
+        <is>
+          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+        </is>
+      </c>
+      <c r="AJ300" s="5" t="inlineStr">
+        <is>
+          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+        </is>
+      </c>
+      <c r="AK300" s="5" t="inlineStr">
+        <is>
+          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+        </is>
+      </c>
+      <c r="AL300" s="5" t="inlineStr">
+        <is>
+          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+        </is>
+      </c>
+      <c r="AM300" s="5" t="inlineStr">
+        <is>
+          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+        </is>
+      </c>
       <c r="AN300" s="5" t="n"/>
-      <c r="AO300" s="5" t="n"/>
+      <c r="AO300" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc (thin - division-report class)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>us-fisher</t>
+          <t>us-eustis</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
+          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -36495,10 +36855,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="G301" s="2" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="H301" s="3">
         <f>IF(F301=0,0,1-G301/F301)</f>
@@ -36535,7 +36895,7 @@
       </c>
       <c r="R301" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S301" s="2" t="n">
@@ -36549,7 +36909,7 @@
       </c>
       <c r="V301" s="2" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Eustis</t>
         </is>
       </c>
       <c r="W301" s="2" t="inlineStr">
@@ -36574,7 +36934,7 @@
       </c>
       <c r="AA301" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-2</t>
+          <t>reg-us-vi-3-2</t>
         </is>
       </c>
       <c r="AB301" s="5" t="n"/>
@@ -36595,12 +36955,12 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>us-fraser</t>
+          <t>us-fisher</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
+          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -36619,10 +36979,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>615</v>
+        <v>1555</v>
       </c>
       <c r="G302" s="2" t="n">
-        <v>615</v>
+        <v>1555</v>
       </c>
       <c r="H302" s="3">
         <f>IF(F302=0,0,1-G302/F302)</f>
@@ -36673,7 +37033,7 @@
       </c>
       <c r="V302" s="2" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="W302" s="2" t="inlineStr">
@@ -36698,69 +37058,33 @@
       </c>
       <c r="AA302" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-3</t>
-        </is>
-      </c>
-      <c r="AB302" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-v-3-2</t>
+        </is>
+      </c>
+      <c r="AB302" s="5" t="n"/>
       <c r="AC302" s="5" t="n"/>
       <c r="AD302" s="5" t="n"/>
       <c r="AE302" s="5" t="n"/>
       <c r="AF302" s="5" t="n"/>
-      <c r="AG302" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
-        </is>
-      </c>
-      <c r="AH302" s="5" t="inlineStr">
-        <is>
-          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
-        </is>
-      </c>
-      <c r="AI302" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~975 compilation hop-flagged</t>
-        </is>
-      </c>
-      <c r="AJ302" s="5" t="inlineStr">
-        <is>
-          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
-        </is>
-      </c>
-      <c r="AK302" s="5" t="inlineStr">
-        <is>
-          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
-        </is>
-      </c>
-      <c r="AL302" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-3 crest fight 18:15-18:45</t>
-        </is>
-      </c>
-      <c r="AM302" s="5" t="inlineStr">
-        <is>
-          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
-        </is>
-      </c>
+      <c r="AG302" s="5" t="n"/>
+      <c r="AH302" s="5" t="n"/>
+      <c r="AI302" s="5" t="n"/>
+      <c r="AJ302" s="5" t="n"/>
+      <c r="AK302" s="5" t="n"/>
+      <c r="AL302" s="5" t="n"/>
+      <c r="AM302" s="5" t="n"/>
       <c r="AN302" s="5" t="n"/>
-      <c r="AO302" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO302" s="5" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>us-garrard</t>
+          <t>us-fraser</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
+          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -36779,10 +37103,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>1290</v>
+        <v>615</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>1290</v>
+        <v>615</v>
       </c>
       <c r="H303" s="3">
         <f>IF(F303=0,0,1-G303/F303)</f>
@@ -36833,7 +37157,7 @@
       </c>
       <c r="V303" s="2" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="W303" s="2" t="inlineStr">
@@ -36858,7 +37182,7 @@
       </c>
       <c r="AA303" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-3</t>
+          <t>reg-us-ii-1-3</t>
         </is>
       </c>
       <c r="AB303" s="5" t="inlineStr">
@@ -36872,37 +37196,37 @@
       <c r="AF303" s="5" t="n"/>
       <c r="AG303" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
         </is>
       </c>
       <c r="AH303" s="5" t="inlineStr">
         <is>
-          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
         </is>
       </c>
       <c r="AI303" s="5" t="inlineStr">
         <is>
-          <t>no brigade primary (open; compilation tier)</t>
+          <t>no primary (negative); ~975 compilation hop-flagged</t>
         </is>
       </c>
       <c r="AJ303" s="5" t="inlineStr">
         <is>
-          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
         </is>
       </c>
       <c r="AK303" s="5" t="inlineStr">
         <is>
-          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
         </is>
       </c>
       <c r="AL303" s="5" t="inlineStr">
         <is>
-          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+          <t>[D] wave-3 crest fight 18:15-18:45</t>
         </is>
       </c>
       <c r="AM303" s="5" t="inlineStr">
         <is>
-          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed ; p11 re-read: 140th NY digit-exact 1+25/5+84/18=133; brigade total row internally perfect 40/142/18=200; small rows off-by-one open (199 vs 200)</t>
+          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AN303" s="5" t="n"/>
@@ -36915,12 +37239,12 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>us-grant</t>
+          <t>us-garrard</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
+          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -36939,10 +37263,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>1830</v>
+        <v>1290</v>
       </c>
       <c r="G304" s="2" t="n">
-        <v>1830</v>
+        <v>1290</v>
       </c>
       <c r="H304" s="3">
         <f>IF(F304=0,0,1-G304/F304)</f>
@@ -36993,7 +37317,7 @@
       </c>
       <c r="V304" s="2" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="W304" s="2" t="inlineStr">
@@ -37018,33 +37342,69 @@
       </c>
       <c r="AA304" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-1</t>
-        </is>
-      </c>
-      <c r="AB304" s="5" t="n"/>
+          <t>reg-us-v-2-3</t>
+        </is>
+      </c>
+      <c r="AB304" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC304" s="5" t="n"/>
       <c r="AD304" s="5" t="n"/>
       <c r="AE304" s="5" t="n"/>
       <c r="AF304" s="5" t="n"/>
-      <c r="AG304" s="5" t="n"/>
-      <c r="AH304" s="5" t="n"/>
-      <c r="AI304" s="5" t="n"/>
-      <c r="AJ304" s="5" t="n"/>
-      <c r="AK304" s="5" t="n"/>
-      <c r="AL304" s="5" t="n"/>
-      <c r="AM304" s="5" t="n"/>
+      <c r="AG304" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+        </is>
+      </c>
+      <c r="AH304" s="5" t="inlineStr">
+        <is>
+          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+        </is>
+      </c>
+      <c r="AI304" s="5" t="inlineStr">
+        <is>
+          <t>no brigade primary (open; compilation tier)</t>
+        </is>
+      </c>
+      <c r="AJ304" s="5" t="inlineStr">
+        <is>
+          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+        </is>
+      </c>
+      <c r="AK304" s="5" t="inlineStr">
+        <is>
+          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+        </is>
+      </c>
+      <c r="AL304" s="5" t="inlineStr">
+        <is>
+          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+        </is>
+      </c>
+      <c r="AM304" s="5" t="inlineStr">
+        <is>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed ; p11 re-read: 140th NY digit-exact 1+25/5+84/18=133; brigade total row internally perfect 40/142/18=200; small rows off-by-one open (199 vs 200)</t>
+        </is>
+      </c>
       <c r="AN304" s="5" t="n"/>
-      <c r="AO304" s="5" t="n"/>
+      <c r="AO304" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>us-greene</t>
+          <t>us-grant</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
+          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -37063,10 +37423,10 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>1125</v>
+        <v>1830</v>
       </c>
       <c r="G305" s="2" t="n">
-        <v>1125</v>
+        <v>1830</v>
       </c>
       <c r="H305" s="3">
         <f>IF(F305=0,0,1-G305/F305)</f>
@@ -37117,7 +37477,7 @@
       </c>
       <c r="V305" s="2" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="W305" s="2" t="inlineStr">
@@ -37142,69 +37502,33 @@
       </c>
       <c r="AA305" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-3</t>
-        </is>
-      </c>
-      <c r="AB305" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-2-1</t>
+        </is>
+      </c>
+      <c r="AB305" s="5" t="n"/>
       <c r="AC305" s="5" t="n"/>
       <c r="AD305" s="5" t="n"/>
       <c r="AE305" s="5" t="n"/>
       <c r="AF305" s="5" t="n"/>
-      <c r="AG305" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
-        </is>
-      </c>
-      <c r="AH305" s="5" t="inlineStr">
-        <is>
-          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
-        </is>
-      </c>
-      <c r="AI305" s="5" t="inlineStr">
-        <is>
-          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
-        </is>
-      </c>
-      <c r="AJ305" s="5" t="inlineStr">
-        <is>
-          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
-        </is>
-      </c>
-      <c r="AK305" s="5" t="inlineStr">
-        <is>
-          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
-        </is>
-      </c>
-      <c r="AL305" s="5" t="inlineStr">
-        <is>
-          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
-        </is>
-      </c>
-      <c r="AM305" s="5" t="inlineStr">
-        <is>
-          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
-        </is>
-      </c>
+      <c r="AG305" s="5" t="n"/>
+      <c r="AH305" s="5" t="n"/>
+      <c r="AI305" s="5" t="n"/>
+      <c r="AJ305" s="5" t="n"/>
+      <c r="AK305" s="5" t="n"/>
+      <c r="AL305" s="5" t="n"/>
+      <c r="AM305" s="5" t="n"/>
       <c r="AN305" s="5" t="n"/>
-      <c r="AO305" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO305" s="5" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>us-harris</t>
+          <t>us-greene</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
+          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -37223,10 +37547,10 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>565</v>
+        <v>1125</v>
       </c>
       <c r="G306" s="2" t="n">
-        <v>565</v>
+        <v>1125</v>
       </c>
       <c r="H306" s="3">
         <f>IF(F306=0,0,1-G306/F306)</f>
@@ -37273,11 +37597,11 @@
         <v>0</v>
       </c>
       <c r="U306" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V306" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Greene</t>
         </is>
       </c>
       <c r="W306" s="2" t="inlineStr">
@@ -37302,12 +37626,12 @@
       </c>
       <c r="AA306" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-2</t>
+          <t>reg-us-xii-2-3</t>
         </is>
       </c>
       <c r="AB306" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (the breached base wall)</t>
+          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
         </is>
       </c>
       <c r="AC306" s="5" t="n"/>
@@ -37316,37 +37640,37 @@
       <c r="AF306" s="5" t="n"/>
       <c r="AG306" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged; July 1 knoll extension pass 10 (drawn crest bar 57 m from the Barlow statue; the Barlow-wounding pin in Ames's echelon record)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
         </is>
       </c>
       <c r="AH306" s="5" t="inlineStr">
         <is>
-          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4 ; p11: the structured Barlow-Gordon record added (contemporary layer adopted - the July 7 letter + Gordon's OR pin; the 1903 memoir NO status)</t>
+          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
         </is>
       </c>
       <c r="AI306" s="5" t="inlineStr">
         <is>
-          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
+          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
         </is>
       </c>
       <c r="AJ306" s="5" t="inlineStr">
         <is>
-          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
+          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
         </is>
       </c>
       <c r="AK306" s="5" t="inlineStr">
         <is>
-          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
+          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
         </is>
       </c>
       <c r="AL306" s="5" t="inlineStr">
         <is>
-          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
+          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
         </is>
       </c>
       <c r="AM306" s="5" t="inlineStr">
         <is>
-          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
+          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
         </is>
       </c>
       <c r="AN306" s="5" t="n"/>
@@ -37359,12 +37683,12 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>us-harrow</t>
+          <t>us-harris</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Harrow's Brigade</t>
+          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -37383,76 +37707,76 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>1410</v>
+        <v>565</v>
       </c>
       <c r="G307" s="2" t="n">
-        <v>630</v>
+        <v>565</v>
       </c>
       <c r="H307" s="3">
         <f>IF(F307=0,0,1-G307/F307)</f>
         <v/>
       </c>
       <c r="I307" s="2" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L307" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N307" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O307" s="2" t="n">
-        <v>121.7</v>
+        <v>0</v>
       </c>
       <c r="P307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q307" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V307" s="2" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="R307" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="S307" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T307" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U307" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V307" s="2" t="inlineStr">
-        <is>
-          <t>Harrow</t>
-        </is>
-      </c>
-      <c r="W307" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
@@ -37462,12 +37786,12 @@
       </c>
       <c r="AA307" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-2-1</t>
+          <t>reg-us-xi-1-2</t>
         </is>
       </c>
       <c r="AB307" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (crisis incline-right)</t>
+          <t>authored-ok (the breached base wall)</t>
         </is>
       </c>
       <c r="AC307" s="5" t="n"/>
@@ -37476,37 +37800,37 @@
       <c r="AF307" s="5" t="n"/>
       <c r="AG307" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged; July 1 knoll extension pass 10 (drawn crest bar 57 m from the Barlow statue; the Barlow-wounding pin in Ames's echelon record)</t>
         </is>
       </c>
       <c r="AH307" s="5" t="inlineStr">
         <is>
-          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
+          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4 ; p11: the structured Barlow-Gordon record added (contemporary layer adopted - the July 7 letter + Gordon's OR pin; the 1903 memoir NO status)</t>
         </is>
       </c>
       <c r="AI307" s="5" t="inlineStr">
         <is>
-          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
+          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
         </is>
       </c>
       <c r="AJ307" s="5" t="inlineStr">
         <is>
-          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
+          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
         </is>
       </c>
       <c r="AK307" s="5" t="inlineStr">
         <is>
-          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
+          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
         </is>
       </c>
       <c r="AL307" s="5" t="inlineStr">
         <is>
-          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
+          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
         </is>
       </c>
       <c r="AM307" s="5" t="inlineStr">
         <is>
-          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
+          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
         </is>
       </c>
       <c r="AN307" s="5" t="n"/>
@@ -37519,12 +37843,12 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>us-kane</t>
+          <t>us-harrow</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
+          <t>Harrow's Brigade</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -37543,42 +37867,42 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>600</v>
+        <v>1410</v>
       </c>
       <c r="G308" s="2" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="H308" s="3">
         <f>IF(F308=0,0,1-G308/F308)</f>
         <v/>
       </c>
       <c r="I308" s="2" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K308" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L308" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M308" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N308" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>0</v>
+        <v>121.7</v>
       </c>
       <c r="P308" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R308" s="2" t="inlineStr">
@@ -37587,17 +37911,17 @@
         </is>
       </c>
       <c r="S308" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T308" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U308" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V308" s="2" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="W308" s="2" t="inlineStr">
@@ -37607,12 +37931,12 @@
       </c>
       <c r="X308" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
@@ -37622,12 +37946,12 @@
       </c>
       <c r="AA308" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-2</t>
+          <t>reg-us-ii-2-1</t>
         </is>
       </c>
       <c r="AB308" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (crisis incline-right)</t>
         </is>
       </c>
       <c r="AC308" s="5" t="n"/>
@@ -37636,37 +37960,37 @@
       <c r="AF308" s="5" t="n"/>
       <c r="AG308" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder; the 9 a.m. relief clock landed pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-2-1-harrow.md; division-sum gap 3,580 vs 3,773 recorded; pass-5: July 2 evening counterattack leg both-sided (1st MN bracketed after CA-J2A-9, before sunset ED-31); 1st MN regiment-grain upgrade pass 6</t>
         </is>
       </c>
       <c r="AH308" s="5" t="inlineStr">
         <is>
-          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
+          <t>Harrow to division (Gibbon w) -&gt; Heath (19ME) took brigade; Ward (15MA)/Huston (82NY) mw Jul 2; Colvill/Adams/Downie (1MN) w</t>
         </is>
       </c>
       <c r="AI308" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY: 652 in action (Kane p. 848)</t>
+          <t>1,410 (build, hop); division primary 3,773 in / 1,657 lost (or-27-1-harrow)</t>
         </is>
       </c>
       <c r="AJ308" s="5" t="inlineStr">
         <is>
-          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
+          <t>[E] single-line axis x~4384, z 4560-4645: 19ME(4384,4644) 15MA(4384,4610) 1MN(4385,4567) 82NY(4385,4564); Rorty's guns inside the span (4412,4597)</t>
         </is>
       </c>
       <c r="AK308" s="5" t="inlineStr">
         <is>
-          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
+          <t>[C Jul 2] 15MA+82NY to Emmitsburg Rd + retire; [D] 1MN charge; [A vs CA-J3A-9] incline-right to the Copse [B: 2-5 min]; PASS-6: the 1st MN moment closed BOTH-SIDED at regiment grain (Coates primary + Wilcox p. 618 receiving side + j2-04 drawn pair; monument 232-of-330 ledger vs return 224, ED-52)</t>
         </is>
       </c>
       <c r="AL308" s="5" t="inlineStr">
         <is>
-          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
+          <t>[C +7] 'At 1 p.m....until nearly 3 p.m.' cannonade; enemy 'from the woods, 1,000 yards in front'; melee 'nearly an hour'; convergence-target statement (Hall's right/Webb's left)</t>
         </is>
       </c>
       <c r="AM308" s="5" t="inlineStr">
         <is>
-          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening); p. 184 rows (pass 10): 98 = 29 Pa 66, 109 Pa 10, 111 Pa 22 (sum exact)</t>
+          <t>722 two-day (148k/574w, report) vs 768 (tablet) - carried; Jul 2 pins Ward/Huston mw; Jul 3 Blinn mw</t>
         </is>
       </c>
       <c r="AN308" s="5" t="n"/>
@@ -37679,12 +38003,12 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>us-kelly</t>
+          <t>us-kane</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
+          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -37703,10 +38027,10 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="G309" s="2" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="H309" s="3">
         <f>IF(F309=0,0,1-G309/F309)</f>
@@ -37757,7 +38081,7 @@
       </c>
       <c r="V309" s="2" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="W309" s="2" t="inlineStr">
@@ -37782,12 +38106,12 @@
       </c>
       <c r="AA309" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-2</t>
+          <t>reg-us-xii-2-2</t>
         </is>
       </c>
       <c r="AB309" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC309" s="5" t="n"/>
@@ -37796,37 +38120,37 @@
       <c r="AF309" s="5" t="n"/>
       <c r="AG309" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder; the 9 a.m. relief clock landed pass 10</t>
         </is>
       </c>
       <c r="AH309" s="5" t="inlineStr">
         <is>
-          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
+          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
         </is>
       </c>
       <c r="AI309" s="5" t="inlineStr">
         <is>
-          <t>530 into action PRIMARY (Kelly)</t>
+          <t>PRIMARY: 652 in action (Kane p. 848)</t>
         </is>
       </c>
       <c r="AJ309" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
+          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
         </is>
       </c>
       <c r="AK309" s="5" t="inlineStr">
         <is>
-          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
+          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
         </is>
       </c>
       <c r="AL309" s="5" t="inlineStr">
         <is>
-          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
+          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
         </is>
       </c>
       <c r="AM309" s="5" t="inlineStr">
         <is>
-          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
+          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening); p. 184 rows (pass 10): 98 = 29 Pa 66, 109 Pa 10, 111 Pa 22 (sum exact)</t>
         </is>
       </c>
       <c r="AN309" s="5" t="n"/>
@@ -37839,12 +38163,12 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>us-krzyzanowski</t>
+          <t>us-kelly</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
+          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -37863,10 +38187,10 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>750</v>
+        <v>330</v>
       </c>
       <c r="G310" s="2" t="n">
-        <v>750</v>
+        <v>330</v>
       </c>
       <c r="H310" s="3">
         <f>IF(F310=0,0,1-G310/F310)</f>
@@ -37917,7 +38241,7 @@
       </c>
       <c r="V310" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="W310" s="2" t="inlineStr">
@@ -37942,12 +38266,12 @@
       </c>
       <c r="AA310" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-2</t>
+          <t>reg-us-ii-1-2</t>
         </is>
       </c>
       <c r="AB310" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC310" s="5" t="n"/>
@@ -37956,55 +38280,55 @@
       <c r="AF310" s="5" t="n"/>
       <c r="AG310" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-3-2-krzyzanowski.md; CA-J1P-3 receiving center</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
         </is>
       </c>
       <c r="AH310" s="5" t="inlineStr">
         <is>
-          <t>Krzyzanowski (no own report - verified negative); Col. J.S. Robinson (82nd OH) severely w; 26th WI Boebel w -&gt; Fuchs -&gt; Jacobs</t>
+          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
         </is>
       </c>
       <c r="AI310" s="5" t="inlineStr">
         <is>
-          <t>82nd OH PRIMARY 312 PFD (-&gt;220 Jul 11 bracket); no brigade primary; B&amp;M-repro 1,403 (hop)</t>
+          <t>530 into action PRIMARY (Kelly)</t>
         </is>
       </c>
       <c r="AJ310" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00 secondhand] arrival + the line north of town (82nd OH left, 26th WI right); [C ~16:00] the Cemetery Hill stone-fence rally; the cemetery-building position Jul 2-5</t>
+          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
         </is>
       </c>
       <c r="AK310" s="5" t="inlineStr">
         <is>
-          <t>[D] the forward commitment; the division-ordered fall-back through town; the ~16:00 rally</t>
+          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
         </is>
       </c>
       <c r="AL310" s="5" t="inlineStr">
         <is>
-          <t>The open-field stand vs Gordon/Doles converging (both-sided); the town gauntlet; July 2-3 attested-quiet (26th WI no-loss negative)</t>
+          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
         </is>
       </c>
       <c r="AM310" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183 digit-exact: 20/140/181/111/217 = 669; 82nd OH report=return EXACT 181; July 1 near-total</t>
+          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
         </is>
       </c>
       <c r="AN310" s="5" t="n"/>
       <c r="AO310" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>us-lockwood</t>
+          <t>us-krzyzanowski</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
+          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -38023,10 +38347,10 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>1650</v>
+        <v>750</v>
       </c>
       <c r="G311" s="2" t="n">
-        <v>1650</v>
+        <v>750</v>
       </c>
       <c r="H311" s="3">
         <f>IF(F311=0,0,1-G311/F311)</f>
@@ -38077,7 +38401,7 @@
       </c>
       <c r="V311" s="2" t="inlineStr">
         <is>
-          <t>Lockwood</t>
+          <t>Krzyżanowski</t>
         </is>
       </c>
       <c r="W311" s="2" t="inlineStr">
@@ -38102,12 +38426,12 @@
       </c>
       <c r="AA311" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-2</t>
+          <t>reg-us-xi-3-2</t>
         </is>
       </c>
       <c r="AB311" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AC311" s="5" t="n"/>
@@ -38116,55 +38440,55 @@
       <c r="AF311" s="5" t="n"/>
       <c r="AG311" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md; Maulsby pp. 805-807 in full + p. 184 rows (174) pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-2-krzyzanowski.md; CA-J1P-3 receiving center</t>
         </is>
       </c>
       <c r="AH311" s="5" t="inlineStr">
         <is>
-          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
+          <t>Krzyzanowski (no own report - verified negative); Col. J.S. Robinson (82nd OH) severely w; 26th WI Boebel w -&gt; Fuchs -&gt; Jacobs</t>
         </is>
       </c>
       <c r="AI311" s="5" t="inlineStr">
         <is>
-          <t>GEARY PRIMARY (pass 10): '1,700 strong' reported 7.30 a.m. July 3</t>
+          <t>82nd OH PRIMARY 312 PFD (-&gt;220 Jul 11 bracket); no brigade primary; B&amp;M-repro 1,403 (hop)</t>
         </is>
       </c>
       <c r="AJ311" s="5" t="inlineStr">
         <is>
-          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
+          <t>[C ~14:00 secondhand] arrival + the line north of town (82nd OH left, 26th WI right); [C ~16:00] the Cemetery Hill stone-fence rally; the cemetery-building position Jul 2-5</t>
         </is>
       </c>
       <c r="AK311" s="5" t="inlineStr">
         <is>
-          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
+          <t>[D] the forward commitment; the division-ordered fall-back through town; the ~16:00 rally</t>
         </is>
       </c>
       <c r="AL311" s="5" t="inlineStr">
         <is>
-          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
+          <t>The open-field stand vs Gordon/Doles converging (both-sided); the town gauntlet; July 2-3 attested-quiet (26th WI no-loss negative)</t>
         </is>
       </c>
       <c r="AM311" s="5" t="inlineStr">
         <is>
-          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
+          <t>Return p. 183 digit-exact: 20/140/181/111/217 = 669; 82nd OH report=return EXACT 181; July 1 near-total</t>
         </is>
       </c>
       <c r="AN311" s="5" t="n"/>
       <c r="AO311" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T3 (July 1 grain; full arc T2)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>us-madill</t>
+          <t>us-lockwood</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
+          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -38183,10 +38507,10 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>775</v>
+        <v>1650</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>775</v>
+        <v>1650</v>
       </c>
       <c r="H312" s="3">
         <f>IF(F312=0,0,1-G312/F312)</f>
@@ -38223,7 +38547,7 @@
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S312" s="2" t="n">
@@ -38237,7 +38561,7 @@
       </c>
       <c r="V312" s="2" t="inlineStr">
         <is>
-          <t>Madill</t>
+          <t>Lockwood</t>
         </is>
       </c>
       <c r="W312" s="2" t="inlineStr">
@@ -38262,12 +38586,12 @@
       </c>
       <c r="AA312" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-1</t>
+          <t>reg-us-xii-1-2</t>
         </is>
       </c>
       <c r="AB312" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 static-then-forced-back)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC312" s="5" t="n"/>
@@ -38276,55 +38600,55 @@
       <c r="AF312" s="5" t="n"/>
       <c r="AG312" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md; Maulsby pp. 805-807 in full + p. 184 rows (174) pass 10</t>
         </is>
       </c>
       <c r="AH312" s="5" t="inlineStr">
         <is>
-          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
+          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
         </is>
       </c>
       <c r="AI312" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
+          <t>GEARY PRIMARY (pass 10): '1,700 strong' reported 7.30 a.m. July 3</t>
         </is>
       </c>
       <c r="AJ312" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
+          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
         </is>
       </c>
       <c r="AK312" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
+          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
         </is>
       </c>
       <c r="AL312" s="5" t="inlineStr">
         <is>
-          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
+          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
         </is>
       </c>
       <c r="AM312" s="5" t="inlineStr">
         <is>
-          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
+          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
         </is>
       </c>
       <c r="AN312" s="5" t="n"/>
       <c r="AO312" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>us-mccandless</t>
+          <t>us-madill</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
+          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -38343,10 +38667,10 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>1095</v>
+        <v>775</v>
       </c>
       <c r="G313" s="2" t="n">
-        <v>1095</v>
+        <v>775</v>
       </c>
       <c r="H313" s="3">
         <f>IF(F313=0,0,1-G313/F313)</f>
@@ -38383,7 +38707,7 @@
       </c>
       <c r="R313" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S313" s="2" t="n">
@@ -38397,7 +38721,7 @@
       </c>
       <c r="V313" s="2" t="inlineStr">
         <is>
-          <t>McCandless</t>
+          <t>Madill</t>
         </is>
       </c>
       <c r="W313" s="2" t="inlineStr">
@@ -38422,12 +38746,12 @@
       </c>
       <c r="AA313" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-1</t>
+          <t>reg-us-iii-1-1</t>
         </is>
       </c>
       <c r="AB313" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
+          <t>authored-ok (July 2 static-then-forced-back)</t>
         </is>
       </c>
       <c r="AC313" s="5" t="n"/>
@@ -38436,37 +38760,37 @@
       <c r="AF313" s="5" t="n"/>
       <c r="AG313" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
         </is>
       </c>
       <c r="AH313" s="5" t="inlineStr">
         <is>
-          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
+          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
         </is>
       </c>
       <c r="AI313" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
+          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
         </is>
       </c>
       <c r="AJ313" s="5" t="inlineStr">
         <is>
-          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
+          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
         </is>
       </c>
       <c r="AK313" s="5" t="inlineStr">
         <is>
-          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
+          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
         </is>
       </c>
       <c r="AL313" s="5" t="inlineStr">
         <is>
-          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
+          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
         </is>
       </c>
       <c r="AM313" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
+          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
         </is>
       </c>
       <c r="AN313" s="5" t="n"/>
@@ -38479,12 +38803,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>us-mcdougall</t>
+          <t>us-mccandless</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
+          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -38503,10 +38827,10 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>1755</v>
+        <v>1095</v>
       </c>
       <c r="G314" s="2" t="n">
-        <v>1755</v>
+        <v>1095</v>
       </c>
       <c r="H314" s="3">
         <f>IF(F314=0,0,1-G314/F314)</f>
@@ -38557,7 +38881,7 @@
       </c>
       <c r="V314" s="2" t="inlineStr">
         <is>
-          <t>McDougall</t>
+          <t>McCandless</t>
         </is>
       </c>
       <c r="W314" s="2" t="inlineStr">
@@ -38582,12 +38906,12 @@
       </c>
       <c r="AA314" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-1</t>
+          <t>reg-us-v-3-1</t>
         </is>
       </c>
       <c r="AB314" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
         </is>
       </c>
       <c r="AC314" s="5" t="n"/>
@@ -38596,55 +38920,55 @@
       <c r="AF314" s="5" t="n"/>
       <c r="AG314" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
+          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
         </is>
       </c>
       <c r="AH314" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
+          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
         </is>
       </c>
       <c r="AI314" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AJ314" s="5" t="inlineStr">
         <is>
-          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
+          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
         </is>
       </c>
       <c r="AK314" s="5" t="inlineStr">
         <is>
-          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
+          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
         </is>
       </c>
       <c r="AL314" s="5" t="inlineStr">
         <is>
-          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
+          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
         </is>
       </c>
       <c r="AM314" s="5" t="inlineStr">
         <is>
-          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
+          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
         </is>
       </c>
       <c r="AN314" s="5" t="n"/>
       <c r="AO314" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>us-mckeen</t>
+          <t>us-mcdougall</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
+          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -38663,10 +38987,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>520</v>
+        <v>1755</v>
       </c>
       <c r="G315" s="2" t="n">
-        <v>520</v>
+        <v>1755</v>
       </c>
       <c r="H315" s="3">
         <f>IF(F315=0,0,1-G315/F315)</f>
@@ -38717,7 +39041,7 @@
       </c>
       <c r="V315" s="2" t="inlineStr">
         <is>
-          <t>McKeen</t>
+          <t>McDougall</t>
         </is>
       </c>
       <c r="W315" s="2" t="inlineStr">
@@ -38742,12 +39066,12 @@
       </c>
       <c r="AA315" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-1</t>
+          <t>reg-us-xii-1-1</t>
         </is>
       </c>
       <c r="AB315" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AC315" s="5" t="n"/>
@@ -38756,55 +39080,55 @@
       <c r="AF315" s="5" t="n"/>
       <c r="AG315" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
         </is>
       </c>
       <c r="AH315" s="5" t="inlineStr">
         <is>
-          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
         </is>
       </c>
       <c r="AI315" s="5" t="inlineStr">
         <is>
-          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+          <t>OPEN (no primary; no hop)</t>
         </is>
       </c>
       <c r="AJ315" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
         </is>
       </c>
       <c r="AK315" s="5" t="inlineStr">
         <is>
-          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
         </is>
       </c>
       <c r="AL315" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
         </is>
       </c>
       <c r="AM315" s="5" t="inlineStr">
         <is>
-          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
         </is>
       </c>
       <c r="AN315" s="5" t="n"/>
       <c r="AO315" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>us-meredith</t>
+          <t>us-mckeen</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
+          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -38823,10 +39147,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="H316" s="3">
         <f>IF(F316=0,0,1-G316/F316)</f>
@@ -38877,7 +39201,7 @@
       </c>
       <c r="V316" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>McKeen</t>
         </is>
       </c>
       <c r="W316" s="2" t="inlineStr">
@@ -38902,12 +39226,12 @@
       </c>
       <c r="AA316" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-1</t>
+          <t>reg-us-ii-1-1</t>
         </is>
       </c>
       <c r="AB316" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC316" s="5" t="n"/>
@@ -38916,37 +39240,37 @@
       <c r="AF316" s="5" t="n"/>
       <c r="AG316" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-1-1-meredith.md; the 1,000-vs-75 Archer-capture-count conflict carried</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
         </is>
       </c>
       <c r="AH316" s="5" t="inlineStr">
         <is>
-          <t>Meredith (w July 1) -&gt; Robinson (7th Wis, pinned in Dawes); 6th Wis + brigade guard detached as corps reserve; Morrow w&amp;c; 24th Mich officer ledger 8k/14w</t>
+          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
         </is>
       </c>
       <c r="AI316" s="5" t="inlineStr">
         <is>
-          <t>24th Mich PRIMARY 496; brigade aggregate open ; p11 sweep: B&amp;M-repro 1,829 brigade hop beside the 24th Mich 496 primary</t>
+          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
         </is>
       </c>
       <c r="AJ316" s="5" t="inlineStr">
         <is>
-          <t>[B+drawn] the Willoughby Run charge ground (j1-03 bars; Archer-captured marker on the axis); McPherson's woods line (order 19-24-7 curved); j1-13 seminary barricade drawn; Culp's Hill evening</t>
+          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
         </is>
       </c>
       <c r="AK316" s="5" t="inlineStr">
         <is>
-          <t>[D] the unloaded double-quick charge; the east-bank withdrawal; step-by-step to the barricade; through town to Culp's Hill</t>
+          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
         </is>
       </c>
       <c r="AL316" s="5" t="inlineStr">
         <is>
-          <t>the Archer capture (Maloney/2nd Wis, both-sided w/ Shepard's ~75-pocket); the 6th Wis railroad-cut charge (Blair's 2nd Miss surrender, flag, 2nd Me gun recaptured); the woods defense vs the 26th NC (facing color ledgers)</t>
+          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
         </is>
       </c>
       <c r="AM316" s="5" t="inlineStr">
         <is>
-          <t>return (p. 173) 1,153 (the heaviest Union brigade) - 19 Ind 210, 24 Mich 363, 2 Wis 233, 6 Wis 168, 7 Wis 178; single-day concentration, three episodes; 24th Mich nine flag carriers / four bearers k</t>
+          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
         </is>
       </c>
       <c r="AN316" s="5" t="n"/>
@@ -38959,12 +39283,12 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>us-neill</t>
+          <t>us-meredith</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
+          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -38983,10 +39307,10 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>1775</v>
+        <v>730</v>
       </c>
       <c r="G317" s="2" t="n">
-        <v>1775</v>
+        <v>730</v>
       </c>
       <c r="H317" s="3">
         <f>IF(F317=0,0,1-G317/F317)</f>
@@ -39027,7 +39351,7 @@
         </is>
       </c>
       <c r="S317" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T317" s="2" t="n">
         <v>0</v>
@@ -39037,7 +39361,7 @@
       </c>
       <c r="V317" s="2" t="inlineStr">
         <is>
-          <t>Neill</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="W317" s="2" t="inlineStr">
@@ -39052,7 +39376,7 @@
       </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z317" s="2" t="inlineStr">
@@ -39062,33 +39386,69 @@
       </c>
       <c r="AA317" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-2</t>
-        </is>
-      </c>
-      <c r="AB317" s="5" t="n"/>
+          <t>reg-us-i-1-1</t>
+        </is>
+      </c>
+      <c r="AB317" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC317" s="5" t="n"/>
       <c r="AD317" s="5" t="n"/>
       <c r="AE317" s="5" t="n"/>
       <c r="AF317" s="5" t="n"/>
-      <c r="AG317" s="5" t="n"/>
-      <c r="AH317" s="5" t="n"/>
-      <c r="AI317" s="5" t="n"/>
-      <c r="AJ317" s="5" t="n"/>
-      <c r="AK317" s="5" t="n"/>
-      <c r="AL317" s="5" t="n"/>
-      <c r="AM317" s="5" t="n"/>
+      <c r="AG317" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-i-1-1-meredith.md; the 1,000-vs-75 Archer-capture-count conflict carried</t>
+        </is>
+      </c>
+      <c r="AH317" s="5" t="inlineStr">
+        <is>
+          <t>Meredith (w July 1) -&gt; Robinson (7th Wis, pinned in Dawes); 6th Wis + brigade guard detached as corps reserve; Morrow w&amp;c; 24th Mich officer ledger 8k/14w</t>
+        </is>
+      </c>
+      <c r="AI317" s="5" t="inlineStr">
+        <is>
+          <t>24th Mich PRIMARY 496; brigade aggregate open ; p11 sweep: B&amp;M-repro 1,829 brigade hop beside the 24th Mich 496 primary</t>
+        </is>
+      </c>
+      <c r="AJ317" s="5" t="inlineStr">
+        <is>
+          <t>[B+drawn] the Willoughby Run charge ground (j1-03 bars; Archer-captured marker on the axis); McPherson's woods line (order 19-24-7 curved); j1-13 seminary barricade drawn; Culp's Hill evening</t>
+        </is>
+      </c>
+      <c r="AK317" s="5" t="inlineStr">
+        <is>
+          <t>[D] the unloaded double-quick charge; the east-bank withdrawal; step-by-step to the barricade; through town to Culp's Hill</t>
+        </is>
+      </c>
+      <c r="AL317" s="5" t="inlineStr">
+        <is>
+          <t>the Archer capture (Maloney/2nd Wis, both-sided w/ Shepard's ~75-pocket); the 6th Wis railroad-cut charge (Blair's 2nd Miss surrender, flag, 2nd Me gun recaptured); the woods defense vs the 26th NC (facing color ledgers)</t>
+        </is>
+      </c>
+      <c r="AM317" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 173) 1,153 (the heaviest Union brigade) - 19 Ind 210, 24 Mich 363, 2 Wis 233, 6 Wis 168, 7 Wis 178; single-day concentration, three episodes; 24th Mich nine flag carriers / four bearers k</t>
+        </is>
+      </c>
       <c r="AN317" s="5" t="n"/>
-      <c r="AO317" s="5" t="n"/>
+      <c r="AO317" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>us-nevin</t>
+          <t>us-neill</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
+          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -39107,10 +39467,10 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>1370</v>
+        <v>1775</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>1370</v>
+        <v>1775</v>
       </c>
       <c r="H318" s="3">
         <f>IF(F318=0,0,1-G318/F318)</f>
@@ -39151,7 +39511,7 @@
         </is>
       </c>
       <c r="S318" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T318" s="2" t="n">
         <v>0</v>
@@ -39161,7 +39521,7 @@
       </c>
       <c r="V318" s="2" t="inlineStr">
         <is>
-          <t>Nevin</t>
+          <t>Neill</t>
         </is>
       </c>
       <c r="W318" s="2" t="inlineStr">
@@ -39176,7 +39536,7 @@
       </c>
       <c r="Y318" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z318" s="2" t="inlineStr">
@@ -39186,69 +39546,33 @@
       </c>
       <c r="AA318" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-3</t>
-        </is>
-      </c>
-      <c r="AB318" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 W5 executor)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-2-2</t>
+        </is>
+      </c>
+      <c r="AB318" s="5" t="n"/>
       <c r="AC318" s="5" t="n"/>
       <c r="AD318" s="5" t="n"/>
       <c r="AE318" s="5" t="n"/>
       <c r="AF318" s="5" t="n"/>
-      <c r="AG318" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
-        </is>
-      </c>
-      <c r="AH318" s="5" t="inlineStr">
-        <is>
-          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
-        </is>
-      </c>
-      <c r="AI318" s="5" t="inlineStr">
-        <is>
-          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
-        </is>
-      </c>
-      <c r="AJ318" s="5" t="inlineStr">
-        <is>
-          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
-        </is>
-      </c>
-      <c r="AK318" s="5" t="inlineStr">
-        <is>
-          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
-        </is>
-      </c>
-      <c r="AL318" s="5" t="inlineStr">
-        <is>
-          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
-        </is>
-      </c>
-      <c r="AM318" s="5" t="inlineStr">
-        <is>
-          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
-        </is>
-      </c>
+      <c r="AG318" s="5" t="n"/>
+      <c r="AH318" s="5" t="n"/>
+      <c r="AI318" s="5" t="n"/>
+      <c r="AJ318" s="5" t="n"/>
+      <c r="AK318" s="5" t="n"/>
+      <c r="AL318" s="5" t="n"/>
+      <c r="AM318" s="5" t="n"/>
       <c r="AN318" s="5" t="n"/>
-      <c r="AO318" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO318" s="5" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>us-rice</t>
+          <t>us-nevin</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
+          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -39267,10 +39591,10 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>985</v>
+        <v>1370</v>
       </c>
       <c r="G319" s="2" t="n">
-        <v>985</v>
+        <v>1370</v>
       </c>
       <c r="H319" s="3">
         <f>IF(F319=0,0,1-G319/F319)</f>
@@ -39321,7 +39645,7 @@
       </c>
       <c r="V319" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Nevin</t>
         </is>
       </c>
       <c r="W319" s="2" t="inlineStr">
@@ -39346,12 +39670,12 @@
       </c>
       <c r="AA319" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-3</t>
+          <t>reg-us-vi-3-3</t>
         </is>
       </c>
       <c r="AB319" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+          <t>authored-ok (July 2 W5 executor)</t>
         </is>
       </c>
       <c r="AC319" s="5" t="n"/>
@@ -39360,37 +39684,37 @@
       <c r="AF319" s="5" t="n"/>
       <c r="AG319" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
         </is>
       </c>
       <c r="AH319" s="5" t="inlineStr">
         <is>
-          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
         </is>
       </c>
       <c r="AI319" s="5" t="inlineStr">
         <is>
-          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
         </is>
       </c>
       <c r="AJ319" s="5" t="inlineStr">
         <is>
-          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
         </is>
       </c>
       <c r="AK319" s="5" t="inlineStr">
         <is>
-          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
         </is>
       </c>
       <c r="AL319" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
         </is>
       </c>
       <c r="AM319" s="5" t="inlineStr">
         <is>
-          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
         </is>
       </c>
       <c r="AN319" s="5" t="n"/>
@@ -39403,12 +39727,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>us-russell</t>
+          <t>us-rice</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
+          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -39427,10 +39751,10 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>1480</v>
+        <v>985</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>1480</v>
+        <v>985</v>
       </c>
       <c r="H320" s="3">
         <f>IF(F320=0,0,1-G320/F320)</f>
@@ -39481,7 +39805,7 @@
       </c>
       <c r="V320" s="2" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="W320" s="2" t="inlineStr">
@@ -39506,33 +39830,69 @@
       </c>
       <c r="AA320" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-3</t>
-        </is>
-      </c>
-      <c r="AB320" s="5" t="n"/>
+          <t>reg-us-v-1-3</t>
+        </is>
+      </c>
+      <c r="AB320" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+        </is>
+      </c>
       <c r="AC320" s="5" t="n"/>
       <c r="AD320" s="5" t="n"/>
       <c r="AE320" s="5" t="n"/>
       <c r="AF320" s="5" t="n"/>
-      <c r="AG320" s="5" t="n"/>
-      <c r="AH320" s="5" t="n"/>
-      <c r="AI320" s="5" t="n"/>
-      <c r="AJ320" s="5" t="n"/>
-      <c r="AK320" s="5" t="n"/>
-      <c r="AL320" s="5" t="n"/>
-      <c r="AM320" s="5" t="n"/>
+      <c r="AG320" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+        </is>
+      </c>
+      <c r="AH320" s="5" t="inlineStr">
+        <is>
+          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+        </is>
+      </c>
+      <c r="AI320" s="5" t="inlineStr">
+        <is>
+          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+        </is>
+      </c>
+      <c r="AJ320" s="5" t="inlineStr">
+        <is>
+          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+        </is>
+      </c>
+      <c r="AK320" s="5" t="inlineStr">
+        <is>
+          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+        </is>
+      </c>
+      <c r="AL320" s="5" t="inlineStr">
+        <is>
+          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+        </is>
+      </c>
+      <c r="AM320" s="5" t="inlineStr">
+        <is>
+          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+        </is>
+      </c>
       <c r="AN320" s="5" t="n"/>
-      <c r="AO320" s="5" t="n"/>
+      <c r="AO320" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>us-shaler</t>
+          <t>us-russell</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
+          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -39551,10 +39911,10 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>1770</v>
+        <v>1480</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>1770</v>
+        <v>1480</v>
       </c>
       <c r="H321" s="3">
         <f>IF(F321=0,0,1-G321/F321)</f>
@@ -39564,34 +39924,34 @@
         <v>0</v>
       </c>
       <c r="J321" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K321" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L321" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M321" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N321" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="P321" s="2" t="n">
-        <v>1210.8</v>
+        <v>0</v>
       </c>
       <c r="Q321" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R321" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S321" s="2" t="n">
@@ -39605,7 +39965,7 @@
       </c>
       <c r="V321" s="2" t="inlineStr">
         <is>
-          <t>Shaler</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="W321" s="2" t="inlineStr">
@@ -39615,12 +39975,12 @@
       </c>
       <c r="X321" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y321" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z321" s="2" t="inlineStr">
@@ -39630,7 +39990,7 @@
       </c>
       <c r="AA321" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-1</t>
+          <t>reg-us-vi-1-3</t>
         </is>
       </c>
       <c r="AB321" s="5" t="n"/>
@@ -39651,12 +40011,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>us-sherrill</t>
+          <t>us-shaler</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Sherrill's Brigade (Willard's)</t>
+          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -39675,61 +40035,61 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>1510</v>
+        <v>1770</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>800</v>
+        <v>1770</v>
       </c>
       <c r="H322" s="3">
         <f>IF(F322=0,0,1-G322/F322)</f>
         <v/>
       </c>
       <c r="I322" s="2" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K322" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L322" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M322" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N322" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>70.2</v>
+        <v>1210.8</v>
       </c>
       <c r="P322" s="2" t="n">
-        <v>70.2</v>
+        <v>1210.8</v>
       </c>
       <c r="Q322" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="R322" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="S322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U322" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T322" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U322" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="V322" s="2" t="inlineStr">
         <is>
-          <t>Sherrill</t>
+          <t>Shaler</t>
         </is>
       </c>
       <c r="W322" s="2" t="inlineStr">
@@ -39744,7 +40104,7 @@
       </c>
       <c r="Y322" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="Z322" s="2" t="inlineStr">
@@ -39754,69 +40114,33 @@
       </c>
       <c r="AA322" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-3</t>
-        </is>
-      </c>
-      <c r="AB322" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (one in-window leg)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-3-1</t>
+        </is>
+      </c>
+      <c r="AB322" s="5" t="n"/>
       <c r="AC322" s="5" t="n"/>
       <c r="AD322" s="5" t="n"/>
       <c r="AE322" s="5" t="n"/>
       <c r="AF322" s="5" t="n"/>
-      <c r="AG322" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
-        </is>
-      </c>
-      <c r="AH322" s="5" t="inlineStr">
-        <is>
-          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
-        </is>
-      </c>
-      <c r="AI322" s="5" t="inlineStr">
-        <is>
-          <t>1,510 (build compilation, hop flagged)</t>
-        </is>
-      </c>
-      <c r="AJ322" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
-        </is>
-      </c>
-      <c r="AK322" s="5" t="inlineStr">
-        <is>
-          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
-        </is>
-      </c>
-      <c r="AL322" s="5" t="inlineStr">
-        <is>
-          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
-        </is>
-      </c>
-      <c r="AM322" s="5" t="inlineStr">
-        <is>
-          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
-        </is>
-      </c>
+      <c r="AG322" s="5" t="n"/>
+      <c r="AH322" s="5" t="n"/>
+      <c r="AI322" s="5" t="n"/>
+      <c r="AJ322" s="5" t="n"/>
+      <c r="AK322" s="5" t="n"/>
+      <c r="AL322" s="5" t="n"/>
+      <c r="AM322" s="5" t="n"/>
       <c r="AN322" s="5" t="n"/>
-      <c r="AO322" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AO322" s="5" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>us-smith</t>
+          <t>us-sherrill</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
+          <t>Sherrill's Brigade (Willard's)</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -39835,38 +40159,38 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>1290</v>
+        <v>1510</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>1290</v>
+        <v>800</v>
       </c>
       <c r="H323" s="3">
         <f>IF(F323=0,0,1-G323/F323)</f>
         <v/>
       </c>
       <c r="I323" s="2" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K323" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L323" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M323" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N323" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="P323" s="2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="Q323" s="2" t="inlineStr">
         <is>
@@ -39879,17 +40203,17 @@
         </is>
       </c>
       <c r="S323" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T323" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U323" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V323" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Sherrill</t>
         </is>
       </c>
       <c r="W323" s="2" t="inlineStr">
@@ -39899,12 +40223,12 @@
       </c>
       <c r="X323" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y323" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z323" s="2" t="inlineStr">
@@ -39914,33 +40238,69 @@
       </c>
       <c r="AA323" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-2</t>
-        </is>
-      </c>
-      <c r="AB323" s="5" t="n"/>
+          <t>reg-us-ii-3-3</t>
+        </is>
+      </c>
+      <c r="AB323" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (one in-window leg)</t>
+        </is>
+      </c>
       <c r="AC323" s="5" t="n"/>
       <c r="AD323" s="5" t="n"/>
       <c r="AE323" s="5" t="n"/>
       <c r="AF323" s="5" t="n"/>
-      <c r="AG323" s="5" t="n"/>
-      <c r="AH323" s="5" t="n"/>
-      <c r="AI323" s="5" t="n"/>
-      <c r="AJ323" s="5" t="n"/>
-      <c r="AK323" s="5" t="n"/>
-      <c r="AL323" s="5" t="n"/>
-      <c r="AM323" s="5" t="n"/>
+      <c r="AG323" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
+        </is>
+      </c>
+      <c r="AH323" s="5" t="inlineStr">
+        <is>
+          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
+        </is>
+      </c>
+      <c r="AI323" s="5" t="inlineStr">
+        <is>
+          <t>1,510 (build compilation, hop flagged)</t>
+        </is>
+      </c>
+      <c r="AJ323" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
+        </is>
+      </c>
+      <c r="AK323" s="5" t="inlineStr">
+        <is>
+          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
+        </is>
+      </c>
+      <c r="AL323" s="5" t="inlineStr">
+        <is>
+          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
+        </is>
+      </c>
+      <c r="AM323" s="5" t="inlineStr">
+        <is>
+          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
+        </is>
+      </c>
       <c r="AN323" s="5" t="n"/>
-      <c r="AO323" s="5" t="n"/>
+      <c r="AO323" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>us-smyth</t>
+          <t>us-smith</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Smyth's Brigade</t>
+          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -39959,32 +40319,32 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>825</v>
+        <v>1290</v>
       </c>
       <c r="H324" s="3">
         <f>IF(F324=0,0,1-G324/F324)</f>
         <v/>
       </c>
       <c r="I324" s="2" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K324" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L324" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N324" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O324" s="2" t="n">
         <v>0</v>
@@ -40003,17 +40363,17 @@
         </is>
       </c>
       <c r="S324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U324" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V324" s="2" t="inlineStr">
         <is>
-          <t>Smyth</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="W324" s="2" t="inlineStr">
@@ -40023,12 +40383,12 @@
       </c>
       <c r="X324" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Y324" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Z324" s="2" t="inlineStr">
@@ -40038,69 +40398,33 @@
       </c>
       <c r="AA324" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-2</t>
-        </is>
-      </c>
-      <c r="AB324" s="5" t="inlineStr">
-        <is>
-          <t>attested-static (July 2-4 wall line)</t>
-        </is>
-      </c>
+          <t>reg-us-xi-2-2</t>
+        </is>
+      </c>
+      <c r="AB324" s="5" t="n"/>
       <c r="AC324" s="5" t="n"/>
       <c r="AD324" s="5" t="n"/>
       <c r="AE324" s="5" t="n"/>
       <c r="AF324" s="5" t="n"/>
-      <c r="AG324" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
-        </is>
-      </c>
-      <c r="AH324" s="5" t="inlineStr">
-        <is>
-          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
-        </is>
-      </c>
-      <c r="AI324" s="5" t="inlineStr">
-        <is>
-          <t>1,190 (build compilation, hop flagged; no primary)</t>
-        </is>
-      </c>
-      <c r="AJ324" s="5" t="inlineStr">
-        <is>
-          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
-        </is>
-      </c>
-      <c r="AK324" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
-        </is>
-      </c>
-      <c r="AL324" s="5" t="inlineStr">
-        <is>
-          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
-        </is>
-      </c>
-      <c r="AM324" s="5" t="inlineStr">
-        <is>
-          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
-        </is>
-      </c>
+      <c r="AG324" s="5" t="n"/>
+      <c r="AH324" s="5" t="n"/>
+      <c r="AI324" s="5" t="n"/>
+      <c r="AJ324" s="5" t="n"/>
+      <c r="AK324" s="5" t="n"/>
+      <c r="AL324" s="5" t="n"/>
+      <c r="AM324" s="5" t="n"/>
       <c r="AN324" s="5" t="n"/>
-      <c r="AO324" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AO324" s="5" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>us-sweitzer</t>
+          <t>us-smyth</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
+          <t>Smyth's Brigade</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -40119,32 +40443,32 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>995</v>
+        <v>1190</v>
       </c>
       <c r="G325" s="2" t="n">
-        <v>995</v>
+        <v>825</v>
       </c>
       <c r="H325" s="3">
         <f>IF(F325=0,0,1-G325/F325)</f>
         <v/>
       </c>
       <c r="I325" s="2" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K325" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L325" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M325" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N325" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O325" s="2" t="n">
         <v>0</v>
@@ -40163,17 +40487,17 @@
         </is>
       </c>
       <c r="S325" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T325" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U325" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V325" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer</t>
+          <t>Smyth</t>
         </is>
       </c>
       <c r="W325" s="2" t="inlineStr">
@@ -40183,12 +40507,12 @@
       </c>
       <c r="X325" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y325" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z325" s="2" t="inlineStr">
@@ -40198,12 +40522,12 @@
       </c>
       <c r="AA325" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-2</t>
+          <t>reg-us-ii-3-2</t>
         </is>
       </c>
       <c r="AB325" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 twice-committed)</t>
+          <t>attested-static (July 2-4 wall line)</t>
         </is>
       </c>
       <c r="AC325" s="5" t="n"/>
@@ -40212,55 +40536,55 @@
       <c r="AF325" s="5" t="n"/>
       <c r="AG325" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
         </is>
       </c>
       <c r="AH325" s="5" t="inlineStr">
         <is>
-          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
+          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
         </is>
       </c>
       <c r="AI325" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
+          <t>1,190 (build compilation, hop flagged; no primary)</t>
         </is>
       </c>
       <c r="AJ325" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
+          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
         </is>
       </c>
       <c r="AK325" s="5" t="inlineStr">
         <is>
-          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
+          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
         </is>
       </c>
       <c r="AL325" s="5" t="inlineStr">
         <is>
-          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
+          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
         </is>
       </c>
       <c r="AM325" s="5" t="inlineStr">
         <is>
-          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
+          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
         </is>
       </c>
       <c r="AN325" s="5" t="n"/>
       <c r="AO325" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>us-tilton</t>
+          <t>us-sweitzer</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
+          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -40279,10 +40603,10 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>530</v>
+        <v>995</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>530</v>
+        <v>995</v>
       </c>
       <c r="H326" s="3">
         <f>IF(F326=0,0,1-G326/F326)</f>
@@ -40333,7 +40657,7 @@
       </c>
       <c r="V326" s="2" t="inlineStr">
         <is>
-          <t>Tilton</t>
+          <t>Sweitzer</t>
         </is>
       </c>
       <c r="W326" s="2" t="inlineStr">
@@ -40358,12 +40682,12 @@
       </c>
       <c r="AA326" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-1</t>
+          <t>reg-us-v-1-2</t>
         </is>
       </c>
       <c r="AB326" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 twice-committed)</t>
         </is>
       </c>
       <c r="AC326" s="5" t="n"/>
@@ -40372,37 +40696,37 @@
       <c r="AF326" s="5" t="n"/>
       <c r="AG326" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
         </is>
       </c>
       <c r="AH326" s="5" t="inlineStr">
         <is>
-          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
         </is>
       </c>
       <c r="AI326" s="5" t="inlineStr">
         <is>
-          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
         </is>
       </c>
       <c r="AJ326" s="5" t="inlineStr">
         <is>
-          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
         </is>
       </c>
       <c r="AK326" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
         </is>
       </c>
       <c r="AL326" s="5" t="inlineStr">
         <is>
-          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
         </is>
       </c>
       <c r="AM326" s="5" t="inlineStr">
         <is>
-          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AN326" s="5" t="n"/>
@@ -40415,12 +40739,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>us-torbert</t>
+          <t>us-tilton</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
+          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -40439,10 +40763,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>1320</v>
+        <v>530</v>
       </c>
       <c r="G327" s="2" t="n">
-        <v>1320</v>
+        <v>530</v>
       </c>
       <c r="H327" s="3">
         <f>IF(F327=0,0,1-G327/F327)</f>
@@ -40493,7 +40817,7 @@
       </c>
       <c r="V327" s="2" t="inlineStr">
         <is>
-          <t>Torbert</t>
+          <t>Tilton</t>
         </is>
       </c>
       <c r="W327" s="2" t="inlineStr">
@@ -40518,33 +40842,69 @@
       </c>
       <c r="AA327" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-1</t>
-        </is>
-      </c>
-      <c r="AB327" s="5" t="n"/>
+          <t>reg-us-v-1-1</t>
+        </is>
+      </c>
+      <c r="AB327" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (July 2 mover)</t>
+        </is>
+      </c>
       <c r="AC327" s="5" t="n"/>
       <c r="AD327" s="5" t="n"/>
       <c r="AE327" s="5" t="n"/>
       <c r="AF327" s="5" t="n"/>
-      <c r="AG327" s="5" t="n"/>
-      <c r="AH327" s="5" t="n"/>
-      <c r="AI327" s="5" t="n"/>
-      <c r="AJ327" s="5" t="n"/>
-      <c r="AK327" s="5" t="n"/>
-      <c r="AL327" s="5" t="n"/>
-      <c r="AM327" s="5" t="n"/>
+      <c r="AG327" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+        </is>
+      </c>
+      <c r="AH327" s="5" t="inlineStr">
+        <is>
+          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+        </is>
+      </c>
+      <c r="AI327" s="5" t="inlineStr">
+        <is>
+          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+        </is>
+      </c>
+      <c r="AJ327" s="5" t="inlineStr">
+        <is>
+          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+        </is>
+      </c>
+      <c r="AK327" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+        </is>
+      </c>
+      <c r="AL327" s="5" t="inlineStr">
+        <is>
+          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+        </is>
+      </c>
+      <c r="AM327" s="5" t="inlineStr">
+        <is>
+          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+        </is>
+      </c>
       <c r="AN327" s="5" t="n"/>
-      <c r="AO327" s="5" t="n"/>
+      <c r="AO327" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>us-detrobriand</t>
+          <t>us-torbert</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
+          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -40563,10 +40923,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>895</v>
+        <v>1320</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>895</v>
+        <v>1320</v>
       </c>
       <c r="H328" s="3">
         <f>IF(F328=0,0,1-G328/F328)</f>
@@ -40603,7 +40963,7 @@
       </c>
       <c r="R328" s="2" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>line</t>
         </is>
       </c>
       <c r="S328" s="2" t="n">
@@ -40617,7 +40977,7 @@
       </c>
       <c r="V328" s="2" t="inlineStr">
         <is>
-          <t>Trobriand</t>
+          <t>Torbert</t>
         </is>
       </c>
       <c r="W328" s="2" t="inlineStr">
@@ -40642,69 +41002,33 @@
       </c>
       <c r="AA328" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-3</t>
-        </is>
-      </c>
-      <c r="AB328" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (July 2 mover)</t>
-        </is>
-      </c>
+          <t>reg-us-vi-1-1</t>
+        </is>
+      </c>
+      <c r="AB328" s="5" t="n"/>
       <c r="AC328" s="5" t="n"/>
       <c r="AD328" s="5" t="n"/>
       <c r="AE328" s="5" t="n"/>
       <c r="AF328" s="5" t="n"/>
-      <c r="AG328" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
-        </is>
-      </c>
-      <c r="AH328" s="5" t="inlineStr">
-        <is>
-          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
-        </is>
-      </c>
-      <c r="AI328" s="5" t="inlineStr">
-        <is>
-          <t>no primary (negative); ~1,387 compilation hop-flagged ; p11: the 1,387 hop CONFIRMED at the sweep source</t>
-        </is>
-      </c>
-      <c r="AJ328" s="5" t="inlineStr">
-        <is>
-          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
-        </is>
-      </c>
-      <c r="AK328" s="5" t="inlineStr">
-        <is>
-          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
-        </is>
-      </c>
-      <c r="AL328" s="5" t="inlineStr">
-        <is>
-          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances) ; p11 clock re-read: 'About 2 p. m.' line-of-battle formation = the tablet's 2-3 P.M. (report=tablet pair; profile upgraded)</t>
-        </is>
-      </c>
-      <c r="AM328" s="5" t="inlineStr">
-        <is>
-          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
-        </is>
-      </c>
+      <c r="AG328" s="5" t="n"/>
+      <c r="AH328" s="5" t="n"/>
+      <c r="AI328" s="5" t="n"/>
+      <c r="AJ328" s="5" t="n"/>
+      <c r="AK328" s="5" t="n"/>
+      <c r="AL328" s="5" t="n"/>
+      <c r="AM328" s="5" t="n"/>
       <c r="AN328" s="5" t="n"/>
-      <c r="AO328" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AO328" s="5" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>us-vonamsberg</t>
+          <t>us-detrobriand</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -40723,10 +41047,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="G329" s="2" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="H329" s="3">
         <f>IF(F329=0,0,1-G329/F329)</f>
@@ -40763,7 +41087,7 @@
       </c>
       <c r="R329" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="S329" s="2" t="n">
@@ -40777,7 +41101,7 @@
       </c>
       <c r="V329" s="2" t="inlineStr">
         <is>
-          <t>Amsberg</t>
+          <t>Trobriand</t>
         </is>
       </c>
       <c r="W329" s="2" t="inlineStr">
@@ -40802,12 +41126,12 @@
       </c>
       <c r="AA329" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-1</t>
+          <t>reg-us-iii-1-3</t>
         </is>
       </c>
       <c r="AB329" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AC329" s="5" t="n"/>
@@ -40816,55 +41140,55 @@
       <c r="AF329" s="5" t="n"/>
       <c r="AG329" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-3-1-schimmelfennig.md; Dobke 1:30 feeds ED-69</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
         </is>
       </c>
       <c r="AH329" s="5" t="inlineStr">
         <is>
-          <t>THE CASCADE UP: Howard-&gt;field, Schurz-&gt;corps, Schimmelfennig-&gt;division (cut off in town Jul 1-4), von Amsberg-&gt;brigade at commitment</t>
+          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
         </is>
       </c>
       <c r="AI329" s="5" t="inlineStr">
         <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,670 (hop); 45th NY one-third-assembled fraction; Schurz 'hardly over 6,000' division frame</t>
+          <t>no primary (negative); ~1,387 compilation hop-flagged ; p11: the 1,387 hop CONFIRMED at the sweep source</t>
         </is>
       </c>
       <c r="AJ329" s="5" t="inlineStr">
         <is>
-          <t>[C 11:00-11:30] the I-Corps-right deploy (45th NY skirmish line, Dilger rear, 61st OH right); the open-field line under Oak Hill fire; [D ~16:00] the seminary cover halt; the town maze; Cemetery Hill stone fence</t>
+          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
         </is>
       </c>
       <c r="AK329" s="5" t="inlineStr">
         <is>
-          <t>[C] double-quick through town to deploy; the 16:00 retreat + THE ALLEY-TRAP town leg (~100 escaped); the July 2 night mile to the Culp's stone wall</t>
+          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
         </is>
       </c>
       <c r="AL329" s="5" t="inlineStr">
         <is>
-          <t>[C 13:30 early-lean] the flank fire + surrender event (the O'Neal/Iverson front from the XI side); the 157th NY vs Doles episode both-sided; the cross-corps retreat-cover order</t>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances) ; p11 clock re-read: 'About 2 p. m.' line-of-battle formation = the tablet's 2-3 P.M. (report=tablet pair; profile upgraded)</t>
         </is>
       </c>
       <c r="AM329" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183 digit-exact: 112/224/307/54/110 = 807 (rows sum); missing 453 = the town pockets</t>
+          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
         </is>
       </c>
       <c r="AN329" s="5" t="n"/>
       <c r="AO329" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>us-vongilsa</t>
+          <t>us-vonamsberg</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -40883,10 +41207,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>605</v>
+        <v>875</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>605</v>
+        <v>875</v>
       </c>
       <c r="H330" s="3">
         <f>IF(F330=0,0,1-G330/F330)</f>
@@ -40937,7 +41261,7 @@
       </c>
       <c r="V330" s="2" t="inlineStr">
         <is>
-          <t>Gilsa</t>
+          <t>Amsberg</t>
         </is>
       </c>
       <c r="W330" s="2" t="inlineStr">
@@ -40962,7 +41286,7 @@
       </c>
       <c r="AA330" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-1</t>
+          <t>reg-us-xi-3-1</t>
         </is>
       </c>
       <c r="AB330" s="5" t="inlineStr">
@@ -40976,48 +41300,208 @@
       <c r="AF330" s="5" t="n"/>
       <c r="AG330" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-1-1-vongilsa.md; the which-brigade-broke-first Schurz-vs-Ames conflict carried</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-1-schimmelfennig.md; Dobke 1:30 feeds ED-69</t>
         </is>
       </c>
       <c r="AH330" s="5" t="inlineStr">
         <is>
-          <t>von Gilsa; NO brigade report (verified negative); 41st NY absent July 1 (arrived ~10 p.m.)</t>
+          <t>THE CASCADE UP: Howard-&gt;field, Schurz-&gt;corps, Schimmelfennig-&gt;division (cut off in town Jul 1-4), von Amsberg-&gt;brigade at commitment</t>
         </is>
       </c>
       <c r="AI330" s="5" t="inlineStr">
         <is>
-          <t>OPEN; three-regiment knoll line (structural) ; p11 sweep: B&amp;M-repro 1,118 (hop)</t>
+          <t>No brigade primary (negative); B&amp;M-repro 1,670 (hop); 45th NY one-third-assembled fraction; Schurz 'hardly over 6,000' division frame</t>
         </is>
       </c>
       <c r="AJ330" s="5" t="inlineStr">
         <is>
-          <t>[D+drawn] the knoll north face under the Gordon line; the ECH marker = July 2-3 semantics; no located July 1 brigade marker (negative)</t>
+          <t>[C 11:00-11:30] the I-Corps-right deploy (45th NY skirmish line, Dilger rear, 61st OH right); the open-field line under Oak Hill fire; [D ~16:00] the seminary cover halt; the town maze; Cemetery Hill stone fence</t>
         </is>
       </c>
       <c r="AK330" s="5" t="inlineStr">
         <is>
-          <t>[D ~15:00-15:30 bracket] Barlow's forward tilt; the break under enfilade + frontal charge; through town</t>
+          <t>[C] double-quick through town to deploy; the 16:00 retreat + THE ALLEY-TRAP town leg (~100 escaped); the July 2 night mile to the Culp's stone wall</t>
         </is>
       </c>
       <c r="AL330" s="5" t="inlineStr">
         <is>
-          <t>the receiving side of the 50-paces fight (attested by the attacker); the corps' capture-mass retreat</t>
+          <t>[C 13:30 early-lean] the flank fire + surrender event (the O'Neal/Iverson front from the XI side); the 157th NY vs Doles episode both-sided; the cross-corps retreat-cover order</t>
         </is>
       </c>
       <c r="AM330" s="5" t="inlineStr">
         <is>
-          <t>return (p. 182) 527 - 41 NY 75 (July 2-3 only - structural day-split anchor), 54 NY 102, 68 NY 138, 153 Pa 211</t>
+          <t>Return p. 183 digit-exact: 112/224/307/54/110 = 807 (rows sum); missing 453 = the town pockets</t>
         </is>
       </c>
       <c r="AN330" s="5" t="n"/>
       <c r="AO330" s="5" t="inlineStr">
         <is>
+          <t>T3 (July 1 grain; full arc T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>us-vongilsa</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="H331" s="3">
+        <f>IF(F331=0,0,1-G331/F331)</f>
+        <v/>
+      </c>
+      <c r="I331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V331" s="2" t="inlineStr">
+        <is>
+          <t>Gilsa</t>
+        </is>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-1-1</t>
+        </is>
+      </c>
+      <c r="AB331" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
+      <c r="AC331" s="5" t="n"/>
+      <c r="AD331" s="5" t="n"/>
+      <c r="AE331" s="5" t="n"/>
+      <c r="AF331" s="5" t="n"/>
+      <c r="AG331" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-1-vongilsa.md; the which-brigade-broke-first Schurz-vs-Ames conflict carried</t>
+        </is>
+      </c>
+      <c r="AH331" s="5" t="inlineStr">
+        <is>
+          <t>von Gilsa; NO brigade report (verified negative); 41st NY absent July 1 (arrived ~10 p.m.)</t>
+        </is>
+      </c>
+      <c r="AI331" s="5" t="inlineStr">
+        <is>
+          <t>OPEN; three-regiment knoll line (structural) ; p11 sweep: B&amp;M-repro 1,118 (hop)</t>
+        </is>
+      </c>
+      <c r="AJ331" s="5" t="inlineStr">
+        <is>
+          <t>[D+drawn] the knoll north face under the Gordon line; the ECH marker = July 2-3 semantics; no located July 1 brigade marker (negative)</t>
+        </is>
+      </c>
+      <c r="AK331" s="5" t="inlineStr">
+        <is>
+          <t>[D ~15:00-15:30 bracket] Barlow's forward tilt; the break under enfilade + frontal charge; through town</t>
+        </is>
+      </c>
+      <c r="AL331" s="5" t="inlineStr">
+        <is>
+          <t>the receiving side of the 50-paces fight (attested by the attacker); the corps' capture-mass retreat</t>
+        </is>
+      </c>
+      <c r="AM331" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 182) 527 - 41 NY 75 (July 2-3 only - structural day-split anchor), 54 NY 102, 68 NY 138, 153 Pa 211</t>
+        </is>
+      </c>
+      <c r="AN331" s="5" t="n"/>
+      <c r="AO331" s="5" t="inlineStr">
+        <is>
           <t>T2 (honestly thin)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO330"/>
+  <autoFilter ref="A1:AO331"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -7321,20 +7321,56 @@
           <t>reg-csa-1c-bn-henry</t>
         </is>
       </c>
-      <c r="AB74" s="5" t="n"/>
+      <c r="AB74" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC74" s="5" t="n"/>
       <c r="AD74" s="5" t="n"/>
       <c r="AE74" s="5" t="n"/>
       <c r="AF74" s="5" t="n"/>
-      <c r="AG74" s="5" t="n"/>
-      <c r="AH74" s="5" t="n"/>
-      <c r="AI74" s="5" t="n"/>
-      <c r="AJ74" s="5" t="n"/>
-      <c r="AK74" s="5" t="n"/>
-      <c r="AL74" s="5" t="n"/>
-      <c r="AM74" s="5" t="n"/>
+      <c r="AG74" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-1c-bn-henry.md; closes the First Corps battalion arc's one gap (pass-12 triage)</t>
+        </is>
+      </c>
+      <c r="AH74" s="5" t="inlineStr">
+        <is>
+          <t>Maj. Mathis W. Henry; 4 batteries (Latham/Branch, Bachman/German, Garden/Palmetto, Reilly/Rowan); own report fetch-verified (No. 463, pp. 427-428)</t>
+        </is>
+      </c>
+      <c r="AI74" s="5" t="inlineStr">
+        <is>
+          <t>OPEN — no personnel total in report or tablet</t>
+        </is>
+      </c>
+      <c r="AJ74" s="5" t="inlineStr">
+        <is>
+          <t>[C report-primary] July 2 pm, 2 of 4 batteries (Reilly/Latham) engaged 'on the right of our line'; July 3 whole battalion; July-2/3 SCF-adjacent fire</t>
+        </is>
+      </c>
+      <c r="AK74" s="5" t="inlineStr">
+        <is>
+          <t>Reilly's/Latham's into line July 2 (16:00); Bachman's/Garden's join by July 3</t>
+        </is>
+      </c>
+      <c r="AL74" s="5" t="inlineStr">
+        <is>
+          <t>1,500 rounds report=tablet exact; TWO battery markers (Latham's, Garden's) independently credit ~17:00 fire vs Farnsworth's charge — new CA-SCF-2 CSA-side corroboration (now 5 sources)</t>
+        </is>
+      </c>
+      <c r="AM74" s="5" t="inlineStr">
+        <is>
+          <t>Report=tablet digit-exact: K4/W23 (no M/C stated)</t>
+        </is>
+      </c>
       <c r="AN74" s="5" t="n"/>
-      <c r="AO74" s="5" t="n"/>
+      <c r="AO74" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain, ED-36 pattern)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -8885,20 +8921,56 @@
           <t>reg-csa-3c-bn-lane</t>
         </is>
       </c>
-      <c r="AB84" s="5" t="n"/>
+      <c r="AB84" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC84" s="5" t="n"/>
       <c r="AD84" s="5" t="n"/>
       <c r="AE84" s="5" t="n"/>
       <c r="AF84" s="5" t="n"/>
-      <c r="AG84" s="5" t="n"/>
-      <c r="AH84" s="5" t="n"/>
-      <c r="AI84" s="5" t="n"/>
-      <c r="AJ84" s="5" t="n"/>
-      <c r="AK84" s="5" t="n"/>
-      <c r="AL84" s="5" t="n"/>
-      <c r="AM84" s="5" t="n"/>
+      <c r="AG84" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-bn-lane.md; closes the Third Corps battalion arc's one gap (pass-12 triage)</t>
+        </is>
+      </c>
+      <c r="AH84" s="5" t="inlineStr">
+        <is>
+          <t>Maj. John Lane; 3 batteries (Ross/A, Patterson/B, Wingfield/C); own report fetch-verified (No. 548, pp. 635-636) — Capt. Wingfield w July 3</t>
+        </is>
+      </c>
+      <c r="AI84" s="5" t="inlineStr">
+        <is>
+          <t>OPEN — no personnel total in report or tablet</t>
+        </is>
+      </c>
+      <c r="AJ84" s="5" t="inlineStr">
+        <is>
+          <t>[C report-primary] ridge east of town, '~1,400 yards' from Cemetery Hill; Patterson's battery detached to Wilcox's brigade July 2 am — cross-reference to csa-3c-and-1-wilcox.md and CA-J2A-10</t>
+        </is>
+      </c>
+      <c r="AK84" s="5" t="inlineStr">
+        <is>
+          <t>Patterson's detachment leg (named trigger + destination activity); remainder static on the ridge</t>
+        </is>
+      </c>
+      <c r="AL84" s="5" t="inlineStr">
+        <is>
+          <t>Ross's/Wingfield's markers both name CA-J3A-1 cannonade participation — new geographic witnesses from Anderson's front</t>
+        </is>
+      </c>
+      <c r="AM84" s="5" t="inlineStr">
+        <is>
+          <t>DOUBLE digit-exact 3-way cross-check: battery-marker sums = battalion tablet on BOTH rounds (1,082) and casualties (30); Lane's OWN report gives a conflicting total (29) — ED-74 candidate proposed</t>
+        </is>
+      </c>
       <c r="AN84" s="5" t="n"/>
-      <c r="AO84" s="5" t="n"/>
+      <c r="AO84" s="5" t="inlineStr">
+        <is>
+          <t>T4 (battalion grain, own-report primary)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -18005,20 +18077,56 @@
           <t>reg-csa-3c-and-2</t>
         </is>
       </c>
-      <c r="AB152" s="5" t="n"/>
+      <c r="AB152" s="5" t="inlineStr">
+        <is>
+          <t>attested-static</t>
+        </is>
+      </c>
       <c r="AC152" s="5" t="n"/>
       <c r="AD152" s="5" t="n"/>
       <c r="AE152" s="5" t="n"/>
       <c r="AF152" s="5" t="n"/>
-      <c r="AG152" s="5" t="n"/>
-      <c r="AH152" s="5" t="n"/>
-      <c r="AI152" s="5" t="n"/>
-      <c r="AJ152" s="5" t="n"/>
-      <c r="AK152" s="5" t="n"/>
-      <c r="AL152" s="5" t="n"/>
-      <c r="AM152" s="5" t="n"/>
+      <c r="AG152" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-2-mahone.md; the famous CSA non-participation; cross-refs Wright's/Lang's dossiers (the neighbors that advanced)</t>
+        </is>
+      </c>
+      <c r="AH152" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. William Mahone throughout; own report fetch-verified (dated July 10, 1863)</t>
+        </is>
+      </c>
+      <c r="AI152" s="5" t="inlineStr">
+        <is>
+          <t>Report=tablet digit-exact: Present 1,500</t>
+        </is>
+      </c>
+      <c r="AJ152" s="5" t="inlineStr">
+        <is>
+          <t>[C report-primary] 'immediately in front of the enemy, in support of Pegram's batteries' — cross-ref csa-3c-bn-pegram.md; arrived forenoon July 2, unchanged through July 4</t>
+        </is>
+      </c>
+      <c r="AK152" s="5" t="inlineStr">
+        <is>
+          <t>NONE — the defining fact is the absence of a July 2 advance leg</t>
+        </is>
+      </c>
+      <c r="AL152" s="5" t="inlineStr">
+        <is>
+          <t>Skirmish line only both days, report=tablet corroborating; report is SILENT on why the brigade did not advance to support Wright's/Posey's requests — first-class negative</t>
+        </is>
+      </c>
+      <c r="AM152" s="5" t="inlineStr">
+        <is>
+          <t>Report=tablet digit-exact: K8/W55/M39 = 102, mainly from shelling while stationary</t>
+        </is>
+      </c>
       <c r="AN152" s="5" t="n"/>
-      <c r="AO152" s="5" t="n"/>
+      <c r="AO152" s="5" t="inlineStr">
+        <is>
+          <t>T4 (own-report primary, negative-evidence class)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -18609,20 +18717,56 @@
           <t>reg-csa-3c-and-5</t>
         </is>
       </c>
-      <c r="AB156" s="5" t="n"/>
+      <c r="AB156" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC156" s="5" t="n"/>
       <c r="AD156" s="5" t="n"/>
       <c r="AE156" s="5" t="n"/>
       <c r="AF156" s="5" t="n"/>
-      <c r="AG156" s="5" t="n"/>
-      <c r="AH156" s="5" t="n"/>
-      <c r="AI156" s="5" t="n"/>
-      <c r="AJ156" s="5" t="n"/>
-      <c r="AK156" s="5" t="n"/>
-      <c r="AL156" s="5" t="n"/>
-      <c r="AM156" s="5" t="n"/>
+      <c r="AG156" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-and-5-posey.md; the PARTIAL-advance case between Mahone's none and Wright's/Lang's full advance</t>
+        </is>
+      </c>
+      <c r="AH156" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Carnot Posey throughout; own report fetch-verified (dated July 29, 1863)</t>
+        </is>
+      </c>
+      <c r="AI156" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: tablet 1,150 vs web-research 1,320 — not resolved</t>
+        </is>
+      </c>
+      <c r="AJ156" s="5" t="inlineStr">
+        <is>
+          <t>[C report-primary] open field w/ woods both flanks; advance '200-300 yds beyond the barn and house, which were burned' = the Bliss farm — NEW cross-ref to csa-3c-pen-3-thomas.md; withdrew to rear of Pegram's battery</t>
+        </is>
+      </c>
+      <c r="AK156" s="5" t="inlineStr">
+        <is>
+          <t>FOUR-STAGE piecemeal commitment (48th/19th, then 16th, then 12th) — Posey's own report blames this for the advance's failure to cohere</t>
+        </is>
+      </c>
+      <c r="AL156" s="5" t="inlineStr">
+        <is>
+          <t>Skirmish-grain success (pushed Union pickets back, drove artillerists off guns briefly) but never joined the main Cemetery Ridge assault</t>
+        </is>
+      </c>
+      <c r="AM156" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: tablet K12/W71=83 vs web-research K15/W68=83 — same total, different split, not resolved</t>
+        </is>
+      </c>
       <c r="AN156" s="5" t="n"/>
-      <c r="AO156" s="5" t="n"/>
+      <c r="AO156" s="5" t="inlineStr">
+        <is>
+          <t>T4 (own-report primary, partial-advance class)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -19693,20 +19837,56 @@
           <t>reg-csa-3c-pen-3</t>
         </is>
       </c>
-      <c r="AB163" s="5" t="n"/>
+      <c r="AB163" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC163" s="5" t="n"/>
       <c r="AD163" s="5" t="n"/>
       <c r="AE163" s="5" t="n"/>
       <c r="AF163" s="5" t="n"/>
-      <c r="AG163" s="5" t="n"/>
-      <c r="AH163" s="5" t="n"/>
-      <c r="AI163" s="5" t="n"/>
-      <c r="AJ163" s="5" t="n"/>
-      <c r="AK163" s="5" t="n"/>
-      <c r="AL163" s="5" t="n"/>
-      <c r="AM163" s="5" t="n"/>
+      <c r="AG163" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-3c-pen-3-thomas.md; REGISTER CORRECTION — Thomas is Pender's Division per reg-csa-3c-pen-3, not Anderson's, despite the task's framing (noted, not silently fixed)</t>
+        </is>
+      </c>
+      <c r="AH163" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Edward L. Thomas throughout; own report NOT directly fetched this pass (civilwarhome.com mirror confirmed dead) — attributed grade only</t>
+        </is>
+      </c>
+      <c r="AI163" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: ~1,400 attributed vs tablet 'about 1200' — not resolved</t>
+        </is>
+      </c>
+      <c r="AJ163" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] July 1 reserve then McMillan's Woods; July 2 22:00 to Long Lane, flanked by McGowan's/Perrin's brigade (left) and the Bliss House/Barn (right) — same farm as csa-3c-and-5-posey.md's EC3.2, new cross-ref</t>
+        </is>
+      </c>
+      <c r="AK163" s="5" t="inlineStr">
+        <is>
+          <t>Reserve-&gt;McMillan's Woods (sunset J1); artillery-support-&gt;Long Lane (22:00 J2); skirmish line-&gt;Seminary Ridge (after dark J3)</t>
+        </is>
+      </c>
+      <c r="AL163" s="5" t="inlineStr">
+        <is>
+          <t>July 1-2 reserve/artillery-support only; July 3 'severe skirmishing... most of the day' — NOT a quiet-flank case despite the task's framing</t>
+        </is>
+      </c>
+      <c r="AM163" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: K34/W179/M57 = 270 — HIGHEST of the three brigades in this pass's batch (Mahone 102, Posey 83)</t>
+        </is>
+      </c>
       <c r="AN163" s="5" t="n"/>
-      <c r="AO163" s="5" t="n"/>
+      <c r="AO163" s="5" t="inlineStr">
+        <is>
+          <t>T3 (tablet + attributed-report grain)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -21249,20 +21429,56 @@
           <t>reg-us-v-arty</t>
         </is>
       </c>
-      <c r="AB177" s="5" t="n"/>
+      <c r="AB177" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC177" s="5" t="n"/>
       <c r="AD177" s="5" t="n"/>
       <c r="AE177" s="5" t="n"/>
       <c r="AF177" s="5" t="n"/>
-      <c r="AG177" s="5" t="n"/>
-      <c r="AH177" s="5" t="n"/>
-      <c r="AI177" s="5" t="n"/>
-      <c r="AJ177" s="5" t="n"/>
-      <c r="AK177" s="5" t="n"/>
-      <c r="AL177" s="5" t="n"/>
-      <c r="AM177" s="5" t="n"/>
+      <c r="AG177" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-arty-martin.md; the pass-12-recommended Union corps-arty group, picked over III/VI on a reasoned (not exhaustive) source check</t>
+        </is>
+      </c>
+      <c r="AH177" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Augustus P. Martin; 5 batteries (Hazlett's/Rittenhouse's, Walcott's, Watson's, Gibbs's, Barnes's); own report fetch-verified (No. 221, pp. 659-661)</t>
+        </is>
+      </c>
+      <c r="AI177" s="5" t="inlineStr">
+        <is>
+          <t>937 men / 48 guns (tablet, search-summary grade, not page-verified)</t>
+        </is>
+      </c>
+      <c r="AJ177" s="5" t="inlineStr">
+        <is>
+          <t>[C report-primary] brigade arrival 16:00-17:00 July 2; Battery I 'not to be found' — reassigned by III Corps staff without record (cross-corps command friction)</t>
+        </is>
+      </c>
+      <c r="AK177" s="5" t="inlineStr">
+        <is>
+          <t>Brigade-wide arrival only; individual battery legs not authored beyond Rittenhouse's existing dossier</t>
+        </is>
+      </c>
+      <c r="AL177" s="5" t="inlineStr">
+        <is>
+          <t>Hazlett k ('shot in the head... died at 8 p.m.', upgrades the tablet-only pin on file); Battery I overrun then RETAKEN by Lt. Peeples w/ the Garibaldi Guards</t>
+        </is>
+      </c>
+      <c r="AM177" s="5" t="inlineStr">
+        <is>
+          <t>Report-primary brigade total: K9/W33/M2 = 44; Battery D's own component (7k/6w) not yet reconciled with us-btty-rittenhouse.md's existing EC6</t>
+        </is>
+      </c>
       <c r="AN177" s="5" t="n"/>
-      <c r="AO177" s="5" t="n"/>
+      <c r="AO177" s="5" t="inlineStr">
+        <is>
+          <t>T4 (brigade grain)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -22449,20 +22665,56 @@
           <t>reg-us-ha-2-1</t>
         </is>
       </c>
-      <c r="AB189" s="5" t="n"/>
+      <c r="AB189" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC189" s="5" t="n"/>
       <c r="AD189" s="5" t="n"/>
       <c r="AE189" s="5" t="n"/>
       <c r="AF189" s="5" t="n"/>
-      <c r="AG189" s="5" t="n"/>
-      <c r="AH189" s="5" t="n"/>
-      <c r="AI189" s="5" t="n"/>
-      <c r="AJ189" s="5" t="n"/>
-      <c r="AK189" s="5" t="n"/>
-      <c r="AL189" s="5" t="n"/>
-      <c r="AM189" s="5" t="n"/>
+      <c r="AG189" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-randol.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
+        </is>
+      </c>
+      <c r="AH189" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Alanson M. Randol throughout; split command July 3 (Chester's section w/ Custer's brigade, Kinney's section near Hanover Road); armament discrepancy flagged (tablet '4 12-Pdrs' vs horse-arty convention of 3-in rifles)</t>
+        </is>
+      </c>
+      <c r="AI189" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: 84 men (report-adjacent, not a B&amp;M hop)</t>
+        </is>
+      </c>
+      <c r="AJ189" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] with 1st Brig 2nd Cav Div, not engaged July 1-2; PASS-13 SHEET-CROP: Chester's section (10569,5638) and Kinney's section (10354,5270), ~370 m apart — first drawn confirmation the tablet split is real</t>
+        </is>
+      </c>
+      <c r="AK189" s="5" t="inlineStr">
+        <is>
+          <t>Not authored — no trigger/timing for either section located</t>
+        </is>
+      </c>
+      <c r="AL189" s="5" t="inlineStr">
+        <is>
+          <t>Chester's section co-named in McIntosh's tablet as CA-ECF-2 co-executor (~14:00); Kinney's section 'remained near Hanover Road', no engagement claimed</t>
+        </is>
+      </c>
+      <c r="AM189" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: 'suffered no casualties' — explicit zero, both sections combined</t>
+        </is>
+      </c>
       <c r="AN189" s="5" t="n"/>
-      <c r="AO189" s="5" t="n"/>
+      <c r="AO189" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain, split-section)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -24105,20 +24357,56 @@
           <t>reg-us-ha-1-4</t>
         </is>
       </c>
-      <c r="AB207" s="5" t="n"/>
+      <c r="AB207" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC207" s="5" t="n"/>
       <c r="AD207" s="5" t="n"/>
       <c r="AE207" s="5" t="n"/>
       <c r="AF207" s="5" t="n"/>
-      <c r="AG207" s="5" t="n"/>
-      <c r="AH207" s="5" t="n"/>
-      <c r="AI207" s="5" t="n"/>
-      <c r="AJ207" s="5" t="n"/>
-      <c r="AK207" s="5" t="n"/>
-      <c r="AL207" s="5" t="n"/>
-      <c r="AM207" s="5" t="n"/>
+      <c r="AG207" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-pennington.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
+        </is>
+      </c>
+      <c r="AH207" s="5" t="inlineStr">
+        <is>
+          <t>Lieut. A. C. M. Pennington Jr. throughout; six 3-in rifles (no armament discrepancy); parent Robertson's report defers narrative to Custer's</t>
+        </is>
+      </c>
+      <c r="AI207" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: 129 men</t>
+        </is>
+      </c>
+      <c r="AJ207" s="5" t="inlineStr">
+        <is>
+          <t>[C, shared w/ Custer's brigade] Hanover Rd/Low Dutch sector; PASS-13 SHEET-CROP: 'PENNINGTON/CLARK BAT.M' at (10072,5237), south of Custer's block; 'Clark' unidentified</t>
+        </is>
+      </c>
+      <c r="AK207" s="5" t="inlineStr">
+        <is>
+          <t>Inferred-by-attachment to Custer's brigade only</t>
+        </is>
+      </c>
+      <c r="AL207" s="5" t="inlineStr">
+        <is>
+          <t>July 2 Hunterstown; July 3 ~14:00 CA-ECF-2, report=tablet agreement ('engaged all day' / 'on the right of the Union Army') — the pass's second report=tablet pair</t>
+        </is>
+      </c>
+      <c r="AM207" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: wounded 1 officer only (no enlisted figure stated)</t>
+        </is>
+      </c>
       <c r="AN207" s="5" t="n"/>
-      <c r="AO207" s="5" t="n"/>
+      <c r="AO207" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -33121,20 +33409,56 @@
           <t>reg-us-hq-provost</t>
         </is>
       </c>
-      <c r="AB276" s="5" t="n"/>
+      <c r="AB276" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC276" s="5" t="n"/>
       <c r="AD276" s="5" t="n"/>
       <c r="AE276" s="5" t="n"/>
       <c r="AF276" s="5" t="n"/>
-      <c r="AG276" s="5" t="n"/>
-      <c r="AH276" s="5" t="n"/>
-      <c r="AI276" s="5" t="n"/>
-      <c r="AJ276" s="5" t="n"/>
-      <c r="AK276" s="5" t="n"/>
-      <c r="AL276" s="5" t="n"/>
-      <c r="AM276" s="5" t="n"/>
+      <c r="AG276" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-hq-provost-patrick.md; the cheap command-record closer named in the task; thinnest sourcing of this pass's command batch (only the 93rd NY tablet is fetch-verified)</t>
+        </is>
+      </c>
+      <c r="AH276" s="5" t="inlineStr">
+        <is>
+          <t>Brig. Gen. Marsena R. Patrick, Provost Marshal General; 93rd NY served as HQ guard (own tablet fetch-verified)</t>
+        </is>
+      </c>
+      <c r="AI276" s="5" t="inlineStr">
+        <is>
+          <t>93rd NY: 399 (tablet); whole command: 1,750 (attributed, not reconciled with the 399 figure)</t>
+        </is>
+      </c>
+      <c r="AJ276" s="5" t="inlineStr">
+        <is>
+          <t>[D attributed] Sheely Farm HQ; [C tablet] 93rd NY near the Leister House/Taneytown Rd — the two positions not reconciled into one command anchor</t>
+        </is>
+      </c>
+      <c r="AK276" s="5" t="inlineStr">
+        <is>
+          <t>Not authored — rear-area, non-maneuvering command</t>
+        </is>
+      </c>
+      <c r="AL276" s="5" t="inlineStr">
+        <is>
+          <t>Patrick's own diary quote (attributed): checked straggler disorder, organized a guard keeping ~2,000 CSA prisoners safe after the July 3 repulse — downstream CA-J3A-9/10 context</t>
+        </is>
+      </c>
+      <c r="AM276" s="5" t="inlineStr">
+        <is>
+          <t>1 killed, 4 wounded (attributed, whole command)</t>
+        </is>
+      </c>
       <c r="AN276" s="5" t="n"/>
-      <c r="AO276" s="5" t="n"/>
+      <c r="AO276" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command record)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -20441,20 +20441,56 @@
           <t>reg-us-ha-1</t>
         </is>
       </c>
-      <c r="AB167" s="5" t="n"/>
+      <c r="AB167" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC167" s="5" t="n"/>
       <c r="AD167" s="5" t="n"/>
       <c r="AE167" s="5" t="n"/>
       <c r="AF167" s="5" t="n"/>
-      <c r="AG167" s="5" t="n"/>
-      <c r="AH167" s="5" t="n"/>
-      <c r="AI167" s="5" t="n"/>
-      <c r="AJ167" s="5" t="n"/>
-      <c r="AK167" s="5" t="n"/>
-      <c r="AL167" s="5" t="n"/>
-      <c r="AM167" s="5" t="n"/>
+      <c r="AG167" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ha-1-robertson.md; the July3 Tyler-succession cross-ref to reg-us-ar-hq</t>
+        </is>
+      </c>
+      <c r="AH167" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde Horse Arty (9th MI/6th NY/2nd US B&amp;L/2nd US M/4th US E); Capt. James M. Robertson; report-primary</t>
+        </is>
+      </c>
+      <c r="AI167" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ167" s="5" t="inlineStr">
+        <is>
+          <t>[C report] approach march June28-Jul1; [C] July3 assumed Artillery Reserve command after Tyler's sunstroke; batteries split 3 theaters July3 (Pennington ECF, Elder SCF sheet-confirmed, Daniels Cemetery Ridge)</t>
+        </is>
+      </c>
+      <c r="AK167" s="5" t="inlineStr">
+        <is>
+          <t>[C] approach legs; [D] July2 reserve shift</t>
+        </is>
+      </c>
+      <c r="AL167" s="5" t="inlineStr">
+        <is>
+          <t>[C] Daniels 9th MI engaged under Newton; Martin/Heaton 'In Reserve' both tablets</t>
+        </is>
+      </c>
+      <c r="AM167" s="5" t="inlineStr">
+        <is>
+          <t>tablet 8 (2k/1+5w); Daniels component 1k/4w/23 horses</t>
+        </is>
+      </c>
       <c r="AN167" s="5" t="n"/>
-      <c r="AO167" s="5" t="n"/>
+      <c r="AO167" s="5" t="inlineStr">
+        <is>
+          <t>T3 (command grain, own-report primary)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -20529,20 +20565,56 @@
           <t>reg-us-ar-1r</t>
         </is>
       </c>
-      <c r="AB168" s="5" t="n"/>
+      <c r="AB168" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC168" s="5" t="n"/>
       <c r="AD168" s="5" t="n"/>
       <c r="AE168" s="5" t="n"/>
       <c r="AF168" s="5" t="n"/>
-      <c r="AG168" s="5" t="n"/>
-      <c r="AH168" s="5" t="n"/>
-      <c r="AI168" s="5" t="n"/>
-      <c r="AJ168" s="5" t="n"/>
-      <c r="AK168" s="5" t="n"/>
-      <c r="AL168" s="5" t="n"/>
-      <c r="AM168" s="5" t="n"/>
+      <c r="AG168" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-1r-ransom.md; explains Tyler's own 'no report from Ransom's battery' line as an old-habit naming artifact</t>
+        </is>
+      </c>
+      <c r="AH168" s="5" t="inlineStr">
+        <is>
+          <t>1st Regular Bde Artillery Reserve (1US-H Mason/3US-F&amp;K Turnbull/4US-C Thomas/5US-C Weir); Capt Dunbar R. Ransom (w Jul3); NO brigade report exists - CONFIRMED by direct page check</t>
+        </is>
+      </c>
+      <c r="AI168" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ168" s="5" t="inlineStr">
+        <is>
+          <t>not authored - no report to supply one</t>
+        </is>
+      </c>
+      <c r="AK168" s="5" t="inlineStr">
+        <is>
+          <t>not authored</t>
+        </is>
+      </c>
+      <c r="AL168" s="5" t="inlineStr">
+        <is>
+          <t>not authored - see us-btty-weir.md</t>
+        </is>
+      </c>
+      <c r="AM168" s="5" t="inlineStr">
+        <is>
+          <t>tablet 68 (1off+12men k/4off+49w/2 missing)</t>
+        </is>
+      </c>
       <c r="AN168" s="5" t="n"/>
-      <c r="AO168" s="5" t="n"/>
+      <c r="AO168" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command record, confirmed no-report class)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -20741,20 +20813,56 @@
           <t>reg-us-ha-2</t>
         </is>
       </c>
-      <c r="AB170" s="5" t="n"/>
+      <c r="AB170" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC170" s="5" t="n"/>
       <c r="AD170" s="5" t="n"/>
       <c r="AE170" s="5" t="n"/>
       <c r="AF170" s="5" t="n"/>
-      <c r="AG170" s="5" t="n"/>
-      <c r="AH170" s="5" t="n"/>
-      <c r="AI170" s="5" t="n"/>
-      <c r="AJ170" s="5" t="n"/>
-      <c r="AK170" s="5" t="n"/>
-      <c r="AL170" s="5" t="n"/>
-      <c r="AM170" s="5" t="n"/>
+      <c r="AG170" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ha-2-tidball.md</t>
+        </is>
+      </c>
+      <c r="AH170" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde Horse Arty (1st US E&amp;G/1st US K/2nd US A/3rd US C); Capt. John C. Tidball; report is a forwarding letter</t>
+        </is>
+      </c>
+      <c r="AI170" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ170" s="5" t="inlineStr">
+        <is>
+          <t>[D] no brigade-level anchor; batteries dispersed (Calef Jul1 w/Gamble, Randol ECF, Graham SCF w/Merritt, Fuller off-map Westminster)</t>
+        </is>
+      </c>
+      <c r="AK170" s="5" t="inlineStr">
+        <is>
+          <t>not authored</t>
+        </is>
+      </c>
+      <c r="AL170" s="5" t="inlineStr">
+        <is>
+          <t>forwarding-letter only; no first-hand narrative</t>
+        </is>
+      </c>
+      <c r="AM170" s="5" t="inlineStr">
+        <is>
+          <t>tablet 15 (2k/13w)</t>
+        </is>
+      </c>
       <c r="AN170" s="5" t="n"/>
-      <c r="AO170" s="5" t="n"/>
+      <c r="AO170" s="5" t="inlineStr">
+        <is>
+          <t>T2 (command record, forwarding-letter class)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -20829,20 +20937,56 @@
           <t>reg-us-ar-2v</t>
         </is>
       </c>
-      <c r="AB171" s="5" t="n"/>
+      <c r="AB171" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC171" s="5" t="n"/>
       <c r="AD171" s="5" t="n"/>
       <c r="AE171" s="5" t="n"/>
       <c r="AF171" s="5" t="n"/>
-      <c r="AG171" s="5" t="n"/>
-      <c r="AH171" s="5" t="n"/>
-      <c r="AI171" s="5" t="n"/>
-      <c r="AJ171" s="5" t="n"/>
-      <c r="AK171" s="5" t="n"/>
-      <c r="AL171" s="5" t="n"/>
-      <c r="AM171" s="5" t="n"/>
+      <c r="AG171" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-2v-taft.md; ties into East Cemetery Hill's Howard-reporting chain</t>
+        </is>
+      </c>
+      <c r="AH171" s="5" t="inlineStr">
+        <is>
+          <t>2nd Volunteer Bde Artillery Reserve (1CT-Hvy-B Brooker/1CT-Hvy-M Pratt/2CT Sterling/5NY Taft); Capt Elijah D. Taft; own report scoped to HIS OWN battery only</t>
+        </is>
+      </c>
+      <c r="AI171" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ171" s="5" t="inlineStr">
+        <is>
+          <t>[C ~16:30-17:00] Taneytown march, cemetery arrival, reported to HOWARD (XI Corps), in position 5pm Jul2</t>
+        </is>
+      </c>
+      <c r="AK171" s="5" t="inlineStr">
+        <is>
+          <t>[B] the staged approach march; [D ~10:00 Jul5] return march</t>
+        </is>
+      </c>
+      <c r="AL171" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00 &amp; 13:30+ Jul3] sustained fire, one 20-pdr Parrott burst; itemized rounds expended</t>
+        </is>
+      </c>
+      <c r="AM171" s="5" t="inlineStr">
+        <is>
+          <t>tablet 8 (1k/5w/2 missing); Taft's own battery: FOUR individually-timed casualties (Begg mw, Thalheimer mw, Dillon, Wittenberg)</t>
+        </is>
+      </c>
       <c r="AN171" s="5" t="n"/>
-      <c r="AO171" s="5" t="n"/>
+      <c r="AO171" s="5" t="inlineStr">
+        <is>
+          <t>T3 (own-battery-scoped report)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -20917,20 +21061,56 @@
           <t>reg-us-ar-3v</t>
         </is>
       </c>
-      <c r="AB172" s="5" t="n"/>
+      <c r="AB172" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC172" s="5" t="n"/>
       <c r="AD172" s="5" t="n"/>
       <c r="AE172" s="5" t="n"/>
       <c r="AF172" s="5" t="n"/>
-      <c r="AG172" s="5" t="n"/>
-      <c r="AH172" s="5" t="n"/>
-      <c r="AI172" s="5" t="n"/>
-      <c r="AJ172" s="5" t="n"/>
-      <c r="AK172" s="5" t="n"/>
-      <c r="AL172" s="5" t="n"/>
-      <c r="AM172" s="5" t="n"/>
+      <c r="AG172" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-3v-huntington.md</t>
+        </is>
+      </c>
+      <c r="AH172" s="5" t="inlineStr">
+        <is>
+          <t>3rd Volunteer Bde Artillery Reserve (1NH Edgell/1OH-H Norton/1PA-F&amp;G Ricketts/1WV-C Hill); Capt James F. Huntington; NO brigade report - 3rd confirmed instance of the class pattern</t>
+        </is>
+      </c>
+      <c r="AI172" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ172" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:30 Jul2] Edgell's Cemetery Hill position; [C ~16:00] Norton's position; [D] Ricketts already T4 on own dossier</t>
+        </is>
+      </c>
+      <c r="AK172" s="5" t="inlineStr">
+        <is>
+          <t>[C] Edgell's move + Jul3 relocation to a cornfield near the Baltimore turnpike</t>
+        </is>
+      </c>
+      <c r="AL172" s="5" t="inlineStr">
+        <is>
+          <t>[C] Edgell vs Chambersburg-Rd CSA guns, 105 then 353 total rounds (scope, not conflict); 3 wounded/3 horses/1 wheel-axle</t>
+        </is>
+      </c>
+      <c r="AM172" s="5" t="inlineStr">
+        <is>
+          <t>tablet 37 (10k/1off+23w/3 missing)</t>
+        </is>
+      </c>
       <c r="AN172" s="5" t="n"/>
-      <c r="AO172" s="5" t="n"/>
+      <c r="AO172" s="5" t="inlineStr">
+        <is>
+          <t>T3 (battery-grain own-reports; no brigade report)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -21005,20 +21185,56 @@
           <t>reg-us-ar-4v</t>
         </is>
       </c>
-      <c r="AB173" s="5" t="n"/>
+      <c r="AB173" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC173" s="5" t="n"/>
       <c r="AD173" s="5" t="n"/>
       <c r="AE173" s="5" t="n"/>
       <c r="AF173" s="5" t="n"/>
-      <c r="AG173" s="5" t="n"/>
-      <c r="AH173" s="5" t="n"/>
-      <c r="AI173" s="5" t="n"/>
-      <c r="AJ173" s="5" t="n"/>
-      <c r="AK173" s="5" t="n"/>
-      <c r="AL173" s="5" t="n"/>
-      <c r="AM173" s="5" t="n"/>
+      <c r="AG173" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-ar-4v-fitzhugh.md; the ONE of four AR brigades this pass with a real brigade narrative</t>
+        </is>
+      </c>
+      <c r="AH173" s="5" t="inlineStr">
+        <is>
+          <t>4th Volunteer Bde Artillery Reserve (6ME Dow/1MD-A Rigby/1NJ-A Parsons/1NY-G Ames/1NY-K Fitzhugh); Capt Robert H. Fitzhugh; GENUINE brigade report (the one exception)</t>
+        </is>
+      </c>
+      <c r="AI173" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ173" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00 Jul2] Taneytown arrival; [C] Tyler's own order dispersing 2 batteries to the Baltimore Pike near Slocum; Dow/Ames detached under McGilvery, Rigby to XII Corps; [C ~13:00 Jul3] Hunt personally orders remainder to Webb's fence</t>
+        </is>
+      </c>
+      <c r="AK173" s="5" t="inlineStr">
+        <is>
+          <t>[C ~08:00] the arrival march; [C ~13:00, ED-41 trigger=Hunt's order] the crisis-reinforcement displacement</t>
+        </is>
+      </c>
+      <c r="AL173" s="5" t="inlineStr">
+        <is>
+          <t>[C ~13:00-14:00] Parsons ~40 rds shrapnel into CSA flank; Fitzhugh's K vs CSA guns ~1,000 yds; repulsed within 'half or three-quarters of an hour' (new duration detail)</t>
+        </is>
+      </c>
+      <c r="AM173" s="5" t="inlineStr">
+        <is>
+          <t>tablet 36 (2k/34w); K+11NY component 7w/5 horses/89 rds (EXACT match to us-btty-fitzhugh.md's own return); Parsons component '2 killed' (partial)</t>
+        </is>
+      </c>
       <c r="AN173" s="5" t="n"/>
-      <c r="AO173" s="5" t="n"/>
+      <c r="AO173" s="5" t="inlineStr">
+        <is>
+          <t>T4 (a genuine brigade command report)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -21341,20 +21557,56 @@
           <t>reg-us-iii-arty</t>
         </is>
       </c>
-      <c r="AB176" s="5" t="n"/>
+      <c r="AB176" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC176" s="5" t="n"/>
       <c r="AD176" s="5" t="n"/>
       <c r="AE176" s="5" t="n"/>
       <c r="AF176" s="5" t="n"/>
-      <c r="AG176" s="5" t="n"/>
-      <c r="AH176" s="5" t="n"/>
-      <c r="AI176" s="5" t="n"/>
-      <c r="AJ176" s="5" t="n"/>
-      <c r="AK176" s="5" t="n"/>
-      <c r="AL176" s="5" t="n"/>
-      <c r="AM176" s="5" t="n"/>
+      <c r="AG176" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-iii-arty-randolph.md; closes the last uncovered Union corps-artillery group</t>
+        </is>
+      </c>
+      <c r="AH176" s="5" t="inlineStr">
+        <is>
+          <t>Artillery Brigade III Corps (2NJ/1NY-D Winslow/4NY Smith/1RI-E/4US-K); Capt George E. Randolph (w Jul2)-&gt;Capt A.J. Clark; BOTH own reports fetched</t>
+        </is>
+      </c>
+      <c r="AI176" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ176" s="5" t="inlineStr">
+        <is>
+          <t>[C] approach march Jun28-Jul1; [C] Jul2 Emmitsburg Rd salient line (Birney's ground); [C ~09:30] Clark's early long-range fire; [C 13:00-13:30] Sickles repositioning notice; [D] extended gun line to dark</t>
+        </is>
+      </c>
+      <c r="AK176" s="5" t="inlineStr">
+        <is>
+          <t>[C] the march; [C ~09:30] Clark's deployment; [C 13:00+] the repositioning</t>
+        </is>
+      </c>
+      <c r="AL176" s="5" t="inlineStr">
+        <is>
+          <t>[C] solid shot-&gt;case-&gt;canister sequence; [C ~15:00+] the rolling infantry assault 'shortly after 3pm'; [C] battery-by-piece withdrawal; [C ~17:30] Seeley's crisis, wounded, Lt James succeeds</t>
+        </is>
+      </c>
+      <c r="AM176" s="5" t="inlineStr">
+        <is>
+          <t>tablet 106 (8k/3off+78w/17 missing); 3 officer casualties (Randolph, Bucklyn, Seeley) match the tablet's '3 Officers' wounded exactly</t>
+        </is>
+      </c>
       <c r="AN176" s="5" t="n"/>
-      <c r="AO176" s="5" t="n"/>
+      <c r="AO176" s="5" t="inlineStr">
+        <is>
+          <t>T4 (group grain, own-report primary)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -34577,20 +34829,56 @@
           <t>reg-us-vi-1-2</t>
         </is>
       </c>
-      <c r="AB284" s="5" t="n"/>
+      <c r="AB284" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC284" s="5" t="n"/>
       <c r="AD284" s="5" t="n"/>
       <c r="AE284" s="5" t="n"/>
       <c r="AF284" s="5" t="n"/>
-      <c r="AG284" s="5" t="n"/>
-      <c r="AH284" s="5" t="n"/>
-      <c r="AI284" s="5" t="n"/>
-      <c r="AJ284" s="5" t="n"/>
-      <c r="AK284" s="5" t="n"/>
-      <c r="AL284" s="5" t="n"/>
-      <c r="AM284" s="5" t="n"/>
+      <c r="AG284" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-2-bartlett.md; resolves Nevin's 'triple command succession' hazard</t>
+        </is>
+      </c>
+      <c r="AH284" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde 1st Div VI Corps (5ME/121NY/95,96PA); Brig Gen J.J. Bartlett; report=tablet; GENUINELY ENGAGED</t>
+        </is>
+      </c>
+      <c r="AI284" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ284" s="5" t="inlineStr">
+        <is>
+          <t>[D] Jul2 arrival ~5pm supporting Sykes; [C] Jul3 composite command of Nevin's 3rd Bde 3rd Div for the Crawford-support Wheatfield sweep (three-dossier cross-ref: this + us-vi-3-3-nevin.md + us-v-3-1-mccandless.md)</t>
+        </is>
+      </c>
+      <c r="AK284" s="5" t="inlineStr">
+        <is>
+          <t>[C ~17:00-18:00] the composite-command advance</t>
+        </is>
+      </c>
+      <c r="AL284" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul3 ~200 CSA prisoners + 15th GA colors captured jointly w/ McCandless</t>
+        </is>
+      </c>
+      <c r="AM284" s="5" t="inlineStr">
+        <is>
+          <t>own-bde tablet 5 (1k/4w); composite-command loss separately stated 'between 20 and 30'</t>
+        </is>
+      </c>
       <c r="AN284" s="5" t="n"/>
-      <c r="AO284" s="5" t="n"/>
+      <c r="AO284" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -37261,20 +37549,56 @@
           <t>reg-us-vi-3-2</t>
         </is>
       </c>
-      <c r="AB301" s="5" t="n"/>
+      <c r="AB301" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC301" s="5" t="n"/>
       <c r="AD301" s="5" t="n"/>
       <c r="AE301" s="5" t="n"/>
       <c r="AF301" s="5" t="n"/>
-      <c r="AG301" s="5" t="n"/>
-      <c r="AH301" s="5" t="n"/>
-      <c r="AI301" s="5" t="n"/>
-      <c r="AJ301" s="5" t="n"/>
-      <c r="AK301" s="5" t="n"/>
-      <c r="AL301" s="5" t="n"/>
-      <c r="AM301" s="5" t="n"/>
+      <c r="AG301" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-2-eustis.md; the corpus's 4th confirmed no-report-class Union brigade</t>
+        </is>
+      </c>
+      <c r="AH301" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde 3rd Div VI Corps (7,10,37MA/2RI); Col Henry L. Eustis; NO brigade report - confirmed, only Rogers's 2nd RI regimental report fills the numbered slot</t>
+        </is>
+      </c>
+      <c r="AI301" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ301" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00] arrival; [C] Jul3 right-centre reserve reporting to Newton, 'not engaged but subject to artillery fire'</t>
+        </is>
+      </c>
+      <c r="AK301" s="5" t="inlineStr">
+        <is>
+          <t>not authored</t>
+        </is>
+      </c>
+      <c r="AL301" s="5" t="inlineStr">
+        <is>
+          <t>[D] present-but-not-firing; Rogers's 2RI: 'the hottest of the battle'/'severest engagement of the war' (tension w/ 'not engaged')</t>
+        </is>
+      </c>
+      <c r="AM301" s="5" t="inlineStr">
+        <is>
+          <t>tablet 69 (3k/2off+39w/25 missing) - the missing-25 figure has NO attested cause, honestly flagged</t>
+        </is>
+      </c>
       <c r="AN301" s="5" t="n"/>
-      <c r="AO301" s="5" t="n"/>
+      <c r="AO301" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -37829,20 +38153,56 @@
           <t>reg-us-vi-2-1</t>
         </is>
       </c>
-      <c r="AB305" s="5" t="n"/>
+      <c r="AB305" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC305" s="5" t="n"/>
       <c r="AD305" s="5" t="n"/>
       <c r="AE305" s="5" t="n"/>
       <c r="AF305" s="5" t="n"/>
-      <c r="AG305" s="5" t="n"/>
-      <c r="AH305" s="5" t="n"/>
-      <c r="AI305" s="5" t="n"/>
-      <c r="AJ305" s="5" t="n"/>
-      <c r="AK305" s="5" t="n"/>
-      <c r="AL305" s="5" t="n"/>
-      <c r="AM305" s="5" t="n"/>
+      <c r="AG305" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-2-1-grant.md; fetched pages surfaced only a June Franklin's-Crossing letter, not Gettysburg</t>
+        </is>
+      </c>
+      <c r="AH305" s="5" t="inlineStr">
+        <is>
+          <t>2nd Bde 2nd Div VI Corps, the Vermont Bde (2/3/4/5/6 VT); Col Lewis A. Grant; OR entry's Gettysburg content NOT located</t>
+        </is>
+      </c>
+      <c r="AI305" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ305" s="5" t="inlineStr">
+        <is>
+          <t>[C ~17:00] 33mi march arrived 5pm Jul2; [C] Jul3 right on Round-Top-east-slope, left on Taneytown Rd, 'under no fire except artillery'</t>
+        </is>
+      </c>
+      <c r="AK305" s="5" t="inlineStr">
+        <is>
+          <t>[B] the march; [D] short Jul3 advance</t>
+        </is>
+      </c>
+      <c r="AL305" s="5" t="inlineStr">
+        <is>
+          <t>[D] present-but-not-firing, ED-44 class; 5th VT on picket Jul2 night</t>
+        </is>
+      </c>
+      <c r="AM305" s="5" t="inlineStr">
+        <is>
+          <t>tablet 1w</t>
+        </is>
+      </c>
       <c r="AN305" s="5" t="n"/>
-      <c r="AO305" s="5" t="n"/>
+      <c r="AO305" s="5" t="inlineStr">
+        <is>
+          <t>T3 (tablet-primary; report access gap honestly recorded)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -39873,20 +40233,56 @@
           <t>reg-us-vi-2-2</t>
         </is>
       </c>
-      <c r="AB318" s="5" t="n"/>
+      <c r="AB318" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC318" s="5" t="n"/>
       <c r="AD318" s="5" t="n"/>
       <c r="AE318" s="5" t="n"/>
       <c r="AF318" s="5" t="n"/>
-      <c r="AG318" s="5" t="n"/>
-      <c r="AH318" s="5" t="n"/>
-      <c r="AI318" s="5" t="n"/>
-      <c r="AJ318" s="5" t="n"/>
-      <c r="AK318" s="5" t="n"/>
-      <c r="AL318" s="5" t="n"/>
-      <c r="AM318" s="5" t="n"/>
+      <c r="AG318" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-2-2-neill.md; the corps's least-static brigade this pass</t>
+        </is>
+      </c>
+      <c r="AH318" s="5" t="inlineStr">
+        <is>
+          <t>3rd Bde 2nd Div VI Corps (7ME(6co)/43,49,77NY/61PA); Brig Gen T.H. Neill; report thin on the battle days</t>
+        </is>
+      </c>
+      <c r="AI318" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ318" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jul2 arrival then DETACHED ~6pm to hold Powers Hill (Meade's direct order); [C] Jul3 crossed Rock Creek to extreme right, connecting w/ cavalry pickets (Slocum's order)</t>
+        </is>
+      </c>
+      <c r="AK318" s="5" t="inlineStr">
+        <is>
+          <t>[C] Powers Hill leg; [C] Rock Creek crossing leg</t>
+        </is>
+      </c>
+      <c r="AL318" s="5" t="inlineStr">
+        <is>
+          <t>[D] ground-security/liaison roles, no documented firing episode</t>
+        </is>
+      </c>
+      <c r="AM318" s="5" t="inlineStr">
+        <is>
+          <t>tablet 15 (1 off+1 man k/11w/2 missing) - cause not attested</t>
+        </is>
+      </c>
       <c r="AN318" s="5" t="n"/>
-      <c r="AO318" s="5" t="n"/>
+      <c r="AO318" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -40317,20 +40713,56 @@
           <t>reg-us-vi-1-3</t>
         </is>
       </c>
-      <c r="AB321" s="5" t="n"/>
+      <c r="AB321" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC321" s="5" t="n"/>
       <c r="AD321" s="5" t="n"/>
       <c r="AE321" s="5" t="n"/>
       <c r="AF321" s="5" t="n"/>
-      <c r="AG321" s="5" t="n"/>
-      <c r="AH321" s="5" t="n"/>
-      <c r="AI321" s="5" t="n"/>
-      <c r="AJ321" s="5" t="n"/>
-      <c r="AK321" s="5" t="n"/>
-      <c r="AL321" s="5" t="n"/>
-      <c r="AM321" s="5" t="n"/>
+      <c r="AG321" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-3-russell.md</t>
+        </is>
+      </c>
+      <c r="AH321" s="5" t="inlineStr">
+        <is>
+          <t>3rd Bde 1st Div VI Corps (6ME/49(4co)/119PA/5WI); Brig Gen D.A. Russell; report=tablet</t>
+        </is>
+      </c>
+      <c r="AI321" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ321" s="5" t="inlineStr">
+        <is>
+          <t>[C ~16:00] arrival; [C] Jul3 extreme left then left-centre 'anticipated attack on the center' (report's cause, tablet's terser text)</t>
+        </is>
+      </c>
+      <c r="AK321" s="5" t="inlineStr">
+        <is>
+          <t>[B] the march; [D] the afternoon shift</t>
+        </is>
+      </c>
+      <c r="AL321" s="5" t="inlineStr">
+        <is>
+          <t>[D] attested-static both sources: 'Not engaged' / 'not actually engaged'</t>
+        </is>
+      </c>
+      <c r="AM321" s="5" t="inlineStr">
+        <is>
+          <t>CONFLICT: tablet 2w vs report's 'no casualties' - carried unresolved</t>
+        </is>
+      </c>
       <c r="AN321" s="5" t="n"/>
-      <c r="AO321" s="5" t="n"/>
+      <c r="AO321" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -40441,20 +40873,56 @@
           <t>reg-us-vi-3-1</t>
         </is>
       </c>
-      <c r="AB322" s="5" t="n"/>
+      <c r="AB322" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC322" s="5" t="n"/>
       <c r="AD322" s="5" t="n"/>
       <c r="AE322" s="5" t="n"/>
       <c r="AF322" s="5" t="n"/>
-      <c r="AG322" s="5" t="n"/>
-      <c r="AH322" s="5" t="n"/>
-      <c r="AI322" s="5" t="n"/>
-      <c r="AJ322" s="5" t="n"/>
-      <c r="AK322" s="5" t="n"/>
-      <c r="AL322" s="5" t="n"/>
-      <c r="AM322" s="5" t="n"/>
+      <c r="AG322" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-1-shaler.md; CLOSES the corps HQ dossier's own flagged verification item; feeds CA-J3M-2/4</t>
+        </is>
+      </c>
+      <c r="AH322" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde 3rd Div VI Corps (65,67,122NY/23,82PA); Brig Gen Alexander Shaler; TWO reports (battle narrative + Nov1863 correction letter)</t>
+        </is>
+      </c>
+      <c r="AI322" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ322" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00] arrival; [C ~08:00 Jul3] detached to Culp's Hill supporting Geary; regiment-grain sub-hour ladder 9:00-11:30am; [C ~15:30] withdrew under fire to III Corps center-rear reserve</t>
+        </is>
+      </c>
+      <c r="AK322" s="5" t="inlineStr">
+        <is>
+          <t>[C] the 8am detachment leg; [C] the 3:30pm withdrawal leg</t>
+        </is>
+      </c>
+      <c r="AL322" s="5" t="inlineStr">
+        <is>
+          <t>[C] ENGAGED 9-11am under Geary, 'severe fire'/'galling fire of musketry'</t>
+        </is>
+      </c>
+      <c r="AM322" s="5" t="inlineStr">
+        <is>
+          <t>tablet 74 (1off+14men k/3off+53w/3 missing) - heaviest VI Corps brigade loss this pass</t>
+        </is>
+      </c>
       <c r="AN322" s="5" t="n"/>
-      <c r="AO322" s="5" t="n"/>
+      <c r="AO322" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -41329,20 +41797,56 @@
           <t>reg-us-vi-1-1</t>
         </is>
       </c>
-      <c r="AB328" s="5" t="n"/>
+      <c r="AB328" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC328" s="5" t="n"/>
       <c r="AD328" s="5" t="n"/>
       <c r="AE328" s="5" t="n"/>
       <c r="AF328" s="5" t="n"/>
-      <c r="AG328" s="5" t="n"/>
-      <c r="AH328" s="5" t="n"/>
-      <c r="AI328" s="5" t="n"/>
-      <c r="AJ328" s="5" t="n"/>
-      <c r="AK328" s="5" t="n"/>
-      <c r="AL328" s="5" t="n"/>
-      <c r="AM328" s="5" t="n"/>
+      <c r="AG328" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-1-torbert.md</t>
+        </is>
+      </c>
+      <c r="AH328" s="5" t="inlineStr">
+        <is>
+          <t>1st Bde 1st Div VI Corps (1/2/3/15 NJ); Brig Gen A.T.A. Torbert; report=tablet</t>
+        </is>
+      </c>
+      <c r="AI328" s="5" t="inlineStr">
+        <is>
+          <t>1,663 (106 off/1,557 enl, report-primary itemized)</t>
+        </is>
+      </c>
+      <c r="AJ328" s="5" t="inlineStr">
+        <is>
+          <t>[C ~16:00] 35mi march, arrived 4pm Jul2; [C] LRT reserve; [C] Jul3 Weikert-House-area center</t>
+        </is>
+      </c>
+      <c r="AK328" s="5" t="inlineStr">
+        <is>
+          <t>[B] the 35mi march</t>
+        </is>
+      </c>
+      <c r="AL328" s="5" t="inlineStr">
+        <is>
+          <t>[D] attested-static, picket only; 11 wounded on picket Jul3</t>
+        </is>
+      </c>
+      <c r="AM328" s="5" t="inlineStr">
+        <is>
+          <t>tablet 11w = report's Jul3 picket figure exact; report's broader 1k/17w is a CAMPAIGN total (scope, not conflict)</t>
+        </is>
+      </c>
       <c r="AN328" s="5" t="n"/>
-      <c r="AO328" s="5" t="n"/>
+      <c r="AO328" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -4977,20 +4977,56 @@
           <t>reg-csa-cav-ha-7</t>
         </is>
       </c>
-      <c r="AB49" s="5" t="n"/>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (attested-absent-from-combat)</t>
+        </is>
+      </c>
       <c r="AC49" s="5" t="n"/>
       <c r="AD49" s="5" t="n"/>
       <c r="AE49" s="5" t="n"/>
       <c r="AF49" s="5" t="n"/>
-      <c r="AG49" s="5" t="n"/>
-      <c r="AH49" s="5" t="n"/>
-      <c r="AI49" s="5" t="n"/>
-      <c r="AJ49" s="5" t="n"/>
-      <c r="AK49" s="5" t="n"/>
-      <c r="AL49" s="5" t="n"/>
-      <c r="AM49" s="5" t="n"/>
+      <c r="AG49" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/csa-cav-ha-mcclanahan.md; bonus closer, not part of the task's core 23; closes needs-own-dossier to true zero</t>
+        </is>
+      </c>
+      <c r="AH49" s="5" t="inlineStr">
+        <is>
+          <t>Capt. John H. McClanahan, w/ Imboden's semi-independent command; NOT part of Beckham's Stuart HA bn</t>
+        </is>
+      </c>
+      <c r="AI49" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AJ49" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED reached field margin only noon Jul3, retired w/ trains at night - never fought</t>
+        </is>
+      </c>
+      <c r="AK49" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AL49" s="5" t="inlineStr">
+        <is>
+          <t>train-guard duty Jul1-3; post-battle Williamsport action flagged as out-of-scope context</t>
+        </is>
+      </c>
+      <c r="AM49" s="5" t="inlineStr">
+        <is>
+          <t>'No report nor details of losses made' (formal negative)</t>
+        </is>
+      </c>
       <c r="AN49" s="5" t="n"/>
-      <c r="AO49" s="5" t="n"/>
+      <c r="AO49" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -21805,20 +21841,56 @@
           <t>reg-us-vi-arty</t>
         </is>
       </c>
-      <c r="AB178" s="5" t="n"/>
+      <c r="AB178" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (command/frame grain)</t>
+        </is>
+      </c>
       <c r="AC178" s="5" t="n"/>
       <c r="AD178" s="5" t="n"/>
       <c r="AE178" s="5" t="n"/>
       <c r="AF178" s="5" t="n"/>
-      <c r="AG178" s="5" t="n"/>
-      <c r="AH178" s="5" t="n"/>
-      <c r="AI178" s="5" t="n"/>
-      <c r="AJ178" s="5" t="n"/>
-      <c r="AK178" s="5" t="n"/>
-      <c r="AL178" s="5" t="n"/>
-      <c r="AM178" s="5" t="n"/>
+      <c r="AG178" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-vi-arty-tompkins.md; tablet 9-bty/54-gun vs register 8/48 discrepancy unresolved</t>
+        </is>
+      </c>
+      <c r="AH178" s="5" t="inlineStr">
+        <is>
+          <t>8 batteries (McCartney/Cowan/Harn/Waterman/Adams/Williston/Butler/L.Martin); Col. C.H.Tompkins; NO brigade report - 5 batteries filed own numbered reports (238-242) addressed to Tompkins</t>
+        </is>
+      </c>
+      <c r="AI178" s="5" t="inlineStr">
+        <is>
+          <t>937 men/48 guns (search-stage)</t>
+        </is>
+      </c>
+      <c r="AJ178" s="5" t="inlineStr">
+        <is>
+          <t>Weickert farm reserve ground; Ziegler's Grove convergence (4 batteries) Jul3 post-repulse</t>
+        </is>
+      </c>
+      <c r="AK178" s="5" t="inlineStr">
+        <is>
+          <t>not authored - no consolidated report</t>
+        </is>
+      </c>
+      <c r="AL178" s="5" t="inlineStr">
+        <is>
+          <t>'not actively engaged' except Cowan's; McCartney arrived after repulse</t>
+        </is>
+      </c>
+      <c r="AM178" s="5" t="inlineStr">
+        <is>
+          <t>tablet 12 total, not reconciled vs per-battery (mostly zero) tablets</t>
+        </is>
+      </c>
       <c r="AN178" s="5" t="n"/>
-      <c r="AO178" s="5" t="n"/>
+      <c r="AO178" s="5" t="inlineStr">
+        <is>
+          <t>T2 command record</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -23041,20 +23113,56 @@
           <t>reg-us-ar-1r-2</t>
         </is>
       </c>
-      <c r="AB190" s="5" t="n"/>
+      <c r="AB190" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC190" s="5" t="n"/>
       <c r="AD190" s="5" t="n"/>
       <c r="AE190" s="5" t="n"/>
       <c r="AF190" s="5" t="n"/>
-      <c r="AG190" s="5" t="n"/>
-      <c r="AH190" s="5" t="n"/>
-      <c r="AI190" s="5" t="n"/>
-      <c r="AJ190" s="5" t="n"/>
-      <c r="AK190" s="5" t="n"/>
-      <c r="AL190" s="5" t="n"/>
-      <c r="AM190" s="5" t="n"/>
+      <c r="AG190" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-turnbull.md; TRIAGE CORRECTION - lost guns in combat, strongest contradiction of static-park</t>
+        </is>
+      </c>
+      <c r="AH190" s="5" t="inlineStr">
+        <is>
+          <t>Lt. John C. Turnbull, Batteries F&amp;K 3US; 6x12pdr</t>
+        </is>
+      </c>
+      <c r="AI190" s="5" t="inlineStr">
+        <is>
+          <t>145 men</t>
+        </is>
+      </c>
+      <c r="AJ190" s="5" t="inlineStr">
+        <is>
+          <t>[D Jul1] crest near Meade's HQ; [D Jul2] log house/Emmitsburg Rd w/Humphreys; [D Jul3] Taneytown Rd/Cemetery Hill</t>
+        </is>
+      </c>
+      <c r="AK190" s="5" t="inlineStr">
+        <is>
+          <t>[D] 3-position chain Jul1-3</t>
+        </is>
+      </c>
+      <c r="AL190" s="5" t="inlineStr">
+        <is>
+          <t>engaged Jul2, COMPELLED TO RETIRE, lost 4 guns+45 horses (recaptured)</t>
+        </is>
+      </c>
+      <c r="AM190" s="5" t="inlineStr">
+        <is>
+          <t>1off+8k/14w/1m = 24</t>
+        </is>
+      </c>
       <c r="AN190" s="5" t="n"/>
-      <c r="AO190" s="5" t="n"/>
+      <c r="AO190" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -23217,20 +23325,56 @@
           <t>reg-us-ar-2v-1</t>
         </is>
       </c>
-      <c r="AB192" s="5" t="n"/>
+      <c r="AB192" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (attested-absent)</t>
+        </is>
+      </c>
       <c r="AC192" s="5" t="n"/>
       <c r="AD192" s="5" t="n"/>
       <c r="AE192" s="5" t="n"/>
       <c r="AF192" s="5" t="n"/>
-      <c r="AG192" s="5" t="n"/>
-      <c r="AH192" s="5" t="n"/>
-      <c r="AI192" s="5" t="n"/>
-      <c r="AJ192" s="5" t="n"/>
-      <c r="AK192" s="5" t="n"/>
-      <c r="AL192" s="5" t="n"/>
-      <c r="AM192" s="5" t="n"/>
+      <c r="AG192" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-brooker.md; TRIAGE CONFIRMED (the exception to this pass's corrections)</t>
+        </is>
+      </c>
+      <c r="AH192" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Albert F. Brooker, Battery B 1CT Heavy; 4x4.5in siege rifle</t>
+        </is>
+      </c>
+      <c r="AI192" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AJ192" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED never at Gettysburg - held at Westminster MD (siege ordnance unsuited to rapid movement)</t>
+        </is>
+      </c>
+      <c r="AK192" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AL192" s="5" t="inlineStr">
+        <is>
+          <t>held at Westminster throughout</t>
+        </is>
+      </c>
+      <c r="AM192" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="AN192" s="5" t="n"/>
-      <c r="AO192" s="5" t="n"/>
+      <c r="AO192" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -24521,20 +24665,56 @@
           <t>reg-us-ar-2v-2</t>
         </is>
       </c>
-      <c r="AB206" s="5" t="n"/>
+      <c r="AB206" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (attested-absent)</t>
+        </is>
+      </c>
       <c r="AC206" s="5" t="n"/>
       <c r="AD206" s="5" t="n"/>
       <c r="AE206" s="5" t="n"/>
       <c r="AF206" s="5" t="n"/>
-      <c r="AG206" s="5" t="n"/>
-      <c r="AH206" s="5" t="n"/>
-      <c r="AI206" s="5" t="n"/>
-      <c r="AJ206" s="5" t="n"/>
-      <c r="AK206" s="5" t="n"/>
-      <c r="AL206" s="5" t="n"/>
-      <c r="AM206" s="5" t="n"/>
+      <c r="AG206" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-pratt.md; TRIAGE CONFIRMED; brigade's 8-casualty total therefore belongs entirely to Sterling's+Taft's batteries</t>
+        </is>
+      </c>
+      <c r="AH206" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Franklin A. Pratt, Battery M 1CT Heavy; 4x4.5in siege rifle</t>
+        </is>
+      </c>
+      <c r="AI206" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AJ206" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED never engaged - Westminster MD w/ Brooker's battery</t>
+        </is>
+      </c>
+      <c r="AK206" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AL206" s="5" t="inlineStr">
+        <is>
+          <t>held at Westminster</t>
+        </is>
+      </c>
+      <c r="AM206" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="AN206" s="5" t="n"/>
-      <c r="AO206" s="5" t="n"/>
+      <c r="AO206" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -24893,20 +25073,56 @@
           <t>reg-us-ar-4v-4</t>
         </is>
       </c>
-      <c r="AB209" s="5" t="n"/>
+      <c r="AB209" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC209" s="5" t="n"/>
       <c r="AD209" s="5" t="n"/>
       <c r="AE209" s="5" t="n"/>
       <c r="AF209" s="5" t="n"/>
-      <c r="AG209" s="5" t="n"/>
-      <c r="AH209" s="5" t="n"/>
-      <c r="AI209" s="5" t="n"/>
-      <c r="AJ209" s="5" t="n"/>
-      <c r="AK209" s="5" t="n"/>
-      <c r="AL209" s="5" t="n"/>
-      <c r="AM209" s="5" t="n"/>
+      <c r="AG209" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-ames.md; TRIAGE CORRECTION, closes the 13-battery sweep</t>
+        </is>
+      </c>
+      <c r="AH209" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Nelson Ames, Battery G 1NY; 6x12pdr Nap</t>
+        </is>
+      </c>
+      <c r="AI209" s="5" t="inlineStr">
+        <is>
+          <t>132 men</t>
+        </is>
+      </c>
+      <c r="AJ209" s="5" t="inlineStr">
+        <is>
+          <t>[A 15:00-17:30 Jul2] Peach Orchard w/ III Corps; [D Jul3] Cemetery Ridge w/ II Corps 1st Div</t>
+        </is>
+      </c>
+      <c r="AK209" s="5" t="inlineStr">
+        <is>
+          <t>[A] into Peach Orchard line; [D] relocate to II Corps ground</t>
+        </is>
+      </c>
+      <c r="AL209" s="5" t="inlineStr">
+        <is>
+          <t>3-5:30pm Peach Orchard fight (precisely timed)</t>
+        </is>
+      </c>
+      <c r="AM209" s="5" t="inlineStr">
+        <is>
+          <t>7w</t>
+        </is>
+      </c>
       <c r="AN209" s="5" t="n"/>
-      <c r="AO209" s="5" t="n"/>
+      <c r="AO209" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -26437,20 +26653,56 @@
           <t>reg-us-ar-4v-1</t>
         </is>
       </c>
-      <c r="AB220" s="5" t="n"/>
+      <c r="AB220" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC220" s="5" t="n"/>
       <c r="AD220" s="5" t="n"/>
       <c r="AE220" s="5" t="n"/>
       <c r="AF220" s="5" t="n"/>
-      <c r="AG220" s="5" t="n"/>
-      <c r="AH220" s="5" t="n"/>
-      <c r="AI220" s="5" t="n"/>
-      <c r="AJ220" s="5" t="n"/>
-      <c r="AK220" s="5" t="n"/>
-      <c r="AL220" s="5" t="n"/>
-      <c r="AM220" s="5" t="n"/>
+      <c r="AG220" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-dow.md; TRIAGE CORRECTION</t>
+        </is>
+      </c>
+      <c r="AH220" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Edwin B. Dow, 6th Maine Battery(F); 4x12pdr Nap</t>
+        </is>
+      </c>
+      <c r="AI220" s="5" t="inlineStr">
+        <is>
+          <t>103 men</t>
+        </is>
+      </c>
+      <c r="AJ220" s="5" t="inlineStr">
+        <is>
+          <t>detached under McGilvery (Fitzhugh's own report)</t>
+        </is>
+      </c>
+      <c r="AK220" s="5" t="inlineStr">
+        <is>
+          <t>not authored beyond detachment</t>
+        </is>
+      </c>
+      <c r="AL220" s="5" t="inlineStr">
+        <is>
+          <t>Jul3 pre-charge cannonade duel</t>
+        </is>
+      </c>
+      <c r="AM220" s="5" t="inlineStr">
+        <is>
+          <t>13w (all attributed to the cannonade)</t>
+        </is>
+      </c>
       <c r="AN220" s="5" t="n"/>
-      <c r="AO220" s="5" t="n"/>
+      <c r="AO220" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -26561,20 +26813,56 @@
           <t>reg-us-ar-3v-1</t>
         </is>
       </c>
-      <c r="AB221" s="5" t="n"/>
+      <c r="AB221" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC221" s="5" t="n"/>
       <c r="AD221" s="5" t="n"/>
       <c r="AE221" s="5" t="n"/>
       <c r="AF221" s="5" t="n"/>
-      <c r="AG221" s="5" t="n"/>
-      <c r="AH221" s="5" t="n"/>
-      <c r="AI221" s="5" t="n"/>
-      <c r="AJ221" s="5" t="n"/>
-      <c r="AK221" s="5" t="n"/>
-      <c r="AL221" s="5" t="n"/>
-      <c r="AM221" s="5" t="n"/>
+      <c r="AG221" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-edgell.md; matches Taft's-battery triage-mismatch pattern exactly</t>
+        </is>
+      </c>
+      <c r="AH221" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Frederick M. Edgell, 1st NH Battery; own report</t>
+        </is>
+      </c>
+      <c r="AI221" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ221" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:30 Jul2] Cemetery Hill nr seminary; [D Jul3] relocated to cornfield nr Baltimore turnpike</t>
+        </is>
+      </c>
+      <c r="AK221" s="5" t="inlineStr">
+        <is>
+          <t>[C] into position; [D] relocation</t>
+        </is>
+      </c>
+      <c r="AL221" s="5" t="inlineStr">
+        <is>
+          <t>counter-battery fire; 105rds sub-total/353 total (2 scopes, not conflict)</t>
+        </is>
+      </c>
+      <c r="AM221" s="5" t="inlineStr">
+        <is>
+          <t>3w(1 serious)/3horses k</t>
+        </is>
+      </c>
       <c r="AN221" s="5" t="n"/>
-      <c r="AO221" s="5" t="n"/>
+      <c r="AO221" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -26685,20 +26973,56 @@
           <t>reg-us-ha-1-5</t>
         </is>
       </c>
-      <c r="AB222" s="5" t="n"/>
+      <c r="AB222" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC222" s="5" t="n"/>
       <c r="AD222" s="5" t="n"/>
       <c r="AE222" s="5" t="n"/>
       <c r="AF222" s="5" t="n"/>
-      <c r="AG222" s="5" t="n"/>
-      <c r="AH222" s="5" t="n"/>
-      <c r="AI222" s="5" t="n"/>
-      <c r="AJ222" s="5" t="n"/>
-      <c r="AK222" s="5" t="n"/>
-      <c r="AL222" s="5" t="n"/>
-      <c r="AM222" s="5" t="n"/>
+      <c r="AG222" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-elder.md; 3rd independent Union SCF corroboration (ED-72)</t>
+        </is>
+      </c>
+      <c r="AH222" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Samuel S. Elder, Battery E 4US; 4x3in rifle (sub-6-gun)</t>
+        </is>
+      </c>
+      <c r="AI222" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ222" s="5" t="inlineStr">
+        <is>
+          <t>[C Jun29] detached to 3rd Cav Div; [D Jul3] Bushman Hill SW of Round Top; sheet-crop confirmed beside Farnsworth's Bde</t>
+        </is>
+      </c>
+      <c r="AK222" s="5" t="inlineStr">
+        <is>
+          <t>[C Jun29] detachment; [D Jul3] into position</t>
+        </is>
+      </c>
+      <c r="AL222" s="5" t="inlineStr">
+        <is>
+          <t>South Cavalry Field ~17:30, CA-SCF-2</t>
+        </is>
+      </c>
+      <c r="AM222" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="AN222" s="5" t="n"/>
-      <c r="AO222" s="5" t="n"/>
+      <c r="AO222" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -26969,20 +27293,56 @@
           <t>reg-us-ha-2-2</t>
         </is>
       </c>
-      <c r="AB224" s="5" t="n"/>
+      <c r="AB224" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC224" s="5" t="n"/>
       <c r="AD224" s="5" t="n"/>
       <c r="AE224" s="5" t="n"/>
       <c r="AF224" s="5" t="n"/>
-      <c r="AG224" s="5" t="n"/>
-      <c r="AH224" s="5" t="n"/>
-      <c r="AI224" s="5" t="n"/>
-      <c r="AJ224" s="5" t="n"/>
-      <c r="AK224" s="5" t="n"/>
-      <c r="AL224" s="5" t="n"/>
-      <c r="AM224" s="5" t="n"/>
+      <c r="AG224" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-graham.md</t>
+        </is>
+      </c>
+      <c r="AH224" s="5" t="inlineStr">
+        <is>
+          <t>Capt. (bvt LtCol) William M. Graham, Battery K 1US; 6x3in rifle</t>
+        </is>
+      </c>
+      <c r="AI224" s="5" t="inlineStr">
+        <is>
+          <t>114 men (search-summary)</t>
+        </is>
+      </c>
+      <c r="AJ224" s="5" t="inlineStr">
+        <is>
+          <t>South Cavalry Field Jul3, left w/ cavalry, engaged Farnsworth's/Merritt's attacks</t>
+        </is>
+      </c>
+      <c r="AK224" s="5" t="inlineStr">
+        <is>
+          <t>not authored</t>
+        </is>
+      </c>
+      <c r="AL224" s="5" t="inlineStr">
+        <is>
+          <t>SCF action alongside Farnsworth's/Merritt's brigades</t>
+        </is>
+      </c>
+      <c r="AM224" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="AN224" s="5" t="n"/>
-      <c r="AO224" s="5" t="n"/>
+      <c r="AO224" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -27341,20 +27701,56 @@
           <t>reg-us-ar-3v-4</t>
         </is>
       </c>
-      <c r="AB227" s="5" t="n"/>
+      <c r="AB227" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC227" s="5" t="n"/>
       <c r="AD227" s="5" t="n"/>
       <c r="AE227" s="5" t="n"/>
       <c r="AF227" s="5" t="n"/>
-      <c r="AG227" s="5" t="n"/>
-      <c r="AH227" s="5" t="n"/>
-      <c r="AI227" s="5" t="n"/>
-      <c r="AJ227" s="5" t="n"/>
-      <c r="AK227" s="5" t="n"/>
-      <c r="AL227" s="5" t="n"/>
-      <c r="AM227" s="5" t="n"/>
+      <c r="AG227" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-hill.md; TRIAGE CORRECTION, per-day casualty date split</t>
+        </is>
+      </c>
+      <c r="AH227" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Wallace Hill, Battery C 1WV; 4x10pdr Parrott (sub-6-gun)</t>
+        </is>
+      </c>
+      <c r="AI227" s="5" t="inlineStr">
+        <is>
+          <t>124 men</t>
+        </is>
+      </c>
+      <c r="AJ227" s="5" t="inlineStr">
+        <is>
+          <t>Cemetery Hill, right on cemetery/left near stonewall by road</t>
+        </is>
+      </c>
+      <c r="AK227" s="5" t="inlineStr">
+        <is>
+          <t>not authored - single position only</t>
+        </is>
+      </c>
+      <c r="AL227" s="5" t="inlineStr">
+        <is>
+          <t>fought Jul2-3</t>
+        </is>
+      </c>
+      <c r="AM227" s="5" t="inlineStr">
+        <is>
+          <t>2k(named+dated: Braddock Jul2, Lacy Jul3)/2w</t>
+        </is>
+      </c>
       <c r="AN227" s="5" t="n"/>
-      <c r="AO227" s="5" t="n"/>
+      <c r="AO227" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -27713,20 +28109,56 @@
           <t>reg-us-ar-1r-1</t>
         </is>
       </c>
-      <c r="AB230" s="5" t="n"/>
+      <c r="AB230" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC230" s="5" t="n"/>
       <c r="AD230" s="5" t="n"/>
       <c r="AE230" s="5" t="n"/>
       <c r="AF230" s="5" t="n"/>
-      <c r="AG230" s="5" t="n"/>
-      <c r="AH230" s="5" t="n"/>
-      <c r="AI230" s="5" t="n"/>
-      <c r="AJ230" s="5" t="n"/>
-      <c r="AK230" s="5" t="n"/>
-      <c r="AL230" s="5" t="n"/>
-      <c r="AM230" s="5" t="n"/>
+      <c r="AG230" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-eakin.md; corrects static-park triage</t>
+        </is>
+      </c>
+      <c r="AH230" s="5" t="inlineStr">
+        <is>
+          <t>Lt. Chandler P. Eakin (w Jul2), Lt. Philip D. Mason succ.; Battery H 1US; 6x12pdr</t>
+        </is>
+      </c>
+      <c r="AI230" s="5" t="inlineStr">
+        <is>
+          <t>153 men</t>
+        </is>
+      </c>
+      <c r="AJ230" s="5" t="inlineStr">
+        <is>
+          <t>Cemetery Hill facing Emmitsburg Rd</t>
+        </is>
+      </c>
+      <c r="AK230" s="5" t="inlineStr">
+        <is>
+          <t>not authored - no leg located</t>
+        </is>
+      </c>
+      <c r="AL230" s="5" t="inlineStr">
+        <is>
+          <t>engaged Jul2-3 (TRIAGE CORRECTION: was static-park, actually 2-day fight)</t>
+        </is>
+      </c>
+      <c r="AM230" s="5" t="inlineStr">
+        <is>
+          <t>1k/1off+7w/1m = 10 total</t>
+        </is>
+      </c>
       <c r="AN230" s="5" t="n"/>
-      <c r="AO230" s="5" t="n"/>
+      <c r="AO230" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -27837,20 +28269,56 @@
           <t>reg-us-ar-3v-2</t>
         </is>
       </c>
-      <c r="AB231" s="5" t="n"/>
+      <c r="AB231" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC231" s="5" t="n"/>
       <c r="AD231" s="5" t="n"/>
       <c r="AE231" s="5" t="n"/>
       <c r="AF231" s="5" t="n"/>
-      <c r="AG231" s="5" t="n"/>
-      <c r="AH231" s="5" t="n"/>
-      <c r="AI231" s="5" t="n"/>
-      <c r="AJ231" s="5" t="n"/>
-      <c r="AK231" s="5" t="n"/>
-      <c r="AL231" s="5" t="n"/>
-      <c r="AM231" s="5" t="n"/>
+      <c r="AG231" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-norton-1oh.md; TRIAGE CORRECTION</t>
+        </is>
+      </c>
+      <c r="AH231" s="5" t="inlineStr">
+        <is>
+          <t>Lt. George W. Norton, Battery H 1OH ('Huntington's Ohio Battery'); 6x3in Ord Rifle; DISTINCT from the LRT-witness Norton on us-btty-rittenhouse.md</t>
+        </is>
+      </c>
+      <c r="AI231" s="5" t="inlineStr">
+        <is>
+          <t>123 men</t>
+        </is>
+      </c>
+      <c r="AJ231" s="5" t="inlineStr">
+        <is>
+          <t>Cemetery Hill, relieved a 'badly shot up' battery in place, held through the close</t>
+        </is>
+      </c>
+      <c r="AK231" s="5" t="inlineStr">
+        <is>
+          <t>[D] arrival-&gt;relief-in-place</t>
+        </is>
+      </c>
+      <c r="AL231" s="5" t="inlineStr">
+        <is>
+          <t>relief-in-place + sustained defense</t>
+        </is>
+      </c>
+      <c r="AM231" s="5" t="inlineStr">
+        <is>
+          <t>2k(named: Schram,Kirsh)/1mw(named: Edmunds)/4w</t>
+        </is>
+      </c>
       <c r="AN231" s="5" t="n"/>
-      <c r="AO231" s="5" t="n"/>
+      <c r="AO231" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -28405,20 +28873,56 @@
           <t>reg-us-ar-4v-2</t>
         </is>
       </c>
-      <c r="AB235" s="5" t="n"/>
+      <c r="AB235" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC235" s="5" t="n"/>
       <c r="AD235" s="5" t="n"/>
       <c r="AE235" s="5" t="n"/>
       <c r="AF235" s="5" t="n"/>
-      <c r="AG235" s="5" t="n"/>
-      <c r="AH235" s="5" t="n"/>
-      <c r="AI235" s="5" t="n"/>
-      <c r="AJ235" s="5" t="n"/>
-      <c r="AK235" s="5" t="n"/>
-      <c r="AL235" s="5" t="n"/>
-      <c r="AM235" s="5" t="n"/>
+      <c r="AG235" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-rigby.md; TRIAGE CORRECTION</t>
+        </is>
+      </c>
+      <c r="AH235" s="5" t="inlineStr">
+        <is>
+          <t>Capt. James H. Rigby, Battery A 1MD; 6x ord rifle; distinct from CSA '1st Maryland Battery' (Dement) - collision resolved</t>
+        </is>
+      </c>
+      <c r="AI235" s="5" t="inlineStr">
+        <is>
+          <t>4off+102men</t>
+        </is>
+      </c>
+      <c r="AJ235" s="5" t="inlineStr">
+        <is>
+          <t>Powers Hill per Tyler's own order (XII Corps ground)</t>
+        </is>
+      </c>
+      <c r="AK235" s="5" t="inlineStr">
+        <is>
+          <t>not authored beyond assignment</t>
+        </is>
+      </c>
+      <c r="AL235" s="5" t="inlineStr">
+        <is>
+          <t>Culp's Hill infantry + Benner's Hill CSA arty duel; 211 rds fired</t>
+        </is>
+      </c>
+      <c r="AM235" s="5" t="inlineStr">
+        <is>
+          <t>0 (engaged but zero-loss)</t>
+        </is>
+      </c>
       <c r="AN235" s="5" t="n"/>
-      <c r="AO235" s="5" t="n"/>
+      <c r="AO235" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -28973,20 +29477,56 @@
           <t>reg-us-ar-2v-3</t>
         </is>
       </c>
-      <c r="AB239" s="5" t="n"/>
+      <c r="AB239" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC239" s="5" t="n"/>
       <c r="AD239" s="5" t="n"/>
       <c r="AE239" s="5" t="n"/>
       <c r="AF239" s="5" t="n"/>
-      <c r="AG239" s="5" t="n"/>
-      <c r="AH239" s="5" t="n"/>
-      <c r="AI239" s="5" t="n"/>
-      <c r="AJ239" s="5" t="n"/>
-      <c r="AK239" s="5" t="n"/>
-      <c r="AL239" s="5" t="n"/>
-      <c r="AM239" s="5" t="n"/>
+      <c r="AG239" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-sterling.md; TRIAGE CORRECTION</t>
+        </is>
+      </c>
+      <c r="AH239" s="5" t="inlineStr">
+        <is>
+          <t>Capt. John William Sterling, 2CT Light Battery; UNIQUE ordnance - 4x14pdr James Rifle+2x12pdr howitzer, only such battery at Gettysburg</t>
+        </is>
+      </c>
+      <c r="AI239" s="5" t="inlineStr">
+        <is>
+          <t>106 men</t>
+        </is>
+      </c>
+      <c r="AJ239" s="5" t="inlineStr">
+        <is>
+          <t>[D Jul2] reinforced III Corps line, retired into McGilvery's composite line left of II Corps</t>
+        </is>
+      </c>
+      <c r="AK239" s="5" t="inlineStr">
+        <is>
+          <t>[D] reinforce-&gt;retire to McGilvery line</t>
+        </is>
+      </c>
+      <c r="AL239" s="5" t="inlineStr">
+        <is>
+          <t>McGilvery-line reinforcement</t>
+        </is>
+      </c>
+      <c r="AM239" s="5" t="inlineStr">
+        <is>
+          <t>3w/2m = 5</t>
+        </is>
+      </c>
       <c r="AN239" s="5" t="n"/>
-      <c r="AO239" s="5" t="n"/>
+      <c r="AO239" s="5" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -29345,20 +29885,56 @@
           <t>reg-us-ar-2v-4</t>
         </is>
       </c>
-      <c r="AB242" s="5" t="n"/>
+      <c r="AB242" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC242" s="5" t="n"/>
       <c r="AD242" s="5" t="n"/>
       <c r="AE242" s="5" t="n"/>
       <c r="AF242" s="5" t="n"/>
-      <c r="AG242" s="5" t="n"/>
-      <c r="AH242" s="5" t="n"/>
-      <c r="AI242" s="5" t="n"/>
-      <c r="AJ242" s="5" t="n"/>
-      <c r="AK242" s="5" t="n"/>
-      <c r="AL242" s="5" t="n"/>
-      <c r="AM242" s="5" t="n"/>
+      <c r="AG242" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-taft.md; THE PASS'S LARGEST TRIAGE/RESEARCH MISMATCH - own commander's report was already the parent brigade dossier's primary source</t>
+        </is>
+      </c>
+      <c r="AH242" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Elijah D. Taft (also 2VBde cmdr), 5th NY Battery; own report No.325</t>
+        </is>
+      </c>
+      <c r="AI242" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ242" s="5" t="inlineStr">
+        <is>
+          <t>[C] Taneytown-&gt;10:30am arrival-&gt;4pm cemetery-&gt;5pm position, reporting direct to Howard (XI Corps)</t>
+        </is>
+      </c>
+      <c r="AK242" s="5" t="inlineStr">
+        <is>
+          <t>[B] staged approach; [D] return march Jul5</t>
+        </is>
+      </c>
+      <c r="AL242" s="5" t="inlineStr">
+        <is>
+          <t>counter-battery+infantry fire Jul2; sustained fire Jul3, 20pdr Parrott muzzle burst; itemized rds (80/63/32/382/557)</t>
+        </is>
+      </c>
+      <c r="AM242" s="5" t="inlineStr">
+        <is>
+          <t>4 individually-timed pins (Begg mw died Jul7, Thalheimer mw died midnight Jul3, Dillon slight, Wittenberg severe); brigade tablet total 8 in tension w/ 4 named</t>
+        </is>
+      </c>
       <c r="AN242" s="5" t="n"/>
-      <c r="AO242" s="5" t="n"/>
+      <c r="AO242" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -29469,20 +30045,56 @@
           <t>reg-us-ar-1r-3</t>
         </is>
       </c>
-      <c r="AB243" s="5" t="n"/>
+      <c r="AB243" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC243" s="5" t="n"/>
       <c r="AD243" s="5" t="n"/>
       <c r="AE243" s="5" t="n"/>
       <c r="AF243" s="5" t="n"/>
-      <c r="AG243" s="5" t="n"/>
-      <c r="AH243" s="5" t="n"/>
-      <c r="AI243" s="5" t="n"/>
-      <c r="AJ243" s="5" t="n"/>
-      <c r="AK243" s="5" t="n"/>
-      <c r="AL243" s="5" t="n"/>
-      <c r="AM243" s="5" t="n"/>
+      <c r="AG243" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-evanthomas.md; TRIAGE CORRECTION, richest of the 3 1st-Regular corrections</t>
+        </is>
+      </c>
+      <c r="AH243" s="5" t="inlineStr">
+        <is>
+          <t>Lt. (bvt Maj) Evan Thomas, Battery C 4US; 6x12pdr; son of Adj-Gen Lorenzo Thomas; k 1873 vs Modoc</t>
+        </is>
+      </c>
+      <c r="AI243" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ243" s="5" t="inlineStr">
+        <is>
+          <t>[D Jul2] Leister House crest near Meade's HQ; [D Jul3am] unchanged, engaged CSA arty across Seminary Ridge; slight shift pre-charge; post-bombardment-&gt;Arty Reserve</t>
+        </is>
+      </c>
+      <c r="AK243" s="5" t="inlineStr">
+        <is>
+          <t>[D] 3-leg chain Jul2-3</t>
+        </is>
+      </c>
+      <c r="AL243" s="5" t="inlineStr">
+        <is>
+          <t>'actively engaged' Jul2; Jul3 direct-hit caisson explosion, 3 more blew, drew CSA cheer; 14VT collateral casualties nearby</t>
+        </is>
+      </c>
+      <c r="AM243" s="5" t="inlineStr">
+        <is>
+          <t>1k/1off+16w = 18, +2 named later deaths (Campbell, McNeal)</t>
+        </is>
+      </c>
       <c r="AN243" s="5" t="n"/>
-      <c r="AO243" s="5" t="n"/>
+      <c r="AO243" s="5" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -37709,20 +38321,56 @@
           <t>reg-us-v-3-2</t>
         </is>
       </c>
-      <c r="AB302" s="5" t="n"/>
+      <c r="AB302" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC302" s="5" t="n"/>
       <c r="AD302" s="5" t="n"/>
       <c r="AE302" s="5" t="n"/>
       <c r="AF302" s="5" t="n"/>
-      <c r="AG302" s="5" t="n"/>
-      <c r="AH302" s="5" t="n"/>
-      <c r="AI302" s="5" t="n"/>
-      <c r="AJ302" s="5" t="n"/>
-      <c r="AK302" s="5" t="n"/>
-      <c r="AL302" s="5" t="n"/>
-      <c r="AM302" s="5" t="n"/>
+      <c r="AG302" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-v-3-2-fisher.md; independent-discovery claim flagged not adjudicated vs Rice/Chamberlain (403-blocked source)</t>
+        </is>
+      </c>
+      <c r="AH302" s="5" t="inlineStr">
+        <is>
+          <t>Col. Joseph W. Fisher, 5th/9th/10th/11th/12th PA Reserves; own report No.213-class</t>
+        </is>
+      </c>
+      <c r="AI302" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ302" s="5" t="inlineStr">
+        <is>
+          <t>[C ~22:00] Big Round Top occupation; stone wall built overnight</t>
+        </is>
+      </c>
+      <c r="AK302" s="5" t="inlineStr">
+        <is>
+          <t>[D] march to the extreme left July 2; [A ~22:00] ascent of Big Round Top w/ 20th Maine</t>
+        </is>
+      </c>
+      <c r="AL302" s="5" t="inlineStr">
+        <is>
+          <t>over 30 prisoners; 1000+ stand of arms claimed, 80 CSA dead buried (own report, unverified vs CSA side)</t>
+        </is>
+      </c>
+      <c r="AM302" s="5" t="inlineStr">
+        <is>
+          <t>55 (1off+5men k/3off+46w) = McCandless 155 + Fisher 55 = Crawford 210 exact</t>
+        </is>
+      </c>
       <c r="AN302" s="5" t="n"/>
-      <c r="AO302" s="5" t="n"/>
+      <c r="AO302" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -41193,20 +41841,56 @@
           <t>reg-us-xi-2-2</t>
         </is>
       </c>
-      <c r="AB324" s="5" t="n"/>
+      <c r="AB324" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AC324" s="5" t="n"/>
       <c r="AD324" s="5" t="n"/>
       <c r="AE324" s="5" t="n"/>
       <c r="AF324" s="5" t="n"/>
-      <c r="AG324" s="5" t="n"/>
-      <c r="AH324" s="5" t="n"/>
-      <c r="AI324" s="5" t="n"/>
-      <c r="AJ324" s="5" t="n"/>
-      <c r="AK324" s="5" t="n"/>
-      <c r="AL324" s="5" t="n"/>
-      <c r="AM324" s="5" t="n"/>
+      <c r="AG324" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-2-2-smith.md; 33MA/Avery-repulse cross-ref flagged not verified</t>
+        </is>
+      </c>
+      <c r="AH324" s="5" t="inlineStr">
+        <is>
+          <t>Col. Orland Smith, 33MA/136NY/55OH/73OH; own report OR27/1 pp.722-725; identity verified NOT W.Smith CSA</t>
+        </is>
+      </c>
+      <c r="AI324" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AJ324" s="5" t="inlineStr">
+        <is>
+          <t>[C ~14:00 Jul1] Cemetery Hill wall, Emmitsburg/Taneytown Rds; von Steinwehr calls it 'First Bde' internally, Smith's own report says 'Second Bde' matching register</t>
+        </is>
+      </c>
+      <c r="AK324" s="5" t="inlineStr">
+        <is>
+          <t>[C] Jun12-Jul1 full march itinerary; 38mi/24.5hrs Boonsborough-Emmitsburg</t>
+        </is>
+      </c>
+      <c r="AL324" s="5" t="inlineStr">
+        <is>
+          <t>continuous skirmish Jul1-3; no direct assault Jul2 night; Jul3 assault redirected to II Corps</t>
+        </is>
+      </c>
+      <c r="AM324" s="5" t="inlineStr">
+        <is>
+          <t>REPORT-VS-TABLET CONFLICT: tablet 348 (51k/278w/19m) vs report 345 (66k/259w/26m) - every category disagrees, not adjudicated</t>
+        </is>
+      </c>
       <c r="AN324" s="5" t="n"/>
-      <c r="AO324" s="5" t="n"/>
+      <c r="AO324" s="5" t="inlineStr">
+        <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -9518,29 +9518,29 @@
         <v>384</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="H88" s="3">
         <f>IF(F88=0,0,1-G88/F88)</f>
         <v/>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>0</v>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -14831,10 +14831,10 @@
         <v>8</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M132" s="2" t="n">
         <v>0</v>
@@ -27619,26 +27619,26 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H227" s="3">
         <f>IF(F227=0,0,1-G227/F227)</f>
         <v/>
       </c>
       <c r="I227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L227" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M227" s="2" t="n">
         <v>0</v>
@@ -27683,7 +27683,7 @@
       </c>
       <c r="X227" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y227" s="2" t="inlineStr">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="S236" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T236" s="2" t="n">
         <v>0</v>
@@ -29803,32 +29803,32 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G242" s="2" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H242" s="3">
         <f>IF(F242=0,0,1-G242/F242)</f>
         <v/>
       </c>
       <c r="I242" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L242" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N242" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>0</v>
@@ -39227,7 +39227,7 @@
         <v>5</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>121.7</v>
+        <v>217</v>
       </c>
       <c r="P308" s="2" t="n">
         <v>0</v>
@@ -42402,23 +42402,23 @@
         <v>1320</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>1320</v>
+        <v>1309</v>
       </c>
       <c r="H328" s="3">
         <f>IF(F328=0,0,1-G328/F328)</f>
         <v/>
       </c>
       <c r="I328" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J328" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K328" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L328" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" s="2" t="n">
         <v>0</v>
@@ -42463,12 +42463,12 @@
       </c>
       <c r="X328" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Y328" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="Z328" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H102" s="3">
         <f>IF(F102=0,0,1-G102/F102)</f>
@@ -11275,10 +11275,10 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H103" s="3">
         <f>IF(F103=0,0,1-G103/F103)</f>
@@ -11875,10 +11875,10 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H108" s="3">
         <f>IF(F108=0,0,1-G108/F108)</f>
@@ -12955,10 +12955,10 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H117" s="3">
         <f>IF(F117=0,0,1-G117/F117)</f>
@@ -13555,10 +13555,10 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H122" s="3">
         <f>IF(F122=0,0,1-G122/F122)</f>
@@ -13798,14 +13798,14 @@
         <v>440</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="H124" s="3">
         <f>IF(F124=0,0,1-G124/F124)</f>
         <v/>
       </c>
       <c r="I124" s="2" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>7</v>
@@ -13918,14 +13918,14 @@
         <v>440</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="H125" s="3">
         <f>IF(F125=0,0,1-G125/F125)</f>
         <v/>
       </c>
       <c r="I125" s="2" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>7</v>
@@ -14658,14 +14658,14 @@
         <v>880</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>780</v>
+        <v>732</v>
       </c>
       <c r="H131" s="3">
         <f>IF(F131=0,0,1-G131/F131)</f>
         <v/>
       </c>
       <c r="I131" s="2" t="n">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>8</v>
@@ -15135,10 +15135,10 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>1480</v>
+        <v>1427</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>539</v>
+        <v>486</v>
       </c>
       <c r="H134" s="3">
         <f>IF(F134=0,0,1-G134/F134)</f>
@@ -15148,10 +15148,10 @@
         <v>941</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>9</v>
@@ -15160,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O134" s="2" t="n">
         <v>2349.8</v>
@@ -17871,17 +17871,17 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>651</v>
+        <v>315</v>
       </c>
       <c r="H151" s="3">
         <f>IF(F151=0,0,1-G151/F151)</f>
         <v/>
       </c>
       <c r="I151" s="2" t="n">
-        <v>599</v>
+        <v>185</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>9</v>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -10435,26 +10435,26 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="H96" s="3">
         <f>IF(F96=0,0,1-G96/F96)</f>
         <v/>
       </c>
       <c r="I96" s="2" t="n">
-        <v>360</v>
+        <v>226</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M96" s="2" t="n">
         <v>0</v>
@@ -10555,17 +10555,17 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="H97" s="3">
         <f>IF(F97=0,0,1-G97/F97)</f>
         <v/>
       </c>
       <c r="I97" s="2" t="n">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>9</v>
@@ -11755,26 +11755,26 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="H107" s="3">
         <f>IF(F107=0,0,1-G107/F107)</f>
         <v/>
       </c>
       <c r="I107" s="2" t="n">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M107" s="2" t="n">
         <v>0</v>
@@ -11995,17 +11995,17 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="H109" s="3">
         <f>IF(F109=0,0,1-G109/F109)</f>
         <v/>
       </c>
       <c r="I109" s="2" t="n">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>8</v>
@@ -12355,17 +12355,17 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="H112" s="3">
         <f>IF(F112=0,0,1-G112/F112)</f>
         <v/>
       </c>
       <c r="I112" s="2" t="n">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>8</v>
@@ -12475,17 +12475,17 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="H113" s="3">
         <f>IF(F113=0,0,1-G113/F113)</f>
         <v/>
       </c>
       <c r="I113" s="2" t="n">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>9</v>
@@ -12595,17 +12595,17 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="H114" s="3">
         <f>IF(F114=0,0,1-G114/F114)</f>
         <v/>
       </c>
       <c r="I114" s="2" t="n">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>9</v>
@@ -12835,17 +12835,17 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="H116" s="3">
         <f>IF(F116=0,0,1-G116/F116)</f>
         <v/>
       </c>
       <c r="I116" s="2" t="n">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>8</v>
@@ -14815,26 +14815,26 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>2000</v>
+        <v>1293</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>603</v>
+        <v>387</v>
       </c>
       <c r="H132" s="3">
         <f>IF(F132=0,0,1-G132/F132)</f>
         <v/>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1397</v>
+        <v>906</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>9</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M132" s="2" t="n">
         <v>0</v>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="AI132" s="5" t="inlineStr">
         <is>
-          <t>2,000 'present first day' (stone-sentinels, scope caveat); 11th Miss DETACHED Jul 1 (division train guard, primary) - fresh regiment atop Jul 1 survivors on Jul 3</t>
+          <t>2,000 'present first day' (stone-sentinels, scope caveat); 11th Miss DETACHED Jul 1 (division train guard, primary) - fresh regiment atop Jul 1 survivors on Jul 3 -- ED-75 (2026-07-13): PROVISIONAL-ADOPTED placeholder (1,293 = ~900 three-regiment survivors + 393 11th Miss's own tablet-corroborated July-3 strength; envelope 1,100-1,550, INFERRED), superseded on arrival by Busey &amp; Martin page-level figures (owner purchase intent stated)</t>
         </is>
       </c>
       <c r="AJ132" s="5" t="inlineStr">
@@ -15471,26 +15471,26 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>595</v>
+        <v>268</v>
       </c>
       <c r="H136" s="3">
         <f>IF(F136=0,0,1-G136/F136)</f>
         <v/>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1405</v>
+        <v>632</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M136" s="2" t="n">
         <v>0</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AI136" s="5" t="inlineStr">
         <is>
-          <t>2,000 'present on the first day' (stone-sentinels, Jul-1 scope caveat); 26NC regt primary: 800+ -&gt; 216 unhurt (Jul 1) -&gt; ~80 (Jul 4) (young-26nc); Jul 3 basis ~900 [B subtraction, open for primary]</t>
+          <t>2,000 'present on the first day' (stone-sentinels, Jul-1 scope caveat); 26NC regt primary: 800+ -&gt; 216 unhurt (Jul 1) -&gt; ~80 (Jul 4) (young-26nc); Jul 3 basis ~900 [B subtraction] -- ED-75 (2026-07-13): PROVISIONAL-ADOPTED placeholder (900, envelope 750-1,050, INFERRED), superseded on arrival by Busey &amp; Martin page-level figures (owner purchase intent stated)</t>
         </is>
       </c>
       <c r="AJ136" s="5" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AP$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Units'!$A$1:$AP$340</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP338"/>
+  <dimension ref="A1:AP340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -16501,22 +16501,22 @@
         <v>1109</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P140" s="2" t="n">
-        <v>6194</v>
+        <v>9336</v>
       </c>
       <c r="Q140" s="2" t="n">
         <v>5126</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="T140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U140" s="2" t="n">
         <v>0</v>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17491,10 +17491,10 @@
         <v>420</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M146" s="2" t="n">
         <v>1</v>
@@ -17503,10 +17503,10 @@
         <v>0</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P146" s="2" t="n">
-        <v>1907.2</v>
+        <v>2022.7</v>
       </c>
       <c r="Q146" s="2" t="n">
         <v>514</v>
@@ -17518,11 +17518,11 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>line/scattered</t>
         </is>
       </c>
       <c r="T146" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U146" s="2" t="n">
         <v>0</v>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G153" s="2" t="n">
@@ -18646,10 +18646,10 @@
         <v>390</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M153" s="2" t="n">
         <v>1</v>
@@ -18658,10 +18658,10 @@
         <v>0</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>1373.6</v>
+        <v>1387.5</v>
       </c>
       <c r="Q153" s="2" t="n">
         <v>626.5</v>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="T153" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U153" s="2" t="n">
         <v>0</v>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
@@ -18811,10 +18811,10 @@
         <v>694</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M154" s="2" t="n">
         <v>4</v>
@@ -18823,10 +18823,10 @@
         <v>0</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P154" s="2" t="n">
-        <v>6147.6</v>
+        <v>6759.4</v>
       </c>
       <c r="Q154" s="2" t="n">
         <v>4786.7</v>
@@ -18842,7 +18842,7 @@
         </is>
       </c>
       <c r="T154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U154" s="2" t="n">
         <v>0</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -19801,10 +19801,10 @@
         <v>140</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L160" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M160" s="2" t="n">
         <v>2</v>
@@ -19813,10 +19813,10 @@
         <v>0</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P160" s="2" t="n">
-        <v>3193.5</v>
+        <v>3872.2</v>
       </c>
       <c r="Q160" s="2" t="n">
         <v>2907.4</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="T160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U160" s="2" t="n">
         <v>0</v>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
@@ -19966,22 +19966,22 @@
         <v>680</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P161" s="2" t="n">
-        <v>1622</v>
+        <v>1823.7</v>
       </c>
       <c r="Q161" s="2" t="n">
         <v>1053</v>
@@ -19993,11 +19993,11 @@
       </c>
       <c r="S161" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>line/scattered</t>
         </is>
       </c>
       <c r="T161" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U161" s="2" t="n">
         <v>0</v>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -20131,10 +20131,10 @@
         <v>330</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M162" s="2" t="n">
         <v>1</v>
@@ -20143,10 +20143,10 @@
         <v>0</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>745.1</v>
+        <v>981.1</v>
       </c>
       <c r="Q162" s="2" t="n">
         <v>395.6</v>
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="T162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U162" s="2" t="n">
         <v>0</v>
@@ -22539,12 +22539,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-arty</t>
+          <t>reg-us-v-b1</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Artillery Brigade, XII Corps</t>
+          <t>3rd Massachusetts Battery (C)</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>artillery-brigade</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -22582,16 +22582,16 @@
       <c r="T180" s="2" t="inlineStr"/>
       <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W180" s="2" t="inlineStr">
         <is>
-          <t>Artillery Brigade</t>
-        </is>
-      </c>
-      <c r="X180" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>3rd Massachusetts</t>
+        </is>
+      </c>
+      <c r="X180" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr"/>
@@ -22607,69 +22607,33 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-arty</t>
-        </is>
-      </c>
-      <c r="AC180" s="5" t="inlineStr">
-        <is>
-          <t>not-yet-cast (group grain)</t>
-        </is>
-      </c>
+          <t>reg-us-v-b1</t>
+        </is>
+      </c>
+      <c r="AC180" s="5" t="n"/>
       <c r="AD180" s="5" t="n"/>
       <c r="AE180" s="5" t="n"/>
       <c r="AF180" s="5" t="n"/>
       <c r="AG180" s="5" t="n"/>
-      <c r="AH180" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-arty-muhlenberg.md; report-vs-tablet conflicts (20-vs-26 guns; 10:00-vs-10:30 end) carried on CA-J3M-1/4</t>
-        </is>
-      </c>
-      <c r="AI180" s="5" t="inlineStr">
-        <is>
-          <t>Muhlenberg (1st Lt, 4th US) commanding; F 4th US (Rugg), K 5th US (Kinzie), Knap's E PA (Atwell), M 1st NY (Winegar)</t>
-        </is>
-      </c>
-      <c r="AJ180" s="5" t="inlineStr">
-        <is>
-          <t>20 guns in the July 3 program BY THE AUTHOR (10 rifles + 10 Napoleons) vs tablet 26 — Rigby A 1st MD reconciliation flagged, not adopted; personnel OPEN</t>
-        </is>
-      </c>
-      <c r="AK180" s="5" t="inlineStr">
-        <is>
-          <t>[E] the pike/Powers/McAllister's program arc 600-800 yards out (four program-ground markers registered incl. Rigby); July 2 park negative (F + K 'remained in park')</t>
-        </is>
-      </c>
-      <c r="AL180" s="5" t="inlineStr">
-        <is>
-          <t>[C ~17:00 July 2] the Geary/Van Reed forward sections; otherwise attested-static</t>
-        </is>
-      </c>
-      <c r="AM180" s="5" t="inlineStr">
-        <is>
-          <t>THE CA-J3M-1 AUTHOR PRIMARY: 4.30 open / 15 min without intermission / 5.30 resume / 'until 10 a.m.'; Williams verbatim-class corroboration; the July 2 eight-gun thirty-minute Latimer duel received; NO rounds figures (verified negative)</t>
-        </is>
-      </c>
-      <c r="AN180" s="5" t="inlineStr">
-        <is>
-          <t>9 w aggregate (return p. 185) + the July 2 section losses itemized; July-2-weighted</t>
-        </is>
-      </c>
+      <c r="AH180" s="5" t="n"/>
+      <c r="AI180" s="5" t="n"/>
+      <c r="AJ180" s="5" t="n"/>
+      <c r="AK180" s="5" t="n"/>
+      <c r="AL180" s="5" t="n"/>
+      <c r="AM180" s="5" t="n"/>
+      <c r="AN180" s="5" t="n"/>
       <c r="AO180" s="5" t="n"/>
-      <c r="AP180" s="5" t="inlineStr">
-        <is>
-          <t>T3 (group grain)</t>
-        </is>
-      </c>
+      <c r="AP180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b1</t>
+          <t>reg-us-ha-1-2</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>3rd Massachusetts Battery (C)</t>
+          <t>6th New York Battery</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -22707,16 +22671,16 @@
       <c r="T181" s="2" t="inlineStr"/>
       <c r="U181" s="2" t="inlineStr"/>
       <c r="V181" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W181" s="2" t="inlineStr">
         <is>
-          <t>3rd Massachusetts</t>
-        </is>
-      </c>
-      <c r="X181" s="4" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>6th New</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr"/>
@@ -22732,7 +22696,7 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b1</t>
+          <t>reg-us-ha-1-2</t>
         </is>
       </c>
       <c r="AC181" s="5" t="n"/>
@@ -22753,12 +22717,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-2</t>
+          <t>reg-us-ha-1-1</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>6th New York Battery</t>
+          <t>9th Michigan Battery</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -22800,7 +22764,7 @@
       </c>
       <c r="W182" s="2" t="inlineStr">
         <is>
-          <t>6th New</t>
+          <t>9th Michigan</t>
         </is>
       </c>
       <c r="X182" s="2" t="inlineStr">
@@ -22821,7 +22785,7 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-2</t>
+          <t>reg-us-ha-1-1</t>
         </is>
       </c>
       <c r="AC182" s="5" t="n"/>
@@ -22842,12 +22806,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-1</t>
+          <t>reg-us-ha-1-3</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>9th Michigan Battery</t>
+          <t>Batteries B &amp; L, 2nd US</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -22885,16 +22849,16 @@
       <c r="T183" s="2" t="inlineStr"/>
       <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W183" s="2" t="inlineStr">
         <is>
-          <t>9th Michigan</t>
-        </is>
-      </c>
-      <c r="X183" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Batteries B &amp; L</t>
+        </is>
+      </c>
+      <c r="X183" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr"/>
@@ -22910,7 +22874,7 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-1</t>
+          <t>reg-us-ha-1-3</t>
         </is>
       </c>
       <c r="AC183" s="5" t="n"/>
@@ -22931,12 +22895,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-3</t>
+          <t>reg-us-ha-2-1</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Batteries B &amp; L, 2nd US</t>
+          <t>Batteries E &amp; G, 1st US</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -22978,7 +22942,7 @@
       </c>
       <c r="W184" s="2" t="inlineStr">
         <is>
-          <t>Batteries B &amp; L</t>
+          <t>Batteries E &amp; G</t>
         </is>
       </c>
       <c r="X184" s="4" t="inlineStr">
@@ -22999,33 +22963,69 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-3</t>
-        </is>
-      </c>
-      <c r="AC184" s="5" t="n"/>
+          <t>reg-us-ha-2-1</t>
+        </is>
+      </c>
+      <c r="AC184" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok</t>
+        </is>
+      </c>
       <c r="AD184" s="5" t="n"/>
       <c r="AE184" s="5" t="n"/>
       <c r="AF184" s="5" t="n"/>
       <c r="AG184" s="5" t="n"/>
-      <c r="AH184" s="5" t="n"/>
-      <c r="AI184" s="5" t="n"/>
-      <c r="AJ184" s="5" t="n"/>
-      <c r="AK184" s="5" t="n"/>
-      <c r="AL184" s="5" t="n"/>
-      <c r="AM184" s="5" t="n"/>
-      <c r="AN184" s="5" t="n"/>
+      <c r="AH184" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-randol.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
+        </is>
+      </c>
+      <c r="AI184" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Alanson M. Randol throughout; split command July 3 (Chester's section w/ Custer's brigade, Kinney's section near Hanover Road); armament discrepancy flagged (tablet '4 12-Pdrs' vs horse-arty convention of 3-in rifles)</t>
+        </is>
+      </c>
+      <c r="AJ184" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: 84 men (report-adjacent, not a B&amp;M hop)</t>
+        </is>
+      </c>
+      <c r="AK184" s="5" t="inlineStr">
+        <is>
+          <t>[C tablet] with 1st Brig 2nd Cav Div, not engaged July 1-2; PASS-13 SHEET-CROP: Chester's section (10569,5638) and Kinney's section (10354,5270), ~370 m apart — first drawn confirmation the tablet split is real</t>
+        </is>
+      </c>
+      <c r="AL184" s="5" t="inlineStr">
+        <is>
+          <t>Not authored — no trigger/timing for either section located</t>
+        </is>
+      </c>
+      <c r="AM184" s="5" t="inlineStr">
+        <is>
+          <t>Chester's section co-named in McIntosh's tablet as CA-ECF-2 co-executor (~14:00); Kinney's section 'remained near Hanover Road', no engagement claimed</t>
+        </is>
+      </c>
+      <c r="AN184" s="5" t="inlineStr">
+        <is>
+          <t>Tablet: 'suffered no casualties' — explicit zero, both sections combined</t>
+        </is>
+      </c>
       <c r="AO184" s="5" t="n"/>
-      <c r="AP184" s="5" t="n"/>
+      <c r="AP184" s="5" t="inlineStr">
+        <is>
+          <t>T3 (ECF grain, split-section)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-2-1</t>
+          <t>reg-us-ar-1r-2</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Batteries E &amp; G, 1st US</t>
+          <t>Batteries F &amp; K, 3rd US</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="W185" s="2" t="inlineStr">
         <is>
-          <t>Batteries E &amp; G</t>
+          <t>Batteries F &amp; K</t>
         </is>
       </c>
       <c r="X185" s="4" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-2-1</t>
+          <t>reg-us-ar-1r-2</t>
         </is>
       </c>
       <c r="AC185" s="5" t="inlineStr">
@@ -23102,55 +23102,55 @@
       <c r="AG185" s="5" t="n"/>
       <c r="AH185" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-randol.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-turnbull.md; TRIAGE CORRECTION - lost guns in combat, strongest contradiction of static-park</t>
         </is>
       </c>
       <c r="AI185" s="5" t="inlineStr">
         <is>
-          <t>Capt. Alanson M. Randol throughout; split command July 3 (Chester's section w/ Custer's brigade, Kinney's section near Hanover Road); armament discrepancy flagged (tablet '4 12-Pdrs' vs horse-arty convention of 3-in rifles)</t>
+          <t>Lt. John C. Turnbull, Batteries F&amp;K 3US; 6x12pdr</t>
         </is>
       </c>
       <c r="AJ185" s="5" t="inlineStr">
         <is>
-          <t>Tablet: 84 men (report-adjacent, not a B&amp;M hop)</t>
+          <t>145 men</t>
         </is>
       </c>
       <c r="AK185" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] with 1st Brig 2nd Cav Div, not engaged July 1-2; PASS-13 SHEET-CROP: Chester's section (10569,5638) and Kinney's section (10354,5270), ~370 m apart — first drawn confirmation the tablet split is real</t>
+          <t>[D Jul1] crest near Meade's HQ; [D Jul2] log house/Emmitsburg Rd w/Humphreys; [D Jul3] Taneytown Rd/Cemetery Hill</t>
         </is>
       </c>
       <c r="AL185" s="5" t="inlineStr">
         <is>
-          <t>Not authored — no trigger/timing for either section located</t>
+          <t>[D] 3-position chain Jul1-3</t>
         </is>
       </c>
       <c r="AM185" s="5" t="inlineStr">
         <is>
-          <t>Chester's section co-named in McIntosh's tablet as CA-ECF-2 co-executor (~14:00); Kinney's section 'remained near Hanover Road', no engagement claimed</t>
+          <t>engaged Jul2, COMPELLED TO RETIRE, lost 4 guns+45 horses (recaptured)</t>
         </is>
       </c>
       <c r="AN185" s="5" t="inlineStr">
         <is>
-          <t>Tablet: 'suffered no casualties' — explicit zero, both sections combined</t>
+          <t>1off+8k/14w/1m = 24</t>
         </is>
       </c>
       <c r="AO185" s="5" t="n"/>
       <c r="AP185" s="5" t="inlineStr">
         <is>
-          <t>T3 (ECF grain, split-section)</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-1r-2</t>
+          <t>reg-us-ar-2v-1</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Batteries F &amp; K, 3rd US</t>
+          <t>Battery B, 1st Connecticut Heavy</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -23188,16 +23188,16 @@
       <c r="T186" s="2" t="inlineStr"/>
       <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W186" s="2" t="inlineStr">
         <is>
-          <t>Batteries F &amp; K</t>
-        </is>
-      </c>
-      <c r="X186" s="4" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Battery B</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr"/>
@@ -23213,12 +23213,12 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-1r-2</t>
+          <t>reg-us-ar-2v-1</t>
         </is>
       </c>
       <c r="AC186" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (attested-absent)</t>
         </is>
       </c>
       <c r="AD186" s="5" t="n"/>
@@ -23227,55 +23227,55 @@
       <c r="AG186" s="5" t="n"/>
       <c r="AH186" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-turnbull.md; TRIAGE CORRECTION - lost guns in combat, strongest contradiction of static-park</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-brooker.md; TRIAGE CONFIRMED (the exception to this pass's corrections)</t>
         </is>
       </c>
       <c r="AI186" s="5" t="inlineStr">
         <is>
-          <t>Lt. John C. Turnbull, Batteries F&amp;K 3US; 6x12pdr</t>
+          <t>Capt. Albert F. Brooker, Battery B 1CT Heavy; 4x4.5in siege rifle</t>
         </is>
       </c>
       <c r="AJ186" s="5" t="inlineStr">
         <is>
-          <t>145 men</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="AK186" s="5" t="inlineStr">
         <is>
-          <t>[D Jul1] crest near Meade's HQ; [D Jul2] log house/Emmitsburg Rd w/Humphreys; [D Jul3] Taneytown Rd/Cemetery Hill</t>
+          <t>CONFIRMED never at Gettysburg - held at Westminster MD (siege ordnance unsuited to rapid movement)</t>
         </is>
       </c>
       <c r="AL186" s="5" t="inlineStr">
         <is>
-          <t>[D] 3-position chain Jul1-3</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="AM186" s="5" t="inlineStr">
         <is>
-          <t>engaged Jul2, COMPELLED TO RETIRE, lost 4 guns+45 horses (recaptured)</t>
+          <t>held at Westminster throughout</t>
         </is>
       </c>
       <c r="AN186" s="5" t="inlineStr">
         <is>
-          <t>1off+8k/14w/1m = 24</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="AO186" s="5" t="n"/>
       <c r="AP186" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-2v-1</t>
+          <t>reg-us-v-b2</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Battery B, 1st Connecticut Heavy</t>
+          <t>Battery C, 1st New York Light</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -23313,16 +23313,16 @@
       <c r="T187" s="2" t="inlineStr"/>
       <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W187" s="2" t="inlineStr">
         <is>
-          <t>Battery B</t>
-        </is>
-      </c>
-      <c r="X187" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Battery C</t>
+        </is>
+      </c>
+      <c r="X187" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr"/>
@@ -23338,69 +23338,33 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-2v-1</t>
-        </is>
-      </c>
-      <c r="AC187" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (attested-absent)</t>
-        </is>
-      </c>
+          <t>reg-us-v-b2</t>
+        </is>
+      </c>
+      <c r="AC187" s="5" t="n"/>
       <c r="AD187" s="5" t="n"/>
       <c r="AE187" s="5" t="n"/>
       <c r="AF187" s="5" t="n"/>
       <c r="AG187" s="5" t="n"/>
-      <c r="AH187" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-brooker.md; TRIAGE CONFIRMED (the exception to this pass's corrections)</t>
-        </is>
-      </c>
-      <c r="AI187" s="5" t="inlineStr">
-        <is>
-          <t>Capt. Albert F. Brooker, Battery B 1CT Heavy; 4x4.5in siege rifle</t>
-        </is>
-      </c>
-      <c r="AJ187" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="AK187" s="5" t="inlineStr">
-        <is>
-          <t>CONFIRMED never at Gettysburg - held at Westminster MD (siege ordnance unsuited to rapid movement)</t>
-        </is>
-      </c>
-      <c r="AL187" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="AM187" s="5" t="inlineStr">
-        <is>
-          <t>held at Westminster throughout</t>
-        </is>
-      </c>
-      <c r="AN187" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="AH187" s="5" t="n"/>
+      <c r="AI187" s="5" t="n"/>
+      <c r="AJ187" s="5" t="n"/>
+      <c r="AK187" s="5" t="n"/>
+      <c r="AL187" s="5" t="n"/>
+      <c r="AM187" s="5" t="n"/>
+      <c r="AN187" s="5" t="n"/>
       <c r="AO187" s="5" t="n"/>
-      <c r="AP187" s="5" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
+      <c r="AP187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b2</t>
+          <t>reg-us-vi-b4</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Battery C, 1st New York Light</t>
+          <t>Battery C, 1st Rhode Island Light</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -23463,7 +23427,7 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b2</t>
+          <t>reg-us-vi-b4</t>
         </is>
       </c>
       <c r="AC188" s="5" t="n"/>
@@ -23484,12 +23448,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-b4</t>
+          <t>reg-us-ha-2-4</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Battery C, 1st Rhode Island Light</t>
+          <t>Battery C, 3rd US</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -23552,7 +23516,7 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-b4</t>
+          <t>reg-us-ha-2-4</t>
         </is>
       </c>
       <c r="AC189" s="5" t="n"/>
@@ -23573,12 +23537,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-2-4</t>
+          <t>reg-us-vi-b5</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Battery C, 3rd US</t>
+          <t>Battery G, 1st Rhode Island Light</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -23620,7 +23584,7 @@
       </c>
       <c r="W190" s="2" t="inlineStr">
         <is>
-          <t>Battery C</t>
+          <t>Battery G</t>
         </is>
       </c>
       <c r="X190" s="4" t="inlineStr">
@@ -23641,7 +23605,7 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-2-4</t>
+          <t>reg-us-vi-b5</t>
         </is>
       </c>
       <c r="AC190" s="5" t="n"/>
@@ -23662,12 +23626,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-b5</t>
+          <t>reg-us-xi-b4</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Battery G, 1st Rhode Island Light</t>
+          <t>Battery K, 1st Ohio Light</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -23705,16 +23669,16 @@
       <c r="T191" s="2" t="inlineStr"/>
       <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="2" t="inlineStr">
         <is>
-          <t>Battery G</t>
-        </is>
-      </c>
-      <c r="X191" s="4" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
+          <t>Battery K</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr"/>
@@ -23730,7 +23694,7 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-b5</t>
+          <t>reg-us-xi-b4</t>
         </is>
       </c>
       <c r="AC191" s="5" t="n"/>
@@ -23751,12 +23715,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-b4</t>
+          <t>reg-us-v-b3</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Battery K, 1st Ohio Light</t>
+          <t>Battery L, 1st Ohio Light</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -23794,16 +23758,16 @@
       <c r="T192" s="2" t="inlineStr"/>
       <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W192" s="2" t="inlineStr">
         <is>
-          <t>Battery K</t>
-        </is>
-      </c>
-      <c r="X192" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Battery L</t>
+        </is>
+      </c>
+      <c r="X192" s="4" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr"/>
@@ -23819,7 +23783,7 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-b4</t>
+          <t>reg-us-v-b3</t>
         </is>
       </c>
       <c r="AC192" s="5" t="n"/>
@@ -23840,12 +23804,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b3</t>
+          <t>reg-us-ar-2v-2</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Battery L, 1st Ohio Light</t>
+          <t>Battery M, 1st Connecticut Heavy</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -23887,7 +23851,7 @@
       </c>
       <c r="W193" s="2" t="inlineStr">
         <is>
-          <t>Battery L</t>
+          <t>Battery M</t>
         </is>
       </c>
       <c r="X193" s="4" t="inlineStr">
@@ -23908,33 +23872,69 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-b3</t>
-        </is>
-      </c>
-      <c r="AC193" s="5" t="n"/>
+          <t>reg-us-ar-2v-2</t>
+        </is>
+      </c>
+      <c r="AC193" s="5" t="inlineStr">
+        <is>
+          <t>authored-ok (attested-absent)</t>
+        </is>
+      </c>
       <c r="AD193" s="5" t="n"/>
       <c r="AE193" s="5" t="n"/>
       <c r="AF193" s="5" t="n"/>
       <c r="AG193" s="5" t="n"/>
-      <c r="AH193" s="5" t="n"/>
-      <c r="AI193" s="5" t="n"/>
-      <c r="AJ193" s="5" t="n"/>
-      <c r="AK193" s="5" t="n"/>
-      <c r="AL193" s="5" t="n"/>
-      <c r="AM193" s="5" t="n"/>
-      <c r="AN193" s="5" t="n"/>
+      <c r="AH193" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-btty-pratt.md; TRIAGE CONFIRMED; brigade's 8-casualty total therefore belongs entirely to Sterling's+Taft's batteries</t>
+        </is>
+      </c>
+      <c r="AI193" s="5" t="inlineStr">
+        <is>
+          <t>Capt. Franklin A. Pratt, Battery M 1CT Heavy; 4x4.5in siege rifle</t>
+        </is>
+      </c>
+      <c r="AJ193" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AK193" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED never engaged - Westminster MD w/ Brooker's battery</t>
+        </is>
+      </c>
+      <c r="AL193" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AM193" s="5" t="inlineStr">
+        <is>
+          <t>held at Westminster</t>
+        </is>
+      </c>
+      <c r="AN193" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="AO193" s="5" t="n"/>
-      <c r="AP193" s="5" t="n"/>
+      <c r="AP193" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-2v-2</t>
+          <t>reg-us-ha-1-4</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Battery M, 1st Connecticut Heavy</t>
+          <t>Battery M, 2nd US</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -23997,12 +23997,12 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-2v-2</t>
+          <t>reg-us-ha-1-4</t>
         </is>
       </c>
       <c r="AC194" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (attested-absent)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD194" s="5" t="n"/>
@@ -24011,55 +24011,55 @@
       <c r="AG194" s="5" t="n"/>
       <c r="AH194" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-pratt.md; TRIAGE CONFIRMED; brigade's 8-casualty total therefore belongs entirely to Sterling's+Taft's batteries</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-pennington.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
         </is>
       </c>
       <c r="AI194" s="5" t="inlineStr">
         <is>
-          <t>Capt. Franklin A. Pratt, Battery M 1CT Heavy; 4x4.5in siege rifle</t>
+          <t>Lieut. A. C. M. Pennington Jr. throughout; six 3-in rifles (no armament discrepancy); parent Robertson's report defers narrative to Custer's</t>
         </is>
       </c>
       <c r="AJ194" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Tablet: 129 men</t>
         </is>
       </c>
       <c r="AK194" s="5" t="inlineStr">
         <is>
-          <t>CONFIRMED never engaged - Westminster MD w/ Brooker's battery</t>
+          <t>[C, shared w/ Custer's brigade] Hanover Rd/Low Dutch sector; PASS-13 SHEET-CROP: 'PENNINGTON/CLARK BAT.M' at (10072,5237), south of Custer's block; 'Clark' unidentified</t>
         </is>
       </c>
       <c r="AL194" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Inferred-by-attachment to Custer's brigade only</t>
         </is>
       </c>
       <c r="AM194" s="5" t="inlineStr">
         <is>
-          <t>held at Westminster</t>
+          <t>July 2 Hunterstown; July 3 ~14:00 CA-ECF-2, report=tablet agreement ('engaged all day' / 'on the right of the Union Army') — the pass's second report=tablet pair</t>
         </is>
       </c>
       <c r="AN194" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Tablet: wounded 1 officer only (no enlisted figure stated)</t>
         </is>
       </c>
       <c r="AO194" s="5" t="n"/>
       <c r="AP194" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3 (ECF grain)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-4</t>
+          <t>reg-us-arty-hq</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Battery M, 2nd US</t>
+          <t>Artillery command, Army of the Potomac (Chief of Artillery)</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>command</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -24101,7 +24101,7 @@
       </c>
       <c r="W195" s="2" t="inlineStr">
         <is>
-          <t>Battery M</t>
+          <t>Artillery command</t>
         </is>
       </c>
       <c r="X195" s="4" t="inlineStr">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ha-1-4</t>
+          <t>reg-us-arty-hq</t>
         </is>
       </c>
       <c r="AC195" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>command record</t>
         </is>
       </c>
       <c r="AD195" s="5" t="n"/>
@@ -24136,55 +24136,55 @@
       <c r="AG195" s="5" t="n"/>
       <c r="AH195" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-pennington.md; self-surfaced by pass-12's McIntosh tablet quote; closed pass 13</t>
+          <t>Dossier: reconstruction/dossiers/us-arty-hq-hunt.md; NEW register row this pass</t>
         </is>
       </c>
       <c r="AI195" s="5" t="inlineStr">
         <is>
-          <t>Lieut. A. C. M. Pennington Jr. throughout; six 3-in rifles (no armament discrepancy); parent Robertson's report defers narrative to Custer's</t>
+          <t>Brig. Gen. H.J. Hunt, Chief of Artillery AoP; authority contested by Hancock on the II Corps front - the dispute IS CA-J3A-4's sectoral shape</t>
         </is>
       </c>
       <c r="AJ195" s="5" t="inlineStr">
         <is>
-          <t>Tablet: 129 men</t>
+          <t>n/a (command entry); Reserve 2,375 men / 114 guns nominal under command</t>
         </is>
       </c>
       <c r="AK195" s="5" t="inlineStr">
         <is>
-          <t>[C, shared w/ Custer's brigade] Hanover Rd/Low Dutch sector; PASS-13 SHEET-CROP: 'PENNINGTON/CLARK BAT.M' at (10072,5237), south of Custer's block; 'Clark' unidentified</t>
+          <t>[C] ~11-13:00 line inspection ride; [A vs CA-J3A-1] on Little Round Top at the opening; [A window] at Cowan's guns at the climax (horse shot, brown-1985-filson)</t>
         </is>
       </c>
       <c r="AL195" s="5" t="inlineStr">
         <is>
-          <t>Inferred-by-attachment to Custer's brigade only</t>
+          <t>command-grain ride sequence (times the order delivery)</t>
         </is>
       </c>
       <c r="AM195" s="5" t="inlineStr">
         <is>
-          <t>July 2 Hunterstown; July 3 ~14:00 CA-ECF-2, report=tablet agreement ('engaged all day' / 'on the right of the Union Army') — the pass's second report=tablet pair</t>
+          <t>[C 10:00] husband-ammunition instruction verbatim; [C 14:30] 'About 2.30 p.m. ... I directed that the fire should be gradually stopped... and the enemy soon slackened his fire also' (or-27-1-hunt) = CA-J3A-4 clock-fixed by its author; [C ~15:00] 'About 3 p.m., and soon after the enemy's fire had ceased, he formed a column of attack'; [B] 32,781 rounds of 270/gun carried - the economy arithmetic primary</t>
         </is>
       </c>
       <c r="AN195" s="5" t="inlineStr">
         <is>
-          <t>Tablet: wounded 1 officer only (no enlisted figure stated)</t>
+          <t>army artillery return: 7 off + 98 men k, 33 off + 532 w, 67 m, 881 horses (or-27-1-hunt); July 3 officer list confirms Rorty/Cushing k, Woodruff/Milne mw</t>
         </is>
       </c>
       <c r="AO195" s="5" t="n"/>
       <c r="AP195" s="5" t="inlineStr">
         <is>
-          <t>T3 (ECF grain)</t>
+          <t>T2 (command record; order events clock-fixed)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>reg-us-arty-hq</t>
+          <t>us-btty-martin-5us</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Artillery command, Army of the Potomac (Chief of Artillery)</t>
+          <t>(Leonard) Martin's Battery F, 5th US Artillery</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>command</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -24202,57 +24202,97 @@
           <t>artillery</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>july3-afternoon</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>125</v>
+      </c>
       <c r="I196" s="3">
         <f>IF(G196=0,0,1-H196/G196)</f>
         <v/>
       </c>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr"/>
-      <c r="M196" s="2" t="inlineStr"/>
-      <c r="N196" s="2" t="inlineStr"/>
-      <c r="O196" s="2" t="inlineStr"/>
-      <c r="P196" s="2" t="inlineStr"/>
-      <c r="Q196" s="2" t="inlineStr"/>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="J196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P196" s="2" t="n">
+        <v>2153.4</v>
+      </c>
+      <c r="Q196" s="2" t="n">
+        <v>2153.4</v>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>column/line</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V196" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W196" s="2" t="inlineStr">
         <is>
-          <t>Artillery command</t>
-        </is>
-      </c>
-      <c r="X196" s="4" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="Y196" s="2" t="inlineStr"/>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
         <is>
-          <t>not-yet-cast</t>
+          <t>in-build</t>
         </is>
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>reg-us-arty-hq</t>
+          <t>reg-us-vi-b8</t>
         </is>
       </c>
       <c r="AC196" s="5" t="inlineStr">
         <is>
-          <t>command record</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD196" s="5" t="n"/>
@@ -24261,55 +24301,55 @@
       <c r="AG196" s="5" t="n"/>
       <c r="AH196" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-arty-hq-hunt.md; NEW register row this pass</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-martin-5us.md; name-collision w/ XII Corps Kinzie battery resolved distinct</t>
         </is>
       </c>
       <c r="AI196" s="5" t="inlineStr">
         <is>
-          <t>Brig. Gen. H.J. Hunt, Chief of Artillery AoP; authority contested by Hancock on the II Corps front - the dispute IS CA-J3A-4's sectoral shape</t>
+          <t>Lt. Leonard Martin, Battery F 5US (VI Corps - DISTINCT from Kinzie's XII Corps Battery F 5US); 6x10pdr Parrott</t>
         </is>
       </c>
       <c r="AJ196" s="5" t="inlineStr">
         <is>
-          <t>n/a (command entry); Reserve 2,375 men / 114 guns nominal under command</t>
+          <t>3off+122men</t>
         </is>
       </c>
       <c r="AK196" s="5" t="inlineStr">
         <is>
-          <t>[C] ~11-13:00 line inspection ride; [A vs CA-J3A-1] on Little Round Top at the opening; [A window] at Cowan's guns at the climax (horse shot, brown-1985-filson)</t>
+          <t>[D Jul3] reserve -&gt; Ziegler's Grove; monument itself sits on the grove</t>
         </is>
       </c>
       <c r="AL196" s="5" t="inlineStr">
         <is>
-          <t>command-grain ride sequence (times the order delivery)</t>
+          <t>[D] arrival-&gt;reserve-&gt;Ziegler's Grove</t>
         </is>
       </c>
       <c r="AM196" s="5" t="inlineStr">
         <is>
-          <t>[C 10:00] husband-ammunition instruction verbatim; [C 14:30] 'About 2.30 p.m. ... I directed that the fire should be gradually stopped... and the enemy soon slackened his fire also' (or-27-1-hunt) = CA-J3A-4 clock-fixed by its author; [C ~15:00] 'About 3 p.m., and soon after the enemy's fire had ceased, he formed a column of attack'; [B] 32,781 rounds of 270/gun carried - the economy arithmetic primary</t>
+          <t>reserve/reinforcement</t>
         </is>
       </c>
       <c r="AN196" s="5" t="inlineStr">
         <is>
-          <t>army artillery return: 7 off + 98 men k, 33 off + 532 w, 67 m, 881 horses (or-27-1-hunt); July 3 officer list confirms Rorty/Cushing k, Woodruff/Milne mw</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AO196" s="5" t="n"/>
       <c r="AP196" s="5" t="inlineStr">
         <is>
-          <t>T2 (command record; order events clock-fixed)</t>
+          <t>T2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>us-btty-martin-5us</t>
+          <t>us-btty-ames</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>(Leonard) Martin's Battery F, 5th US Artillery</t>
+          <t>Ames's Battery G, 1st New York Light Artillery</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -24329,14 +24369,14 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I197" s="3">
         <f>IF(G197=0,0,1-H197/G197)</f>
@@ -24346,25 +24386,25 @@
         <v>0</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O197" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P197" s="2" t="n">
-        <v>2153.4</v>
+        <v>706.5</v>
       </c>
       <c r="Q197" s="2" t="n">
-        <v>2153.4</v>
+        <v>706.5</v>
       </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
@@ -24373,21 +24413,21 @@
       </c>
       <c r="S197" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="T197" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V197" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W197" s="2" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Ames</t>
         </is>
       </c>
       <c r="X197" s="2" t="inlineStr">
@@ -24397,12 +24437,12 @@
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24412,7 +24452,7 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-b8</t>
+          <t>reg-us-ar-4v-4</t>
         </is>
       </c>
       <c r="AC197" s="5" t="inlineStr">
@@ -24426,55 +24466,55 @@
       <c r="AG197" s="5" t="n"/>
       <c r="AH197" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-martin-5us.md; name-collision w/ XII Corps Kinzie battery resolved distinct</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-ames.md; TRIAGE CORRECTION, closes the 13-battery sweep</t>
         </is>
       </c>
       <c r="AI197" s="5" t="inlineStr">
         <is>
-          <t>Lt. Leonard Martin, Battery F 5US (VI Corps - DISTINCT from Kinzie's XII Corps Battery F 5US); 6x10pdr Parrott</t>
+          <t>Capt. Nelson Ames, Battery G 1NY; 6x12pdr Nap</t>
         </is>
       </c>
       <c r="AJ197" s="5" t="inlineStr">
         <is>
-          <t>3off+122men</t>
+          <t>132 men</t>
         </is>
       </c>
       <c r="AK197" s="5" t="inlineStr">
         <is>
-          <t>[D Jul3] reserve -&gt; Ziegler's Grove; monument itself sits on the grove</t>
+          <t>[A 15:00-17:30 Jul2] Peach Orchard w/ III Corps; [D Jul3] Cemetery Ridge w/ II Corps 1st Div</t>
         </is>
       </c>
       <c r="AL197" s="5" t="inlineStr">
         <is>
-          <t>[D] arrival-&gt;reserve-&gt;Ziegler's Grove</t>
+          <t>[A] into Peach Orchard line; [D] relocate to II Corps ground</t>
         </is>
       </c>
       <c r="AM197" s="5" t="inlineStr">
         <is>
-          <t>reserve/reinforcement</t>
+          <t>3-5:30pm Peach Orchard fight (precisely timed)</t>
         </is>
       </c>
       <c r="AN197" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7w</t>
         </is>
       </c>
       <c r="AO197" s="5" t="n"/>
       <c r="AP197" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>us-btty-ames</t>
+          <t>us-btty-arnold</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Ames's Battery G, 1st New York Light Artillery</t>
+          <t>Arnold's Battery A, 1st Rhode Island Light Artillery</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -24498,71 +24538,71 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="I198" s="3">
         <f>IF(G198=0,0,1-H198/G198)</f>
         <v/>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M198" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N198" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P198" s="2" t="n">
-        <v>706.5</v>
-      </c>
-      <c r="Q198" s="2" t="n">
-        <v>706.5</v>
-      </c>
-      <c r="R198" s="2" t="inlineStr">
+      <c r="U198" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V198" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Arnold</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S198" s="2" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="T198" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U198" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V198" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W198" s="2" t="inlineStr">
-        <is>
-          <t>Ames</t>
-        </is>
-      </c>
-      <c r="X198" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
@@ -24577,12 +24617,12 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ar-4v-4</t>
+          <t>reg-us-ii-b2</t>
         </is>
       </c>
       <c r="AC198" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (ED-7 stands)</t>
         </is>
       </c>
       <c r="AD198" s="5" t="n"/>
@@ -24591,55 +24631,55 @@
       <c r="AG198" s="5" t="n"/>
       <c r="AH198" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-ames.md; TRIAGE CORRECTION, closes the 13-battery sweep</t>
+          <t>Dossier: reconstruction/dossiers/us-btty-arnold.md</t>
         </is>
       </c>
       <c r="AI198" s="5" t="inlineStr">
         <is>
-          <t>Capt. Nelson Ames, Battery G 1NY; 6x12pdr Nap</t>
+          <t>Capt. Arnold survived unwounded ('gallantly fighting his own battery and saving it', or-27-1-hazard); 6x 3-in Ordnance rifles</t>
         </is>
       </c>
       <c r="AJ198" s="5" t="inlineStr">
         <is>
-          <t>132 men</t>
+          <t>139 men (stone-sentinels; civilwarintheeast derivative corroboration only)</t>
         </is>
       </c>
       <c r="AK198" s="5" t="inlineStr">
         <is>
-          <t>[A 15:00-17:30 Jul2] Peach Orchard w/ III Corps; [D Jul3] Cemetery Ridge w/ II Corps 1st Div</t>
+          <t>[E] wall N of inner angle (4425,4955) f260 +-30m, ~80m N of Angle corner (Bachelder); attested-static with ED-7 withdrawal dispute riding the claim</t>
         </is>
       </c>
       <c r="AL198" s="5" t="inlineStr">
         <is>
-          <t>[A] into Peach Orchard line; [D] relocate to II Corps ground</t>
+          <t>none authored (ED-7: neither withdrawal-timing reading strong enough to move traced geometry)</t>
         </is>
       </c>
       <c r="AM198" s="5" t="inlineStr">
         <is>
-          <t>3-5:30pm Peach Orchard fight (precisely timed)</t>
+          <t>[A window] served through the cannonade; 'expended every round, and the lines of the enemy still advanced' (or-27-1-hazard); [D] 'final shots were double-shotted canister' into Fry/Marshall; then withdrew his own AND Cushing's battery (Hazard); Hunt: withdrawn 'toward the close'</t>
         </is>
       </c>
       <c r="AN198" s="5" t="inlineStr">
         <is>
-          <t>7w</t>
+          <t>4k/24w of 139 (stone-sentinels); July 3 cannonade-window dominated; pin (negative): Arnold unwounded per Hazard's report</t>
         </is>
       </c>
       <c r="AO198" s="5" t="n"/>
       <c r="AP198" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>us-btty-arnold</t>
+          <t>us-xii-arty</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Arnold's Battery A, 1st Rhode Island Light Artillery</t>
+          <t>Artillery Brigade, XII Corps (Muhlenberg)</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -24659,36 +24699,36 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july3-morning</t>
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>139</v>
+        <v>480</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="I199" s="3">
         <f>IF(G199=0,0,1-H199/G199)</f>
         <v/>
       </c>
       <c r="J199" s="2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L199" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="N199" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>8</v>
       </c>
       <c r="P199" s="2" t="n">
         <v>0</v>
@@ -24710,14 +24750,14 @@
         <v>2</v>
       </c>
       <c r="U199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V199" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="W199" s="2" t="inlineStr">
         <is>
-          <t>Arnold</t>
+          <t>Artillery Brigade</t>
         </is>
       </c>
       <c r="X199" s="2" t="inlineStr">
@@ -24727,7 +24767,7 @@
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
@@ -24742,59 +24782,23 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-b2</t>
-        </is>
-      </c>
-      <c r="AC199" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (ED-7 stands)</t>
-        </is>
-      </c>
+          <t>reg-us-xii-arty</t>
+        </is>
+      </c>
+      <c r="AC199" s="5" t="n"/>
       <c r="AD199" s="5" t="n"/>
       <c r="AE199" s="5" t="n"/>
       <c r="AF199" s="5" t="n"/>
       <c r="AG199" s="5" t="n"/>
-      <c r="AH199" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-btty-arnold.md</t>
-        </is>
-      </c>
-      <c r="AI199" s="5" t="inlineStr">
-        <is>
-          <t>Capt. Arnold survived unwounded ('gallantly fighting his own battery and saving it', or-27-1-hazard); 6x 3-in Ordnance rifles</t>
-        </is>
-      </c>
-      <c r="AJ199" s="5" t="inlineStr">
-        <is>
-          <t>139 men (stone-sentinels; civilwarintheeast derivative corroboration only)</t>
-        </is>
-      </c>
-      <c r="AK199" s="5" t="inlineStr">
-        <is>
-          <t>[E] wall N of inner angle (4425,4955) f260 +-30m, ~80m N of Angle corner (Bachelder); attested-static with ED-7 withdrawal dispute riding the claim</t>
-        </is>
-      </c>
-      <c r="AL199" s="5" t="inlineStr">
-        <is>
-          <t>none authored (ED-7: neither withdrawal-timing reading strong enough to move traced geometry)</t>
-        </is>
-      </c>
-      <c r="AM199" s="5" t="inlineStr">
-        <is>
-          <t>[A window] served through the cannonade; 'expended every round, and the lines of the enemy still advanced' (or-27-1-hazard); [D] 'final shots were double-shotted canister' into Fry/Marshall; then withdrew his own AND Cushing's battery (Hazard); Hunt: withdrawn 'toward the close'</t>
-        </is>
-      </c>
-      <c r="AN199" s="5" t="inlineStr">
-        <is>
-          <t>4k/24w of 139 (stone-sentinels); July 3 cannonade-window dominated; pin (negative): Arnold unwounded per Hazard's report</t>
-        </is>
-      </c>
+      <c r="AH199" s="5" t="n"/>
+      <c r="AI199" s="5" t="n"/>
+      <c r="AJ199" s="5" t="n"/>
+      <c r="AK199" s="5" t="n"/>
+      <c r="AL199" s="5" t="n"/>
+      <c r="AM199" s="5" t="n"/>
+      <c r="AN199" s="5" t="n"/>
       <c r="AO199" s="5" t="n"/>
-      <c r="AP199" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AP199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -37577,12 +37581,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>us-6wi</t>
+          <t>us-27in</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>6th Wisconsin (Meredith's)</t>
+          <t>27th Indiana (Colgrove's)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -37602,51 +37606,51 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon</t>
+          <t>july3-morning</t>
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="I290" s="3">
         <f>IF(G290=0,0,1-H290/G290)</f>
         <v/>
       </c>
       <c r="J290" s="2" t="n">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L290" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M290" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N290" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P290" s="2" t="n">
-        <v>6893.6</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q290" s="2" t="n">
-        <v>1350.9</v>
+        <v>0</v>
       </c>
       <c r="R290" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S290" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line/scattered</t>
         </is>
       </c>
       <c r="T290" s="2" t="n">
@@ -37660,7 +37664,7 @@
       </c>
       <c r="W290" s="2" t="inlineStr">
         <is>
-          <t>(Meredith</t>
+          <t>(Colgrove</t>
         </is>
       </c>
       <c r="X290" s="2" t="inlineStr">
@@ -37702,12 +37706,12 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>us-8oh</t>
+          <t>us-2ma</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>8th Ohio Infantry</t>
+          <t>2nd Massachusetts (Colgrove's)</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -37727,42 +37731,42 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july3-morning</t>
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>164</v>
+        <v>316</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="I291" s="3">
         <f>IF(G291=0,0,1-H291/G291)</f>
         <v/>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L291" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M291" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N291" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O291" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="P291" s="2" t="n">
-        <v>219.5</v>
+        <v>117</v>
       </c>
       <c r="Q291" s="2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
@@ -37771,7 +37775,7 @@
       </c>
       <c r="S291" s="2" t="inlineStr">
         <is>
-          <t>line/skirmish</t>
+          <t>line/scattered</t>
         </is>
       </c>
       <c r="T291" s="2" t="n">
@@ -37781,11 +37785,11 @@
         <v>0</v>
       </c>
       <c r="V291" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W291" s="2" t="inlineStr">
         <is>
-          <t>8th Ohio</t>
+          <t>(Colgrove</t>
         </is>
       </c>
       <c r="X291" s="2" t="inlineStr">
@@ -37809,66 +37813,30 @@
         </is>
       </c>
       <c r="AB291" s="2" t="inlineStr"/>
-      <c r="AC291" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok</t>
-        </is>
-      </c>
+      <c r="AC291" s="5" t="n"/>
       <c r="AD291" s="5" t="n"/>
       <c r="AE291" s="5" t="n"/>
       <c r="AF291" s="5" t="n"/>
       <c r="AG291" s="5" t="n"/>
-      <c r="AH291" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
-        </is>
-      </c>
-      <c r="AI291" s="5" t="inlineStr">
-        <is>
-          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
-        </is>
-      </c>
-      <c r="AJ291" s="5" t="inlineStr">
-        <is>
-          <t>no primary; build 209 (compilation, flagged)</t>
-        </is>
-      </c>
-      <c r="AK291" s="5" t="inlineStr">
-        <is>
-          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
-        </is>
-      </c>
-      <c r="AL291" s="5" t="inlineStr">
-        <is>
-          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
-        </is>
-      </c>
-      <c r="AM291" s="5" t="inlineStr">
-        <is>
-          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
-        </is>
-      </c>
-      <c r="AN291" s="5" t="inlineStr">
-        <is>
-          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
-        </is>
-      </c>
+      <c r="AH291" s="5" t="n"/>
+      <c r="AI291" s="5" t="n"/>
+      <c r="AJ291" s="5" t="n"/>
+      <c r="AK291" s="5" t="n"/>
+      <c r="AL291" s="5" t="n"/>
+      <c r="AM291" s="5" t="n"/>
+      <c r="AN291" s="5" t="n"/>
       <c r="AO291" s="5" t="n"/>
-      <c r="AP291" s="5" t="inlineStr">
-        <is>
-          <t>T4 full-arc</t>
-        </is>
-      </c>
+      <c r="AP291" s="5" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>us-bartlett</t>
+          <t>us-6wi</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
+          <t>6th Wisconsin (Meredith's)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -37888,27 +37856,27 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon</t>
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1325</v>
+        <v>333</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>1325</v>
+        <v>165</v>
       </c>
       <c r="I292" s="3">
         <f>IF(G292=0,0,1-H292/G292)</f>
         <v/>
       </c>
       <c r="J292" s="2" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L292" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M292" s="2" t="n">
         <v>4</v>
@@ -37917,13 +37885,13 @@
         <v>0</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P292" s="2" t="n">
-        <v>1952.7</v>
+        <v>6893.6</v>
       </c>
       <c r="Q292" s="2" t="n">
-        <v>1901.3</v>
+        <v>1350.9</v>
       </c>
       <c r="R292" s="2" t="inlineStr">
         <is>
@@ -37936,17 +37904,17 @@
         </is>
       </c>
       <c r="T292" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U292" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V292" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W292" s="2" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>(Meredith</t>
         </is>
       </c>
       <c r="X292" s="2" t="inlineStr">
@@ -37961,7 +37929,7 @@
       </c>
       <c r="Z292" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA292" s="2" t="inlineStr">
@@ -37969,71 +37937,31 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AB292" s="2" t="inlineStr">
-        <is>
-          <t>reg-us-vi-1-2</t>
-        </is>
-      </c>
-      <c r="AC292" s="5" t="inlineStr">
-        <is>
-          <t>authored-ok (command/frame grain)</t>
-        </is>
-      </c>
+      <c r="AB292" s="2" t="inlineStr"/>
+      <c r="AC292" s="5" t="n"/>
       <c r="AD292" s="5" t="n"/>
       <c r="AE292" s="5" t="n"/>
       <c r="AF292" s="5" t="n"/>
       <c r="AG292" s="5" t="n"/>
-      <c r="AH292" s="5" t="inlineStr">
-        <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-1-2-bartlett.md; resolves Nevin's 'triple command succession' hazard</t>
-        </is>
-      </c>
-      <c r="AI292" s="5" t="inlineStr">
-        <is>
-          <t>2nd Bde 1st Div VI Corps (5ME/121NY/95,96PA); Brig Gen J.J. Bartlett; report=tablet; GENUINELY ENGAGED</t>
-        </is>
-      </c>
-      <c r="AJ292" s="5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="AK292" s="5" t="inlineStr">
-        <is>
-          <t>[D] Jul2 arrival ~5pm supporting Sykes; [C] Jul3 composite command of Nevin's 3rd Bde 3rd Div for the Crawford-support Wheatfield sweep (three-dossier cross-ref: this + us-vi-3-3-nevin.md + us-v-3-1-mccandless.md)</t>
-        </is>
-      </c>
-      <c r="AL292" s="5" t="inlineStr">
-        <is>
-          <t>[C ~17:00-18:00] the composite-command advance</t>
-        </is>
-      </c>
-      <c r="AM292" s="5" t="inlineStr">
-        <is>
-          <t>[C] Jul3 ~200 CSA prisoners + 15th GA colors captured jointly w/ McCandless</t>
-        </is>
-      </c>
-      <c r="AN292" s="5" t="inlineStr">
-        <is>
-          <t>own-bde tablet 5 (1k/4w); composite-command loss separately stated 'between 20 and 30'</t>
-        </is>
-      </c>
+      <c r="AH292" s="5" t="n"/>
+      <c r="AI292" s="5" t="n"/>
+      <c r="AJ292" s="5" t="n"/>
+      <c r="AK292" s="5" t="n"/>
+      <c r="AL292" s="5" t="n"/>
+      <c r="AM292" s="5" t="n"/>
+      <c r="AN292" s="5" t="n"/>
       <c r="AO292" s="5" t="n"/>
-      <c r="AP292" s="5" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="AP292" s="5" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>us-baxter</t>
+          <t>us-8oh</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
+          <t>8th Ohio Infantry</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -38053,42 +37981,42 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1452</v>
+        <v>164</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>800</v>
+        <v>118</v>
       </c>
       <c r="I293" s="3">
         <f>IF(G293=0,0,1-H293/G293)</f>
         <v/>
       </c>
       <c r="J293" s="2" t="n">
-        <v>652</v>
+        <v>46</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L293" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M293" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N293" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O293" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P293" s="2" t="n">
-        <v>8930.299999999999</v>
+        <v>219.5</v>
       </c>
       <c r="Q293" s="2" t="n">
-        <v>25.5</v>
+        <v>64</v>
       </c>
       <c r="R293" s="2" t="inlineStr">
         <is>
@@ -38097,7 +38025,7 @@
       </c>
       <c r="S293" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line/skirmish</t>
         </is>
       </c>
       <c r="T293" s="2" t="n">
@@ -38107,11 +38035,11 @@
         <v>0</v>
       </c>
       <c r="V293" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W293" s="2" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>8th Ohio</t>
         </is>
       </c>
       <c r="X293" s="2" t="inlineStr">
@@ -38134,14 +38062,10 @@
           <t>in-build</t>
         </is>
       </c>
-      <c r="AB293" s="2" t="inlineStr">
-        <is>
-          <t>reg-us-i-2-2</t>
-        </is>
-      </c>
+      <c r="AB293" s="2" t="inlineStr"/>
       <c r="AC293" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD293" s="5" t="n"/>
@@ -38150,55 +38074,55 @@
       <c r="AG293" s="5" t="n"/>
       <c r="AH293" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-2-2-baxter.md; CA-J1P-2 Union receiving executor</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md (first-class element); clockProfile or-27-1-sawyer -55 [-70,-40] weak (late-stated cluster)</t>
         </is>
       </c>
       <c r="AI293" s="5" t="inlineStr">
         <is>
-          <t>Baxter uninjured; Bates w x2, Wheelock captured/escaped, Lt. Thomas k in the streets; Coulter+11th Pa transferred out to 1st Bde</t>
+          <t>Lt. Col. Franklin Sawyer; detached from Carroll on the advanced picket line from Jul 2 evening, 24+ hours (or-27-1-sawyer; or-27-1-carroll)</t>
         </is>
       </c>
       <c r="AJ293" s="5" t="inlineStr">
         <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,452 (hop); division frame 'less than 2,500' (Robinson) CONFLICTS with the two-brigade B&amp;M sum 2,989 - both carried</t>
+          <t>no primary; build 209 (compilation, flagged)</t>
         </is>
       </c>
       <c r="AK293" s="5" t="inlineStr">
         <is>
-          <t>[C 11:00] arrival; the two front-changes to the Oak Ridge crest (the pass-10 drawn wall bar = this line); [C ~17:00] the Emmitsburg-road line; [C Jul 2 10:00] relieved by Webb; the July 2-3 support ladder (six clocked moves); [C Jul 3 ~13:00] Cemetery Hill right-front under the cannonade ~2 h, then Hays's right</t>
+          <t>[C/E] advanced picket line W of the corridor + reserve knoll: j3-02 draws TWO '8 ohio' bars (4255,5308)/(4390,5273) +-120m; j3-03 bars not redrawn (cartographic omission - presence attested through the action)</t>
         </is>
       </c>
       <c r="AL293" s="5" t="inlineStr">
         <is>
-          <t>[D] the relief hand-off ~15:00+ (Coulter's after-3, ammunition exhausted); the town retreat under fire; the clocked July 2-3 ladder</t>
+          <t>[D] Jul 2 evening forward to the picket line; [D] THE FLANK ACTION: 'changed front forward on the left company ... front to the left flank of the advancing rebel column' (Brockenbrough's documented counterpart)</t>
         </is>
       </c>
       <c r="AM293" s="5" t="inlineStr">
         <is>
-          <t>THE IVERSON REPULSE RECEIVING RECORD: the deadly fire, the charge (88th Pa two flags + 97th NY one), the 12th Mass flank fire 'great influence upon its surrender'; Coulter 12:30 general-firing pin; division 'three flags and about 1,000 prisoners'; the Northrup conduct record</t>
+          <t>[C -55] 'Soon after 2 p.m. ... sixty-four pieces ... in a semicircle which inclosed my position'; [D] flank fire BEFORE Smyth's front volley (sequence bracket); ~200 prisoners, 3 flags (34th NC, 38th Va - pocket mixing)</t>
         </is>
       </c>
       <c r="AN293" s="5" t="inlineStr">
         <is>
-          <t>Return p. 174 rows (not digit-re-read); division 'lost considerably more than half' of &lt;2,500 (primary); shape: the Oak Ridge window + the town capture spike; July 3 'considerable loss' skirmish clear (unquantified)</t>
+          <t>return 102 = report 102 EXACT; SPLIT IS PRIMARY: ~45 of 102 fell on the picket line BY NOON Jul 3 - flat-attrition-then-moderate-spike shape (ED-50 candidate), NOT a climax spike</t>
         </is>
       </c>
       <c r="AO293" s="5" t="n"/>
       <c r="AP293" s="5" t="inlineStr">
         <is>
-          <t>T4 (July 1 grain; full arc T3)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>us-berdan</t>
+          <t>us-bartlett</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
+          <t>Bartlett's Brigade (2nd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -38222,38 +38146,38 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1500</v>
+        <v>1325</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>1405</v>
+        <v>1325</v>
       </c>
       <c r="I294" s="3">
         <f>IF(G294=0,0,1-H294/G294)</f>
         <v/>
       </c>
       <c r="J294" s="2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L294" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N294" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P294" s="2" t="n">
-        <v>1663.1</v>
+        <v>1952.7</v>
       </c>
       <c r="Q294" s="2" t="n">
-        <v>1591.5</v>
+        <v>1901.3</v>
       </c>
       <c r="R294" s="2" t="inlineStr">
         <is>
@@ -38266,7 +38190,7 @@
         </is>
       </c>
       <c r="T294" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U294" s="2" t="n">
         <v>0</v>
@@ -38276,7 +38200,7 @@
       </c>
       <c r="W294" s="2" t="inlineStr">
         <is>
-          <t>Berdan</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="X294" s="2" t="inlineStr">
@@ -38291,7 +38215,7 @@
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA294" s="2" t="inlineStr">
@@ -38301,12 +38225,12 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-2</t>
+          <t>reg-us-vi-1-2</t>
         </is>
       </c>
       <c r="AC294" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 defender)</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD294" s="5" t="n"/>
@@ -38315,55 +38239,55 @@
       <c r="AG294" s="5" t="n"/>
       <c r="AH294" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-2-bartlett.md; resolves Nevin's 'triple command succession' hazard</t>
         </is>
       </c>
       <c r="AI294" s="5" t="inlineStr">
         <is>
-          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
+          <t>2nd Bde 1st Div VI Corps (5ME/121NY/95,96PA); Brig Gen J.J. Bartlett; report=tablet; GENUINELY ENGAGED</t>
         </is>
       </c>
       <c r="AJ294" s="5" t="inlineStr">
         <is>
-          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK294" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
+          <t>[D] Jul2 arrival ~5pm supporting Sykes; [C] Jul3 composite command of Nevin's 3rd Bde 3rd Div for the Crawford-support Wheatfield sweep (three-dossier cross-ref: this + us-vi-3-3-nevin.md + us-v-3-1-mccandless.md)</t>
         </is>
       </c>
       <c r="AL294" s="5" t="inlineStr">
         <is>
-          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
+          <t>[C ~17:00-18:00] the composite-command advance</t>
         </is>
       </c>
       <c r="AM294" s="5" t="inlineStr">
         <is>
-          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
+          <t>[C] Jul3 ~200 CSA prisoners + 15th GA colors captured jointly w/ McCandless</t>
         </is>
       </c>
       <c r="AN294" s="5" t="inlineStr">
         <is>
-          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
+          <t>own-bde tablet 5 (1k/4w); composite-command loss separately stated 'between 20 and 30'</t>
         </is>
       </c>
       <c r="AO294" s="5" t="n"/>
       <c r="AP294" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>us-biddle</t>
+          <t>us-baxter</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
+          <t>Baxter's Brigade (2nd Bde, 2nd Div, I Corps)</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -38387,38 +38311,38 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1287</v>
+        <v>1452</v>
       </c>
       <c r="H295" s="2" t="n">
-        <v>460</v>
+        <v>800</v>
       </c>
       <c r="I295" s="3">
         <f>IF(G295=0,0,1-H295/G295)</f>
         <v/>
       </c>
       <c r="J295" s="2" t="n">
-        <v>827</v>
+        <v>652</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L295" s="2" t="n">
         <v>14</v>
       </c>
       <c r="M295" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N295" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O295" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P295" s="2" t="n">
-        <v>5917.2</v>
+        <v>8930.299999999999</v>
       </c>
       <c r="Q295" s="2" t="n">
-        <v>751.7</v>
+        <v>25.5</v>
       </c>
       <c r="R295" s="2" t="inlineStr">
         <is>
@@ -38431,7 +38355,7 @@
         </is>
       </c>
       <c r="T295" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U295" s="2" t="n">
         <v>0</v>
@@ -38441,7 +38365,7 @@
       </c>
       <c r="W295" s="2" t="inlineStr">
         <is>
-          <t>Biddle</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="X295" s="2" t="inlineStr">
@@ -38466,12 +38390,12 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-1</t>
+          <t>reg-us-i-2-2</t>
         </is>
       </c>
       <c r="AC295" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AD295" s="5" t="n"/>
@@ -38480,55 +38404,55 @@
       <c r="AG295" s="5" t="n"/>
       <c r="AH295" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
+          <t>Dossier: reconstruction/dossiers/us-i-2-2-baxter.md; CA-J1P-2 Union receiving executor</t>
         </is>
       </c>
       <c r="AI295" s="5" t="inlineStr">
         <is>
-          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
+          <t>Baxter uninjured; Bates w x2, Wheelock captured/escaped, Lt. Thomas k in the streets; Coulter+11th Pa transferred out to 1st Bde</t>
         </is>
       </c>
       <c r="AJ295" s="5" t="inlineStr">
         <is>
-          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale ; p11 back-extension: July 1 PRIMARY 1,287 in / 440 k&amp;w + 457 m / 390 left (dated July 2) - the day split lands; B&amp;M-repro 1,361 (hop)</t>
+          <t>No brigade primary (negative); B&amp;M-repro 1,452 (hop); division frame 'less than 2,500' (Robinson) CONFLICTS with the two-brigade B&amp;M sum 2,989 - both carried</t>
         </is>
       </c>
       <c r="AK295" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
+          <t>[C 11:00] arrival; the two front-changes to the Oak Ridge crest (the pass-10 drawn wall bar = this line); [C ~17:00] the Emmitsburg-road line; [C Jul 2 10:00] relieved by Webb; the July 2-3 support ladder (six clocked moves); [C Jul 3 ~13:00] Cemetery Hill right-front under the cannonade ~2 h, then Hays's right</t>
         </is>
       </c>
       <c r="AL295" s="5" t="inlineStr">
         <is>
-          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
+          <t>[D] the relief hand-off ~15:00+ (Coulter's after-3, ammunition exhausted); the town retreat under fire; the clocked July 2-3 ladder</t>
         </is>
       </c>
       <c r="AM295" s="5" t="inlineStr">
         <is>
-          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
+          <t>THE IVERSON REPULSE RECEIVING RECORD: the deadly fire, the charge (88th Pa two flags + 97th NY one), the 12th Mass flank fire 'great influence upon its surrender'; Coulter 12:30 general-firing pin; division 'three flags and about 1,000 prisoners'; the Northrup conduct record</t>
         </is>
       </c>
       <c r="AN295" s="5" t="inlineStr">
         <is>
-          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
+          <t>Return p. 174 rows (not digit-re-read); division 'lost considerably more than half' of &lt;2,500 (primary); shape: the Oak Ridge window + the town capture spike; July 3 'considerable loss' skirmish clear (unquantified)</t>
         </is>
       </c>
       <c r="AO295" s="5" t="n"/>
       <c r="AP295" s="5" t="inlineStr">
         <is>
-          <t>T4 (July 1 grain; July 3 T3) - p11 upgrade</t>
+          <t>T4 (July 1 grain; full arc T3)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>us-brewster</t>
+          <t>us-berdan</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
+          <t>Berdan's Brigade (2nd Bde, 1st Div, III Corps — Ward's)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -38552,38 +38476,38 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1837</v>
+        <v>1500</v>
       </c>
       <c r="H296" s="2" t="n">
-        <v>1060</v>
+        <v>1405</v>
       </c>
       <c r="I296" s="3">
         <f>IF(G296=0,0,1-H296/G296)</f>
         <v/>
       </c>
       <c r="J296" s="2" t="n">
-        <v>777</v>
+        <v>95</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L296" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M296" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N296" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P296" s="2" t="n">
-        <v>1965.1</v>
+        <v>1663.1</v>
       </c>
       <c r="Q296" s="2" t="n">
-        <v>1219.5</v>
+        <v>1591.5</v>
       </c>
       <c r="R296" s="2" t="inlineStr">
         <is>
@@ -38606,7 +38530,7 @@
       </c>
       <c r="W296" s="2" t="inlineStr">
         <is>
-          <t>Brewster</t>
+          <t>Berdan</t>
         </is>
       </c>
       <c r="X296" s="2" t="inlineStr">
@@ -38631,12 +38555,12 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-2</t>
+          <t>reg-us-iii-1-2</t>
         </is>
       </c>
       <c r="AC296" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 defender)</t>
         </is>
       </c>
       <c r="AD296" s="5" t="n"/>
@@ -38645,37 +38569,37 @@
       <c r="AG296" s="5" t="n"/>
       <c r="AH296" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-2-ward.md; tablet's 'forced back 4-5 P.M.' is a UNION early-tablet exemplar (ED-58 candidate)</t>
         </is>
       </c>
       <c r="AI296" s="5" t="inlineStr">
         <is>
-          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
+          <t>Ward's bde (20IN/3ME/4ME/86NY/124NY/99PA/1-2USSS); Wheeler (20IN) k, Van Horne Ellis (124NY) k (monument check point), Walker (4ME) w</t>
         </is>
       </c>
       <c r="AJ296" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
+          <t>~1,500 effectives PRIMARY (Ward) - loss 781 = 52%, worst Union brigade ratio on the southern field</t>
         </is>
       </c>
       <c r="AK296" s="5" t="inlineStr">
         <is>
-          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
+          <t>[C tablet] Houck's Ridge line, left on the rocky eminence; tablet (3764,2670) OSM 19.7m; [E drawn j2-03] Ward's Brig + 86NY/124NY/99P bars (3841-3856,2665-2795)</t>
         </is>
       </c>
       <c r="AL296" s="5" t="inlineStr">
         <is>
-          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
+          <t>[D duration] 90-min oscillating stone-wall fight - TWO-SIDED agreement with the 48th AL's hour-and-a-half; [A vs CA-J2A-5] forced off as the Den fell</t>
         </is>
       </c>
       <c r="AM296" s="5" t="inlineStr">
         <is>
-          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
+          <t>[D] held-fire-to-200yd volley discipline record; 'nearly two hours' front</t>
         </is>
       </c>
       <c r="AN296" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
+          <t>return 781 adopted (report 'nearly 800' carried, ED-52); 4th ME row CLEAN RE-READ pass 8: 2+9k/3+56w/4+70m = 144 (the column noise closed; the 74 missing = the Den pocket); ~all July 2</t>
         </is>
       </c>
       <c r="AO296" s="5" t="n"/>
@@ -38688,12 +38612,12 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>us-brooke</t>
+          <t>us-biddle</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
+          <t>Biddle's Brigade (1st Bde, 3rd Div, I Corps — Col. Gates at the line)</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -38713,11 +38637,11 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>850</v>
+        <v>1287</v>
       </c>
       <c r="H297" s="2" t="n">
         <v>460</v>
@@ -38727,41 +38651,41 @@
         <v/>
       </c>
       <c r="J297" s="2" t="n">
-        <v>390</v>
+        <v>827</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L297" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P297" s="2" t="n">
+        <v>5917.2</v>
+      </c>
+      <c r="Q297" s="2" t="n">
+        <v>751.7</v>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>column/line</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="N297" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O297" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P297" s="2" t="n">
-        <v>3365.2</v>
-      </c>
-      <c r="Q297" s="2" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="R297" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S297" s="2" t="inlineStr">
-        <is>
-          <t>column/line</t>
-        </is>
-      </c>
-      <c r="T297" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="U297" s="2" t="n">
         <v>0</v>
@@ -38771,7 +38695,7 @@
       </c>
       <c r="W297" s="2" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Biddle</t>
         </is>
       </c>
       <c r="X297" s="2" t="inlineStr">
@@ -38796,12 +38720,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-4</t>
+          <t>reg-us-i-3-1</t>
         </is>
       </c>
       <c r="AC297" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD297" s="5" t="n"/>
@@ -38810,55 +38734,55 @@
       <c r="AG297" s="5" t="n"/>
       <c r="AH297" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-1-biddle.md; 121st/142nd Pa Jul 3 slots sheet-only (flagged)</t>
         </is>
       </c>
       <c r="AI297" s="5" t="inlineStr">
         <is>
-          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
+          <t>Biddle w Jul 1; Rowley register commander; Col. T.B. Gates (20th NYSM) commanded the 2-regiment front element Jul 3, reporting direct to Doubleday (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AJ297" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
+          <t>no Jul 3 primary; build 460 remnant (compilation, flagged); Jul 1 wreck 898 of ~1,350-1,500 explains scale ; p11 back-extension: July 1 PRIMARY 1,287 in / 440 k&amp;w + 457 m / 390 left (dated July 2) - the day split lands; B&amp;M-repro 1,361 (hop)</t>
         </is>
       </c>
       <c r="AK297" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
+          <t>[C] Jul 2 ~17:00 'last and lowest of the ridges' between the roads; [C/E] Jul 3 front line = 80th NY + 151st Pa with the Vermonters (or-27-1-doubleday p.258); j3-02 bars (4482,4569)+(4625,4515); j3-03 (4591,4559) +-120m</t>
         </is>
       </c>
       <c r="AL297" s="5" t="inlineStr">
         <is>
-          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
+          <t>[D] THE CLIMAX LEG: 'by the right flank up to the foot of the bluff, delivering our fire as we marched' then two regiments to the fence - a firing flank-march toward the Copse (~200-400m)</t>
         </is>
       </c>
       <c r="AM297" s="5" t="inlineStr">
         <is>
-          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
+          <t>[D] fire on the march; volley 'at very short range, who now completely broke'; large prisoner haul; 2 colors left on the ground (or-27-1-gates)</t>
         </is>
       </c>
       <c r="AN297" s="5" t="inlineStr">
         <is>
-          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
+          <t>return 898 (80NY 170, 121Pa 179, 142Pa 211, 151Pa 337); DAY SPLIT NOT PRIMARY-SEPARABLE (Gates's 170 = the 80th's battle total, not a Jul 3 figure) - the T4 blocker, recorded honestly</t>
         </is>
       </c>
       <c r="AO297" s="5" t="n"/>
       <c r="AP297" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 (July 1 grain; July 3 T3) - p11 upgrade</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>us-burbank</t>
+          <t>us-brewster</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
+          <t>Brewster's Excelsior Brigade (2nd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -38882,38 +38806,38 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>958</v>
+        <v>1837</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>505</v>
+        <v>1060</v>
       </c>
       <c r="I298" s="3">
         <f>IF(G298=0,0,1-H298/G298)</f>
         <v/>
       </c>
       <c r="J298" s="2" t="n">
-        <v>453</v>
+        <v>777</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L298" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N298" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P298" s="2" t="n">
-        <v>1581.5</v>
+        <v>1965.1</v>
       </c>
       <c r="Q298" s="2" t="n">
-        <v>709.4</v>
+        <v>1219.5</v>
       </c>
       <c r="R298" s="2" t="inlineStr">
         <is>
@@ -38936,7 +38860,7 @@
       </c>
       <c r="W298" s="2" t="inlineStr">
         <is>
-          <t>Burbank</t>
+          <t>Brewster</t>
         </is>
       </c>
       <c r="X298" s="2" t="inlineStr">
@@ -38961,12 +38885,12 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-2</t>
+          <t>reg-us-iii-2-2</t>
         </is>
       </c>
       <c r="AC298" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD298" s="5" t="n"/>
@@ -38975,37 +38899,37 @@
       <c r="AG298" s="5" t="n"/>
       <c r="AH298" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-2-brewster.md; recovery-side exemplar for ED-61</t>
         </is>
       </c>
       <c r="AI298" s="5" t="inlineStr">
         <is>
-          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
+          <t>Brewster's Excelsior bde (70/71/72/73/74/120 NY); Brewster unwounded; Sgt. Hogan (3rd Excelsior) the 8th-Fla-colors captor</t>
         </is>
       </c>
       <c r="AJ298" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
+          <t>B&amp;M-type 1,837 (hop flagged); recharge party ~150 (end-state fragment)</t>
         </is>
       </c>
       <c r="AK298" s="5" t="inlineStr">
         <is>
-          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
+          <t>[C] second line ~13:00, 73rd NY forward at the crest; tablet (3448.1,3722.7) (100.6 m Excelsior pair FLAGGED); [D] 73rd NY at Graham's front - monument (3329.5,3678.5) 73 m from the j2-04 '4 Ex' drawn label, both order ends primary; [E drawn j2-04] rally bars mid-field (3524,3896)</t>
         </is>
       </c>
       <c r="AL298" s="5" t="inlineStr">
         <is>
-          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
+          <t>[C agreeing] 4 p.m. advance under the left-flank artillery; [D trigger] the collapse withdrawal 'in good order, but with terrible loss'; [D after-sunset] THE RECHARGE - colors + 30 prisoners + guns recaptured (CA-J2A-11 bracket)</t>
         </is>
       </c>
       <c r="AM298" s="5" t="inlineStr">
         <is>
-          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
+          <t>[D] the artillery endurance (massed battalions - heaviest pre-musketry window this pass); the interleaved fight (regiments on three fronts); the 8th FLORIDA COLORS BOTH-SIDED (Hogan = Perry advanced tablet = Lang's record)</t>
         </is>
       </c>
       <c r="AN298" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
+          <t>TRIPLE EXACT report = tablet = return 778 (12+118/50+523/73); episode: artillery window substantial, collapse window dominant, July 3 nonzero</t>
         </is>
       </c>
       <c r="AO298" s="5" t="n"/>
@@ -39018,12 +38942,12 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>us-burling</t>
+          <t>us-brooke</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
+          <t>Brooke's Brigade (4th Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -39047,23 +38971,23 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>1365</v>
+        <v>850</v>
       </c>
       <c r="H299" s="2" t="n">
-        <v>850</v>
+        <v>460</v>
       </c>
       <c r="I299" s="3">
         <f>IF(G299=0,0,1-H299/G299)</f>
         <v/>
       </c>
       <c r="J299" s="2" t="n">
-        <v>515</v>
+        <v>390</v>
       </c>
       <c r="K299" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L299" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M299" s="2" t="n">
         <v>2</v>
@@ -39072,13 +38996,13 @@
         <v>0</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P299" s="2" t="n">
-        <v>1132.2</v>
+        <v>3365.2</v>
       </c>
       <c r="Q299" s="2" t="n">
-        <v>1068.4</v>
+        <v>46.1</v>
       </c>
       <c r="R299" s="2" t="inlineStr">
         <is>
@@ -39091,7 +39015,7 @@
         </is>
       </c>
       <c r="T299" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U299" s="2" t="n">
         <v>0</v>
@@ -39101,7 +39025,7 @@
       </c>
       <c r="W299" s="2" t="inlineStr">
         <is>
-          <t>Burling</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="X299" s="2" t="inlineStr">
@@ -39126,12 +39050,12 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-3</t>
+          <t>reg-us-ii-1-4</t>
         </is>
       </c>
       <c r="AC299" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 DISPERSED class)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD299" s="5" t="n"/>
@@ -39140,55 +39064,55 @@
       <c r="AG299" s="5" t="n"/>
       <c r="AH299" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-4-brooke.md</t>
         </is>
       </c>
       <c r="AI299" s="5" t="inlineStr">
         <is>
-          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
+          <t>Brooke's bde (27CT/2DE/64NY/53PA/145PA); Brooke 'severely bruised' (register w); Merwin (27CT) k</t>
         </is>
       </c>
       <c r="AJ299" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
+          <t>no primary (negative); ~850 compilation hop-flagged; return 389 = ~46% - proportionally heaviest in the division</t>
         </is>
       </c>
       <c r="AK299" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
+          <t>[A vs CA-J2A-8 +20-30min] FARTHEST ADVANCE tablet ON the Rose-ravine crest (3403,2913, OSM delta 56m flagged); [E drawn j2-04] CALDWELL'S DIV/Brooke's Brig labels at the apex (3487-3503,3230-3274)</t>
         </is>
       </c>
       <c r="AL299" s="5" t="inlineStr">
         <is>
-          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
+          <t>[D] passage-of-lines thru Cross; [B] 500m contested sweep 12-20 min; [D first-person] flanks-turned withdrawal 'unless I retired all would be killed or captured'</t>
         </is>
       </c>
       <c r="AM299" s="5" t="inlineStr">
         <is>
-          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
+          <t>[D] continuous fire fight; unsupported at the crest (negative-evidence class on support)</t>
         </is>
       </c>
       <c r="AN299" s="5" t="inlineStr">
         <is>
-          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
+          <t>return 389 (2DE 84, 64NY 98, 53PA 80, 145PA 90, 27CT 37); split: waves 3-4 carry ~all (deepest position = longest exposure)</t>
         </is>
       </c>
       <c r="AO299" s="5" t="n"/>
       <c r="AP299" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (dispersed class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>us-candy</t>
+          <t>us-burbank</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
+          <t>Burbank's US Regular Brigade (2nd Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -39212,26 +39136,26 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>1400</v>
+        <v>958</v>
       </c>
       <c r="H300" s="2" t="n">
-        <v>1400</v>
+        <v>505</v>
       </c>
       <c r="I300" s="3">
         <f>IF(G300=0,0,1-H300/G300)</f>
         <v/>
       </c>
       <c r="J300" s="2" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="K300" s="2" t="n">
         <v>8</v>
       </c>
       <c r="L300" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M300" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N300" s="2" t="n">
         <v>0</v>
@@ -39240,10 +39164,10 @@
         <v>8</v>
       </c>
       <c r="P300" s="2" t="n">
-        <v>1694.5</v>
+        <v>1581.5</v>
       </c>
       <c r="Q300" s="2" t="n">
-        <v>0</v>
+        <v>709.4</v>
       </c>
       <c r="R300" s="2" t="inlineStr">
         <is>
@@ -39256,7 +39180,7 @@
         </is>
       </c>
       <c r="T300" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U300" s="2" t="n">
         <v>0</v>
@@ -39266,7 +39190,7 @@
       </c>
       <c r="W300" s="2" t="inlineStr">
         <is>
-          <t>Candy</t>
+          <t>Burbank</t>
         </is>
       </c>
       <c r="X300" s="2" t="inlineStr">
@@ -39281,7 +39205,7 @@
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -39291,12 +39215,12 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-1</t>
+          <t>reg-us-v-2-2</t>
         </is>
       </c>
       <c r="AC300" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 single-window mover)</t>
         </is>
       </c>
       <c r="AD300" s="5" t="n"/>
@@ -39305,55 +39229,55 @@
       <c r="AG300" s="5" t="n"/>
       <c r="AH300" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md; the Geary 5/5.45/6 a.m. ladder + rows landed pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-2-burbank.md; ED-58 V Corps regulars exemplar (+80)</t>
         </is>
       </c>
       <c r="AI300" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
+          <t>Burbank's 2nd Regulars (2/7/10/11/17 US); Burbank unwounded; officer block: 40 of 80 officers casualties (7k/33w) - the intensity primary</t>
         </is>
       </c>
       <c r="AJ300" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>PRIMARY 'less than 900 muskets' beside B&amp;M 958 all-ranks (two-scope, carried un-averaged - the Tilton pattern)</t>
         </is>
       </c>
       <c r="AK300" s="5" t="inlineStr">
         <is>
-          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
+          <t>[D] morning right of XII Corps; [C +80] 'about 5 p.m.' stated deployment to the LRT north slope (~18:15-18:40 canonical); [D] the advance line at the fence/stone wall on the Wheatfield's edge (Sweitzer's fence ground); tablet (3888.6,2907.8) + j2-04 bar column</t>
         </is>
       </c>
       <c r="AL300" s="5" t="inlineStr">
         <is>
-          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
+          <t>[B 8-12 min] deployment leg; [B 4-7 min] the double-quick marsh crossing + ascent; [D trigger + B 5-8 min] THE FLANK-FIRE EXTRACTION ('moving through a wheat-field to our rear' -&gt; both-flank fire on the recrossing)</t>
         </is>
       </c>
       <c r="AM300" s="5" t="inlineStr">
         <is>
-          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
+          <t>[D] the stone-wall fight vs Wofford's sweep + the renewal (the W4 mechanism's fifth attestation); July 3 'was not engaged again' (negative closure)</t>
         </is>
       </c>
       <c r="AN300" s="5" t="inlineStr">
         <is>
-          <t>p. 184 rows (pass 10): 139 = 5 OH 18, 7 OH 18, 29 OH 38, 66 OH 17, 28 Pa 28, 147 Pa 20 (sum exact)</t>
+          <t>tablet = return EXACT 447 (7+71/32+310/27) 'of 900 muskets' - ~50% rate, the pass's highest; single-window dominant, extraction the peak; officer half-loss pins intensity</t>
         </is>
       </c>
       <c r="AO300" s="5" t="n"/>
       <c r="AP300" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>us-carr</t>
+          <t>us-burling</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
+          <t>Burling's Brigade (3rd Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -39377,23 +39301,23 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>1718</v>
+        <v>1365</v>
       </c>
       <c r="H301" s="2" t="n">
-        <v>925</v>
+        <v>850</v>
       </c>
       <c r="I301" s="3">
         <f>IF(G301=0,0,1-H301/G301)</f>
         <v/>
       </c>
       <c r="J301" s="2" t="n">
-        <v>793</v>
+        <v>515</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L301" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M301" s="2" t="n">
         <v>2</v>
@@ -39402,13 +39326,13 @@
         <v>0</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P301" s="2" t="n">
-        <v>1004.4</v>
+        <v>1132.2</v>
       </c>
       <c r="Q301" s="2" t="n">
-        <v>921.4</v>
+        <v>1068.4</v>
       </c>
       <c r="R301" s="2" t="inlineStr">
         <is>
@@ -39421,17 +39345,17 @@
         </is>
       </c>
       <c r="T301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V301" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V301" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="W301" s="2" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Burling</t>
         </is>
       </c>
       <c r="X301" s="2" t="inlineStr">
@@ -39456,12 +39380,12 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-2-1</t>
+          <t>reg-us-iii-2-3</t>
         </is>
       </c>
       <c r="AC301" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 DISPERSED class)</t>
         </is>
       </c>
       <c r="AD301" s="5" t="n"/>
@@ -39470,55 +39394,55 @@
       <c r="AG301" s="5" t="n"/>
       <c r="AH301" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-3-burling.md; the dispersed-class EC4/EC6 structure recorded as reusable method</t>
         </is>
       </c>
       <c r="AI301" s="5" t="inlineStr">
         <is>
-          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
+          <t>Burling's bde (2 NH, 5/6/7/8 NJ, 115 PA); Burling unwounded; pin: Lt. Clark (ambulance officer) mw 'died on the field' (staff-echelon class)</t>
         </is>
       </c>
       <c r="AJ301" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
+          <t>B&amp;M-type 1,365 (hop flagged); 115th PA 'about 140' (regiment-grain primary)</t>
         </is>
       </c>
       <c r="AK301" s="5" t="inlineStr">
         <is>
-          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
+          <t>[C tablet] reserve mass in rear of Brewster ~15:00-17:00; tablet (3556.4,2999.4) stands on the DETACHED-majority ground (semantics noted); THE DISPERSAL LEDGER: 2NH+7NJ-&gt;Graham, 5NJ-&gt;Seeley picket, 6NJ-&gt;Ward, 8NJ+115PA-&gt;Wheatfield ('taken from me without my knowledge'), Burling+115PA-&gt;Humphreys - each drawn on its host's ground (j2-03/j2-04 bars)</t>
         </is>
       </c>
       <c r="AL301" s="5" t="inlineStr">
         <is>
-          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
+          <t>NO single-body leg after ~17:00 - detachments inherit host legs (Graham's collapse; ED-57 waves); brigade centroid a fiction after the dispersal (AUTHORING NOTE)</t>
         </is>
       </c>
       <c r="AM301" s="5" t="inlineStr">
         <is>
-          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
+          <t>[D] reserve's flank-artillery endurance at 1,000 yards; detachment fights via hosts (2nd NH's orchard fight = 193, the ledger's bloodiest); Burling's rally fragment</t>
         </is>
       </c>
       <c r="AN301" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
+          <t>TRIPLE EXACT report = tablet = return 513 (6+53/43+333/78); Humphreys's division-grain 430 k+w consistent as the k+w component; apportionment BY DETACHMENT (sum of five host curves, not a unit spike)</t>
         </is>
       </c>
       <c r="AO301" s="5" t="n"/>
       <c r="AP301" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 full-arc (dispersed class)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>us-carroll</t>
+          <t>us-candy</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
+          <t>Candy's Brigade (1st Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -39538,14 +39462,14 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G302" s="2" t="n">
-        <v>640</v>
+        <v>1400</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>640</v>
+        <v>1400</v>
       </c>
       <c r="I302" s="3">
         <f>IF(G302=0,0,1-H302/G302)</f>
@@ -39555,10 +39479,10 @@
         <v>0</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L302" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M302" s="2" t="n">
         <v>0</v>
@@ -39567,13 +39491,13 @@
         <v>0</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P302" s="2" t="n">
-        <v>822.3</v>
+        <v>1938.7</v>
       </c>
       <c r="Q302" s="2" t="n">
-        <v>813.7</v>
+        <v>0</v>
       </c>
       <c r="R302" s="2" t="inlineStr">
         <is>
@@ -39592,11 +39516,11 @@
         <v>0</v>
       </c>
       <c r="V302" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W302" s="2" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Candy</t>
         </is>
       </c>
       <c r="X302" s="2" t="inlineStr">
@@ -39621,12 +39545,12 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-1</t>
+          <t>reg-us-xii-2-1</t>
         </is>
       </c>
       <c r="AC302" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD302" s="5" t="n"/>
@@ -39635,55 +39559,55 @@
       <c r="AG302" s="5" t="n"/>
       <c r="AH302" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-1-candy.md; the Geary 5/5.45/6 a.m. ladder + rows landed pass 10</t>
         </is>
       </c>
       <c r="AI302" s="5" t="inlineStr">
         <is>
-          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
+          <t>1st Bde 2nd Div XII (5/7/29/66 OH, 28/147 PA); Candy throughout</t>
         </is>
       </c>
       <c r="AJ302" s="5" t="inlineStr">
         <is>
-          <t>no primary; build 640 (compilation, flagged)</t>
+          <t>OPEN (no primary; no hop)</t>
         </is>
       </c>
       <c r="AK302" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
+          <t>[E] reserve hollow (j3-01 CANDY'S BRIG label (5620,5114); HQ pin w/ OSM duplicates flagged); [D] the 66th OH outside-the-works ground (mon-66oh, non-works-line semantics)</t>
         </is>
       </c>
       <c r="AL302" s="5" t="inlineStr">
         <is>
-          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
+          <t>[C 19:00-&gt;00:30] the wrong-road round trip ('supposed to be General Hancock's'; 28th PA 12.30 a.m. forward); [D] the 66th OH over-the-crest deployment; rotation legs</t>
         </is>
       </c>
       <c r="AM302" s="5" t="inlineStr">
         <is>
-          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
+          <t>the confusion confession; the 3.45 a.m. pre-program clock (profiled [-45,15]); the 66th OH enfilade; rotation service</t>
         </is>
       </c>
       <c r="AN302" s="5" t="inlineStr">
         <is>
-          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
+          <t>p. 184 rows (pass 10): 139 = 5 OH 18, 7 OH 18, 29 OH 38, 66 OH 17, 28 Pa 28, 147 Pa 20 (sum exact)</t>
         </is>
       </c>
       <c r="AO302" s="5" t="n"/>
       <c r="AP302" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>us-colgrove</t>
+          <t>us-carr</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
+          <t>Carr's Brigade (1st Bde, 2nd Div, III Corps)</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -39707,38 +39631,38 @@
         </is>
       </c>
       <c r="G303" s="2" t="n">
-        <v>1170</v>
+        <v>1718</v>
       </c>
       <c r="H303" s="2" t="n">
-        <v>1170</v>
+        <v>925</v>
       </c>
       <c r="I303" s="3">
         <f>IF(G303=0,0,1-H303/G303)</f>
         <v/>
       </c>
       <c r="J303" s="2" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L303" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N303" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P303" s="2" t="n">
-        <v>1103.4</v>
+        <v>1004.4</v>
       </c>
       <c r="Q303" s="2" t="n">
-        <v>0</v>
+        <v>921.4</v>
       </c>
       <c r="R303" s="2" t="inlineStr">
         <is>
@@ -39751,17 +39675,17 @@
         </is>
       </c>
       <c r="T303" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U303" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V303" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W303" s="2" t="inlineStr">
         <is>
-          <t>Colgrove</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="X303" s="2" t="inlineStr">
@@ -39776,7 +39700,7 @@
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -39786,12 +39710,12 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-3</t>
+          <t>reg-us-iii-2-1</t>
         </is>
       </c>
       <c r="AC303" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (the CA-J3M-3 executor)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD303" s="5" t="n"/>
@@ -39800,37 +39724,37 @@
       <c r="AG303" s="5" t="n"/>
       <c r="AH303" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-2-1-carr.md; the 4.08/3.22 minute-precision AGREEING clocks = the ED-58 counter-exemplar (profiled medium)</t>
         </is>
       </c>
       <c r="AI303" s="5" t="inlineStr">
         <is>
-          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
+          <t>Carr's bde (1/11/16 MA, 12 NH, 11 NJ, 26 PA; 84 PA detached); Carr unwounded</t>
         </is>
       </c>
       <c r="AJ303" s="5" t="inlineStr">
         <is>
-          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
+          <t>B&amp;M-type 1,718 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AK303" s="5" t="inlineStr">
         <is>
-          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
+          <t>[C ~0 medium] the road line at 4.08 p.m. stated (~16:10 canonical); tablet (3681.8,4287.2) + Rogers-house marker ON the line (28 m agreement with the drawn house); [E drawn j2-03] 'Carr's Brig' (3826,4331), 1st MA drawn as separate forward skirmish element (3463,4407); [E drawn j2-04] 'CARR.' with NE withdrawal arrows (3669,4283)</t>
         </is>
       </c>
       <c r="AL303" s="5" t="inlineStr">
         <is>
-          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
+          <t>[C 4.08 p.m.] the 300-yard advance; [D trigger] change of front when the left gave way; [B 12-18 min] the division fighting-withdrawal leg; the dusk counterattack return</t>
         </is>
       </c>
       <c r="AM303" s="5" t="inlineStr">
         <is>
-          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
+          <t>[D] skirmish screen from ~11 a.m., front 'merely made demonstrations' until the collapse; the front+flank fire window 18:30-19:15 (Wilcox/Lang receiving counterparts); July 3 close-column under the cannonade (tablet 'suffered severely')</t>
         </is>
       </c>
       <c r="AN303" s="5" t="inlineStr">
         <is>
-          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
+          <t>tablet = return EXACT 790 (10+111/45+559/2+63); episode: the evening window dominant + a July 3 artillery component - two-day shape</t>
         </is>
       </c>
       <c r="AO303" s="5" t="n"/>
@@ -39843,12 +39767,12 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>us-coster</t>
+          <t>us-carroll</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
+          <t>Carroll's Brigade (1st Bde, 3rd Div, II Corps — minus the 8th Ohio)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -39868,27 +39792,27 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G304" s="2" t="n">
-        <v>1156</v>
+        <v>640</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>655</v>
+        <v>640</v>
       </c>
       <c r="I304" s="3">
         <f>IF(G304=0,0,1-H304/G304)</f>
         <v/>
       </c>
       <c r="J304" s="2" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="K304" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L304" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M304" s="2" t="n">
         <v>0</v>
@@ -39897,13 +39821,13 @@
         <v>0</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P304" s="2" t="n">
-        <v>3972.6</v>
+        <v>822.3</v>
       </c>
       <c r="Q304" s="2" t="n">
-        <v>455.5</v>
+        <v>813.7</v>
       </c>
       <c r="R304" s="2" t="inlineStr">
         <is>
@@ -39912,7 +39836,7 @@
       </c>
       <c r="S304" s="2" t="inlineStr">
         <is>
-          <t>column/line/scattered</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="T304" s="2" t="n">
@@ -39922,11 +39846,11 @@
         <v>0</v>
       </c>
       <c r="V304" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W304" s="2" t="inlineStr">
         <is>
-          <t>Coster</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="X304" s="2" t="inlineStr">
@@ -39951,12 +39875,12 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-1</t>
+          <t>reg-us-ii-3-1</t>
         </is>
       </c>
       <c r="AC304" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (WITH CAUTION: three regiments are NOT on the II Corps front July 3)</t>
         </is>
       </c>
       <c r="AD304" s="5" t="n"/>
@@ -39965,55 +39889,55 @@
       <c r="AG304" s="5" t="n"/>
       <c r="AH304" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-2-1-coster.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-1-carroll.md; AUTHORING FLAG: any July 3 render placing these three regiments at the II Corps front contradicts the primary</t>
         </is>
       </c>
       <c r="AI304" s="5" t="inlineStr">
         <is>
-          <t>Coster; NO report at any brigade echelon (verified negative - the third XI no-report brigade)</t>
+          <t>Col. S.S. Carroll; 14th Ind (Coons), 4th Oh (Carpenter), 7th WV (Lockwood); report written July 5 AT Two Taverns (earliest-dated Union brigade report fetched)</t>
         </is>
       </c>
       <c r="AJ304" s="5" t="inlineStr">
         <is>
-          <t>No primary (negative); B&amp;M-repro 1,156 (hop); the brickyard force = three regiments (73rd Pa stayed on the hill)</t>
+          <t>no primary; build 640 (compilation, flagged)</t>
         </is>
       </c>
       <c r="AK304" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00 via von Steinwehr] Cemetery Hill NE supporting Wiedrich (+ the stone-church regiment); [D] the brickyard line NE of town; the fall-back with the brick-house stopper; the hill's NE front July 2-3</t>
+          <t>[C] Jul 2 ~08:00 between Woodruff and Taneytown road; [D vs CA-J2E-3] Jul 2 ~20:00 -&gt; East Cemetery Hill, HELD THROUGH JULY 5 (j2-05 script label (5100,5624) +-150m; residual bars (4671,5265)) | pass-8: label re-read 27 m repeatability; ECH HQ marker (5024.1,5793.3) 34 m from mon-ricketts</t>
         </is>
       </c>
       <c r="AL304" s="5" t="inlineStr">
         <is>
-          <t>[D] the through-town commitment to the brickyard; the covered fall-back</t>
+          <t>[D vs CA-J2E-3] the night rush, 3 regiments, 14th Ind leading, guided by Howard's aide; no return leg Jul 3</t>
         </is>
       </c>
       <c r="AM304" s="5" t="inlineStr">
         <is>
-          <t>The brickyard delaying action (division grain + BOTH-SIDED by Hays/Avery pass 10); the brick-house stopper</t>
+          <t>[D] ECH night fight among Wiedrich/Ricketts guns (or-27-2-hays opposite); [A window] Jul 3 'exposed to a great deal of cross-firing' on the hill (ED-44-class under-fire state); ledger 252 prisoners/113 wounded/37 buried/349 arms</t>
         </is>
       </c>
       <c r="AN304" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183: 252/200/111/34 = 597 aggregate-exact (m column row-forced 313, noisy); the minutes-scale single-spike wreck second only to Iverson's</t>
+          <t>return 211: 14th Ind 31, 4th Oh 31, 8th Oh 102 (own row), 7th WV 47; episode split Jul-2-night + Jul-3-crossfire dominant (no per-day primary)</t>
         </is>
       </c>
       <c r="AO304" s="5" t="n"/>
       <c r="AP304" s="5" t="inlineStr">
         <is>
-          <t>T2 (honestly thin; the fight T3 via the attackers)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>us-coulter</t>
+          <t>us-colgrove</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
+          <t>Colgrove's Brigade (3rd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -40033,42 +39957,42 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G305" s="2" t="n">
-        <v>1262</v>
+        <v>1170</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="I305" s="3">
         <f>IF(G305=0,0,1-H305/G305)</f>
         <v/>
       </c>
       <c r="J305" s="2" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="K305" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L305" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N305" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O305" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P305" s="2" t="n">
-        <v>7940.8</v>
+        <v>1249.1</v>
       </c>
       <c r="Q305" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R305" s="2" t="inlineStr">
         <is>
@@ -40091,7 +40015,7 @@
       </c>
       <c r="W305" s="2" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Colgrove</t>
         </is>
       </c>
       <c r="X305" s="2" t="inlineStr">
@@ -40116,12 +40040,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-2-1</t>
+          <t>reg-us-xii-1-3</t>
         </is>
       </c>
       <c r="AC305" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (the CA-J3M-3 executor)</t>
         </is>
       </c>
       <c r="AD305" s="5" t="n"/>
@@ -40130,55 +40054,55 @@
       <c r="AG305" s="5" t="n"/>
       <c r="AH305" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-2-1-paul.md; the ED-52 Union day-split exemplar</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-3-colgrove.md; THE SPANGLER'S MEADOW TWO-POLE record -&gt; ED-64 candidate (5.30/6 a.m. executor pole vs Ruger ~10 a.m. + Bachelder 8-11 sheet)</t>
         </is>
       </c>
       <c r="AI305" s="5" t="inlineStr">
         <is>
-          <t>THE CASCADE: Paul severely w -&gt; Leonard w -&gt; Root w -&gt; Coulter (assigned on Cemetery Hill, w himself July 3) - five commanders; three Paul staff missing</t>
+          <t>3rd Bde 1st Div XII (27 IN/2 MA/13 NJ/107 NY/3 WI); Ruger to div morning July 2, Colgrove up; MUDGE k in the charge (Morse succession primary)</t>
         </is>
       </c>
       <c r="AJ305" s="5" t="inlineStr">
         <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,537 (hop); 16th Me ~275 literature-class NOT hopped</t>
+          <t>27th IN 339 PRIMARY (=monument exact); 2nd MA 294 EM + 22 officers (Cogswell + monument); other three OPEN</t>
         </is>
       </c>
       <c r="AK305" s="5" t="inlineStr">
         <is>
-          <t>[D] the seminary rail-barricade (Paul entrenching - the artifact Perrin stormed, both-sided); the Oak Ridge relief slots; the 16th Maine sacrifice hill; Cemetery Hill; the Baxter-parallel July 2-3 ladder</t>
+          <t>[A] the meadow's south works (mon-2ma START-line semantics; mon-27in; HQ pin); [D] the 27th IN advance marker (6115.9,4964.0) = 79 m north of main (the '90 yards'); j3-01 position vs j3-02 charge drawn states 59/69 m from the stones</t>
         </is>
       </c>
       <c r="AL305" s="5" t="inlineStr">
         <is>
-          <t>[D ~15:00] the relief insertion (Coulter-clocked); the 16th Me detachment + three-stage collapse; the town retreat</t>
+          <t>[C] the July 2 left-wing round trip (back 'about 10 p.m.'); [B] the 100-yard double-quick charge + the 27th's double-distance oblique; [C ~17:00] 13 NJ/107 NY to Gregg</t>
         </is>
       </c>
       <c r="AM305" s="5" t="inlineStr">
         <is>
-          <t>The repeated-attacks repulse record (division grain); the 16th Maine hold-as-long-as-there-is-a-man order VERBATIM; July 2 dark gauntlet run; July 3 arrival at the repulse</t>
+          <t>THE ORDER-CORRUPTION PAIR ('The general directs that you advance your line immediately' via Lt. Snow vs Ruger's skirmishers-first intent); the no-skirmish decision primary; charge-repulse-counter-repulse; ~100 prisoners</t>
         </is>
       </c>
       <c r="AN305" s="5" t="inlineStr">
         <is>
-          <t>THE DAY-SPLIT PRIMARY: 776/28/14/3 = 821 (Coulter's table, excl. 11th Pa Jul 1); 16th Me July 1 223 (162 m = the pocket)</t>
+          <t>return 279 (27 IN 110 / 2 MA 136 = 88% of it); Fesler's charge-vs-works itemized split (98 of 111 in the charge); the 110/111/112 and 130/135/136 component clusters ALL carried</t>
         </is>
       </c>
       <c r="AO305" s="5" t="n"/>
       <c r="AP305" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>us-cutler</t>
+          <t>us-coster</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
+          <t>Coster's Brigade (1st Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -40198,42 +40122,42 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G306" s="2" t="n">
-        <v>1220</v>
+        <v>1156</v>
       </c>
       <c r="H306" s="2" t="n">
-        <v>1015</v>
+        <v>655</v>
       </c>
       <c r="I306" s="3">
         <f>IF(G306=0,0,1-H306/G306)</f>
         <v/>
       </c>
       <c r="J306" s="2" t="n">
-        <v>205</v>
+        <v>501</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N306" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P306" s="2" t="n">
-        <v>7473.3</v>
+        <v>3972.6</v>
       </c>
       <c r="Q306" s="2" t="n">
-        <v>1352.5</v>
+        <v>455.5</v>
       </c>
       <c r="R306" s="2" t="inlineStr">
         <is>
@@ -40242,11 +40166,11 @@
       </c>
       <c r="S306" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>column/line/scattered</t>
         </is>
       </c>
       <c r="T306" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U306" s="2" t="n">
         <v>0</v>
@@ -40256,7 +40180,7 @@
       </c>
       <c r="W306" s="2" t="inlineStr">
         <is>
-          <t>Cutler</t>
+          <t>Coster</t>
         </is>
       </c>
       <c r="X306" s="2" t="inlineStr">
@@ -40281,12 +40205,12 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-2</t>
+          <t>reg-us-xi-2-1</t>
         </is>
       </c>
       <c r="AC306" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AD306" s="5" t="n"/>
@@ -40295,55 +40219,55 @@
       <c r="AG306" s="5" t="n"/>
       <c r="AH306" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-1-2-cutler.md; three agreeing clocks (10/2/4)</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-2-1-coster.md</t>
         </is>
       </c>
       <c r="AI306" s="5" t="inlineStr">
         <is>
-          <t>Cutler; Grover k, Miller w (the order-undelivered cause), Biddle (95 NY) w; 7th Ind detached in rear July 1</t>
+          <t>Coster; NO report at any brigade echelon (verified negative - the third XI no-report brigade)</t>
         </is>
       </c>
       <c r="AJ306" s="5" t="inlineStr">
         <is>
-          <t>regiment primaries: 147 NY 380, 76 NY 375, 56 Pa 252</t>
+          <t>No primary (negative); B&amp;M-repro 1,156 (hop); the brickyard force = three regiments (73rd Pa stayed on the hill)</t>
         </is>
       </c>
       <c r="AK306" s="5" t="inlineStr">
         <is>
-          <t>[B+drawn] the opening line across the RR (j1-03 CUTLER label + 147 NY bar + HALL 2'ME); the 2 o'clock changed front; the embankment retreat line; the 7th Ind Culp's Hill first-occupation pin; July 2-3 next to Greene</t>
+          <t>[C ~14:00 via von Steinwehr] Cemetery Hill NE supporting Wiedrich (+ the stone-church regiment); [D] the brickyard line NE of town; the fall-back with the brick-house stopper; the hill's NE front July 2-3</t>
         </is>
       </c>
       <c r="AL306" s="5" t="inlineStr">
         <is>
-          <t>[D] leading-brigade march; the Wadsworth fall-back; the changed front; the perfect-steadiness embankment retreat</t>
+          <t>[D] the through-town commitment to the brickyard; the covered fall-back</t>
         </is>
       </c>
       <c r="AM306" s="5" t="inlineStr">
         <is>
-          <t>first infantry engaged ('in action from 10 a.m. until 4 p.m.'); the 147th's stranded half-hour; the afternoon flank volley (a CSA regiment surrendered - Iverson-front both-sided); Hubbard's 18-man provost guard in the line</t>
+          <t>The brickyard delaying action (division grain + BOTH-SIDED by Hays/Avery pass 10); the brick-house stopper</t>
         </is>
       </c>
       <c r="AN306" s="5" t="inlineStr">
         <is>
-          <t>return (p. 173) 1,002; RATE-CLASS primaries: 147 NY 207/380 in half an hour, 76 NY 169 in thirty minutes</t>
+          <t>Return p. 183: 252/200/111/34 = 597 aggregate-exact (m column row-forced 313, noisy); the minutes-scale single-spike wreck second only to Iverson's</t>
         </is>
       </c>
       <c r="AO306" s="5" t="n"/>
       <c r="AP306" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T2 (honestly thin; the fight T3 via the attackers)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>us-dana</t>
+          <t>us-coulter</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
+          <t>Coulter's Brigade (1st Bde, 2nd Div, I Corps — Paul's)</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -40367,38 +40291,38 @@
         </is>
       </c>
       <c r="G307" s="2" t="n">
-        <v>1317</v>
+        <v>1262</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="I307" s="3">
         <f>IF(G307=0,0,1-H307/G307)</f>
         <v/>
       </c>
       <c r="J307" s="2" t="n">
-        <v>852</v>
+        <v>752</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L307" s="2" t="n">
         <v>16</v>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N307" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O307" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P307" s="2" t="n">
-        <v>7301.7</v>
+        <v>7940.8</v>
       </c>
       <c r="Q307" s="2" t="n">
-        <v>750</v>
+        <v>10</v>
       </c>
       <c r="R307" s="2" t="inlineStr">
         <is>
@@ -40411,7 +40335,7 @@
         </is>
       </c>
       <c r="T307" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U307" s="2" t="n">
         <v>0</v>
@@ -40421,7 +40345,7 @@
       </c>
       <c r="W307" s="2" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="X307" s="2" t="inlineStr">
@@ -40446,12 +40370,12 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-3-2</t>
+          <t>reg-us-i-2-1</t>
         </is>
       </c>
       <c r="AC307" s="5" t="inlineStr">
         <is>
-          <t>attested-static (sheet grain)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AD307" s="5" t="n"/>
@@ -40460,55 +40384,55 @@
       <c r="AG307" s="5" t="n"/>
       <c r="AH307" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
+          <t>Dossier: reconstruction/dossiers/us-i-2-1-paul.md; the ED-52 Union day-split exemplar</t>
         </is>
       </c>
       <c r="AI307" s="5" t="inlineStr">
         <is>
-          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
+          <t>THE CASCADE: Paul severely w -&gt; Leonard w -&gt; Root w -&gt; Coulter (assigned on Cemetery Hill, w himself July 3) - five commanders; three Paul staff missing</t>
         </is>
       </c>
       <c r="AJ307" s="5" t="inlineStr">
         <is>
-          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
+          <t>No brigade primary (negative); B&amp;M-repro 1,537 (hop); 16th Me ~275 literature-class NOT hopped</t>
         </is>
       </c>
       <c r="AK307" s="5" t="inlineStr">
         <is>
-          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
+          <t>[D] the seminary rail-barricade (Paul entrenching - the artifact Perrin stormed, both-sided); the Oak Ridge relief slots; the 16th Maine sacrifice hill; Cemetery Hill; the Baxter-parallel July 2-3 ladder</t>
         </is>
       </c>
       <c r="AL307" s="5" t="inlineStr">
         <is>
-          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
+          <t>[D ~15:00] the relief insertion (Coulter-clocked); the 16th Me detachment + three-stage collapse; the town retreat</t>
         </is>
       </c>
       <c r="AM307" s="5" t="inlineStr">
         <is>
-          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative) ; p11 back-extension: Roy Stone's report in full - the 11:00 / 12-1 Oak Hill enfilade / 1.30 grand-advance clock ladder (ED-69 candidate primary); the RR-cut episode; the cascade in action; 'nearly two-thirds... fell'</t>
+          <t>The repeated-attacks repulse record (division grain); the 16th Maine hold-as-long-as-there-is-a-man order VERBATIM; July 2 dark gauntlet run; July 3 arrival at the repulse</t>
         </is>
       </c>
       <c r="AN307" s="5" t="inlineStr">
         <is>
-          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
+          <t>THE DAY-SPLIT PRIMARY: 776/28/14/3 = 821 (Coulter's table, excl. 11th Pa Jul 1); 16th Me July 1 223 (162 m = the pocket)</t>
         </is>
       </c>
       <c r="AO307" s="5" t="n"/>
       <c r="AP307" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 (July 1 grain; full arc T2)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>us-day</t>
+          <t>us-cutler</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
+          <t>Cutler's Brigade (2nd Bde, 1st Div, I Corps)</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -40528,72 +40452,72 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G308" s="2" t="n">
-        <v>1574</v>
+        <v>1220</v>
       </c>
       <c r="H308" s="2" t="n">
-        <v>1170</v>
+        <v>1015</v>
       </c>
       <c r="I308" s="3">
         <f>IF(G308=0,0,1-H308/G308)</f>
         <v/>
       </c>
       <c r="J308" s="2" t="n">
-        <v>404</v>
+        <v>205</v>
       </c>
       <c r="K308" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L308" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M308" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>7473.3</v>
+      </c>
+      <c r="Q308" s="2" t="n">
+        <v>1352.5</v>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>column/line</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N308" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P308" s="2" t="n">
-        <v>1477.1</v>
-      </c>
-      <c r="Q308" s="2" t="n">
-        <v>685.4</v>
-      </c>
-      <c r="R308" s="2" t="inlineStr">
+      <c r="U308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V308" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>Cutler</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S308" s="2" t="inlineStr">
-        <is>
-          <t>column/line</t>
-        </is>
-      </c>
-      <c r="T308" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U308" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V308" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W308" s="2" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="X308" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
           <t>T1</t>
@@ -40611,12 +40535,12 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-1</t>
+          <t>reg-us-i-1-2</t>
         </is>
       </c>
       <c r="AC308" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 single-window mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD308" s="5" t="n"/>
@@ -40625,55 +40549,55 @@
       <c r="AG308" s="5" t="n"/>
       <c r="AH308" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
+          <t>Dossier: reconstruction/dossiers/us-i-1-2-cutler.md; three agreeing clocks (10/2/4)</t>
         </is>
       </c>
       <c r="AI308" s="5" t="inlineStr">
         <is>
-          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
+          <t>Cutler; Grover k, Miller w (the order-undelivered cause), Biddle (95 NY) w; 7th Ind detached in rear July 1</t>
         </is>
       </c>
       <c r="AJ308" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
+          <t>regiment primaries: 147 NY 380, 76 NY 375, 56 Pa 252</t>
         </is>
       </c>
       <c r="AK308" s="5" t="inlineStr">
         <is>
-          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
+          <t>[B+drawn] the opening line across the RR (j1-03 CUTLER label + 147 NY bar + HALL 2'ME); the 2 o'clock changed front; the embankment retreat line; the 7th Ind Culp's Hill first-occupation pin; July 2-3 next to Greene</t>
         </is>
       </c>
       <c r="AL308" s="5" t="inlineStr">
         <is>
-          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
+          <t>[D] leading-brigade march; the Wadsworth fall-back; the changed front; the perfect-steadiness embankment retreat</t>
         </is>
       </c>
       <c r="AM308" s="5" t="inlineStr">
         <is>
-          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
+          <t>first infantry engaged ('in action from 10 a.m. until 4 p.m.'); the 147th's stranded half-hour; the afternoon flank volley (a CSA regiment surrendered - Iverson-front both-sided); Hubbard's 18-man provost guard in the line</t>
         </is>
       </c>
       <c r="AN308" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
+          <t>return (p. 173) 1,002; RATE-CLASS primaries: 147 NY 207/380 in half an hour, 76 NY 169 in thirty minutes</t>
         </is>
       </c>
       <c r="AO308" s="5" t="n"/>
       <c r="AP308" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc (thin - division-report class)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>us-eustis</t>
+          <t>us-dana</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
+          <t>Dana's Brigade (2nd Bde, 3rd Div, I Corps — Stone's)</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -40693,55 +40617,55 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G309" s="2" t="n">
-        <v>1595</v>
+        <v>1317</v>
       </c>
       <c r="H309" s="2" t="n">
-        <v>1595</v>
+        <v>465</v>
       </c>
       <c r="I309" s="3">
         <f>IF(G309=0,0,1-H309/G309)</f>
         <v/>
       </c>
       <c r="J309" s="2" t="n">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="K309" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L309" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P309" s="2" t="n">
+        <v>7301.7</v>
+      </c>
+      <c r="Q309" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>column/line</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="M309" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N309" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O309" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P309" s="2" t="n">
-        <v>2419.9</v>
-      </c>
-      <c r="Q309" s="2" t="n">
-        <v>2219.6</v>
-      </c>
-      <c r="R309" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S309" s="2" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="T309" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="U309" s="2" t="n">
         <v>0</v>
@@ -40751,7 +40675,7 @@
       </c>
       <c r="W309" s="2" t="inlineStr">
         <is>
-          <t>Eustis</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="X309" s="2" t="inlineStr">
@@ -40766,7 +40690,7 @@
       </c>
       <c r="Z309" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA309" s="2" t="inlineStr">
@@ -40776,12 +40700,12 @@
       </c>
       <c r="AB309" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-2</t>
+          <t>reg-us-i-3-2</t>
         </is>
       </c>
       <c r="AC309" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>attested-static (sheet grain)</t>
         </is>
       </c>
       <c r="AD309" s="5" t="n"/>
@@ -40790,55 +40714,55 @@
       <c r="AG309" s="5" t="n"/>
       <c r="AH309" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-3-2-eustis.md; the corpus's 4th confirmed no-report-class Union brigade</t>
+          <t>Dossier: reconstruction/dossiers/us-i-3-2-stone.md; NO brigade/regimental report fetched for Jul 2-3 - 150th Pa regimental history is the upgrade route (standing list); pass-5: 150th Pa history standing fetch LANDED - static July 2 reading corrected, named July 3 morning losses</t>
         </is>
       </c>
       <c r="AI309" s="5" t="inlineStr">
         <is>
-          <t>2nd Bde 3rd Div VI Corps (7,10,37MA/2RI); Col Henry L. Eustis; NO brigade report - confirmed, only Rogers's 2nd RI regimental report fills the numbered slot</t>
+          <t>Stone w Jul 1 -&gt; Wister w Jul 1 -&gt; Col. E.L. Dana (143rd Pa) through the battle's end; 143rd/149th/150th Pa</t>
         </is>
       </c>
       <c r="AJ309" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>150th Pa 'aggregate for duty ... one hundred and nine' July 2 morning (chamberlin-150pa-1895, primary-adjacent); build 465 brigade remnant consistent</t>
         </is>
       </c>
       <c r="AK309" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00] arrival; [C] Jul3 right-centre reserve reporting to Newton, 'not engaged but subject to artillery fire'</t>
+          <t>[C/E] Jul 3 second/third lines behind the Vermont/Gates front (or-27-1-doubleday p.258); j3-02 STONE. (4636,4453); j3-03 STONE'S BRIG. (4755,4466) +-120m, SHALER adjacent - static across both drawn states</t>
         </is>
       </c>
       <c r="AL309" s="5" t="inlineStr">
         <is>
-          <t>not authored</t>
+          <t>[C ~18:00] July 2 double-quick down the Taneytown road to Humphreys's rear; 149th+150th to the Emmitsburg road recovering TWO GUNS (Doubleday concurring); night picket left of Codori; [C 07:00-08:00] July 3 relief under fire</t>
         </is>
       </c>
       <c r="AM309" s="5" t="inlineStr">
         <is>
-          <t>[D] present-but-not-firing; Rogers's 2RI: 'the hottest of the battle'/'severest engagement of the war' (tension w/ 'not engaged')</t>
+          <t>[E] present under the cannonade's overs; NO fire window attested Jul 3 (consistent negative) ; p11 back-extension: Roy Stone's report in full - the 11:00 / 12-1 Oak Hill enfilade / 1.30 grand-advance clock ladder (ED-69 candidate primary); the RR-cut episode; the cascade in action; 'nearly two-thirds... fell'</t>
         </is>
       </c>
       <c r="AN309" s="5" t="inlineStr">
         <is>
-          <t>tablet 69 (3k/2off+39w/25 missing) - the missing-25 figure has NO attested cause, honestly flagged</t>
+          <t>return 853 (143Pa 253, 149Pa 336, 150Pa 264); Jul 1 overwhelmingly dominant [D]; build 0 in-window decay consistent</t>
         </is>
       </c>
       <c r="AO309" s="5" t="n"/>
       <c r="AP309" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>us-fisher</t>
+          <t>us-day</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
+          <t>Day's US Regular Brigade (1st Bde, 2nd Div, V Corps)</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -40862,26 +40786,26 @@
         </is>
       </c>
       <c r="G310" s="2" t="n">
-        <v>1610</v>
+        <v>1574</v>
       </c>
       <c r="H310" s="2" t="n">
-        <v>1555</v>
+        <v>1170</v>
       </c>
       <c r="I310" s="3">
         <f>IF(G310=0,0,1-H310/G310)</f>
         <v/>
       </c>
       <c r="J310" s="2" t="n">
-        <v>55</v>
+        <v>404</v>
       </c>
       <c r="K310" s="2" t="n">
         <v>8</v>
       </c>
       <c r="L310" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M310" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N310" s="2" t="n">
         <v>0</v>
@@ -40890,10 +40814,10 @@
         <v>8</v>
       </c>
       <c r="P310" s="2" t="n">
-        <v>1158.2</v>
+        <v>1477.1</v>
       </c>
       <c r="Q310" s="2" t="n">
-        <v>1147.1</v>
+        <v>685.4</v>
       </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
@@ -40906,17 +40830,17 @@
         </is>
       </c>
       <c r="T310" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U310" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V310" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W310" s="2" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="X310" s="2" t="inlineStr">
@@ -40941,12 +40865,12 @@
       </c>
       <c r="AB310" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-2</t>
+          <t>reg-us-v-2-1</t>
         </is>
       </c>
       <c r="AC310" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 single-window mover)</t>
         </is>
       </c>
       <c r="AD310" s="5" t="n"/>
@@ -40955,55 +40879,55 @@
       <c r="AG310" s="5" t="n"/>
       <c r="AH310" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-3-2-fisher.md; independent-discovery claim flagged not adjudicated vs Rice/Chamberlain (403-blocked source)</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-1-day.md</t>
         </is>
       </c>
       <c r="AI310" s="5" t="inlineStr">
         <is>
-          <t>Col. Joseph W. Fisher, 5th/9th/10th/11th/12th PA Reserves; own report No.213-class</t>
+          <t>Day's 1st Regulars (3/4/6/12/14 US); Day unwounded; Van Rensselaer (AAAG) w; Freedley (3rd US) w commanding in action (Sheridan absent - honest command-absence record). Day's No. 204 is a FORWARDING COVER ('not called on myself for a report') - self-documented negative</t>
         </is>
       </c>
       <c r="AJ310" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>B&amp;M-type 1,574 (hop flagged); no primary (contrast Burbank's musket count)</t>
         </is>
       </c>
       <c r="AK310" s="5" t="inlineStr">
         <is>
-          <t>[C ~22:00] Big Round Top occupation; stone wall built overnight</t>
+          <t>[D] Baltimore-Pike ground then LRT north slope late day; [D] advanced across Plum Run valley behind Burbank facing the Wheatfield; tablet (3942.1,2879.1) + drawn bars (3912,2814) + division tablet cluster ~120 m; [D] retired to LRT, night to east-side woods; July 3 'remained in same position'</t>
         </is>
       </c>
       <c r="AL310" s="5" t="inlineStr">
         <is>
-          <t>[D] march to the extreme left July 2; [A ~22:00] ascent of Big Round Top w/ 20th Maine</t>
+          <t>[B 3-6 min] the double-quick swampy-ground crossing (Ayres); [D trigger] THE FACE-ABOUT WITHDRAWAL through the W4 crossfire ([B] 5-8 min return leg)</t>
         </is>
       </c>
       <c r="AM310" s="5" t="inlineStr">
         <is>
-          <t>over 30 prisoners; 1000+ stand of arms claimed, 80 CSA dead buried (own report, unverified vs CSA side)</t>
+          <t>[D] second-line fire behind Burbank; withdrawal under front+flank fire (tablet wording); July 3-4 not engaged [E/negative]</t>
         </is>
       </c>
       <c r="AN310" s="5" t="inlineStr">
         <is>
-          <t>55 (1off+5men k/3off+46w) = McCandless 155 + Fisher 55 = Crawford 210 exact</t>
+          <t>tablet = return EXACT 382 (1+45/13+305/18); SINGLE-WINDOW shape ~18:15-19:00 (in-and-out under fire); July 3 ~zero</t>
         </is>
       </c>
       <c r="AO310" s="5" t="n"/>
       <c r="AP310" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4 full-arc (thin - division-report class)</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>us-fraser</t>
+          <t>us-eustis</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
+          <t>Eustis's Brigade (2nd Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -41027,38 +40951,38 @@
         </is>
       </c>
       <c r="G311" s="2" t="n">
-        <v>975</v>
+        <v>1595</v>
       </c>
       <c r="H311" s="2" t="n">
-        <v>615</v>
+        <v>1595</v>
       </c>
       <c r="I311" s="3">
         <f>IF(G311=0,0,1-H311/G311)</f>
         <v/>
       </c>
       <c r="J311" s="2" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="K311" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L311" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M311" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N311" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O311" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="P311" s="2" t="n">
-        <v>2840.4</v>
+        <v>2419.9</v>
       </c>
       <c r="Q311" s="2" t="n">
-        <v>121</v>
+        <v>2219.6</v>
       </c>
       <c r="R311" s="2" t="inlineStr">
         <is>
@@ -41067,11 +40991,11 @@
       </c>
       <c r="S311" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>column</t>
         </is>
       </c>
       <c r="T311" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U311" s="2" t="n">
         <v>0</v>
@@ -41081,7 +41005,7 @@
       </c>
       <c r="W311" s="2" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Eustis</t>
         </is>
       </c>
       <c r="X311" s="2" t="inlineStr">
@@ -41096,7 +41020,7 @@
       </c>
       <c r="Z311" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA311" s="2" t="inlineStr">
@@ -41106,12 +41030,12 @@
       </c>
       <c r="AB311" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-3</t>
+          <t>reg-us-vi-3-2</t>
         </is>
       </c>
       <c r="AC311" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD311" s="5" t="n"/>
@@ -41120,55 +41044,55 @@
       <c r="AG311" s="5" t="n"/>
       <c r="AH311" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-2-eustis.md; the corpus's 4th confirmed no-report-class Union brigade</t>
         </is>
       </c>
       <c r="AI311" s="5" t="inlineStr">
         <is>
-          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
+          <t>2nd Bde 3rd Div VI Corps (7,10,37MA/2RI); Col Henry L. Eustis; NO brigade report - confirmed, only Rogers's 2nd RI regimental report fills the numbered slot</t>
         </is>
       </c>
       <c r="AJ311" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~975 compilation hop-flagged</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK311" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
+          <t>[C ~14:00] arrival; [C] Jul3 right-centre reserve reporting to Newton, 'not engaged but subject to artillery fire'</t>
         </is>
       </c>
       <c r="AL311" s="5" t="inlineStr">
         <is>
-          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
+          <t>not authored</t>
         </is>
       </c>
       <c r="AM311" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-3 crest fight 18:15-18:45</t>
+          <t>[D] present-but-not-firing; Rogers's 2RI: 'the hottest of the battle'/'severest engagement of the war' (tension w/ 'not engaged')</t>
         </is>
       </c>
       <c r="AN311" s="5" t="inlineStr">
         <is>
-          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
+          <t>tablet 69 (3k/2off+39w/25 missing) - the missing-25 figure has NO attested cause, honestly flagged</t>
         </is>
       </c>
       <c r="AO311" s="5" t="n"/>
       <c r="AP311" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>us-garrard</t>
+          <t>us-fisher</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
+          <t>Fisher's Pennsylvania Reserves Brigade (3rd Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -41192,17 +41116,17 @@
         </is>
       </c>
       <c r="G312" s="2" t="n">
-        <v>1490</v>
+        <v>1610</v>
       </c>
       <c r="H312" s="2" t="n">
-        <v>1290</v>
+        <v>1555</v>
       </c>
       <c r="I312" s="3">
         <f>IF(G312=0,0,1-H312/G312)</f>
         <v/>
       </c>
       <c r="J312" s="2" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="K312" s="2" t="n">
         <v>8</v>
@@ -41220,10 +41144,10 @@
         <v>8</v>
       </c>
       <c r="P312" s="2" t="n">
-        <v>1006.9</v>
+        <v>1158.2</v>
       </c>
       <c r="Q312" s="2" t="n">
-        <v>948.1</v>
+        <v>1147.1</v>
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
@@ -41236,7 +41160,7 @@
         </is>
       </c>
       <c r="T312" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U312" s="2" t="n">
         <v>0</v>
@@ -41246,7 +41170,7 @@
       </c>
       <c r="W312" s="2" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="X312" s="2" t="inlineStr">
@@ -41271,12 +41195,12 @@
       </c>
       <c r="AB312" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-2-3</t>
+          <t>reg-us-v-3-2</t>
         </is>
       </c>
       <c r="AC312" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD312" s="5" t="n"/>
@@ -41285,37 +41209,37 @@
       <c r="AG312" s="5" t="n"/>
       <c r="AH312" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
+          <t>Dossier: reconstruction/dossiers/us-v-3-2-fisher.md; independent-discovery claim flagged not adjudicated vs Rice/Chamberlain (403-blocked source)</t>
         </is>
       </c>
       <c r="AI312" s="5" t="inlineStr">
         <is>
-          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
+          <t>Col. Joseph W. Fisher, 5th/9th/10th/11th/12th PA Reserves; own report No.213-class</t>
         </is>
       </c>
       <c r="AJ312" s="5" t="inlineStr">
         <is>
-          <t>no brigade primary (open; compilation tier)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK312" s="5" t="inlineStr">
         <is>
-          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
+          <t>[C ~22:00] Big Round Top occupation; stone wall built overnight</t>
         </is>
       </c>
       <c r="AL312" s="5" t="inlineStr">
         <is>
-          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
+          <t>[D] march to the extreme left July 2; [A ~22:00] ascent of Big Round Top w/ 20th Maine</t>
         </is>
       </c>
       <c r="AM312" s="5" t="inlineStr">
         <is>
-          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
+          <t>over 30 prisoners; 1000+ stand of arms claimed, 80 CSA dead buried (own report, unverified vs CSA side)</t>
         </is>
       </c>
       <c r="AN312" s="5" t="inlineStr">
         <is>
-          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed ; p11 re-read: 140th NY digit-exact 1+25/5+84/18=133; brigade total row internally perfect 40/142/18=200; small rows off-by-one open (199 vs 200)</t>
+          <t>55 (1off+5men k/3off+46w) = McCandless 155 + Fisher 55 = Crawford 210 exact</t>
         </is>
       </c>
       <c r="AO312" s="5" t="n"/>
@@ -41328,12 +41252,12 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>us-grant</t>
+          <t>us-fraser</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
+          <t>Fraser's Brigade (3rd Bde, 1st Div, II Corps — Zook's)</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -41357,38 +41281,38 @@
         </is>
       </c>
       <c r="G313" s="2" t="n">
-        <v>1830</v>
+        <v>975</v>
       </c>
       <c r="H313" s="2" t="n">
-        <v>1830</v>
+        <v>615</v>
       </c>
       <c r="I313" s="3">
         <f>IF(G313=0,0,1-H313/G313)</f>
         <v/>
       </c>
       <c r="J313" s="2" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="K313" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L313" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L313" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M313" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N313" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P313" s="2" t="n">
-        <v>1914.5</v>
+        <v>2840.4</v>
       </c>
       <c r="Q313" s="2" t="n">
-        <v>1901.6</v>
+        <v>121</v>
       </c>
       <c r="R313" s="2" t="inlineStr">
         <is>
@@ -41401,7 +41325,7 @@
         </is>
       </c>
       <c r="T313" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U313" s="2" t="n">
         <v>0</v>
@@ -41411,7 +41335,7 @@
       </c>
       <c r="W313" s="2" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="X313" s="2" t="inlineStr">
@@ -41426,7 +41350,7 @@
       </c>
       <c r="Z313" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA313" s="2" t="inlineStr">
@@ -41436,12 +41360,12 @@
       </c>
       <c r="AB313" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-1</t>
+          <t>reg-us-ii-1-3</t>
         </is>
       </c>
       <c r="AC313" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD313" s="5" t="n"/>
@@ -41450,55 +41374,55 @@
       <c r="AG313" s="5" t="n"/>
       <c r="AH313" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-2-1-grant.md; fetched pages surfaced only a June Franklin's-Crossing letter, not Gettysburg</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-3-zook.md</t>
         </is>
       </c>
       <c r="AI313" s="5" t="inlineStr">
         <is>
-          <t>2nd Bde 2nd Div VI Corps, the Vermont Bde (2/3/4/5/6 VT); Col Lewis A. Grant; OR entry's Gettysburg content NOT located</t>
+          <t>Zook's bde (52NY/57NY/66NY/140PA); Zook mw at the advance's start (statue on Wheatfield Rd = check point) -&gt; Fraser; Col. Roberts (140PA) k</t>
         </is>
       </c>
       <c r="AJ313" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>no primary (negative); ~975 compilation hop-flagged</t>
         </is>
       </c>
       <c r="AK313" s="5" t="inlineStr">
         <is>
-          <t>[C ~17:00] 33mi march arrived 5pm Jul2; [C] Jul3 right on Round-Top-east-slope, left on Taneytown Rd, 'under no fire except artillery'</t>
+          <t>[A vs CA-J2A-8] 'most advanced position on the crest of a small hill' (stony hill N crest); tablet (3576,3138) OSM delta 54m FLAGGED</t>
         </is>
       </c>
       <c r="AL313" s="5" t="inlineStr">
         <is>
-          <t>[B] the march; [D] short Jul3 advance</t>
+          <t>[D] committed right prong; stated line-order 140PA-66NY-52NY-57NY (the batch's only one); retreat when 'fresh troops' flanked both wings (= Wofford axis, both-sided)</t>
         </is>
       </c>
       <c r="AM313" s="5" t="inlineStr">
         <is>
-          <t>[D] present-but-not-firing, ED-44 class; 5th VT on picket Jul2 night</t>
+          <t>[D] wave-3 crest fight 18:15-18:45</t>
         </is>
       </c>
       <c r="AN313" s="5" t="inlineStr">
         <is>
-          <t>tablet 1w</t>
+          <t>return 358 (140th PA 241 = 67% of brigade loss - the right-flank/Wofford-axis intensity shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AO313" s="5" t="n"/>
       <c r="AP313" s="5" t="inlineStr">
         <is>
-          <t>T3 (tablet-primary; report access gap honestly recorded)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>us-greene</t>
+          <t>us-garrard</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
+          <t>Garrard's Brigade (3rd Bde, 2nd Div, V Corps — Weed's)</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -41522,23 +41446,23 @@
         </is>
       </c>
       <c r="G314" s="2" t="n">
-        <v>1350</v>
+        <v>1490</v>
       </c>
       <c r="H314" s="2" t="n">
-        <v>1125</v>
+        <v>1290</v>
       </c>
       <c r="I314" s="3">
         <f>IF(G314=0,0,1-H314/G314)</f>
         <v/>
       </c>
       <c r="J314" s="2" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="K314" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L314" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M314" s="2" t="n">
         <v>0</v>
@@ -41547,26 +41471,26 @@
         <v>0</v>
       </c>
       <c r="O314" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P314" s="2" t="n">
-        <v>80</v>
+        <v>1006.9</v>
       </c>
       <c r="Q314" s="2" t="n">
-        <v>80</v>
+        <v>948.1</v>
       </c>
       <c r="R314" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="S314" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="T314" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U314" s="2" t="n">
         <v>0</v>
@@ -41576,7 +41500,7 @@
       </c>
       <c r="W314" s="2" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="X314" s="2" t="inlineStr">
@@ -41601,12 +41525,12 @@
       </c>
       <c r="AB314" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-3</t>
+          <t>reg-us-v-2-3</t>
         </is>
       </c>
       <c r="AC314" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD314" s="5" t="n"/>
@@ -41615,37 +41539,37 @@
       <c r="AG314" s="5" t="n"/>
       <c r="AH314" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
+          <t>Dossier: reconstruction/dossiers/us-v-2-3-weed.md; paired battery us-btty-rittenhouse.md</t>
         </is>
       </c>
       <c r="AI314" s="5" t="inlineStr">
         <is>
-          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
+          <t>Weed's bde (140/146 NY, 91/155 PA); Weed mw on the summit near the battery, d. ~21:00 ('dead as Julius Caesar', Farley) -&gt; Garrard; O'Rorke mw at the head of the 140th; Hazlett pin paired (one primary)</t>
         </is>
       </c>
       <c r="AJ314" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
+          <t>no brigade primary (open; compilation tier)</t>
         </is>
       </c>
       <c r="AK314" s="5" t="inlineStr">
         <is>
-          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
+          <t>[D] the Sickles-diversion + Sykes double-quick recall (or-27-1-sykes); [E drawn j2-03] WEED bar at the summit (4169,2640) +-62 m with the signal station; night stone wall half-way down the slope (primary)</t>
         </is>
       </c>
       <c r="AL314" s="5" t="inlineStr">
         <is>
-          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
+          <t>[B] 140th's summit rush 300-400 m at the double, in by companies without loading (Farley); brigade following under Weed</t>
         </is>
       </c>
       <c r="AM314" s="5" t="inlineStr">
         <is>
-          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
+          <t>[D] the 17:30-18:30 crisis fire on the 16th MI right; summit hold under Devil's Den sharpshooter fire; July 3 held (battery window on the paired dossier)</t>
         </is>
       </c>
       <c r="AN314" s="5" t="inlineStr">
         <is>
-          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
+          <t>return: 140th NY 133 exact; brigade 200, division 1,029; three regiment rows digit-noisy (flagged); pins O'Rorke early / Weed late / Hazlett after Weed ; p11 re-read: 140th NY digit-exact 1+25/5+84/18=133; brigade total row internally perfect 40/142/18=200; small rows off-by-one open (199 vs 200)</t>
         </is>
       </c>
       <c r="AO314" s="5" t="n"/>
@@ -41658,12 +41582,12 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>us-harris</t>
+          <t>us-grant</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
+          <t>Grant's Vermont Brigade (2nd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -41683,42 +41607,42 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G315" s="2" t="n">
-        <v>1300</v>
+        <v>1830</v>
       </c>
       <c r="H315" s="2" t="n">
-        <v>565</v>
+        <v>1830</v>
       </c>
       <c r="I315" s="3">
         <f>IF(G315=0,0,1-H315/G315)</f>
         <v/>
       </c>
       <c r="J315" s="2" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="K315" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L315" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M315" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N315" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P315" s="2" t="n">
-        <v>4777.6</v>
+        <v>1914.5</v>
       </c>
       <c r="Q315" s="2" t="n">
-        <v>724</v>
+        <v>1901.6</v>
       </c>
       <c r="R315" s="2" t="inlineStr">
         <is>
@@ -41731,17 +41655,17 @@
         </is>
       </c>
       <c r="T315" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U315" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V315" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W315" s="2" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="X315" s="2" t="inlineStr">
@@ -41756,7 +41680,7 @@
       </c>
       <c r="Z315" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA315" s="2" t="inlineStr">
@@ -41766,12 +41690,12 @@
       </c>
       <c r="AB315" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-2</t>
+          <t>reg-us-vi-2-1</t>
         </is>
       </c>
       <c r="AC315" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (the breached base wall)</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD315" s="5" t="n"/>
@@ -41780,55 +41704,55 @@
       <c r="AG315" s="5" t="n"/>
       <c r="AH315" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged; July 1 knoll extension pass 10 (drawn crest bar 57 m from the Barlow statue; the Barlow-wounding pin in Ames's echelon record)</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-2-1-grant.md; fetched pages surfaced only a June Franklin's-Crossing letter, not Gettysburg</t>
         </is>
       </c>
       <c r="AI315" s="5" t="inlineStr">
         <is>
-          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4 ; p11: the structured Barlow-Gordon record added (contemporary layer adopted - the July 7 letter + Gordon's OR pin; the 1903 memoir NO status)</t>
+          <t>2nd Bde 2nd Div VI Corps, the Vermont Bde (2/3/4/5/6 VT); Col Lewis A. Grant; OR entry's Gettysburg content NOT located</t>
         </is>
       </c>
       <c r="AJ315" s="5" t="inlineStr">
         <is>
-          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK315" s="5" t="inlineStr">
         <is>
-          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
+          <t>[C ~17:00] 33mi march arrived 5pm Jul2; [C] Jul3 right on Round-Top-east-slope, left on Taneytown Rd, 'under no fire except artillery'</t>
         </is>
       </c>
       <c r="AL315" s="5" t="inlineStr">
         <is>
-          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
+          <t>[B] the march; [D] short Jul3 advance</t>
         </is>
       </c>
       <c r="AM315" s="5" t="inlineStr">
         <is>
-          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
+          <t>[D] present-but-not-firing, ED-44 class; 5th VT on picket Jul2 night</t>
         </is>
       </c>
       <c r="AN315" s="5" t="inlineStr">
         <is>
-          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
+          <t>tablet 1w</t>
         </is>
       </c>
       <c r="AO315" s="5" t="n"/>
       <c r="AP315" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 (tablet-primary; report access gap honestly recorded)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>us-kane</t>
+          <t>us-greene</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
+          <t>Greene's Brigade (3rd Bde, 2nd Div, XII Corps)</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -41848,27 +41772,27 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G316" s="2" t="n">
-        <v>600</v>
+        <v>1350</v>
       </c>
       <c r="H316" s="2" t="n">
-        <v>600</v>
+        <v>1125</v>
       </c>
       <c r="I316" s="3">
         <f>IF(G316=0,0,1-H316/G316)</f>
         <v/>
       </c>
       <c r="J316" s="2" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="K316" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L316" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M316" s="2" t="n">
         <v>0</v>
@@ -41877,26 +41801,26 @@
         <v>0</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P316" s="2" t="n">
-        <v>1551.8</v>
+        <v>80</v>
       </c>
       <c r="Q316" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R316" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S316" s="2" t="inlineStr">
         <is>
-          <t>column/line</t>
+          <t>line</t>
         </is>
       </c>
       <c r="T316" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U316" s="2" t="n">
         <v>0</v>
@@ -41906,7 +41830,7 @@
       </c>
       <c r="W316" s="2" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Greene</t>
         </is>
       </c>
       <c r="X316" s="2" t="inlineStr">
@@ -41931,12 +41855,12 @@
       </c>
       <c r="AB316" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-2-2</t>
+          <t>reg-us-xii-2-3</t>
         </is>
       </c>
       <c r="AC316" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (CA-J2E-2 executor, the evening chain's Union spine)</t>
         </is>
       </c>
       <c r="AD316" s="5" t="n"/>
@@ -41945,37 +41869,37 @@
       <c r="AG316" s="5" t="n"/>
       <c r="AH316" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder; the 9 a.m. relief clock landed pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-3-greene.md; CA-J2E-1 primary (6.30) + E-2 both-sided (w/ Nicholls 19:00) -&gt; ED-62 evidence | PASS 9: July 3 morning frame hardened around the spine (Kane 3.30/seven-hours/10.30; Muhlenberg program; the Rodes wave opposite).</t>
         </is>
       </c>
       <c r="AI316" s="5" t="inlineStr">
         <is>
-          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
+          <t>Greene's bde (60/78/102/137/149 NY); Lane (102d) w night July 2 -&gt; Stegman; Randall (149th Lt Col) w July 3</t>
         </is>
       </c>
       <c r="AJ316" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY: 652 in action (Kane p. 848)</t>
+          <t>PRIMARY table: 'My brigade 1,350' + reinforcement ledger (355 I Corps + 400 XI + 1,000 Candy = 3,105; 'not more than 1,300 in the lines at any one time')</t>
         </is>
       </c>
       <c r="AK316" s="5" t="inlineStr">
         <is>
-          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
+          <t>[A whole-evening] the crest works (monument chain 60th NY-&gt;statue-&gt;137th; drawn bars 80-m line class); [A vs E-3] the 137th NY perpendicular refusal (mon-137ny (5814.1,5305.0), Kane's-Pos'n label 150 m)</t>
         </is>
       </c>
       <c r="AL316" s="5" t="inlineStr">
         <is>
-          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
+          <t>[D&lt;-CA-J2E-1 6.30 stated] the occupy-everything extension that could not complete; [D] Ireland's refusal + contraction in the dark</t>
         </is>
       </c>
       <c r="AM316" s="5" t="inlineStr">
         <is>
-          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
+          <t>[A 'a few minutes before 7 p.m.'] the four-charge defense (Geary: 2.5 h); [C 20:00] the right-flank crisis (=Steuart's lodgment, both-sided); the relief-rotation mechanism verbatim; enemy-loss survey (391+~150 dead, 130 prisoners, Leigh k both-sided)</t>
         </is>
       </c>
       <c r="AN316" s="5" t="inlineStr">
         <is>
-          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening); p. 184 rows (pass 10): 98 = 29 Pa 66, 109 Pa 10, 111 Pa 22 (sum exact)</t>
+          <t>report table 307 (62/213/32) vs return 303 (67/212/24) - component conflict BOTH carried; 137th NY 137 = the refused flank's cost; episode split in the regiment rows</t>
         </is>
       </c>
       <c r="AO316" s="5" t="n"/>
@@ -41988,12 +41912,12 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>us-kelly</t>
+          <t>us-harris</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
+          <t>Harris's Brigade (2nd Bde, 1st Div, XI Corps — Ames's)</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -42013,72 +41937,72 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G317" s="2" t="n">
-        <v>530</v>
+        <v>1300</v>
       </c>
       <c r="H317" s="2" t="n">
-        <v>330</v>
+        <v>565</v>
       </c>
       <c r="I317" s="3">
         <f>IF(G317=0,0,1-H317/G317)</f>
         <v/>
       </c>
       <c r="J317" s="2" t="n">
-        <v>200</v>
+        <v>735</v>
       </c>
       <c r="K317" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L317" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P317" s="2" t="n">
+        <v>4777.6</v>
+      </c>
+      <c r="Q317" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr">
+        <is>
+          <t>column/line</t>
+        </is>
+      </c>
+      <c r="T317" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N317" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O317" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P317" s="2" t="n">
-        <v>3060.7</v>
-      </c>
-      <c r="Q317" s="2" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="R317" s="2" t="inlineStr">
+      <c r="U317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V317" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S317" s="2" t="inlineStr">
-        <is>
-          <t>column/line</t>
-        </is>
-      </c>
-      <c r="T317" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U317" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V317" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W317" s="2" t="inlineStr">
-        <is>
-          <t>Kelly</t>
-        </is>
-      </c>
-      <c r="X317" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
           <t>T1</t>
@@ -42096,12 +42020,12 @@
       </c>
       <c r="AB317" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-2</t>
+          <t>reg-us-xi-1-2</t>
         </is>
       </c>
       <c r="AC317" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (the breached base wall)</t>
         </is>
       </c>
       <c r="AD317" s="5" t="n"/>
@@ -42110,37 +42034,37 @@
       <c r="AG317" s="5" t="n"/>
       <c r="AH317" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-2-harris.md; NO von Gilsa brigade report (verified negative) - cheap future closer flagged; July 1 knoll extension pass 10 (drawn crest bar 57 m from the Barlow statue; the Barlow-wounding pin in Ames's echelon record)</t>
         </is>
       </c>
       <c r="AI317" s="5" t="inlineStr">
         <is>
-          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
+          <t>Ames -&gt; division (Barlow w July 1) -&gt; HARRIS commanding the bde from late July 1; Fowler (17th CT) k July 1; Noble took over July 4 ; p11: the structured Barlow-Gordon record added (contemporary layer adopted - the July 7 letter + Gordon's OR pin; the 1903 memoir NO status)</t>
         </is>
       </c>
       <c r="AJ317" s="5" t="inlineStr">
         <is>
-          <t>530 into action PRIMARY (Kelly)</t>
+          <t>aggregate OPEN; PRIMARIES: 75th OH marched ~160 -&gt; 91 after July 1; neighbor 41st NY 218 (Einsiedel) - the brigade fought July 2 at a fraction of its return basis</t>
         </is>
       </c>
       <c r="AK317" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
+          <t>[E] the base stone wall (mon-25-75oh (5065.9,5977.3), mon-17ct (5099.2,5909.9)); [D] THE VACATED SPACE (the 17th CT move - the gap primary); [D] the re-formed rear wall</t>
         </is>
       </c>
       <c r="AL317" s="5" t="inlineStr">
         <is>
-          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
+          <t>[D] the near-sundown re-shuffle whose vacancy became the breach; [D ~20:00] the break ('in front and on the flank and rear at nearly the same time... few escaped, and those only in the darkness and smoke' - the same darkness BOTH sides claim as cover)</t>
         </is>
       </c>
       <c r="AM317" s="5" t="inlineStr">
         <is>
-          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
+          <t>all-day sharpshooter attrition (brick-kiln/houses); the wall fight; von Gilsa frame via the 41st NY (Theinhardt's stand 'until a regiment of the Second Corps arrived')</t>
         </is>
       </c>
       <c r="AN317" s="5" t="inlineStr">
         <is>
-          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
+          <t>return 778 (m-heavy 344; 17th CT 197); per-day split reconstruction BOUNDED by the two strength datapoints (July 1 dominant)</t>
         </is>
       </c>
       <c r="AO317" s="5" t="n"/>
@@ -42153,12 +42077,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>us-krzyzanowski</t>
+          <t>us-kane</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
+          <t>Kane's Brigade (2nd Bde, 2nd Div, XII Corps — Col. Cobham)</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -42178,27 +42102,27 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G318" s="2" t="n">
-        <v>1403</v>
+        <v>600</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="I318" s="3">
         <f>IF(G318=0,0,1-H318/G318)</f>
         <v/>
       </c>
       <c r="J318" s="2" t="n">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="K318" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L318" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M318" s="2" t="n">
         <v>0</v>
@@ -42207,13 +42131,13 @@
         <v>0</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P318" s="2" t="n">
-        <v>4704.7</v>
+        <v>1551.8</v>
       </c>
       <c r="Q318" s="2" t="n">
-        <v>767.4</v>
+        <v>0</v>
       </c>
       <c r="R318" s="2" t="inlineStr">
         <is>
@@ -42226,7 +42150,7 @@
         </is>
       </c>
       <c r="T318" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U318" s="2" t="n">
         <v>0</v>
@@ -42236,7 +42160,7 @@
       </c>
       <c r="W318" s="2" t="inlineStr">
         <is>
-          <t>Krzyżanowski</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="X318" s="2" t="inlineStr">
@@ -42261,12 +42185,12 @@
       </c>
       <c r="AB318" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-2</t>
+          <t>reg-us-xii-2-2</t>
         </is>
       </c>
       <c r="AC318" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD318" s="5" t="n"/>
@@ -42275,55 +42199,55 @@
       <c r="AG318" s="5" t="n"/>
       <c r="AH318" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-3-2-krzyzanowski.md; CA-J1P-3 receiving center</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-2-2-kane.md; the morning chain's cleanest receiving-side ladder; the 9 a.m. relief clock landed pass 10</t>
         </is>
       </c>
       <c r="AI318" s="5" t="inlineStr">
         <is>
-          <t>Krzyzanowski (no own report - verified negative); Col. J.S. Robinson (82nd OH) severely w; 26th WI Boebel w -&gt; Fuchs -&gt; Jacobs</t>
+          <t>2nd Bde 2nd Div XII (29/109/111 PA); the Cobham-Kane-Cobham command passage (ambulance arrival 6 a.m. July 2)</t>
         </is>
       </c>
       <c r="AJ318" s="5" t="inlineStr">
         <is>
-          <t>82nd OH PRIMARY 312 PFD (-&gt;220 Jul 11 bracket); no brigade primary; B&amp;M-repro 1,403 (hop)</t>
+          <t>PRIMARY: 652 in action (Kane p. 848)</t>
         </is>
       </c>
       <c r="AK318" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00 secondhand] arrival + the line north of town (82nd OH left, 26th WI right); [C ~16:00] the Cemetery Hill stone-fence rally; the cemetery-building position Jul 2-5</t>
+          <t>[A] works between Greene's right and Candy (mon-109pa/111pa/29pa chain + HQ pin, OSM 'Huey' mislabel flagged); j2-04 vacated vs j3-02 returned KANE labels</t>
         </is>
       </c>
       <c r="AL318" s="5" t="inlineStr">
         <is>
-          <t>[D] the forward commitment; the division-ordered fall-back through town; the ~16:00 rally</t>
+          <t>[D] the wrong-object march; [B ~1 mile dark + two fire contacts] the groping return past Greene's right</t>
         </is>
       </c>
       <c r="AM318" s="5" t="inlineStr">
         <is>
-          <t>The open-field stand vs Gordon/Doles converging (both-sided); the town gauntlet; July 2-3 attested-quiet (26th WI no-loss negative)</t>
+          <t>the night-discovery primary ('thus discovering that the enemy had entire possession of our works'); July 3: 3.30 attack, 'Johnson's division led, followed by Rodes''; SEVEN HOURS 'until about 10.30' + column-of-regiments last effort</t>
         </is>
       </c>
       <c r="AN318" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183 digit-exact: 20/140/181/111/217 = 669; 82nd OH report=return EXACT 181; July 1 near-total</t>
+          <t>Kane 96 vs Cobham 98 = return 98 (killed exact 23 at all three); July-3-weighted (absent July 2 evening); p. 184 rows (pass 10): 98 = 29 Pa 66, 109 Pa 10, 111 Pa 22 (sum exact)</t>
         </is>
       </c>
       <c r="AO318" s="5" t="n"/>
       <c r="AP318" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>us-lockwood</t>
+          <t>us-kelly</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
+          <t>Kelly's Irish Brigade (2nd Bde, 1st Div, II Corps)</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -42347,26 +42271,26 @@
         </is>
       </c>
       <c r="G319" s="2" t="n">
-        <v>1650</v>
+        <v>530</v>
       </c>
       <c r="H319" s="2" t="n">
-        <v>1650</v>
+        <v>330</v>
       </c>
       <c r="I319" s="3">
         <f>IF(G319=0,0,1-H319/G319)</f>
         <v/>
       </c>
       <c r="J319" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K319" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L319" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N319" s="2" t="n">
         <v>0</v>
@@ -42375,10 +42299,10 @@
         <v>9</v>
       </c>
       <c r="P319" s="2" t="n">
-        <v>5528.6</v>
+        <v>3060.7</v>
       </c>
       <c r="Q319" s="2" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="R319" s="2" t="inlineStr">
         <is>
@@ -42391,7 +42315,7 @@
         </is>
       </c>
       <c r="T319" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U319" s="2" t="n">
         <v>0</v>
@@ -42401,7 +42325,7 @@
       </c>
       <c r="W319" s="2" t="inlineStr">
         <is>
-          <t>Lockwood</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="X319" s="2" t="inlineStr">
@@ -42416,7 +42340,7 @@
       </c>
       <c r="Z319" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA319" s="2" t="inlineStr">
@@ -42426,12 +42350,12 @@
       </c>
       <c r="AB319" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-2</t>
+          <t>reg-us-ii-1-2</t>
         </is>
       </c>
       <c r="AC319" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD319" s="5" t="n"/>
@@ -42440,55 +42364,55 @@
       <c r="AG319" s="5" t="n"/>
       <c r="AH319" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md; Maulsby pp. 805-807 in full + p. 184 rows (174) pass 10</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-2-kelly.md</t>
         </is>
       </c>
       <c r="AI319" s="5" t="inlineStr">
         <is>
-          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
+          <t>Irish Bde (28MA/63NY/69NY/88NY/116PA); Kelly unwounded. Tablet NAMES its opponent (G.T. Anderson's bde) - tablet-layer both-siding</t>
         </is>
       </c>
       <c r="AJ319" s="5" t="inlineStr">
         <is>
-          <t>GEARY PRIMARY (pass 10): '1,700 strong' reported 7.30 a.m. July 3</t>
+          <t>530 into action PRIMARY (Kelly)</t>
         </is>
       </c>
       <c r="AK319" s="5" t="inlineStr">
         <is>
-          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
+          <t>[A vs CA-J2A-8] stony hill ('very large rocks'); tablet (3526,3160) + Celtic cross (3574,3111)</t>
         </is>
       </c>
       <c r="AL319" s="5" t="inlineStr">
         <is>
-          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
+          <t>[C +70] 'about 5 p.m.' move; [B] wheat+wood advance 10-15 min; [D] withdrawal under flank pressure thru 'terrific fire'</t>
         </is>
       </c>
       <c r="AM319" s="5" t="inlineStr">
         <is>
-          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
+          <t>[D] 45-MINUTE duration primary for the stony-hill fight; prisoners taken</t>
         </is>
       </c>
       <c r="AN319" s="5" t="inlineStr">
         <is>
-          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
+          <t>return 198 adopted vs report 202 carried (ED-52 exemplar); 28th MA carries the missing (35) in the withdrawal</t>
         </is>
       </c>
       <c r="AO319" s="5" t="n"/>
       <c r="AP319" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>us-madill</t>
+          <t>us-krzyzanowski</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
+          <t>Krzyżanowski's Brigade (2nd Bde, 3rd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -42508,42 +42432,42 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G320" s="2" t="n">
-        <v>1516</v>
+        <v>1403</v>
       </c>
       <c r="H320" s="2" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="I320" s="3">
         <f>IF(G320=0,0,1-H320/G320)</f>
         <v/>
       </c>
       <c r="J320" s="2" t="n">
-        <v>741</v>
+        <v>653</v>
       </c>
       <c r="K320" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L320" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N320" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P320" s="2" t="n">
-        <v>1383.1</v>
+        <v>4704.7</v>
       </c>
       <c r="Q320" s="2" t="n">
-        <v>1318.2</v>
+        <v>767.4</v>
       </c>
       <c r="R320" s="2" t="inlineStr">
         <is>
@@ -42566,7 +42490,7 @@
       </c>
       <c r="W320" s="2" t="inlineStr">
         <is>
-          <t>Madill</t>
+          <t>Krzyżanowski</t>
         </is>
       </c>
       <c r="X320" s="2" t="inlineStr">
@@ -42591,12 +42515,12 @@
       </c>
       <c r="AB320" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-1</t>
+          <t>reg-us-xi-3-2</t>
         </is>
       </c>
       <c r="AC320" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 static-then-forced-back)</t>
+          <t>unauthored</t>
         </is>
       </c>
       <c r="AD320" s="5" t="n"/>
@@ -42605,55 +42529,55 @@
       <c r="AG320" s="5" t="n"/>
       <c r="AH320" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-2-krzyzanowski.md; CA-J1P-3 receiving center</t>
         </is>
       </c>
       <c r="AI320" s="5" t="inlineStr">
         <is>
-          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
+          <t>Krzyzanowski (no own report - verified negative); Col. J.S. Robinson (82nd OH) severely w; 26th WI Boebel w -&gt; Fuchs -&gt; Jacobs</t>
         </is>
       </c>
       <c r="AJ320" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
+          <t>82nd OH PRIMARY 312 PFD (-&gt;220 Jul 11 bracket); no brigade primary; B&amp;M-repro 1,403 (hop)</t>
         </is>
       </c>
       <c r="AK320" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
+          <t>[C ~14:00 secondhand] arrival + the line north of town (82nd OH left, 26th WI right); [C ~16:00] the Cemetery Hill stone-fence rally; the cemetery-building position Jul 2-5</t>
         </is>
       </c>
       <c r="AL320" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
+          <t>[D] the forward commitment; the division-ordered fall-back through town; the ~16:00 rally</t>
         </is>
       </c>
       <c r="AM320" s="5" t="inlineStr">
         <is>
-          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
+          <t>The open-field stand vs Gordon/Doles converging (both-sided); the town gauntlet; July 2-3 attested-quiet (26th WI no-loss negative)</t>
         </is>
       </c>
       <c r="AN320" s="5" t="inlineStr">
         <is>
-          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
+          <t>Return p. 183 digit-exact: 20/140/181/111/217 = 669; 82nd OH report=return EXACT 181; July 1 near-total</t>
         </is>
       </c>
       <c r="AO320" s="5" t="n"/>
       <c r="AP320" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 (July 1 grain; full arc T2)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>us-mccandless</t>
+          <t>us-lockwood</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
+          <t>Lockwood's Brigade (2nd Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -42673,42 +42597,42 @@
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G321" s="2" t="n">
-        <v>1243</v>
+        <v>1650</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>1095</v>
+        <v>1650</v>
       </c>
       <c r="I321" s="3">
         <f>IF(G321=0,0,1-H321/G321)</f>
         <v/>
       </c>
       <c r="J321" s="2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="K321" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L321" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M321" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N321" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P321" s="2" t="n">
-        <v>1462.8</v>
+        <v>5968</v>
       </c>
       <c r="Q321" s="2" t="n">
-        <v>831.7</v>
+        <v>0</v>
       </c>
       <c r="R321" s="2" t="inlineStr">
         <is>
@@ -42731,7 +42655,7 @@
       </c>
       <c r="W321" s="2" t="inlineStr">
         <is>
-          <t>McCandless</t>
+          <t>Lockwood</t>
         </is>
       </c>
       <c r="X321" s="2" t="inlineStr">
@@ -42741,7 +42665,7 @@
       </c>
       <c r="Y321" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z321" s="2" t="inlineStr">
@@ -42756,12 +42680,12 @@
       </c>
       <c r="AB321" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-3-1</t>
+          <t>reg-us-xii-1-2</t>
         </is>
       </c>
       <c r="AC321" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD321" s="5" t="n"/>
@@ -42770,55 +42694,55 @@
       <c r="AG321" s="5" t="n"/>
       <c r="AH321" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-2-lockwood.md; Maulsby pp. 805-807 in full + p. 184 rows (174) pass 10</t>
         </is>
       </c>
       <c r="AI321" s="5" t="inlineStr">
         <is>
-          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
+          <t>2nd (unattached) Bde 1st Div XII (1 MD PHB/1 MD ES/150 NY); Lockwood senior-but-new; ED-61 command-grain claimant (pass 8)</t>
         </is>
       </c>
       <c r="AJ321" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
+          <t>GEARY PRIMARY (pass 10): '1,700 strong' reported 7.30 a.m. July 3</t>
         </is>
       </c>
       <c r="AK321" s="5" t="inlineStr">
         <is>
-          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
+          <t>[C] 8 a.m. July 2 arrival; [D] the July 2 evening McGilvery-line ground; [E] July 3 behind the left (HQ + three regimentals registered; 1st MD PHB at the meadow's NW woods)</t>
         </is>
       </c>
       <c r="AL321" s="5" t="inlineStr">
         <is>
-          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
+          <t>[B] the 1-mile double-quick July 2 (Maulsby); [C ~06:00] the woods deployment order; [C ~14:00] the left-center round trip (Ruger's brigade-numbering slip flagged)</t>
         </is>
       </c>
       <c r="AM321" s="5" t="inlineStr">
         <is>
-          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
+          <t>battery support at the program's edge; the 1st MD PHB woods engagement (the ~06:00 flank congestion fact in ED-64's conflation analysis)</t>
         </is>
       </c>
       <c r="AN321" s="5" t="inlineStr">
         <is>
-          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
+          <t>return 174 (1st MD PHB 104 = the woods fight's weight); no per-day primary</t>
         </is>
       </c>
       <c r="AO321" s="5" t="n"/>
       <c r="AP321" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>us-mcdougall</t>
+          <t>us-madill</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
+          <t>Madill's Brigade (1st Bde, 1st Div, III Corps — Graham's)</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -42842,38 +42766,38 @@
         </is>
       </c>
       <c r="G322" s="2" t="n">
-        <v>1755</v>
+        <v>1516</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>1755</v>
+        <v>775</v>
       </c>
       <c r="I322" s="3">
         <f>IF(G322=0,0,1-H322/G322)</f>
         <v/>
       </c>
       <c r="J322" s="2" t="n">
-        <v>0</v>
+        <v>741</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L322" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M322" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N322" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P322" s="2" t="n">
-        <v>1319.6</v>
+        <v>1383.1</v>
       </c>
       <c r="Q322" s="2" t="n">
-        <v>0</v>
+        <v>1318.2</v>
       </c>
       <c r="R322" s="2" t="inlineStr">
         <is>
@@ -42886,7 +42810,7 @@
         </is>
       </c>
       <c r="T322" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U322" s="2" t="n">
         <v>0</v>
@@ -42896,7 +42820,7 @@
       </c>
       <c r="W322" s="2" t="inlineStr">
         <is>
-          <t>McDougall</t>
+          <t>Madill</t>
         </is>
       </c>
       <c r="X322" s="2" t="inlineStr">
@@ -42911,7 +42835,7 @@
       </c>
       <c r="Z322" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA322" s="2" t="inlineStr">
@@ -42921,12 +42845,12 @@
       </c>
       <c r="AB322" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xii-1-1</t>
+          <t>reg-us-iii-1-1</t>
         </is>
       </c>
       <c r="AC322" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (July 2 static-then-forced-back)</t>
         </is>
       </c>
       <c r="AD322" s="5" t="n"/>
@@ -42935,55 +42859,55 @@
       <c r="AG322" s="5" t="n"/>
       <c r="AH322" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-1-graham.md</t>
         </is>
       </c>
       <c r="AI322" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
+          <t>Graham's bde (57/63/68/105/114/141 PA); GRAHAM w&amp;c at the Peach Orchard (tablet verbatim + Birney + Tippin's seam moment) -&gt; Tippin. NO brigade-echelon OR report (verified-negative, page-probed 495-506 - the Union member of the no-report-T4 class)</t>
         </is>
       </c>
       <c r="AJ322" s="5" t="inlineStr">
         <is>
-          <t>OPEN (no primary; no hop)</t>
+          <t>B&amp;M-type 1,516 (hop flagged); no primary; 141st PA took 200 (Birney, regiment-grain primary)</t>
         </is>
       </c>
       <c r="AK322" s="5" t="inlineStr">
         <is>
-          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
+          <t>[C tablet] the apex from ~15:00 (CA-J2A-1); tablet (3317.7,3859.7) dms+OSM 3.5 m; [E drawn j2-03] 'Graham's Brig' (3405,3719), orchard bars (3308,3677), Sherfy (3216,3800), Clark/Phillips gun line - the apex drawn TWO-FRONTED; detached 7NJ/4th Excelsior drawn ON his ground (j2-03/j2-04)</t>
         </is>
       </c>
       <c r="AL322" s="5" t="inlineStr">
         <is>
-          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
+          <t>[C tablet] advance to the apex ~15:00-15:30; [B] Tippin's 'nearly two hours' under fire = the CA-J2A-2-&gt;9 gap (duration AGREES with the chain); [A vs CA-J2A-9] the Barksdale-axis collapse, fell back 'to the next ridge' (Birney)</t>
         </is>
       </c>
       <c r="AM322" s="5" t="inlineStr">
         <is>
-          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
+          <t>[D] 63rd PA picket fire from morning; the endurance window behind Clark's battery; the two-front apex fight (Kershaw faces + Barksdale axis); July 3 reserve [E]</t>
         </is>
       </c>
       <c r="AN322" s="5" t="inlineStr">
         <is>
-          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
+          <t>return = tablet EXACT 740 (6+61/45+463/6+159); 141st PA 149 = Birney's 149-of-200 EXACT; 57th PA 115 report=return; episode: 17:30-19:00 dominant, captures at the collapse; 114th PA k-column noise flagged</t>
         </is>
       </c>
       <c r="AO322" s="5" t="n"/>
       <c r="AP322" s="5" t="inlineStr">
         <is>
-          <t>T3 full-arc</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>us-mckeen</t>
+          <t>us-mccandless</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
+          <t>McCandless's Pennsylvania Reserves Brigade (1st Bde, 3rd Div, V Corps)</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -43007,38 +42931,38 @@
         </is>
       </c>
       <c r="G323" s="2" t="n">
-        <v>780</v>
+        <v>1243</v>
       </c>
       <c r="H323" s="2" t="n">
-        <v>520</v>
+        <v>1095</v>
       </c>
       <c r="I323" s="3">
         <f>IF(G323=0,0,1-H323/G323)</f>
         <v/>
       </c>
       <c r="J323" s="2" t="n">
-        <v>260</v>
+        <v>148</v>
       </c>
       <c r="K323" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L323" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N323" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P323" s="2" t="n">
-        <v>3110.7</v>
+        <v>1462.8</v>
       </c>
       <c r="Q323" s="2" t="n">
-        <v>94.3</v>
+        <v>831.7</v>
       </c>
       <c r="R323" s="2" t="inlineStr">
         <is>
@@ -43061,7 +42985,7 @@
       </c>
       <c r="W323" s="2" t="inlineStr">
         <is>
-          <t>McKeen</t>
+          <t>McCandless</t>
         </is>
       </c>
       <c r="X323" s="2" t="inlineStr">
@@ -43071,7 +42995,7 @@
       </c>
       <c r="Y323" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z323" s="2" t="inlineStr">
@@ -43086,12 +43010,12 @@
       </c>
       <c r="AB323" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-1-1</t>
+          <t>reg-us-v-3-1</t>
         </is>
       </c>
       <c r="AC323" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>authored-ok (July 2 W5 executor; July 3 sweep)</t>
         </is>
       </c>
       <c r="AD323" s="5" t="n"/>
@@ -43100,37 +43024,37 @@
       <c r="AG323" s="5" t="n"/>
       <c r="AH323" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
+          <t>Dossier: reconstruction/dossiers/us-v-3-1-mccandless.md; July 3 opponent MISATTRIBUTION carried (Crawford names G.T. Anderson; colors/prisoners fix Benning's 15th GA)</t>
         </is>
       </c>
       <c r="AI323" s="5" t="inlineStr">
         <is>
-          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
+          <t>McCandless's 1st PA Reserves (30/31/35/42 PA); pin: Col. C. F. Taylor (Bucktails) k in the charge</t>
         </is>
       </c>
       <c r="AJ323" s="5" t="inlineStr">
         <is>
-          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
+          <t>B&amp;M-type 1,243 (hop flagged); no primary</t>
         </is>
       </c>
       <c r="AK323" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
+          <t>[C +75] posted 'at 5 p.m.' stated on the rocky hillside - the 700-YARDS-TO-THE-WALL charge-geometry PRIMARY; [D+drawn] the wall end-line: j2-05 'McCANDLESS Brigade' (4016,2996) re-read 21 m vs pass 6, bar to (3898,2823), retiring red in front; tablet (3937.3,3042.0) July-3 semantics, SS-vs-OSM 64.4 m FLAGGED</t>
         </is>
       </c>
       <c r="AL323" s="5" t="inlineStr">
         <is>
-          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
+          <t>[B 4-6 min; A vs CA-J2A-11] THE W5 CHARGE - volley-then-run 700 yd, wall struggle; trigger = retiring units clearing the front; collision partner = Wofford's sunset-order withdrawal (both-sided at executor grain); [D] July 3 sweep -&gt; 15th GA collision</t>
         </is>
       </c>
       <c r="AM323" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
+          <t>[D] two-volleys-then-charge discipline (shared with Nevin); overnight wall hold; July 3 recovery ledger (~200 prisoners, 15th GA colors, Napoleon + 3 caissons, 7,000 stand of arms)</t>
         </is>
       </c>
       <c r="AN323" s="5" t="inlineStr">
         <is>
-          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
+          <t>tablet = return EXACT 155 (2+18/14+118/3); Crawford's stated 210 = McCandless 155 + Fisher 55 EXACT (three-way division agreement); Taylor k in the charge window; July 3 light</t>
         </is>
       </c>
       <c r="AO323" s="5" t="n"/>
@@ -43143,12 +43067,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>us-meredith</t>
+          <t>us-mcdougall</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
+          <t>McDougall's Brigade (1st Bde, 1st Div, XII Corps)</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -43168,27 +43092,27 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G324" s="2" t="n">
-        <v>1496</v>
+        <v>1755</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>730</v>
+        <v>1755</v>
       </c>
       <c r="I324" s="3">
         <f>IF(G324=0,0,1-H324/G324)</f>
         <v/>
       </c>
       <c r="J324" s="2" t="n">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="K324" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L324" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M324" s="2" t="n">
         <v>0</v>
@@ -43197,13 +43121,13 @@
         <v>0</v>
       </c>
       <c r="O324" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P324" s="2" t="n">
-        <v>6294.3</v>
+        <v>1793</v>
       </c>
       <c r="Q324" s="2" t="n">
-        <v>1350.9</v>
+        <v>0</v>
       </c>
       <c r="R324" s="2" t="inlineStr">
         <is>
@@ -43216,7 +43140,7 @@
         </is>
       </c>
       <c r="T324" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U324" s="2" t="n">
         <v>0</v>
@@ -43226,7 +43150,7 @@
       </c>
       <c r="W324" s="2" t="inlineStr">
         <is>
-          <t>Meredith</t>
+          <t>McDougall</t>
         </is>
       </c>
       <c r="X324" s="2" t="inlineStr">
@@ -43251,7 +43175,7 @@
       </c>
       <c r="AB324" s="2" t="inlineStr">
         <is>
-          <t>reg-us-i-1-1</t>
+          <t>reg-us-xii-1-1</t>
         </is>
       </c>
       <c r="AC324" s="5" t="inlineStr">
@@ -43265,55 +43189,55 @@
       <c r="AG324" s="5" t="n"/>
       <c r="AH324" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-i-1-1-meredith.md; the 1,000-vs-75 Archer-capture-count conflict carried</t>
+          <t>Dossier: reconstruction/dossiers/us-xii-1-1-mcdougall.md; the July 2/3 seam's Union-decision record</t>
         </is>
       </c>
       <c r="AI324" s="5" t="inlineStr">
         <is>
-          <t>Meredith (w July 1) -&gt; Robinson (7th Wis, pinned in Dawes); 6th Wis + brigade guard detached as corps reserve; Morrow w&amp;c; 24th Mich officer ledger 8k/14w</t>
+          <t>1st Bde 1st Div XII (5 CT/20 CT/3 MD/123 NY/145 NY/46 PA); McDougall throughout</t>
         </is>
       </c>
       <c r="AJ324" s="5" t="inlineStr">
         <is>
-          <t>24th Mich PRIMARY 496; brigade aggregate open ; p11 sweep: B&amp;M-repro 1,829 brigade hop beside the 24th Mich 496 primary</t>
+          <t>OPEN (no primary; no hop)</t>
         </is>
       </c>
       <c r="AK324" s="5" t="inlineStr">
         <is>
-          <t>[B+drawn] the Willoughby Run charge ground (j1-03 bars; Archer-captured marker on the axis); McPherson's woods line (order 19-24-7 curved); j1-13 seminary barricade drawn; Culp's Hill evening</t>
+          <t>[E] lower-hill works chain (HQ + five regimentals registered; 5th CT node NEGATIVE); j2-04 vacated label; j3-01 rally-ground read (5991,4530)</t>
         </is>
       </c>
       <c r="AL324" s="5" t="inlineStr">
         <is>
-          <t>[D] the unloaded double-quick charge; the east-bank withdrawal; step-by-step to the barricade; through town to Culp's Hill</t>
+          <t>[D] the 1.5-mile round trip; THE STOPPED NIGHT APPROACH (skirmisher discovery, no night assault, arms-down); [D] the 123rd NY works reoccupation (CA-J3M-4 executor)</t>
         </is>
       </c>
       <c r="AM324" s="5" t="inlineStr">
         <is>
-          <t>the Archer capture (Maloney/2nd Wis, both-sided w/ Shepard's ~75-pocket); the 6th Wis railroad-cut charge (Blair's 2nd Miss surrender, flag, 2nd Me gun recaptured); the woods defense vs the 26th NC (facing color ledgers)</t>
+          <t>the 20th CT woods fight under friendly overhead artillery (FRIENDLY-FIRE record); July 4 reconnaissance detachment</t>
         </is>
       </c>
       <c r="AN324" s="5" t="inlineStr">
         <is>
-          <t>return (p. 173) 1,153 (the heaviest Union brigade) - 19 Ind 210, 24 Mich 363, 2 Wis 233, 6 Wis 168, 7 Wis 178; single-day concentration, three episodes; 24th Mich nine flag carriers / four bearers k</t>
+          <t>return 80 (20th CT 28 the woods cost); friendly-fire component unnumbered (flagged)</t>
         </is>
       </c>
       <c r="AO324" s="5" t="n"/>
       <c r="AP324" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3 full-arc</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>us-neill</t>
+          <t>us-mckeen</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
+          <t>McKeen's Brigade (1st Bde, 1st Div, II Corps — Cross's)</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -43337,38 +43261,38 @@
         </is>
       </c>
       <c r="G325" s="2" t="n">
-        <v>1775</v>
+        <v>780</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>1775</v>
+        <v>520</v>
       </c>
       <c r="I325" s="3">
         <f>IF(G325=0,0,1-H325/G325)</f>
         <v/>
       </c>
       <c r="J325" s="2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="K325" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L325" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L325" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="M325" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N325" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P325" s="2" t="n">
-        <v>2830.3</v>
+        <v>3110.7</v>
       </c>
       <c r="Q325" s="2" t="n">
-        <v>2763.9</v>
+        <v>94.3</v>
       </c>
       <c r="R325" s="2" t="inlineStr">
         <is>
@@ -43391,7 +43315,7 @@
       </c>
       <c r="W325" s="2" t="inlineStr">
         <is>
-          <t>Neill</t>
+          <t>McKeen</t>
         </is>
       </c>
       <c r="X325" s="2" t="inlineStr">
@@ -43416,12 +43340,12 @@
       </c>
       <c r="AB325" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-2-2</t>
+          <t>reg-us-ii-1-1</t>
         </is>
       </c>
       <c r="AC325" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD325" s="5" t="n"/>
@@ -43430,55 +43354,55 @@
       <c r="AG325" s="5" t="n"/>
       <c r="AH325" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-2-2-neill.md; the corps's least-static brigade this pass</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-1-1-cross.md</t>
         </is>
       </c>
       <c r="AI325" s="5" t="inlineStr">
         <is>
-          <t>3rd Bde 2nd Div VI Corps (7ME(6co)/43,49,77NY/61PA); Brig Gen T.H. Neill; report thin on the battle days</t>
+          <t>Cross's bde (5NH/61NY/81PA/148PA); Cross mw 'early in this engagement' wave-3 opening ~18:15-18:30 -&gt; McKeen. 5th NH monument = fall-vicinity check point</t>
         </is>
       </c>
       <c r="AJ325" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>780 muskets PRIMARY (McKeen) - the batch's cleanest strength+loss pairing</t>
         </is>
       </c>
       <c r="AK325" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul2 arrival then DETACHED ~6pm to hold Powers Hill (Meade's direct order); [C] Jul3 crossed Rock Creek to extreme right, connecting w/ cavalry pickets (Slocum's order)</t>
+          <t>[C tablet] II Corps line 10:00; [A vs CA-J2A-8] stone wall E of Wheatfield (tablet (3865,2994), OSM xcheck 15m); [D] farthest = wheat's far end +400yd; [E drawn j2-04] 'Cross Brig' bar (3862,3088)</t>
         </is>
       </c>
       <c r="AL325" s="5" t="inlineStr">
         <is>
-          <t>[C] Powers Hill leg; [C] Rock Creek crossing leg</t>
+          <t>[A] division move ~18:00 (stated '5 p.m.' class, +60-70 early); [B] 400yd wheat advance 8-15 min; [D] Brooke passage-of-lines relief; withdrawal with division</t>
         </is>
       </c>
       <c r="AM325" s="5" t="inlineStr">
         <is>
-          <t>[D] ground-security/liaison roles, no documented firing episode</t>
+          <t>[D] wave-3 assault fire; ammunition exhaustion = relief trigger; July 3 breastworks, not assaulted</t>
         </is>
       </c>
       <c r="AN325" s="5" t="inlineStr">
         <is>
-          <t>tablet 15 (1 off+1 man k/11w/2 missing) - cause not attested</t>
+          <t>report=return EXACT 330 (59/259/12 stated vs 57/260/13 block; composition drift carried); split: wave 3 dominant, Cross pins the spike's front edge</t>
         </is>
       </c>
       <c r="AO325" s="5" t="n"/>
       <c r="AP325" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>us-nevin</t>
+          <t>us-meredith</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
+          <t>Meredith's Iron Brigade (Col. Wm. W. Robinson)</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -43498,42 +43422,42 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G326" s="2" t="n">
-        <v>1368</v>
+        <v>1496</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>1345</v>
+        <v>730</v>
       </c>
       <c r="I326" s="3">
         <f>IF(G326=0,0,1-H326/G326)</f>
         <v/>
       </c>
       <c r="J326" s="2" t="n">
-        <v>23</v>
+        <v>766</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L326" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N326" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P326" s="2" t="n">
-        <v>2090.9</v>
+        <v>6294.3</v>
       </c>
       <c r="Q326" s="2" t="n">
-        <v>2004.4</v>
+        <v>1350.9</v>
       </c>
       <c r="R326" s="2" t="inlineStr">
         <is>
@@ -43546,7 +43470,7 @@
         </is>
       </c>
       <c r="T326" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U326" s="2" t="n">
         <v>0</v>
@@ -43556,7 +43480,7 @@
       </c>
       <c r="W326" s="2" t="inlineStr">
         <is>
-          <t>Nevin</t>
+          <t>Meredith</t>
         </is>
       </c>
       <c r="X326" s="2" t="inlineStr">
@@ -43566,7 +43490,7 @@
       </c>
       <c r="Y326" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z326" s="2" t="inlineStr">
@@ -43581,12 +43505,12 @@
       </c>
       <c r="AB326" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-3</t>
+          <t>reg-us-i-1-1</t>
         </is>
       </c>
       <c r="AC326" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 W5 executor)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD326" s="5" t="n"/>
@@ -43595,37 +43519,37 @@
       <c r="AG326" s="5" t="n"/>
       <c r="AH326" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
+          <t>Dossier: reconstruction/dossiers/us-i-1-1-meredith.md; the 1,000-vs-75 Archer-capture-count conflict carried</t>
         </is>
       </c>
       <c r="AI326" s="5" t="inlineStr">
         <is>
-          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
+          <t>Meredith (w July 1) -&gt; Robinson (7th Wis, pinned in Dawes); 6th Wis + brigade guard detached as corps reserve; Morrow w&amp;c; 24th Mich officer ledger 8k/14w</t>
         </is>
       </c>
       <c r="AJ326" s="5" t="inlineStr">
         <is>
-          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
+          <t>24th Mich PRIMARY 496; brigade aggregate open ; p11 sweep: B&amp;M-repro 1,829 brigade hop beside the 24th Mich 496 primary</t>
         </is>
       </c>
       <c r="AK326" s="5" t="inlineStr">
         <is>
-          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
+          <t>[B+drawn] the Willoughby Run charge ground (j1-03 bars; Archer-captured marker on the axis); McPherson's woods line (order 19-24-7 curved); j1-13 seminary barricade drawn; Culp's Hill evening</t>
         </is>
       </c>
       <c r="AL326" s="5" t="inlineStr">
         <is>
-          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
+          <t>[D] the unloaded double-quick charge; the east-bank withdrawal; step-by-step to the barricade; through town to Culp's Hill</t>
         </is>
       </c>
       <c r="AM326" s="5" t="inlineStr">
         <is>
-          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
+          <t>the Archer capture (Maloney/2nd Wis, both-sided w/ Shepard's ~75-pocket); the 6th Wis railroad-cut charge (Blair's 2nd Miss surrender, flag, 2nd Me gun recaptured); the woods defense vs the 26th NC (facing color ledgers)</t>
         </is>
       </c>
       <c r="AN326" s="5" t="inlineStr">
         <is>
-          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
+          <t>return (p. 173) 1,153 (the heaviest Union brigade) - 19 Ind 210, 24 Mich 363, 2 Wis 233, 6 Wis 168, 7 Wis 178; single-day concentration, three episodes; 24th Mich nine flag carriers / four bearers k</t>
         </is>
       </c>
       <c r="AO326" s="5" t="n"/>
@@ -43638,12 +43562,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>us-rice</t>
+          <t>us-neill</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
+          <t>Neill's Brigade (3rd Bde, 2nd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -43667,38 +43591,38 @@
         </is>
       </c>
       <c r="G327" s="2" t="n">
-        <v>1336</v>
+        <v>1775</v>
       </c>
       <c r="H327" s="2" t="n">
-        <v>985</v>
+        <v>1775</v>
       </c>
       <c r="I327" s="3">
         <f>IF(G327=0,0,1-H327/G327)</f>
         <v/>
       </c>
       <c r="J327" s="2" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="K327" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L327" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M327" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N327" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P327" s="2" t="n">
-        <v>1529.4</v>
+        <v>2830.3</v>
       </c>
       <c r="Q327" s="2" t="n">
-        <v>655.2</v>
+        <v>2763.9</v>
       </c>
       <c r="R327" s="2" t="inlineStr">
         <is>
@@ -43721,7 +43645,7 @@
       </c>
       <c r="W327" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Neill</t>
         </is>
       </c>
       <c r="X327" s="2" t="inlineStr">
@@ -43746,12 +43670,12 @@
       </c>
       <c r="AB327" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-3</t>
+          <t>reg-us-vi-2-2</t>
         </is>
       </c>
       <c r="AC327" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD327" s="5" t="n"/>
@@ -43760,55 +43684,55 @@
       <c r="AG327" s="5" t="n"/>
       <c r="AH327" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-2-2-neill.md; the corps's least-static brigade this pass</t>
         </is>
       </c>
       <c r="AI327" s="5" t="inlineStr">
         <is>
-          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
+          <t>3rd Bde 2nd Div VI Corps (7ME(6co)/43,49,77NY/61PA); Brig Gen T.H. Neill; report thin on the battle days</t>
         </is>
       </c>
       <c r="AJ327" s="5" t="inlineStr">
         <is>
-          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK327" s="5" t="inlineStr">
         <is>
-          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
+          <t>[C] Jul2 arrival then DETACHED ~6pm to hold Powers Hill (Meade's direct order); [C] Jul3 crossed Rock Creek to extreme right, connecting w/ cavalry pickets (Slocum's order)</t>
         </is>
       </c>
       <c r="AL327" s="5" t="inlineStr">
         <is>
-          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
+          <t>[C] Powers Hill leg; [C] Rock Creek crossing leg</t>
         </is>
       </c>
       <c r="AM327" s="5" t="inlineStr">
         <is>
-          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
+          <t>[D] ground-security/liaison roles, no documented firing episode</t>
         </is>
       </c>
       <c r="AN327" s="5" t="inlineStr">
         <is>
-          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
+          <t>tablet 15 (1 off+1 man k/11w/2 missing) - cause not attested</t>
         </is>
       </c>
       <c r="AO327" s="5" t="n"/>
       <c r="AP327" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>us-russell</t>
+          <t>us-nevin</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
+          <t>Nevin's Brigade (3rd Bde, 3rd Div, VI Corps — Wheaton's)</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -43832,23 +43756,23 @@
         </is>
       </c>
       <c r="G328" s="2" t="n">
-        <v>1480</v>
+        <v>1368</v>
       </c>
       <c r="H328" s="2" t="n">
-        <v>1480</v>
+        <v>1345</v>
       </c>
       <c r="I328" s="3">
         <f>IF(G328=0,0,1-H328/G328)</f>
         <v/>
       </c>
       <c r="J328" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K328" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L328" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="L328" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="M328" s="2" t="n">
         <v>4</v>
@@ -43857,13 +43781,13 @@
         <v>0</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P328" s="2" t="n">
-        <v>2278.8</v>
+        <v>2090.9</v>
       </c>
       <c r="Q328" s="2" t="n">
-        <v>2167.8</v>
+        <v>2004.4</v>
       </c>
       <c r="R328" s="2" t="inlineStr">
         <is>
@@ -43876,7 +43800,7 @@
         </is>
       </c>
       <c r="T328" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U328" s="2" t="n">
         <v>0</v>
@@ -43886,7 +43810,7 @@
       </c>
       <c r="W328" s="2" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Nevin</t>
         </is>
       </c>
       <c r="X328" s="2" t="inlineStr">
@@ -43896,12 +43820,12 @@
       </c>
       <c r="Y328" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z328" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA328" s="2" t="inlineStr">
@@ -43911,12 +43835,12 @@
       </c>
       <c r="AB328" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-3</t>
+          <t>reg-us-vi-3-3</t>
         </is>
       </c>
       <c r="AC328" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>authored-ok (July 2 W5 executor)</t>
         </is>
       </c>
       <c r="AD328" s="5" t="n"/>
@@ -43925,55 +43849,55 @@
       <c r="AG328" s="5" t="n"/>
       <c r="AH328" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-1-3-russell.md</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-3-nevin.md; proposed ED-61 - ADOPTED 2026-07-11 (pass-8 batch ruling, precondition satisfied first); EC6 return row closed pass 8</t>
         </is>
       </c>
       <c r="AI328" s="5" t="inlineStr">
         <is>
-          <t>3rd Bde 1st Div VI Corps (6ME/49(4co)/119PA/5WI); Brig Gen D.A. Russell; report=tablet</t>
+          <t>Wheaton's/Nevin's bde (62 NY, 93/98/102/139 PA); TRIPLE succession Wheaton-&gt;Nevin-&gt;Bartlett-attached (rendering-metadata hazard noted)</t>
         </is>
       </c>
       <c r="AJ328" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>B&amp;M-type 1,368 (hop flagged); 34-mile/17-hour forced-march fatigue qualifier (primary)</t>
         </is>
       </c>
       <c r="AK328" s="5" t="inlineStr">
         <is>
-          <t>[C ~16:00] arrival; [C] Jul3 extreme left then left-centre 'anticipated attack on the center' (report's cause, tablet's terser text)</t>
+          <t>[C +75] deployed 'At 4.30 p.m.' stated (~18:45-19:15 canonical) on the LRT north slope - 'barely gotten into position' when the W4 collapse swept past (the seam verbatim); [E drawn j2-05] 'NEVIN' (4306,3075) re-read 47 m vs pass 6; tablet at the Weickert farm (4201.9,3060.0) dms+OSM 9 m</t>
         </is>
       </c>
       <c r="AL328" s="5" t="inlineStr">
         <is>
-          <t>[B] the march; [D] the afternoon shift</t>
+          <t>[B primary] the forced march; [D trigger; A-bracket vs CA-J2A-11] the countercharge - two volleys then charge vs Wofford's retiring column (tablet NAMES Wofford; order-vs-charge collision both-sided); [B 4-6 min] swamp crossing + 100-yard halt</t>
         </is>
       </c>
       <c r="AM328" s="5" t="inlineStr">
         <is>
-          <t>[D] attested-static both sources: 'Not engaged' / 'not actually engaged'</t>
+          <t>[D] THE GUN RECOVERY 'two light 12-pounder brass pieces' = tablet's 'two Napoleon guns' - the ED-61 pool with Brewster/Crawford/Barksdale-left-on-field records; July 3: 10 a.m. recon repulsed, 2 p.m. shelled, 6 p.m. Crawford support 'recapturing artillery'</t>
         </is>
       </c>
       <c r="AN328" s="5" t="inlineStr">
         <is>
-          <t>CONFLICT: tablet 2w vs report's 'no casualties' - carried unresolved</t>
+          <t>tablet 53 (2k/7+44w) = return p. 182 row 2k/7+44w = 53 TABLET=RETURN EXACT at component grain (pass-8 fetch closed the pass-7 flag); two-episode light shape</t>
         </is>
       </c>
       <c r="AO328" s="5" t="n"/>
       <c r="AP328" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>us-shaler</t>
+          <t>us-rice</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
+          <t>Rice's Brigade (3rd Bde, 1st Div, V Corps — Vincent's)</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -43997,26 +43921,26 @@
         </is>
       </c>
       <c r="G329" s="2" t="n">
-        <v>1770</v>
+        <v>1336</v>
       </c>
       <c r="H329" s="2" t="n">
-        <v>1770</v>
+        <v>985</v>
       </c>
       <c r="I329" s="3">
         <f>IF(G329=0,0,1-H329/G329)</f>
         <v/>
       </c>
       <c r="J329" s="2" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="K329" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L329" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N329" s="2" t="n">
         <v>0</v>
@@ -44025,10 +43949,10 @@
         <v>9</v>
       </c>
       <c r="P329" s="2" t="n">
-        <v>3654.8</v>
+        <v>1529.4</v>
       </c>
       <c r="Q329" s="2" t="n">
-        <v>2065.3</v>
+        <v>655.2</v>
       </c>
       <c r="R329" s="2" t="inlineStr">
         <is>
@@ -44041,7 +43965,7 @@
         </is>
       </c>
       <c r="T329" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U329" s="2" t="n">
         <v>0</v>
@@ -44051,7 +43975,7 @@
       </c>
       <c r="W329" s="2" t="inlineStr">
         <is>
-          <t>Shaler</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="X329" s="2" t="inlineStr">
@@ -44061,12 +43985,12 @@
       </c>
       <c r="Y329" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z329" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA329" s="2" t="inlineStr">
@@ -44076,12 +44000,12 @@
       </c>
       <c r="AB329" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-3-1</t>
+          <t>reg-us-v-1-3</t>
         </is>
       </c>
       <c r="AC329" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>authored-ok (July 2 mover; July 3 ED-44 class)</t>
         </is>
       </c>
       <c r="AD329" s="5" t="n"/>
@@ -44090,55 +44014,55 @@
       <c r="AG329" s="5" t="n"/>
       <c r="AH329" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-3-1-shaler.md; CLOSES the corps HQ dossier's own flagged verification item; feeds CA-J3M-2/4</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-3-vincent.md; Warren letters = CA-J2A-4 primary base</t>
         </is>
       </c>
       <c r="AI329" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 3rd Div VI Corps (65,67,122NY/23,82PA); Brig Gen Alexander Shaler; TWO reports (battle narrative + Nov1863 correction letter)</t>
+          <t>Vincent's bde (20 ME/16 MI/44 NY/83 PA); Vincent mw July 2 (16th MI crisis; d. July 7) -&gt; Rice; Linscott mw 21:00</t>
         </is>
       </c>
       <c r="AJ329" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>'about 1,000 muskets' - the brigade commander's own statement (primary, or-27-1-rice-vincent)</t>
         </is>
       </c>
       <c r="AK329" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00] arrival; [C ~08:00 Jul3] detached to Culp's Hill supporting Geary; regiment-grain sub-hour ladder 9:00-11:30am; [C ~15:30] withdrew under fire to III Corps center-rear reserve</t>
+          <t>[C +45] extreme left 'about 4 p.m.' stated; line 20ME|83PA|44NY|16MI; [E drawn j2-03] VINCENT'S SPUR label (4256,2309), 16 MICH (4158,2503); [C 21:00] 20th ME ON Great Round Top - DRAWN on j2-05; July 3 relieved to the CENTER as reserve (primary - ED-54 candidate placement rule)</t>
         </is>
       </c>
       <c r="AL329" s="5" t="inlineStr">
         <is>
-          <t>[C] the 8am detachment leg; [C] the 3:30pm withdrawal leg</t>
+          <t>[D+B] the self-diverted rush to the hill (~700 m at the double); the 20th ME left-refuse + right-wheel charge; the 21:00 night ascent (~200 men, no firing)</t>
         </is>
       </c>
       <c r="AM329" s="5" t="inlineStr">
         <is>
-          <t>[C] ENGAGED 9-11am under Geary, 'severe fire'/'galling fire of musketry'</t>
+          <t>[A vs CA-J2A-6] the defense 16:45-19:00; ammunition crisis (brigade-attested); 'now 8 o clock in the evening' repulse-complete clock (best Union primary end-clock of the phase); 500+ prisoners/1,000 muskets</t>
         </is>
       </c>
       <c r="AN329" s="5" t="inlineStr">
         <is>
-          <t>tablet 74 (1off+14men k/3off+53w/3 missing) - heaviest VI Corps brigade loss this pass</t>
+          <t>return exact-grain: 20 ME 125, 16 MI 60, 44 NY 111, 83 PA 55 = 352 (ED-52 basis; 20th ME narrative 130-136 carried not promoted); single-window brigade (July 3 lossless per Rice)</t>
         </is>
       </c>
       <c r="AO329" s="5" t="n"/>
       <c r="AP329" s="5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>us-sherrill</t>
+          <t>us-russell</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Sherrill's Brigade (Willard's)</t>
+          <t>Russell's Brigade (3rd Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -44162,38 +44086,38 @@
         </is>
       </c>
       <c r="G330" s="2" t="n">
-        <v>1510</v>
+        <v>1480</v>
       </c>
       <c r="H330" s="2" t="n">
-        <v>800</v>
+        <v>1480</v>
       </c>
       <c r="I330" s="3">
         <f>IF(G330=0,0,1-H330/G330)</f>
         <v/>
       </c>
       <c r="J330" s="2" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="K330" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L330" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M330" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N330" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O330" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="P330" s="2" t="n">
-        <v>2163.2</v>
+        <v>2278.8</v>
       </c>
       <c r="Q330" s="2" t="n">
-        <v>70.2</v>
+        <v>2167.8</v>
       </c>
       <c r="R330" s="2" t="inlineStr">
         <is>
@@ -44206,17 +44130,17 @@
         </is>
       </c>
       <c r="T330" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U330" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V330" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W330" s="2" t="inlineStr">
         <is>
-          <t>Sherrill</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="X330" s="2" t="inlineStr">
@@ -44226,12 +44150,12 @@
       </c>
       <c r="Y330" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z330" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA330" s="2" t="inlineStr">
@@ -44241,12 +44165,12 @@
       </c>
       <c r="AB330" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-3</t>
+          <t>reg-us-vi-1-3</t>
         </is>
       </c>
       <c r="AC330" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (one in-window leg)</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD330" s="5" t="n"/>
@@ -44255,55 +44179,55 @@
       <c r="AG330" s="5" t="n"/>
       <c r="AH330" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-3-russell.md</t>
         </is>
       </c>
       <c r="AI330" s="5" t="inlineStr">
         <is>
-          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
+          <t>3rd Bde 1st Div VI Corps (6ME/49(4co)/119PA/5WI); Brig Gen D.A. Russell; report=tablet</t>
         </is>
       </c>
       <c r="AJ330" s="5" t="inlineStr">
         <is>
-          <t>1,510 (build compilation, hop flagged)</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK330" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
+          <t>[C ~16:00] arrival; [C] Jul3 extreme left then left-centre 'anticipated attack on the center' (report's cause, tablet's terser text)</t>
         </is>
       </c>
       <c r="AL330" s="5" t="inlineStr">
         <is>
-          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
+          <t>[B] the march; [D] the afternoon shift</t>
         </is>
       </c>
       <c r="AM330" s="5" t="inlineStr">
         <is>
-          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
+          <t>[D] attested-static both sources: 'Not engaged' / 'not actually engaged'</t>
         </is>
       </c>
       <c r="AN330" s="5" t="inlineStr">
         <is>
-          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
+          <t>CONFLICT: tablet 2w vs report's 'no casualties' - carried unresolved</t>
         </is>
       </c>
       <c r="AO330" s="5" t="n"/>
       <c r="AP330" s="5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>us-smith</t>
+          <t>us-shaler</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
+          <t>Shaler's Brigade (1st Bde, 3rd Div, VI Corps)</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -44323,42 +44247,42 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-morning/july3-afternoon</t>
         </is>
       </c>
       <c r="G331" s="2" t="n">
-        <v>1600</v>
+        <v>1770</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>1290</v>
+        <v>1770</v>
       </c>
       <c r="I331" s="3">
         <f>IF(G331=0,0,1-H331/G331)</f>
         <v/>
       </c>
       <c r="J331" s="2" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="K331" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L331" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L331" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="M331" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N331" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O331" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P331" s="2" t="n">
-        <v>549.2</v>
+        <v>5136.1</v>
       </c>
       <c r="Q331" s="2" t="n">
-        <v>549.2</v>
+        <v>2065.3</v>
       </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
@@ -44377,11 +44301,11 @@
         <v>0</v>
       </c>
       <c r="V331" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W331" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Shaler</t>
         </is>
       </c>
       <c r="X331" s="2" t="inlineStr">
@@ -44391,12 +44315,12 @@
       </c>
       <c r="Y331" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z331" s="2" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AA331" s="2" t="inlineStr">
@@ -44406,12 +44330,12 @@
       </c>
       <c r="AB331" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-2-2</t>
+          <t>reg-us-vi-3-1</t>
         </is>
       </c>
       <c r="AC331" s="5" t="inlineStr">
         <is>
-          <t>authored-ok</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD331" s="5" t="n"/>
@@ -44420,12 +44344,12 @@
       <c r="AG331" s="5" t="n"/>
       <c r="AH331" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-2-2-smith.md; 33MA/Avery-repulse cross-ref flagged not verified</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-3-1-shaler.md; CLOSES the corps HQ dossier's own flagged verification item; feeds CA-J3M-2/4</t>
         </is>
       </c>
       <c r="AI331" s="5" t="inlineStr">
         <is>
-          <t>Col. Orland Smith, 33MA/136NY/55OH/73OH; own report OR27/1 pp.722-725; identity verified NOT W.Smith CSA</t>
+          <t>1st Bde 3rd Div VI Corps (65,67,122NY/23,82PA); Brig Gen Alexander Shaler; TWO reports (battle narrative + Nov1863 correction letter)</t>
         </is>
       </c>
       <c r="AJ331" s="5" t="inlineStr">
@@ -44435,40 +44359,40 @@
       </c>
       <c r="AK331" s="5" t="inlineStr">
         <is>
-          <t>[C ~14:00 Jul1] Cemetery Hill wall, Emmitsburg/Taneytown Rds; von Steinwehr calls it 'First Bde' internally, Smith's own report says 'Second Bde' matching register</t>
+          <t>[C ~14:00] arrival; [C ~08:00 Jul3] detached to Culp's Hill supporting Geary; regiment-grain sub-hour ladder 9:00-11:30am; [C ~15:30] withdrew under fire to III Corps center-rear reserve</t>
         </is>
       </c>
       <c r="AL331" s="5" t="inlineStr">
         <is>
-          <t>[C] Jun12-Jul1 full march itinerary; 38mi/24.5hrs Boonsborough-Emmitsburg</t>
+          <t>[C] the 8am detachment leg; [C] the 3:30pm withdrawal leg</t>
         </is>
       </c>
       <c r="AM331" s="5" t="inlineStr">
         <is>
-          <t>continuous skirmish Jul1-3; no direct assault Jul2 night; Jul3 assault redirected to II Corps</t>
+          <t>[C] ENGAGED 9-11am under Geary, 'severe fire'/'galling fire of musketry'</t>
         </is>
       </c>
       <c r="AN331" s="5" t="inlineStr">
         <is>
-          <t>REPORT-VS-TABLET CONFLICT: tablet 348 (51k/278w/19m) vs report 345 (66k/259w/26m) - every category disagrees, not adjudicated</t>
+          <t>tablet 74 (1off+14men k/3off+53w/3 missing) - heaviest VI Corps brigade loss this pass</t>
         </is>
       </c>
       <c r="AO331" s="5" t="n"/>
       <c r="AP331" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>us-smyth</t>
+          <t>us-sherrill</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Smyth's Brigade</t>
+          <t>Sherrill's Brigade (Willard's)</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -44492,47 +44416,47 @@
         </is>
       </c>
       <c r="G332" s="2" t="n">
-        <v>1190</v>
+        <v>1510</v>
       </c>
       <c r="H332" s="2" t="n">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="I332" s="3">
         <f>IF(G332=0,0,1-H332/G332)</f>
         <v/>
       </c>
       <c r="J332" s="2" t="n">
-        <v>365</v>
+        <v>710</v>
       </c>
       <c r="K332" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L332" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M332" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N332" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P332" s="2" t="n">
-        <v>0</v>
+        <v>2163.2</v>
       </c>
       <c r="Q332" s="2" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="R332" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="S332" s="2" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="T332" s="2" t="n">
@@ -44542,11 +44466,11 @@
         <v>0</v>
       </c>
       <c r="V332" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W332" s="2" t="inlineStr">
         <is>
-          <t>Smyth</t>
+          <t>Sherrill</t>
         </is>
       </c>
       <c r="X332" s="2" t="inlineStr">
@@ -44571,12 +44495,12 @@
       </c>
       <c r="AB332" s="2" t="inlineStr">
         <is>
-          <t>reg-us-ii-3-2</t>
+          <t>reg-us-ii-3-3</t>
         </is>
       </c>
       <c r="AC332" s="5" t="inlineStr">
         <is>
-          <t>attested-static (July 2-4 wall line)</t>
+          <t>authored-ok (one in-window leg)</t>
         </is>
       </c>
       <c r="AD332" s="5" t="n"/>
@@ -44585,37 +44509,37 @@
       <c r="AG332" s="5" t="n"/>
       <c r="AH332" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-3-willard.md; 4-lines vs Smyth's 3-lines carried</t>
         </is>
       </c>
       <c r="AI332" s="5" t="inlineStr">
         <is>
-          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
+          <t>Willard k Jul 2 -&gt; Sherrill mw Jul 3 ('about 4 p.m.' stated) -&gt; Bull; 39/111/125/126 NY</t>
         </is>
       </c>
       <c r="AJ332" s="5" t="inlineStr">
         <is>
-          <t>1,190 (build compilation, hop flagged; no primary)</t>
+          <t>1,510 (build compilation, hop flagged)</t>
         </is>
       </c>
       <c r="AK332" s="5" t="inlineStr">
         <is>
-          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
+          <t>[C] Jul 2 massed near Bryan barn; Jul 2 evening Plum Run charge ground; [E Jul 3] slope east of wall, monuments interleave Smyth's row (39NY 4467,4988; 125NY 4468,5053; 111NY 4458,5127; 126NY 4543,5267)</t>
         </is>
       </c>
       <c r="AL332" s="5" t="inlineStr">
         <is>
-          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
+          <t>[C ~15:00 Jul 2] quarter-mile left; [D] Plum Run charge; [A vs CA-J3A-5 tablet 15:00] moved up to Smyth's line [B: 2-4 min]</t>
         </is>
       </c>
       <c r="AM332" s="5" t="inlineStr">
         <is>
-          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
+          <t>[C] 39NY skirmish (28 lost, exact); [C +7] 'About 1 p.m....about two hours' cannonade; [A] 4-line advance repulsed 'after an engagement of about an hour'</t>
         </is>
       </c>
       <c r="AN332" s="5" t="inlineStr">
         <is>
-          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
+          <t>report: attested-unreported ('unable to report'); tablet 714; episode pins: 39NY 28 (Jul 2 skirmish), Willard k, Sherrill mw</t>
         </is>
       </c>
       <c r="AO332" s="5" t="n"/>
@@ -44628,12 +44552,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>us-sweitzer</t>
+          <t>us-smith</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
+          <t>Smith's Brigade (2nd Bde, 2nd Div, XI Corps)</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -44653,27 +44577,27 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G333" s="2" t="n">
-        <v>1010</v>
+        <v>1600</v>
       </c>
       <c r="H333" s="2" t="n">
-        <v>995</v>
+        <v>1290</v>
       </c>
       <c r="I333" s="3">
         <f>IF(G333=0,0,1-H333/G333)</f>
         <v/>
       </c>
       <c r="J333" s="2" t="n">
-        <v>15</v>
+        <v>310</v>
       </c>
       <c r="K333" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L333" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M333" s="2" t="n">
         <v>2</v>
@@ -44682,13 +44606,13 @@
         <v>0</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P333" s="2" t="n">
-        <v>2845.9</v>
+        <v>549.2</v>
       </c>
       <c r="Q333" s="2" t="n">
-        <v>632.9</v>
+        <v>549.2</v>
       </c>
       <c r="R333" s="2" t="inlineStr">
         <is>
@@ -44701,17 +44625,17 @@
         </is>
       </c>
       <c r="T333" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V333" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W333" s="2" t="inlineStr">
         <is>
-          <t>Sweitzer</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="X333" s="2" t="inlineStr">
@@ -44736,12 +44660,12 @@
       </c>
       <c r="AB333" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-2</t>
+          <t>reg-us-xi-2-2</t>
         </is>
       </c>
       <c r="AC333" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 twice-committed)</t>
+          <t>authored-ok</t>
         </is>
       </c>
       <c r="AD333" s="5" t="n"/>
@@ -44750,37 +44674,37 @@
       <c r="AG333" s="5" t="n"/>
       <c r="AH333" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
+          <t>Dossier: reconstruction/dossiers/us-xi-2-2-smith.md; 33MA/Avery-repulse cross-ref flagged not verified</t>
         </is>
       </c>
       <c r="AI333" s="5" t="inlineStr">
         <is>
-          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
+          <t>Col. Orland Smith, 33MA/136NY/55OH/73OH; own report OR27/1 pp.722-725; identity verified NOT W.Smith CSA</t>
         </is>
       </c>
       <c r="AJ333" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
+          <t>open</t>
         </is>
       </c>
       <c r="AK333" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
+          <t>[C ~14:00 Jul1] Cemetery Hill wall, Emmitsburg/Taneytown Rds; von Steinwehr calls it 'First Bde' internally, Smith's own report says 'Second Bde' matching register</t>
         </is>
       </c>
       <c r="AL333" s="5" t="inlineStr">
         <is>
-          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
+          <t>[C] Jun12-Jul1 full march itinerary; 38mi/24.5hrs Boonsborough-Emmitsburg</t>
         </is>
       </c>
       <c r="AM333" s="5" t="inlineStr">
         <is>
-          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
+          <t>continuous skirmish Jul1-3; no direct assault Jul2 night; Jul3 assault redirected to II Corps</t>
         </is>
       </c>
       <c r="AN333" s="5" t="inlineStr">
         <is>
-          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
+          <t>REPORT-VS-TABLET CONFLICT: tablet 348 (51k/278w/19m) vs report 345 (66k/259w/26m) - every category disagrees, not adjudicated</t>
         </is>
       </c>
       <c r="AO333" s="5" t="n"/>
@@ -44793,12 +44717,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>us-tilton</t>
+          <t>us-smyth</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
+          <t>Smyth's Brigade</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -44822,26 +44746,26 @@
         </is>
       </c>
       <c r="G334" s="2" t="n">
-        <v>654</v>
+        <v>1190</v>
       </c>
       <c r="H334" s="2" t="n">
-        <v>530</v>
+        <v>825</v>
       </c>
       <c r="I334" s="3">
         <f>IF(G334=0,0,1-H334/G334)</f>
         <v/>
       </c>
       <c r="J334" s="2" t="n">
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="K334" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L334" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M334" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="M334" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="N334" s="2" t="n">
         <v>0</v>
@@ -44850,43 +44774,43 @@
         <v>9</v>
       </c>
       <c r="P334" s="2" t="n">
-        <v>2966.7</v>
+        <v>0</v>
       </c>
       <c r="Q334" s="2" t="n">
-        <v>740.9</v>
+        <v>0</v>
       </c>
       <c r="R334" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V334" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Smyth</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S334" s="2" t="inlineStr">
-        <is>
-          <t>column/line</t>
-        </is>
-      </c>
-      <c r="T334" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U334" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V334" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W334" s="2" t="inlineStr">
-        <is>
-          <t>Tilton</t>
-        </is>
-      </c>
-      <c r="X334" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="Y334" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z334" s="2" t="inlineStr">
@@ -44901,12 +44825,12 @@
       </c>
       <c r="AB334" s="2" t="inlineStr">
         <is>
-          <t>reg-us-v-1-1</t>
+          <t>reg-us-ii-3-2</t>
         </is>
       </c>
       <c r="AC334" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (July 2 mover)</t>
+          <t>attested-static (July 2-4 wall line)</t>
         </is>
       </c>
       <c r="AD334" s="5" t="n"/>
@@ -44915,55 +44839,55 @@
       <c r="AG334" s="5" t="n"/>
       <c r="AH334" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
+          <t>Dossier: reconstruction/dossiers/us-ii-3-2-smyth.md</t>
         </is>
       </c>
       <c r="AI334" s="5" t="inlineStr">
         <is>
-          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
+          <t>Col. Smyth w July 3 during cannonade -&gt; Lt. Col. Pierce; 14CT/1DE/12NJ/10NYbn/108NY (or-27-1-smyth)</t>
         </is>
       </c>
       <c r="AJ334" s="5" t="inlineStr">
         <is>
-          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
+          <t>1,190 (build compilation, hop flagged; no primary)</t>
         </is>
       </c>
       <c r="AK334" s="5" t="inlineStr">
         <is>
-          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
+          <t>[C] wall S of Bryan barn from 04:00 Jul 2; monument row 14CT(4449,4951) 1DE(4451,5038) 12NJ(4453,5096) 108NY(4527,5218); Bachelder j3-03 concurs (20-30m)</t>
         </is>
       </c>
       <c r="AL334" s="5" t="inlineStr">
         <is>
-          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
+          <t>[C] Jul 1 march (06:30 order); [C] 04:00 Jul 2 posting; static after</t>
         </is>
       </c>
       <c r="AM334" s="5" t="inlineStr">
         <is>
-          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
+          <t>[C] 1DE skirmish + 108NY supports Woodruff 08:00 Jul 2; Bliss barn burned Jul 3 (14CT); [C -53] 'At 2 p.m.' cannonade (cluster member); [A] 3-line repulse, 12NJ fire at 20 yd, 1,200-1,500 prisoners, 9 flags</t>
         </is>
       </c>
       <c r="AN334" s="5" t="inlineStr">
         <is>
-          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
+          <t>352 (his OR recap) vs 366 (tablet) - both carried; 108NY 'about half' lost; pins Smyth w (cannonade), Lt. Smith k (flag in hand)</t>
         </is>
       </c>
       <c r="AO334" s="5" t="n"/>
       <c r="AP334" s="5" t="inlineStr">
         <is>
-          <t>T4 full-arc</t>
+          <t>T4</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>us-torbert</t>
+          <t>us-sweitzer</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
+          <t>Sweitzer's Brigade (2nd Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -44987,38 +44911,38 @@
         </is>
       </c>
       <c r="G335" s="2" t="n">
-        <v>1320</v>
+        <v>1010</v>
       </c>
       <c r="H335" s="2" t="n">
-        <v>1309</v>
+        <v>995</v>
       </c>
       <c r="I335" s="3">
         <f>IF(G335=0,0,1-H335/G335)</f>
         <v/>
       </c>
       <c r="J335" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K335" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L335" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M335" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M335" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="N335" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P335" s="2" t="n">
-        <v>1875.7</v>
+        <v>2845.9</v>
       </c>
       <c r="Q335" s="2" t="n">
-        <v>1875.6</v>
+        <v>632.9</v>
       </c>
       <c r="R335" s="2" t="inlineStr">
         <is>
@@ -45031,7 +44955,7 @@
         </is>
       </c>
       <c r="T335" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U335" s="2" t="n">
         <v>0</v>
@@ -45041,7 +44965,7 @@
       </c>
       <c r="W335" s="2" t="inlineStr">
         <is>
-          <t>Torbert</t>
+          <t>Sweitzer</t>
         </is>
       </c>
       <c r="X335" s="2" t="inlineStr">
@@ -45051,7 +44975,7 @@
       </c>
       <c r="Y335" s="2" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="Z335" s="2" t="inlineStr">
@@ -45066,12 +44990,12 @@
       </c>
       <c r="AB335" s="2" t="inlineStr">
         <is>
-          <t>reg-us-vi-1-1</t>
+          <t>reg-us-v-1-2</t>
         </is>
       </c>
       <c r="AC335" s="5" t="inlineStr">
         <is>
-          <t>authored-ok (command/frame grain)</t>
+          <t>authored-ok (July 2 twice-committed)</t>
         </is>
       </c>
       <c r="AD335" s="5" t="n"/>
@@ -45080,55 +45004,55 @@
       <c r="AG335" s="5" t="n"/>
       <c r="AH335" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-vi-1-1-torbert.md</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-2-sweitzer.md</t>
         </is>
       </c>
       <c r="AI335" s="5" t="inlineStr">
         <is>
-          <t>1st Bde 1st Div VI Corps (1/2/3/15 NJ); Brig Gen A.T.A. Torbert; report=tablet</t>
+          <t>Sweitzer's bde (9MA detached/32MA/4MI/62PA); Jeffords (4MI) mw with the colors at the fence (monument check point); Lowry (62PA) k</t>
         </is>
       </c>
       <c r="AJ335" s="5" t="inlineStr">
         <is>
-          <t>1,663 (106 off/1,557 enl, report-primary itemized)</t>
+          <t>no primary (negative); ~1,010 incl. detached 9th MA (~420) - two-scope range carried</t>
         </is>
       </c>
       <c r="AK335" s="5" t="inlineStr">
         <is>
-          <t>[C ~16:00] 35mi march, arrived 4pm Jul2; [C] LRT reserve; [C] Jul3 Weikert-House-area center</t>
+          <t>[C tablet] first position woods at Wheatfield W (tablet (3670,2996) OSM-primary; j2-03 bar (3514,3077)); [A vs CA-J2A-8] SECOND position = the stone fence; j2-04 draws 'Sweitzer's Brigade' ON the fence (3706,2988) = 40m-class agreement with the 4th MI monument (3678,3012)</t>
         </is>
       </c>
       <c r="AL335" s="5" t="inlineStr">
         <is>
-          <t>[B] the 35mi march</t>
+          <t>[D] conditional first withdrawal (Prescott exchange); [D trigger] THE SECOND ADVANCE at Caldwell's personal request (both-command-sided); [D] caught-in-rear crisis + fighting extraction</t>
         </is>
       </c>
       <c r="AM335" s="5" t="inlineStr">
         <is>
-          <t>[D] attested-static, picket only; 11 wounded on picket Jul3</t>
+          <t>[D] the fence fight front-and-rear ~18:45-19:10; friendly-fire misread moment (smoke record)</t>
         </is>
       </c>
       <c r="AN335" s="5" t="inlineStr">
         <is>
-          <t>tablet 11w = report's Jul3 picket figure exact; report's broader 1k/17w is a CAMPAIGN total (scope, not conflict)</t>
+          <t>return 427 (4MI 165, 62PA 175; 121 c/m concentrate in the cut-off pair - capture-pocket shape); no report total (negative)</t>
         </is>
       </c>
       <c r="AO335" s="5" t="n"/>
       <c r="AP335" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4 full-arc</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>us-detrobriand</t>
+          <t>us-tilton</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
+          <t>Tilton's Brigade (1st Bde, 1st Div, V Corps)</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -45152,38 +45076,38 @@
         </is>
       </c>
       <c r="G336" s="2" t="n">
-        <v>1387</v>
+        <v>654</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>895</v>
+        <v>530</v>
       </c>
       <c r="I336" s="3">
         <f>IF(G336=0,0,1-H336/G336)</f>
         <v/>
       </c>
       <c r="J336" s="2" t="n">
-        <v>492</v>
+        <v>124</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L336" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N336" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P336" s="2" t="n">
-        <v>1429.6</v>
+        <v>2966.7</v>
       </c>
       <c r="Q336" s="2" t="n">
-        <v>1429</v>
+        <v>740.9</v>
       </c>
       <c r="R336" s="2" t="inlineStr">
         <is>
@@ -45206,7 +45130,7 @@
       </c>
       <c r="W336" s="2" t="inlineStr">
         <is>
-          <t>Trobriand</t>
+          <t>Tilton</t>
         </is>
       </c>
       <c r="X336" s="2" t="inlineStr">
@@ -45231,7 +45155,7 @@
       </c>
       <c r="AB336" s="2" t="inlineStr">
         <is>
-          <t>reg-us-iii-1-3</t>
+          <t>reg-us-v-1-1</t>
         </is>
       </c>
       <c r="AC336" s="5" t="inlineStr">
@@ -45245,37 +45169,37 @@
       <c r="AG336" s="5" t="n"/>
       <c r="AH336" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
+          <t>Dossier: reconstruction/dossiers/us-v-1-1-tilton.md; subject of the de Trobriand accusation - ED-59 candidate</t>
         </is>
       </c>
       <c r="AI336" s="5" t="inlineStr">
         <is>
-          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
+          <t>Tilton's bde (18MA/22MA/1MI/118PA); Tilton unwounded</t>
         </is>
       </c>
       <c r="AJ336" s="5" t="inlineStr">
         <is>
-          <t>no primary (negative); ~1,387 compilation hop-flagged ; p11: the 1,387 hop CONFIRMED at the sweep source</t>
+          <t>654 into action (Barnes PRIMARY) vs 'only 474' post-fight (two-scope, flagged not averaged)</t>
         </is>
       </c>
       <c r="AK336" s="5" t="inlineStr">
         <is>
-          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
+          <t>[C +75] stony hill woods S of Rose's house; tablet (3480,3138) OSM-primary; [E drawn j2-03] BARNES' DIV (3394,3301) + Tilton bar (3436,3204) pre-withdrawal; July 3 = LRT garrison relief (interlocks ED-54)</t>
         </is>
       </c>
       <c r="AL336" s="5" t="inlineStr">
         <is>
-          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
+          <t>[C tablet] Baltimore Pike -&gt; Third Corps support after 16:00; [D first-person] withdrawal on personally-reconnoitered Rose-house-axis outflanking (the ED-59 causal core)</t>
         </is>
       </c>
       <c r="AM336" s="5" t="inlineStr">
         <is>
-          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances) ; p11 clock re-read: 'About 2 p. m.' line-of-battle formation = the tablet's 2-3 P.M. (report=tablet pair; profile upgraded)</t>
+          <t>[D] twice repulsed Kershaw's left (wave 2)</t>
         </is>
       </c>
       <c r="AN336" s="5" t="inlineStr">
         <is>
-          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
+          <t>return 125 adopted vs report 109 carried (ED-52); ~all in the wave-2 stand</t>
         </is>
       </c>
       <c r="AO336" s="5" t="n"/>
@@ -45288,12 +45212,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>us-vonamsberg</t>
+          <t>us-torbert</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+          <t>Torbert's New Jersey Brigade (1st Bde, 1st Div, VI Corps)</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -45313,42 +45237,42 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G337" s="2" t="n">
-        <v>1670</v>
+        <v>1320</v>
       </c>
       <c r="H337" s="2" t="n">
-        <v>875</v>
+        <v>1309</v>
       </c>
       <c r="I337" s="3">
         <f>IF(G337=0,0,1-H337/G337)</f>
         <v/>
       </c>
       <c r="J337" s="2" t="n">
-        <v>795</v>
+        <v>11</v>
       </c>
       <c r="K337" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L337" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="M337" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N337" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P337" s="2" t="n">
-        <v>6381.4</v>
+        <v>1875.7</v>
       </c>
       <c r="Q337" s="2" t="n">
-        <v>964.4</v>
+        <v>1875.6</v>
       </c>
       <c r="R337" s="2" t="inlineStr">
         <is>
@@ -45357,11 +45281,11 @@
       </c>
       <c r="S337" s="2" t="inlineStr">
         <is>
-          <t>column/line/skirmish</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="T337" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U337" s="2" t="n">
         <v>0</v>
@@ -45371,7 +45295,7 @@
       </c>
       <c r="W337" s="2" t="inlineStr">
         <is>
-          <t>Amsberg</t>
+          <t>Torbert</t>
         </is>
       </c>
       <c r="X337" s="2" t="inlineStr">
@@ -45381,7 +45305,7 @@
       </c>
       <c r="Y337" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z337" s="2" t="inlineStr">
@@ -45396,12 +45320,12 @@
       </c>
       <c r="AB337" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-3-1</t>
+          <t>reg-us-vi-1-1</t>
         </is>
       </c>
       <c r="AC337" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (command/frame grain)</t>
         </is>
       </c>
       <c r="AD337" s="5" t="n"/>
@@ -45410,55 +45334,55 @@
       <c r="AG337" s="5" t="n"/>
       <c r="AH337" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-3-1-schimmelfennig.md; Dobke 1:30 feeds ED-69</t>
+          <t>Dossier: reconstruction/dossiers/us-vi-1-1-torbert.md</t>
         </is>
       </c>
       <c r="AI337" s="5" t="inlineStr">
         <is>
-          <t>THE CASCADE UP: Howard-&gt;field, Schurz-&gt;corps, Schimmelfennig-&gt;division (cut off in town Jul 1-4), von Amsberg-&gt;brigade at commitment</t>
+          <t>1st Bde 1st Div VI Corps (1/2/3/15 NJ); Brig Gen A.T.A. Torbert; report=tablet</t>
         </is>
       </c>
       <c r="AJ337" s="5" t="inlineStr">
         <is>
-          <t>No brigade primary (negative); B&amp;M-repro 1,670 (hop); 45th NY one-third-assembled fraction; Schurz 'hardly over 6,000' division frame</t>
+          <t>1,663 (106 off/1,557 enl, report-primary itemized)</t>
         </is>
       </c>
       <c r="AK337" s="5" t="inlineStr">
         <is>
-          <t>[C 11:00-11:30] the I-Corps-right deploy (45th NY skirmish line, Dilger rear, 61st OH right); the open-field line under Oak Hill fire; [D ~16:00] the seminary cover halt; the town maze; Cemetery Hill stone fence</t>
+          <t>[C ~16:00] 35mi march, arrived 4pm Jul2; [C] LRT reserve; [C] Jul3 Weikert-House-area center</t>
         </is>
       </c>
       <c r="AL337" s="5" t="inlineStr">
         <is>
-          <t>[C] double-quick through town to deploy; the 16:00 retreat + THE ALLEY-TRAP town leg (~100 escaped); the July 2 night mile to the Culp's stone wall</t>
+          <t>[B] the 35mi march</t>
         </is>
       </c>
       <c r="AM337" s="5" t="inlineStr">
         <is>
-          <t>[C 13:30 early-lean] the flank fire + surrender event (the O'Neal/Iverson front from the XI side); the 157th NY vs Doles episode both-sided; the cross-corps retreat-cover order</t>
+          <t>[D] attested-static, picket only; 11 wounded on picket Jul3</t>
         </is>
       </c>
       <c r="AN337" s="5" t="inlineStr">
         <is>
-          <t>Return p. 183 digit-exact: 112/224/307/54/110 = 807 (rows sum); missing 453 = the town pockets</t>
+          <t>tablet 11w = report's Jul3 picket figure exact; report's broader 1k/17w is a CAMPAIGN total (scope, not conflict)</t>
         </is>
       </c>
       <c r="AO337" s="5" t="n"/>
       <c r="AP337" s="5" t="inlineStr">
         <is>
-          <t>T3 (July 1 grain; full arc T2)</t>
+          <t>T3</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>us-vongilsa</t>
+          <t>us-detrobriand</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+          <t>de Trobriand's Brigade (3rd Bde, 1st Div, III Corps)</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -45478,42 +45402,42 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+          <t>july2-afternoon/july2-evening/july3-afternoon</t>
         </is>
       </c>
       <c r="G338" s="2" t="n">
-        <v>800</v>
+        <v>1387</v>
       </c>
       <c r="H338" s="2" t="n">
-        <v>605</v>
+        <v>895</v>
       </c>
       <c r="I338" s="3">
         <f>IF(G338=0,0,1-H338/G338)</f>
         <v/>
       </c>
       <c r="J338" s="2" t="n">
-        <v>195</v>
+        <v>492</v>
       </c>
       <c r="K338" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L338" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M338" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N338" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O338" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P338" s="2" t="n">
-        <v>4958.5</v>
+        <v>1429.6</v>
       </c>
       <c r="Q338" s="2" t="n">
-        <v>620.1</v>
+        <v>1429</v>
       </c>
       <c r="R338" s="2" t="inlineStr">
         <is>
@@ -45522,11 +45446,11 @@
       </c>
       <c r="S338" s="2" t="inlineStr">
         <is>
-          <t>column/line/routed</t>
+          <t>column/line</t>
         </is>
       </c>
       <c r="T338" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U338" s="2" t="n">
         <v>0</v>
@@ -45536,7 +45460,7 @@
       </c>
       <c r="W338" s="2" t="inlineStr">
         <is>
-          <t>Gilsa</t>
+          <t>Trobriand</t>
         </is>
       </c>
       <c r="X338" s="2" t="inlineStr">
@@ -45561,12 +45485,12 @@
       </c>
       <c r="AB338" s="2" t="inlineStr">
         <is>
-          <t>reg-us-xi-1-1</t>
+          <t>reg-us-iii-1-3</t>
         </is>
       </c>
       <c r="AC338" s="5" t="inlineStr">
         <is>
-          <t>unauthored</t>
+          <t>authored-ok (July 2 mover)</t>
         </is>
       </c>
       <c r="AD338" s="5" t="n"/>
@@ -45575,48 +45499,378 @@
       <c r="AG338" s="5" t="n"/>
       <c r="AH338" s="5" t="inlineStr">
         <is>
-          <t>Dossier: reconstruction/dossiers/us-xi-1-1-vongilsa.md; the which-brigade-broke-first Schurz-vs-Ames conflict carried</t>
+          <t>Dossier: reconstruction/dossiers/us-iii-1-3-detrobriand.md; carries the ED-59-candidate withdrawal accusation vs Tilton/Sweitzer</t>
         </is>
       </c>
       <c r="AI338" s="5" t="inlineStr">
         <is>
-          <t>von Gilsa; NO brigade report (verified negative); 41st NY absent July 1 (arrived ~10 p.m.)</t>
+          <t>de Trobriand's bde (17ME/3MI/5MI/40NY/110PA); Pierce (3MI) w-amp, Pulford (5MI) w, Jones (110PA) w</t>
         </is>
       </c>
       <c r="AJ338" s="5" t="inlineStr">
         <is>
-          <t>OPEN; three-regiment knoll line (structural) ; p11 sweep: B&amp;M-repro 1,118 (hop)</t>
+          <t>no primary (negative); ~1,387 compilation hop-flagged ; p11: the 1,387 hop CONFIRMED at the sweep source</t>
         </is>
       </c>
       <c r="AK338" s="5" t="inlineStr">
         <is>
-          <t>[D+drawn] the knoll north face under the Gordon line; the ECH marker = July 2-3 semantics; no located July 1 brigade marker (negative)</t>
+          <t>[C tablet 'between 2 and 3 P.M.'] the apex-of-the-angle deployment; tablet (3659,3049) OSM delta 0.9m - the register's cleanest agreement; 17th ME wall (3633,2965); [E drawn j2-03] Winslow in the field NE (3734,3141), line bar (3604,2997)</t>
         </is>
       </c>
       <c r="AL338" s="5" t="inlineStr">
         <is>
-          <t>[D ~15:00-15:30 bracket] Barlow's forward tilt; the break under enfilade + frontal charge; through town</t>
+          <t>[D] contraction onto the ravine-wall line; [D trigger] 'our ammunition was just exhausted' when Caldwell relieved (wave-2/3 seam)</t>
         </is>
       </c>
       <c r="AM338" s="5" t="inlineStr">
         <is>
-          <t>the receiving side of the 50-paces fight (attested by the attacker); the corps' capture-mass retreat</t>
+          <t>[D] wave-1 defense vs Anderson (5th MI half-loss stand, both-sided with White's three advances) ; p11 clock re-read: 'About 2 p. m.' line-of-battle formation = the tablet's 2-3 P.M. (report=tablet pair; profile upgraded)</t>
         </is>
       </c>
       <c r="AN338" s="5" t="inlineStr">
         <is>
-          <t>return (p. 182) 527 - 41 NY 75 (July 2-3 only - structural day-split anchor), 54 NY 102, 68 NY 138, 153 Pa 211</t>
+          <t>report=return EXACT 490 (40th NY's 150 tactically belongs to Ward's front - cross-charge noted); split: waves 1-2 dominate</t>
         </is>
       </c>
       <c r="AO338" s="5" t="n"/>
       <c r="AP338" s="5" t="inlineStr">
         <is>
+          <t>T4 full-arc</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>us-vonamsberg</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>von Amsberg's Brigade (1st Bde, 3rd Div, XI Corps — Schimmelfennig's)</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>july1-morning/july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>1670</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="I339" s="3">
+        <f>IF(G339=0,0,1-H339/G339)</f>
+        <v/>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="K339" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L339" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="P339" s="2" t="n">
+        <v>6381.4</v>
+      </c>
+      <c r="Q339" s="2" t="n">
+        <v>964.4</v>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>column/line/skirmish</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Amsberg</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Z339" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AB339" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-3-1</t>
+        </is>
+      </c>
+      <c r="AC339" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
+      <c r="AD339" s="5" t="n"/>
+      <c r="AE339" s="5" t="n"/>
+      <c r="AF339" s="5" t="n"/>
+      <c r="AG339" s="5" t="n"/>
+      <c r="AH339" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-3-1-schimmelfennig.md; Dobke 1:30 feeds ED-69</t>
+        </is>
+      </c>
+      <c r="AI339" s="5" t="inlineStr">
+        <is>
+          <t>THE CASCADE UP: Howard-&gt;field, Schurz-&gt;corps, Schimmelfennig-&gt;division (cut off in town Jul 1-4), von Amsberg-&gt;brigade at commitment</t>
+        </is>
+      </c>
+      <c r="AJ339" s="5" t="inlineStr">
+        <is>
+          <t>No brigade primary (negative); B&amp;M-repro 1,670 (hop); 45th NY one-third-assembled fraction; Schurz 'hardly over 6,000' division frame</t>
+        </is>
+      </c>
+      <c r="AK339" s="5" t="inlineStr">
+        <is>
+          <t>[C 11:00-11:30] the I-Corps-right deploy (45th NY skirmish line, Dilger rear, 61st OH right); the open-field line under Oak Hill fire; [D ~16:00] the seminary cover halt; the town maze; Cemetery Hill stone fence</t>
+        </is>
+      </c>
+      <c r="AL339" s="5" t="inlineStr">
+        <is>
+          <t>[C] double-quick through town to deploy; the 16:00 retreat + THE ALLEY-TRAP town leg (~100 escaped); the July 2 night mile to the Culp's stone wall</t>
+        </is>
+      </c>
+      <c r="AM339" s="5" t="inlineStr">
+        <is>
+          <t>[C 13:30 early-lean] the flank fire + surrender event (the O'Neal/Iverson front from the XI side); the 157th NY vs Doles episode both-sided; the cross-corps retreat-cover order</t>
+        </is>
+      </c>
+      <c r="AN339" s="5" t="inlineStr">
+        <is>
+          <t>Return p. 183 digit-exact: 112/224/307/54/110 = 807 (rows sum); missing 453 = the town pockets</t>
+        </is>
+      </c>
+      <c r="AO339" s="5" t="n"/>
+      <c r="AP339" s="5" t="inlineStr">
+        <is>
+          <t>T3 (July 1 grain; full arc T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>us-vongilsa</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>von Gilsa's Brigade (1st Bde, 1st Div, XI Corps)</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>infantry</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>july1-afternoon/july2-afternoon/july2-evening/july3-afternoon</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I340" s="3">
+        <f>IF(G340=0,0,1-H340/G340)</f>
+        <v/>
+      </c>
+      <c r="J340" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="K340" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P340" s="2" t="n">
+        <v>4958.5</v>
+      </c>
+      <c r="Q340" s="2" t="n">
+        <v>620.1</v>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>column/line/routed</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Gilsa</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="Z340" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>in-build</t>
+        </is>
+      </c>
+      <c r="AB340" s="2" t="inlineStr">
+        <is>
+          <t>reg-us-xi-1-1</t>
+        </is>
+      </c>
+      <c r="AC340" s="5" t="inlineStr">
+        <is>
+          <t>unauthored</t>
+        </is>
+      </c>
+      <c r="AD340" s="5" t="n"/>
+      <c r="AE340" s="5" t="n"/>
+      <c r="AF340" s="5" t="n"/>
+      <c r="AG340" s="5" t="n"/>
+      <c r="AH340" s="5" t="inlineStr">
+        <is>
+          <t>Dossier: reconstruction/dossiers/us-xi-1-1-vongilsa.md; the which-brigade-broke-first Schurz-vs-Ames conflict carried</t>
+        </is>
+      </c>
+      <c r="AI340" s="5" t="inlineStr">
+        <is>
+          <t>von Gilsa; NO brigade report (verified negative); 41st NY absent July 1 (arrived ~10 p.m.)</t>
+        </is>
+      </c>
+      <c r="AJ340" s="5" t="inlineStr">
+        <is>
+          <t>OPEN; three-regiment knoll line (structural) ; p11 sweep: B&amp;M-repro 1,118 (hop)</t>
+        </is>
+      </c>
+      <c r="AK340" s="5" t="inlineStr">
+        <is>
+          <t>[D+drawn] the knoll north face under the Gordon line; the ECH marker = July 2-3 semantics; no located July 1 brigade marker (negative)</t>
+        </is>
+      </c>
+      <c r="AL340" s="5" t="inlineStr">
+        <is>
+          <t>[D ~15:00-15:30 bracket] Barlow's forward tilt; the break under enfilade + frontal charge; through town</t>
+        </is>
+      </c>
+      <c r="AM340" s="5" t="inlineStr">
+        <is>
+          <t>the receiving side of the 50-paces fight (attested by the attacker); the corps' capture-mass retreat</t>
+        </is>
+      </c>
+      <c r="AN340" s="5" t="inlineStr">
+        <is>
+          <t>return (p. 182) 527 - 41 NY 75 (July 2-3 only - structural day-split anchor), 54 NY 102, 68 NY 138, 153 Pa 211</t>
+        </is>
+      </c>
+      <c r="AO340" s="5" t="n"/>
+      <c r="AP340" s="5" t="inlineStr">
+        <is>
           <t>T2 (honestly thin)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP338"/>
+  <autoFilter ref="A1:AP340"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -16491,23 +16491,23 @@
         <v>2294</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>1185</v>
+        <v>1378</v>
       </c>
       <c r="I140" s="3">
         <f>IF(G140=0,0,1-H140/G140)</f>
         <v/>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1109</v>
+        <v>916</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>21</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N140" s="2" t="n">
         <v>0</v>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="Y140" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="Z140" s="2" t="inlineStr">
@@ -17481,14 +17481,14 @@
         <v>1600</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>1180</v>
+        <v>1139</v>
       </c>
       <c r="I146" s="3">
         <f>IF(G146=0,0,1-H146/G146)</f>
         <v/>
       </c>
       <c r="J146" s="2" t="n">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>16</v>
@@ -18636,14 +18636,14 @@
         <v>1100</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="I153" s="3">
         <f>IF(G153=0,0,1-H153/G153)</f>
         <v/>
       </c>
       <c r="J153" s="2" t="n">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>14</v>
@@ -19956,14 +19956,14 @@
         <v>1700</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>1020</v>
+        <v>998</v>
       </c>
       <c r="I161" s="3">
         <f>IF(G161=0,0,1-H161/G161)</f>
         <v/>
       </c>
       <c r="J161" s="2" t="n">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>15</v>
@@ -20121,14 +20121,14 @@
         <v>1450</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="I162" s="3">
         <f>IF(G162=0,0,1-H162/G162)</f>
         <v/>
       </c>
       <c r="J162" s="2" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>13</v>
@@ -39469,14 +39469,14 @@
         <v>1400</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>1400</v>
+        <v>1261</v>
       </c>
       <c r="I302" s="3">
         <f>IF(G302=0,0,1-H302/G302)</f>
         <v/>
       </c>
       <c r="J302" s="2" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="K302" s="2" t="n">
         <v>13</v>
@@ -39964,14 +39964,14 @@
         <v>1170</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>1170</v>
+        <v>891</v>
       </c>
       <c r="I305" s="3">
         <f>IF(G305=0,0,1-H305/G305)</f>
         <v/>
       </c>
       <c r="J305" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K305" s="2" t="n">
         <v>12</v>
@@ -41779,14 +41779,14 @@
         <v>1350</v>
       </c>
       <c r="H316" s="2" t="n">
-        <v>1125</v>
+        <v>1007</v>
       </c>
       <c r="I316" s="3">
         <f>IF(G316=0,0,1-H316/G316)</f>
         <v/>
       </c>
       <c r="J316" s="2" t="n">
-        <v>225</v>
+        <v>343</v>
       </c>
       <c r="K316" s="2" t="n">
         <v>14</v>
@@ -42109,14 +42109,14 @@
         <v>600</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>600</v>
+        <v>502</v>
       </c>
       <c r="I318" s="3">
         <f>IF(G318=0,0,1-H318/G318)</f>
         <v/>
       </c>
       <c r="J318" s="2" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K318" s="2" t="n">
         <v>13</v>
@@ -42604,14 +42604,14 @@
         <v>1650</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>1650</v>
+        <v>1476</v>
       </c>
       <c r="I321" s="3">
         <f>IF(G321=0,0,1-H321/G321)</f>
         <v/>
       </c>
       <c r="J321" s="2" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K321" s="2" t="n">
         <v>14</v>
@@ -43099,14 +43099,14 @@
         <v>1755</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>1755</v>
+        <v>1675</v>
       </c>
       <c r="I324" s="3">
         <f>IF(G324=0,0,1-H324/G324)</f>
         <v/>
       </c>
       <c r="J324" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K324" s="2" t="n">
         <v>14</v>
@@ -44254,14 +44254,14 @@
         <v>1770</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>1770</v>
+        <v>1696</v>
       </c>
       <c r="I331" s="3">
         <f>IF(G331=0,0,1-H331/G331)</f>
         <v/>
       </c>
       <c r="J331" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K331" s="2" t="n">
         <v>14</v>
@@ -44320,7 +44320,7 @@
       </c>
       <c r="Z331" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="AA331" s="2" t="inlineStr">

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -10746,19 +10746,19 @@
         <v>158</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P97" s="2" t="n">
         <v>2622.2</v>
@@ -11996,19 +11996,19 @@
         <v>158</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P107" s="2" t="n">
         <v>2469.8</v>
@@ -12746,19 +12746,19 @@
         <v>158</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P113" s="2" t="n">
         <v>2404.4</v>
@@ -12871,19 +12871,19 @@
         <v>158</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P114" s="2" t="n">
         <v>2561.1</v>
@@ -14121,19 +14121,19 @@
         <v>74</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P124" s="2" t="n">
         <v>735.6</v>
@@ -14246,19 +14246,19 @@
         <v>74</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P125" s="2" t="n">
         <v>877.5</v>
@@ -15000,19 +15000,19 @@
         <v>148</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>8</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P131" s="2" t="n">
         <v>4964.9</v>
@@ -15841,19 +15841,19 @@
         <v>1732</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P136" s="2" t="n">
         <v>7023</v>
@@ -17946,19 +17946,19 @@
         <v>1005</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L149" s="2" t="n">
         <v>8</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P149" s="2" t="n">
         <v>7059.9</v>

--- a/docs/reconstruction/audit/unit-master-table.xlsx
+++ b/docs/reconstruction/audit/unit-master-table.xlsx
@@ -10871,19 +10871,19 @@
         <v>146</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P98" s="2" t="n">
         <v>2477.9</v>
@@ -10996,19 +10996,19 @@
         <v>136</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P99" s="2" t="n">
         <v>2362.2</v>
@@ -11121,19 +11121,19 @@
         <v>135</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P100" s="2" t="n">
         <v>2431.2</v>
@@ -11246,19 +11246,19 @@
         <v>238</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P101" s="2" t="n">
         <v>2690.5</v>
@@ -11621,19 +11621,19 @@
         <v>136</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P104" s="2" t="n">
         <v>2321.5</v>
@@ -11746,19 +11746,19 @@
         <v>146</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P105" s="2" t="n">
         <v>2695.9</v>
@@ -11871,19 +11871,19 @@
         <v>146</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P106" s="2" t="n">
         <v>2568.8</v>
@@ -12371,19 +12371,19 @@
         <v>238</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P110" s="2" t="n">
         <v>2784.1</v>
@@ -12496,19 +12496,19 @@
         <v>146</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P111" s="2" t="n">
         <v>2545.4</v>
@@ -12996,19 +12996,19 @@
         <v>238</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P115" s="2" t="n">
         <v>2643.7</v>
@@ -13371,19 +13371,19 @@
         <v>238</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P118" s="2" t="n">
         <v>2791.4</v>
@@ -13496,19 +13496,19 @@
         <v>136</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P119" s="2" t="n">
         <v>2447.6</v>
@@ -13621,19 +13621,19 @@
         <v>135</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P120" s="2" t="n">
         <v>2350.7</v>
@@ -13746,19 +13746,19 @@
         <v>146</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P121" s="2" t="n">
         <v>2458</v>
@@ -13996,19 +13996,19 @@
         <v>238</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P123" s="2" t="n">
         <v>2852.1</v>
@@ -14835,19 +14835,19 @@
         <v>1191</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P130" s="2" t="n">
         <v>2593.7</v>
@@ -15330,19 +15330,19 @@
         <v>677</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>11</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P133" s="2" t="n">
         <v>6538.5</v>
@@ -15676,19 +15676,19 @@
         <v>731</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P135" s="2" t="n">
         <v>2458</v>
